--- a/archivos/BD_Dashboard.xlsx
+++ b/archivos/BD_Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mexscitum-my.sharepoint.com/personal/erik_torres_scitum_com_mx/Documents/Documentos/Proyectos/AEROMEXICO/17471 - PA ION/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="56" documentId="11_F25DC773A252ABDACC1048E8499F6DC65BDE58F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8259406E-5403-46E6-A420-202EA4EB1F48}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="11_F25DC773A252ABDACC1048E8499F6DC65BDE58F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B72C6E12-F850-4A5D-A893-08FC509E685B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
     <author>Erik Alejandro Torres Piña</author>
   </authors>
   <commentList>
-    <comment ref="F41" authorId="0" shapeId="0" xr:uid="{BCD4C578-7D36-426A-8138-0CC5D6A72D93}">
+    <comment ref="F41" authorId="0" shapeId="0" xr:uid="{3AD437B5-2F1A-46A9-A39C-8A16D59FD71D}">
       <text>
         <r>
           <rPr>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="327">
   <si>
     <t>TIER</t>
   </si>
@@ -131,9 +131,6 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>TBD</t>
-  </si>
-  <si>
     <t>Listo para programar</t>
   </si>
   <si>
@@ -1037,26 +1034,36 @@
     <t>AWS East</t>
   </si>
   <si>
-    <t>22, 23 o 25 de junio</t>
-  </si>
-  <si>
-    <t>25 o 26 de junio</t>
-  </si>
-  <si>
-    <t>23 o 26 de junio</t>
-  </si>
-  <si>
     <t>Aeroméxico reporta que no recibió el equipo. SCITUM levantó el reporte. Numero de reporte DHL: CS62301998 Ejecutivo DHL seguimiento de reporte: Jesus Hernández. 25-jun-2026 AMX confirma recepción de equipo</t>
   </si>
   <si>
-    <t>Total</t>
+    <t>Esquema
+Operativo</t>
+  </si>
+  <si>
+    <t>HA</t>
+  </si>
+  <si>
+    <t>Programada</t>
+  </si>
+  <si>
+    <t>se necesita informar con 48hrs de anticipación para solicitar al aeropuerto el acceso a cuarto de comunicación, compartir nombre del técnico</t>
+  </si>
+  <si>
+    <t>no requiere de permisos especiales solo tienen que anunciarse con la gerente Martha Liliana Gil.</t>
+  </si>
+  <si>
+    <t>No requieren de permisos especiales solo tendrán que anunciarse con Jose Garden</t>
+  </si>
+  <si>
+    <t>Stand Alone</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1114,15 +1121,8 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Century Gothic"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1144,12 +1144,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF7C7AC"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -1181,7 +1175,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1227,15 +1221,6 @@
     </xf>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1334,7 +1319,7 @@
     </dxf>
     <dxf>
       <font>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
       </font>
       <fill>
         <patternFill>
@@ -1354,11 +1339,11 @@
     </dxf>
     <dxf>
       <font>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="3" tint="0.749961851863155"/>
+          <bgColor rgb="FFA6C9EC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1368,13 +1353,13 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
+          <bgColor rgb="FFFBE2D5"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
       </font>
       <fill>
         <patternFill>
@@ -1384,7 +1369,7 @@
     </dxf>
     <dxf>
       <font>
-        <color theme="0"/>
+        <color rgb="FFFFFFFF"/>
       </font>
       <fill>
         <patternFill>
@@ -1394,17 +1379,17 @@
     </dxf>
     <dxf>
       <font>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+          <bgColor rgb="FFD0D0D0"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <color theme="1"/>
+        <color rgb="FF000000"/>
       </font>
       <fill>
         <patternFill>
@@ -1414,7 +1399,7 @@
     </dxf>
     <dxf>
       <font>
-        <color theme="0"/>
+        <color rgb="FFFFFFFF"/>
       </font>
       <fill>
         <patternFill>
@@ -1583,10 +1568,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1855,7 +1836,7 @@
   <sheetPr>
     <tabColor theme="5" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:N174"/>
+  <dimension ref="A1:O173"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.140625" bestFit="1" customWidth="1"/>
@@ -1865,10 +1846,9 @@
     <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="44.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1888,31 +1868,34 @@
         <v>5</v>
       </c>
       <c r="G1" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -1924,27 +1907,32 @@
         <v>15</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="H2" s="7">
         <v>46210</v>
       </c>
-      <c r="H2" s="6"/>
-      <c r="I2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="10">
+        <v>0.625</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>322</v>
+      </c>
       <c r="L2" s="6"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M2" s="6"/>
+      <c r="N2" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="O2" s="8"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -1956,27 +1944,32 @@
         <v>15</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" s="2">
-        <v>46192</v>
-      </c>
-      <c r="H3" s="6"/>
-      <c r="I3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="6"/>
+      <c r="G3" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="H3" s="7">
+        <v>46211</v>
+      </c>
+      <c r="I3" s="6"/>
+      <c r="J3" s="10">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>322</v>
+      </c>
       <c r="L3" s="6"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M3" s="6"/>
+      <c r="N3" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="O3" s="8"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>1</v>
       </c>
@@ -1991,26 +1984,31 @@
         <v>209</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="H4" s="6"/>
-      <c r="I4" s="3">
-        <v>0.375</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="N4" s="8"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G4" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="H4" s="7">
+        <v>46204</v>
+      </c>
+      <c r="I4" s="6"/>
+      <c r="J4" s="10">
+        <v>0.875</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="L4" s="7">
+        <v>46182</v>
+      </c>
+      <c r="M4" s="7"/>
+      <c r="N4" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="O4" s="8"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>1</v>
       </c>
@@ -2022,29 +2020,28 @@
         <v>15</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="2">
-        <v>46197</v>
-      </c>
-      <c r="H5" s="6"/>
-      <c r="I5" s="3">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="K5" s="7">
-        <v>46182</v>
-      </c>
-      <c r="L5" s="7"/>
-      <c r="M5" s="8"/>
-      <c r="N5" s="8"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="H5" s="1"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="O5" s="8"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>1</v>
       </c>
@@ -2053,62 +2050,68 @@
         <v>14</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" s="6"/>
+        <v>29</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
-      <c r="J6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="K6" s="7">
+      <c r="J6" s="6"/>
+      <c r="K6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L6" s="7">
         <v>46189</v>
       </c>
-      <c r="L6" s="6">
+      <c r="M6" s="6">
         <v>1.1000000000000001</v>
       </c>
-      <c r="M6" s="8"/>
       <c r="N6" s="8"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O6" s="8"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>2</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>15</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="G7" s="6"/>
+        <v>33</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
-      <c r="J7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="K7" s="7">
+      <c r="J7" s="6"/>
+      <c r="K7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L7" s="7">
         <v>46189</v>
       </c>
-      <c r="L7" s="6">
+      <c r="M7" s="6">
         <v>1.3</v>
       </c>
-      <c r="M7" s="8"/>
       <c r="N7" s="8"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O7" s="8"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>3</v>
       </c>
@@ -2117,30 +2120,33 @@
         <v>14</v>
       </c>
       <c r="D8" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="F8" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8" s="6"/>
+      <c r="G8" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
-      <c r="J8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="K8" s="7">
+      <c r="J8" s="6"/>
+      <c r="K8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L8" s="7">
         <v>46189</v>
       </c>
-      <c r="L8" s="6">
+      <c r="M8" s="6">
         <v>1.2</v>
       </c>
-      <c r="M8" s="8"/>
       <c r="N8" s="8"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O8" s="8"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>1</v>
       </c>
@@ -2152,31 +2158,30 @@
         <v>15</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="H9" s="6"/>
-      <c r="I9" s="3">
-        <v>0.375</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="K9" s="7">
+        <v>23</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L9" s="7">
         <v>46182</v>
       </c>
-      <c r="L9" s="7"/>
-      <c r="M9" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="N9" s="8"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M9" s="7"/>
+      <c r="N9" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="O9" s="8"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>1</v>
       </c>
@@ -2188,31 +2193,30 @@
         <v>15</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F10" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="H10" s="1"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L10" s="7">
+        <v>46182</v>
+      </c>
+      <c r="M10" s="7"/>
+      <c r="N10" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="H10" s="6"/>
-      <c r="I10" s="3">
-        <v>0.375</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="K10" s="7">
-        <v>46182</v>
-      </c>
-      <c r="L10" s="7"/>
-      <c r="M10" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="N10" s="8"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O10" s="8"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>2</v>
       </c>
@@ -2224,27 +2228,28 @@
         <v>15</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="3">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="K11" s="6"/>
+        <v>39</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="H11" s="2"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="6" t="s">
+        <v>18</v>
+      </c>
       <c r="L11" s="6"/>
-      <c r="M11" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="N11" s="8"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M11" s="6"/>
+      <c r="N11" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="O11" s="8"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>1</v>
       </c>
@@ -2253,30 +2258,33 @@
         <v>14</v>
       </c>
       <c r="D12" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="F12" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G12" s="6"/>
+      <c r="G12" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
-      <c r="J12" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K12" s="7">
+      <c r="J12" s="6"/>
+      <c r="K12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="7">
         <v>46182</v>
       </c>
-      <c r="L12" s="7"/>
-      <c r="M12" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="N12" s="8"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M12" s="7"/>
+      <c r="N12" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="O12" s="8"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>3</v>
       </c>
@@ -2285,30 +2293,33 @@
         <v>14</v>
       </c>
       <c r="D13" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="F13" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G13" s="6"/>
+      <c r="G13" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
-      <c r="J13" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K13" s="7">
+      <c r="J13" s="6"/>
+      <c r="K13" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="7">
         <v>46189</v>
       </c>
-      <c r="L13" s="6">
+      <c r="M13" s="6">
         <v>1.4</v>
       </c>
-      <c r="M13" s="8"/>
       <c r="N13" s="8"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O13" s="8"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>3</v>
       </c>
@@ -2317,30 +2328,33 @@
         <v>14</v>
       </c>
       <c r="D14" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="F14" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G14" s="6"/>
+      <c r="G14" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
-      <c r="J14" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K14" s="7">
+      <c r="J14" s="6"/>
+      <c r="K14" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="7">
         <v>46189</v>
       </c>
-      <c r="L14" s="6">
+      <c r="M14" s="6">
         <v>1.5</v>
       </c>
-      <c r="M14" s="8"/>
       <c r="N14" s="8"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O14" s="8"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>3</v>
       </c>
@@ -2349,30 +2363,33 @@
         <v>14</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G15" s="6"/>
+        <v>38</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H15" s="6"/>
       <c r="I15" s="6"/>
-      <c r="J15" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K15" s="7">
+      <c r="J15" s="6"/>
+      <c r="K15" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="7">
         <v>46189</v>
       </c>
-      <c r="L15" s="6">
+      <c r="M15" s="6">
         <v>1.6</v>
       </c>
-      <c r="M15" s="8"/>
       <c r="N15" s="8"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O15" s="8"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>1</v>
       </c>
@@ -2381,28 +2398,31 @@
         <v>14</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="G16" s="6"/>
+        <v>56</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
-      <c r="J16" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6">
+      <c r="J16" s="6"/>
+      <c r="K16" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6">
         <v>2.1</v>
       </c>
-      <c r="M16" s="8"/>
       <c r="N16" s="8"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O16" s="8"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>1</v>
       </c>
@@ -2414,25 +2434,28 @@
         <v>15</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="G17" s="6"/>
+        <v>57</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H17" s="6"/>
       <c r="I17" s="6"/>
-      <c r="J17" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6">
+      <c r="J17" s="6"/>
+      <c r="K17" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6">
         <v>2.8</v>
       </c>
-      <c r="M17" s="8"/>
       <c r="N17" s="8"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O17" s="8"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>1</v>
       </c>
@@ -2441,28 +2464,31 @@
         <v>14</v>
       </c>
       <c r="D18" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F18" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E18" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="G18" s="6"/>
+      <c r="G18" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H18" s="6"/>
       <c r="I18" s="6"/>
-      <c r="J18" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="K18" s="6"/>
-      <c r="L18" s="15">
+      <c r="J18" s="6"/>
+      <c r="K18" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="L18" s="6"/>
+      <c r="M18" s="15">
         <v>2.1</v>
       </c>
-      <c r="M18" s="8"/>
       <c r="N18" s="8"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O18" s="8"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>1</v>
       </c>
@@ -2471,28 +2497,31 @@
         <v>14</v>
       </c>
       <c r="D19" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="F19" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="E19" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="G19" s="6"/>
+      <c r="G19" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H19" s="6"/>
       <c r="I19" s="6"/>
-      <c r="J19" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6">
+      <c r="J19" s="6"/>
+      <c r="K19" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6">
         <v>2.2999999999999998</v>
       </c>
-      <c r="M19" s="8"/>
       <c r="N19" s="8"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O19" s="8"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>2</v>
       </c>
@@ -2501,28 +2530,31 @@
         <v>14</v>
       </c>
       <c r="D20" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="F20" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="E20" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="G20" s="6"/>
+      <c r="G20" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
-      <c r="J20" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6">
+      <c r="J20" s="6"/>
+      <c r="K20" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6">
         <v>2.5</v>
       </c>
-      <c r="M20" s="8"/>
       <c r="N20" s="8"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O20" s="8"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>2</v>
       </c>
@@ -2531,28 +2563,31 @@
         <v>14</v>
       </c>
       <c r="D21" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="F21" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E21" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="G21" s="6"/>
+      <c r="G21" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
-      <c r="J21" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6">
+      <c r="J21" s="6"/>
+      <c r="K21" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="L21" s="6"/>
+      <c r="M21" s="6">
         <v>2.2000000000000002</v>
       </c>
-      <c r="M21" s="8"/>
       <c r="N21" s="8"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O21" s="8"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>3</v>
       </c>
@@ -2561,28 +2596,31 @@
         <v>14</v>
       </c>
       <c r="D22" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="F22" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="E22" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="G22" s="6"/>
+      <c r="G22" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H22" s="6"/>
       <c r="I22" s="6"/>
-      <c r="J22" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6">
+      <c r="J22" s="6"/>
+      <c r="K22" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6">
         <v>2.7</v>
       </c>
-      <c r="M22" s="8"/>
       <c r="N22" s="8"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O22" s="8"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>3</v>
       </c>
@@ -2591,28 +2629,31 @@
         <v>14</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="G23" s="6"/>
+        <v>68</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>
-      <c r="J23" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6">
+      <c r="J23" s="6"/>
+      <c r="K23" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6">
         <v>2.6</v>
       </c>
-      <c r="M23" s="8"/>
       <c r="N23" s="8"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O23" s="8"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>3</v>
       </c>
@@ -2621,28 +2662,31 @@
         <v>14</v>
       </c>
       <c r="D24" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="F24" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="E24" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="G24" s="6"/>
+      <c r="G24" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
-      <c r="J24" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6">
+      <c r="J24" s="6"/>
+      <c r="K24" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6">
         <v>2.9</v>
       </c>
-      <c r="M24" s="8"/>
       <c r="N24" s="8"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O24" s="8"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>3</v>
       </c>
@@ -2651,28 +2695,31 @@
         <v>14</v>
       </c>
       <c r="D25" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="F25" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="E25" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="G25" s="6"/>
+      <c r="G25" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H25" s="6"/>
       <c r="I25" s="6"/>
-      <c r="J25" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="K25" s="6"/>
-      <c r="L25" s="6">
+      <c r="J25" s="6"/>
+      <c r="K25" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6">
         <v>2.4</v>
       </c>
-      <c r="M25" s="8"/>
       <c r="N25" s="8"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O25" s="8"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>1</v>
       </c>
@@ -2681,28 +2728,31 @@
         <v>14</v>
       </c>
       <c r="D26" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="F26" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="E26" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="G26" s="6"/>
+      <c r="G26" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H26" s="6"/>
       <c r="I26" s="6"/>
-      <c r="J26" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="K26" s="6"/>
-      <c r="L26" s="6">
+      <c r="J26" s="6"/>
+      <c r="K26" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6">
         <v>3.1</v>
       </c>
-      <c r="M26" s="8"/>
       <c r="N26" s="8"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O26" s="8"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>3</v>
       </c>
@@ -2711,28 +2761,31 @@
         <v>14</v>
       </c>
       <c r="D27" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="F27" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E27" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="G27" s="6"/>
+      <c r="G27" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H27" s="6"/>
       <c r="I27" s="6"/>
-      <c r="J27" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="K27" s="6"/>
-      <c r="L27" s="6">
+      <c r="J27" s="6"/>
+      <c r="K27" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="L27" s="6"/>
+      <c r="M27" s="6">
         <v>3.2</v>
       </c>
-      <c r="M27" s="8"/>
       <c r="N27" s="8"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O27" s="8"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>3</v>
       </c>
@@ -2744,27 +2797,30 @@
         <v>15</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F28" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="H28" s="9"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="L28" s="6"/>
+      <c r="M28" s="6">
+        <v>3.3</v>
+      </c>
+      <c r="N28" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="G28" s="9"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="K28" s="6"/>
-      <c r="L28" s="6">
-        <v>3.3</v>
-      </c>
-      <c r="M28" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="N28" s="8"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O28" s="8"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>2</v>
       </c>
@@ -2776,27 +2832,30 @@
         <v>15</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="G29" s="9"/>
-      <c r="H29" s="6"/>
+        <v>47</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="H29" s="9"/>
       <c r="I29" s="6"/>
-      <c r="J29" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="K29" s="6"/>
-      <c r="L29" s="6">
+      <c r="J29" s="6"/>
+      <c r="K29" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="L29" s="6"/>
+      <c r="M29" s="6">
         <v>3.4</v>
       </c>
-      <c r="M29" s="8" t="s">
-        <v>317</v>
-      </c>
-      <c r="N29" s="8"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N29" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="O29" s="8"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>3</v>
       </c>
@@ -2808,25 +2867,28 @@
         <v>15</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F30" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="H30" s="9"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="L30" s="6"/>
+      <c r="M30" s="6"/>
+      <c r="N30" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="G30" s="9"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="K30" s="6"/>
-      <c r="L30" s="6"/>
-      <c r="M30" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="N30" s="8"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O30" s="8"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>2</v>
       </c>
@@ -2838,25 +2900,28 @@
         <v>15</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F31" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="H31" s="9"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="G31" s="9"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="K31" s="6"/>
-      <c r="L31" s="6"/>
-      <c r="M31" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="N31" s="8"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O31" s="8"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>3</v>
       </c>
@@ -2868,53 +2933,59 @@
         <v>15</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F32" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="H32" s="9"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="10"/>
+      <c r="K32" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="L32" s="6"/>
+      <c r="M32" s="6"/>
+      <c r="N32" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="G32" s="9"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="K32" s="6"/>
-      <c r="L32" s="6"/>
-      <c r="M32" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="N32" s="8"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O32" s="8"/>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>1</v>
       </c>
       <c r="B33" s="6"/>
       <c r="C33" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D33" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="F33" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E33" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="G33" s="9"/>
-      <c r="H33" s="6"/>
+      <c r="G33" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="H33" s="9"/>
       <c r="I33" s="6"/>
-      <c r="J33" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="K33" s="6"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="L33" s="6"/>
-      <c r="M33" s="8"/>
+      <c r="M33" s="6"/>
       <c r="N33" s="8"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O33" s="8"/>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>1</v>
       </c>
@@ -2923,2632 +2994,2914 @@
         <v>14</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="G34" s="6"/>
+        <v>50</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H34" s="6"/>
       <c r="I34" s="6"/>
-      <c r="J34" s="6" t="s">
+      <c r="J34" s="6"/>
+      <c r="K34" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="L34" s="6"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="K34" s="6"/>
-      <c r="L34" s="6"/>
-      <c r="M34" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="N34" s="8"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O34" s="8"/>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>0</v>
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="F35" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="D35" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="G35" s="6"/>
+      <c r="G35" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H35" s="6"/>
       <c r="I35" s="6"/>
-      <c r="J35" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K35" s="6"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L35" s="6"/>
-      <c r="M35" s="8"/>
+      <c r="M35" s="6"/>
       <c r="N35" s="8"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O35" s="8"/>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>0</v>
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="G36" s="6"/>
+        <v>76</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H36" s="6"/>
       <c r="I36" s="6"/>
-      <c r="J36" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K36" s="6"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L36" s="6"/>
-      <c r="M36" s="8"/>
+      <c r="M36" s="6"/>
       <c r="N36" s="8"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O36" s="8"/>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>0</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="G37" s="6"/>
+        <v>77</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H37" s="6"/>
       <c r="I37" s="6"/>
-      <c r="J37" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K37" s="6"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L37" s="6"/>
-      <c r="M37" s="8"/>
+      <c r="M37" s="6"/>
       <c r="N37" s="8"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O37" s="8"/>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>0</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="G38" s="6"/>
+        <v>79</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H38" s="6"/>
       <c r="I38" s="6"/>
-      <c r="J38" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K38" s="6"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L38" s="6"/>
-      <c r="M38" s="8"/>
+      <c r="M38" s="6"/>
       <c r="N38" s="8"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O38" s="8"/>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>0</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="G39" s="6"/>
+        <v>80</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H39" s="6"/>
       <c r="I39" s="6"/>
-      <c r="J39" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K39" s="6"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L39" s="6"/>
-      <c r="M39" s="8"/>
+      <c r="M39" s="6"/>
       <c r="N39" s="8"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O39" s="8"/>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>0</v>
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G40" s="6"/>
+        <v>81</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H40" s="6"/>
       <c r="I40" s="6"/>
-      <c r="J40" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K40" s="6"/>
+      <c r="J40" s="6"/>
+      <c r="K40" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L40" s="6"/>
-      <c r="M40" s="8"/>
+      <c r="M40" s="6"/>
       <c r="N40" s="8"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O40" s="8"/>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
         <v>0</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="F41" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="D41" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="E41" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="F41" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="G41" s="11"/>
+      <c r="G41" s="11" t="s">
+        <v>321</v>
+      </c>
       <c r="H41" s="11"/>
       <c r="I41" s="11"/>
-      <c r="J41" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K41" s="11"/>
+      <c r="J41" s="11"/>
+      <c r="K41" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L41" s="11"/>
-      <c r="M41" s="12"/>
+      <c r="M41" s="11"/>
       <c r="N41" s="12"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O41" s="12"/>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>0</v>
       </c>
       <c r="B42" s="6"/>
       <c r="C42" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="G42" s="6"/>
+        <v>84</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H42" s="6"/>
       <c r="I42" s="6"/>
-      <c r="J42" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K42" s="6"/>
+      <c r="J42" s="6"/>
+      <c r="K42" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L42" s="6"/>
-      <c r="M42" s="8"/>
+      <c r="M42" s="6"/>
       <c r="N42" s="8"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O42" s="8"/>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>1</v>
       </c>
       <c r="B43" s="6"/>
       <c r="C43" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="F43" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="D43" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="G43" s="6"/>
+      <c r="G43" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H43" s="6"/>
       <c r="I43" s="6"/>
-      <c r="J43" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K43" s="6"/>
+      <c r="J43" s="6"/>
+      <c r="K43" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L43" s="6"/>
-      <c r="M43" s="8"/>
+      <c r="M43" s="6"/>
       <c r="N43" s="8"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O43" s="8"/>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>1</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="G44" s="6"/>
+        <v>87</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H44" s="6"/>
       <c r="I44" s="6"/>
-      <c r="J44" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K44" s="6"/>
+      <c r="J44" s="6"/>
+      <c r="K44" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L44" s="6"/>
-      <c r="M44" s="8"/>
+      <c r="M44" s="6"/>
       <c r="N44" s="8"/>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O44" s="8"/>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>1</v>
       </c>
       <c r="B45" s="6"/>
       <c r="C45" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="G45" s="6"/>
+        <v>88</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H45" s="6"/>
       <c r="I45" s="6"/>
-      <c r="J45" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K45" s="6"/>
+      <c r="J45" s="6"/>
+      <c r="K45" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L45" s="6"/>
-      <c r="M45" s="8"/>
+      <c r="M45" s="6"/>
       <c r="N45" s="8"/>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O45" s="8"/>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>1</v>
       </c>
       <c r="B46" s="6"/>
       <c r="C46" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="G46" s="6"/>
+        <v>89</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H46" s="6"/>
       <c r="I46" s="6"/>
-      <c r="J46" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K46" s="6"/>
+      <c r="J46" s="6"/>
+      <c r="K46" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L46" s="6"/>
-      <c r="M46" s="8"/>
+      <c r="M46" s="6"/>
       <c r="N46" s="8"/>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O46" s="8"/>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>1</v>
       </c>
       <c r="B47" s="6"/>
       <c r="C47" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="G47" s="6"/>
+        <v>90</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H47" s="6"/>
       <c r="I47" s="6"/>
-      <c r="J47" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K47" s="6"/>
+      <c r="J47" s="6"/>
+      <c r="K47" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L47" s="6"/>
-      <c r="M47" s="8"/>
+      <c r="M47" s="6"/>
       <c r="N47" s="8"/>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O47" s="8"/>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>1</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="G48" s="6"/>
+        <v>91</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H48" s="6"/>
       <c r="I48" s="6"/>
-      <c r="J48" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K48" s="6"/>
+      <c r="J48" s="6"/>
+      <c r="K48" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L48" s="6"/>
-      <c r="M48" s="8"/>
+      <c r="M48" s="6"/>
       <c r="N48" s="8"/>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O48" s="8"/>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>1</v>
       </c>
       <c r="B49" s="6"/>
       <c r="C49" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="G49" s="6"/>
+        <v>92</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H49" s="6"/>
       <c r="I49" s="6"/>
-      <c r="J49" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K49" s="6"/>
+      <c r="J49" s="6"/>
+      <c r="K49" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L49" s="6"/>
-      <c r="M49" s="8"/>
+      <c r="M49" s="6"/>
       <c r="N49" s="8"/>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O49" s="8"/>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>1</v>
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="G50" s="6"/>
+        <v>93</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H50" s="6"/>
       <c r="I50" s="6"/>
-      <c r="J50" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K50" s="6"/>
+      <c r="J50" s="6"/>
+      <c r="K50" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L50" s="6"/>
-      <c r="M50" s="8"/>
+      <c r="M50" s="6"/>
       <c r="N50" s="8"/>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O50" s="8"/>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>1</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="G51" s="6"/>
+        <v>93</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H51" s="6"/>
       <c r="I51" s="6"/>
-      <c r="J51" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K51" s="6"/>
+      <c r="J51" s="6"/>
+      <c r="K51" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L51" s="6"/>
-      <c r="M51" s="8"/>
+      <c r="M51" s="6"/>
       <c r="N51" s="8"/>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O51" s="8"/>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>1</v>
       </c>
       <c r="B52" s="6"/>
       <c r="C52" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="G52" s="6"/>
+        <v>94</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H52" s="6"/>
       <c r="I52" s="6"/>
-      <c r="J52" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K52" s="6"/>
+      <c r="J52" s="6"/>
+      <c r="K52" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L52" s="6"/>
-      <c r="M52" s="8"/>
+      <c r="M52" s="6"/>
       <c r="N52" s="8"/>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O52" s="8"/>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>1</v>
       </c>
       <c r="B53" s="6"/>
       <c r="C53" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="G53" s="6"/>
+        <v>95</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H53" s="6"/>
       <c r="I53" s="6"/>
-      <c r="J53" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K53" s="6"/>
+      <c r="J53" s="6"/>
+      <c r="K53" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L53" s="6"/>
-      <c r="M53" s="8"/>
+      <c r="M53" s="6"/>
       <c r="N53" s="8"/>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O53" s="8"/>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
         <v>1</v>
       </c>
       <c r="B54" s="6"/>
       <c r="C54" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="G54" s="6"/>
+        <v>95</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H54" s="6"/>
       <c r="I54" s="6"/>
-      <c r="J54" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K54" s="6"/>
+      <c r="J54" s="6"/>
+      <c r="K54" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L54" s="6"/>
-      <c r="M54" s="8"/>
+      <c r="M54" s="6"/>
       <c r="N54" s="8"/>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O54" s="8"/>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
         <v>1</v>
       </c>
       <c r="B55" s="6"/>
       <c r="C55" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="G55" s="6"/>
+        <v>96</v>
+      </c>
+      <c r="G55" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H55" s="6"/>
       <c r="I55" s="6"/>
-      <c r="J55" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K55" s="6"/>
+      <c r="J55" s="6"/>
+      <c r="K55" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L55" s="6"/>
-      <c r="M55" s="8"/>
+      <c r="M55" s="6"/>
       <c r="N55" s="8"/>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O55" s="8"/>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
         <v>1</v>
       </c>
       <c r="B56" s="6"/>
       <c r="C56" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="G56" s="6"/>
+        <v>97</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H56" s="6"/>
       <c r="I56" s="6"/>
-      <c r="J56" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K56" s="6"/>
+      <c r="J56" s="6"/>
+      <c r="K56" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L56" s="6"/>
-      <c r="M56" s="8"/>
+      <c r="M56" s="6"/>
       <c r="N56" s="8"/>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O56" s="8"/>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
         <v>1</v>
       </c>
       <c r="B57" s="6"/>
       <c r="C57" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="F57" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="D57" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="F57" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G57" s="6"/>
+      <c r="G57" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H57" s="6"/>
       <c r="I57" s="6"/>
-      <c r="J57" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K57" s="6"/>
+      <c r="J57" s="6"/>
+      <c r="K57" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L57" s="6"/>
-      <c r="M57" s="8"/>
+      <c r="M57" s="6"/>
       <c r="N57" s="8"/>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O57" s="8"/>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
         <v>1</v>
       </c>
       <c r="B58" s="6"/>
       <c r="C58" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="G58" s="6"/>
+        <v>100</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H58" s="6"/>
       <c r="I58" s="6"/>
-      <c r="J58" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K58" s="6"/>
+      <c r="J58" s="6"/>
+      <c r="K58" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L58" s="6"/>
-      <c r="M58" s="8"/>
+      <c r="M58" s="6"/>
       <c r="N58" s="8"/>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O58" s="8"/>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
         <v>1</v>
       </c>
       <c r="B59" s="6"/>
       <c r="C59" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G59" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="G59" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H59" s="6"/>
       <c r="I59" s="6"/>
-      <c r="J59" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K59" s="6"/>
+      <c r="J59" s="6"/>
+      <c r="K59" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L59" s="6"/>
-      <c r="M59" s="8"/>
+      <c r="M59" s="6"/>
       <c r="N59" s="8"/>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O59" s="8"/>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
         <v>1</v>
       </c>
       <c r="B60" s="6"/>
       <c r="C60" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="G60" s="6"/>
+        <v>102</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H60" s="6"/>
       <c r="I60" s="6"/>
-      <c r="J60" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K60" s="6"/>
+      <c r="J60" s="6"/>
+      <c r="K60" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L60" s="6"/>
-      <c r="M60" s="8"/>
+      <c r="M60" s="6"/>
       <c r="N60" s="8"/>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O60" s="8"/>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
         <v>1</v>
       </c>
       <c r="B61" s="6"/>
       <c r="C61" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="G61" s="6"/>
+        <v>103</v>
+      </c>
+      <c r="G61" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H61" s="6"/>
       <c r="I61" s="6"/>
-      <c r="J61" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K61" s="6"/>
+      <c r="J61" s="6"/>
+      <c r="K61" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L61" s="6"/>
-      <c r="M61" s="8"/>
+      <c r="M61" s="6"/>
       <c r="N61" s="8"/>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O61" s="8"/>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
         <v>1</v>
       </c>
       <c r="B62" s="6"/>
       <c r="C62" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D62" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="F62" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E62" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="F62" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="G62" s="6"/>
+      <c r="G62" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H62" s="6"/>
       <c r="I62" s="6"/>
-      <c r="J62" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K62" s="6"/>
+      <c r="J62" s="6"/>
+      <c r="K62" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L62" s="6"/>
-      <c r="M62" s="8"/>
+      <c r="M62" s="6"/>
       <c r="N62" s="8"/>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O62" s="8"/>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
         <v>1</v>
       </c>
       <c r="B63" s="6"/>
       <c r="C63" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="G63" s="6"/>
+        <v>104</v>
+      </c>
+      <c r="G63" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H63" s="6"/>
       <c r="I63" s="6"/>
-      <c r="J63" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K63" s="6"/>
+      <c r="J63" s="6"/>
+      <c r="K63" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L63" s="6"/>
-      <c r="M63" s="8"/>
+      <c r="M63" s="6"/>
       <c r="N63" s="8"/>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O63" s="8"/>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
         <v>1</v>
       </c>
       <c r="B64" s="6"/>
       <c r="C64" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="G64" s="6"/>
+        <v>105</v>
+      </c>
+      <c r="G64" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H64" s="6"/>
       <c r="I64" s="6"/>
-      <c r="J64" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K64" s="6"/>
+      <c r="J64" s="6"/>
+      <c r="K64" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L64" s="6"/>
-      <c r="M64" s="8"/>
+      <c r="M64" s="6"/>
       <c r="N64" s="8"/>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O64" s="8"/>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
         <v>1</v>
       </c>
       <c r="B65" s="6"/>
       <c r="C65" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="G65" s="6"/>
+        <v>106</v>
+      </c>
+      <c r="G65" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H65" s="6"/>
       <c r="I65" s="6"/>
-      <c r="J65" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K65" s="6"/>
+      <c r="J65" s="6"/>
+      <c r="K65" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L65" s="6"/>
-      <c r="M65" s="8"/>
+      <c r="M65" s="6"/>
       <c r="N65" s="8"/>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O65" s="8"/>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
         <v>2</v>
       </c>
       <c r="B66" s="6"/>
       <c r="C66" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="G66" s="6"/>
+        <v>107</v>
+      </c>
+      <c r="G66" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H66" s="6"/>
       <c r="I66" s="6"/>
-      <c r="J66" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K66" s="6"/>
+      <c r="J66" s="6"/>
+      <c r="K66" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L66" s="6"/>
-      <c r="M66" s="8"/>
+      <c r="M66" s="6"/>
       <c r="N66" s="8"/>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O66" s="8"/>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>2</v>
       </c>
       <c r="B67" s="6"/>
       <c r="C67" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="G67" s="6"/>
+        <v>108</v>
+      </c>
+      <c r="G67" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H67" s="6"/>
       <c r="I67" s="6"/>
-      <c r="J67" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K67" s="6"/>
+      <c r="J67" s="6"/>
+      <c r="K67" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L67" s="6"/>
-      <c r="M67" s="8"/>
+      <c r="M67" s="6"/>
       <c r="N67" s="8"/>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O67" s="8"/>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
         <v>2</v>
       </c>
       <c r="B68" s="6"/>
       <c r="C68" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="G68" s="6"/>
+        <v>109</v>
+      </c>
+      <c r="G68" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H68" s="6"/>
       <c r="I68" s="6"/>
-      <c r="J68" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K68" s="6"/>
+      <c r="J68" s="6"/>
+      <c r="K68" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L68" s="6"/>
-      <c r="M68" s="8"/>
+      <c r="M68" s="6"/>
       <c r="N68" s="8"/>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O68" s="8"/>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
         <v>2</v>
       </c>
       <c r="B69" s="6"/>
       <c r="C69" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="G69" s="6"/>
+        <v>110</v>
+      </c>
+      <c r="G69" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H69" s="6"/>
       <c r="I69" s="6"/>
-      <c r="J69" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K69" s="6"/>
+      <c r="J69" s="6"/>
+      <c r="K69" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L69" s="6"/>
-      <c r="M69" s="8"/>
+      <c r="M69" s="6"/>
       <c r="N69" s="8"/>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O69" s="8"/>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
         <v>2</v>
       </c>
       <c r="B70" s="6"/>
       <c r="C70" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="G70" s="6"/>
+        <v>111</v>
+      </c>
+      <c r="G70" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H70" s="6"/>
       <c r="I70" s="6"/>
-      <c r="J70" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K70" s="6"/>
+      <c r="J70" s="6"/>
+      <c r="K70" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L70" s="6"/>
-      <c r="M70" s="8"/>
+      <c r="M70" s="6"/>
       <c r="N70" s="8"/>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O70" s="8"/>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
         <v>2</v>
       </c>
       <c r="B71" s="6"/>
       <c r="C71" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="G71" s="6"/>
+        <v>112</v>
+      </c>
+      <c r="G71" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H71" s="6"/>
       <c r="I71" s="6"/>
-      <c r="J71" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K71" s="6"/>
+      <c r="J71" s="6"/>
+      <c r="K71" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L71" s="6"/>
-      <c r="M71" s="8"/>
+      <c r="M71" s="6"/>
       <c r="N71" s="8"/>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O71" s="8"/>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
         <v>2</v>
       </c>
       <c r="B72" s="6"/>
       <c r="C72" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="G72" s="6"/>
+        <v>113</v>
+      </c>
+      <c r="G72" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H72" s="6"/>
       <c r="I72" s="6"/>
-      <c r="J72" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K72" s="6"/>
+      <c r="J72" s="6"/>
+      <c r="K72" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L72" s="6"/>
-      <c r="M72" s="8"/>
+      <c r="M72" s="6"/>
       <c r="N72" s="8"/>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O72" s="8"/>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
         <v>2</v>
       </c>
       <c r="B73" s="6"/>
       <c r="C73" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="G73" s="6"/>
+        <v>94</v>
+      </c>
+      <c r="G73" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H73" s="6"/>
       <c r="I73" s="6"/>
-      <c r="J73" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K73" s="6"/>
+      <c r="J73" s="6"/>
+      <c r="K73" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L73" s="6"/>
-      <c r="M73" s="8"/>
+      <c r="M73" s="6"/>
       <c r="N73" s="8"/>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O73" s="8"/>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
         <v>2</v>
       </c>
       <c r="B74" s="6"/>
       <c r="C74" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="G74" s="6"/>
+        <v>90</v>
+      </c>
+      <c r="G74" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H74" s="6"/>
       <c r="I74" s="6"/>
-      <c r="J74" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K74" s="6"/>
+      <c r="J74" s="6"/>
+      <c r="K74" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L74" s="6"/>
-      <c r="M74" s="8"/>
+      <c r="M74" s="6"/>
       <c r="N74" s="8"/>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O74" s="8"/>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
         <v>2</v>
       </c>
       <c r="B75" s="6"/>
       <c r="C75" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="G75" s="6"/>
+        <v>114</v>
+      </c>
+      <c r="G75" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H75" s="6"/>
       <c r="I75" s="6"/>
-      <c r="J75" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K75" s="6"/>
+      <c r="J75" s="6"/>
+      <c r="K75" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L75" s="6"/>
-      <c r="M75" s="8"/>
+      <c r="M75" s="6"/>
       <c r="N75" s="8"/>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O75" s="8"/>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
         <v>2</v>
       </c>
       <c r="B76" s="6"/>
       <c r="C76" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="G76" s="6"/>
+        <v>115</v>
+      </c>
+      <c r="G76" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H76" s="6"/>
       <c r="I76" s="6"/>
-      <c r="J76" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K76" s="6"/>
+      <c r="J76" s="6"/>
+      <c r="K76" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L76" s="6"/>
-      <c r="M76" s="8"/>
+      <c r="M76" s="6"/>
       <c r="N76" s="8"/>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O76" s="8"/>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
         <v>2</v>
       </c>
       <c r="B77" s="6"/>
       <c r="C77" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="G77" s="6"/>
+        <v>116</v>
+      </c>
+      <c r="G77" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H77" s="6"/>
       <c r="I77" s="6"/>
-      <c r="J77" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K77" s="6"/>
+      <c r="J77" s="6"/>
+      <c r="K77" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L77" s="6"/>
-      <c r="M77" s="8"/>
+      <c r="M77" s="6"/>
       <c r="N77" s="8"/>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O77" s="8"/>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
         <v>2</v>
       </c>
       <c r="B78" s="6"/>
       <c r="C78" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="G78" s="6"/>
+        <v>109</v>
+      </c>
+      <c r="G78" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H78" s="6"/>
       <c r="I78" s="6"/>
-      <c r="J78" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K78" s="6"/>
+      <c r="J78" s="6"/>
+      <c r="K78" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L78" s="6"/>
-      <c r="M78" s="8"/>
+      <c r="M78" s="6"/>
       <c r="N78" s="8"/>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O78" s="8"/>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
         <v>2</v>
       </c>
       <c r="B79" s="6"/>
       <c r="C79" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="G79" s="6"/>
+        <v>117</v>
+      </c>
+      <c r="G79" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H79" s="6"/>
       <c r="I79" s="6"/>
-      <c r="J79" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K79" s="6"/>
+      <c r="J79" s="6"/>
+      <c r="K79" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L79" s="6"/>
-      <c r="M79" s="8"/>
+      <c r="M79" s="6"/>
       <c r="N79" s="8"/>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O79" s="8"/>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
         <v>2</v>
       </c>
       <c r="B80" s="6"/>
       <c r="C80" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="G80" s="6"/>
+        <v>118</v>
+      </c>
+      <c r="G80" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H80" s="6"/>
       <c r="I80" s="6"/>
-      <c r="J80" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K80" s="6"/>
+      <c r="J80" s="6"/>
+      <c r="K80" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L80" s="6"/>
-      <c r="M80" s="8"/>
+      <c r="M80" s="6"/>
       <c r="N80" s="8"/>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O80" s="8"/>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
         <v>2</v>
       </c>
       <c r="B81" s="6"/>
       <c r="C81" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="G81" s="6"/>
+        <v>92</v>
+      </c>
+      <c r="G81" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H81" s="6"/>
       <c r="I81" s="6"/>
-      <c r="J81" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K81" s="6"/>
+      <c r="J81" s="6"/>
+      <c r="K81" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L81" s="6"/>
-      <c r="M81" s="8"/>
+      <c r="M81" s="6"/>
       <c r="N81" s="8"/>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O81" s="8"/>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
         <v>2</v>
       </c>
       <c r="B82" s="6"/>
       <c r="C82" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="G82" s="6"/>
+        <v>119</v>
+      </c>
+      <c r="G82" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H82" s="6"/>
       <c r="I82" s="6"/>
-      <c r="J82" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K82" s="6"/>
+      <c r="J82" s="6"/>
+      <c r="K82" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L82" s="6"/>
-      <c r="M82" s="8"/>
+      <c r="M82" s="6"/>
       <c r="N82" s="8"/>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O82" s="8"/>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
         <v>2</v>
       </c>
       <c r="B83" s="6"/>
       <c r="C83" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="G83" s="6"/>
+        <v>120</v>
+      </c>
+      <c r="G83" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H83" s="6"/>
       <c r="I83" s="6"/>
-      <c r="J83" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K83" s="6"/>
+      <c r="J83" s="6"/>
+      <c r="K83" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L83" s="6"/>
-      <c r="M83" s="8"/>
+      <c r="M83" s="6"/>
       <c r="N83" s="8"/>
-    </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O83" s="8"/>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
         <v>2</v>
       </c>
       <c r="B84" s="6"/>
       <c r="C84" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="G84" s="6"/>
+        <v>111</v>
+      </c>
+      <c r="G84" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H84" s="6"/>
       <c r="I84" s="6"/>
-      <c r="J84" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K84" s="6"/>
+      <c r="J84" s="6"/>
+      <c r="K84" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L84" s="6"/>
-      <c r="M84" s="8"/>
+      <c r="M84" s="6"/>
       <c r="N84" s="8"/>
-    </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O84" s="8"/>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
         <v>2</v>
       </c>
       <c r="B85" s="6"/>
       <c r="C85" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="G85" s="6"/>
+        <v>121</v>
+      </c>
+      <c r="G85" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H85" s="6"/>
       <c r="I85" s="6"/>
-      <c r="J85" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K85" s="6"/>
+      <c r="J85" s="6"/>
+      <c r="K85" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L85" s="6"/>
-      <c r="M85" s="8"/>
+      <c r="M85" s="6"/>
       <c r="N85" s="8"/>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O85" s="8"/>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
         <v>2</v>
       </c>
       <c r="B86" s="6"/>
       <c r="C86" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G86" s="6"/>
+        <v>99</v>
+      </c>
+      <c r="G86" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H86" s="6"/>
       <c r="I86" s="6"/>
-      <c r="J86" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K86" s="6"/>
+      <c r="J86" s="6"/>
+      <c r="K86" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L86" s="6"/>
-      <c r="M86" s="8"/>
+      <c r="M86" s="6"/>
       <c r="N86" s="8"/>
-    </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O86" s="8"/>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
         <v>2</v>
       </c>
       <c r="B87" s="6"/>
       <c r="C87" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F87" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="G87" s="6"/>
+        <v>122</v>
+      </c>
+      <c r="G87" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H87" s="6"/>
       <c r="I87" s="6"/>
-      <c r="J87" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K87" s="6"/>
+      <c r="J87" s="6"/>
+      <c r="K87" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L87" s="6"/>
-      <c r="M87" s="8"/>
+      <c r="M87" s="6"/>
       <c r="N87" s="8"/>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O87" s="8"/>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="6">
         <v>2</v>
       </c>
       <c r="B88" s="6"/>
       <c r="C88" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="G88" s="6"/>
+        <v>123</v>
+      </c>
+      <c r="G88" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H88" s="6"/>
       <c r="I88" s="6"/>
-      <c r="J88" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K88" s="6"/>
+      <c r="J88" s="6"/>
+      <c r="K88" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L88" s="6"/>
-      <c r="M88" s="8"/>
+      <c r="M88" s="6"/>
       <c r="N88" s="8"/>
-    </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O88" s="8"/>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
         <v>2</v>
       </c>
       <c r="B89" s="6"/>
       <c r="C89" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F89" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="G89" s="6"/>
+        <v>124</v>
+      </c>
+      <c r="G89" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H89" s="6"/>
       <c r="I89" s="6"/>
-      <c r="J89" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K89" s="6"/>
+      <c r="J89" s="6"/>
+      <c r="K89" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L89" s="6"/>
-      <c r="M89" s="8"/>
+      <c r="M89" s="6"/>
       <c r="N89" s="8"/>
-    </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O89" s="8"/>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="6">
         <v>2</v>
       </c>
       <c r="B90" s="6"/>
       <c r="C90" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="G90" s="6"/>
+        <v>106</v>
+      </c>
+      <c r="G90" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H90" s="6"/>
       <c r="I90" s="6"/>
-      <c r="J90" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K90" s="6"/>
+      <c r="J90" s="6"/>
+      <c r="K90" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L90" s="6"/>
-      <c r="M90" s="8"/>
+      <c r="M90" s="6"/>
       <c r="N90" s="8"/>
-    </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O90" s="8"/>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
         <v>2</v>
       </c>
       <c r="B91" s="6"/>
       <c r="C91" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="G91" s="6"/>
+        <v>125</v>
+      </c>
+      <c r="G91" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H91" s="6"/>
       <c r="I91" s="6"/>
-      <c r="J91" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K91" s="6"/>
+      <c r="J91" s="6"/>
+      <c r="K91" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L91" s="6"/>
-      <c r="M91" s="8"/>
+      <c r="M91" s="6"/>
       <c r="N91" s="8"/>
-    </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O91" s="8"/>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
         <v>3</v>
       </c>
       <c r="B92" s="6"/>
       <c r="C92" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="G92" s="6"/>
+        <v>126</v>
+      </c>
+      <c r="G92" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H92" s="6"/>
       <c r="I92" s="6"/>
-      <c r="J92" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K92" s="6"/>
+      <c r="J92" s="6"/>
+      <c r="K92" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L92" s="6"/>
-      <c r="M92" s="8"/>
+      <c r="M92" s="6"/>
       <c r="N92" s="8"/>
-    </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O92" s="8"/>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="6">
         <v>3</v>
       </c>
       <c r="B93" s="6"/>
       <c r="C93" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="G93" s="6"/>
+        <v>126</v>
+      </c>
+      <c r="G93" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H93" s="6"/>
       <c r="I93" s="6"/>
-      <c r="J93" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K93" s="6"/>
+      <c r="J93" s="6"/>
+      <c r="K93" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L93" s="6"/>
-      <c r="M93" s="8"/>
+      <c r="M93" s="6"/>
       <c r="N93" s="8"/>
-    </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O93" s="8"/>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
         <v>3</v>
       </c>
       <c r="B94" s="6"/>
       <c r="C94" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="G94" s="6"/>
+        <v>127</v>
+      </c>
+      <c r="G94" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H94" s="6"/>
       <c r="I94" s="6"/>
-      <c r="J94" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K94" s="6"/>
+      <c r="J94" s="6"/>
+      <c r="K94" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L94" s="6"/>
-      <c r="M94" s="8"/>
+      <c r="M94" s="6"/>
       <c r="N94" s="8"/>
-    </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O94" s="8"/>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="6">
         <v>3</v>
       </c>
       <c r="B95" s="6"/>
       <c r="C95" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="G95" s="6"/>
+        <v>128</v>
+      </c>
+      <c r="G95" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H95" s="6"/>
       <c r="I95" s="6"/>
-      <c r="J95" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K95" s="6"/>
+      <c r="J95" s="6"/>
+      <c r="K95" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L95" s="6"/>
-      <c r="M95" s="8"/>
+      <c r="M95" s="6"/>
       <c r="N95" s="8"/>
-    </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O95" s="8"/>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
         <v>3</v>
       </c>
       <c r="B96" s="6"/>
       <c r="C96" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="G96" s="6"/>
+        <v>129</v>
+      </c>
+      <c r="G96" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H96" s="6"/>
       <c r="I96" s="6"/>
-      <c r="J96" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K96" s="6"/>
+      <c r="J96" s="6"/>
+      <c r="K96" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L96" s="6"/>
-      <c r="M96" s="8"/>
+      <c r="M96" s="6"/>
       <c r="N96" s="8"/>
-    </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O96" s="8"/>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
         <v>3</v>
       </c>
       <c r="B97" s="6"/>
       <c r="C97" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="G97" s="6"/>
+        <v>129</v>
+      </c>
+      <c r="G97" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H97" s="6"/>
       <c r="I97" s="6"/>
-      <c r="J97" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K97" s="6"/>
+      <c r="J97" s="6"/>
+      <c r="K97" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L97" s="6"/>
-      <c r="M97" s="8"/>
+      <c r="M97" s="6"/>
       <c r="N97" s="8"/>
-    </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O97" s="8"/>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
         <v>3</v>
       </c>
       <c r="B98" s="6"/>
       <c r="C98" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F98" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="G98" s="6"/>
+        <v>130</v>
+      </c>
+      <c r="G98" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H98" s="6"/>
       <c r="I98" s="6"/>
-      <c r="J98" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K98" s="6"/>
+      <c r="J98" s="6"/>
+      <c r="K98" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L98" s="6"/>
-      <c r="M98" s="8"/>
+      <c r="M98" s="6"/>
       <c r="N98" s="8"/>
-    </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O98" s="8"/>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="6">
         <v>3</v>
       </c>
       <c r="B99" s="6"/>
       <c r="C99" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F99" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="G99" s="6"/>
+        <v>118</v>
+      </c>
+      <c r="G99" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H99" s="6"/>
       <c r="I99" s="6"/>
-      <c r="J99" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K99" s="6"/>
+      <c r="J99" s="6"/>
+      <c r="K99" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L99" s="6"/>
-      <c r="M99" s="8"/>
+      <c r="M99" s="6"/>
       <c r="N99" s="8"/>
-    </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O99" s="8"/>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" s="6">
         <v>3</v>
       </c>
       <c r="B100" s="6"/>
       <c r="C100" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F100" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="G100" s="6"/>
+        <v>131</v>
+      </c>
+      <c r="G100" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H100" s="6"/>
       <c r="I100" s="6"/>
-      <c r="J100" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K100" s="6"/>
+      <c r="J100" s="6"/>
+      <c r="K100" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L100" s="6"/>
-      <c r="M100" s="8"/>
+      <c r="M100" s="6"/>
       <c r="N100" s="8"/>
-    </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O100" s="8"/>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="6">
         <v>3</v>
       </c>
       <c r="B101" s="6"/>
       <c r="C101" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F101" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="G101" s="6"/>
+        <v>131</v>
+      </c>
+      <c r="G101" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H101" s="6"/>
       <c r="I101" s="6"/>
-      <c r="J101" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K101" s="6"/>
+      <c r="J101" s="6"/>
+      <c r="K101" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L101" s="6"/>
-      <c r="M101" s="8"/>
+      <c r="M101" s="6"/>
       <c r="N101" s="8"/>
-    </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O101" s="8"/>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" s="6">
         <v>3</v>
       </c>
       <c r="B102" s="6"/>
       <c r="C102" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="G102" s="6"/>
+        <v>119</v>
+      </c>
+      <c r="G102" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H102" s="6"/>
       <c r="I102" s="6"/>
-      <c r="J102" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K102" s="6"/>
+      <c r="J102" s="6"/>
+      <c r="K102" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L102" s="6"/>
-      <c r="M102" s="8"/>
+      <c r="M102" s="6"/>
       <c r="N102" s="8"/>
-    </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O102" s="8"/>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" s="6">
         <v>3</v>
       </c>
       <c r="B103" s="6"/>
       <c r="C103" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F103" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="G103" s="6"/>
+        <v>120</v>
+      </c>
+      <c r="G103" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H103" s="6"/>
       <c r="I103" s="6"/>
-      <c r="J103" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K103" s="6"/>
+      <c r="J103" s="6"/>
+      <c r="K103" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L103" s="6"/>
-      <c r="M103" s="8"/>
+      <c r="M103" s="6"/>
       <c r="N103" s="8"/>
-    </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O103" s="8"/>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" s="6">
         <v>3</v>
       </c>
       <c r="B104" s="6"/>
       <c r="C104" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F104" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="G104" s="6"/>
+        <v>132</v>
+      </c>
+      <c r="G104" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H104" s="6"/>
       <c r="I104" s="6"/>
-      <c r="J104" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K104" s="6"/>
+      <c r="J104" s="6"/>
+      <c r="K104" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L104" s="6"/>
-      <c r="M104" s="8"/>
+      <c r="M104" s="6"/>
       <c r="N104" s="8"/>
-    </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O104" s="8"/>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" s="6">
         <v>3</v>
       </c>
       <c r="B105" s="6"/>
       <c r="C105" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="G105" s="6"/>
+        <v>133</v>
+      </c>
+      <c r="G105" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H105" s="6"/>
       <c r="I105" s="6"/>
-      <c r="J105" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K105" s="6"/>
+      <c r="J105" s="6"/>
+      <c r="K105" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L105" s="6"/>
-      <c r="M105" s="8"/>
+      <c r="M105" s="6"/>
       <c r="N105" s="8"/>
-    </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O105" s="8"/>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" s="6">
         <v>3</v>
       </c>
       <c r="B106" s="6"/>
       <c r="C106" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="G106" s="6"/>
+        <v>121</v>
+      </c>
+      <c r="G106" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H106" s="6"/>
       <c r="I106" s="6"/>
-      <c r="J106" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K106" s="6"/>
+      <c r="J106" s="6"/>
+      <c r="K106" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L106" s="6"/>
-      <c r="M106" s="8"/>
+      <c r="M106" s="6"/>
       <c r="N106" s="8"/>
-    </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O106" s="8"/>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" s="6">
         <v>3</v>
       </c>
       <c r="B107" s="6"/>
       <c r="C107" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F107" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="G107" s="6"/>
+        <v>134</v>
+      </c>
+      <c r="G107" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H107" s="6"/>
       <c r="I107" s="6"/>
-      <c r="J107" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K107" s="6"/>
+      <c r="J107" s="6"/>
+      <c r="K107" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L107" s="6"/>
-      <c r="M107" s="8"/>
+      <c r="M107" s="6"/>
       <c r="N107" s="8"/>
-    </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O107" s="8"/>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" s="6">
         <v>3</v>
       </c>
       <c r="B108" s="6"/>
       <c r="C108" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F108" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="G108" s="6"/>
+        <v>134</v>
+      </c>
+      <c r="G108" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H108" s="6"/>
       <c r="I108" s="6"/>
-      <c r="J108" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K108" s="6"/>
+      <c r="J108" s="6"/>
+      <c r="K108" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L108" s="6"/>
-      <c r="M108" s="8"/>
+      <c r="M108" s="6"/>
       <c r="N108" s="8"/>
-    </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O108" s="8"/>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109" s="6">
         <v>3</v>
       </c>
       <c r="B109" s="6"/>
       <c r="C109" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="G109" s="6"/>
+        <v>135</v>
+      </c>
+      <c r="G109" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H109" s="6"/>
       <c r="I109" s="6"/>
-      <c r="J109" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K109" s="6"/>
+      <c r="J109" s="6"/>
+      <c r="K109" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L109" s="6"/>
-      <c r="M109" s="8"/>
+      <c r="M109" s="6"/>
       <c r="N109" s="8"/>
-    </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O109" s="8"/>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110" s="6">
         <v>3</v>
       </c>
       <c r="B110" s="6"/>
       <c r="C110" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="G110" s="6"/>
+        <v>136</v>
+      </c>
+      <c r="G110" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H110" s="6"/>
       <c r="I110" s="6"/>
-      <c r="J110" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K110" s="6"/>
+      <c r="J110" s="6"/>
+      <c r="K110" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L110" s="6"/>
-      <c r="M110" s="8"/>
+      <c r="M110" s="6"/>
       <c r="N110" s="8"/>
-    </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O110" s="8"/>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111" s="6">
         <v>3</v>
       </c>
       <c r="B111" s="6"/>
       <c r="C111" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F111" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="G111" s="6"/>
+        <v>137</v>
+      </c>
+      <c r="G111" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H111" s="6"/>
       <c r="I111" s="6"/>
-      <c r="J111" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K111" s="6"/>
+      <c r="J111" s="6"/>
+      <c r="K111" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L111" s="6"/>
-      <c r="M111" s="8"/>
+      <c r="M111" s="6"/>
       <c r="N111" s="8"/>
-    </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O111" s="8"/>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112" s="6">
         <v>3</v>
       </c>
       <c r="B112" s="6"/>
       <c r="C112" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F112" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="G112" s="6"/>
+        <v>138</v>
+      </c>
+      <c r="G112" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H112" s="6"/>
       <c r="I112" s="6"/>
-      <c r="J112" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K112" s="6"/>
+      <c r="J112" s="6"/>
+      <c r="K112" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L112" s="6"/>
-      <c r="M112" s="8"/>
+      <c r="M112" s="6"/>
       <c r="N112" s="8"/>
-    </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O112" s="8"/>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113" s="6">
         <v>3</v>
       </c>
       <c r="B113" s="6"/>
       <c r="C113" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="G113" s="6"/>
+        <v>138</v>
+      </c>
+      <c r="G113" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H113" s="6"/>
       <c r="I113" s="6"/>
-      <c r="J113" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K113" s="6"/>
+      <c r="J113" s="6"/>
+      <c r="K113" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L113" s="6"/>
-      <c r="M113" s="8"/>
+      <c r="M113" s="6"/>
       <c r="N113" s="8"/>
-    </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O113" s="8"/>
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114" s="6">
         <v>3</v>
       </c>
       <c r="B114" s="6"/>
       <c r="C114" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F114" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="G114" s="6"/>
+        <v>122</v>
+      </c>
+      <c r="G114" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H114" s="6"/>
       <c r="I114" s="6"/>
-      <c r="J114" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K114" s="6"/>
+      <c r="J114" s="6"/>
+      <c r="K114" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L114" s="6"/>
-      <c r="M114" s="8"/>
+      <c r="M114" s="6"/>
       <c r="N114" s="8"/>
-    </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O114" s="8"/>
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115" s="6">
         <v>3</v>
       </c>
       <c r="B115" s="6"/>
       <c r="C115" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="G115" s="6"/>
+        <v>139</v>
+      </c>
+      <c r="G115" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H115" s="6"/>
       <c r="I115" s="6"/>
-      <c r="J115" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K115" s="6"/>
+      <c r="J115" s="6"/>
+      <c r="K115" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L115" s="6"/>
-      <c r="M115" s="8"/>
+      <c r="M115" s="6"/>
       <c r="N115" s="8"/>
-    </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O115" s="8"/>
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116" s="6">
         <v>3</v>
       </c>
       <c r="B116" s="6"/>
       <c r="C116" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="G116" s="6"/>
+        <v>139</v>
+      </c>
+      <c r="G116" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H116" s="6"/>
       <c r="I116" s="6"/>
-      <c r="J116" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K116" s="6"/>
+      <c r="J116" s="6"/>
+      <c r="K116" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L116" s="6"/>
-      <c r="M116" s="8"/>
+      <c r="M116" s="6"/>
       <c r="N116" s="8"/>
-    </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O116" s="8"/>
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117" s="6">
         <v>3</v>
       </c>
       <c r="B117" s="6"/>
       <c r="C117" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="G117" s="6"/>
+        <v>124</v>
+      </c>
+      <c r="G117" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H117" s="6"/>
       <c r="I117" s="6"/>
-      <c r="J117" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K117" s="6"/>
+      <c r="J117" s="6"/>
+      <c r="K117" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L117" s="6"/>
-      <c r="M117" s="8"/>
+      <c r="M117" s="6"/>
       <c r="N117" s="8"/>
-    </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O117" s="8"/>
+    </row>
+    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118" s="6">
         <v>3</v>
       </c>
       <c r="B118" s="6"/>
       <c r="C118" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="G118" s="6"/>
+        <v>140</v>
+      </c>
+      <c r="G118" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H118" s="6"/>
       <c r="I118" s="6"/>
-      <c r="J118" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K118" s="6"/>
+      <c r="J118" s="6"/>
+      <c r="K118" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L118" s="6"/>
-      <c r="M118" s="8"/>
+      <c r="M118" s="6"/>
       <c r="N118" s="8"/>
-    </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O118" s="8"/>
+    </row>
+    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119" s="6">
         <v>3</v>
       </c>
       <c r="B119" s="6"/>
       <c r="C119" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F119" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="G119" s="6"/>
+        <v>125</v>
+      </c>
+      <c r="G119" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H119" s="6"/>
       <c r="I119" s="6"/>
-      <c r="J119" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K119" s="6"/>
+      <c r="J119" s="6"/>
+      <c r="K119" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L119" s="6"/>
-      <c r="M119" s="8"/>
+      <c r="M119" s="6"/>
       <c r="N119" s="8"/>
-    </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O119" s="8"/>
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120" s="6">
         <v>3</v>
       </c>
       <c r="B120" s="6"/>
       <c r="C120" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F120" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G120" s="6"/>
+        <v>141</v>
+      </c>
+      <c r="G120" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H120" s="6"/>
       <c r="I120" s="6"/>
-      <c r="J120" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K120" s="6"/>
+      <c r="J120" s="6"/>
+      <c r="K120" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L120" s="6"/>
-      <c r="M120" s="8"/>
+      <c r="M120" s="6"/>
       <c r="N120" s="8"/>
-    </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O120" s="8"/>
+    </row>
+    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121" s="6">
         <v>3</v>
       </c>
       <c r="B121" s="6"/>
       <c r="C121" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F121" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="G121" s="6"/>
+        <v>89</v>
+      </c>
+      <c r="G121" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H121" s="6"/>
       <c r="I121" s="6"/>
-      <c r="J121" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K121" s="6"/>
+      <c r="J121" s="6"/>
+      <c r="K121" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L121" s="6"/>
-      <c r="M121" s="8"/>
+      <c r="M121" s="6"/>
       <c r="N121" s="8"/>
-    </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O121" s="8"/>
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122" s="6">
         <v>3</v>
       </c>
       <c r="B122" s="6"/>
       <c r="C122" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F122" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="G122" s="6"/>
+        <v>100</v>
+      </c>
+      <c r="G122" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H122" s="6"/>
       <c r="I122" s="6"/>
-      <c r="J122" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K122" s="6"/>
+      <c r="J122" s="6"/>
+      <c r="K122" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L122" s="6"/>
-      <c r="M122" s="8"/>
+      <c r="M122" s="6"/>
       <c r="N122" s="8"/>
-    </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O122" s="8"/>
+    </row>
+    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123" s="6">
         <v>3</v>
       </c>
       <c r="B123" s="6"/>
       <c r="C123" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E123" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F123" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="G123" s="6"/>
+        <v>104</v>
+      </c>
+      <c r="G123" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H123" s="6"/>
       <c r="I123" s="6"/>
-      <c r="J123" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K123" s="6"/>
+      <c r="J123" s="6"/>
+      <c r="K123" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L123" s="6"/>
-      <c r="M123" s="8"/>
+      <c r="M123" s="6"/>
       <c r="N123" s="8"/>
-    </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O123" s="8"/>
+    </row>
+    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124" s="6">
         <v>3</v>
       </c>
       <c r="B124" s="6"/>
       <c r="C124" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F124" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="G124" s="6"/>
+        <v>105</v>
+      </c>
+      <c r="G124" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H124" s="6"/>
       <c r="I124" s="6"/>
-      <c r="J124" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K124" s="6"/>
+      <c r="J124" s="6"/>
+      <c r="K124" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L124" s="6"/>
-      <c r="M124" s="8"/>
+      <c r="M124" s="6"/>
       <c r="N124" s="8"/>
-    </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O124" s="8"/>
+    </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125" s="6">
         <v>3</v>
       </c>
       <c r="B125" s="6"/>
       <c r="C125" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E125" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F125" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="G125" s="6"/>
+        <v>108</v>
+      </c>
+      <c r="G125" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H125" s="6"/>
       <c r="I125" s="6"/>
-      <c r="J125" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K125" s="6"/>
+      <c r="J125" s="6"/>
+      <c r="K125" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L125" s="6"/>
-      <c r="M125" s="8"/>
+      <c r="M125" s="6"/>
       <c r="N125" s="8"/>
-    </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O125" s="8"/>
+    </row>
+    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A126" s="6">
         <v>3</v>
       </c>
       <c r="B126" s="6"/>
       <c r="C126" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F126" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="G126" s="6"/>
+        <v>112</v>
+      </c>
+      <c r="G126" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H126" s="6"/>
       <c r="I126" s="6"/>
-      <c r="J126" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K126" s="6"/>
+      <c r="J126" s="6"/>
+      <c r="K126" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L126" s="6"/>
-      <c r="M126" s="8"/>
+      <c r="M126" s="6"/>
       <c r="N126" s="8"/>
-    </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O126" s="8"/>
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A127" s="6">
         <v>3</v>
       </c>
       <c r="B127" s="6"/>
       <c r="C127" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F127" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="G127" s="6"/>
+        <v>113</v>
+      </c>
+      <c r="G127" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H127" s="6"/>
       <c r="I127" s="6"/>
-      <c r="J127" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K127" s="6"/>
+      <c r="J127" s="6"/>
+      <c r="K127" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L127" s="6"/>
-      <c r="M127" s="8"/>
+      <c r="M127" s="6"/>
       <c r="N127" s="8"/>
-    </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O127" s="8"/>
+    </row>
+    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A128" s="6">
         <v>2</v>
       </c>
@@ -5557,26 +5910,29 @@
         <v>14</v>
       </c>
       <c r="D128" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E128" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="F128" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="E128" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="F128" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="G128" s="6"/>
+      <c r="G128" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H128" s="6"/>
       <c r="I128" s="6"/>
-      <c r="J128" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K128" s="6"/>
+      <c r="J128" s="6"/>
+      <c r="K128" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L128" s="6"/>
-      <c r="M128" s="8"/>
+      <c r="M128" s="6"/>
       <c r="N128" s="8"/>
-    </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O128" s="8"/>
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A129" s="6">
         <v>2</v>
       </c>
@@ -5585,26 +5941,29 @@
         <v>14</v>
       </c>
       <c r="D129" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="E129" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="F129" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="E129" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="F129" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="G129" s="6"/>
+      <c r="G129" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H129" s="6"/>
       <c r="I129" s="6"/>
-      <c r="J129" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K129" s="6"/>
+      <c r="J129" s="6"/>
+      <c r="K129" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L129" s="6"/>
-      <c r="M129" s="8"/>
+      <c r="M129" s="6"/>
       <c r="N129" s="8"/>
-    </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O129" s="8"/>
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A130" s="6">
         <v>2</v>
       </c>
@@ -5613,54 +5972,60 @@
         <v>14</v>
       </c>
       <c r="D130" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="E130" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="F130" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="E130" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="F130" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="G130" s="6"/>
+      <c r="G130" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H130" s="6"/>
       <c r="I130" s="6"/>
-      <c r="J130" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K130" s="6"/>
+      <c r="J130" s="6"/>
+      <c r="K130" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L130" s="6"/>
-      <c r="M130" s="8"/>
+      <c r="M130" s="6"/>
       <c r="N130" s="8"/>
-    </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O130" s="8"/>
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A131" s="6">
         <v>2</v>
       </c>
       <c r="B131" s="6"/>
       <c r="C131" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D131" s="6" t="s">
         <v>15</v>
       </c>
       <c r="E131" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F131" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G131" s="6"/>
+        <v>25</v>
+      </c>
+      <c r="G131" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H131" s="6"/>
       <c r="I131" s="6"/>
-      <c r="J131" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K131" s="6"/>
+      <c r="J131" s="6"/>
+      <c r="K131" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L131" s="6"/>
-      <c r="M131" s="8"/>
+      <c r="M131" s="6"/>
       <c r="N131" s="8"/>
-    </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O131" s="8"/>
+    </row>
+    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A132" s="6">
         <v>3</v>
       </c>
@@ -5672,23 +6037,26 @@
         <v>15</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F132" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="G132" s="6"/>
+        <v>153</v>
+      </c>
+      <c r="G132" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H132" s="6"/>
       <c r="I132" s="6"/>
-      <c r="J132" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K132" s="6"/>
+      <c r="J132" s="6"/>
+      <c r="K132" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L132" s="6"/>
-      <c r="M132" s="8"/>
+      <c r="M132" s="6"/>
       <c r="N132" s="8"/>
-    </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O132" s="8"/>
+    </row>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A133" s="6">
         <v>3</v>
       </c>
@@ -5700,23 +6068,26 @@
         <v>15</v>
       </c>
       <c r="E133" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F133" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="G133" s="6"/>
+        <v>154</v>
+      </c>
+      <c r="G133" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H133" s="6"/>
       <c r="I133" s="6"/>
-      <c r="J133" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K133" s="6"/>
+      <c r="J133" s="6"/>
+      <c r="K133" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L133" s="6"/>
-      <c r="M133" s="8"/>
+      <c r="M133" s="6"/>
       <c r="N133" s="8"/>
-    </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O133" s="8"/>
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A134" s="6">
         <v>3</v>
       </c>
@@ -5725,26 +6096,29 @@
         <v>14</v>
       </c>
       <c r="D134" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="E134" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="F134" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="E134" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="F134" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="G134" s="6"/>
+      <c r="G134" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H134" s="6"/>
       <c r="I134" s="6"/>
-      <c r="J134" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K134" s="6"/>
+      <c r="J134" s="6"/>
+      <c r="K134" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L134" s="6"/>
-      <c r="M134" s="8"/>
+      <c r="M134" s="6"/>
       <c r="N134" s="8"/>
-    </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O134" s="8"/>
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A135" s="6">
         <v>3</v>
       </c>
@@ -5756,23 +6130,26 @@
         <v>15</v>
       </c>
       <c r="E135" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F135" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="G135" s="6"/>
+        <v>157</v>
+      </c>
+      <c r="G135" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H135" s="6"/>
       <c r="I135" s="6"/>
-      <c r="J135" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K135" s="6"/>
+      <c r="J135" s="6"/>
+      <c r="K135" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L135" s="6"/>
-      <c r="M135" s="8"/>
+      <c r="M135" s="6"/>
       <c r="N135" s="8"/>
-    </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O135" s="8"/>
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A136" s="6">
         <v>3</v>
       </c>
@@ -5784,23 +6161,26 @@
         <v>15</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F136" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="G136" s="6"/>
+        <v>160</v>
+      </c>
+      <c r="G136" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H136" s="6"/>
       <c r="I136" s="6"/>
-      <c r="J136" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K136" s="6"/>
+      <c r="J136" s="6"/>
+      <c r="K136" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L136" s="6"/>
-      <c r="M136" s="8"/>
+      <c r="M136" s="6"/>
       <c r="N136" s="8"/>
-    </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O136" s="8"/>
+    </row>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A137" s="6">
         <v>3</v>
       </c>
@@ -5812,23 +6192,26 @@
         <v>15</v>
       </c>
       <c r="E137" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F137" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="G137" s="6"/>
+        <v>161</v>
+      </c>
+      <c r="G137" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H137" s="6"/>
       <c r="I137" s="6"/>
-      <c r="J137" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K137" s="6"/>
+      <c r="J137" s="6"/>
+      <c r="K137" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L137" s="6"/>
-      <c r="M137" s="8"/>
+      <c r="M137" s="6"/>
       <c r="N137" s="8"/>
-    </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O137" s="8"/>
+    </row>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A138" s="6">
         <v>3</v>
       </c>
@@ -5837,578 +6220,638 @@
         <v>14</v>
       </c>
       <c r="D138" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="E138" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="F138" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="E138" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="F138" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="G138" s="6"/>
+      <c r="G138" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H138" s="6"/>
       <c r="I138" s="6"/>
-      <c r="J138" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K138" s="6"/>
+      <c r="J138" s="6"/>
+      <c r="K138" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L138" s="6"/>
-      <c r="M138" s="8"/>
+      <c r="M138" s="6"/>
       <c r="N138" s="8"/>
-    </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O138" s="8"/>
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A139" s="6">
         <v>3</v>
       </c>
       <c r="B139" s="6"/>
       <c r="C139" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E139" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F139" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="G139" s="6"/>
+        <v>164</v>
+      </c>
+      <c r="G139" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H139" s="6"/>
       <c r="I139" s="6"/>
-      <c r="J139" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K139" s="6"/>
+      <c r="J139" s="6"/>
+      <c r="K139" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L139" s="6"/>
-      <c r="M139" s="8"/>
+      <c r="M139" s="6"/>
       <c r="N139" s="8"/>
-    </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O139" s="8"/>
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A140" s="6">
         <v>3</v>
       </c>
       <c r="B140" s="6"/>
       <c r="C140" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F140" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="G140" s="6"/>
+        <v>165</v>
+      </c>
+      <c r="G140" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H140" s="6"/>
       <c r="I140" s="6"/>
-      <c r="J140" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K140" s="6"/>
+      <c r="J140" s="6"/>
+      <c r="K140" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L140" s="6"/>
-      <c r="M140" s="8"/>
+      <c r="M140" s="6"/>
       <c r="N140" s="8"/>
-    </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O140" s="8"/>
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A141" s="6">
         <v>3</v>
       </c>
       <c r="B141" s="6"/>
       <c r="C141" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E141" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F141" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="G141" s="6"/>
+        <v>166</v>
+      </c>
+      <c r="G141" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H141" s="6"/>
       <c r="I141" s="6"/>
-      <c r="J141" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K141" s="6"/>
+      <c r="J141" s="6"/>
+      <c r="K141" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L141" s="6"/>
-      <c r="M141" s="8"/>
+      <c r="M141" s="6"/>
       <c r="N141" s="8"/>
-    </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O141" s="8"/>
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A142" s="6">
         <v>3</v>
       </c>
       <c r="B142" s="6"/>
       <c r="C142" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F142" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="G142" s="6"/>
+        <v>167</v>
+      </c>
+      <c r="G142" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H142" s="6"/>
       <c r="I142" s="6"/>
-      <c r="J142" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K142" s="6"/>
+      <c r="J142" s="6"/>
+      <c r="K142" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L142" s="6"/>
-      <c r="M142" s="8"/>
+      <c r="M142" s="6"/>
       <c r="N142" s="8"/>
-    </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O142" s="8"/>
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A143" s="6">
         <v>3</v>
       </c>
       <c r="B143" s="6"/>
       <c r="C143" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E143" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F143" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="G143" s="6"/>
+        <v>168</v>
+      </c>
+      <c r="G143" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H143" s="6"/>
       <c r="I143" s="6"/>
-      <c r="J143" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K143" s="6"/>
+      <c r="J143" s="6"/>
+      <c r="K143" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L143" s="6"/>
-      <c r="M143" s="8"/>
+      <c r="M143" s="6"/>
       <c r="N143" s="8"/>
-    </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O143" s="8"/>
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A144" s="6">
         <v>3</v>
       </c>
       <c r="B144" s="6"/>
       <c r="C144" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F144" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="G144" s="6"/>
+        <v>169</v>
+      </c>
+      <c r="G144" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H144" s="6"/>
       <c r="I144" s="6"/>
-      <c r="J144" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K144" s="6"/>
+      <c r="J144" s="6"/>
+      <c r="K144" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L144" s="6"/>
-      <c r="M144" s="8"/>
+      <c r="M144" s="6"/>
       <c r="N144" s="8"/>
-    </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O144" s="8"/>
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A145" s="6">
         <v>3</v>
       </c>
       <c r="B145" s="6"/>
       <c r="C145" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E145" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F145" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="G145" s="6"/>
+        <v>170</v>
+      </c>
+      <c r="G145" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H145" s="6"/>
       <c r="I145" s="6"/>
-      <c r="J145" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K145" s="6"/>
+      <c r="J145" s="6"/>
+      <c r="K145" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L145" s="6"/>
-      <c r="M145" s="8"/>
+      <c r="M145" s="6"/>
       <c r="N145" s="8"/>
-    </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O145" s="8"/>
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A146" s="6">
         <v>3</v>
       </c>
       <c r="B146" s="6"/>
       <c r="C146" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F146" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="G146" s="6"/>
+        <v>171</v>
+      </c>
+      <c r="G146" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H146" s="6"/>
       <c r="I146" s="6"/>
-      <c r="J146" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K146" s="6"/>
+      <c r="J146" s="6"/>
+      <c r="K146" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L146" s="6"/>
-      <c r="M146" s="8"/>
+      <c r="M146" s="6"/>
       <c r="N146" s="8"/>
-    </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O146" s="8"/>
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A147" s="6">
         <v>3</v>
       </c>
       <c r="B147" s="6"/>
       <c r="C147" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="D147" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E147" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="F147" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="D147" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="E147" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="F147" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="G147" s="6"/>
+      <c r="G147" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H147" s="6"/>
       <c r="I147" s="6"/>
-      <c r="J147" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K147" s="6"/>
+      <c r="J147" s="6"/>
+      <c r="K147" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L147" s="6"/>
-      <c r="M147" s="8"/>
+      <c r="M147" s="6"/>
       <c r="N147" s="8"/>
-    </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O147" s="8"/>
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A148" s="6">
         <v>3</v>
       </c>
       <c r="B148" s="6"/>
       <c r="C148" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F148" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="G148" s="6"/>
+        <v>174</v>
+      </c>
+      <c r="G148" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H148" s="6"/>
       <c r="I148" s="6"/>
-      <c r="J148" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K148" s="6"/>
+      <c r="J148" s="6"/>
+      <c r="K148" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L148" s="6"/>
-      <c r="M148" s="8"/>
+      <c r="M148" s="6"/>
       <c r="N148" s="8"/>
-    </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O148" s="8"/>
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A149" s="6">
         <v>3</v>
       </c>
       <c r="B149" s="6"/>
       <c r="C149" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E149" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F149" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="G149" s="6"/>
+        <v>175</v>
+      </c>
+      <c r="G149" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H149" s="6"/>
       <c r="I149" s="6"/>
-      <c r="J149" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K149" s="6"/>
+      <c r="J149" s="6"/>
+      <c r="K149" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L149" s="6"/>
-      <c r="M149" s="8"/>
+      <c r="M149" s="6"/>
       <c r="N149" s="8"/>
-    </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O149" s="8"/>
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A150" s="6">
         <v>3</v>
       </c>
       <c r="B150" s="6"/>
       <c r="C150" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F150" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="G150" s="6"/>
+        <v>176</v>
+      </c>
+      <c r="G150" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H150" s="6"/>
       <c r="I150" s="6"/>
-      <c r="J150" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K150" s="6"/>
+      <c r="J150" s="6"/>
+      <c r="K150" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L150" s="6"/>
-      <c r="M150" s="8"/>
+      <c r="M150" s="6"/>
       <c r="N150" s="8"/>
-    </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O150" s="8"/>
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A151" s="6">
         <v>3</v>
       </c>
       <c r="B151" s="6"/>
       <c r="C151" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E151" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F151" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="G151" s="6"/>
+        <v>177</v>
+      </c>
+      <c r="G151" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H151" s="6"/>
       <c r="I151" s="6"/>
-      <c r="J151" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K151" s="6"/>
+      <c r="J151" s="6"/>
+      <c r="K151" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L151" s="6"/>
-      <c r="M151" s="8"/>
+      <c r="M151" s="6"/>
       <c r="N151" s="8"/>
-    </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O151" s="8"/>
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A152" s="6">
         <v>3</v>
       </c>
       <c r="B152" s="6"/>
       <c r="C152" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F152" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="G152" s="6"/>
+        <v>178</v>
+      </c>
+      <c r="G152" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H152" s="6"/>
       <c r="I152" s="6"/>
-      <c r="J152" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K152" s="6"/>
+      <c r="J152" s="6"/>
+      <c r="K152" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L152" s="6"/>
-      <c r="M152" s="8"/>
+      <c r="M152" s="6"/>
       <c r="N152" s="8"/>
-    </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O152" s="8"/>
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A153" s="6">
         <v>3</v>
       </c>
       <c r="B153" s="6"/>
       <c r="C153" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E153" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F153" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="G153" s="6"/>
+        <v>179</v>
+      </c>
+      <c r="G153" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H153" s="6"/>
       <c r="I153" s="6"/>
-      <c r="J153" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K153" s="6"/>
+      <c r="J153" s="6"/>
+      <c r="K153" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L153" s="6"/>
-      <c r="M153" s="8"/>
+      <c r="M153" s="6"/>
       <c r="N153" s="8"/>
-    </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O153" s="8"/>
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A154" s="6">
         <v>3</v>
       </c>
       <c r="B154" s="6"/>
       <c r="C154" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F154" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="G154" s="6"/>
+        <v>180</v>
+      </c>
+      <c r="G154" s="6" t="s">
+        <v>326</v>
+      </c>
       <c r="H154" s="6"/>
       <c r="I154" s="6"/>
-      <c r="J154" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K154" s="6"/>
+      <c r="J154" s="6"/>
+      <c r="K154" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="L154" s="6"/>
-      <c r="M154" s="8"/>
+      <c r="M154" s="6"/>
       <c r="N154" s="8"/>
-    </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O154" s="8"/>
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A155" s="6">
         <v>0</v>
       </c>
       <c r="B155" s="6"/>
       <c r="C155" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D155" s="6" t="s">
         <v>15</v>
       </c>
       <c r="E155" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F155" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="G155" s="7">
+        <v>181</v>
+      </c>
+      <c r="G155" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="H155" s="7">
         <v>46094</v>
       </c>
-      <c r="H155" s="10">
+      <c r="I155" s="10">
         <v>0.41666666666666669</v>
       </c>
-      <c r="I155" s="6" t="s">
+      <c r="J155" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J155" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="K155" s="6"/>
+      <c r="K155" s="6" t="s">
+        <v>78</v>
+      </c>
       <c r="L155" s="6"/>
-      <c r="M155" s="8"/>
+      <c r="M155" s="6"/>
       <c r="N155" s="8"/>
-    </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O155" s="8"/>
+    </row>
+    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A156" s="6">
         <v>0</v>
       </c>
       <c r="B156" s="6"/>
       <c r="C156" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D156" s="6" t="s">
         <v>15</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F156" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="G156" s="7">
+        <v>182</v>
+      </c>
+      <c r="G156" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="H156" s="7">
         <v>46094</v>
       </c>
-      <c r="H156" s="10">
+      <c r="I156" s="10">
         <v>0.41666666666666669</v>
       </c>
-      <c r="I156" s="6" t="s">
+      <c r="J156" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J156" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="K156" s="6"/>
+      <c r="K156" s="6" t="s">
+        <v>78</v>
+      </c>
       <c r="L156" s="6"/>
-      <c r="M156" s="8"/>
+      <c r="M156" s="6"/>
       <c r="N156" s="8"/>
-    </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O156" s="8"/>
+    </row>
+    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A157" s="6">
         <v>0</v>
       </c>
       <c r="B157" s="6"/>
       <c r="C157" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="D157" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E157" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D157" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="E157" s="6" t="s">
+      <c r="F157" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="F157" s="6" t="s">
+      <c r="G157" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="H157" s="7">
+        <v>46095</v>
+      </c>
+      <c r="I157" s="10">
+        <v>0.625</v>
+      </c>
+      <c r="J157" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="K157" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="L157" s="6"/>
+      <c r="M157" s="6"/>
+      <c r="N157" s="8"/>
+      <c r="O157" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="G157" s="7">
-        <v>46095</v>
-      </c>
-      <c r="H157" s="10">
-        <v>0.625</v>
-      </c>
-      <c r="I157" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="J157" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="K157" s="6"/>
-      <c r="L157" s="6"/>
-      <c r="M157" s="8"/>
-      <c r="N157" s="8" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A158" s="6">
         <v>3</v>
       </c>
@@ -6420,27 +6863,30 @@
         <v>15</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F158" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="G158" s="7">
+        <v>187</v>
+      </c>
+      <c r="G158" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="H158" s="7">
         <v>46128</v>
       </c>
-      <c r="H158" s="10">
+      <c r="I158" s="10">
         <v>0.29166666666666669</v>
       </c>
-      <c r="I158" s="6"/>
-      <c r="J158" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="K158" s="6"/>
+      <c r="J158" s="6"/>
+      <c r="K158" s="6" t="s">
+        <v>78</v>
+      </c>
       <c r="L158" s="6"/>
-      <c r="M158" s="8"/>
+      <c r="M158" s="6"/>
       <c r="N158" s="8"/>
-    </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O158" s="8"/>
+    </row>
+    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A159" s="6">
         <v>3</v>
       </c>
@@ -6452,29 +6898,32 @@
         <v>15</v>
       </c>
       <c r="E159" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F159" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="G159" s="7">
+        <v>188</v>
+      </c>
+      <c r="G159" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="H159" s="7">
         <v>46139</v>
       </c>
-      <c r="H159" s="10">
+      <c r="I159" s="10">
         <v>0.25</v>
       </c>
-      <c r="I159" s="10">
+      <c r="J159" s="10">
         <v>0.33333333333333331</v>
       </c>
-      <c r="J159" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="K159" s="6"/>
+      <c r="K159" s="6" t="s">
+        <v>78</v>
+      </c>
       <c r="L159" s="6"/>
-      <c r="M159" s="8"/>
+      <c r="M159" s="6"/>
       <c r="N159" s="8"/>
-    </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O159" s="8"/>
+    </row>
+    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A160" s="6">
         <v>3</v>
       </c>
@@ -6483,32 +6932,35 @@
         <v>14</v>
       </c>
       <c r="D160" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="E160" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="F160" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="E160" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="F160" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="G160" s="7">
+      <c r="G160" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="H160" s="7">
         <v>46141</v>
       </c>
-      <c r="H160" s="10">
+      <c r="I160" s="10">
         <v>0.67361111111111116</v>
       </c>
-      <c r="I160" s="10">
+      <c r="J160" s="10">
         <v>0.96527777777777779</v>
       </c>
-      <c r="J160" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="K160" s="6"/>
+      <c r="K160" s="6" t="s">
+        <v>78</v>
+      </c>
       <c r="L160" s="6"/>
-      <c r="M160" s="8"/>
+      <c r="M160" s="6"/>
       <c r="N160" s="8"/>
-    </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O160" s="8"/>
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A161" s="6">
         <v>3</v>
       </c>
@@ -6520,29 +6972,32 @@
         <v>15</v>
       </c>
       <c r="E161" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F161" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="G161" s="7">
+        <v>191</v>
+      </c>
+      <c r="G161" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="H161" s="7">
         <v>46146</v>
       </c>
-      <c r="H161" s="10">
+      <c r="I161" s="10">
         <v>0.33333333333333331</v>
       </c>
-      <c r="I161" s="10">
+      <c r="J161" s="10">
         <v>0.41666666666666669</v>
       </c>
-      <c r="J161" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="K161" s="6"/>
+      <c r="K161" s="6" t="s">
+        <v>78</v>
+      </c>
       <c r="L161" s="6"/>
-      <c r="M161" s="8"/>
+      <c r="M161" s="6"/>
       <c r="N161" s="8"/>
-    </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O161" s="8"/>
+    </row>
+    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A162" s="6">
         <v>3</v>
       </c>
@@ -6551,32 +7006,35 @@
         <v>14</v>
       </c>
       <c r="D162" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="E162" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="F162" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="E162" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="F162" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="G162" s="7">
+      <c r="G162" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="H162" s="7">
         <v>46147</v>
       </c>
-      <c r="H162" s="10">
+      <c r="I162" s="10">
         <v>0.45833333333333331</v>
       </c>
-      <c r="I162" s="10">
+      <c r="J162" s="10">
         <v>0.5</v>
       </c>
-      <c r="J162" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="K162" s="6"/>
+      <c r="K162" s="6" t="s">
+        <v>78</v>
+      </c>
       <c r="L162" s="6"/>
-      <c r="M162" s="8"/>
+      <c r="M162" s="6"/>
       <c r="N162" s="8"/>
-    </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O162" s="8"/>
+    </row>
+    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A163" s="6">
         <v>1</v>
       </c>
@@ -6588,29 +7046,32 @@
         <v>15</v>
       </c>
       <c r="E163" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F163" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="G163" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="H163" s="7">
+        <v>46147</v>
+      </c>
+      <c r="I163" s="10">
+        <v>0.625</v>
+      </c>
+      <c r="J163" s="6"/>
+      <c r="K163" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="L163" s="6"/>
+      <c r="M163" s="6"/>
+      <c r="N163" s="8"/>
+      <c r="O163" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="G163" s="7">
-        <v>46147</v>
-      </c>
-      <c r="H163" s="10">
-        <v>0.625</v>
-      </c>
-      <c r="I163" s="6"/>
-      <c r="J163" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="K163" s="6"/>
-      <c r="L163" s="6"/>
-      <c r="M163" s="8"/>
-      <c r="N163" s="8" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A164" s="6">
         <v>3</v>
       </c>
@@ -6622,29 +7083,32 @@
         <v>15</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F164" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="G164" s="7">
+        <v>196</v>
+      </c>
+      <c r="G164" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="H164" s="7">
         <v>46149</v>
       </c>
-      <c r="H164" s="10">
+      <c r="I164" s="10">
         <v>0.33333333333333331</v>
       </c>
-      <c r="I164" s="10">
+      <c r="J164" s="10">
         <v>0.41666666666666669</v>
       </c>
-      <c r="J164" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="K164" s="6"/>
+      <c r="K164" s="6" t="s">
+        <v>78</v>
+      </c>
       <c r="L164" s="6"/>
-      <c r="M164" s="8"/>
+      <c r="M164" s="6"/>
       <c r="N164" s="8"/>
-    </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O164" s="8"/>
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A165" s="6">
         <v>3</v>
       </c>
@@ -6653,32 +7117,35 @@
         <v>14</v>
       </c>
       <c r="D165" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="E165" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="F165" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="E165" s="6" t="s">
-        <v>305</v>
-      </c>
-      <c r="F165" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="G165" s="7">
+      <c r="G165" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="H165" s="7">
         <v>46155</v>
       </c>
-      <c r="H165" s="6"/>
-      <c r="I165" s="10">
+      <c r="I165" s="6"/>
+      <c r="J165" s="10">
         <v>0.45833333333333331</v>
       </c>
-      <c r="J165" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="K165" s="6"/>
+      <c r="K165" s="6" t="s">
+        <v>78</v>
+      </c>
       <c r="L165" s="6"/>
-      <c r="M165" s="8"/>
-      <c r="N165" s="8" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M165" s="6"/>
+      <c r="N165" s="8"/>
+      <c r="O165" s="8" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A166" s="6">
         <v>3</v>
       </c>
@@ -6690,27 +7157,30 @@
         <v>15</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F166" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="G166" s="7">
+        <v>199</v>
+      </c>
+      <c r="G166" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="H166" s="7">
         <v>46156</v>
       </c>
-      <c r="H166" s="6"/>
-      <c r="I166" s="10">
+      <c r="I166" s="6"/>
+      <c r="J166" s="10">
         <v>0.625</v>
       </c>
-      <c r="J166" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="K166" s="6"/>
+      <c r="K166" s="6" t="s">
+        <v>78</v>
+      </c>
       <c r="L166" s="6"/>
-      <c r="M166" s="8"/>
+      <c r="M166" s="6"/>
       <c r="N166" s="8"/>
-    </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O166" s="8"/>
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A167" s="6">
         <v>2</v>
       </c>
@@ -6722,29 +7192,32 @@
         <v>15</v>
       </c>
       <c r="E167" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F167" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="G167" s="7">
+        <v>200</v>
+      </c>
+      <c r="G167" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="H167" s="7">
         <v>46163</v>
       </c>
-      <c r="H167" s="10">
+      <c r="I167" s="10">
         <v>0.29166666666666669</v>
       </c>
-      <c r="I167" s="10">
+      <c r="J167" s="10">
         <v>0.33333333333333331</v>
       </c>
-      <c r="J167" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="K167" s="6"/>
+      <c r="K167" s="6" t="s">
+        <v>78</v>
+      </c>
       <c r="L167" s="6"/>
-      <c r="M167" s="8"/>
+      <c r="M167" s="6"/>
       <c r="N167" s="8"/>
-    </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O167" s="8"/>
+    </row>
+    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A168" s="6">
         <v>2</v>
       </c>
@@ -6756,29 +7229,32 @@
         <v>15</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F168" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="G168" s="7">
+        <v>201</v>
+      </c>
+      <c r="G168" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="H168" s="7">
         <v>46164</v>
       </c>
-      <c r="H168" s="6"/>
-      <c r="I168" s="10">
+      <c r="I168" s="6"/>
+      <c r="J168" s="10">
         <v>0.375</v>
       </c>
-      <c r="J168" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="K168" s="6"/>
+      <c r="K168" s="6" t="s">
+        <v>78</v>
+      </c>
       <c r="L168" s="6"/>
-      <c r="M168" s="8"/>
-      <c r="N168" s="8" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M168" s="6"/>
+      <c r="N168" s="8"/>
+      <c r="O168" s="8" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A169" s="6">
         <v>3</v>
       </c>
@@ -6787,34 +7263,37 @@
         <v>14</v>
       </c>
       <c r="D169" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="E169" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="F169" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="E169" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="F169" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="G169" s="7">
+      <c r="G169" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="H169" s="7">
         <v>46167</v>
       </c>
-      <c r="H169" s="10">
+      <c r="I169" s="10">
         <v>0.22916666666666666</v>
       </c>
-      <c r="I169" s="10">
+      <c r="J169" s="10">
         <v>0.5625</v>
       </c>
-      <c r="J169" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="K169" s="6"/>
+      <c r="K169" s="6" t="s">
+        <v>78</v>
+      </c>
       <c r="L169" s="6"/>
-      <c r="M169" s="8"/>
-      <c r="N169" s="8" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M169" s="6"/>
+      <c r="N169" s="8"/>
+      <c r="O169" s="8" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A170" s="6">
         <v>3</v>
       </c>
@@ -6826,31 +7305,34 @@
         <v>15</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F170" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="G170" s="13">
+        <v>204</v>
+      </c>
+      <c r="G170" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="H170" s="13">
         <v>46170</v>
       </c>
-      <c r="H170" s="10">
+      <c r="I170" s="10">
         <v>0.33333333333333331</v>
       </c>
-      <c r="I170" s="14">
+      <c r="J170" s="14">
         <v>0.41666666666666669</v>
       </c>
-      <c r="J170" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="K170" s="6"/>
+      <c r="K170" s="6" t="s">
+        <v>78</v>
+      </c>
       <c r="L170" s="6"/>
-      <c r="M170" s="8"/>
-      <c r="N170" s="8" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M170" s="6"/>
+      <c r="N170" s="8"/>
+      <c r="O170" s="8" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A171" s="6">
         <v>3</v>
       </c>
@@ -6859,109 +7341,98 @@
         <v>14</v>
       </c>
       <c r="D171" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E171" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F171" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="G171" s="7">
+        <v>205</v>
+      </c>
+      <c r="G171" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="H171" s="7">
         <v>46174</v>
       </c>
-      <c r="H171" s="10">
+      <c r="I171" s="10">
         <v>0.64583333333333337</v>
       </c>
-      <c r="I171" s="10">
+      <c r="J171" s="10">
         <v>0.72916666666666663</v>
       </c>
-      <c r="J171" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="K171" s="6"/>
+      <c r="K171" s="6" t="s">
+        <v>78</v>
+      </c>
       <c r="L171" s="6"/>
-      <c r="M171" s="8"/>
+      <c r="M171" s="6"/>
       <c r="N171" s="8"/>
-    </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O171" s="8"/>
+    </row>
+    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A172" s="6">
         <v>0</v>
       </c>
       <c r="B172" s="6"/>
       <c r="C172" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D172" s="6" t="s">
         <v>15</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F172" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="G172" s="6"/>
+        <v>143</v>
+      </c>
+      <c r="G172" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H172" s="6"/>
       <c r="I172" s="6"/>
-      <c r="J172" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="K172" s="6"/>
+      <c r="J172" s="6"/>
+      <c r="K172" s="6" t="s">
+        <v>314</v>
+      </c>
       <c r="L172" s="6"/>
-      <c r="M172" s="8"/>
+      <c r="M172" s="6"/>
       <c r="N172" s="8"/>
-    </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O172" s="8"/>
+    </row>
+    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A173" s="6">
         <v>0</v>
       </c>
       <c r="B173" s="6"/>
       <c r="C173" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D173" s="6" t="s">
         <v>15</v>
       </c>
       <c r="E173" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F173" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="G173" s="6"/>
+        <v>144</v>
+      </c>
+      <c r="G173" s="6" t="s">
+        <v>321</v>
+      </c>
       <c r="H173" s="6"/>
       <c r="I173" s="6"/>
-      <c r="J173" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="K173" s="6"/>
+      <c r="J173" s="6"/>
+      <c r="K173" s="6" t="s">
+        <v>314</v>
+      </c>
       <c r="L173" s="6"/>
-      <c r="M173" s="8"/>
+      <c r="M173" s="6"/>
       <c r="N173" s="8"/>
-    </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A174" s="16" t="s">
-        <v>324</v>
-      </c>
-      <c r="B174" s="16"/>
-      <c r="C174" s="16"/>
-      <c r="D174" s="16"/>
-      <c r="E174" s="16"/>
-      <c r="F174" s="16">
-        <v>172</v>
-      </c>
-      <c r="G174" s="16"/>
-      <c r="H174" s="17"/>
-      <c r="I174" s="17"/>
-      <c r="J174" s="16"/>
-      <c r="K174" s="16"/>
-      <c r="L174" s="16"/>
-      <c r="M174" s="18"/>
-      <c r="N174" s="18"/>
+      <c r="O173" s="8"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:N173">
+  <conditionalFormatting sqref="K2:O173">
     <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
       <formula>"Impl. Cancelada"</formula>
     </cfRule>

--- a/archivos/BD_Dashboard.xlsx
+++ b/archivos/BD_Dashboard.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mexscitum-my.sharepoint.com/personal/erik_torres_scitum_com_mx/Documents/Documentos/Proyectos/AEROMEXICO/17471 - PA ION/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mexscitum-my.sharepoint.com/personal/erik_torres_scitum_com_mx/Documents/Documentos/ETP/GitHub/SCITUM-AMX/archivos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="69" documentId="11_F25DC773A252ABDACC1048E8499F6DC65BDE58F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78A1AA4B-CE87-4E4F-A87C-FA78CAEE5368}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="11_F25DC773A252ABDACC1048E8499F6DC65BDE58F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0F907C1-7661-4B2A-B37B-A4E596B1FA6D}"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="10240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inventario SDWAN &amp; FW" sheetId="2" r:id="rId1"/>
@@ -46,7 +46,7 @@
     <author>Erik Alejandro Torres Piña</author>
   </authors>
   <commentList>
-    <comment ref="F43" authorId="0" shapeId="0" xr:uid="{F99C63D2-BA4B-429A-B8DC-F93333A314E6}">
+    <comment ref="F47" authorId="0" shapeId="0" xr:uid="{7CC6357A-B412-45CB-BD3D-D6499F9D7776}">
       <text>
         <r>
           <rPr>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1438" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1069" uniqueCount="328">
   <si>
     <t>TIER</t>
   </si>
@@ -116,9 +116,6 @@
     <t>Dependencias</t>
   </si>
   <si>
-    <t>Estatus Issue</t>
-  </si>
-  <si>
     <t>ATO Internacional</t>
   </si>
   <si>
@@ -635,9 +632,6 @@
     <t>CECAM</t>
   </si>
   <si>
-    <t>Programado</t>
-  </si>
-  <si>
     <t>Washington (IAD)</t>
   </si>
   <si>
@@ -660,9 +654,6 @@
   </si>
   <si>
     <t>San Francisco (SFO)</t>
-  </si>
-  <si>
-    <t>Pendiente</t>
   </si>
   <si>
     <t>Newark (EWR)</t>
@@ -1062,407 +1053,13 @@
     <t>Stand Alone</t>
   </si>
   <si>
-    <t>IDC</t>
-  </si>
-  <si>
-    <t># identidad</t>
-  </si>
-  <si>
-    <t>Contacto en ATO</t>
-  </si>
-  <si>
-    <t>Teléfono Contacto ATO</t>
-  </si>
-  <si>
     <t>Enlace Telmex</t>
   </si>
   <si>
-    <t>Aaron Bailey – (725)-247-5589</t>
-  </si>
-  <si>
-    <t>Edson Cicolani - (689) 316-4132</t>
-  </si>
-  <si>
-    <t>Joseph Kohut - (954) 648-1059 - jkohut@stillriveritsystems.com</t>
-  </si>
-  <si>
-    <t>Ramon Sanchez</t>
-  </si>
-  <si>
-    <t>Akindele Akindutire</t>
-  </si>
-  <si>
-    <t>Balram Tamang</t>
-  </si>
-  <si>
-    <t>Sarah Meyer</t>
-  </si>
-  <si>
-    <t>George Allotey</t>
-  </si>
-  <si>
-    <t>Jesus Angel Vera Martinez</t>
-  </si>
-  <si>
     <t>SI</t>
   </si>
   <si>
-    <t>Ricardo García Cervantes</t>
-  </si>
-  <si>
-    <t>Steven William Klein 609-556-2236</t>
-  </si>
-  <si>
-    <t>****1514</t>
-  </si>
-  <si>
-    <t>Jorge Carpio Olmos +18098474546</t>
-  </si>
-  <si>
-    <t>402-1109783-3</t>
-  </si>
-  <si>
-    <t>JORGE VAZQUEZ
-Duty Manager</t>
-  </si>
-  <si>
-    <t>(702)237 4037
-(702)328 9012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Martha Liliana Gil </t>
-  </si>
-  <si>
-    <t>(321)945-4696</t>
-  </si>
-  <si>
-    <t>Jose Garden</t>
-  </si>
-  <si>
-    <t>(305) 450-3932</t>
-  </si>
-  <si>
-    <t>Alejandra Alfaro</t>
-  </si>
-  <si>
-    <t>832-453-1240</t>
-  </si>
-  <si>
-    <t>HERCY CASTILLO
-Duty Manager</t>
-  </si>
-  <si>
-    <t>(514)266 6274
-(514)617 7774</t>
-  </si>
-  <si>
-    <t>Said German</t>
-  </si>
-  <si>
-    <t>(832) 287-7841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SANTIAGO LOAIZA SUESCA </t>
-  </si>
-  <si>
-    <t>+57 322 3686761</t>
-  </si>
-  <si>
-    <t>Andrea Julissa Madrid</t>
-  </si>
-  <si>
-    <t>346-563-5011</t>
-  </si>
-  <si>
-    <t>Elizabeth Arceo</t>
-  </si>
-  <si>
-    <t>(562)541 4005</t>
-  </si>
-  <si>
-    <t>Luis Alejandrez</t>
-  </si>
-  <si>
-    <t>+1(801)-941-8973</t>
-  </si>
-  <si>
-    <t>Cesar Napoleon Alvarenga Diaz</t>
-  </si>
-  <si>
-    <t>684-839-2883</t>
-  </si>
-  <si>
-    <t>DIANA CERON</t>
-  </si>
-  <si>
-    <t>503 7749 5641</t>
-  </si>
-  <si>
-    <t>FRANCIS ANTONIO VLASSOPOULOS</t>
-  </si>
-  <si>
-    <t>+1 (849) 456-4085</t>
-  </si>
-  <si>
-    <t>DIEGO GABRIEL SALAMANCA LEAÑO</t>
-  </si>
-  <si>
-    <t>+57 310 7953708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IVONNE ESPERANZA CHAPARRO CHICA </t>
-  </si>
-  <si>
-    <t>57-3187082766</t>
-  </si>
-  <si>
-    <t>Jessica Dinora Bobadilla
-Edwin Montero</t>
-  </si>
-  <si>
-    <t>832-731-2136
-(773) 706-5939</t>
-  </si>
-  <si>
-    <t>+506 8909 9019</t>
-  </si>
-  <si>
-    <t>CARLOS RAFAEL SARDA</t>
-  </si>
-  <si>
-    <t>502 5697 8364</t>
-  </si>
-  <si>
-    <t>FABIOLA BARONI</t>
-  </si>
-  <si>
-    <t>51 955 339 868</t>
-  </si>
-  <si>
-    <t>HELEN CRISTINA CARLOTA</t>
-  </si>
-  <si>
-    <t>+55 11 99480-3717</t>
-  </si>
-  <si>
-    <t>MIGUEL BALMACEDA</t>
-  </si>
-  <si>
-    <t>505 5839 4100</t>
-  </si>
-  <si>
-    <t>ELIZABETH GONZALEZ MARIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> (57) (322) 2170458 </t>
-  </si>
-  <si>
-    <t>IVELIS NIETO</t>
-  </si>
-  <si>
-    <t>+504 9612-0369</t>
-  </si>
-  <si>
-    <t>NAMJOO KIM</t>
-  </si>
-  <si>
-    <t>82(10)-8421-0091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANUSKA SANCHEZ SABRIZ </t>
-  </si>
-  <si>
-    <t>34 610404207</t>
-  </si>
-  <si>
-    <t>TAKU SATO</t>
-  </si>
-  <si>
-    <t>81 90-5219-6039</t>
-  </si>
-  <si>
-    <t>MYNOR GARCIA
-Supervisor</t>
-  </si>
-  <si>
-    <t>(916)501 7801
-(916)388 4126</t>
-  </si>
-  <si>
-    <t>MARCELA STIA
-Duty Manager</t>
-  </si>
-  <si>
-    <t>(281)323 0060
-(669)237 8646</t>
-  </si>
-  <si>
-    <t>Juan Pablo Blanco</t>
-  </si>
-  <si>
-    <t>650-703-1375</t>
-  </si>
-  <si>
-    <t>Ivan Vukov</t>
-  </si>
-  <si>
-    <t>+1 404 384 9180</t>
-  </si>
-  <si>
-    <t>Victor Ambrosio</t>
-  </si>
-  <si>
-    <t>(213)257 4257</t>
-  </si>
-  <si>
-    <t>No encontrado</t>
-  </si>
-  <si>
-    <t>Cesar Antonio Morante Jarama</t>
-  </si>
-  <si>
-    <t>778-952-7663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rafik Benamor </t>
-  </si>
-  <si>
-    <t>00 31 (6) 14 32 98 95</t>
-  </si>
-  <si>
-    <t>SEBASTIAN ACCORINTI</t>
-  </si>
-  <si>
-    <t>54 (911) 6398 3069</t>
-  </si>
-  <si>
-    <t>FRANCOIS GALLEGO</t>
-  </si>
-  <si>
-    <t>Cel.(+33) 0626718480</t>
-  </si>
-  <si>
-    <t>GLADYS SURIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(787) 639-2685
-(787) 949-4621
-</t>
-  </si>
-  <si>
-    <t>MARGARITA VELASCO
-Supervisor</t>
-  </si>
-  <si>
-    <t>(559)835 1021
-(559)293 7737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CARLOS AGUIRRE </t>
-  </si>
-  <si>
-    <t>+53 509 27 212</t>
-  </si>
-  <si>
-    <t>Debbie Honojosa</t>
-  </si>
-  <si>
-    <t>385-267-4335</t>
-  </si>
-  <si>
-    <t>Luis Alfredo Merida</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> (801) 695-8996</t>
-  </si>
-  <si>
-    <t>Ruddy Paniagua</t>
-  </si>
-  <si>
-    <t>+1 (689) 309-2653</t>
-  </si>
-  <si>
-    <t>JUANITA CARDENAS CARDENAS</t>
-  </si>
-  <si>
-    <t>+1(689)-309-2665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MARINA JOLIC </t>
-  </si>
-  <si>
-    <t>+447 442 750079</t>
-  </si>
-  <si>
-    <t>Juan Sebastian Garnica Paredes</t>
-  </si>
-  <si>
-    <t>689-309-2661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANJULHY DOMISOL BATISTA GONZALEZ </t>
-  </si>
-  <si>
-    <t>+507 6052 5616</t>
-  </si>
-  <si>
-    <t>VERONICA DAWSON
-Duty Manager
-Duty Manager</t>
-  </si>
-  <si>
-    <t>(650)333-8156
-(415)579 8360
-(415)579 8459</t>
-  </si>
-  <si>
-    <t>Tomas Alfonso Mosquera Orozco</t>
-  </si>
-  <si>
-    <t>213-257-6378</t>
-  </si>
-  <si>
-    <t>HECTOR CERDA</t>
-  </si>
-  <si>
-    <t>+56 9 6675 7344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Karen Jannette Rimola, Paola Marcela Rodriguez
-</t>
-  </si>
-  <si>
-    <t>619-721-2787, 630-763-8811</t>
-  </si>
-  <si>
-    <t>Jose Luis Luevano</t>
-  </si>
-  <si>
-    <t>(281) 236-3964</t>
-  </si>
-  <si>
-    <t>Analia Arellanos</t>
-  </si>
-  <si>
-    <t>(303) 875-3931</t>
-  </si>
-  <si>
-    <t>DENSIS CASTILLO</t>
-  </si>
-  <si>
-    <t>+39 339 530 3102</t>
-  </si>
-  <si>
-    <t>Rene Mauricio Ramirez Arevalo</t>
-  </si>
-  <si>
-    <t>650-250-6656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLEURY PAMELA BORREL DE OLIVO </t>
-  </si>
-  <si>
-    <t>+1 849 585 6332</t>
+    <t>Se requiere llenar formulario</t>
   </si>
 </sst>
 </file>
@@ -1648,283 +1245,13 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="38">
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFA6C9EC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFBE2D5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD0D0D0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFA6C9EC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFBE2D5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD0D0D0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFA6C9EC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFBE2D5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD0D0D0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="11">
     <dxf>
       <font>
         <color rgb="FF000000"/>
@@ -2073,8 +1400,8 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Estilo de tabla 1" pivot="0" count="2" xr9:uid="{91CECC61-D972-4E77-B7C8-EE0397AA0D98}">
-      <tableStyleElement type="wholeTable" dxfId="37"/>
-      <tableStyleElement type="headerRow" dxfId="36"/>
+      <tableStyleElement type="wholeTable" dxfId="10"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -2354,7 +1681,7 @@
   <sheetPr>
     <tabColor theme="5" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:T174"/>
+  <dimension ref="A1:O174"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.140625" bestFit="1" customWidth="1"/>
@@ -2362,12 +1689,11 @@
     <col min="3" max="3" width="22.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="44.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.85546875" customWidth="1"/>
     <col min="7" max="7" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -2387,7 +1713,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>6</v>
@@ -2411,43 +1737,28 @@
         <v>12</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="R1" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="S1" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="T1" s="4" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>2</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>16</v>
-      </c>
       <c r="G2" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H2" s="6">
         <v>46210</v>
@@ -2457,45 +1768,34 @@
         <v>0.625</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
       <c r="N2" s="7" t="s">
-        <v>324</v>
-      </c>
-      <c r="O2" s="7"/>
-      <c r="P2" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5" t="s">
-        <v>348</v>
-      </c>
-      <c r="S2" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="T2" s="5"/>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+        <v>321</v>
+      </c>
+      <c r="O2" s="5"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>1</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>15</v>
-      </c>
       <c r="E3" s="5" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H3" s="6">
         <v>46211</v>
@@ -2505,45 +1805,34 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="L3" s="5"/>
       <c r="M3" s="5"/>
       <c r="N3" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="O3" s="7"/>
-      <c r="P3" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="S3" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="T3" s="5"/>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+        <v>322</v>
+      </c>
+      <c r="O3" s="5"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>1</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>15</v>
-      </c>
       <c r="E4" s="5" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H4" s="6">
         <v>46204</v>
@@ -2553,6145 +1842,4784 @@
         <v>0.875</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="L4" s="6">
         <v>46182</v>
       </c>
       <c r="M4" s="6"/>
       <c r="N4" s="7" t="s">
-        <v>326</v>
-      </c>
-      <c r="O4" s="7"/>
-      <c r="P4" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="S4" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="T4" s="5"/>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+      <c r="O4" s="5"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>1</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="H5" s="1"/>
+        <v>319</v>
+      </c>
+      <c r="H5" s="5"/>
       <c r="I5" s="5"/>
-      <c r="J5" s="3"/>
+      <c r="J5" s="5"/>
       <c r="K5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
+        <v>17</v>
+      </c>
+      <c r="L5" s="6">
+        <v>46189</v>
+      </c>
+      <c r="M5" s="5">
+        <v>1.01</v>
+      </c>
       <c r="N5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="O5" s="7"/>
-      <c r="P5" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="Q5" s="5"/>
-      <c r="R5" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="S5" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="T5" s="5"/>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+      <c r="O5" s="5"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L6" s="6">
         <v>46189</v>
       </c>
       <c r="M6" s="5">
-        <v>1.1000000000000001</v>
+        <v>1.02</v>
       </c>
       <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
-      <c r="R6" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="S6" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="T6" s="5"/>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O6" s="5"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>2</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>33</v>
-      </c>
       <c r="G7" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
       <c r="K7" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L7" s="6">
         <v>46189</v>
       </c>
       <c r="M7" s="5">
-        <v>1.3</v>
+        <v>1.03</v>
       </c>
       <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="S7" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="T7" s="5"/>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O7" s="5"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>3</v>
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
       <c r="K8" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L8" s="6">
         <v>46189</v>
       </c>
       <c r="M8" s="5">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="5"/>
-      <c r="R8" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="S8" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="T8" s="5"/>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O8" s="5"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>1</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>15</v>
-      </c>
       <c r="E9" s="5" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="H9" s="2"/>
+        <v>319</v>
+      </c>
+      <c r="H9" s="1"/>
       <c r="I9" s="5"/>
       <c r="J9" s="3"/>
       <c r="K9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L9" s="6">
-        <v>46182</v>
-      </c>
-      <c r="M9" s="6"/>
+        <v>17</v>
+      </c>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
       <c r="N9" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="O9" s="7"/>
-      <c r="P9" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="Q9" s="5"/>
-      <c r="R9" s="5" t="s">
-        <v>362</v>
-      </c>
-      <c r="S9" s="5" t="s">
-        <v>363</v>
-      </c>
-      <c r="T9" s="5"/>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="O9" s="5"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>1</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>15</v>
-      </c>
       <c r="E10" s="5" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="H10" s="1"/>
+        <v>319</v>
+      </c>
+      <c r="H10" s="2"/>
       <c r="I10" s="5"/>
       <c r="J10" s="3"/>
       <c r="K10" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L10" s="6">
         <v>46182</v>
       </c>
       <c r="M10" s="6"/>
       <c r="N10" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="O10" s="7"/>
-      <c r="P10" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="Q10" s="5"/>
-      <c r="R10" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="S10" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="T10" s="5"/>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+        <v>312</v>
+      </c>
+      <c r="O10" s="5"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>15</v>
-      </c>
       <c r="E11" s="5" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="H11" s="2"/>
+        <v>319</v>
+      </c>
+      <c r="H11" s="1"/>
       <c r="I11" s="5"/>
       <c r="J11" s="3"/>
       <c r="K11" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
+        <v>17</v>
+      </c>
+      <c r="L11" s="6">
+        <v>46182</v>
+      </c>
+      <c r="M11" s="6"/>
       <c r="N11" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="O11" s="7"/>
-      <c r="P11" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="Q11" s="5"/>
-      <c r="R11" s="5" t="s">
-        <v>366</v>
-      </c>
-      <c r="S11" s="5" t="s">
-        <v>367</v>
-      </c>
-      <c r="T11" s="5"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+      <c r="O11" s="5"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="E12" s="5" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="H12" s="5"/>
+        <v>319</v>
+      </c>
+      <c r="H12" s="2"/>
       <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
+      <c r="J12" s="3"/>
       <c r="K12" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L12" s="6">
-        <v>46182</v>
-      </c>
-      <c r="M12" s="6"/>
+        <v>17</v>
+      </c>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
       <c r="N12" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="O12" s="7"/>
-      <c r="P12" s="5"/>
-      <c r="Q12" s="5"/>
-      <c r="R12" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="S12" s="5" t="s">
-        <v>369</v>
-      </c>
-      <c r="T12" s="5"/>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+        <v>316</v>
+      </c>
+      <c r="O12" s="5"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>3</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D13" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E13" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>35</v>
-      </c>
       <c r="G13" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
       <c r="K13" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L13" s="6">
         <v>46189</v>
       </c>
       <c r="M13" s="5">
-        <v>1.4</v>
+        <v>1.04</v>
       </c>
       <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="5"/>
-      <c r="R13" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="S13" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="T13" s="5"/>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O13" s="5"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>3</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D14" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>37</v>
-      </c>
       <c r="G14" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
       <c r="K14" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L14" s="6">
         <v>46189</v>
       </c>
       <c r="M14" s="5">
-        <v>1.5</v>
+        <v>1.05</v>
       </c>
       <c r="N14" s="7"/>
-      <c r="O14" s="7"/>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="5"/>
-      <c r="R14" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="S14" s="5" t="s">
-        <v>373</v>
-      </c>
-      <c r="T14" s="5"/>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O14" s="5"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="5"/>
       <c r="K15" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L15" s="6">
-        <v>46189</v>
-      </c>
-      <c r="M15" s="5">
-        <v>1.6</v>
-      </c>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="5"/>
-      <c r="R15" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="S15" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="T15" s="5"/>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+        <v>46182</v>
+      </c>
+      <c r="M15" s="6"/>
+      <c r="N15" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="O15" s="5"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>1</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>30</v>
-      </c>
       <c r="E16" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>56</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
       <c r="J16" s="5"/>
       <c r="K16" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="L16" s="5"/>
       <c r="M16" s="5">
-        <v>2.1</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="5"/>
-      <c r="R16" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="S16" s="5" t="s">
-        <v>377</v>
-      </c>
-      <c r="T16" s="5"/>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O16" s="5"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
       <c r="K17" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="L17" s="5"/>
       <c r="M17" s="5">
-        <v>2.8</v>
+        <v>2.02</v>
       </c>
       <c r="N17" s="7"/>
-      <c r="O17" s="7"/>
-      <c r="P17" s="5"/>
-      <c r="Q17" s="5"/>
-      <c r="R17" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="S17" s="5" t="s">
-        <v>379</v>
-      </c>
-      <c r="T17" s="5"/>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O17" s="5"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
       <c r="J18" s="5"/>
       <c r="K18" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="L18" s="5"/>
-      <c r="M18" s="14">
-        <v>2.1</v>
+      <c r="M18" s="5">
+        <v>2.0299999999999998</v>
       </c>
       <c r="N18" s="7"/>
-      <c r="O18" s="7"/>
-      <c r="P18" s="5"/>
-      <c r="Q18" s="5"/>
-      <c r="R18" s="5">
-        <v>0</v>
-      </c>
-      <c r="S18" s="5" t="s">
-        <v>380</v>
-      </c>
-      <c r="T18" s="5"/>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O18" s="5"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
       <c r="J19" s="5"/>
       <c r="K19" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="L19" s="5"/>
       <c r="M19" s="5">
-        <v>2.2999999999999998</v>
+        <v>2.04</v>
       </c>
       <c r="N19" s="7"/>
-      <c r="O19" s="7"/>
-      <c r="P19" s="5"/>
-      <c r="Q19" s="5"/>
-      <c r="R19" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="S19" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="T19" s="5"/>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O19" s="5"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>2</v>
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D20" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="F20" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="E20" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>63</v>
-      </c>
       <c r="G20" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
       <c r="J20" s="5"/>
       <c r="K20" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="L20" s="5"/>
       <c r="M20" s="5">
-        <v>2.5</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="N20" s="7"/>
-      <c r="O20" s="7"/>
-      <c r="P20" s="5"/>
-      <c r="Q20" s="5"/>
-      <c r="R20" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="S20" s="5" t="s">
-        <v>384</v>
-      </c>
-      <c r="T20" s="5"/>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O20" s="5"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>2</v>
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D21" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="F21" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E21" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>65</v>
-      </c>
       <c r="G21" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
       <c r="J21" s="5"/>
       <c r="K21" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="L21" s="5"/>
       <c r="M21" s="5">
-        <v>2.2000000000000002</v>
+        <v>2.06</v>
       </c>
       <c r="N21" s="7"/>
-      <c r="O21" s="7"/>
-      <c r="P21" s="5"/>
-      <c r="Q21" s="5"/>
-      <c r="R21" s="5" t="s">
-        <v>385</v>
-      </c>
-      <c r="S21" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="T21" s="5"/>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O21" s="5"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
       <c r="J22" s="5"/>
       <c r="K22" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="L22" s="5"/>
       <c r="M22" s="5">
-        <v>2.7</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="N22" s="7"/>
-      <c r="O22" s="7"/>
-      <c r="P22" s="5"/>
-      <c r="Q22" s="5"/>
-      <c r="R22" s="5" t="s">
-        <v>387</v>
-      </c>
-      <c r="S22" s="5" t="s">
-        <v>388</v>
-      </c>
-      <c r="T22" s="5"/>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O22" s="5"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
       <c r="J23" s="5"/>
       <c r="K23" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="L23" s="5"/>
-      <c r="M23" s="5">
-        <v>2.6</v>
+      <c r="M23" s="14">
+        <v>2.08</v>
       </c>
       <c r="N23" s="7"/>
-      <c r="O23" s="7"/>
-      <c r="P23" s="5"/>
-      <c r="Q23" s="5"/>
-      <c r="R23" s="5" t="s">
-        <v>389</v>
-      </c>
-      <c r="S23" s="5" t="s">
-        <v>390</v>
-      </c>
-      <c r="T23" s="5"/>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O23" s="5"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
       <c r="J24" s="5"/>
       <c r="K24" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="L24" s="5"/>
       <c r="M24" s="5">
-        <v>2.9</v>
+        <v>2.09</v>
       </c>
       <c r="N24" s="7"/>
-      <c r="O24" s="7"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="5"/>
-      <c r="R24" s="5" t="s">
-        <v>391</v>
-      </c>
-      <c r="S24" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="T24" s="5"/>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O24" s="5"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>3</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D25" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="F25" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E25" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>72</v>
-      </c>
       <c r="G25" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
       <c r="J25" s="5"/>
       <c r="K25" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="L25" s="5"/>
-      <c r="M25" s="5">
-        <v>2.4</v>
+      <c r="M25" s="14">
+        <v>2.1</v>
       </c>
       <c r="N25" s="7"/>
-      <c r="O25" s="7"/>
-      <c r="P25" s="5"/>
-      <c r="Q25" s="5"/>
-      <c r="R25" s="5" t="s">
-        <v>393</v>
-      </c>
-      <c r="S25" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="T25" s="5"/>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O25" s="5"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>1</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D26" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="F26" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="E26" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>146</v>
-      </c>
       <c r="G26" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
       <c r="J26" s="5"/>
       <c r="K26" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="L26" s="5"/>
       <c r="M26" s="5">
-        <v>3.1</v>
+        <v>3.01</v>
       </c>
       <c r="N26" s="7"/>
-      <c r="O26" s="7"/>
-      <c r="P26" s="5"/>
-      <c r="Q26" s="5"/>
-      <c r="R26" s="5" t="s">
-        <v>395</v>
-      </c>
-      <c r="S26" s="5" t="s">
-        <v>396</v>
-      </c>
-      <c r="T26" s="5"/>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O26" s="5"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>3</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D27" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="F27" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="E27" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>159</v>
-      </c>
       <c r="G27" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H27" s="5"/>
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
       <c r="K27" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="L27" s="5"/>
       <c r="M27" s="5">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="N27" s="7"/>
-      <c r="O27" s="7"/>
-      <c r="P27" s="5"/>
-      <c r="Q27" s="5"/>
-      <c r="R27" s="5" t="s">
-        <v>397</v>
-      </c>
-      <c r="S27" s="5" t="s">
-        <v>398</v>
-      </c>
-      <c r="T27" s="5"/>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O27" s="5"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>3</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D28" s="5" t="s">
-        <v>15</v>
-      </c>
       <c r="E28" s="5" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H28" s="8"/>
       <c r="I28" s="5"/>
       <c r="J28" s="5"/>
       <c r="K28" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="L28" s="5"/>
       <c r="M28" s="5">
-        <v>3.3</v>
+        <v>3.03</v>
       </c>
       <c r="N28" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="O28" s="7"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="5"/>
-      <c r="R28" s="5" t="s">
-        <v>399</v>
-      </c>
-      <c r="S28" s="5" t="s">
-        <v>400</v>
-      </c>
-      <c r="T28" s="5"/>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+      <c r="O28" s="5"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>2</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D29" s="5" t="s">
-        <v>15</v>
-      </c>
       <c r="E29" s="5" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H29" s="8"/>
       <c r="I29" s="5"/>
       <c r="J29" s="5"/>
       <c r="K29" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="L29" s="5"/>
       <c r="M29" s="5">
-        <v>3.4</v>
+        <v>3.04</v>
       </c>
       <c r="N29" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="O29" s="7"/>
-      <c r="P29" s="5"/>
-      <c r="Q29" s="5"/>
-      <c r="R29" s="5" t="s">
-        <v>401</v>
-      </c>
-      <c r="S29" s="5" t="s">
-        <v>402</v>
-      </c>
-      <c r="T29" s="5"/>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+        <v>313</v>
+      </c>
+      <c r="O29" s="5"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>3</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>15</v>
-      </c>
       <c r="E30" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H30" s="8"/>
       <c r="I30" s="5"/>
       <c r="J30" s="5"/>
       <c r="K30" s="5" t="s">
-        <v>40</v>
+        <v>308</v>
       </c>
       <c r="L30" s="5"/>
-      <c r="M30" s="5"/>
+      <c r="M30" s="5">
+        <v>4.01</v>
+      </c>
       <c r="N30" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="O30" s="7"/>
-      <c r="P30" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="Q30" s="5"/>
-      <c r="R30" s="5" t="s">
-        <v>403</v>
-      </c>
-      <c r="S30" s="5" t="s">
-        <v>404</v>
-      </c>
-      <c r="T30" s="5"/>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+      <c r="O30" s="5"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5" t="s">
-        <v>14</v>
+        <v>84</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>222</v>
+        <v>266</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>45</v>
+        <v>126</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="H31" s="8"/>
+        <v>324</v>
+      </c>
+      <c r="H31" s="5"/>
       <c r="I31" s="5"/>
       <c r="J31" s="5"/>
       <c r="K31" s="5" t="s">
-        <v>40</v>
+        <v>308</v>
       </c>
       <c r="L31" s="5"/>
-      <c r="M31" s="5"/>
-      <c r="N31" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="O31" s="7"/>
-      <c r="P31" s="5"/>
-      <c r="Q31" s="5"/>
-      <c r="R31" s="5" t="s">
-        <v>405</v>
-      </c>
-      <c r="S31" s="5" t="s">
-        <v>406</v>
-      </c>
-      <c r="T31" s="5"/>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="M31" s="5">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="N31" s="7"/>
+      <c r="O31" s="5"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>3</v>
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5" t="s">
-        <v>14</v>
+        <v>84</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>224</v>
+        <v>268</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>48</v>
+        <v>129</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="H32" s="8"/>
+        <v>324</v>
+      </c>
+      <c r="H32" s="5"/>
       <c r="I32" s="5"/>
-      <c r="J32" s="9"/>
+      <c r="J32" s="5"/>
       <c r="K32" s="5" t="s">
-        <v>40</v>
+        <v>308</v>
       </c>
       <c r="L32" s="5"/>
-      <c r="M32" s="5"/>
-      <c r="N32" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="O32" s="7"/>
-      <c r="P32" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="Q32" s="5"/>
-      <c r="R32" s="5" t="s">
-        <v>407</v>
-      </c>
-      <c r="S32" s="5" t="s">
-        <v>408</v>
-      </c>
-      <c r="T32" s="5"/>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="M32" s="5">
+        <v>4.03</v>
+      </c>
+      <c r="N32" s="7"/>
+      <c r="O32" s="5"/>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>226</v>
+        <v>291</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>55</v>
+        <v>163</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="H33" s="8"/>
+        <v>324</v>
+      </c>
+      <c r="H33" s="5"/>
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
       <c r="K33" s="5" t="s">
-        <v>51</v>
+        <v>308</v>
       </c>
       <c r="L33" s="5"/>
-      <c r="M33" s="5"/>
+      <c r="M33" s="5">
+        <v>4.04</v>
+      </c>
       <c r="N33" s="7"/>
-      <c r="O33" s="7"/>
-      <c r="P33" s="5"/>
-      <c r="Q33" s="5"/>
-      <c r="R33" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S33" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T33" s="5"/>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O33" s="5"/>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5" t="s">
-        <v>14</v>
+        <v>84</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>225</v>
+        <v>273</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>50</v>
+        <v>134</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
       <c r="J34" s="5"/>
       <c r="K34" s="5" t="s">
-        <v>51</v>
+        <v>308</v>
       </c>
       <c r="L34" s="5"/>
-      <c r="M34" s="5"/>
-      <c r="N34" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="O34" s="7"/>
-      <c r="P34" s="5"/>
-      <c r="Q34" s="5"/>
-      <c r="R34" s="5" t="s">
-        <v>410</v>
-      </c>
-      <c r="S34" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="T34" s="5"/>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="M34" s="5">
+        <v>4.05</v>
+      </c>
+      <c r="N34" s="7"/>
+      <c r="O34" s="5"/>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="H35" s="5"/>
+        <v>319</v>
+      </c>
+      <c r="H35" s="8"/>
       <c r="I35" s="5"/>
       <c r="J35" s="5"/>
       <c r="K35" s="5" t="s">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="L35" s="5"/>
       <c r="M35" s="5"/>
-      <c r="N35" s="7"/>
-      <c r="O35" s="7"/>
-      <c r="P35" s="5"/>
-      <c r="Q35" s="5"/>
-      <c r="R35" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S35" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T35" s="5" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="N35" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="O35" s="5"/>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>244</v>
+        <v>221</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="H36" s="5"/>
+        <v>324</v>
+      </c>
+      <c r="H36" s="8"/>
       <c r="I36" s="5"/>
-      <c r="J36" s="5"/>
+      <c r="J36" s="9"/>
       <c r="K36" s="5" t="s">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="L36" s="5"/>
       <c r="M36" s="5"/>
-      <c r="N36" s="7"/>
-      <c r="O36" s="7"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="5"/>
-      <c r="R36" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S36" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T36" s="5" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="N36" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="O36" s="5"/>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="D37" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="F37" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E37" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>115</v>
-      </c>
       <c r="G37" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="H37" s="5"/>
+        <v>319</v>
+      </c>
+      <c r="H37" s="8"/>
       <c r="I37" s="5"/>
       <c r="J37" s="5"/>
       <c r="K37" s="5" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="L37" s="5"/>
       <c r="M37" s="5"/>
       <c r="N37" s="7"/>
-      <c r="O37" s="7"/>
-      <c r="P37" s="5"/>
-      <c r="Q37" s="5"/>
-      <c r="R37" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S37" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T37" s="5" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O37" s="5"/>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H38" s="5"/>
       <c r="I38" s="5"/>
       <c r="J38" s="5"/>
       <c r="K38" s="5" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="L38" s="5"/>
       <c r="M38" s="5"/>
-      <c r="N38" s="7"/>
-      <c r="O38" s="7"/>
-      <c r="P38" s="5"/>
-      <c r="Q38" s="5"/>
-      <c r="R38" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S38" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T38" s="5"/>
-    </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="N38" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="O38" s="5"/>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>0</v>
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H39" s="5"/>
       <c r="I39" s="5"/>
       <c r="J39" s="5"/>
       <c r="K39" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L39" s="5"/>
       <c r="M39" s="5"/>
       <c r="N39" s="7"/>
-      <c r="O39" s="7"/>
-      <c r="P39" s="5"/>
-      <c r="Q39" s="5"/>
-      <c r="R39" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S39" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T39" s="5"/>
-    </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O39" s="5" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
       <c r="J40" s="5"/>
       <c r="K40" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L40" s="5"/>
       <c r="M40" s="5"/>
       <c r="N40" s="7"/>
-      <c r="O40" s="7"/>
-      <c r="P40" s="5"/>
-      <c r="Q40" s="5"/>
-      <c r="R40" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S40" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T40" s="5"/>
-    </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O40" s="5" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H41" s="5"/>
       <c r="I41" s="5"/>
       <c r="J41" s="5"/>
       <c r="K41" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L41" s="5"/>
       <c r="M41" s="5"/>
       <c r="N41" s="7"/>
-      <c r="O41" s="7"/>
-      <c r="P41" s="5"/>
-      <c r="Q41" s="5"/>
-      <c r="R41" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S41" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T41" s="5"/>
-    </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O41" s="5" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
         <v>0</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="F42" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="D42" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F42" s="5" t="s">
-        <v>81</v>
-      </c>
       <c r="G42" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H42" s="5"/>
       <c r="I42" s="5"/>
       <c r="J42" s="5"/>
       <c r="K42" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L42" s="5"/>
       <c r="M42" s="5"/>
       <c r="N42" s="7"/>
-      <c r="O42" s="7"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="5"/>
-      <c r="R42" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S42" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T42" s="5"/>
-    </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A43" s="10">
+      <c r="O42" s="5"/>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A43" s="5">
         <v>0</v>
       </c>
       <c r="B43" s="5"/>
-      <c r="C43" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="D43" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E43" s="10" t="s">
-        <v>237</v>
-      </c>
-      <c r="F43" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="G43" s="10" t="s">
-        <v>322</v>
-      </c>
-      <c r="H43" s="10"/>
-      <c r="I43" s="10"/>
-      <c r="J43" s="10"/>
+      <c r="C43" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5"/>
+      <c r="J43" s="5"/>
       <c r="K43" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="L43" s="10"/>
-      <c r="M43" s="10"/>
-      <c r="N43" s="11"/>
-      <c r="O43" s="11"/>
-      <c r="P43" s="10"/>
-      <c r="Q43" s="10"/>
-      <c r="R43" s="10" t="s">
-        <v>409</v>
-      </c>
-      <c r="S43" s="10" t="s">
-        <v>409</v>
-      </c>
-      <c r="T43" s="10"/>
-    </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+      <c r="L43" s="5"/>
+      <c r="M43" s="5"/>
+      <c r="N43" s="7"/>
+      <c r="O43" s="5"/>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
         <v>0</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H44" s="5"/>
       <c r="I44" s="5"/>
       <c r="J44" s="5"/>
       <c r="K44" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L44" s="5"/>
       <c r="M44" s="5"/>
       <c r="N44" s="7"/>
-      <c r="O44" s="7"/>
-      <c r="P44" s="5"/>
-      <c r="Q44" s="5"/>
-      <c r="R44" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S44" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T44" s="5"/>
-    </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O44" s="5"/>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H45" s="5"/>
       <c r="I45" s="5"/>
       <c r="J45" s="5"/>
       <c r="K45" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L45" s="5"/>
       <c r="M45" s="5"/>
       <c r="N45" s="7"/>
-      <c r="O45" s="7"/>
-      <c r="P45" s="5"/>
-      <c r="Q45" s="5"/>
-      <c r="R45" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S45" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T45" s="5"/>
-    </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O45" s="5"/>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
       <c r="J46" s="5"/>
       <c r="K46" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L46" s="5"/>
       <c r="M46" s="5"/>
       <c r="N46" s="7"/>
-      <c r="O46" s="7"/>
-      <c r="P46" s="5"/>
-      <c r="Q46" s="5"/>
-      <c r="R46" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S46" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T46" s="5"/>
-    </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A47" s="5">
-        <v>1</v>
+      <c r="O46" s="5"/>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A47" s="10">
+        <v>0</v>
       </c>
       <c r="B47" s="5"/>
-      <c r="C47" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="F47" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="H47" s="5"/>
-      <c r="I47" s="5"/>
-      <c r="J47" s="5"/>
+      <c r="C47" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E47" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="G47" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="H47" s="10"/>
+      <c r="I47" s="10"/>
+      <c r="J47" s="10"/>
       <c r="K47" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="L47" s="5"/>
-      <c r="M47" s="5"/>
-      <c r="N47" s="7"/>
-      <c r="O47" s="7"/>
-      <c r="P47" s="5"/>
-      <c r="Q47" s="5"/>
-      <c r="R47" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S47" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T47" s="5"/>
-    </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+      <c r="L47" s="10"/>
+      <c r="M47" s="10"/>
+      <c r="N47" s="11"/>
+      <c r="O47" s="10"/>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H48" s="5"/>
       <c r="I48" s="5"/>
       <c r="J48" s="5"/>
       <c r="K48" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L48" s="5"/>
       <c r="M48" s="5"/>
       <c r="N48" s="7"/>
-      <c r="O48" s="7"/>
-      <c r="P48" s="5"/>
-      <c r="Q48" s="5"/>
-      <c r="R48" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S48" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T48" s="5"/>
-    </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O48" s="5"/>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
         <v>1</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="F49" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="D49" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="F49" s="5" t="s">
-        <v>90</v>
-      </c>
       <c r="G49" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H49" s="5"/>
       <c r="I49" s="5"/>
       <c r="J49" s="5"/>
       <c r="K49" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L49" s="5"/>
       <c r="M49" s="5"/>
       <c r="N49" s="7"/>
-      <c r="O49" s="7"/>
-      <c r="P49" s="5"/>
-      <c r="Q49" s="5"/>
-      <c r="R49" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S49" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T49" s="5"/>
-    </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O49" s="5"/>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
         <v>1</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H50" s="5"/>
       <c r="I50" s="5"/>
       <c r="J50" s="5"/>
       <c r="K50" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L50" s="5"/>
       <c r="M50" s="5"/>
       <c r="N50" s="7"/>
-      <c r="O50" s="7"/>
-      <c r="P50" s="5"/>
-      <c r="Q50" s="5"/>
-      <c r="R50" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S50" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T50" s="5"/>
-    </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O50" s="5"/>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
         <v>1</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H51" s="5"/>
       <c r="I51" s="5"/>
       <c r="J51" s="5"/>
       <c r="K51" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L51" s="5"/>
       <c r="M51" s="5"/>
       <c r="N51" s="7"/>
-      <c r="O51" s="7"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="5"/>
-      <c r="R51" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S51" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T51" s="5"/>
-    </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O51" s="5"/>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
         <v>1</v>
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H52" s="5"/>
       <c r="I52" s="5"/>
       <c r="J52" s="5"/>
       <c r="K52" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L52" s="5"/>
       <c r="M52" s="5"/>
       <c r="N52" s="7"/>
-      <c r="O52" s="7"/>
-      <c r="P52" s="5"/>
-      <c r="Q52" s="5"/>
-      <c r="R52" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S52" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T52" s="5"/>
-    </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O52" s="5"/>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
         <v>1</v>
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H53" s="5"/>
       <c r="I53" s="5"/>
       <c r="J53" s="5"/>
       <c r="K53" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L53" s="5"/>
       <c r="M53" s="5"/>
       <c r="N53" s="7"/>
-      <c r="O53" s="7"/>
-      <c r="P53" s="5"/>
-      <c r="Q53" s="5"/>
-      <c r="R53" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S53" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T53" s="5"/>
-    </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O53" s="5"/>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
         <v>1</v>
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H54" s="5"/>
       <c r="I54" s="5"/>
       <c r="J54" s="5"/>
       <c r="K54" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L54" s="5"/>
       <c r="M54" s="5"/>
       <c r="N54" s="7"/>
-      <c r="O54" s="7"/>
-      <c r="P54" s="5"/>
-      <c r="Q54" s="5"/>
-      <c r="R54" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S54" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T54" s="5"/>
-    </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O54" s="5"/>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
         <v>1</v>
       </c>
       <c r="B55" s="5"/>
       <c r="C55" s="5" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H55" s="5"/>
       <c r="I55" s="5"/>
       <c r="J55" s="5"/>
       <c r="K55" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L55" s="5"/>
       <c r="M55" s="5"/>
       <c r="N55" s="7"/>
-      <c r="O55" s="7"/>
-      <c r="P55" s="5"/>
-      <c r="Q55" s="5"/>
-      <c r="R55" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S55" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T55" s="5"/>
-    </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O55" s="5"/>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
         <v>1</v>
       </c>
       <c r="B56" s="5"/>
       <c r="C56" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H56" s="5"/>
       <c r="I56" s="5"/>
       <c r="J56" s="5"/>
       <c r="K56" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L56" s="5"/>
       <c r="M56" s="5"/>
       <c r="N56" s="7"/>
-      <c r="O56" s="7"/>
-      <c r="P56" s="5"/>
-      <c r="Q56" s="5"/>
-      <c r="R56" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S56" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T56" s="5"/>
-    </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O56" s="5"/>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
         <v>1</v>
       </c>
       <c r="B57" s="5"/>
       <c r="C57" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H57" s="5"/>
       <c r="I57" s="5"/>
       <c r="J57" s="5"/>
       <c r="K57" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L57" s="5"/>
       <c r="M57" s="5"/>
       <c r="N57" s="7"/>
-      <c r="O57" s="7"/>
-      <c r="P57" s="5"/>
-      <c r="Q57" s="5"/>
-      <c r="R57" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S57" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T57" s="5"/>
-    </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O57" s="5"/>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
         <v>1</v>
       </c>
       <c r="B58" s="5"/>
       <c r="C58" s="5" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H58" s="5"/>
       <c r="I58" s="5"/>
       <c r="J58" s="5"/>
       <c r="K58" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L58" s="5"/>
       <c r="M58" s="5"/>
       <c r="N58" s="7"/>
-      <c r="O58" s="7"/>
-      <c r="P58" s="5"/>
-      <c r="Q58" s="5"/>
-      <c r="R58" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S58" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T58" s="5"/>
-    </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O58" s="5"/>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
         <v>1</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H59" s="5"/>
       <c r="I59" s="5"/>
       <c r="J59" s="5"/>
       <c r="K59" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L59" s="5"/>
       <c r="M59" s="5"/>
       <c r="N59" s="7"/>
-      <c r="O59" s="7"/>
-      <c r="P59" s="5"/>
-      <c r="Q59" s="5"/>
-      <c r="R59" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S59" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T59" s="5"/>
-    </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O59" s="5"/>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
         <v>1</v>
       </c>
       <c r="B60" s="5"/>
       <c r="C60" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H60" s="5"/>
       <c r="I60" s="5"/>
       <c r="J60" s="5"/>
       <c r="K60" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L60" s="5"/>
       <c r="M60" s="5"/>
       <c r="N60" s="7"/>
-      <c r="O60" s="7"/>
-      <c r="P60" s="5"/>
-      <c r="Q60" s="5"/>
-      <c r="R60" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S60" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T60" s="5"/>
-    </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O60" s="5"/>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="5">
         <v>1</v>
       </c>
       <c r="B61" s="5"/>
       <c r="C61" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H61" s="5"/>
       <c r="I61" s="5"/>
       <c r="J61" s="5"/>
       <c r="K61" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L61" s="5"/>
       <c r="M61" s="5"/>
       <c r="N61" s="7"/>
-      <c r="O61" s="7"/>
-      <c r="P61" s="5"/>
-      <c r="Q61" s="5"/>
-      <c r="R61" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S61" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T61" s="5"/>
-    </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O61" s="5"/>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
         <v>1</v>
       </c>
       <c r="B62" s="5"/>
       <c r="C62" s="5" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H62" s="5"/>
       <c r="I62" s="5"/>
       <c r="J62" s="5"/>
       <c r="K62" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L62" s="5"/>
       <c r="M62" s="5"/>
       <c r="N62" s="7"/>
-      <c r="O62" s="7"/>
-      <c r="P62" s="5"/>
-      <c r="Q62" s="5"/>
-      <c r="R62" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S62" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T62" s="5"/>
-    </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O62" s="5"/>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="5">
         <v>1</v>
       </c>
       <c r="B63" s="5"/>
       <c r="C63" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H63" s="5"/>
       <c r="I63" s="5"/>
       <c r="J63" s="5"/>
       <c r="K63" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L63" s="5"/>
       <c r="M63" s="5"/>
       <c r="N63" s="7"/>
-      <c r="O63" s="7"/>
-      <c r="P63" s="5"/>
-      <c r="Q63" s="5"/>
-      <c r="R63" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S63" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T63" s="5"/>
-    </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O63" s="5"/>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
         <v>1</v>
       </c>
       <c r="B64" s="5"/>
       <c r="C64" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H64" s="5"/>
       <c r="I64" s="5"/>
       <c r="J64" s="5"/>
       <c r="K64" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L64" s="5"/>
       <c r="M64" s="5"/>
       <c r="N64" s="7"/>
-      <c r="O64" s="7"/>
-      <c r="P64" s="5"/>
-      <c r="Q64" s="5"/>
-      <c r="R64" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S64" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T64" s="5"/>
-    </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O64" s="5"/>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="5">
         <v>1</v>
       </c>
       <c r="B65" s="5"/>
       <c r="C65" s="5" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H65" s="5"/>
       <c r="I65" s="5"/>
       <c r="J65" s="5"/>
       <c r="K65" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L65" s="5"/>
       <c r="M65" s="5"/>
       <c r="N65" s="7"/>
-      <c r="O65" s="7"/>
-      <c r="P65" s="5"/>
-      <c r="Q65" s="5"/>
-      <c r="R65" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S65" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T65" s="5"/>
-    </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O65" s="5"/>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="5">
         <v>1</v>
       </c>
       <c r="B66" s="5"/>
       <c r="C66" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H66" s="5"/>
       <c r="I66" s="5"/>
       <c r="J66" s="5"/>
       <c r="K66" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L66" s="5"/>
       <c r="M66" s="5"/>
       <c r="N66" s="7"/>
-      <c r="O66" s="7"/>
-      <c r="P66" s="5"/>
-      <c r="Q66" s="5"/>
-      <c r="R66" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S66" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T66" s="5"/>
-    </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O66" s="5"/>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B67" s="5"/>
       <c r="C67" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D67" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="F67" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E67" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="F67" s="5" t="s">
-        <v>107</v>
-      </c>
       <c r="G67" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H67" s="5"/>
       <c r="I67" s="5"/>
       <c r="J67" s="5"/>
       <c r="K67" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L67" s="5"/>
       <c r="M67" s="5"/>
       <c r="N67" s="7"/>
-      <c r="O67" s="7"/>
-      <c r="P67" s="5"/>
-      <c r="Q67" s="5"/>
-      <c r="R67" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S67" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T67" s="5"/>
-    </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O67" s="5"/>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B68" s="5"/>
       <c r="C68" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H68" s="5"/>
       <c r="I68" s="5"/>
       <c r="J68" s="5"/>
       <c r="K68" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L68" s="5"/>
       <c r="M68" s="5"/>
       <c r="N68" s="7"/>
-      <c r="O68" s="7"/>
-      <c r="P68" s="5"/>
-      <c r="Q68" s="5"/>
-      <c r="R68" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S68" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T68" s="5"/>
-    </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O68" s="5"/>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B69" s="5"/>
       <c r="C69" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H69" s="5"/>
       <c r="I69" s="5"/>
       <c r="J69" s="5"/>
       <c r="K69" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L69" s="5"/>
       <c r="M69" s="5"/>
       <c r="N69" s="7"/>
-      <c r="O69" s="7"/>
-      <c r="P69" s="5"/>
-      <c r="Q69" s="5"/>
-      <c r="R69" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S69" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T69" s="5"/>
-    </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O69" s="5"/>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B70" s="5"/>
       <c r="C70" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H70" s="5"/>
       <c r="I70" s="5"/>
       <c r="J70" s="5"/>
       <c r="K70" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L70" s="5"/>
       <c r="M70" s="5"/>
       <c r="N70" s="7"/>
-      <c r="O70" s="7"/>
-      <c r="P70" s="5"/>
-      <c r="Q70" s="5"/>
-      <c r="R70" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S70" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T70" s="5"/>
-    </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O70" s="5"/>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="5">
         <v>2</v>
       </c>
       <c r="B71" s="5"/>
       <c r="C71" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H71" s="5"/>
       <c r="I71" s="5"/>
       <c r="J71" s="5"/>
       <c r="K71" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L71" s="5"/>
       <c r="M71" s="5"/>
       <c r="N71" s="7"/>
-      <c r="O71" s="7"/>
-      <c r="P71" s="5"/>
-      <c r="Q71" s="5"/>
-      <c r="R71" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S71" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T71" s="5"/>
-    </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O71" s="5"/>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="5">
         <v>2</v>
       </c>
       <c r="B72" s="5"/>
       <c r="C72" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H72" s="5"/>
       <c r="I72" s="5"/>
       <c r="J72" s="5"/>
       <c r="K72" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L72" s="5"/>
       <c r="M72" s="5"/>
       <c r="N72" s="7"/>
-      <c r="O72" s="7"/>
-      <c r="P72" s="5"/>
-      <c r="Q72" s="5"/>
-      <c r="R72" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S72" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T72" s="5"/>
-    </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O72" s="5"/>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="5">
         <v>2</v>
       </c>
       <c r="B73" s="5"/>
       <c r="C73" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H73" s="5"/>
       <c r="I73" s="5"/>
       <c r="J73" s="5"/>
       <c r="K73" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L73" s="5"/>
       <c r="M73" s="5"/>
       <c r="N73" s="7"/>
-      <c r="O73" s="7"/>
-      <c r="P73" s="5"/>
-      <c r="Q73" s="5"/>
-      <c r="R73" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S73" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T73" s="5"/>
-    </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O73" s="5"/>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="5">
         <v>2</v>
       </c>
       <c r="B74" s="5"/>
       <c r="C74" s="5" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H74" s="5"/>
       <c r="I74" s="5"/>
       <c r="J74" s="5"/>
       <c r="K74" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L74" s="5"/>
       <c r="M74" s="5"/>
       <c r="N74" s="7"/>
-      <c r="O74" s="7"/>
-      <c r="P74" s="5"/>
-      <c r="Q74" s="5"/>
-      <c r="R74" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S74" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T74" s="5"/>
-    </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O74" s="5"/>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="5">
         <v>2</v>
       </c>
       <c r="B75" s="5"/>
       <c r="C75" s="5" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H75" s="5"/>
       <c r="I75" s="5"/>
       <c r="J75" s="5"/>
       <c r="K75" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L75" s="5"/>
       <c r="M75" s="5"/>
       <c r="N75" s="7"/>
-      <c r="O75" s="7"/>
-      <c r="P75" s="5"/>
-      <c r="Q75" s="5"/>
-      <c r="R75" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S75" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T75" s="5"/>
-    </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O75" s="5"/>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
         <v>2</v>
       </c>
       <c r="B76" s="5"/>
       <c r="C76" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H76" s="5"/>
       <c r="I76" s="5"/>
       <c r="J76" s="5"/>
       <c r="K76" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L76" s="5"/>
       <c r="M76" s="5"/>
       <c r="N76" s="7"/>
-      <c r="O76" s="7"/>
-      <c r="P76" s="5"/>
-      <c r="Q76" s="5"/>
-      <c r="R76" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S76" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T76" s="5"/>
-    </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O76" s="5"/>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="5">
         <v>2</v>
       </c>
       <c r="B77" s="5"/>
       <c r="C77" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H77" s="5"/>
       <c r="I77" s="5"/>
       <c r="J77" s="5"/>
       <c r="K77" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L77" s="5"/>
       <c r="M77" s="5"/>
       <c r="N77" s="7"/>
-      <c r="O77" s="7"/>
-      <c r="P77" s="5"/>
-      <c r="Q77" s="5"/>
-      <c r="R77" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S77" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T77" s="5"/>
-    </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O77" s="5"/>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="5">
         <v>2</v>
       </c>
       <c r="B78" s="5"/>
       <c r="C78" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H78" s="5"/>
       <c r="I78" s="5"/>
       <c r="J78" s="5"/>
       <c r="K78" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L78" s="5"/>
       <c r="M78" s="5"/>
       <c r="N78" s="7"/>
-      <c r="O78" s="7"/>
-      <c r="P78" s="5"/>
-      <c r="Q78" s="5"/>
-      <c r="R78" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S78" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T78" s="5"/>
-    </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O78" s="5"/>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="5">
         <v>2</v>
       </c>
       <c r="B79" s="5"/>
       <c r="C79" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>260</v>
+        <v>237</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H79" s="5"/>
       <c r="I79" s="5"/>
       <c r="J79" s="5"/>
       <c r="K79" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L79" s="5"/>
       <c r="M79" s="5"/>
       <c r="N79" s="7"/>
-      <c r="O79" s="7"/>
-      <c r="P79" s="5"/>
-      <c r="Q79" s="5"/>
-      <c r="R79" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S79" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T79" s="5"/>
-    </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O79" s="5"/>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="5">
         <v>2</v>
       </c>
       <c r="B80" s="5"/>
       <c r="C80" s="5" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>261</v>
+        <v>234</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H80" s="5"/>
       <c r="I80" s="5"/>
       <c r="J80" s="5"/>
       <c r="K80" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L80" s="5"/>
       <c r="M80" s="5"/>
       <c r="N80" s="7"/>
-      <c r="O80" s="7"/>
-      <c r="P80" s="5"/>
-      <c r="Q80" s="5"/>
-      <c r="R80" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S80" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T80" s="5"/>
-    </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O80" s="5"/>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="5">
         <v>2</v>
       </c>
       <c r="B81" s="5"/>
       <c r="C81" s="5" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H81" s="5"/>
       <c r="I81" s="5"/>
       <c r="J81" s="5"/>
       <c r="K81" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L81" s="5"/>
       <c r="M81" s="5"/>
       <c r="N81" s="7"/>
-      <c r="O81" s="7"/>
-      <c r="P81" s="5"/>
-      <c r="Q81" s="5"/>
-      <c r="R81" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S81" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T81" s="5"/>
-    </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O81" s="5"/>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="5">
         <v>2</v>
       </c>
       <c r="B82" s="5"/>
       <c r="C82" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H82" s="5"/>
       <c r="I82" s="5"/>
       <c r="J82" s="5"/>
       <c r="K82" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L82" s="5"/>
       <c r="M82" s="5"/>
       <c r="N82" s="7"/>
-      <c r="O82" s="7"/>
-      <c r="P82" s="5"/>
-      <c r="Q82" s="5"/>
-      <c r="R82" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S82" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T82" s="5"/>
-    </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O82" s="5"/>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="5">
         <v>2</v>
       </c>
       <c r="B83" s="5"/>
       <c r="C83" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H83" s="5"/>
       <c r="I83" s="5"/>
       <c r="J83" s="5"/>
       <c r="K83" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L83" s="5"/>
       <c r="M83" s="5"/>
       <c r="N83" s="7"/>
-      <c r="O83" s="7"/>
-      <c r="P83" s="5"/>
-      <c r="Q83" s="5"/>
-      <c r="R83" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S83" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T83" s="5"/>
-    </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O83" s="5"/>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="5">
         <v>2</v>
       </c>
       <c r="B84" s="5"/>
       <c r="C84" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H84" s="5"/>
       <c r="I84" s="5"/>
       <c r="J84" s="5"/>
       <c r="K84" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L84" s="5"/>
       <c r="M84" s="5"/>
       <c r="N84" s="7"/>
-      <c r="O84" s="7"/>
-      <c r="P84" s="5"/>
-      <c r="Q84" s="5"/>
-      <c r="R84" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S84" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T84" s="5"/>
-    </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O84" s="5"/>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="5">
         <v>2</v>
       </c>
       <c r="B85" s="5"/>
       <c r="C85" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>264</v>
+        <v>238</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H85" s="5"/>
       <c r="I85" s="5"/>
       <c r="J85" s="5"/>
       <c r="K85" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L85" s="5"/>
       <c r="M85" s="5"/>
       <c r="N85" s="7"/>
-      <c r="O85" s="7"/>
-      <c r="P85" s="5"/>
-      <c r="Q85" s="5"/>
-      <c r="R85" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S85" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T85" s="5"/>
-    </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O85" s="5"/>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="5">
         <v>2</v>
       </c>
       <c r="B86" s="5"/>
       <c r="C86" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H86" s="5"/>
       <c r="I86" s="5"/>
       <c r="J86" s="5"/>
       <c r="K86" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L86" s="5"/>
       <c r="M86" s="5"/>
       <c r="N86" s="7"/>
-      <c r="O86" s="7"/>
-      <c r="P86" s="5"/>
-      <c r="Q86" s="5"/>
-      <c r="R86" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S86" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T86" s="5"/>
-    </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O86" s="5"/>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="5">
         <v>2</v>
       </c>
       <c r="B87" s="5"/>
       <c r="C87" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H87" s="5"/>
       <c r="I87" s="5"/>
       <c r="J87" s="5"/>
       <c r="K87" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L87" s="5"/>
       <c r="M87" s="5"/>
       <c r="N87" s="7"/>
-      <c r="O87" s="7"/>
-      <c r="P87" s="5"/>
-      <c r="Q87" s="5"/>
-      <c r="R87" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S87" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T87" s="5"/>
-    </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O87" s="5"/>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="5">
         <v>2</v>
       </c>
       <c r="B88" s="5"/>
       <c r="C88" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H88" s="5"/>
       <c r="I88" s="5"/>
       <c r="J88" s="5"/>
       <c r="K88" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L88" s="5"/>
       <c r="M88" s="5"/>
       <c r="N88" s="7"/>
-      <c r="O88" s="7"/>
-      <c r="P88" s="5"/>
-      <c r="Q88" s="5"/>
-      <c r="R88" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S88" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T88" s="5"/>
-    </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O88" s="5"/>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="5">
         <v>2</v>
       </c>
       <c r="B89" s="5"/>
       <c r="C89" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H89" s="5"/>
       <c r="I89" s="5"/>
       <c r="J89" s="5"/>
       <c r="K89" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L89" s="5"/>
       <c r="M89" s="5"/>
       <c r="N89" s="7"/>
-      <c r="O89" s="7"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="5"/>
-      <c r="R89" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S89" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T89" s="5"/>
-    </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O89" s="5"/>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="5">
         <v>2</v>
       </c>
       <c r="B90" s="5"/>
       <c r="C90" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H90" s="5"/>
       <c r="I90" s="5"/>
       <c r="J90" s="5"/>
       <c r="K90" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L90" s="5"/>
       <c r="M90" s="5"/>
       <c r="N90" s="7"/>
-      <c r="O90" s="7"/>
-      <c r="P90" s="5"/>
-      <c r="Q90" s="5"/>
-      <c r="R90" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S90" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T90" s="5"/>
-    </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O90" s="5"/>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="5">
         <v>2</v>
       </c>
       <c r="B91" s="5"/>
       <c r="C91" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H91" s="5"/>
       <c r="I91" s="5"/>
       <c r="J91" s="5"/>
       <c r="K91" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L91" s="5"/>
       <c r="M91" s="5"/>
       <c r="N91" s="7"/>
-      <c r="O91" s="7"/>
-      <c r="P91" s="5"/>
-      <c r="Q91" s="5"/>
-      <c r="R91" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S91" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T91" s="5"/>
-    </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O91" s="5"/>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B92" s="5"/>
       <c r="C92" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>268</v>
+        <v>245</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G92" s="5" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="H92" s="5"/>
       <c r="I92" s="5"/>
       <c r="J92" s="5"/>
       <c r="K92" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L92" s="5"/>
       <c r="M92" s="5"/>
       <c r="N92" s="7"/>
-      <c r="O92" s="7"/>
-      <c r="P92" s="5"/>
-      <c r="Q92" s="5"/>
-      <c r="R92" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S92" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T92" s="5"/>
-    </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O92" s="5"/>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B93" s="5"/>
       <c r="C93" s="5" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="H93" s="5"/>
       <c r="I93" s="5"/>
       <c r="J93" s="5"/>
       <c r="K93" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L93" s="5"/>
       <c r="M93" s="5"/>
       <c r="N93" s="7"/>
-      <c r="O93" s="7"/>
-      <c r="P93" s="5"/>
-      <c r="Q93" s="5"/>
-      <c r="R93" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S93" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T93" s="5"/>
-    </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O93" s="5"/>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B94" s="5"/>
       <c r="C94" s="5" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>269</v>
+        <v>249</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="H94" s="5"/>
       <c r="I94" s="5"/>
       <c r="J94" s="5"/>
       <c r="K94" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L94" s="5"/>
       <c r="M94" s="5"/>
       <c r="N94" s="7"/>
-      <c r="O94" s="7"/>
-      <c r="P94" s="5"/>
-      <c r="Q94" s="5"/>
-      <c r="R94" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S94" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T94" s="5"/>
-    </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O94" s="5"/>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B95" s="5"/>
       <c r="C95" s="5" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="H95" s="5"/>
       <c r="I95" s="5"/>
       <c r="J95" s="5"/>
       <c r="K95" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L95" s="5"/>
       <c r="M95" s="5"/>
       <c r="N95" s="7"/>
-      <c r="O95" s="7"/>
-      <c r="P95" s="5"/>
-      <c r="Q95" s="5"/>
-      <c r="R95" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S95" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T95" s="5"/>
-    </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O95" s="5"/>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="5">
         <v>3</v>
       </c>
       <c r="B96" s="5"/>
       <c r="C96" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H96" s="5"/>
       <c r="I96" s="5"/>
       <c r="J96" s="5"/>
       <c r="K96" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L96" s="5"/>
       <c r="M96" s="5"/>
       <c r="N96" s="7"/>
-      <c r="O96" s="7"/>
-      <c r="P96" s="5"/>
-      <c r="Q96" s="5"/>
-      <c r="R96" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S96" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T96" s="5"/>
-    </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O96" s="5"/>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="5">
         <v>3</v>
       </c>
       <c r="B97" s="5"/>
       <c r="C97" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H97" s="5"/>
       <c r="I97" s="5"/>
       <c r="J97" s="5"/>
       <c r="K97" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L97" s="5"/>
       <c r="M97" s="5"/>
       <c r="N97" s="7"/>
-      <c r="O97" s="7"/>
-      <c r="P97" s="5"/>
-      <c r="Q97" s="5"/>
-      <c r="R97" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S97" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T97" s="5"/>
-    </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O97" s="5"/>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="5">
         <v>3</v>
       </c>
       <c r="B98" s="5"/>
       <c r="C98" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H98" s="5"/>
       <c r="I98" s="5"/>
       <c r="J98" s="5"/>
       <c r="K98" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L98" s="5"/>
       <c r="M98" s="5"/>
       <c r="N98" s="7"/>
-      <c r="O98" s="7"/>
-      <c r="P98" s="5"/>
-      <c r="Q98" s="5"/>
-      <c r="R98" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S98" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T98" s="5"/>
-    </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O98" s="5"/>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="5">
         <v>3</v>
       </c>
       <c r="B99" s="5"/>
       <c r="C99" s="5" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H99" s="5"/>
       <c r="I99" s="5"/>
       <c r="J99" s="5"/>
       <c r="K99" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L99" s="5"/>
       <c r="M99" s="5"/>
       <c r="N99" s="7"/>
-      <c r="O99" s="7"/>
-      <c r="P99" s="5"/>
-      <c r="Q99" s="5"/>
-      <c r="R99" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S99" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T99" s="5"/>
-    </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O99" s="5"/>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" s="5">
         <v>3</v>
       </c>
       <c r="B100" s="5"/>
       <c r="C100" s="5" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H100" s="5"/>
       <c r="I100" s="5"/>
       <c r="J100" s="5"/>
       <c r="K100" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L100" s="5"/>
       <c r="M100" s="5"/>
       <c r="N100" s="7"/>
-      <c r="O100" s="7"/>
-      <c r="P100" s="5"/>
-      <c r="Q100" s="5"/>
-      <c r="R100" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S100" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T100" s="5"/>
-    </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O100" s="5"/>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="5">
         <v>3</v>
       </c>
       <c r="B101" s="5"/>
       <c r="C101" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H101" s="5"/>
       <c r="I101" s="5"/>
       <c r="J101" s="5"/>
       <c r="K101" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L101" s="5"/>
       <c r="M101" s="5"/>
       <c r="N101" s="7"/>
-      <c r="O101" s="7"/>
-      <c r="P101" s="5"/>
-      <c r="Q101" s="5"/>
-      <c r="R101" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S101" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T101" s="5"/>
-    </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O101" s="5"/>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" s="5">
         <v>3</v>
       </c>
       <c r="B102" s="5"/>
       <c r="C102" s="5" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H102" s="5"/>
       <c r="I102" s="5"/>
       <c r="J102" s="5"/>
       <c r="K102" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L102" s="5"/>
       <c r="M102" s="5"/>
       <c r="N102" s="7"/>
-      <c r="O102" s="7"/>
-      <c r="P102" s="5"/>
-      <c r="Q102" s="5"/>
-      <c r="R102" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S102" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T102" s="5"/>
-    </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O102" s="5"/>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" s="5">
         <v>3</v>
       </c>
       <c r="B103" s="5"/>
       <c r="C103" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H103" s="5"/>
       <c r="I103" s="5"/>
       <c r="J103" s="5"/>
       <c r="K103" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L103" s="5"/>
       <c r="M103" s="5"/>
       <c r="N103" s="7"/>
-      <c r="O103" s="7"/>
-      <c r="P103" s="5"/>
-      <c r="Q103" s="5"/>
-      <c r="R103" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S103" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T103" s="5"/>
-    </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O103" s="5"/>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" s="5">
         <v>3</v>
       </c>
       <c r="B104" s="5"/>
       <c r="C104" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H104" s="5"/>
       <c r="I104" s="5"/>
       <c r="J104" s="5"/>
       <c r="K104" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L104" s="5"/>
       <c r="M104" s="5"/>
       <c r="N104" s="7"/>
-      <c r="O104" s="7"/>
-      <c r="P104" s="5"/>
-      <c r="Q104" s="5"/>
-      <c r="R104" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S104" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T104" s="5"/>
-    </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O104" s="5"/>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" s="5">
         <v>3</v>
       </c>
       <c r="B105" s="5"/>
       <c r="C105" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H105" s="5"/>
       <c r="I105" s="5"/>
       <c r="J105" s="5"/>
       <c r="K105" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L105" s="5"/>
       <c r="M105" s="5"/>
       <c r="N105" s="7"/>
-      <c r="O105" s="7"/>
-      <c r="P105" s="5"/>
-      <c r="Q105" s="5"/>
-      <c r="R105" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S105" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T105" s="5"/>
-    </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O105" s="5"/>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" s="5">
         <v>3</v>
       </c>
       <c r="B106" s="5"/>
       <c r="C106" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H106" s="5"/>
       <c r="I106" s="5"/>
       <c r="J106" s="5"/>
       <c r="K106" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L106" s="5"/>
       <c r="M106" s="5"/>
       <c r="N106" s="7"/>
-      <c r="O106" s="7"/>
-      <c r="P106" s="5"/>
-      <c r="Q106" s="5"/>
-      <c r="R106" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S106" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T106" s="5"/>
-    </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O106" s="5"/>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" s="5">
         <v>3</v>
       </c>
       <c r="B107" s="5"/>
       <c r="C107" s="5" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H107" s="5"/>
       <c r="I107" s="5"/>
       <c r="J107" s="5"/>
       <c r="K107" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L107" s="5"/>
       <c r="M107" s="5"/>
       <c r="N107" s="7"/>
-      <c r="O107" s="7"/>
-      <c r="P107" s="5"/>
-      <c r="Q107" s="5"/>
-      <c r="R107" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S107" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T107" s="5"/>
-    </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O107" s="5"/>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" s="5">
         <v>3</v>
       </c>
       <c r="B108" s="5"/>
       <c r="C108" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="G108" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H108" s="5"/>
       <c r="I108" s="5"/>
       <c r="J108" s="5"/>
       <c r="K108" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L108" s="5"/>
       <c r="M108" s="5"/>
       <c r="N108" s="7"/>
-      <c r="O108" s="7"/>
-      <c r="P108" s="5"/>
-      <c r="Q108" s="5"/>
-      <c r="R108" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S108" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T108" s="5"/>
-    </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O108" s="5"/>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109" s="5">
         <v>3</v>
       </c>
       <c r="B109" s="5"/>
       <c r="C109" s="5" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H109" s="5"/>
       <c r="I109" s="5"/>
       <c r="J109" s="5"/>
       <c r="K109" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L109" s="5"/>
       <c r="M109" s="5"/>
       <c r="N109" s="7"/>
-      <c r="O109" s="7"/>
-      <c r="P109" s="5"/>
-      <c r="Q109" s="5"/>
-      <c r="R109" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S109" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T109" s="5"/>
-    </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O109" s="5"/>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110" s="5">
         <v>3</v>
       </c>
       <c r="B110" s="5"/>
       <c r="C110" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H110" s="5"/>
       <c r="I110" s="5"/>
       <c r="J110" s="5"/>
       <c r="K110" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L110" s="5"/>
       <c r="M110" s="5"/>
       <c r="N110" s="7"/>
-      <c r="O110" s="7"/>
-      <c r="P110" s="5"/>
-      <c r="Q110" s="5"/>
-      <c r="R110" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S110" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T110" s="5"/>
-    </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O110" s="5"/>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111" s="5">
         <v>3</v>
       </c>
       <c r="B111" s="5"/>
       <c r="C111" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G111" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H111" s="5"/>
       <c r="I111" s="5"/>
       <c r="J111" s="5"/>
       <c r="K111" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L111" s="5"/>
       <c r="M111" s="5"/>
       <c r="N111" s="7"/>
-      <c r="O111" s="7"/>
-      <c r="P111" s="5"/>
-      <c r="Q111" s="5"/>
-      <c r="R111" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S111" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T111" s="5"/>
-    </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O111" s="5"/>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112" s="5">
         <v>3</v>
       </c>
       <c r="B112" s="5"/>
       <c r="C112" s="5" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G112" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H112" s="5"/>
       <c r="I112" s="5"/>
       <c r="J112" s="5"/>
       <c r="K112" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L112" s="5"/>
       <c r="M112" s="5"/>
       <c r="N112" s="7"/>
-      <c r="O112" s="7"/>
-      <c r="P112" s="5"/>
-      <c r="Q112" s="5"/>
-      <c r="R112" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S112" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T112" s="5"/>
-    </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O112" s="5"/>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113" s="5">
         <v>3</v>
       </c>
       <c r="B113" s="5"/>
       <c r="C113" s="5" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G113" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H113" s="5"/>
       <c r="I113" s="5"/>
       <c r="J113" s="5"/>
       <c r="K113" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L113" s="5"/>
       <c r="M113" s="5"/>
       <c r="N113" s="7"/>
-      <c r="O113" s="7"/>
-      <c r="P113" s="5"/>
-      <c r="Q113" s="5"/>
-      <c r="R113" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S113" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T113" s="5"/>
-    </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O113" s="5"/>
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114" s="5">
         <v>3</v>
       </c>
       <c r="B114" s="5"/>
       <c r="C114" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="G114" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H114" s="5"/>
       <c r="I114" s="5"/>
       <c r="J114" s="5"/>
       <c r="K114" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L114" s="5"/>
       <c r="M114" s="5"/>
       <c r="N114" s="7"/>
-      <c r="O114" s="7"/>
-      <c r="P114" s="5"/>
-      <c r="Q114" s="5"/>
-      <c r="R114" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S114" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T114" s="5"/>
-    </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O114" s="5"/>
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115" s="5">
         <v>3</v>
       </c>
       <c r="B115" s="5"/>
       <c r="C115" s="5" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="G115" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H115" s="5"/>
       <c r="I115" s="5"/>
       <c r="J115" s="5"/>
       <c r="K115" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L115" s="5"/>
       <c r="M115" s="5"/>
       <c r="N115" s="7"/>
-      <c r="O115" s="7"/>
-      <c r="P115" s="5"/>
-      <c r="Q115" s="5"/>
-      <c r="R115" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S115" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T115" s="5"/>
-    </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O115" s="5"/>
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116" s="5">
         <v>3</v>
       </c>
       <c r="B116" s="5"/>
       <c r="C116" s="5" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G116" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H116" s="5"/>
       <c r="I116" s="5"/>
       <c r="J116" s="5"/>
       <c r="K116" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L116" s="5"/>
       <c r="M116" s="5"/>
       <c r="N116" s="7"/>
-      <c r="O116" s="7"/>
-      <c r="P116" s="5"/>
-      <c r="Q116" s="5"/>
-      <c r="R116" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S116" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T116" s="5"/>
-    </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O116" s="5"/>
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117" s="5">
         <v>3</v>
       </c>
       <c r="B117" s="5"/>
       <c r="C117" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="G117" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H117" s="5"/>
       <c r="I117" s="5"/>
       <c r="J117" s="5"/>
       <c r="K117" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L117" s="5"/>
       <c r="M117" s="5"/>
       <c r="N117" s="7"/>
-      <c r="O117" s="7"/>
-      <c r="P117" s="5"/>
-      <c r="Q117" s="5"/>
-      <c r="R117" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S117" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T117" s="5"/>
-    </row>
-    <row r="118" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O117" s="5"/>
+    </row>
+    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118" s="5">
         <v>3</v>
       </c>
       <c r="B118" s="5"/>
       <c r="C118" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="G118" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H118" s="5"/>
       <c r="I118" s="5"/>
       <c r="J118" s="5"/>
       <c r="K118" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L118" s="5"/>
       <c r="M118" s="5"/>
       <c r="N118" s="7"/>
-      <c r="O118" s="7"/>
-      <c r="P118" s="5"/>
-      <c r="Q118" s="5"/>
-      <c r="R118" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S118" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T118" s="5"/>
-    </row>
-    <row r="119" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O118" s="5"/>
+    </row>
+    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119" s="5">
         <v>3</v>
       </c>
       <c r="B119" s="5"/>
       <c r="C119" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="G119" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H119" s="5"/>
       <c r="I119" s="5"/>
       <c r="J119" s="5"/>
       <c r="K119" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L119" s="5"/>
       <c r="M119" s="5"/>
       <c r="N119" s="7"/>
-      <c r="O119" s="7"/>
-      <c r="P119" s="5"/>
-      <c r="Q119" s="5"/>
-      <c r="R119" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S119" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T119" s="5"/>
-    </row>
-    <row r="120" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O119" s="5"/>
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120" s="5">
         <v>3</v>
       </c>
       <c r="B120" s="5"/>
       <c r="C120" s="5" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>237</v>
+        <v>264</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="G120" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H120" s="5"/>
       <c r="I120" s="5"/>
       <c r="J120" s="5"/>
       <c r="K120" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L120" s="5"/>
       <c r="M120" s="5"/>
       <c r="N120" s="7"/>
-      <c r="O120" s="7"/>
-      <c r="P120" s="5"/>
-      <c r="Q120" s="5"/>
-      <c r="R120" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S120" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T120" s="5"/>
-    </row>
-    <row r="121" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O120" s="5"/>
+    </row>
+    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121" s="5">
         <v>3</v>
       </c>
       <c r="B121" s="5"/>
       <c r="C121" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>89</v>
+        <v>140</v>
       </c>
       <c r="G121" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H121" s="5"/>
       <c r="I121" s="5"/>
       <c r="J121" s="5"/>
       <c r="K121" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L121" s="5"/>
       <c r="M121" s="5"/>
       <c r="N121" s="7"/>
-      <c r="O121" s="7"/>
-      <c r="P121" s="5"/>
-      <c r="Q121" s="5"/>
-      <c r="R121" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S121" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T121" s="5"/>
-    </row>
-    <row r="122" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O121" s="5"/>
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122" s="5">
         <v>3</v>
       </c>
       <c r="B122" s="5"/>
       <c r="C122" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G122" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H122" s="5"/>
       <c r="I122" s="5"/>
       <c r="J122" s="5"/>
       <c r="K122" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L122" s="5"/>
       <c r="M122" s="5"/>
       <c r="N122" s="7"/>
-      <c r="O122" s="7"/>
-      <c r="P122" s="5"/>
-      <c r="Q122" s="5"/>
-      <c r="R122" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S122" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T122" s="5"/>
-    </row>
-    <row r="123" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O122" s="5"/>
+    </row>
+    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123" s="5">
         <v>3</v>
       </c>
       <c r="B123" s="5"/>
       <c r="C123" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H123" s="5"/>
       <c r="I123" s="5"/>
       <c r="J123" s="5"/>
       <c r="K123" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L123" s="5"/>
       <c r="M123" s="5"/>
       <c r="N123" s="7"/>
-      <c r="O123" s="7"/>
-      <c r="P123" s="5"/>
-      <c r="Q123" s="5"/>
-      <c r="R123" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S123" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T123" s="5"/>
-    </row>
-    <row r="124" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O123" s="5"/>
+    </row>
+    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124" s="5">
         <v>3</v>
       </c>
       <c r="B124" s="5"/>
       <c r="C124" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G124" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H124" s="5"/>
       <c r="I124" s="5"/>
       <c r="J124" s="5"/>
       <c r="K124" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L124" s="5"/>
       <c r="M124" s="5"/>
       <c r="N124" s="7"/>
-      <c r="O124" s="7"/>
-      <c r="P124" s="5"/>
-      <c r="Q124" s="5"/>
-      <c r="R124" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S124" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T124" s="5"/>
-    </row>
-    <row r="125" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O124" s="5"/>
+    </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125" s="5">
         <v>3</v>
       </c>
       <c r="B125" s="5"/>
       <c r="C125" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G125" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H125" s="5"/>
       <c r="I125" s="5"/>
       <c r="J125" s="5"/>
       <c r="K125" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L125" s="5"/>
       <c r="M125" s="5"/>
       <c r="N125" s="7"/>
-      <c r="O125" s="7"/>
-      <c r="P125" s="5"/>
-      <c r="Q125" s="5"/>
-      <c r="R125" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S125" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T125" s="5"/>
-    </row>
-    <row r="126" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O125" s="5"/>
+    </row>
+    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A126" s="5">
         <v>3</v>
       </c>
       <c r="B126" s="5"/>
       <c r="C126" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="G126" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H126" s="5"/>
       <c r="I126" s="5"/>
       <c r="J126" s="5"/>
       <c r="K126" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L126" s="5"/>
       <c r="M126" s="5"/>
       <c r="N126" s="7"/>
-      <c r="O126" s="7"/>
-      <c r="P126" s="5"/>
-      <c r="Q126" s="5"/>
-      <c r="R126" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S126" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T126" s="5"/>
-    </row>
-    <row r="127" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O126" s="5"/>
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A127" s="5">
         <v>3</v>
       </c>
       <c r="B127" s="5"/>
       <c r="C127" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G127" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H127" s="5"/>
       <c r="I127" s="5"/>
       <c r="J127" s="5"/>
       <c r="K127" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L127" s="5"/>
       <c r="M127" s="5"/>
       <c r="N127" s="7"/>
-      <c r="O127" s="7"/>
-      <c r="P127" s="5"/>
-      <c r="Q127" s="5"/>
-      <c r="R127" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S127" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T127" s="5"/>
-    </row>
-    <row r="128" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O127" s="5"/>
+    </row>
+    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A128" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B128" s="5"/>
       <c r="C128" s="5" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>147</v>
+        <v>53</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="G128" s="5" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H128" s="5"/>
       <c r="I128" s="5"/>
       <c r="J128" s="5"/>
       <c r="K128" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L128" s="5"/>
       <c r="M128" s="5"/>
       <c r="N128" s="7"/>
-      <c r="O128" s="7"/>
-      <c r="P128" s="5"/>
-      <c r="Q128" s="5"/>
-      <c r="R128" s="5" t="s">
-        <v>412</v>
-      </c>
-      <c r="S128" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="T128" s="5"/>
-    </row>
-    <row r="129" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O128" s="5"/>
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A129" s="5">
         <v>2</v>
       </c>
       <c r="B129" s="5"/>
       <c r="C129" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G129" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H129" s="5"/>
       <c r="I129" s="5"/>
       <c r="J129" s="5"/>
       <c r="K129" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L129" s="5"/>
       <c r="M129" s="5"/>
       <c r="N129" s="7"/>
-      <c r="O129" s="7"/>
-      <c r="P129" s="5"/>
-      <c r="Q129" s="5"/>
-      <c r="R129" s="5" t="s">
-        <v>414</v>
-      </c>
-      <c r="S129" s="5" t="s">
-        <v>415</v>
-      </c>
-      <c r="T129" s="5"/>
-    </row>
-    <row r="130" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O129" s="5"/>
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A130" s="5">
         <v>2</v>
       </c>
       <c r="B130" s="5"/>
       <c r="C130" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G130" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H130" s="5"/>
       <c r="I130" s="5"/>
       <c r="J130" s="5"/>
       <c r="K130" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L130" s="5"/>
       <c r="M130" s="5"/>
       <c r="N130" s="7"/>
-      <c r="O130" s="7"/>
-      <c r="P130" s="5"/>
-      <c r="Q130" s="5"/>
-      <c r="R130" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="S130" s="5" t="s">
-        <v>417</v>
-      </c>
-      <c r="T130" s="5"/>
-    </row>
-    <row r="131" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O130" s="5"/>
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A131" s="5">
         <v>2</v>
       </c>
       <c r="B131" s="5"/>
       <c r="C131" s="5" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>15</v>
+        <v>150</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>211</v>
+        <v>282</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>25</v>
+        <v>151</v>
       </c>
       <c r="G131" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H131" s="5"/>
       <c r="I131" s="5"/>
       <c r="J131" s="5"/>
       <c r="K131" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L131" s="5"/>
       <c r="M131" s="5"/>
       <c r="N131" s="7"/>
-      <c r="O131" s="7"/>
-      <c r="P131" s="5"/>
-      <c r="Q131" s="5"/>
-      <c r="R131" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="S131" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="T131" s="5"/>
-    </row>
-    <row r="132" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O131" s="5"/>
+    </row>
+    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A132" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B132" s="5"/>
       <c r="C132" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D132" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D132" s="5" t="s">
-        <v>15</v>
-      </c>
       <c r="E132" s="5" t="s">
-        <v>286</v>
+        <v>208</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>153</v>
+        <v>24</v>
       </c>
       <c r="G132" s="5" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="H132" s="5"/>
       <c r="I132" s="5"/>
       <c r="J132" s="5"/>
       <c r="K132" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L132" s="5"/>
       <c r="M132" s="5"/>
       <c r="N132" s="7"/>
-      <c r="O132" s="7"/>
-      <c r="P132" s="5"/>
-      <c r="Q132" s="5"/>
-      <c r="R132" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="S132" s="5" t="s">
-        <v>419</v>
-      </c>
-      <c r="T132" s="5"/>
-    </row>
-    <row r="133" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O132" s="5"/>
+    </row>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A133" s="5">
         <v>3</v>
       </c>
       <c r="B133" s="5"/>
       <c r="C133" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D133" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D133" s="5" t="s">
-        <v>15</v>
-      </c>
       <c r="E133" s="5" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G133" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H133" s="5"/>
       <c r="I133" s="5"/>
       <c r="J133" s="5"/>
       <c r="K133" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L133" s="5"/>
       <c r="M133" s="5"/>
       <c r="N133" s="7"/>
-      <c r="O133" s="7"/>
-      <c r="P133" s="5"/>
-      <c r="Q133" s="5"/>
-      <c r="R133" s="5" t="s">
-        <v>420</v>
-      </c>
-      <c r="S133" s="5" t="s">
-        <v>421</v>
-      </c>
-      <c r="T133" s="5"/>
-    </row>
-    <row r="134" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O133" s="5"/>
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A134" s="5">
         <v>3</v>
       </c>
       <c r="B134" s="5"/>
       <c r="C134" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D134" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D134" s="5" t="s">
-        <v>155</v>
-      </c>
       <c r="E134" s="5" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G134" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H134" s="5"/>
       <c r="I134" s="5"/>
       <c r="J134" s="5"/>
       <c r="K134" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L134" s="5"/>
       <c r="M134" s="5"/>
       <c r="N134" s="7"/>
-      <c r="O134" s="7"/>
-      <c r="P134" s="5"/>
-      <c r="Q134" s="5"/>
-      <c r="R134" s="5" t="s">
-        <v>422</v>
-      </c>
-      <c r="S134" s="5" t="s">
-        <v>423</v>
-      </c>
-      <c r="T134" s="5"/>
-    </row>
-    <row r="135" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O134" s="5"/>
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A135" s="5">
         <v>3</v>
       </c>
       <c r="B135" s="5"/>
       <c r="C135" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>15</v>
+        <v>154</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G135" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H135" s="5"/>
       <c r="I135" s="5"/>
       <c r="J135" s="5"/>
       <c r="K135" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L135" s="5"/>
       <c r="M135" s="5"/>
       <c r="N135" s="7"/>
-      <c r="O135" s="7"/>
-      <c r="P135" s="5"/>
-      <c r="Q135" s="5"/>
-      <c r="R135" s="5" t="s">
-        <v>424</v>
-      </c>
-      <c r="S135" s="5" t="s">
-        <v>425</v>
-      </c>
-      <c r="T135" s="5"/>
-    </row>
-    <row r="136" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O135" s="5"/>
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A136" s="5">
         <v>3</v>
       </c>
       <c r="B136" s="5"/>
       <c r="C136" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D136" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D136" s="5" t="s">
-        <v>15</v>
-      </c>
       <c r="E136" s="5" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="G136" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H136" s="5"/>
       <c r="I136" s="5"/>
       <c r="J136" s="5"/>
       <c r="K136" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L136" s="5"/>
       <c r="M136" s="5"/>
       <c r="N136" s="7"/>
-      <c r="O136" s="7"/>
-      <c r="P136" s="5"/>
-      <c r="Q136" s="5"/>
-      <c r="R136" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S136" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T136" s="5"/>
-    </row>
-    <row r="137" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O136" s="5"/>
+    </row>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A137" s="5">
         <v>3</v>
       </c>
       <c r="B137" s="5"/>
       <c r="C137" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D137" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D137" s="5" t="s">
-        <v>15</v>
-      </c>
       <c r="E137" s="5" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G137" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H137" s="5"/>
       <c r="I137" s="5"/>
       <c r="J137" s="5"/>
       <c r="K137" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L137" s="5"/>
       <c r="M137" s="5"/>
       <c r="N137" s="7"/>
-      <c r="O137" s="7"/>
-      <c r="P137" s="5"/>
-      <c r="Q137" s="5"/>
-      <c r="R137" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="S137" s="5" t="s">
-        <v>427</v>
-      </c>
-      <c r="T137" s="5"/>
-    </row>
-    <row r="138" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O137" s="5"/>
+    </row>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A138" s="5">
         <v>3</v>
       </c>
       <c r="B138" s="5"/>
       <c r="C138" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D138" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D138" s="5" t="s">
-        <v>162</v>
-      </c>
       <c r="E138" s="5" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G138" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H138" s="5"/>
       <c r="I138" s="5"/>
       <c r="J138" s="5"/>
       <c r="K138" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L138" s="5"/>
       <c r="M138" s="5"/>
       <c r="N138" s="7"/>
-      <c r="O138" s="7"/>
-      <c r="P138" s="5"/>
-      <c r="Q138" s="5"/>
-      <c r="R138" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S138" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T138" s="5"/>
-    </row>
-    <row r="139" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O138" s="5"/>
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A139" s="5">
         <v>3</v>
       </c>
       <c r="B139" s="5"/>
       <c r="C139" s="5" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>54</v>
+        <v>161</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G139" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H139" s="5"/>
       <c r="I139" s="5"/>
       <c r="J139" s="5"/>
       <c r="K139" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L139" s="5"/>
       <c r="M139" s="5"/>
       <c r="N139" s="7"/>
-      <c r="O139" s="7"/>
-      <c r="P139" s="5"/>
-      <c r="Q139" s="5"/>
-      <c r="R139" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S139" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T139" s="5"/>
-    </row>
-    <row r="140" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O139" s="5"/>
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A140" s="5">
         <v>3</v>
       </c>
       <c r="B140" s="5"/>
       <c r="C140" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="F140" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G140" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H140" s="5"/>
       <c r="I140" s="5"/>
       <c r="J140" s="5"/>
       <c r="K140" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L140" s="5"/>
       <c r="M140" s="5"/>
       <c r="N140" s="7"/>
-      <c r="O140" s="7"/>
-      <c r="P140" s="5"/>
-      <c r="Q140" s="5"/>
-      <c r="R140" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S140" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T140" s="5"/>
-    </row>
-    <row r="141" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O140" s="5"/>
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A141" s="5">
         <v>3</v>
       </c>
       <c r="B141" s="5"/>
       <c r="C141" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G141" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H141" s="5"/>
       <c r="I141" s="5"/>
       <c r="J141" s="5"/>
       <c r="K141" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L141" s="5"/>
       <c r="M141" s="5"/>
       <c r="N141" s="7"/>
-      <c r="O141" s="7"/>
-      <c r="P141" s="5"/>
-      <c r="Q141" s="5"/>
-      <c r="R141" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S141" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T141" s="5"/>
-    </row>
-    <row r="142" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O141" s="5"/>
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A142" s="5">
         <v>3</v>
       </c>
       <c r="B142" s="5"/>
       <c r="C142" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G142" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H142" s="5"/>
       <c r="I142" s="5"/>
       <c r="J142" s="5"/>
       <c r="K142" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L142" s="5"/>
       <c r="M142" s="5"/>
       <c r="N142" s="7"/>
-      <c r="O142" s="7"/>
-      <c r="P142" s="5"/>
-      <c r="Q142" s="5"/>
-      <c r="R142" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S142" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T142" s="5"/>
-    </row>
-    <row r="143" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O142" s="5"/>
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A143" s="5">
         <v>3</v>
       </c>
       <c r="B143" s="5"/>
       <c r="C143" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E143" s="5" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F143" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G143" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H143" s="5"/>
       <c r="I143" s="5"/>
       <c r="J143" s="5"/>
       <c r="K143" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L143" s="5"/>
       <c r="M143" s="5"/>
       <c r="N143" s="7"/>
-      <c r="O143" s="7"/>
-      <c r="P143" s="5"/>
-      <c r="Q143" s="5"/>
-      <c r="R143" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S143" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T143" s="5"/>
-    </row>
-    <row r="144" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O143" s="5"/>
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A144" s="5">
         <v>3</v>
       </c>
       <c r="B144" s="5"/>
       <c r="C144" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F144" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G144" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H144" s="5"/>
       <c r="I144" s="5"/>
       <c r="J144" s="5"/>
       <c r="K144" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L144" s="5"/>
       <c r="M144" s="5"/>
       <c r="N144" s="7"/>
-      <c r="O144" s="7"/>
-      <c r="P144" s="5"/>
-      <c r="Q144" s="5"/>
-      <c r="R144" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S144" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T144" s="5"/>
-    </row>
-    <row r="145" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O144" s="5"/>
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A145" s="5">
         <v>3</v>
       </c>
       <c r="B145" s="5"/>
       <c r="C145" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F145" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G145" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H145" s="5"/>
       <c r="I145" s="5"/>
       <c r="J145" s="5"/>
       <c r="K145" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L145" s="5"/>
       <c r="M145" s="5"/>
       <c r="N145" s="7"/>
-      <c r="O145" s="7"/>
-      <c r="P145" s="5"/>
-      <c r="Q145" s="5"/>
-      <c r="R145" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S145" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T145" s="5"/>
-    </row>
-    <row r="146" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O145" s="5"/>
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A146" s="5">
         <v>3</v>
       </c>
       <c r="B146" s="5"/>
       <c r="C146" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G146" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H146" s="5"/>
       <c r="I146" s="5"/>
       <c r="J146" s="5"/>
       <c r="K146" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L146" s="5"/>
       <c r="M146" s="5"/>
       <c r="N146" s="7"/>
-      <c r="O146" s="7"/>
-      <c r="P146" s="5"/>
-      <c r="Q146" s="5"/>
-      <c r="R146" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S146" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T146" s="5"/>
-    </row>
-    <row r="147" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O146" s="5"/>
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A147" s="5">
         <v>3</v>
       </c>
       <c r="B147" s="5"/>
       <c r="C147" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="D147" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E147" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="F147" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="D147" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="E147" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F147" s="5" t="s">
-        <v>173</v>
-      </c>
       <c r="G147" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H147" s="5"/>
       <c r="I147" s="5"/>
       <c r="J147" s="5"/>
       <c r="K147" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L147" s="5"/>
       <c r="M147" s="5"/>
       <c r="N147" s="7"/>
-      <c r="O147" s="7"/>
-      <c r="P147" s="5"/>
-      <c r="Q147" s="5"/>
-      <c r="R147" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S147" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T147" s="5"/>
-    </row>
-    <row r="148" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O147" s="5"/>
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A148" s="5">
         <v>3</v>
       </c>
       <c r="B148" s="5"/>
       <c r="C148" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G148" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H148" s="5"/>
       <c r="I148" s="5"/>
       <c r="J148" s="5"/>
       <c r="K148" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L148" s="5"/>
       <c r="M148" s="5"/>
       <c r="N148" s="7"/>
-      <c r="O148" s="7"/>
-      <c r="P148" s="5"/>
-      <c r="Q148" s="5"/>
-      <c r="R148" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S148" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T148" s="5"/>
-    </row>
-    <row r="149" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O148" s="5"/>
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A149" s="5">
         <v>3</v>
       </c>
       <c r="B149" s="5"/>
       <c r="C149" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F149" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G149" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H149" s="5"/>
       <c r="I149" s="5"/>
       <c r="J149" s="5"/>
       <c r="K149" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L149" s="5"/>
       <c r="M149" s="5"/>
       <c r="N149" s="7"/>
-      <c r="O149" s="7"/>
-      <c r="P149" s="5"/>
-      <c r="Q149" s="5"/>
-      <c r="R149" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S149" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T149" s="5"/>
-    </row>
-    <row r="150" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O149" s="5"/>
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A150" s="5">
         <v>3</v>
       </c>
       <c r="B150" s="5"/>
       <c r="C150" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G150" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H150" s="5"/>
       <c r="I150" s="5"/>
       <c r="J150" s="5"/>
       <c r="K150" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L150" s="5"/>
       <c r="M150" s="5"/>
       <c r="N150" s="7"/>
-      <c r="O150" s="7"/>
-      <c r="P150" s="5"/>
-      <c r="Q150" s="5"/>
-      <c r="R150" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S150" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T150" s="5"/>
-    </row>
-    <row r="151" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O150" s="5"/>
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A151" s="5">
         <v>3</v>
       </c>
       <c r="B151" s="5"/>
       <c r="C151" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G151" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H151" s="5"/>
       <c r="I151" s="5"/>
       <c r="J151" s="5"/>
       <c r="K151" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L151" s="5"/>
       <c r="M151" s="5"/>
       <c r="N151" s="7"/>
-      <c r="O151" s="7"/>
-      <c r="P151" s="5"/>
-      <c r="Q151" s="5"/>
-      <c r="R151" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S151" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T151" s="5"/>
-    </row>
-    <row r="152" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O151" s="5"/>
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A152" s="5">
         <v>3</v>
       </c>
       <c r="B152" s="5"/>
       <c r="C152" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G152" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H152" s="5"/>
       <c r="I152" s="5"/>
       <c r="J152" s="5"/>
       <c r="K152" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L152" s="5"/>
       <c r="M152" s="5"/>
       <c r="N152" s="7"/>
-      <c r="O152" s="7"/>
-      <c r="P152" s="5"/>
-      <c r="Q152" s="5"/>
-      <c r="R152" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S152" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T152" s="5"/>
-    </row>
-    <row r="153" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O152" s="5"/>
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A153" s="5">
         <v>3</v>
       </c>
       <c r="B153" s="5"/>
       <c r="C153" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G153" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H153" s="5"/>
       <c r="I153" s="5"/>
       <c r="J153" s="5"/>
       <c r="K153" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L153" s="5"/>
       <c r="M153" s="5"/>
       <c r="N153" s="7"/>
-      <c r="O153" s="7"/>
-      <c r="P153" s="5"/>
-      <c r="Q153" s="5"/>
-      <c r="R153" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S153" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T153" s="5"/>
-    </row>
-    <row r="154" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O153" s="5"/>
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A154" s="5">
         <v>3</v>
       </c>
       <c r="B154" s="5"/>
       <c r="C154" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G154" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H154" s="5"/>
       <c r="I154" s="5"/>
       <c r="J154" s="5"/>
       <c r="K154" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L154" s="5"/>
       <c r="M154" s="5"/>
       <c r="N154" s="7"/>
-      <c r="O154" s="7"/>
-      <c r="P154" s="5"/>
-      <c r="Q154" s="5"/>
-      <c r="R154" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S154" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T154" s="5"/>
-    </row>
-    <row r="155" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O154" s="5"/>
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A155" s="5">
         <v>0</v>
       </c>
       <c r="B155" s="5"/>
       <c r="C155" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G155" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H155" s="6">
         <v>46094</v>
@@ -8700,44 +6628,35 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="J155" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K155" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L155" s="5"/>
       <c r="M155" s="5"/>
       <c r="N155" s="7"/>
-      <c r="O155" s="7"/>
-      <c r="P155" s="5"/>
-      <c r="Q155" s="5"/>
-      <c r="R155" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S155" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T155" s="5"/>
-    </row>
-    <row r="156" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O155" s="5"/>
+    </row>
+    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A156" s="5">
         <v>0</v>
       </c>
       <c r="B156" s="5"/>
       <c r="C156" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G156" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H156" s="6">
         <v>46094</v>
@@ -8746,44 +6665,35 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="J156" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K156" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L156" s="5"/>
       <c r="M156" s="5"/>
       <c r="N156" s="7"/>
-      <c r="O156" s="7"/>
-      <c r="P156" s="5"/>
-      <c r="Q156" s="5"/>
-      <c r="R156" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S156" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T156" s="5"/>
-    </row>
-    <row r="157" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O156" s="5"/>
+    </row>
+    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A157" s="5">
         <v>0</v>
       </c>
       <c r="B157" s="5"/>
       <c r="C157" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="D157" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E157" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="D157" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="E157" s="5" t="s">
+      <c r="F157" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="F157" s="5" t="s">
-        <v>185</v>
-      </c>
       <c r="G157" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H157" s="6">
         <v>46095</v>
@@ -8792,46 +6702,35 @@
         <v>0.625</v>
       </c>
       <c r="J157" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K157" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L157" s="5"/>
       <c r="M157" s="5"/>
       <c r="N157" s="7"/>
-      <c r="O157" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="P157" s="5"/>
-      <c r="Q157" s="5"/>
-      <c r="R157" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S157" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T157" s="5"/>
-    </row>
-    <row r="158" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O157" s="5"/>
+    </row>
+    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A158" s="5">
         <v>3</v>
       </c>
       <c r="B158" s="5"/>
       <c r="C158" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D158" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D158" s="5" t="s">
-        <v>15</v>
-      </c>
       <c r="E158" s="5" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G158" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H158" s="6">
         <v>46128</v>
@@ -8841,41 +6740,32 @@
       </c>
       <c r="J158" s="5"/>
       <c r="K158" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L158" s="5"/>
       <c r="M158" s="5"/>
       <c r="N158" s="7"/>
-      <c r="O158" s="7"/>
-      <c r="P158" s="5"/>
-      <c r="Q158" s="5"/>
-      <c r="R158" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="S158" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="T158" s="5"/>
-    </row>
-    <row r="159" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O158" s="5"/>
+    </row>
+    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A159" s="5">
         <v>3</v>
       </c>
       <c r="B159" s="5"/>
       <c r="C159" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D159" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D159" s="5" t="s">
-        <v>15</v>
-      </c>
       <c r="E159" s="5" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="F159" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G159" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H159" s="6">
         <v>46139</v>
@@ -8887,41 +6777,32 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="K159" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L159" s="5"/>
       <c r="M159" s="5"/>
       <c r="N159" s="7"/>
-      <c r="O159" s="7"/>
-      <c r="P159" s="5"/>
-      <c r="Q159" s="5"/>
-      <c r="R159" s="5" t="s">
-        <v>430</v>
-      </c>
-      <c r="S159" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="T159" s="5"/>
-    </row>
-    <row r="160" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O159" s="5"/>
+    </row>
+    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A160" s="5">
         <v>3</v>
       </c>
       <c r="B160" s="5"/>
       <c r="C160" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G160" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H160" s="6">
         <v>46141</v>
@@ -8933,41 +6814,32 @@
         <v>0.96527777777777779</v>
       </c>
       <c r="K160" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L160" s="5"/>
       <c r="M160" s="5"/>
       <c r="N160" s="7"/>
-      <c r="O160" s="7"/>
-      <c r="P160" s="5"/>
-      <c r="Q160" s="5"/>
-      <c r="R160" s="5" t="s">
-        <v>432</v>
-      </c>
-      <c r="S160" s="5" t="s">
-        <v>433</v>
-      </c>
-      <c r="T160" s="5"/>
-    </row>
-    <row r="161" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O160" s="5"/>
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A161" s="5">
         <v>3</v>
       </c>
       <c r="B161" s="5"/>
       <c r="C161" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D161" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D161" s="5" t="s">
-        <v>15</v>
-      </c>
       <c r="E161" s="5" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G161" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H161" s="6">
         <v>46146</v>
@@ -8979,41 +6851,32 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="K161" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L161" s="5"/>
       <c r="M161" s="5"/>
       <c r="N161" s="7"/>
-      <c r="O161" s="7"/>
-      <c r="P161" s="5"/>
-      <c r="Q161" s="5"/>
-      <c r="R161" s="5" t="s">
-        <v>434</v>
-      </c>
-      <c r="S161" s="5" t="s">
-        <v>435</v>
-      </c>
-      <c r="T161" s="5"/>
-    </row>
-    <row r="162" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O161" s="5"/>
+    </row>
+    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A162" s="5">
         <v>3</v>
       </c>
       <c r="B162" s="5"/>
       <c r="C162" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G162" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H162" s="6">
         <v>46147</v>
@@ -9025,41 +6888,32 @@
         <v>0.5</v>
       </c>
       <c r="K162" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L162" s="5"/>
       <c r="M162" s="5"/>
       <c r="N162" s="7"/>
-      <c r="O162" s="7"/>
-      <c r="P162" s="5"/>
-      <c r="Q162" s="5"/>
-      <c r="R162" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="S162" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="T162" s="5"/>
-    </row>
-    <row r="163" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O162" s="5"/>
+    </row>
+    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A163" s="5">
         <v>1</v>
       </c>
       <c r="B163" s="5"/>
       <c r="C163" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D163" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D163" s="5" t="s">
-        <v>15</v>
-      </c>
       <c r="E163" s="5" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G163" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H163" s="6">
         <v>46147</v>
@@ -9069,43 +6923,32 @@
       </c>
       <c r="J163" s="5"/>
       <c r="K163" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L163" s="5"/>
       <c r="M163" s="5"/>
       <c r="N163" s="7"/>
-      <c r="O163" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="P163" s="5"/>
-      <c r="Q163" s="5"/>
-      <c r="R163" s="5" t="s">
-        <v>438</v>
-      </c>
-      <c r="S163" s="5" t="s">
-        <v>439</v>
-      </c>
-      <c r="T163" s="5"/>
-    </row>
-    <row r="164" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O163" s="5"/>
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A164" s="5">
         <v>3</v>
       </c>
       <c r="B164" s="5"/>
       <c r="C164" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D164" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D164" s="5" t="s">
-        <v>15</v>
-      </c>
       <c r="E164" s="5" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G164" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H164" s="6">
         <v>46149</v>
@@ -9117,41 +6960,32 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="K164" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L164" s="5"/>
       <c r="M164" s="5"/>
       <c r="N164" s="7"/>
-      <c r="O164" s="7"/>
-      <c r="P164" s="5"/>
-      <c r="Q164" s="5"/>
-      <c r="R164" s="5" t="s">
-        <v>440</v>
-      </c>
-      <c r="S164" s="5" t="s">
-        <v>441</v>
-      </c>
-      <c r="T164" s="5"/>
-    </row>
-    <row r="165" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O164" s="5"/>
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A165" s="5">
         <v>3</v>
       </c>
       <c r="B165" s="5"/>
       <c r="C165" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F165" s="5" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G165" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H165" s="6">
         <v>46155</v>
@@ -9161,43 +6995,32 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="K165" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L165" s="5"/>
       <c r="M165" s="5"/>
       <c r="N165" s="7"/>
-      <c r="O165" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="P165" s="5"/>
-      <c r="Q165" s="5"/>
-      <c r="R165" s="5" t="s">
-        <v>442</v>
-      </c>
-      <c r="S165" s="5" t="s">
-        <v>443</v>
-      </c>
-      <c r="T165" s="5"/>
-    </row>
-    <row r="166" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O165" s="5"/>
+    </row>
+    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A166" s="5">
         <v>3</v>
       </c>
       <c r="B166" s="5"/>
       <c r="C166" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D166" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D166" s="5" t="s">
-        <v>15</v>
-      </c>
       <c r="E166" s="5" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="G166" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H166" s="6">
         <v>46156</v>
@@ -9207,41 +7030,32 @@
         <v>0.625</v>
       </c>
       <c r="K166" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L166" s="5"/>
       <c r="M166" s="5"/>
       <c r="N166" s="7"/>
-      <c r="O166" s="7"/>
-      <c r="P166" s="5"/>
-      <c r="Q166" s="5"/>
-      <c r="R166" s="5" t="s">
-        <v>444</v>
-      </c>
-      <c r="S166" s="5" t="s">
-        <v>445</v>
-      </c>
-      <c r="T166" s="5"/>
-    </row>
-    <row r="167" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O166" s="5"/>
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A167" s="5">
         <v>2</v>
       </c>
       <c r="B167" s="5"/>
       <c r="C167" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D167" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D167" s="5" t="s">
-        <v>15</v>
-      </c>
       <c r="E167" s="5" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="G167" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H167" s="6">
         <v>46163</v>
@@ -9253,43 +7067,32 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="K167" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L167" s="5"/>
       <c r="M167" s="5"/>
       <c r="N167" s="7"/>
-      <c r="O167" s="7"/>
-      <c r="P167" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="Q167" s="5"/>
-      <c r="R167" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="S167" s="5" t="s">
-        <v>447</v>
-      </c>
-      <c r="T167" s="5"/>
-    </row>
-    <row r="168" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O167" s="5"/>
+    </row>
+    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A168" s="5">
         <v>2</v>
       </c>
       <c r="B168" s="5"/>
       <c r="C168" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D168" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D168" s="5" t="s">
-        <v>15</v>
-      </c>
       <c r="E168" s="5" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="G168" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H168" s="6">
         <v>46164</v>
@@ -9299,45 +7102,32 @@
         <v>0.375</v>
       </c>
       <c r="K168" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L168" s="5"/>
       <c r="M168" s="5"/>
       <c r="N168" s="7"/>
-      <c r="O168" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="P168" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="Q168" s="5"/>
-      <c r="R168" s="5" t="s">
-        <v>448</v>
-      </c>
-      <c r="S168" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="T168" s="5"/>
-    </row>
-    <row r="169" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O168" s="5"/>
+    </row>
+    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A169" s="5">
         <v>3</v>
       </c>
       <c r="B169" s="5"/>
       <c r="C169" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G169" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H169" s="6">
         <v>46167</v>
@@ -9349,45 +7139,32 @@
         <v>0.5625</v>
       </c>
       <c r="K169" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L169" s="5"/>
       <c r="M169" s="5"/>
       <c r="N169" s="7"/>
-      <c r="O169" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="P169" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="Q169" s="5"/>
-      <c r="R169" s="5" t="s">
-        <v>450</v>
-      </c>
-      <c r="S169" s="5" t="s">
-        <v>451</v>
-      </c>
-      <c r="T169" s="5"/>
-    </row>
-    <row r="170" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O169" s="5"/>
+    </row>
+    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A170" s="5">
         <v>3</v>
       </c>
       <c r="B170" s="5"/>
       <c r="C170" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D170" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D170" s="5" t="s">
-        <v>15</v>
-      </c>
       <c r="E170" s="5" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="F170" s="5" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="G170" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H170" s="12">
         <v>46170</v>
@@ -9399,47 +7176,32 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="K170" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L170" s="5"/>
       <c r="M170" s="5"/>
       <c r="N170" s="7"/>
-      <c r="O170" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="P170" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="Q170" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="R170" s="5" t="s">
-        <v>452</v>
-      </c>
-      <c r="S170" s="5" t="s">
-        <v>453</v>
-      </c>
-      <c r="T170" s="5"/>
-    </row>
-    <row r="171" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O170" s="5"/>
+    </row>
+    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A171" s="5">
         <v>3</v>
       </c>
       <c r="B171" s="5"/>
       <c r="C171" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D171" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E171" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="F171" s="5" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G171" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H171" s="6">
         <v>46174</v>
@@ -9451,109 +7213,78 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="K171" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L171" s="5"/>
       <c r="M171" s="5"/>
       <c r="N171" s="7"/>
-      <c r="O171" s="7"/>
-      <c r="P171" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="Q171" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="R171" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="S171" s="5" t="s">
-        <v>455</v>
-      </c>
-      <c r="T171" s="5"/>
-    </row>
-    <row r="172" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O171" s="5"/>
+    </row>
+    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A172" s="5">
         <v>0</v>
       </c>
       <c r="B172" s="5"/>
       <c r="C172" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D172" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E172" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="F172" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="D172" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E172" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="F172" s="5" t="s">
-        <v>143</v>
-      </c>
       <c r="G172" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H172" s="5"/>
       <c r="I172" s="5"/>
       <c r="J172" s="5"/>
       <c r="K172" s="5" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="L172" s="5"/>
       <c r="M172" s="5"/>
       <c r="N172" s="7"/>
-      <c r="O172" s="7"/>
-      <c r="P172" s="5"/>
-      <c r="Q172" s="5"/>
-      <c r="R172" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S172" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T172" s="5"/>
-    </row>
-    <row r="173" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O172" s="5"/>
+    </row>
+    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A173" s="5">
         <v>0</v>
       </c>
       <c r="B173" s="5"/>
       <c r="C173" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D173" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="F173" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G173" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H173" s="5"/>
       <c r="I173" s="5"/>
       <c r="J173" s="5"/>
       <c r="K173" s="5" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="L173" s="5"/>
       <c r="M173" s="5"/>
       <c r="N173" s="7"/>
-      <c r="O173" s="7"/>
-      <c r="P173" s="5"/>
-      <c r="Q173" s="5"/>
-      <c r="R173" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="S173" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="T173" s="5"/>
-    </row>
-    <row r="174" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O173" s="5"/>
+    </row>
+    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A174" s="15" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B174" s="15"/>
       <c r="C174" s="15"/>
@@ -9570,15 +7301,10 @@
       <c r="L174" s="15"/>
       <c r="M174" s="15"/>
       <c r="N174" s="17"/>
-      <c r="O174" s="17"/>
-      <c r="P174" s="15"/>
-      <c r="Q174" s="15"/>
-      <c r="R174" s="15"/>
-      <c r="S174" s="15"/>
-      <c r="T174" s="15"/>
+      <c r="O174" s="15"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="K2:T173">
+  <conditionalFormatting sqref="K2:O173">
     <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
       <formula>"Impl. Cancelada"</formula>
     </cfRule>

--- a/archivos/BD_Dashboard.xlsx
+++ b/archivos/BD_Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mexscitum-my.sharepoint.com/personal/erik_torres_scitum_com_mx/Documents/Documentos/ETP/GitHub/SCITUM-AMX/archivos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="74" documentId="11_F25DC773A252ABDACC1048E8499F6DC65BDE58F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0F907C1-7661-4B2A-B37B-A4E596B1FA6D}"/>
+  <xr:revisionPtr revIDLastSave="75" documentId="11_F25DC773A252ABDACC1048E8499F6DC65BDE58F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37312C66-BAF8-477A-B2A7-73D2D438F0EE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1691,6 +1691,7 @@
     <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="24.85546875" customWidth="1"/>
     <col min="7" max="7" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">

--- a/archivos/BD_Dashboard.xlsx
+++ b/archivos/BD_Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mexscitum-my.sharepoint.com/personal/erik_torres_scitum_com_mx/Documents/Documentos/ETP/GitHub/SCITUM-AMX/archivos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="75" documentId="11_F25DC773A252ABDACC1048E8499F6DC65BDE58F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37312C66-BAF8-477A-B2A7-73D2D438F0EE}"/>
+  <xr:revisionPtr revIDLastSave="77" documentId="11_F25DC773A252ABDACC1048E8499F6DC65BDE58F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BF172CF-6686-440E-9CFD-06B05D27F3C2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1069" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1068" uniqueCount="327">
   <si>
     <t>TIER</t>
   </si>
@@ -1026,9 +1026,6 @@
   </si>
   <si>
     <t>Aeroméxico reporta que no recibió el equipo. SCITUM levantó el reporte. Numero de reporte DHL: CS62301998 Ejecutivo DHL seguimiento de reporte: Jesus Hernández. 25-jun-2026 AMX confirma recepción de equipo</t>
-  </si>
-  <si>
-    <t>Total</t>
   </si>
   <si>
     <t>Esquema
@@ -1066,7 +1063,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1124,15 +1121,8 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Century Gothic"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1154,12 +1144,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF7C7AC"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -1191,7 +1175,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1234,15 +1218,6 @@
     </xf>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1681,7 +1656,7 @@
   <sheetPr>
     <tabColor theme="5" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:O174"/>
+  <dimension ref="A1:O173"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.140625" bestFit="1" customWidth="1"/>
@@ -1695,26 +1670,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="18" t="s">
+      <c r="D1" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="15" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>6</v>
@@ -1738,7 +1713,7 @@
         <v>12</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
@@ -1759,7 +1734,7 @@
         <v>15</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H2" s="6">
         <v>46210</v>
@@ -1769,12 +1744,12 @@
         <v>0.625</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
       <c r="N2" s="7" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O2" s="5"/>
     </row>
@@ -1796,7 +1771,7 @@
         <v>18</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H3" s="6">
         <v>46211</v>
@@ -1806,12 +1781,12 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="L3" s="5"/>
       <c r="M3" s="5"/>
       <c r="N3" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O3" s="5"/>
     </row>
@@ -1833,7 +1808,7 @@
         <v>21</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H4" s="6">
         <v>46204</v>
@@ -1843,14 +1818,14 @@
         <v>0.875</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>320</v>
+        <v>77</v>
       </c>
       <c r="L4" s="6">
         <v>46182</v>
       </c>
       <c r="M4" s="6"/>
       <c r="N4" s="7" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O4" s="5"/>
     </row>
@@ -1872,7 +1847,7 @@
         <v>28</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
@@ -1887,7 +1862,7 @@
         <v>1.01</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O5" s="5"/>
     </row>
@@ -1909,7 +1884,7 @@
         <v>30</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
@@ -1944,7 +1919,7 @@
         <v>32</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
@@ -1979,7 +1954,7 @@
         <v>37</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
@@ -2014,7 +1989,7 @@
         <v>19</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="5"/>
@@ -2047,7 +2022,7 @@
         <v>22</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="5"/>
@@ -2082,7 +2057,7 @@
         <v>24</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="5"/>
@@ -2117,7 +2092,7 @@
         <v>38</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="5"/>
@@ -2150,7 +2125,7 @@
         <v>34</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
@@ -2185,7 +2160,7 @@
         <v>36</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
@@ -2220,7 +2195,7 @@
         <v>27</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
@@ -2255,7 +2230,7 @@
         <v>56</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
@@ -2288,7 +2263,7 @@
         <v>67</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
@@ -2321,7 +2296,7 @@
         <v>66</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
@@ -2354,7 +2329,7 @@
         <v>69</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
@@ -2387,7 +2362,7 @@
         <v>62</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
@@ -2420,7 +2395,7 @@
         <v>64</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
@@ -2453,7 +2428,7 @@
         <v>60</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
@@ -2486,7 +2461,7 @@
         <v>58</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
@@ -2519,7 +2494,7 @@
         <v>55</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
@@ -2552,7 +2527,7 @@
         <v>71</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
@@ -2585,7 +2560,7 @@
         <v>145</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
@@ -2618,7 +2593,7 @@
         <v>158</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H27" s="5"/>
       <c r="I27" s="5"/>
@@ -2651,7 +2626,7 @@
         <v>40</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H28" s="8"/>
       <c r="I28" s="5"/>
@@ -2686,7 +2661,7 @@
         <v>46</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H29" s="8"/>
       <c r="I29" s="5"/>
@@ -2721,7 +2696,7 @@
         <v>42</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H30" s="8"/>
       <c r="I30" s="5"/>
@@ -2756,7 +2731,7 @@
         <v>126</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
@@ -2789,7 +2764,7 @@
         <v>129</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
@@ -2822,7 +2797,7 @@
         <v>163</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
@@ -2855,7 +2830,7 @@
         <v>134</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
@@ -2888,7 +2863,7 @@
         <v>44</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H35" s="8"/>
       <c r="I35" s="5"/>
@@ -2921,7 +2896,7 @@
         <v>47</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H36" s="8"/>
       <c r="I36" s="5"/>
@@ -2954,7 +2929,7 @@
         <v>54</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H37" s="8"/>
       <c r="I37" s="5"/>
@@ -2985,7 +2960,7 @@
         <v>49</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H38" s="5"/>
       <c r="I38" s="5"/>
@@ -3018,7 +2993,7 @@
         <v>78</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H39" s="5"/>
       <c r="I39" s="5"/>
@@ -3030,7 +3005,7 @@
       <c r="M39" s="5"/>
       <c r="N39" s="7"/>
       <c r="O39" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
@@ -3051,7 +3026,7 @@
         <v>94</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
@@ -3063,7 +3038,7 @@
       <c r="M40" s="5"/>
       <c r="N40" s="7"/>
       <c r="O40" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
@@ -3084,7 +3059,7 @@
         <v>114</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H41" s="5"/>
       <c r="I41" s="5"/>
@@ -3096,7 +3071,7 @@
       <c r="M41" s="5"/>
       <c r="N41" s="7"/>
       <c r="O41" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
@@ -3117,7 +3092,7 @@
         <v>73</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H42" s="5"/>
       <c r="I42" s="5"/>
@@ -3148,7 +3123,7 @@
         <v>75</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H43" s="5"/>
       <c r="I43" s="5"/>
@@ -3179,7 +3154,7 @@
         <v>76</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H44" s="5"/>
       <c r="I44" s="5"/>
@@ -3210,7 +3185,7 @@
         <v>79</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H45" s="5"/>
       <c r="I45" s="5"/>
@@ -3241,7 +3216,7 @@
         <v>80</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
@@ -3272,7 +3247,7 @@
         <v>82</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H47" s="10"/>
       <c r="I47" s="10"/>
@@ -3303,7 +3278,7 @@
         <v>83</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H48" s="5"/>
       <c r="I48" s="5"/>
@@ -3334,7 +3309,7 @@
         <v>85</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H49" s="5"/>
       <c r="I49" s="5"/>
@@ -3365,7 +3340,7 @@
         <v>86</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H50" s="5"/>
       <c r="I50" s="5"/>
@@ -3396,7 +3371,7 @@
         <v>87</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H51" s="5"/>
       <c r="I51" s="5"/>
@@ -3427,7 +3402,7 @@
         <v>88</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H52" s="5"/>
       <c r="I52" s="5"/>
@@ -3458,7 +3433,7 @@
         <v>89</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H53" s="5"/>
       <c r="I53" s="5"/>
@@ -3489,7 +3464,7 @@
         <v>90</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H54" s="5"/>
       <c r="I54" s="5"/>
@@ -3520,7 +3495,7 @@
         <v>91</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H55" s="5"/>
       <c r="I55" s="5"/>
@@ -3551,7 +3526,7 @@
         <v>92</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H56" s="5"/>
       <c r="I56" s="5"/>
@@ -3582,7 +3557,7 @@
         <v>92</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H57" s="5"/>
       <c r="I57" s="5"/>
@@ -3613,7 +3588,7 @@
         <v>93</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H58" s="5"/>
       <c r="I58" s="5"/>
@@ -3644,7 +3619,7 @@
         <v>94</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H59" s="5"/>
       <c r="I59" s="5"/>
@@ -3675,7 +3650,7 @@
         <v>95</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H60" s="5"/>
       <c r="I60" s="5"/>
@@ -3706,7 +3681,7 @@
         <v>96</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H61" s="5"/>
       <c r="I61" s="5"/>
@@ -3737,7 +3712,7 @@
         <v>98</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H62" s="5"/>
       <c r="I62" s="5"/>
@@ -3768,7 +3743,7 @@
         <v>99</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H63" s="5"/>
       <c r="I63" s="5"/>
@@ -3799,7 +3774,7 @@
         <v>100</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H64" s="5"/>
       <c r="I64" s="5"/>
@@ -3830,7 +3805,7 @@
         <v>101</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H65" s="5"/>
       <c r="I65" s="5"/>
@@ -3861,7 +3836,7 @@
         <v>102</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H66" s="5"/>
       <c r="I66" s="5"/>
@@ -3892,7 +3867,7 @@
         <v>54</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H67" s="5"/>
       <c r="I67" s="5"/>
@@ -3923,7 +3898,7 @@
         <v>103</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H68" s="5"/>
       <c r="I68" s="5"/>
@@ -3954,7 +3929,7 @@
         <v>104</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H69" s="5"/>
       <c r="I69" s="5"/>
@@ -3985,7 +3960,7 @@
         <v>105</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H70" s="5"/>
       <c r="I70" s="5"/>
@@ -4016,7 +3991,7 @@
         <v>106</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H71" s="5"/>
       <c r="I71" s="5"/>
@@ -4047,7 +4022,7 @@
         <v>107</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H72" s="5"/>
       <c r="I72" s="5"/>
@@ -4078,7 +4053,7 @@
         <v>108</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H73" s="5"/>
       <c r="I73" s="5"/>
@@ -4109,7 +4084,7 @@
         <v>109</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H74" s="5"/>
       <c r="I74" s="5"/>
@@ -4140,7 +4115,7 @@
         <v>110</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H75" s="5"/>
       <c r="I75" s="5"/>
@@ -4171,7 +4146,7 @@
         <v>111</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H76" s="5"/>
       <c r="I76" s="5"/>
@@ -4202,7 +4177,7 @@
         <v>112</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H77" s="5"/>
       <c r="I77" s="5"/>
@@ -4233,7 +4208,7 @@
         <v>93</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H78" s="5"/>
       <c r="I78" s="5"/>
@@ -4264,7 +4239,7 @@
         <v>89</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H79" s="5"/>
       <c r="I79" s="5"/>
@@ -4295,7 +4270,7 @@
         <v>113</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H80" s="5"/>
       <c r="I80" s="5"/>
@@ -4326,7 +4301,7 @@
         <v>115</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H81" s="5"/>
       <c r="I81" s="5"/>
@@ -4357,7 +4332,7 @@
         <v>108</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H82" s="5"/>
       <c r="I82" s="5"/>
@@ -4388,7 +4363,7 @@
         <v>116</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H83" s="5"/>
       <c r="I83" s="5"/>
@@ -4419,7 +4394,7 @@
         <v>117</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H84" s="5"/>
       <c r="I84" s="5"/>
@@ -4450,7 +4425,7 @@
         <v>91</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H85" s="5"/>
       <c r="I85" s="5"/>
@@ -4481,7 +4456,7 @@
         <v>118</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H86" s="5"/>
       <c r="I86" s="5"/>
@@ -4512,7 +4487,7 @@
         <v>119</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H87" s="5"/>
       <c r="I87" s="5"/>
@@ -4543,7 +4518,7 @@
         <v>110</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H88" s="5"/>
       <c r="I88" s="5"/>
@@ -4574,7 +4549,7 @@
         <v>120</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H89" s="5"/>
       <c r="I89" s="5"/>
@@ -4605,7 +4580,7 @@
         <v>98</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H90" s="5"/>
       <c r="I90" s="5"/>
@@ -4636,7 +4611,7 @@
         <v>121</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H91" s="5"/>
       <c r="I91" s="5"/>
@@ -4667,7 +4642,7 @@
         <v>122</v>
       </c>
       <c r="G92" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H92" s="5"/>
       <c r="I92" s="5"/>
@@ -4698,7 +4673,7 @@
         <v>123</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H93" s="5"/>
       <c r="I93" s="5"/>
@@ -4729,7 +4704,7 @@
         <v>105</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H94" s="5"/>
       <c r="I94" s="5"/>
@@ -4760,7 +4735,7 @@
         <v>124</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H95" s="5"/>
       <c r="I95" s="5"/>
@@ -4791,7 +4766,7 @@
         <v>125</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H96" s="5"/>
       <c r="I96" s="5"/>
@@ -4822,7 +4797,7 @@
         <v>125</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H97" s="5"/>
       <c r="I97" s="5"/>
@@ -4853,7 +4828,7 @@
         <v>127</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H98" s="5"/>
       <c r="I98" s="5"/>
@@ -4884,7 +4859,7 @@
         <v>128</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H99" s="5"/>
       <c r="I99" s="5"/>
@@ -4915,7 +4890,7 @@
         <v>128</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H100" s="5"/>
       <c r="I100" s="5"/>
@@ -4946,7 +4921,7 @@
         <v>117</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H101" s="5"/>
       <c r="I101" s="5"/>
@@ -4977,7 +4952,7 @@
         <v>130</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H102" s="5"/>
       <c r="I102" s="5"/>
@@ -5008,7 +4983,7 @@
         <v>130</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H103" s="5"/>
       <c r="I103" s="5"/>
@@ -5039,7 +5014,7 @@
         <v>118</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H104" s="5"/>
       <c r="I104" s="5"/>
@@ -5070,7 +5045,7 @@
         <v>119</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H105" s="5"/>
       <c r="I105" s="5"/>
@@ -5101,7 +5076,7 @@
         <v>131</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H106" s="5"/>
       <c r="I106" s="5"/>
@@ -5132,7 +5107,7 @@
         <v>132</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H107" s="5"/>
       <c r="I107" s="5"/>
@@ -5163,7 +5138,7 @@
         <v>120</v>
       </c>
       <c r="G108" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H108" s="5"/>
       <c r="I108" s="5"/>
@@ -5194,7 +5169,7 @@
         <v>133</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H109" s="5"/>
       <c r="I109" s="5"/>
@@ -5225,7 +5200,7 @@
         <v>133</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H110" s="5"/>
       <c r="I110" s="5"/>
@@ -5256,7 +5231,7 @@
         <v>135</v>
       </c>
       <c r="G111" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H111" s="5"/>
       <c r="I111" s="5"/>
@@ -5287,7 +5262,7 @@
         <v>136</v>
       </c>
       <c r="G112" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H112" s="5"/>
       <c r="I112" s="5"/>
@@ -5318,7 +5293,7 @@
         <v>137</v>
       </c>
       <c r="G113" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H113" s="5"/>
       <c r="I113" s="5"/>
@@ -5349,7 +5324,7 @@
         <v>137</v>
       </c>
       <c r="G114" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H114" s="5"/>
       <c r="I114" s="5"/>
@@ -5380,7 +5355,7 @@
         <v>121</v>
       </c>
       <c r="G115" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H115" s="5"/>
       <c r="I115" s="5"/>
@@ -5411,7 +5386,7 @@
         <v>138</v>
       </c>
       <c r="G116" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H116" s="5"/>
       <c r="I116" s="5"/>
@@ -5442,7 +5417,7 @@
         <v>138</v>
       </c>
       <c r="G117" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H117" s="5"/>
       <c r="I117" s="5"/>
@@ -5473,7 +5448,7 @@
         <v>123</v>
       </c>
       <c r="G118" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H118" s="5"/>
       <c r="I118" s="5"/>
@@ -5504,7 +5479,7 @@
         <v>139</v>
       </c>
       <c r="G119" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H119" s="5"/>
       <c r="I119" s="5"/>
@@ -5535,7 +5510,7 @@
         <v>124</v>
       </c>
       <c r="G120" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H120" s="5"/>
       <c r="I120" s="5"/>
@@ -5566,7 +5541,7 @@
         <v>140</v>
       </c>
       <c r="G121" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H121" s="5"/>
       <c r="I121" s="5"/>
@@ -5597,7 +5572,7 @@
         <v>88</v>
       </c>
       <c r="G122" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H122" s="5"/>
       <c r="I122" s="5"/>
@@ -5628,7 +5603,7 @@
         <v>99</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H123" s="5"/>
       <c r="I123" s="5"/>
@@ -5659,7 +5634,7 @@
         <v>103</v>
       </c>
       <c r="G124" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H124" s="5"/>
       <c r="I124" s="5"/>
@@ -5690,7 +5665,7 @@
         <v>104</v>
       </c>
       <c r="G125" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H125" s="5"/>
       <c r="I125" s="5"/>
@@ -5721,7 +5696,7 @@
         <v>107</v>
       </c>
       <c r="G126" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H126" s="5"/>
       <c r="I126" s="5"/>
@@ -5752,7 +5727,7 @@
         <v>111</v>
       </c>
       <c r="G127" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H127" s="5"/>
       <c r="I127" s="5"/>
@@ -5783,7 +5758,7 @@
         <v>112</v>
       </c>
       <c r="G128" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H128" s="5"/>
       <c r="I128" s="5"/>
@@ -5814,7 +5789,7 @@
         <v>147</v>
       </c>
       <c r="G129" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H129" s="5"/>
       <c r="I129" s="5"/>
@@ -5845,7 +5820,7 @@
         <v>149</v>
       </c>
       <c r="G130" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H130" s="5"/>
       <c r="I130" s="5"/>
@@ -5876,7 +5851,7 @@
         <v>151</v>
       </c>
       <c r="G131" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H131" s="5"/>
       <c r="I131" s="5"/>
@@ -5907,7 +5882,7 @@
         <v>24</v>
       </c>
       <c r="G132" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H132" s="5"/>
       <c r="I132" s="5"/>
@@ -5938,7 +5913,7 @@
         <v>152</v>
       </c>
       <c r="G133" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H133" s="5"/>
       <c r="I133" s="5"/>
@@ -5969,7 +5944,7 @@
         <v>153</v>
       </c>
       <c r="G134" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H134" s="5"/>
       <c r="I134" s="5"/>
@@ -6000,7 +5975,7 @@
         <v>155</v>
       </c>
       <c r="G135" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H135" s="5"/>
       <c r="I135" s="5"/>
@@ -6031,7 +6006,7 @@
         <v>156</v>
       </c>
       <c r="G136" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H136" s="5"/>
       <c r="I136" s="5"/>
@@ -6062,7 +6037,7 @@
         <v>159</v>
       </c>
       <c r="G137" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H137" s="5"/>
       <c r="I137" s="5"/>
@@ -6093,7 +6068,7 @@
         <v>160</v>
       </c>
       <c r="G138" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H138" s="5"/>
       <c r="I138" s="5"/>
@@ -6124,7 +6099,7 @@
         <v>162</v>
       </c>
       <c r="G139" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H139" s="5"/>
       <c r="I139" s="5"/>
@@ -6155,7 +6130,7 @@
         <v>164</v>
       </c>
       <c r="G140" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H140" s="5"/>
       <c r="I140" s="5"/>
@@ -6186,7 +6161,7 @@
         <v>165</v>
       </c>
       <c r="G141" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H141" s="5"/>
       <c r="I141" s="5"/>
@@ -6217,7 +6192,7 @@
         <v>166</v>
       </c>
       <c r="G142" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H142" s="5"/>
       <c r="I142" s="5"/>
@@ -6248,7 +6223,7 @@
         <v>167</v>
       </c>
       <c r="G143" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H143" s="5"/>
       <c r="I143" s="5"/>
@@ -6279,7 +6254,7 @@
         <v>168</v>
       </c>
       <c r="G144" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H144" s="5"/>
       <c r="I144" s="5"/>
@@ -6310,7 +6285,7 @@
         <v>169</v>
       </c>
       <c r="G145" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H145" s="5"/>
       <c r="I145" s="5"/>
@@ -6341,7 +6316,7 @@
         <v>170</v>
       </c>
       <c r="G146" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H146" s="5"/>
       <c r="I146" s="5"/>
@@ -6372,7 +6347,7 @@
         <v>172</v>
       </c>
       <c r="G147" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H147" s="5"/>
       <c r="I147" s="5"/>
@@ -6403,7 +6378,7 @@
         <v>173</v>
       </c>
       <c r="G148" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H148" s="5"/>
       <c r="I148" s="5"/>
@@ -6434,7 +6409,7 @@
         <v>174</v>
       </c>
       <c r="G149" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H149" s="5"/>
       <c r="I149" s="5"/>
@@ -6465,7 +6440,7 @@
         <v>175</v>
       </c>
       <c r="G150" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H150" s="5"/>
       <c r="I150" s="5"/>
@@ -6496,7 +6471,7 @@
         <v>176</v>
       </c>
       <c r="G151" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H151" s="5"/>
       <c r="I151" s="5"/>
@@ -6527,7 +6502,7 @@
         <v>177</v>
       </c>
       <c r="G152" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H152" s="5"/>
       <c r="I152" s="5"/>
@@ -6558,7 +6533,7 @@
         <v>178</v>
       </c>
       <c r="G153" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H153" s="5"/>
       <c r="I153" s="5"/>
@@ -6589,7 +6564,7 @@
         <v>179</v>
       </c>
       <c r="G154" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H154" s="5"/>
       <c r="I154" s="5"/>
@@ -6620,7 +6595,7 @@
         <v>180</v>
       </c>
       <c r="G155" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H155" s="6">
         <v>46094</v>
@@ -6657,7 +6632,7 @@
         <v>181</v>
       </c>
       <c r="G156" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H156" s="6">
         <v>46094</v>
@@ -6694,7 +6669,7 @@
         <v>184</v>
       </c>
       <c r="G157" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H157" s="6">
         <v>46095</v>
@@ -6731,7 +6706,7 @@
         <v>185</v>
       </c>
       <c r="G158" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H158" s="6">
         <v>46128</v>
@@ -6766,7 +6741,7 @@
         <v>186</v>
       </c>
       <c r="G159" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H159" s="6">
         <v>46139</v>
@@ -6803,7 +6778,7 @@
         <v>188</v>
       </c>
       <c r="G160" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H160" s="6">
         <v>46141</v>
@@ -6840,7 +6815,7 @@
         <v>189</v>
       </c>
       <c r="G161" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H161" s="6">
         <v>46146</v>
@@ -6877,7 +6852,7 @@
         <v>191</v>
       </c>
       <c r="G162" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H162" s="6">
         <v>46147</v>
@@ -6914,7 +6889,7 @@
         <v>192</v>
       </c>
       <c r="G163" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H163" s="6">
         <v>46147</v>
@@ -6949,7 +6924,7 @@
         <v>193</v>
       </c>
       <c r="G164" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H164" s="6">
         <v>46149</v>
@@ -6986,7 +6961,7 @@
         <v>195</v>
       </c>
       <c r="G165" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H165" s="6">
         <v>46155</v>
@@ -7021,7 +6996,7 @@
         <v>196</v>
       </c>
       <c r="G166" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H166" s="6">
         <v>46156</v>
@@ -7056,7 +7031,7 @@
         <v>197</v>
       </c>
       <c r="G167" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H167" s="6">
         <v>46163</v>
@@ -7093,7 +7068,7 @@
         <v>198</v>
       </c>
       <c r="G168" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H168" s="6">
         <v>46164</v>
@@ -7128,7 +7103,7 @@
         <v>200</v>
       </c>
       <c r="G169" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H169" s="6">
         <v>46167</v>
@@ -7165,7 +7140,7 @@
         <v>201</v>
       </c>
       <c r="G170" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H170" s="12">
         <v>46170</v>
@@ -7202,7 +7177,7 @@
         <v>202</v>
       </c>
       <c r="G171" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H171" s="6">
         <v>46174</v>
@@ -7239,7 +7214,7 @@
         <v>142</v>
       </c>
       <c r="G172" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H172" s="5"/>
       <c r="I172" s="5"/>
@@ -7270,7 +7245,7 @@
         <v>143</v>
       </c>
       <c r="G173" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H173" s="5"/>
       <c r="I173" s="5"/>
@@ -7282,27 +7257,6 @@
       <c r="M173" s="5"/>
       <c r="N173" s="7"/>
       <c r="O173" s="5"/>
-    </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A174" s="15" t="s">
-        <v>317</v>
-      </c>
-      <c r="B174" s="15"/>
-      <c r="C174" s="15"/>
-      <c r="D174" s="15"/>
-      <c r="E174" s="15"/>
-      <c r="F174" s="15">
-        <v>172</v>
-      </c>
-      <c r="G174" s="15"/>
-      <c r="H174" s="15"/>
-      <c r="I174" s="16"/>
-      <c r="J174" s="15"/>
-      <c r="K174" s="15"/>
-      <c r="L174" s="15"/>
-      <c r="M174" s="15"/>
-      <c r="N174" s="17"/>
-      <c r="O174" s="15"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="K2:O173">

--- a/archivos/BD_Dashboard.xlsx
+++ b/archivos/BD_Dashboard.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mexscitum-my.sharepoint.com/personal/erik_torres_scitum_com_mx/Documents/Documentos/ETP/GitHub/SCITUM-AMX/archivos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="11_F25DC773A252ABDACC1048E8499F6DC65BDE58F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BF172CF-6686-440E-9CFD-06B05D27F3C2}"/>
+  <xr:revisionPtr revIDLastSave="83" documentId="11_F25DC773A252ABDACC1048E8499F6DC65BDE58F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43A9C145-ACE7-4C27-A686-D26D13EC3328}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inventario SDWAN &amp; FW" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Inventario SDWAN &amp; FW'!$A$1:$F$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Inventario SDWAN &amp; FW'!$A$1:$O$173</definedName>
     <definedName name="Project_Start">#REF!</definedName>
     <definedName name="RevisionDateOverall_PROJECT">#REF!</definedName>
   </definedNames>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1068" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="329">
   <si>
     <t>TIER</t>
   </si>
@@ -1057,6 +1057,12 @@
   </si>
   <si>
     <t>Se requiere llenar formulario</t>
+  </si>
+  <si>
+    <t>El envío del equipo se realizó el 09-jun-2026</t>
+  </si>
+  <si>
+    <t>El envío del equipo se realizó el 16-jun-2026</t>
   </si>
 </sst>
 </file>
@@ -1226,7 +1232,187 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="29">
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFA6C9EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFBE2D5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD0D0D0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFA6C9EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFBE2D5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD0D0D0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF000000"/>
@@ -1375,8 +1561,8 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Estilo de tabla 1" pivot="0" count="2" xr9:uid="{91CECC61-D972-4E77-B7C8-EE0397AA0D98}">
-      <tableStyleElement type="wholeTable" dxfId="10"/>
-      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="wholeTable" dxfId="28"/>
+      <tableStyleElement type="headerRow" dxfId="27"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1667,6 +1853,7 @@
     <col min="6" max="6" width="24.85546875" customWidth="1"/>
     <col min="7" max="7" width="17.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="26.140625" customWidth="1"/>
+    <col min="14" max="14" width="187.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -2139,7 +2326,9 @@
       <c r="M13" s="5">
         <v>1.04</v>
       </c>
-      <c r="N13" s="7"/>
+      <c r="N13" s="7" t="s">
+        <v>328</v>
+      </c>
       <c r="O13" s="5"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
@@ -2174,7 +2363,9 @@
       <c r="M14" s="5">
         <v>1.05</v>
       </c>
-      <c r="N14" s="7"/>
+      <c r="N14" s="7" t="s">
+        <v>328</v>
+      </c>
       <c r="O14" s="5"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -2208,7 +2399,7 @@
       </c>
       <c r="M15" s="6"/>
       <c r="N15" s="7" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="O15" s="5"/>
     </row>
@@ -7259,7 +7450,37 @@
       <c r="O173" s="5"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="K2:O173">
+  <autoFilter ref="A1:O173" xr:uid="{0331BFDC-0F24-4E57-9413-AB479E741FFA}"/>
+  <conditionalFormatting sqref="K2:O14 K16:O173 K15:M15 O15">
+    <cfRule type="cellIs" dxfId="26" priority="10" operator="equal">
+      <formula>"Impl. Cancelada"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="25" priority="11" operator="equal">
+      <formula>"Listo para embarcar"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="24" priority="12" operator="equal">
+      <formula>"Equipo en transito"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="23" priority="13" operator="equal">
+      <formula>"Cancelada"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="22" priority="14" operator="equal">
+      <formula>"En preconfiguración"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="21" priority="15" operator="equal">
+      <formula>"Dependencia"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="20" priority="16" operator="equal">
+      <formula>"Listo para programar"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="19" priority="17" operator="equal">
+      <formula>"Exitosa"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="18" priority="18" operator="equal">
+      <formula>"Programada"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N15">
     <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
       <formula>"Impl. Cancelada"</formula>
     </cfRule>

--- a/archivos/BD_Dashboard.xlsx
+++ b/archivos/BD_Dashboard.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mexscitum-my.sharepoint.com/personal/erik_torres_scitum_com_mx/Documents/Documentos/ETP/GitHub/SCITUM-AMX/archivos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="83" documentId="11_F25DC773A252ABDACC1048E8499F6DC65BDE58F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43A9C145-ACE7-4C27-A686-D26D13EC3328}"/>
+  <xr:revisionPtr revIDLastSave="92" documentId="11_F25DC773A252ABDACC1048E8499F6DC65BDE58F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{022355D2-FD7A-440A-9156-0B7E9E491716}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inventario SDWAN &amp; FW" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Inventario SDWAN &amp; FW'!$A$1:$O$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Inventario SDWAN &amp; FW'!$A$1:$G$173</definedName>
     <definedName name="Project_Start">#REF!</definedName>
     <definedName name="RevisionDateOverall_PROJECT">#REF!</definedName>
   </definedNames>
@@ -46,7 +46,7 @@
     <author>Erik Alejandro Torres Piña</author>
   </authors>
   <commentList>
-    <comment ref="F47" authorId="0" shapeId="0" xr:uid="{7CC6357A-B412-45CB-BD3D-D6499F9D7776}">
+    <comment ref="F46" authorId="0" shapeId="0" xr:uid="{6FB5E093-75BB-4CD6-ABA5-AFCD435DECC5}">
       <text>
         <r>
           <rPr>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="333">
   <si>
     <t>TIER</t>
   </si>
@@ -137,9 +137,6 @@
     <t>Nueva York (JFK)</t>
   </si>
   <si>
-    <t>Dependencia de AMX, no tiene UTM ni enlace de internet</t>
-  </si>
-  <si>
     <t>Miami (MIA)</t>
   </si>
   <si>
@@ -152,9 +149,6 @@
     <t>Los Angeles (LAX)</t>
   </si>
   <si>
-    <t>Sin enlace, pendiente la cross</t>
-  </si>
-  <si>
     <t>Canada</t>
   </si>
   <si>
@@ -362,12 +356,6 @@
     <t>Mérida (MID)</t>
   </si>
   <si>
-    <t>Monterrey Terminal A</t>
-  </si>
-  <si>
-    <t>Monterrey (MTY)</t>
-  </si>
-  <si>
     <t xml:space="preserve">ATO Nacional </t>
   </si>
   <si>
@@ -422,9 +410,6 @@
     <t>AEROMEXICO GDL NVO HANGAR DE MANTO</t>
   </si>
   <si>
-    <t>Monterrey (MTY) Hangar</t>
-  </si>
-  <si>
     <t>Ciudad del Carmen (CME)</t>
   </si>
   <si>
@@ -1013,9 +998,6 @@
     <t>Impl. Cancelada</t>
   </si>
   <si>
-    <t>El equipo se envió desde el 09-jun-2026</t>
-  </si>
-  <si>
     <t>Dependencia de AMX, no tiene UTM ni enlace de internet. AMX indico que esperaramos para enviar los equipos</t>
   </si>
   <si>
@@ -1023,9 +1005,6 @@
   </si>
   <si>
     <t>AWS East</t>
-  </si>
-  <si>
-    <t>Aeroméxico reporta que no recibió el equipo. SCITUM levantó el reporte. Numero de reporte DHL: CS62301998 Ejecutivo DHL seguimiento de reporte: Jesus Hernández. 25-jun-2026 AMX confirma recepción de equipo</t>
   </si>
   <si>
     <t>Esquema
@@ -1056,13 +1035,47 @@
     <t>SI</t>
   </si>
   <si>
-    <t>Se requiere llenar formulario</t>
-  </si>
-  <si>
     <t>El envío del equipo se realizó el 09-jun-2026</t>
   </si>
   <si>
     <t>El envío del equipo se realizó el 16-jun-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hace falta la información del segmento de interconexión con el Firewall </t>
+  </si>
+  <si>
+    <t>No se identifica información en el Archivo del drive</t>
+  </si>
+  <si>
+    <t>No hay foto</t>
+  </si>
+  <si>
+    <t>Se requiere llenar formulario para acceso a IDC. La foto parece ser la misma que la de LAS, por favor confirmar</t>
+  </si>
+  <si>
+    <t>Dependencia de AMX, no tiene UTM ni enlace de internet. AMX indico que esperaramos para enviar los equipos.
+No se observa si hay Firewall. No se observa disponibilidad en contacto eléctrico. Se solicita nombre, numero de celular, ID del técnico local (ultimos 4 digitos) y copia de identificación oficial.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No se observa disponibilidad de contactos electricos. Rack elevado, no se observa a que altura. </t>
+  </si>
+  <si>
+    <t>No hay foto. Sin enlace, pendiente la cross</t>
+  </si>
+  <si>
+    <t>Monterrey Terminal A (MTY)</t>
+  </si>
+  <si>
+    <t>Monterrey (MTY_CARGO)</t>
+  </si>
+  <si>
+    <t>Monterrey (MTY_HANGAR) Hangar</t>
+  </si>
+  <si>
+    <t>MTY_CARGO</t>
+  </si>
+  <si>
+    <t>MTY_HANGAR</t>
   </si>
 </sst>
 </file>
@@ -1181,7 +1194,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1228,18 +1241,21 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="29">
+  <dxfs count="12">
     <dxf>
       <font>
         <color rgb="FF000000"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
+          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1335,176 +1351,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFA6C9EC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFBE2D5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD0D0D0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFA6C9EC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFBE2D5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD0D0D0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <b/>
         <i val="0"/>
         <strike val="0"/>
@@ -1561,8 +1407,8 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Estilo de tabla 1" pivot="0" count="2" xr9:uid="{91CECC61-D972-4E77-B7C8-EE0397AA0D98}">
-      <tableStyleElement type="wholeTable" dxfId="28"/>
-      <tableStyleElement type="headerRow" dxfId="27"/>
+      <tableStyleElement type="wholeTable" dxfId="11"/>
+      <tableStyleElement type="headerRow" dxfId="10"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1843,20 +1689,19 @@
     <tabColor theme="5" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:O173"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="4.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="1.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.85546875" customWidth="1"/>
-    <col min="7" max="7" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="26.140625" customWidth="1"/>
-    <col min="14" max="14" width="187.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="1.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.81640625" customWidth="1"/>
+    <col min="7" max="7" width="17.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1876,7 +1721,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>6</v>
@@ -1900,49 +1745,53 @@
         <v>12</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H2" s="6">
         <v>46210</v>
       </c>
       <c r="I2" s="5"/>
       <c r="J2" s="9">
-        <v>0.625</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
+        <v>312</v>
+      </c>
+      <c r="L2" s="6">
+        <v>46189</v>
+      </c>
+      <c r="M2" s="5">
+        <v>1.06</v>
+      </c>
       <c r="N2" s="7" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="O2" s="5"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5" t="s">
@@ -1952,32 +1801,32 @@
         <v>14</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H3" s="6">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="I3" s="5"/>
       <c r="J3" s="9">
-        <v>0.41666666666666669</v>
+        <v>0.625</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="L3" s="5"/>
       <c r="M3" s="5"/>
       <c r="N3" s="7" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="O3" s="5"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" s="5">
         <v>1</v>
       </c>
@@ -1989,34 +1838,32 @@
         <v>14</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H4" s="6">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="I4" s="5"/>
       <c r="J4" s="9">
-        <v>0.875</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="L4" s="6">
-        <v>46182</v>
-      </c>
-      <c r="M4" s="6"/>
+        <v>312</v>
+      </c>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
       <c r="N4" s="7" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="O4" s="5"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" s="5">
         <v>1</v>
       </c>
@@ -2025,16 +1872,16 @@
         <v>13</v>
       </c>
       <c r="D5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>28</v>
-      </c>
       <c r="G5" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
@@ -2049,11 +1896,11 @@
         <v>1.01</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="O5" s="5"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>3</v>
       </c>
@@ -2062,16 +1909,16 @@
         <v>13</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
@@ -2085,28 +1932,30 @@
       <c r="M6" s="5">
         <v>1.02</v>
       </c>
-      <c r="N6" s="7"/>
+      <c r="N6" s="7" t="s">
+        <v>323</v>
+      </c>
       <c r="O6" s="5"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
         <v>2</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
@@ -2120,45 +1969,45 @@
       <c r="M7" s="5">
         <v>1.03</v>
       </c>
-      <c r="N7" s="7"/>
+      <c r="N7" s="7" t="s">
+        <v>323</v>
+      </c>
       <c r="O7" s="5"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="H8" s="5"/>
+        <v>311</v>
+      </c>
+      <c r="H8" s="1"/>
       <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
+      <c r="J8" s="3"/>
       <c r="K8" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="L8" s="6">
-        <v>46189</v>
-      </c>
-      <c r="M8" s="5">
-        <v>1.06</v>
-      </c>
-      <c r="N8" s="7"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="7" t="s">
+        <v>325</v>
+      </c>
       <c r="O8" s="5"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>1</v>
       </c>
@@ -2170,28 +2019,30 @@
         <v>14</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="H9" s="1"/>
+        <v>311</v>
+      </c>
+      <c r="H9" s="2"/>
       <c r="I9" s="5"/>
       <c r="J9" s="3"/>
       <c r="K9" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
+      <c r="L9" s="6">
+        <v>46182</v>
+      </c>
+      <c r="M9" s="6"/>
       <c r="N9" s="7" t="s">
-        <v>20</v>
+        <v>326</v>
       </c>
       <c r="O9" s="5"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>1</v>
       </c>
@@ -2203,15 +2054,15 @@
         <v>14</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="H10" s="2"/>
+        <v>311</v>
+      </c>
+      <c r="H10" s="1"/>
       <c r="I10" s="5"/>
       <c r="J10" s="3"/>
       <c r="K10" s="5" t="s">
@@ -2222,13 +2073,13 @@
       </c>
       <c r="M10" s="6"/>
       <c r="N10" s="7" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="O10" s="5"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5" t="s">
@@ -2238,63 +2089,65 @@
         <v>14</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="H11" s="1"/>
+        <v>311</v>
+      </c>
+      <c r="H11" s="2"/>
       <c r="I11" s="5"/>
       <c r="J11" s="3"/>
       <c r="K11" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="L11" s="6">
-        <v>46182</v>
-      </c>
-      <c r="M11" s="6"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
       <c r="N11" s="7" t="s">
-        <v>25</v>
+        <v>323</v>
       </c>
       <c r="O11" s="5"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="H12" s="2"/>
+        <v>316</v>
+      </c>
+      <c r="H12" s="5"/>
       <c r="I12" s="5"/>
-      <c r="J12" s="3"/>
+      <c r="J12" s="5"/>
       <c r="K12" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
+        <v>22</v>
+      </c>
+      <c r="L12" s="6">
+        <v>46189</v>
+      </c>
+      <c r="M12" s="5">
+        <v>1.04</v>
+      </c>
       <c r="N12" s="7" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="O12" s="5"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
         <v>3</v>
       </c>
@@ -2306,69 +2159,67 @@
         <v>33</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>34</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
       <c r="K13" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L13" s="6">
         <v>46189</v>
       </c>
       <c r="M13" s="5">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="O13" s="5"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
       <c r="K14" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L14" s="6">
-        <v>46189</v>
-      </c>
-      <c r="M14" s="5">
-        <v>1.05</v>
-      </c>
+        <v>46182</v>
+      </c>
+      <c r="M14" s="6"/>
       <c r="N14" s="7" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="O14" s="5"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <v>1</v>
       </c>
@@ -2377,363 +2228,363 @@
         <v>13</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="5"/>
       <c r="K15" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L15" s="6">
-        <v>46182</v>
-      </c>
-      <c r="M15" s="6"/>
-      <c r="N15" s="7" t="s">
-        <v>327</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="N15" s="7"/>
       <c r="O15" s="5"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
       <c r="J16" s="5"/>
       <c r="K16" s="5" t="s">
-        <v>308</v>
+        <v>22</v>
       </c>
       <c r="L16" s="5"/>
       <c r="M16" s="5">
-        <v>2.0099999999999998</v>
+        <v>2.02</v>
       </c>
       <c r="N16" s="7"/>
       <c r="O16" s="5"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
       <c r="K17" s="5" t="s">
-        <v>308</v>
+        <v>22</v>
       </c>
       <c r="L17" s="5"/>
       <c r="M17" s="5">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="N17" s="7"/>
       <c r="O17" s="5"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
       <c r="J18" s="5"/>
       <c r="K18" s="5" t="s">
-        <v>308</v>
+        <v>22</v>
       </c>
       <c r="L18" s="5"/>
       <c r="M18" s="5">
-        <v>2.0299999999999998</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="N18" s="7"/>
       <c r="O18" s="5"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
       <c r="J19" s="5"/>
       <c r="K19" s="5" t="s">
-        <v>308</v>
+        <v>22</v>
       </c>
       <c r="L19" s="5"/>
-      <c r="M19" s="5">
-        <v>2.04</v>
+      <c r="M19" s="14">
+        <v>2.08</v>
       </c>
       <c r="N19" s="7"/>
       <c r="O19" s="5"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
       <c r="J20" s="5"/>
       <c r="K20" s="5" t="s">
-        <v>308</v>
+        <v>22</v>
       </c>
       <c r="L20" s="5"/>
       <c r="M20" s="5">
-        <v>2.0499999999999998</v>
+        <v>2.09</v>
       </c>
       <c r="N20" s="7"/>
       <c r="O20" s="5"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
       <c r="J21" s="5"/>
       <c r="K21" s="5" t="s">
-        <v>308</v>
+        <v>22</v>
       </c>
       <c r="L21" s="5"/>
-      <c r="M21" s="5">
-        <v>2.06</v>
+      <c r="M21" s="14">
+        <v>2.1</v>
       </c>
       <c r="N21" s="7"/>
       <c r="O21" s="5"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="H22" s="5"/>
+        <v>311</v>
+      </c>
+      <c r="H22" s="8"/>
       <c r="I22" s="5"/>
       <c r="J22" s="5"/>
       <c r="K22" s="5" t="s">
-        <v>308</v>
+        <v>22</v>
       </c>
       <c r="L22" s="5"/>
       <c r="M22" s="5">
-        <v>2.0699999999999998</v>
-      </c>
-      <c r="N22" s="7"/>
+        <v>3.04</v>
+      </c>
+      <c r="N22" s="7" t="s">
+        <v>307</v>
+      </c>
       <c r="O22" s="5"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
       <c r="J23" s="5"/>
       <c r="K23" s="5" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="L23" s="5"/>
-      <c r="M23" s="14">
-        <v>2.08</v>
+      <c r="M23" s="5">
+        <v>2.0299999999999998</v>
       </c>
       <c r="N23" s="7"/>
       <c r="O23" s="5"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
       <c r="J24" s="5"/>
       <c r="K24" s="5" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="L24" s="5"/>
       <c r="M24" s="5">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="N24" s="7"/>
       <c r="O24" s="5"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
       <c r="J25" s="5"/>
       <c r="K25" s="5" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="L25" s="5"/>
-      <c r="M25" s="14">
-        <v>2.1</v>
+      <c r="M25" s="5">
+        <v>2.0499999999999998</v>
       </c>
       <c r="N25" s="7"/>
       <c r="O25" s="5"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26" s="5">
         <v>1</v>
       </c>
@@ -2742,22 +2593,22 @@
         <v>13</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
       <c r="J26" s="5"/>
       <c r="K26" s="5" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="L26" s="5"/>
       <c r="M26" s="5">
@@ -2766,7 +2617,7 @@
       <c r="N26" s="7"/>
       <c r="O26" s="5"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" s="5">
         <v>3</v>
       </c>
@@ -2775,22 +2626,22 @@
         <v>13</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H27" s="5"/>
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
       <c r="K27" s="5" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="L27" s="5"/>
       <c r="M27" s="5">
@@ -2799,7 +2650,7 @@
       <c r="N27" s="7"/>
       <c r="O27" s="5"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A28" s="5">
         <v>3</v>
       </c>
@@ -2811,32 +2662,32 @@
         <v>14</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H28" s="8"/>
       <c r="I28" s="5"/>
       <c r="J28" s="5"/>
       <c r="K28" s="5" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="L28" s="5"/>
       <c r="M28" s="5">
         <v>3.03</v>
       </c>
       <c r="N28" s="7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="O28" s="5"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A29" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5" t="s">
@@ -2846,199 +2697,197 @@
         <v>14</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H29" s="8"/>
       <c r="I29" s="5"/>
       <c r="J29" s="5"/>
       <c r="K29" s="5" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="L29" s="5"/>
       <c r="M29" s="5">
-        <v>3.04</v>
+        <v>4.01</v>
       </c>
       <c r="N29" s="7" t="s">
-        <v>313</v>
+        <v>41</v>
       </c>
       <c r="O29" s="5"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A30" s="5">
         <v>3</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5" t="s">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>218</v>
+        <v>261</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>42</v>
+        <v>121</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="H30" s="8"/>
+        <v>316</v>
+      </c>
+      <c r="H30" s="5"/>
       <c r="I30" s="5"/>
       <c r="J30" s="5"/>
       <c r="K30" s="5" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="L30" s="5"/>
       <c r="M30" s="5">
-        <v>4.01</v>
-      </c>
-      <c r="N30" s="7" t="s">
-        <v>43</v>
-      </c>
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="N30" s="7"/>
       <c r="O30" s="5"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31" s="5">
         <v>3</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
       <c r="J31" s="5"/>
       <c r="K31" s="5" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="L31" s="5"/>
       <c r="M31" s="5">
-        <v>4.0199999999999996</v>
+        <v>4.03</v>
       </c>
       <c r="N31" s="7"/>
       <c r="O31" s="5"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A32" s="5">
         <v>3</v>
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
       <c r="J32" s="5"/>
       <c r="K32" s="5" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="L32" s="5"/>
       <c r="M32" s="5">
-        <v>4.03</v>
+        <v>4.04</v>
       </c>
       <c r="N32" s="7"/>
       <c r="O32" s="5"/>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A33" s="5">
         <v>3</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>291</v>
+        <v>268</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
       <c r="K33" s="5" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="L33" s="5"/>
       <c r="M33" s="5">
-        <v>4.04</v>
+        <v>4.05</v>
       </c>
       <c r="N33" s="7"/>
       <c r="O33" s="5"/>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A34" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5" t="s">
-        <v>84</v>
+        <v>13</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>273</v>
+        <v>214</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>134</v>
+        <v>42</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="H34" s="5"/>
+        <v>311</v>
+      </c>
+      <c r="H34" s="8"/>
       <c r="I34" s="5"/>
       <c r="J34" s="5"/>
       <c r="K34" s="5" t="s">
-        <v>308</v>
+        <v>37</v>
       </c>
       <c r="L34" s="5"/>
-      <c r="M34" s="5">
-        <v>4.05</v>
-      </c>
-      <c r="N34" s="7"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="7" t="s">
+        <v>43</v>
+      </c>
       <c r="O34" s="5"/>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A35" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5" t="s">
@@ -3048,2921 +2897,2923 @@
         <v>14</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H35" s="8"/>
       <c r="I35" s="5"/>
-      <c r="J35" s="5"/>
+      <c r="J35" s="9"/>
       <c r="K35" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L35" s="5"/>
       <c r="M35" s="5"/>
       <c r="N35" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O35" s="5"/>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A36" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="H36" s="8"/>
       <c r="I36" s="5"/>
-      <c r="J36" s="9"/>
+      <c r="J36" s="5"/>
       <c r="K36" s="5" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="L36" s="5"/>
       <c r="M36" s="5"/>
-      <c r="N36" s="7" t="s">
-        <v>48</v>
-      </c>
+      <c r="N36" s="7"/>
       <c r="O36" s="5"/>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A37" s="5">
         <v>1</v>
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="H37" s="8"/>
+        <v>311</v>
+      </c>
+      <c r="H37" s="5"/>
       <c r="I37" s="5"/>
       <c r="J37" s="5"/>
       <c r="K37" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L37" s="5"/>
       <c r="M37" s="5"/>
-      <c r="N37" s="7"/>
+      <c r="N37" s="7" t="s">
+        <v>49</v>
+      </c>
       <c r="O37" s="5"/>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A38" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5" t="s">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H38" s="5"/>
       <c r="I38" s="5"/>
       <c r="J38" s="5"/>
       <c r="K38" s="5" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="L38" s="5"/>
       <c r="M38" s="5"/>
-      <c r="N38" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="O38" s="5"/>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N38" s="7"/>
+      <c r="O38" s="5" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A39" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H39" s="5"/>
       <c r="I39" s="5"/>
       <c r="J39" s="5"/>
       <c r="K39" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L39" s="5"/>
       <c r="M39" s="5"/>
-      <c r="N39" s="7"/>
+      <c r="N39" s="7" t="s">
+        <v>321</v>
+      </c>
       <c r="O39" s="5" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A40" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
       <c r="J40" s="5"/>
       <c r="K40" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L40" s="5"/>
       <c r="M40" s="5"/>
-      <c r="N40" s="7"/>
+      <c r="N40" s="7" t="s">
+        <v>322</v>
+      </c>
       <c r="O40" s="5" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A41" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H41" s="5"/>
       <c r="I41" s="5"/>
       <c r="J41" s="5"/>
       <c r="K41" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L41" s="5"/>
       <c r="M41" s="5"/>
       <c r="N41" s="7"/>
-      <c r="O41" s="5" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O41" s="5"/>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A42" s="5">
         <v>0</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F42" s="5" t="s">
         <v>73</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H42" s="5"/>
       <c r="I42" s="5"/>
       <c r="J42" s="5"/>
       <c r="K42" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L42" s="5"/>
       <c r="M42" s="5"/>
       <c r="N42" s="7"/>
       <c r="O42" s="5"/>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A43" s="5">
         <v>0</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H43" s="5"/>
       <c r="I43" s="5"/>
       <c r="J43" s="5"/>
       <c r="K43" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L43" s="5"/>
       <c r="M43" s="5"/>
       <c r="N43" s="7"/>
       <c r="O43" s="5"/>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A44" s="5">
         <v>0</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H44" s="5"/>
       <c r="I44" s="5"/>
       <c r="J44" s="5"/>
       <c r="K44" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L44" s="5"/>
       <c r="M44" s="5"/>
       <c r="N44" s="7"/>
       <c r="O44" s="5"/>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A45" s="5">
         <v>0</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H45" s="5"/>
       <c r="I45" s="5"/>
       <c r="J45" s="5"/>
       <c r="K45" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L45" s="5"/>
       <c r="M45" s="5"/>
       <c r="N45" s="7"/>
       <c r="O45" s="5"/>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A46" s="5">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A46" s="10">
         <v>0</v>
       </c>
       <c r="B46" s="5"/>
-      <c r="C46" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="F46" s="5" t="s">
+      <c r="C46" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E46" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="F46" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="G46" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="H46" s="5"/>
-      <c r="I46" s="5"/>
-      <c r="J46" s="5"/>
+      <c r="G46" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="H46" s="10"/>
+      <c r="I46" s="10"/>
+      <c r="J46" s="10"/>
       <c r="K46" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="L46" s="5"/>
-      <c r="M46" s="5"/>
-      <c r="N46" s="7"/>
-      <c r="O46" s="5"/>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A47" s="10">
+        <v>72</v>
+      </c>
+      <c r="L46" s="10"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="11"/>
+      <c r="O46" s="10"/>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A47" s="5">
         <v>0</v>
       </c>
       <c r="B47" s="5"/>
-      <c r="C47" s="10" t="s">
+      <c r="C47" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="F47" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="D47" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E47" s="10" t="s">
-        <v>234</v>
-      </c>
-      <c r="F47" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="G47" s="10" t="s">
-        <v>318</v>
-      </c>
-      <c r="H47" s="10"/>
-      <c r="I47" s="10"/>
-      <c r="J47" s="10"/>
+      <c r="G47" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="H47" s="5"/>
+      <c r="I47" s="5"/>
+      <c r="J47" s="5"/>
       <c r="K47" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="L47" s="10"/>
-      <c r="M47" s="10"/>
-      <c r="N47" s="11"/>
-      <c r="O47" s="10"/>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+      <c r="L47" s="5"/>
+      <c r="M47" s="5"/>
+      <c r="N47" s="7"/>
+      <c r="O47" s="5"/>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A48" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F48" s="5" t="s">
         <v>83</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H48" s="5"/>
       <c r="I48" s="5"/>
       <c r="J48" s="5"/>
       <c r="K48" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L48" s="5"/>
       <c r="M48" s="5"/>
       <c r="N48" s="7"/>
       <c r="O48" s="5"/>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A49" s="5">
         <v>1</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="F49" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="D49" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="F49" s="5" t="s">
-        <v>85</v>
-      </c>
       <c r="G49" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H49" s="5"/>
       <c r="I49" s="5"/>
       <c r="J49" s="5"/>
       <c r="K49" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L49" s="5"/>
       <c r="M49" s="5"/>
       <c r="N49" s="7"/>
       <c r="O49" s="5"/>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A50" s="5">
         <v>1</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H50" s="5"/>
       <c r="I50" s="5"/>
       <c r="J50" s="5"/>
       <c r="K50" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L50" s="5"/>
       <c r="M50" s="5"/>
       <c r="N50" s="7"/>
       <c r="O50" s="5"/>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A51" s="5">
         <v>1</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H51" s="5"/>
       <c r="I51" s="5"/>
       <c r="J51" s="5"/>
       <c r="K51" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L51" s="5"/>
       <c r="M51" s="5"/>
       <c r="N51" s="7"/>
       <c r="O51" s="5"/>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A52" s="5">
         <v>1</v>
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H52" s="5"/>
       <c r="I52" s="5"/>
       <c r="J52" s="5"/>
       <c r="K52" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L52" s="5"/>
       <c r="M52" s="5"/>
       <c r="N52" s="7"/>
       <c r="O52" s="5"/>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A53" s="5">
         <v>1</v>
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H53" s="5"/>
       <c r="I53" s="5"/>
       <c r="J53" s="5"/>
       <c r="K53" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L53" s="5"/>
       <c r="M53" s="5"/>
       <c r="N53" s="7"/>
       <c r="O53" s="5"/>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A54" s="5">
         <v>1</v>
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H54" s="5"/>
       <c r="I54" s="5"/>
       <c r="J54" s="5"/>
       <c r="K54" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L54" s="5"/>
       <c r="M54" s="5"/>
       <c r="N54" s="7"/>
       <c r="O54" s="5"/>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A55" s="5">
         <v>1</v>
       </c>
       <c r="B55" s="5"/>
       <c r="C55" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H55" s="5"/>
       <c r="I55" s="5"/>
       <c r="J55" s="5"/>
       <c r="K55" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L55" s="5"/>
       <c r="M55" s="5"/>
       <c r="N55" s="7"/>
       <c r="O55" s="5"/>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A56" s="5">
         <v>1</v>
       </c>
       <c r="B56" s="5"/>
       <c r="C56" s="5" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H56" s="5"/>
       <c r="I56" s="5"/>
       <c r="J56" s="5"/>
       <c r="K56" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L56" s="5"/>
       <c r="M56" s="5"/>
       <c r="N56" s="7"/>
       <c r="O56" s="5"/>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A57" s="5">
         <v>1</v>
       </c>
       <c r="B57" s="5"/>
       <c r="C57" s="5" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H57" s="5"/>
       <c r="I57" s="5"/>
       <c r="J57" s="5"/>
       <c r="K57" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L57" s="5"/>
       <c r="M57" s="5"/>
       <c r="N57" s="7"/>
       <c r="O57" s="5"/>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A58" s="5">
         <v>1</v>
       </c>
       <c r="B58" s="5"/>
       <c r="C58" s="5" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H58" s="5"/>
       <c r="I58" s="5"/>
       <c r="J58" s="5"/>
       <c r="K58" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L58" s="5"/>
       <c r="M58" s="5"/>
       <c r="N58" s="7"/>
       <c r="O58" s="5"/>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A59" s="5">
         <v>1</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>94</v>
+        <v>328</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H59" s="5"/>
       <c r="I59" s="5"/>
       <c r="J59" s="5"/>
       <c r="K59" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L59" s="5"/>
       <c r="M59" s="5"/>
       <c r="N59" s="7"/>
       <c r="O59" s="5"/>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A60" s="5">
         <v>1</v>
       </c>
       <c r="B60" s="5"/>
       <c r="C60" s="5" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>234</v>
+        <v>331</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>95</v>
+        <v>329</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H60" s="5"/>
       <c r="I60" s="5"/>
       <c r="J60" s="5"/>
       <c r="K60" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L60" s="5"/>
       <c r="M60" s="5"/>
       <c r="N60" s="7"/>
       <c r="O60" s="5"/>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A61" s="5">
         <v>1</v>
       </c>
       <c r="B61" s="5"/>
       <c r="C61" s="5" t="s">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H61" s="5"/>
       <c r="I61" s="5"/>
       <c r="J61" s="5"/>
       <c r="K61" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L61" s="5"/>
       <c r="M61" s="5"/>
       <c r="N61" s="7"/>
       <c r="O61" s="5"/>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A62" s="5">
         <v>1</v>
       </c>
       <c r="B62" s="5"/>
       <c r="C62" s="5" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H62" s="5"/>
       <c r="I62" s="5"/>
       <c r="J62" s="5"/>
       <c r="K62" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L62" s="5"/>
       <c r="M62" s="5"/>
       <c r="N62" s="7"/>
       <c r="O62" s="5"/>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A63" s="5">
         <v>1</v>
       </c>
       <c r="B63" s="5"/>
       <c r="C63" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H63" s="5"/>
       <c r="I63" s="5"/>
       <c r="J63" s="5"/>
       <c r="K63" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L63" s="5"/>
       <c r="M63" s="5"/>
       <c r="N63" s="7"/>
       <c r="O63" s="5"/>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A64" s="5">
         <v>1</v>
       </c>
       <c r="B64" s="5"/>
       <c r="C64" s="5" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H64" s="5"/>
       <c r="I64" s="5"/>
       <c r="J64" s="5"/>
       <c r="K64" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L64" s="5"/>
       <c r="M64" s="5"/>
       <c r="N64" s="7"/>
       <c r="O64" s="5"/>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A65" s="5">
         <v>1</v>
       </c>
       <c r="B65" s="5"/>
       <c r="C65" s="5" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H65" s="5"/>
       <c r="I65" s="5"/>
       <c r="J65" s="5"/>
       <c r="K65" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L65" s="5"/>
       <c r="M65" s="5"/>
       <c r="N65" s="7"/>
       <c r="O65" s="5"/>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A66" s="5">
         <v>1</v>
       </c>
       <c r="B66" s="5"/>
       <c r="C66" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>246</v>
+        <v>218</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H66" s="5"/>
       <c r="I66" s="5"/>
       <c r="J66" s="5"/>
       <c r="K66" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L66" s="5"/>
       <c r="M66" s="5"/>
       <c r="N66" s="7"/>
       <c r="O66" s="5"/>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A67" s="5">
         <v>1</v>
       </c>
       <c r="B67" s="5"/>
       <c r="C67" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H67" s="5"/>
       <c r="I67" s="5"/>
       <c r="J67" s="5"/>
       <c r="K67" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L67" s="5"/>
       <c r="M67" s="5"/>
       <c r="N67" s="7"/>
       <c r="O67" s="5"/>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A68" s="5">
         <v>1</v>
       </c>
       <c r="B68" s="5"/>
       <c r="C68" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H68" s="5"/>
       <c r="I68" s="5"/>
       <c r="J68" s="5"/>
       <c r="K68" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L68" s="5"/>
       <c r="M68" s="5"/>
       <c r="N68" s="7"/>
       <c r="O68" s="5"/>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A69" s="5">
         <v>1</v>
       </c>
       <c r="B69" s="5"/>
       <c r="C69" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H69" s="5"/>
       <c r="I69" s="5"/>
       <c r="J69" s="5"/>
       <c r="K69" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L69" s="5"/>
       <c r="M69" s="5"/>
       <c r="N69" s="7"/>
       <c r="O69" s="5"/>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A70" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B70" s="5"/>
       <c r="C70" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H70" s="5"/>
       <c r="I70" s="5"/>
       <c r="J70" s="5"/>
       <c r="K70" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L70" s="5"/>
       <c r="M70" s="5"/>
       <c r="N70" s="7"/>
       <c r="O70" s="5"/>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A71" s="5">
         <v>2</v>
       </c>
       <c r="B71" s="5"/>
       <c r="C71" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H71" s="5"/>
       <c r="I71" s="5"/>
       <c r="J71" s="5"/>
       <c r="K71" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L71" s="5"/>
       <c r="M71" s="5"/>
       <c r="N71" s="7"/>
       <c r="O71" s="5"/>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A72" s="5">
         <v>2</v>
       </c>
       <c r="B72" s="5"/>
       <c r="C72" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H72" s="5"/>
       <c r="I72" s="5"/>
       <c r="J72" s="5"/>
       <c r="K72" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L72" s="5"/>
       <c r="M72" s="5"/>
       <c r="N72" s="7"/>
       <c r="O72" s="5"/>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A73" s="5">
         <v>2</v>
       </c>
       <c r="B73" s="5"/>
       <c r="C73" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H73" s="5"/>
       <c r="I73" s="5"/>
       <c r="J73" s="5"/>
       <c r="K73" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L73" s="5"/>
       <c r="M73" s="5"/>
       <c r="N73" s="7"/>
       <c r="O73" s="5"/>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A74" s="5">
         <v>2</v>
       </c>
       <c r="B74" s="5"/>
       <c r="C74" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H74" s="5"/>
       <c r="I74" s="5"/>
       <c r="J74" s="5"/>
       <c r="K74" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L74" s="5"/>
       <c r="M74" s="5"/>
       <c r="N74" s="7"/>
       <c r="O74" s="5"/>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A75" s="5">
         <v>2</v>
       </c>
       <c r="B75" s="5"/>
       <c r="C75" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H75" s="5"/>
       <c r="I75" s="5"/>
       <c r="J75" s="5"/>
       <c r="K75" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L75" s="5"/>
       <c r="M75" s="5"/>
       <c r="N75" s="7"/>
       <c r="O75" s="5"/>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A76" s="5">
         <v>2</v>
       </c>
       <c r="B76" s="5"/>
       <c r="C76" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H76" s="5"/>
       <c r="I76" s="5"/>
       <c r="J76" s="5"/>
       <c r="K76" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L76" s="5"/>
       <c r="M76" s="5"/>
       <c r="N76" s="7"/>
       <c r="O76" s="5"/>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A77" s="5">
         <v>2</v>
       </c>
       <c r="B77" s="5"/>
       <c r="C77" s="5" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>256</v>
+        <v>235</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H77" s="5"/>
       <c r="I77" s="5"/>
       <c r="J77" s="5"/>
       <c r="K77" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L77" s="5"/>
       <c r="M77" s="5"/>
       <c r="N77" s="7"/>
       <c r="O77" s="5"/>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A78" s="5">
         <v>2</v>
       </c>
       <c r="B78" s="5"/>
       <c r="C78" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H78" s="5"/>
       <c r="I78" s="5"/>
       <c r="J78" s="5"/>
       <c r="K78" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L78" s="5"/>
       <c r="M78" s="5"/>
       <c r="N78" s="7"/>
       <c r="O78" s="5"/>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A79" s="5">
         <v>2</v>
       </c>
       <c r="B79" s="5"/>
       <c r="C79" s="5" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H79" s="5"/>
       <c r="I79" s="5"/>
       <c r="J79" s="5"/>
       <c r="K79" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L79" s="5"/>
       <c r="M79" s="5"/>
       <c r="N79" s="7"/>
       <c r="O79" s="5"/>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A80" s="5">
         <v>2</v>
       </c>
       <c r="B80" s="5"/>
       <c r="C80" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>234</v>
+        <v>332</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>113</v>
+        <v>330</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H80" s="5"/>
       <c r="I80" s="5"/>
       <c r="J80" s="5"/>
       <c r="K80" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L80" s="5"/>
       <c r="M80" s="5"/>
       <c r="N80" s="7"/>
       <c r="O80" s="5"/>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A81" s="5">
         <v>2</v>
       </c>
       <c r="B81" s="5"/>
       <c r="C81" s="5" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H81" s="5"/>
       <c r="I81" s="5"/>
       <c r="J81" s="5"/>
       <c r="K81" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L81" s="5"/>
       <c r="M81" s="5"/>
       <c r="N81" s="7"/>
       <c r="O81" s="5"/>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A82" s="5">
         <v>2</v>
       </c>
       <c r="B82" s="5"/>
       <c r="C82" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E82" s="5" t="s">
         <v>252</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H82" s="5"/>
       <c r="I82" s="5"/>
       <c r="J82" s="5"/>
       <c r="K82" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L82" s="5"/>
       <c r="M82" s="5"/>
       <c r="N82" s="7"/>
       <c r="O82" s="5"/>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A83" s="5">
         <v>2</v>
       </c>
       <c r="B83" s="5"/>
       <c r="C83" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H83" s="5"/>
       <c r="I83" s="5"/>
       <c r="J83" s="5"/>
       <c r="K83" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L83" s="5"/>
       <c r="M83" s="5"/>
       <c r="N83" s="7"/>
       <c r="O83" s="5"/>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A84" s="5">
         <v>2</v>
       </c>
       <c r="B84" s="5"/>
       <c r="C84" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>258</v>
+        <v>233</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H84" s="5"/>
       <c r="I84" s="5"/>
       <c r="J84" s="5"/>
       <c r="K84" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L84" s="5"/>
       <c r="M84" s="5"/>
       <c r="N84" s="7"/>
       <c r="O84" s="5"/>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A85" s="5">
         <v>2</v>
       </c>
       <c r="B85" s="5"/>
       <c r="C85" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H85" s="5"/>
       <c r="I85" s="5"/>
       <c r="J85" s="5"/>
       <c r="K85" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L85" s="5"/>
       <c r="M85" s="5"/>
       <c r="N85" s="7"/>
       <c r="O85" s="5"/>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A86" s="5">
         <v>2</v>
       </c>
       <c r="B86" s="5"/>
       <c r="C86" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H86" s="5"/>
       <c r="I86" s="5"/>
       <c r="J86" s="5"/>
       <c r="K86" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L86" s="5"/>
       <c r="M86" s="5"/>
       <c r="N86" s="7"/>
       <c r="O86" s="5"/>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A87" s="5">
         <v>2</v>
       </c>
       <c r="B87" s="5"/>
       <c r="C87" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H87" s="5"/>
       <c r="I87" s="5"/>
       <c r="J87" s="5"/>
       <c r="K87" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L87" s="5"/>
       <c r="M87" s="5"/>
       <c r="N87" s="7"/>
       <c r="O87" s="5"/>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A88" s="5">
         <v>2</v>
       </c>
       <c r="B88" s="5"/>
       <c r="C88" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H88" s="5"/>
       <c r="I88" s="5"/>
       <c r="J88" s="5"/>
       <c r="K88" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L88" s="5"/>
       <c r="M88" s="5"/>
       <c r="N88" s="7"/>
       <c r="O88" s="5"/>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A89" s="5">
         <v>2</v>
       </c>
       <c r="B89" s="5"/>
       <c r="C89" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H89" s="5"/>
       <c r="I89" s="5"/>
       <c r="J89" s="5"/>
       <c r="K89" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L89" s="5"/>
       <c r="M89" s="5"/>
       <c r="N89" s="7"/>
       <c r="O89" s="5"/>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A90" s="5">
         <v>2</v>
       </c>
       <c r="B90" s="5"/>
       <c r="C90" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H90" s="5"/>
       <c r="I90" s="5"/>
       <c r="J90" s="5"/>
       <c r="K90" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L90" s="5"/>
       <c r="M90" s="5"/>
       <c r="N90" s="7"/>
       <c r="O90" s="5"/>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A91" s="5">
         <v>2</v>
       </c>
       <c r="B91" s="5"/>
       <c r="C91" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H91" s="5"/>
       <c r="I91" s="5"/>
       <c r="J91" s="5"/>
       <c r="K91" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L91" s="5"/>
       <c r="M91" s="5"/>
       <c r="N91" s="7"/>
       <c r="O91" s="5"/>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A92" s="5">
         <v>2</v>
       </c>
       <c r="B92" s="5"/>
       <c r="C92" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="G92" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H92" s="5"/>
       <c r="I92" s="5"/>
       <c r="J92" s="5"/>
       <c r="K92" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L92" s="5"/>
       <c r="M92" s="5"/>
       <c r="N92" s="7"/>
       <c r="O92" s="5"/>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A93" s="5">
         <v>2</v>
       </c>
       <c r="B93" s="5"/>
       <c r="C93" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H93" s="5"/>
       <c r="I93" s="5"/>
       <c r="J93" s="5"/>
       <c r="K93" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L93" s="5"/>
       <c r="M93" s="5"/>
       <c r="N93" s="7"/>
       <c r="O93" s="5"/>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A94" s="5">
         <v>2</v>
       </c>
       <c r="B94" s="5"/>
       <c r="C94" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H94" s="5"/>
       <c r="I94" s="5"/>
       <c r="J94" s="5"/>
       <c r="K94" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L94" s="5"/>
       <c r="M94" s="5"/>
       <c r="N94" s="7"/>
       <c r="O94" s="5"/>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A95" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B95" s="5"/>
       <c r="C95" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H95" s="5"/>
       <c r="I95" s="5"/>
       <c r="J95" s="5"/>
       <c r="K95" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L95" s="5"/>
       <c r="M95" s="5"/>
       <c r="N95" s="7"/>
       <c r="O95" s="5"/>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A96" s="5">
         <v>3</v>
       </c>
       <c r="B96" s="5"/>
       <c r="C96" s="5" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H96" s="5"/>
       <c r="I96" s="5"/>
       <c r="J96" s="5"/>
       <c r="K96" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L96" s="5"/>
       <c r="M96" s="5"/>
       <c r="N96" s="7"/>
       <c r="O96" s="5"/>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A97" s="5">
         <v>3</v>
       </c>
       <c r="B97" s="5"/>
       <c r="C97" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H97" s="5"/>
       <c r="I97" s="5"/>
       <c r="J97" s="5"/>
       <c r="K97" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L97" s="5"/>
       <c r="M97" s="5"/>
       <c r="N97" s="7"/>
       <c r="O97" s="5"/>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A98" s="5">
         <v>3</v>
       </c>
       <c r="B98" s="5"/>
       <c r="C98" s="5" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H98" s="5"/>
       <c r="I98" s="5"/>
       <c r="J98" s="5"/>
       <c r="K98" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L98" s="5"/>
       <c r="M98" s="5"/>
       <c r="N98" s="7"/>
       <c r="O98" s="5"/>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A99" s="5">
         <v>3</v>
       </c>
       <c r="B99" s="5"/>
       <c r="C99" s="5" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H99" s="5"/>
       <c r="I99" s="5"/>
       <c r="J99" s="5"/>
       <c r="K99" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L99" s="5"/>
       <c r="M99" s="5"/>
       <c r="N99" s="7"/>
       <c r="O99" s="5"/>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A100" s="5">
         <v>3</v>
       </c>
       <c r="B100" s="5"/>
       <c r="C100" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H100" s="5"/>
       <c r="I100" s="5"/>
       <c r="J100" s="5"/>
       <c r="K100" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L100" s="5"/>
       <c r="M100" s="5"/>
       <c r="N100" s="7"/>
       <c r="O100" s="5"/>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A101" s="5">
         <v>3</v>
       </c>
       <c r="B101" s="5"/>
       <c r="C101" s="5" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H101" s="5"/>
       <c r="I101" s="5"/>
       <c r="J101" s="5"/>
       <c r="K101" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L101" s="5"/>
       <c r="M101" s="5"/>
       <c r="N101" s="7"/>
       <c r="O101" s="5"/>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A102" s="5">
         <v>3</v>
       </c>
       <c r="B102" s="5"/>
       <c r="C102" s="5" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H102" s="5"/>
       <c r="I102" s="5"/>
       <c r="J102" s="5"/>
       <c r="K102" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L102" s="5"/>
       <c r="M102" s="5"/>
       <c r="N102" s="7"/>
       <c r="O102" s="5"/>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A103" s="5">
         <v>3</v>
       </c>
       <c r="B103" s="5"/>
       <c r="C103" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H103" s="5"/>
       <c r="I103" s="5"/>
       <c r="J103" s="5"/>
       <c r="K103" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L103" s="5"/>
       <c r="M103" s="5"/>
       <c r="N103" s="7"/>
       <c r="O103" s="5"/>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A104" s="5">
         <v>3</v>
       </c>
       <c r="B104" s="5"/>
       <c r="C104" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H104" s="5"/>
       <c r="I104" s="5"/>
       <c r="J104" s="5"/>
       <c r="K104" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L104" s="5"/>
       <c r="M104" s="5"/>
       <c r="N104" s="7"/>
       <c r="O104" s="5"/>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A105" s="5">
         <v>3</v>
       </c>
       <c r="B105" s="5"/>
       <c r="C105" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H105" s="5"/>
       <c r="I105" s="5"/>
       <c r="J105" s="5"/>
       <c r="K105" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L105" s="5"/>
       <c r="M105" s="5"/>
       <c r="N105" s="7"/>
       <c r="O105" s="5"/>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A106" s="5">
         <v>3</v>
       </c>
       <c r="B106" s="5"/>
       <c r="C106" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H106" s="5"/>
       <c r="I106" s="5"/>
       <c r="J106" s="5"/>
       <c r="K106" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L106" s="5"/>
       <c r="M106" s="5"/>
       <c r="N106" s="7"/>
       <c r="O106" s="5"/>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A107" s="5">
         <v>3</v>
       </c>
       <c r="B107" s="5"/>
       <c r="C107" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H107" s="5"/>
       <c r="I107" s="5"/>
       <c r="J107" s="5"/>
       <c r="K107" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L107" s="5"/>
       <c r="M107" s="5"/>
       <c r="N107" s="7"/>
       <c r="O107" s="5"/>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A108" s="5">
         <v>3</v>
       </c>
       <c r="B108" s="5"/>
       <c r="C108" s="5" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G108" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H108" s="5"/>
       <c r="I108" s="5"/>
       <c r="J108" s="5"/>
       <c r="K108" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L108" s="5"/>
       <c r="M108" s="5"/>
       <c r="N108" s="7"/>
       <c r="O108" s="5"/>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A109" s="5">
         <v>3</v>
       </c>
       <c r="B109" s="5"/>
       <c r="C109" s="5" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H109" s="5"/>
       <c r="I109" s="5"/>
       <c r="J109" s="5"/>
       <c r="K109" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L109" s="5"/>
       <c r="M109" s="5"/>
       <c r="N109" s="7"/>
       <c r="O109" s="5"/>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A110" s="5">
         <v>3</v>
       </c>
       <c r="B110" s="5"/>
       <c r="C110" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H110" s="5"/>
       <c r="I110" s="5"/>
       <c r="J110" s="5"/>
       <c r="K110" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L110" s="5"/>
       <c r="M110" s="5"/>
       <c r="N110" s="7"/>
       <c r="O110" s="5"/>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A111" s="5">
         <v>3</v>
       </c>
       <c r="B111" s="5"/>
       <c r="C111" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="G111" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H111" s="5"/>
       <c r="I111" s="5"/>
       <c r="J111" s="5"/>
       <c r="K111" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L111" s="5"/>
       <c r="M111" s="5"/>
       <c r="N111" s="7"/>
       <c r="O111" s="5"/>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A112" s="5">
         <v>3</v>
       </c>
       <c r="B112" s="5"/>
       <c r="C112" s="5" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="G112" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H112" s="5"/>
       <c r="I112" s="5"/>
       <c r="J112" s="5"/>
       <c r="K112" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L112" s="5"/>
       <c r="M112" s="5"/>
-      <c r="N112" s="7"/>
+      <c r="N112" s="16"/>
       <c r="O112" s="5"/>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A113" s="5">
         <v>3</v>
       </c>
       <c r="B113" s="5"/>
       <c r="C113" s="5" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="G113" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H113" s="5"/>
       <c r="I113" s="5"/>
       <c r="J113" s="5"/>
       <c r="K113" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L113" s="5"/>
       <c r="M113" s="5"/>
-      <c r="N113" s="7"/>
+      <c r="N113" s="16"/>
       <c r="O113" s="5"/>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A114" s="5">
         <v>3</v>
       </c>
       <c r="B114" s="5"/>
       <c r="C114" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>276</v>
+        <v>257</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="G114" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H114" s="5"/>
       <c r="I114" s="5"/>
       <c r="J114" s="5"/>
       <c r="K114" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L114" s="5"/>
       <c r="M114" s="5"/>
-      <c r="N114" s="7"/>
+      <c r="N114" s="16"/>
       <c r="O114" s="5"/>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A115" s="5">
         <v>3</v>
       </c>
       <c r="B115" s="5"/>
       <c r="C115" s="5" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="G115" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H115" s="5"/>
       <c r="I115" s="5"/>
       <c r="J115" s="5"/>
       <c r="K115" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L115" s="5"/>
       <c r="M115" s="5"/>
-      <c r="N115" s="7"/>
+      <c r="N115" s="16"/>
       <c r="O115" s="5"/>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A116" s="5">
         <v>3</v>
       </c>
       <c r="B116" s="5"/>
       <c r="C116" s="5" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="G116" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H116" s="5"/>
       <c r="I116" s="5"/>
       <c r="J116" s="5"/>
       <c r="K116" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L116" s="5"/>
       <c r="M116" s="5"/>
-      <c r="N116" s="7"/>
+      <c r="N116" s="16"/>
       <c r="O116" s="5"/>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A117" s="5">
         <v>3</v>
       </c>
       <c r="B117" s="5"/>
       <c r="C117" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>277</v>
+        <v>258</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="G117" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H117" s="5"/>
       <c r="I117" s="5"/>
       <c r="J117" s="5"/>
       <c r="K117" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L117" s="5"/>
       <c r="M117" s="5"/>
-      <c r="N117" s="7"/>
+      <c r="N117" s="16"/>
       <c r="O117" s="5"/>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A118" s="5">
         <v>3</v>
       </c>
       <c r="B118" s="5"/>
       <c r="C118" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="G118" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H118" s="5"/>
       <c r="I118" s="5"/>
       <c r="J118" s="5"/>
       <c r="K118" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L118" s="5"/>
       <c r="M118" s="5"/>
-      <c r="N118" s="7"/>
+      <c r="N118" s="16"/>
       <c r="O118" s="5"/>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A119" s="5">
         <v>3</v>
       </c>
       <c r="B119" s="5"/>
       <c r="C119" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>278</v>
+        <v>259</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="G119" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H119" s="5"/>
       <c r="I119" s="5"/>
       <c r="J119" s="5"/>
       <c r="K119" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L119" s="5"/>
       <c r="M119" s="5"/>
-      <c r="N119" s="7"/>
+      <c r="N119" s="16"/>
       <c r="O119" s="5"/>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A120" s="5">
         <v>3</v>
       </c>
       <c r="B120" s="5"/>
       <c r="C120" s="5" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>264</v>
+        <v>229</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G120" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H120" s="5"/>
       <c r="I120" s="5"/>
       <c r="J120" s="5"/>
       <c r="K120" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L120" s="5"/>
       <c r="M120" s="5"/>
-      <c r="N120" s="7"/>
+      <c r="N120" s="16"/>
       <c r="O120" s="5"/>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A121" s="5">
         <v>3</v>
       </c>
       <c r="B121" s="5"/>
       <c r="C121" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>140</v>
+        <v>86</v>
       </c>
       <c r="G121" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H121" s="5"/>
       <c r="I121" s="5"/>
       <c r="J121" s="5"/>
       <c r="K121" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L121" s="5"/>
       <c r="M121" s="5"/>
-      <c r="N121" s="7"/>
+      <c r="N121" s="16"/>
       <c r="O121" s="5"/>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A122" s="5">
         <v>3</v>
       </c>
       <c r="B122" s="5"/>
       <c r="C122" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="G122" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H122" s="5"/>
       <c r="I122" s="5"/>
       <c r="J122" s="5"/>
       <c r="K122" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L122" s="5"/>
       <c r="M122" s="5"/>
-      <c r="N122" s="7"/>
+      <c r="N122" s="16"/>
       <c r="O122" s="5"/>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A123" s="5">
         <v>3</v>
       </c>
       <c r="B123" s="5"/>
       <c r="C123" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F123" s="5" t="s">
         <v>99</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H123" s="5"/>
       <c r="I123" s="5"/>
       <c r="J123" s="5"/>
       <c r="K123" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L123" s="5"/>
       <c r="M123" s="5"/>
-      <c r="N123" s="7"/>
+      <c r="N123" s="16"/>
       <c r="O123" s="5"/>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A124" s="5">
         <v>3</v>
       </c>
       <c r="B124" s="5"/>
       <c r="C124" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G124" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H124" s="5"/>
       <c r="I124" s="5"/>
       <c r="J124" s="5"/>
       <c r="K124" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L124" s="5"/>
       <c r="M124" s="5"/>
-      <c r="N124" s="7"/>
+      <c r="N124" s="16"/>
       <c r="O124" s="5"/>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A125" s="5">
         <v>3</v>
       </c>
       <c r="B125" s="5"/>
       <c r="C125" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G125" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H125" s="5"/>
       <c r="I125" s="5"/>
       <c r="J125" s="5"/>
       <c r="K125" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L125" s="5"/>
       <c r="M125" s="5"/>
-      <c r="N125" s="7"/>
+      <c r="N125" s="16"/>
       <c r="O125" s="5"/>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A126" s="5">
         <v>3</v>
       </c>
       <c r="B126" s="5"/>
       <c r="C126" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F126" s="5" t="s">
         <v>107</v>
       </c>
       <c r="G126" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H126" s="5"/>
       <c r="I126" s="5"/>
       <c r="J126" s="5"/>
       <c r="K126" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L126" s="5"/>
       <c r="M126" s="5"/>
-      <c r="N126" s="7"/>
+      <c r="N126" s="16"/>
       <c r="O126" s="5"/>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A127" s="5">
         <v>3</v>
       </c>
       <c r="B127" s="5"/>
       <c r="C127" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G127" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H127" s="5"/>
       <c r="I127" s="5"/>
       <c r="J127" s="5"/>
       <c r="K127" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L127" s="5"/>
       <c r="M127" s="5"/>
-      <c r="N127" s="7"/>
+      <c r="N127" s="16"/>
       <c r="O127" s="5"/>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A128" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B128" s="5"/>
       <c r="C128" s="5" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>53</v>
+        <v>141</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>256</v>
+        <v>275</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>112</v>
+        <v>142</v>
       </c>
       <c r="G128" s="5" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="H128" s="5"/>
       <c r="I128" s="5"/>
       <c r="J128" s="5"/>
       <c r="K128" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L128" s="5"/>
       <c r="M128" s="5"/>
-      <c r="N128" s="7"/>
+      <c r="N128" s="16"/>
       <c r="O128" s="5"/>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A129" s="5">
         <v>2</v>
       </c>
@@ -5971,29 +5822,29 @@
         <v>13</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G129" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H129" s="5"/>
       <c r="I129" s="5"/>
       <c r="J129" s="5"/>
       <c r="K129" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L129" s="5"/>
       <c r="M129" s="5"/>
-      <c r="N129" s="7"/>
+      <c r="N129" s="16"/>
       <c r="O129" s="5"/>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A130" s="5">
         <v>2</v>
       </c>
@@ -6002,91 +5853,91 @@
         <v>13</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="G130" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H130" s="5"/>
       <c r="I130" s="5"/>
       <c r="J130" s="5"/>
       <c r="K130" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L130" s="5"/>
       <c r="M130" s="5"/>
-      <c r="N130" s="7"/>
+      <c r="N130" s="16"/>
       <c r="O130" s="5"/>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A131" s="5">
         <v>2</v>
       </c>
       <c r="B131" s="5"/>
       <c r="C131" s="5" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>150</v>
+        <v>14</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>282</v>
+        <v>203</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>151</v>
+        <v>23</v>
       </c>
       <c r="G131" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H131" s="5"/>
       <c r="I131" s="5"/>
       <c r="J131" s="5"/>
       <c r="K131" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L131" s="5"/>
       <c r="M131" s="5"/>
-      <c r="N131" s="7"/>
+      <c r="N131" s="16"/>
       <c r="O131" s="5"/>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A132" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B132" s="5"/>
       <c r="C132" s="5" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="D132" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>208</v>
+        <v>278</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>24</v>
+        <v>147</v>
       </c>
       <c r="G132" s="5" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H132" s="5"/>
       <c r="I132" s="5"/>
       <c r="J132" s="5"/>
       <c r="K132" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L132" s="5"/>
       <c r="M132" s="5"/>
-      <c r="N132" s="7"/>
+      <c r="N132" s="16"/>
       <c r="O132" s="5"/>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A133" s="5">
         <v>3</v>
       </c>
@@ -6098,26 +5949,26 @@
         <v>14</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="G133" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H133" s="5"/>
       <c r="I133" s="5"/>
       <c r="J133" s="5"/>
       <c r="K133" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L133" s="5"/>
       <c r="M133" s="5"/>
-      <c r="N133" s="7"/>
+      <c r="N133" s="16"/>
       <c r="O133" s="5"/>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A134" s="5">
         <v>3</v>
       </c>
@@ -6126,29 +5977,29 @@
         <v>13</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>14</v>
+        <v>149</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G134" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H134" s="5"/>
       <c r="I134" s="5"/>
       <c r="J134" s="5"/>
       <c r="K134" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L134" s="5"/>
       <c r="M134" s="5"/>
-      <c r="N134" s="7"/>
+      <c r="N134" s="16"/>
       <c r="O134" s="5"/>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A135" s="5">
         <v>3</v>
       </c>
@@ -6157,29 +6008,29 @@
         <v>13</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>154</v>
+        <v>14</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G135" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H135" s="5"/>
       <c r="I135" s="5"/>
       <c r="J135" s="5"/>
       <c r="K135" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L135" s="5"/>
       <c r="M135" s="5"/>
-      <c r="N135" s="7"/>
+      <c r="N135" s="16"/>
       <c r="O135" s="5"/>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A136" s="5">
         <v>3</v>
       </c>
@@ -6191,26 +6042,26 @@
         <v>14</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G136" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H136" s="5"/>
       <c r="I136" s="5"/>
       <c r="J136" s="5"/>
       <c r="K136" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L136" s="5"/>
       <c r="M136" s="5"/>
-      <c r="N136" s="7"/>
+      <c r="N136" s="16"/>
       <c r="O136" s="5"/>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A137" s="5">
         <v>3</v>
       </c>
@@ -6222,26 +6073,26 @@
         <v>14</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="G137" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H137" s="5"/>
       <c r="I137" s="5"/>
       <c r="J137" s="5"/>
       <c r="K137" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L137" s="5"/>
       <c r="M137" s="5"/>
-      <c r="N137" s="7"/>
+      <c r="N137" s="16"/>
       <c r="O137" s="5"/>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A138" s="5">
         <v>3</v>
       </c>
@@ -6250,543 +6101,549 @@
         <v>13</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>14</v>
+        <v>156</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G138" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H138" s="5"/>
       <c r="I138" s="5"/>
       <c r="J138" s="5"/>
       <c r="K138" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L138" s="5"/>
       <c r="M138" s="5"/>
-      <c r="N138" s="7"/>
+      <c r="N138" s="16"/>
       <c r="O138" s="5"/>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A139" s="5">
         <v>3</v>
       </c>
       <c r="B139" s="5"/>
       <c r="C139" s="5" t="s">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>161</v>
+        <v>51</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G139" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H139" s="5"/>
       <c r="I139" s="5"/>
       <c r="J139" s="5"/>
       <c r="K139" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L139" s="5"/>
       <c r="M139" s="5"/>
-      <c r="N139" s="7"/>
+      <c r="N139" s="16"/>
       <c r="O139" s="5"/>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A140" s="5">
         <v>3</v>
       </c>
       <c r="B140" s="5"/>
       <c r="C140" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="F140" s="5" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G140" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H140" s="5"/>
       <c r="I140" s="5"/>
       <c r="J140" s="5"/>
       <c r="K140" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L140" s="5"/>
       <c r="M140" s="5"/>
-      <c r="N140" s="7"/>
+      <c r="N140" s="16"/>
       <c r="O140" s="5"/>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A141" s="5">
         <v>3</v>
       </c>
       <c r="B141" s="5"/>
       <c r="C141" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>293</v>
+        <v>229</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="G141" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H141" s="5"/>
       <c r="I141" s="5"/>
       <c r="J141" s="5"/>
       <c r="K141" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L141" s="5"/>
       <c r="M141" s="5"/>
-      <c r="N141" s="7"/>
+      <c r="N141" s="16"/>
       <c r="O141" s="5"/>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A142" s="5">
         <v>3</v>
       </c>
       <c r="B142" s="5"/>
       <c r="C142" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="G142" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H142" s="5"/>
       <c r="I142" s="5"/>
       <c r="J142" s="5"/>
       <c r="K142" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L142" s="5"/>
       <c r="M142" s="5"/>
-      <c r="N142" s="7"/>
+      <c r="N142" s="16"/>
       <c r="O142" s="5"/>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A143" s="5">
         <v>3</v>
       </c>
       <c r="B143" s="5"/>
       <c r="C143" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E143" s="5" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F143" s="5" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="G143" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H143" s="5"/>
       <c r="I143" s="5"/>
       <c r="J143" s="5"/>
       <c r="K143" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L143" s="5"/>
       <c r="M143" s="5"/>
-      <c r="N143" s="7"/>
+      <c r="N143" s="16"/>
       <c r="O143" s="5"/>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A144" s="5">
         <v>3</v>
       </c>
       <c r="B144" s="5"/>
       <c r="C144" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F144" s="5" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G144" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H144" s="5"/>
       <c r="I144" s="5"/>
       <c r="J144" s="5"/>
       <c r="K144" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L144" s="5"/>
       <c r="M144" s="5"/>
-      <c r="N144" s="7"/>
+      <c r="N144" s="16"/>
       <c r="O144" s="5"/>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A145" s="5">
         <v>3</v>
       </c>
       <c r="B145" s="5"/>
       <c r="C145" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F145" s="5" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G145" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H145" s="5"/>
       <c r="I145" s="5"/>
       <c r="J145" s="5"/>
       <c r="K145" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L145" s="5"/>
       <c r="M145" s="5"/>
-      <c r="N145" s="7"/>
+      <c r="N145" s="16"/>
       <c r="O145" s="5"/>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A146" s="5">
         <v>3</v>
       </c>
       <c r="B146" s="5"/>
       <c r="C146" s="5" t="s">
-        <v>84</v>
+        <v>166</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="G146" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H146" s="5"/>
       <c r="I146" s="5"/>
       <c r="J146" s="5"/>
       <c r="K146" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L146" s="5"/>
       <c r="M146" s="5"/>
-      <c r="N146" s="7"/>
+      <c r="N146" s="16"/>
       <c r="O146" s="5"/>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A147" s="5">
         <v>3</v>
       </c>
       <c r="B147" s="5"/>
       <c r="C147" s="5" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F147" s="5" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="G147" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H147" s="5"/>
       <c r="I147" s="5"/>
       <c r="J147" s="5"/>
       <c r="K147" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L147" s="5"/>
       <c r="M147" s="5"/>
-      <c r="N147" s="7"/>
+      <c r="N147" s="16"/>
       <c r="O147" s="5"/>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A148" s="5">
         <v>3</v>
       </c>
       <c r="B148" s="5"/>
       <c r="C148" s="5" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="G148" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H148" s="5"/>
       <c r="I148" s="5"/>
       <c r="J148" s="5"/>
       <c r="K148" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L148" s="5"/>
       <c r="M148" s="5"/>
-      <c r="N148" s="7"/>
+      <c r="N148" s="16"/>
       <c r="O148" s="5"/>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A149" s="5">
         <v>3</v>
       </c>
       <c r="B149" s="5"/>
       <c r="C149" s="5" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F149" s="5" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="G149" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H149" s="5"/>
       <c r="I149" s="5"/>
       <c r="J149" s="5"/>
       <c r="K149" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L149" s="5"/>
       <c r="M149" s="5"/>
-      <c r="N149" s="7"/>
+      <c r="N149" s="16"/>
       <c r="O149" s="5"/>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A150" s="5">
         <v>3</v>
       </c>
       <c r="B150" s="5"/>
       <c r="C150" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D150" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E150" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="F150" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="D150" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E150" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="F150" s="5" t="s">
-        <v>175</v>
-      </c>
       <c r="G150" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H150" s="5"/>
       <c r="I150" s="5"/>
       <c r="J150" s="5"/>
       <c r="K150" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L150" s="5"/>
       <c r="M150" s="5"/>
-      <c r="N150" s="7"/>
+      <c r="N150" s="16"/>
       <c r="O150" s="5"/>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A151" s="5">
         <v>3</v>
       </c>
       <c r="B151" s="5"/>
       <c r="C151" s="5" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="G151" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H151" s="5"/>
       <c r="I151" s="5"/>
       <c r="J151" s="5"/>
       <c r="K151" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L151" s="5"/>
       <c r="M151" s="5"/>
-      <c r="N151" s="7"/>
+      <c r="N151" s="16"/>
       <c r="O151" s="5"/>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A152" s="5">
         <v>3</v>
       </c>
       <c r="B152" s="5"/>
       <c r="C152" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="G152" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H152" s="5"/>
       <c r="I152" s="5"/>
       <c r="J152" s="5"/>
       <c r="K152" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L152" s="5"/>
       <c r="M152" s="5"/>
-      <c r="N152" s="7"/>
+      <c r="N152" s="16"/>
       <c r="O152" s="5"/>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A153" s="5">
         <v>3</v>
       </c>
       <c r="B153" s="5"/>
       <c r="C153" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="G153" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H153" s="5"/>
       <c r="I153" s="5"/>
       <c r="J153" s="5"/>
       <c r="K153" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L153" s="5"/>
       <c r="M153" s="5"/>
-      <c r="N153" s="7"/>
+      <c r="N153" s="16"/>
       <c r="O153" s="5"/>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A154" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B154" s="5"/>
       <c r="C154" s="5" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>234</v>
+        <v>304</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G154" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="H154" s="5"/>
-      <c r="I154" s="5"/>
-      <c r="J154" s="5"/>
+        <v>316</v>
+      </c>
+      <c r="H154" s="6">
+        <v>46094</v>
+      </c>
+      <c r="I154" s="9">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="J154" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="K154" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L154" s="5"/>
       <c r="M154" s="5"/>
-      <c r="N154" s="7"/>
+      <c r="N154" s="16"/>
       <c r="O154" s="5"/>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A155" s="5">
         <v>0</v>
       </c>
       <c r="B155" s="5"/>
       <c r="C155" s="5" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D155" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="G155" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H155" s="6">
         <v>46094</v>
@@ -6798,88 +6655,86 @@
         <v>16</v>
       </c>
       <c r="K155" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L155" s="5"/>
       <c r="M155" s="5"/>
-      <c r="N155" s="7"/>
+      <c r="N155" s="16"/>
       <c r="O155" s="5"/>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A156" s="5">
         <v>0</v>
       </c>
       <c r="B156" s="5"/>
       <c r="C156" s="5" t="s">
-        <v>141</v>
+        <v>177</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>310</v>
+        <v>178</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G156" s="5" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="H156" s="6">
-        <v>46094</v>
+        <v>46095</v>
       </c>
       <c r="I156" s="9">
-        <v>0.41666666666666669</v>
+        <v>0.625</v>
       </c>
       <c r="J156" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K156" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L156" s="5"/>
       <c r="M156" s="5"/>
-      <c r="N156" s="7"/>
+      <c r="N156" s="16"/>
       <c r="O156" s="5"/>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A157" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B157" s="5"/>
       <c r="C157" s="5" t="s">
-        <v>182</v>
+        <v>13</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>183</v>
+        <v>289</v>
       </c>
       <c r="F157" s="5" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="G157" s="5" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H157" s="6">
-        <v>46095</v>
+        <v>46128</v>
       </c>
       <c r="I157" s="9">
-        <v>0.625</v>
-      </c>
-      <c r="J157" s="5" t="s">
-        <v>16</v>
-      </c>
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="J157" s="5"/>
       <c r="K157" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L157" s="5"/>
       <c r="M157" s="5"/>
-      <c r="N157" s="7"/>
+      <c r="N157" s="16"/>
       <c r="O157" s="5"/>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A158" s="5">
         <v>3</v>
       </c>
@@ -6891,30 +6746,32 @@
         <v>14</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="G158" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H158" s="6">
-        <v>46128</v>
+        <v>46139</v>
       </c>
       <c r="I158" s="9">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="J158" s="5"/>
+        <v>0.25</v>
+      </c>
+      <c r="J158" s="9">
+        <v>0.33333333333333331</v>
+      </c>
       <c r="K158" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L158" s="5"/>
       <c r="M158" s="5"/>
-      <c r="N158" s="7"/>
+      <c r="N158" s="16"/>
       <c r="O158" s="5"/>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A159" s="5">
         <v>3</v>
       </c>
@@ -6923,35 +6780,35 @@
         <v>13</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>14</v>
+        <v>182</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F159" s="5" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G159" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H159" s="6">
-        <v>46139</v>
+        <v>46141</v>
       </c>
       <c r="I159" s="9">
-        <v>0.25</v>
+        <v>0.67361111111111116</v>
       </c>
       <c r="J159" s="9">
-        <v>0.33333333333333331</v>
+        <v>0.96527777777777779</v>
       </c>
       <c r="K159" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L159" s="5"/>
       <c r="M159" s="5"/>
-      <c r="N159" s="7"/>
+      <c r="N159" s="16"/>
       <c r="O159" s="5"/>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A160" s="5">
         <v>3</v>
       </c>
@@ -6960,35 +6817,35 @@
         <v>13</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>187</v>
+        <v>14</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="G160" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H160" s="6">
-        <v>46141</v>
+        <v>46146</v>
       </c>
       <c r="I160" s="9">
-        <v>0.67361111111111116</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J160" s="9">
-        <v>0.96527777777777779</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="K160" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L160" s="5"/>
       <c r="M160" s="5"/>
-      <c r="N160" s="7"/>
+      <c r="N160" s="16"/>
       <c r="O160" s="5"/>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A161" s="5">
         <v>3</v>
       </c>
@@ -6997,74 +6854,72 @@
         <v>13</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>14</v>
+        <v>185</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G161" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H161" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="I161" s="9">
-        <v>0.33333333333333331</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="J161" s="9">
-        <v>0.41666666666666669</v>
+        <v>0.5</v>
       </c>
       <c r="K161" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L161" s="5"/>
       <c r="M161" s="5"/>
-      <c r="N161" s="7"/>
+      <c r="N161" s="16"/>
       <c r="O161" s="5"/>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A162" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B162" s="5"/>
       <c r="C162" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>190</v>
+        <v>14</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="G162" s="5" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="H162" s="6">
         <v>46147</v>
       </c>
       <c r="I162" s="9">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="J162" s="9">
-        <v>0.5</v>
-      </c>
+        <v>0.625</v>
+      </c>
+      <c r="J162" s="5"/>
       <c r="K162" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L162" s="5"/>
       <c r="M162" s="5"/>
-      <c r="N162" s="7"/>
+      <c r="N162" s="16"/>
       <c r="O162" s="5"/>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A163" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B163" s="5"/>
       <c r="C163" s="5" t="s">
@@ -7074,30 +6929,32 @@
         <v>14</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="G163" s="5" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H163" s="6">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="I163" s="9">
-        <v>0.625</v>
-      </c>
-      <c r="J163" s="5"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J163" s="9">
+        <v>0.41666666666666669</v>
+      </c>
       <c r="K163" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L163" s="5"/>
       <c r="M163" s="5"/>
-      <c r="N163" s="7"/>
+      <c r="N163" s="16"/>
       <c r="O163" s="5"/>
     </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A164" s="5">
         <v>3</v>
       </c>
@@ -7106,35 +6963,33 @@
         <v>13</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>14</v>
+        <v>189</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G164" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H164" s="6">
-        <v>46149</v>
-      </c>
-      <c r="I164" s="9">
-        <v>0.33333333333333331</v>
-      </c>
+        <v>46155</v>
+      </c>
+      <c r="I164" s="5"/>
       <c r="J164" s="9">
-        <v>0.41666666666666669</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="K164" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L164" s="5"/>
       <c r="M164" s="5"/>
-      <c r="N164" s="7"/>
+      <c r="N164" s="16"/>
       <c r="O164" s="5"/>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A165" s="5">
         <v>3</v>
       </c>
@@ -7143,35 +6998,35 @@
         <v>13</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>194</v>
+        <v>14</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="F165" s="5" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="G165" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="H165" s="6">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="I165" s="5"/>
       <c r="J165" s="9">
-        <v>0.45833333333333331</v>
+        <v>0.625</v>
       </c>
       <c r="K165" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L165" s="5"/>
       <c r="M165" s="5"/>
-      <c r="N165" s="7"/>
+      <c r="N165" s="16"/>
       <c r="O165" s="5"/>
     </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A166" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B166" s="5"/>
       <c r="C166" s="5" t="s">
@@ -7181,30 +7036,32 @@
         <v>14</v>
       </c>
       <c r="E166" s="5" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="G166" s="5" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="H166" s="6">
-        <v>46156</v>
-      </c>
-      <c r="I166" s="5"/>
+        <v>46163</v>
+      </c>
+      <c r="I166" s="9">
+        <v>0.29166666666666669</v>
+      </c>
       <c r="J166" s="9">
-        <v>0.625</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="K166" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L166" s="5"/>
       <c r="M166" s="5"/>
-      <c r="N166" s="7"/>
+      <c r="N166" s="16"/>
       <c r="O166" s="5"/>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A167" s="5">
         <v>2</v>
       </c>
@@ -7216,67 +7073,67 @@
         <v>14</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="G167" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H167" s="6">
-        <v>46163</v>
-      </c>
-      <c r="I167" s="9">
-        <v>0.29166666666666669</v>
-      </c>
+        <v>46164</v>
+      </c>
+      <c r="I167" s="5"/>
       <c r="J167" s="9">
-        <v>0.33333333333333331</v>
+        <v>0.375</v>
       </c>
       <c r="K167" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L167" s="5"/>
       <c r="M167" s="5"/>
-      <c r="N167" s="7"/>
+      <c r="N167" s="16"/>
       <c r="O167" s="5"/>
     </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A168" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B168" s="5"/>
       <c r="C168" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>14</v>
+        <v>194</v>
       </c>
       <c r="E168" s="5" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G168" s="5" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H168" s="6">
-        <v>46164</v>
-      </c>
-      <c r="I168" s="5"/>
+        <v>46167</v>
+      </c>
+      <c r="I168" s="9">
+        <v>0.22916666666666666</v>
+      </c>
       <c r="J168" s="9">
-        <v>0.375</v>
+        <v>0.5625</v>
       </c>
       <c r="K168" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L168" s="5"/>
       <c r="M168" s="5"/>
-      <c r="N168" s="7"/>
+      <c r="N168" s="16"/>
       <c r="O168" s="5"/>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A169" s="5">
         <v>3</v>
       </c>
@@ -7285,35 +7142,35 @@
         <v>13</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>199</v>
+        <v>14</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G169" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="H169" s="6">
-        <v>46167</v>
+        <v>316</v>
+      </c>
+      <c r="H169" s="12">
+        <v>46170</v>
       </c>
       <c r="I169" s="9">
-        <v>0.22916666666666666</v>
-      </c>
-      <c r="J169" s="9">
-        <v>0.5625</v>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J169" s="13">
+        <v>0.41666666666666669</v>
       </c>
       <c r="K169" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L169" s="5"/>
       <c r="M169" s="5"/>
-      <c r="N169" s="7"/>
+      <c r="N169" s="16"/>
       <c r="O169" s="5"/>
     </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A170" s="5">
         <v>3</v>
       </c>
@@ -7322,191 +7179,166 @@
         <v>13</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="F170" s="5" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="G170" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="H170" s="12">
-        <v>46170</v>
+        <v>316</v>
+      </c>
+      <c r="H170" s="6">
+        <v>46174</v>
       </c>
       <c r="I170" s="9">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="J170" s="13">
-        <v>0.41666666666666669</v>
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="J170" s="9">
+        <v>0.72916666666666663</v>
       </c>
       <c r="K170" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L170" s="5"/>
       <c r="M170" s="5"/>
-      <c r="N170" s="7"/>
+      <c r="N170" s="16"/>
       <c r="O170" s="5"/>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A171" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B171" s="5"/>
       <c r="C171" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D171" s="5" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="E171" s="5" t="s">
-        <v>307</v>
+        <v>201</v>
       </c>
       <c r="F171" s="5" t="s">
-        <v>202</v>
+        <v>20</v>
       </c>
       <c r="G171" s="5" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="H171" s="6">
-        <v>46174</v>
-      </c>
-      <c r="I171" s="9">
-        <v>0.64583333333333337</v>
-      </c>
+        <v>46204</v>
+      </c>
+      <c r="I171" s="5"/>
       <c r="J171" s="9">
-        <v>0.72916666666666663</v>
+        <v>0.875</v>
       </c>
       <c r="K171" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="L171" s="5"/>
-      <c r="M171" s="5"/>
-      <c r="N171" s="7"/>
+        <v>75</v>
+      </c>
+      <c r="L171" s="6">
+        <v>46182</v>
+      </c>
+      <c r="M171" s="6"/>
+      <c r="N171" s="16" t="s">
+        <v>315</v>
+      </c>
       <c r="O171" s="5"/>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A172" s="5">
         <v>0</v>
       </c>
       <c r="B172" s="5"/>
       <c r="C172" s="5" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D172" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F172" s="5" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="G172" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H172" s="5"/>
       <c r="I172" s="5"/>
       <c r="J172" s="5"/>
       <c r="K172" s="5" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="L172" s="5"/>
       <c r="M172" s="5"/>
-      <c r="N172" s="7"/>
+      <c r="N172" s="16"/>
       <c r="O172" s="5"/>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A173" s="5">
         <v>0</v>
       </c>
       <c r="B173" s="5"/>
       <c r="C173" s="5" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D173" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="F173" s="5" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="G173" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H173" s="5"/>
       <c r="I173" s="5"/>
       <c r="J173" s="5"/>
       <c r="K173" s="5" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="L173" s="5"/>
       <c r="M173" s="5"/>
-      <c r="N173" s="7"/>
+      <c r="N173" s="16"/>
       <c r="O173" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O173" xr:uid="{0331BFDC-0F24-4E57-9413-AB479E741FFA}"/>
-  <conditionalFormatting sqref="K2:O14 K16:O173 K15:M15 O15">
-    <cfRule type="cellIs" dxfId="26" priority="10" operator="equal">
+  <conditionalFormatting sqref="K2:O173">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+      <formula>"Programada"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
       <formula>"Impl. Cancelada"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
       <formula>"Listo para embarcar"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="equal">
       <formula>"Equipo en transito"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
       <formula>"Cancelada"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
       <formula>"En preconfiguración"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="7" operator="equal">
       <formula>"Dependencia"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="8" operator="equal">
       <formula>"Listo para programar"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="9" operator="equal">
       <formula>"Exitosa"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="18" operator="equal">
-      <formula>"Programada"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N15">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
-      <formula>"Impl. Cancelada"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
-      <formula>"Listo para embarcar"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
-      <formula>"Equipo en transito"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
-      <formula>"Cancelada"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
-      <formula>"En preconfiguración"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
-      <formula>"Dependencia"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="7" operator="equal">
-      <formula>"Listo para programar"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="8" operator="equal">
-      <formula>"Exitosa"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="9" operator="equal">
-      <formula>"Programada"</formula>
+    <cfRule type="cellIs" dxfId="0" priority="10" operator="equal">
+      <formula>"Programada."</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/archivos/BD_Dashboard.xlsx
+++ b/archivos/BD_Dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mexscitum-my.sharepoint.com/personal/erik_torres_scitum_com_mx/Documents/Documentos/ETP/GitHub/SCITUM-AMX/archivos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="92" documentId="11_F25DC773A252ABDACC1048E8499F6DC65BDE58F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{022355D2-FD7A-440A-9156-0B7E9E491716}"/>
+  <xr:revisionPtr revIDLastSave="97" documentId="11_F25DC773A252ABDACC1048E8499F6DC65BDE58F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A698EF4-9D56-4CC2-A7FD-A6F94132B163}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inventario SDWAN &amp; FW" sheetId="2" r:id="rId1"/>
@@ -46,7 +46,7 @@
     <author>Erik Alejandro Torres Piña</author>
   </authors>
   <commentList>
-    <comment ref="F46" authorId="0" shapeId="0" xr:uid="{6FB5E093-75BB-4CD6-ABA5-AFCD435DECC5}">
+    <comment ref="F44" authorId="0" shapeId="0" xr:uid="{AFA6DCEB-C9E5-47FD-BAC8-9E7E5F2DE266}">
       <text>
         <r>
           <rPr>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="338">
   <si>
     <t>TIER</t>
   </si>
@@ -264,9 +264,6 @@
   </si>
   <si>
     <t>Sao Paulo (GRU)</t>
-  </si>
-  <si>
-    <t>Ecuador</t>
   </si>
   <si>
     <t>Managua (MGA)</t>
@@ -1076,6 +1073,24 @@
   </si>
   <si>
     <t>MTY_HANGAR</t>
+  </si>
+  <si>
+    <t>Issue</t>
+  </si>
+  <si>
+    <t>Nicaragua</t>
+  </si>
+  <si>
+    <t>Para el HA esta directo ION-ION, posterior Palo Alto hizo una recomendación (por best practices) de conectar a un switch para habilitar el HA.</t>
+  </si>
+  <si>
+    <t>Aeroméxico no proporcionó los cables requeridos para la ventana de implementación. El cliente programará una visita posterior con recursos propios para realizar la conexión del segundo equipo, y SCITUM brindará soporte de forma remota.</t>
+  </si>
+  <si>
+    <t>Fallida</t>
+  </si>
+  <si>
+    <t>Aeroméxico autorizó la instalación temporal de los equipos sobre infraestructura existente de otro proveedor para mantener la ventana de implementación del sitio LAS. Durante la sesión se expusieron los riesgos asociados a esta alternativa y Aeroméxico confirmó la aceptación de dichos riesgos, asumiendo la responsabilidad ante cualquier incidente derivado del movimiento o manipulación de los equipos existentes durante o posterior a la ventana. No se tiene switch, Aeromexico reporta que desconocía esta situación, se conecta un solo equipo ION y no se habilita HA.</t>
   </si>
 </sst>
 </file>
@@ -1688,7 +1703,7 @@
   <sheetPr>
     <tabColor theme="5" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:O173"/>
+  <dimension ref="A1:P173"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.1796875" bestFit="1" customWidth="1"/>
@@ -1698,10 +1713,10 @@
     <col min="5" max="5" width="11.7265625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="24.81640625" customWidth="1"/>
     <col min="7" max="7" width="17.1796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.6328125" customWidth="1"/>
+    <col min="11" max="11" width="17.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1721,7 +1736,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>6</v>
@@ -1745,10 +1760,13 @@
         <v>12</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+        <v>332</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" s="5">
         <v>3</v>
       </c>
@@ -1760,23 +1778,23 @@
         <v>27</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>35</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H2" s="6">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="I2" s="5"/>
       <c r="J2" s="9">
-        <v>0.83333333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="L2" s="6">
         <v>46189</v>
@@ -1785,13 +1803,14 @@
         <v>1.06</v>
       </c>
       <c r="N2" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="O2" s="5"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+        <v>322</v>
+      </c>
+      <c r="O2" s="7"/>
+      <c r="P2" s="5"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5" t="s">
@@ -1801,32 +1820,33 @@
         <v>14</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G3" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="H3" s="12">
+        <v>46225</v>
+      </c>
+      <c r="I3" s="5"/>
+      <c r="J3" s="13">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K3" s="5" t="s">
         <v>311</v>
-      </c>
-      <c r="H3" s="6">
-        <v>46210</v>
-      </c>
-      <c r="I3" s="5"/>
-      <c r="J3" s="9">
-        <v>0.625</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>312</v>
       </c>
       <c r="L3" s="5"/>
       <c r="M3" s="5"/>
       <c r="N3" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="O3" s="5"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+        <v>324</v>
+      </c>
+      <c r="O3" s="7"/>
+      <c r="P3" s="5"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" s="5">
         <v>1</v>
       </c>
@@ -1835,53 +1855,54 @@
         <v>13</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="H4" s="6">
-        <v>46211</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="H4" s="5"/>
       <c r="I4" s="5"/>
-      <c r="J4" s="9">
-        <v>0.41666666666666669</v>
-      </c>
+      <c r="J4" s="5"/>
       <c r="K4" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
+        <v>17</v>
+      </c>
+      <c r="L4" s="6">
+        <v>46189</v>
+      </c>
+      <c r="M4" s="5">
+        <v>1.01</v>
+      </c>
       <c r="N4" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="O4" s="5"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+        <v>323</v>
+      </c>
+      <c r="O4" s="7"/>
+      <c r="P4" s="5"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>205</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
@@ -1893,32 +1914,33 @@
         <v>46189</v>
       </c>
       <c r="M5" s="5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>324</v>
-      </c>
-      <c r="O5" s="5"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+        <v>322</v>
+      </c>
+      <c r="O5" s="7"/>
+      <c r="P5" s="5"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>206</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
@@ -1930,51 +1952,51 @@
         <v>46189</v>
       </c>
       <c r="M6" s="5">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="O6" s="5"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+        <v>322</v>
+      </c>
+      <c r="O6" s="7"/>
+      <c r="P6" s="5"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="H7" s="5"/>
+        <v>310</v>
+      </c>
+      <c r="H7" s="2"/>
       <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
+      <c r="J7" s="3"/>
       <c r="K7" s="5" t="s">
         <v>17</v>
       </c>
       <c r="L7" s="6">
-        <v>46189</v>
-      </c>
-      <c r="M7" s="5">
-        <v>1.03</v>
-      </c>
+        <v>46182</v>
+      </c>
+      <c r="M7" s="6"/>
       <c r="N7" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="O7" s="5"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+        <v>325</v>
+      </c>
+      <c r="O7" s="7"/>
+      <c r="P7" s="5"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>1</v>
       </c>
@@ -1986,13 +2008,13 @@
         <v>14</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="5"/>
@@ -2000,16 +2022,19 @@
       <c r="K8" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
+      <c r="L8" s="6">
+        <v>46182</v>
+      </c>
+      <c r="M8" s="6"/>
       <c r="N8" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="O8" s="5"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+        <v>326</v>
+      </c>
+      <c r="O8" s="7"/>
+      <c r="P8" s="5"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5" t="s">
@@ -2019,13 +2044,13 @@
         <v>14</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="5"/>
@@ -2033,16 +2058,15 @@
       <c r="K9" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="L9" s="6">
-        <v>46182</v>
-      </c>
-      <c r="M9" s="6"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
       <c r="N9" s="7" t="s">
-        <v>326</v>
-      </c>
-      <c r="O9" s="5"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+        <v>322</v>
+      </c>
+      <c r="O9" s="7"/>
+      <c r="P9" s="5"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>1</v>
       </c>
@@ -2051,20 +2075,20 @@
         <v>13</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>203</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="H10" s="1"/>
+        <v>310</v>
+      </c>
+      <c r="H10" s="5"/>
       <c r="I10" s="5"/>
-      <c r="J10" s="3"/>
+      <c r="J10" s="5"/>
       <c r="K10" s="5" t="s">
         <v>17</v>
       </c>
@@ -2073,118 +2097,114 @@
       </c>
       <c r="M10" s="6"/>
       <c r="N10" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="O10" s="5"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+        <v>318</v>
+      </c>
+      <c r="O10" s="7"/>
+      <c r="P10" s="5"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="H11" s="2"/>
+        <v>315</v>
+      </c>
+      <c r="H11" s="5"/>
       <c r="I11" s="5"/>
-      <c r="J11" s="3"/>
+      <c r="J11" s="5"/>
       <c r="K11" s="5" t="s">
         <v>17</v>
       </c>
       <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="O11" s="5"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="M11" s="5">
+        <v>2.02</v>
+      </c>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="5"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
       <c r="K12" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="L12" s="6">
-        <v>46189</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="L12" s="5"/>
       <c r="M12" s="5">
-        <v>1.04</v>
-      </c>
-      <c r="N12" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="O12" s="5"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+        <v>2.06</v>
+      </c>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7"/>
+      <c r="P12" s="5"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
       <c r="K13" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="L13" s="6">
-        <v>46189</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="L13" s="5"/>
       <c r="M13" s="5">
-        <v>1.05</v>
-      </c>
-      <c r="N13" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="O13" s="5"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
+      <c r="P13" s="5"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <v>1</v>
       </c>
@@ -2193,33 +2213,32 @@
         <v>13</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
       <c r="K14" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="L14" s="6">
-        <v>46182</v>
-      </c>
-      <c r="M14" s="6"/>
-      <c r="N14" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="O14" s="5"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+      <c r="L14" s="5"/>
+      <c r="M14" s="14">
+        <v>2.08</v>
+      </c>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="5"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <v>1</v>
       </c>
@@ -2228,115 +2247,118 @@
         <v>13</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="5"/>
       <c r="K15" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="L15" s="5"/>
       <c r="M15" s="5">
-        <v>2.0099999999999998</v>
+        <v>2.09</v>
       </c>
       <c r="N15" s="7"/>
-      <c r="O15" s="5"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O15" s="7"/>
+      <c r="P15" s="5"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
         <v>3</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5" t="s">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>226</v>
+        <v>267</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>65</v>
+        <v>128</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
       <c r="J16" s="5"/>
       <c r="K16" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="L16" s="5"/>
       <c r="M16" s="5">
-        <v>2.02</v>
+        <v>4.05</v>
       </c>
       <c r="N16" s="7"/>
-      <c r="O16" s="5"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O16" s="7"/>
+      <c r="P16" s="5"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5" t="s">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>224</v>
+        <v>262</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>62</v>
+        <v>123</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
       <c r="K17" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="L17" s="5"/>
       <c r="M17" s="5">
-        <v>2.06</v>
+        <v>4.03</v>
       </c>
       <c r="N17" s="7"/>
-      <c r="O17" s="5"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O17" s="7"/>
+      <c r="P17" s="5"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
@@ -2344,32 +2366,37 @@
       <c r="K18" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="L18" s="5"/>
+      <c r="L18" s="6">
+        <v>46189</v>
+      </c>
       <c r="M18" s="5">
-        <v>2.0699999999999998</v>
-      </c>
-      <c r="N18" s="7"/>
-      <c r="O18" s="5"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+        <v>1.04</v>
+      </c>
+      <c r="N18" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="O18" s="7"/>
+      <c r="P18" s="5"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
@@ -2377,14 +2404,19 @@
       <c r="K19" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="L19" s="5"/>
-      <c r="M19" s="14">
-        <v>2.08</v>
-      </c>
-      <c r="N19" s="7"/>
-      <c r="O19" s="5"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="L19" s="6">
+        <v>46189</v>
+      </c>
+      <c r="M19" s="5">
+        <v>1.05</v>
+      </c>
+      <c r="N19" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="O19" s="7"/>
+      <c r="P19" s="5"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <v>1</v>
       </c>
@@ -2393,16 +2425,16 @@
         <v>13</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>219</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
@@ -2410,14 +2442,17 @@
       <c r="K20" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="L20" s="5"/>
+      <c r="L20" s="6">
+        <v>46210</v>
+      </c>
       <c r="M20" s="5">
-        <v>2.09</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="N20" s="7"/>
-      <c r="O20" s="5"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O20" s="7"/>
+      <c r="P20" s="5"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
         <v>3</v>
       </c>
@@ -2426,16 +2461,16 @@
         <v>13</v>
       </c>
       <c r="D21" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="F21" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E21" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>69</v>
-      </c>
       <c r="G21" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
@@ -2443,34 +2478,37 @@
       <c r="K21" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="L21" s="5"/>
+      <c r="L21" s="6">
+        <v>46206</v>
+      </c>
       <c r="M21" s="14">
         <v>2.1</v>
       </c>
       <c r="N21" s="7"/>
-      <c r="O21" s="5"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O21" s="7"/>
+      <c r="P21" s="5"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5" t="s">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>215</v>
+        <v>260</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="H22" s="8"/>
+        <v>315</v>
+      </c>
+      <c r="H22" s="5"/>
       <c r="I22" s="5"/>
       <c r="J22" s="5"/>
       <c r="K22" s="5" t="s">
@@ -2478,214 +2516,219 @@
       </c>
       <c r="L22" s="5"/>
       <c r="M22" s="5">
-        <v>3.04</v>
-      </c>
-      <c r="N22" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="O22" s="5"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="N22" s="7"/>
+      <c r="O22" s="7"/>
+      <c r="P22" s="5"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
         <v>3</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5" t="s">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>225</v>
+        <v>285</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>64</v>
+        <v>157</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
       <c r="J23" s="5"/>
       <c r="K23" s="5" t="s">
-        <v>303</v>
+        <v>22</v>
       </c>
       <c r="L23" s="5"/>
       <c r="M23" s="5">
-        <v>2.0299999999999998</v>
+        <v>4.04</v>
       </c>
       <c r="N23" s="7"/>
-      <c r="O23" s="5"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O23" s="7"/>
+      <c r="P23" s="5"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>66</v>
+        <v>14</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="H24" s="5"/>
+        <v>310</v>
+      </c>
+      <c r="H24" s="8"/>
       <c r="I24" s="5"/>
       <c r="J24" s="5"/>
       <c r="K24" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="L24" s="5"/>
       <c r="M24" s="5">
-        <v>2.04</v>
-      </c>
-      <c r="N24" s="7"/>
-      <c r="O24" s="5"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+        <v>3.04</v>
+      </c>
+      <c r="N24" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="O24" s="7"/>
+      <c r="P24" s="5"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A25" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>59</v>
+        <v>333</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
       <c r="J25" s="5"/>
       <c r="K25" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="L25" s="5"/>
       <c r="M25" s="5">
-        <v>2.0499999999999998</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="N25" s="7"/>
-      <c r="O25" s="5"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O25" s="7"/>
+      <c r="P25" s="5"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A26" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>139</v>
+        <v>65</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>274</v>
+        <v>226</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>140</v>
+        <v>66</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
       <c r="J26" s="5"/>
       <c r="K26" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="L26" s="5"/>
       <c r="M26" s="5">
-        <v>3.01</v>
+        <v>2.04</v>
       </c>
       <c r="N26" s="7"/>
-      <c r="O26" s="5"/>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O26" s="7"/>
+      <c r="P26" s="5"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A27" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>152</v>
+        <v>59</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>282</v>
+        <v>222</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>153</v>
+        <v>60</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="H27" s="5"/>
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
       <c r="K27" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="L27" s="5"/>
       <c r="M27" s="5">
-        <v>3.02</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="N27" s="7"/>
-      <c r="O27" s="5"/>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O27" s="7"/>
+      <c r="P27" s="5"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A28" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>14</v>
+        <v>138</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>212</v>
+        <v>273</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>38</v>
+        <v>139</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="H28" s="8"/>
+        <v>310</v>
+      </c>
+      <c r="H28" s="5"/>
       <c r="I28" s="5"/>
       <c r="J28" s="5"/>
       <c r="K28" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="L28" s="5"/>
       <c r="M28" s="5">
-        <v>3.03</v>
-      </c>
-      <c r="N28" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="O28" s="5"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+        <v>3.01</v>
+      </c>
+      <c r="N28" s="7"/>
+      <c r="O28" s="7"/>
+      <c r="P28" s="5"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A29" s="5">
         <v>3</v>
       </c>
@@ -2694,621 +2737,644 @@
         <v>13</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>14</v>
+        <v>151</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>213</v>
+        <v>281</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>40</v>
+        <v>152</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="H29" s="8"/>
+        <v>315</v>
+      </c>
+      <c r="H29" s="5"/>
       <c r="I29" s="5"/>
       <c r="J29" s="5"/>
       <c r="K29" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="L29" s="5"/>
       <c r="M29" s="5">
-        <v>4.01</v>
-      </c>
-      <c r="N29" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="O29" s="5"/>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+        <v>3.02</v>
+      </c>
+      <c r="N29" s="7"/>
+      <c r="O29" s="7"/>
+      <c r="P29" s="5"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A30" s="5">
         <v>3</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5" t="s">
-        <v>82</v>
+        <v>13</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>261</v>
+        <v>211</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>121</v>
+        <v>38</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="H30" s="5"/>
+        <v>315</v>
+      </c>
+      <c r="H30" s="8"/>
       <c r="I30" s="5"/>
       <c r="J30" s="5"/>
       <c r="K30" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="L30" s="5"/>
       <c r="M30" s="5">
-        <v>4.0199999999999996</v>
-      </c>
-      <c r="N30" s="7"/>
-      <c r="O30" s="5"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+        <v>3.03</v>
+      </c>
+      <c r="N30" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="O30" s="7"/>
+      <c r="P30" s="5"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A31" s="5">
         <v>3</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5" t="s">
-        <v>82</v>
+        <v>13</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>263</v>
+        <v>212</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>124</v>
+        <v>40</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="H31" s="5"/>
+        <v>315</v>
+      </c>
+      <c r="H31" s="8"/>
       <c r="I31" s="5"/>
       <c r="J31" s="5"/>
       <c r="K31" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="L31" s="5"/>
       <c r="M31" s="5">
-        <v>4.03</v>
-      </c>
-      <c r="N31" s="7"/>
-      <c r="O31" s="5"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+        <v>4.01</v>
+      </c>
+      <c r="N31" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="O31" s="7"/>
+      <c r="P31" s="5"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A32" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5" t="s">
-        <v>82</v>
+        <v>13</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>286</v>
+        <v>213</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>158</v>
+        <v>42</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="H32" s="5"/>
+        <v>310</v>
+      </c>
+      <c r="H32" s="8"/>
       <c r="I32" s="5"/>
       <c r="J32" s="5"/>
       <c r="K32" s="5" t="s">
-        <v>303</v>
+        <v>37</v>
       </c>
       <c r="L32" s="5"/>
-      <c r="M32" s="5">
-        <v>4.04</v>
-      </c>
-      <c r="N32" s="7"/>
-      <c r="O32" s="5"/>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="M32" s="5"/>
+      <c r="N32" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="O32" s="7"/>
+      <c r="P32" s="5"/>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A33" s="5">
         <v>3</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5" t="s">
-        <v>82</v>
+        <v>13</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>268</v>
+        <v>215</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>129</v>
+        <v>45</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="H33" s="5"/>
+        <v>315</v>
+      </c>
+      <c r="H33" s="8"/>
       <c r="I33" s="5"/>
-      <c r="J33" s="5"/>
+      <c r="J33" s="9"/>
       <c r="K33" s="5" t="s">
-        <v>303</v>
+        <v>37</v>
       </c>
       <c r="L33" s="5"/>
-      <c r="M33" s="5">
-        <v>4.05</v>
-      </c>
-      <c r="N33" s="7"/>
-      <c r="O33" s="5"/>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="M33" s="5"/>
+      <c r="N33" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="O33" s="7"/>
+      <c r="P33" s="5"/>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A34" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H34" s="8"/>
       <c r="I34" s="5"/>
       <c r="J34" s="5"/>
       <c r="K34" s="5" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="L34" s="5"/>
       <c r="M34" s="5"/>
-      <c r="N34" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="O34" s="5"/>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="N34" s="7"/>
+      <c r="O34" s="7"/>
+      <c r="P34" s="5"/>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A35" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>216</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="H35" s="8"/>
+        <v>310</v>
+      </c>
+      <c r="H35" s="5"/>
       <c r="I35" s="5"/>
-      <c r="J35" s="9"/>
+      <c r="J35" s="5"/>
       <c r="K35" s="5" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="L35" s="5"/>
       <c r="M35" s="5"/>
       <c r="N35" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="O35" s="5"/>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+      <c r="O35" s="7"/>
+      <c r="P35" s="5"/>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A36" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="H36" s="8"/>
+        <v>310</v>
+      </c>
+      <c r="H36" s="5"/>
       <c r="I36" s="5"/>
       <c r="J36" s="5"/>
       <c r="K36" s="5" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="L36" s="5"/>
       <c r="M36" s="5"/>
       <c r="N36" s="7"/>
-      <c r="O36" s="5"/>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O36" s="7"/>
+      <c r="P36" s="5" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A37" s="5">
         <v>1</v>
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5" t="s">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H37" s="5"/>
       <c r="I37" s="5"/>
       <c r="J37" s="5"/>
       <c r="K37" s="5" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="L37" s="5"/>
       <c r="M37" s="5"/>
       <c r="N37" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="O37" s="5"/>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
+        <v>320</v>
+      </c>
+      <c r="O37" s="7"/>
+      <c r="P37" s="5" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A38" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H38" s="5"/>
       <c r="I38" s="5"/>
       <c r="J38" s="5"/>
       <c r="K38" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L38" s="5"/>
       <c r="M38" s="5"/>
-      <c r="N38" s="7"/>
-      <c r="O38" s="5" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="N38" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="O38" s="7"/>
+      <c r="P38" s="5" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A39" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H39" s="5"/>
       <c r="I39" s="5"/>
       <c r="J39" s="5"/>
       <c r="K39" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L39" s="5"/>
       <c r="M39" s="5"/>
-      <c r="N39" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="O39" s="5" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="N39" s="7"/>
+      <c r="O39" s="7"/>
+      <c r="P39" s="5"/>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A40" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
       <c r="J40" s="5"/>
       <c r="K40" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L40" s="5"/>
       <c r="M40" s="5"/>
-      <c r="N40" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="O40" s="5" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="N40" s="7"/>
+      <c r="O40" s="7"/>
+      <c r="P40" s="5"/>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A41" s="5">
         <v>0</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H41" s="5"/>
       <c r="I41" s="5"/>
       <c r="J41" s="5"/>
       <c r="K41" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L41" s="5"/>
       <c r="M41" s="5"/>
       <c r="N41" s="7"/>
-      <c r="O41" s="5"/>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O41" s="7"/>
+      <c r="P41" s="5" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A42" s="5">
         <v>0</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H42" s="5"/>
       <c r="I42" s="5"/>
       <c r="J42" s="5"/>
       <c r="K42" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L42" s="5"/>
       <c r="M42" s="5"/>
       <c r="N42" s="7"/>
-      <c r="O42" s="5"/>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O42" s="7"/>
+      <c r="P42" s="5" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A43" s="5">
         <v>0</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H43" s="5"/>
       <c r="I43" s="5"/>
       <c r="J43" s="5"/>
       <c r="K43" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L43" s="5"/>
       <c r="M43" s="5"/>
       <c r="N43" s="7"/>
-      <c r="O43" s="5"/>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A44" s="5">
+      <c r="O43" s="7"/>
+      <c r="P43" s="5" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A44" s="10">
         <v>0</v>
       </c>
       <c r="B44" s="5"/>
-      <c r="C44" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="H44" s="5"/>
-      <c r="I44" s="5"/>
-      <c r="J44" s="5"/>
+      <c r="C44" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E44" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="F44" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="G44" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="H44" s="10"/>
+      <c r="I44" s="10"/>
+      <c r="J44" s="10"/>
       <c r="K44" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="L44" s="5"/>
-      <c r="M44" s="5"/>
-      <c r="N44" s="7"/>
-      <c r="O44" s="5"/>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
+        <v>71</v>
+      </c>
+      <c r="L44" s="10"/>
+      <c r="M44" s="10"/>
+      <c r="N44" s="11"/>
+      <c r="O44" s="11"/>
+      <c r="P44" s="10"/>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A45" s="5">
         <v>0</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H45" s="5"/>
       <c r="I45" s="5"/>
       <c r="J45" s="5"/>
       <c r="K45" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L45" s="5"/>
       <c r="M45" s="5"/>
       <c r="N45" s="7"/>
-      <c r="O45" s="5"/>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A46" s="10">
-        <v>0</v>
+      <c r="O45" s="7"/>
+      <c r="P45" s="5"/>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A46" s="5">
+        <v>1</v>
       </c>
       <c r="B46" s="5"/>
-      <c r="C46" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="D46" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="E46" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="F46" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="G46" s="10" t="s">
-        <v>311</v>
-      </c>
-      <c r="H46" s="10"/>
-      <c r="I46" s="10"/>
-      <c r="J46" s="10"/>
+      <c r="C46" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="H46" s="5"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="5"/>
       <c r="K46" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="L46" s="10"/>
-      <c r="M46" s="10"/>
-      <c r="N46" s="11"/>
-      <c r="O46" s="10"/>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
+        <v>71</v>
+      </c>
+      <c r="L46" s="5"/>
+      <c r="M46" s="5"/>
+      <c r="N46" s="7"/>
+      <c r="O46" s="7"/>
+      <c r="P46" s="5"/>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A47" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H47" s="5"/>
       <c r="I47" s="5"/>
       <c r="J47" s="5"/>
       <c r="K47" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L47" s="5"/>
       <c r="M47" s="5"/>
       <c r="N47" s="7"/>
-      <c r="O47" s="5"/>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O47" s="7"/>
+      <c r="P47" s="5"/>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A48" s="5">
         <v>1</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>51</v>
@@ -3317,122 +3383,126 @@
         <v>229</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H48" s="5"/>
       <c r="I48" s="5"/>
       <c r="J48" s="5"/>
       <c r="K48" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L48" s="5"/>
       <c r="M48" s="5"/>
       <c r="N48" s="7"/>
-      <c r="O48" s="5"/>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O48" s="7"/>
+      <c r="P48" s="5"/>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A49" s="5">
         <v>1</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H49" s="5"/>
       <c r="I49" s="5"/>
       <c r="J49" s="5"/>
       <c r="K49" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L49" s="5"/>
       <c r="M49" s="5"/>
       <c r="N49" s="7"/>
-      <c r="O49" s="5"/>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O49" s="7"/>
+      <c r="P49" s="5"/>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A50" s="5">
         <v>1</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H50" s="5"/>
       <c r="I50" s="5"/>
       <c r="J50" s="5"/>
       <c r="K50" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L50" s="5"/>
       <c r="M50" s="5"/>
       <c r="N50" s="7"/>
-      <c r="O50" s="5"/>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O50" s="7"/>
+      <c r="P50" s="5"/>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A51" s="5">
         <v>1</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D51" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H51" s="5"/>
       <c r="I51" s="5"/>
       <c r="J51" s="5"/>
       <c r="K51" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L51" s="5"/>
       <c r="M51" s="5"/>
       <c r="N51" s="7"/>
-      <c r="O51" s="5"/>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O51" s="7"/>
+      <c r="P51" s="5"/>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A52" s="5">
         <v>1</v>
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>51</v>
@@ -3441,60 +3511,64 @@
         <v>232</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H52" s="5"/>
       <c r="I52" s="5"/>
       <c r="J52" s="5"/>
       <c r="K52" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L52" s="5"/>
       <c r="M52" s="5"/>
       <c r="N52" s="7"/>
-      <c r="O52" s="5"/>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O52" s="7"/>
+      <c r="P52" s="5" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A53" s="5">
         <v>1</v>
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H53" s="5"/>
       <c r="I53" s="5"/>
       <c r="J53" s="5"/>
       <c r="K53" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L53" s="5"/>
       <c r="M53" s="5"/>
       <c r="N53" s="7"/>
-      <c r="O53" s="5"/>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O53" s="7"/>
+      <c r="P53" s="5"/>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A54" s="5">
         <v>1</v>
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>51</v>
@@ -3506,26 +3580,27 @@
         <v>89</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H54" s="5"/>
       <c r="I54" s="5"/>
       <c r="J54" s="5"/>
       <c r="K54" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L54" s="5"/>
       <c r="M54" s="5"/>
       <c r="N54" s="7"/>
-      <c r="O54" s="5"/>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O54" s="7"/>
+      <c r="P54" s="5"/>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A55" s="5">
         <v>1</v>
       </c>
       <c r="B55" s="5"/>
       <c r="C55" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>51</v>
@@ -3537,20 +3612,21 @@
         <v>90</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H55" s="5"/>
       <c r="I55" s="5"/>
       <c r="J55" s="5"/>
       <c r="K55" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L55" s="5"/>
       <c r="M55" s="5"/>
       <c r="N55" s="7"/>
-      <c r="O55" s="5"/>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O55" s="7"/>
+      <c r="P55" s="5"/>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A56" s="5">
         <v>1</v>
       </c>
@@ -3562,57 +3638,61 @@
         <v>51</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H56" s="5"/>
       <c r="I56" s="5"/>
       <c r="J56" s="5"/>
       <c r="K56" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L56" s="5"/>
       <c r="M56" s="5"/>
       <c r="N56" s="7"/>
-      <c r="O56" s="5"/>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O56" s="7"/>
+      <c r="P56" s="5"/>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A57" s="5">
         <v>1</v>
       </c>
       <c r="B57" s="5"/>
       <c r="C57" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>91</v>
+        <v>327</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H57" s="5"/>
       <c r="I57" s="5"/>
       <c r="J57" s="5"/>
       <c r="K57" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L57" s="5"/>
       <c r="M57" s="5"/>
       <c r="N57" s="7"/>
-      <c r="O57" s="5"/>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O57" s="7"/>
+      <c r="P57" s="5" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A58" s="5">
         <v>1</v>
       </c>
@@ -3624,32 +3704,33 @@
         <v>51</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>236</v>
+        <v>330</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>92</v>
+        <v>328</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H58" s="5"/>
       <c r="I58" s="5"/>
       <c r="J58" s="5"/>
       <c r="K58" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L58" s="5"/>
       <c r="M58" s="5"/>
       <c r="N58" s="7"/>
-      <c r="O58" s="5"/>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O58" s="7"/>
+      <c r="P58" s="5"/>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A59" s="5">
         <v>1</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>51</v>
@@ -3658,122 +3739,130 @@
         <v>237</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>328</v>
+        <v>93</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H59" s="5"/>
       <c r="I59" s="5"/>
       <c r="J59" s="5"/>
       <c r="K59" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L59" s="5"/>
       <c r="M59" s="5"/>
       <c r="N59" s="7"/>
-      <c r="O59" s="5"/>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O59" s="7"/>
+      <c r="P59" s="5"/>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A60" s="5">
         <v>1</v>
       </c>
       <c r="B60" s="5"/>
       <c r="C60" s="5" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>331</v>
+        <v>238</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>329</v>
+        <v>94</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H60" s="5"/>
       <c r="I60" s="5"/>
       <c r="J60" s="5"/>
       <c r="K60" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L60" s="5"/>
       <c r="M60" s="5"/>
       <c r="N60" s="7"/>
-      <c r="O60" s="5"/>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O60" s="7"/>
+      <c r="P60" s="5" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A61" s="5">
         <v>1</v>
       </c>
       <c r="B61" s="5"/>
       <c r="C61" s="5" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H61" s="5"/>
       <c r="I61" s="5"/>
       <c r="J61" s="5"/>
       <c r="K61" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L61" s="5"/>
       <c r="M61" s="5"/>
       <c r="N61" s="7"/>
-      <c r="O61" s="5"/>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O61" s="7"/>
+      <c r="P61" s="5" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A62" s="5">
         <v>1</v>
       </c>
       <c r="B62" s="5"/>
       <c r="C62" s="5" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H62" s="5"/>
       <c r="I62" s="5"/>
       <c r="J62" s="5"/>
       <c r="K62" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L62" s="5"/>
       <c r="M62" s="5"/>
       <c r="N62" s="7"/>
-      <c r="O62" s="5"/>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O62" s="7"/>
+      <c r="P62" s="5"/>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A63" s="5">
         <v>1</v>
       </c>
       <c r="B63" s="5"/>
       <c r="C63" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>51</v>
@@ -3782,60 +3871,62 @@
         <v>240</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H63" s="5"/>
       <c r="I63" s="5"/>
       <c r="J63" s="5"/>
       <c r="K63" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L63" s="5"/>
       <c r="M63" s="5"/>
       <c r="N63" s="7"/>
-      <c r="O63" s="5"/>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O63" s="7"/>
+      <c r="P63" s="5"/>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A64" s="5">
         <v>1</v>
       </c>
       <c r="B64" s="5"/>
       <c r="C64" s="5" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D64" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>97</v>
+        <v>52</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H64" s="5"/>
       <c r="I64" s="5"/>
       <c r="J64" s="5"/>
       <c r="K64" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L64" s="5"/>
       <c r="M64" s="5"/>
       <c r="N64" s="7"/>
-      <c r="O64" s="5"/>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O64" s="7"/>
+      <c r="P64" s="5"/>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A65" s="5">
         <v>1</v>
       </c>
       <c r="B65" s="5"/>
       <c r="C65" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D65" s="5" t="s">
         <v>51</v>
@@ -3847,485 +3938,515 @@
         <v>98</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H65" s="5"/>
       <c r="I65" s="5"/>
       <c r="J65" s="5"/>
       <c r="K65" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L65" s="5"/>
       <c r="M65" s="5"/>
       <c r="N65" s="7"/>
-      <c r="O65" s="5"/>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O65" s="7"/>
+      <c r="P65" s="5" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A66" s="5">
         <v>1</v>
       </c>
       <c r="B66" s="5"/>
       <c r="C66" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D66" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>52</v>
+        <v>99</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H66" s="5"/>
       <c r="I66" s="5"/>
       <c r="J66" s="5"/>
       <c r="K66" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L66" s="5"/>
       <c r="M66" s="5"/>
       <c r="N66" s="7"/>
-      <c r="O66" s="5"/>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O66" s="7"/>
+      <c r="P66" s="5"/>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A67" s="5">
         <v>1</v>
       </c>
       <c r="B67" s="5"/>
       <c r="C67" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D67" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H67" s="5"/>
       <c r="I67" s="5"/>
       <c r="J67" s="5"/>
       <c r="K67" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L67" s="5"/>
       <c r="M67" s="5"/>
       <c r="N67" s="7"/>
-      <c r="O67" s="5"/>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O67" s="7"/>
+      <c r="P67" s="5"/>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A68" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B68" s="5"/>
       <c r="C68" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D68" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H68" s="5"/>
       <c r="I68" s="5"/>
       <c r="J68" s="5"/>
       <c r="K68" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L68" s="5"/>
       <c r="M68" s="5"/>
       <c r="N68" s="7"/>
-      <c r="O68" s="5"/>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O68" s="7"/>
+      <c r="P68" s="5"/>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A69" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B69" s="5"/>
       <c r="C69" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D69" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H69" s="5"/>
       <c r="I69" s="5"/>
       <c r="J69" s="5"/>
       <c r="K69" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L69" s="5"/>
       <c r="M69" s="5"/>
       <c r="N69" s="7"/>
-      <c r="O69" s="5"/>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O69" s="7"/>
+      <c r="P69" s="5" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A70" s="5">
         <v>2</v>
       </c>
       <c r="B70" s="5"/>
       <c r="C70" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D70" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H70" s="5"/>
       <c r="I70" s="5"/>
       <c r="J70" s="5"/>
       <c r="K70" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L70" s="5"/>
       <c r="M70" s="5"/>
       <c r="N70" s="7"/>
-      <c r="O70" s="5"/>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O70" s="7"/>
+      <c r="P70" s="5" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A71" s="5">
         <v>2</v>
       </c>
       <c r="B71" s="5"/>
       <c r="C71" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D71" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H71" s="5"/>
       <c r="I71" s="5"/>
       <c r="J71" s="5"/>
       <c r="K71" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L71" s="5"/>
       <c r="M71" s="5"/>
       <c r="N71" s="7"/>
-      <c r="O71" s="5"/>
-    </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O71" s="7"/>
+      <c r="P71" s="5" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A72" s="5">
         <v>2</v>
       </c>
       <c r="B72" s="5"/>
       <c r="C72" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D72" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H72" s="5"/>
       <c r="I72" s="5"/>
       <c r="J72" s="5"/>
       <c r="K72" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L72" s="5"/>
       <c r="M72" s="5"/>
       <c r="N72" s="7"/>
-      <c r="O72" s="5"/>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O72" s="7"/>
+      <c r="P72" s="5"/>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A73" s="5">
         <v>2</v>
       </c>
       <c r="B73" s="5"/>
       <c r="C73" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D73" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H73" s="5"/>
       <c r="I73" s="5"/>
       <c r="J73" s="5"/>
       <c r="K73" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L73" s="5"/>
       <c r="M73" s="5"/>
       <c r="N73" s="7"/>
-      <c r="O73" s="5"/>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O73" s="7"/>
+      <c r="P73" s="5" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A74" s="5">
         <v>2</v>
       </c>
       <c r="B74" s="5"/>
       <c r="C74" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D74" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H74" s="5"/>
       <c r="I74" s="5"/>
       <c r="J74" s="5"/>
       <c r="K74" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L74" s="5"/>
       <c r="M74" s="5"/>
       <c r="N74" s="7"/>
-      <c r="O74" s="5"/>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O74" s="7"/>
+      <c r="P74" s="5" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A75" s="5">
         <v>2</v>
       </c>
       <c r="B75" s="5"/>
       <c r="C75" s="5" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="D75" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H75" s="5"/>
       <c r="I75" s="5"/>
       <c r="J75" s="5"/>
       <c r="K75" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L75" s="5"/>
       <c r="M75" s="5"/>
       <c r="N75" s="7"/>
-      <c r="O75" s="5"/>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O75" s="7"/>
+      <c r="P75" s="5"/>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A76" s="5">
         <v>2</v>
       </c>
       <c r="B76" s="5"/>
       <c r="C76" s="5" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="D76" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H76" s="5"/>
       <c r="I76" s="5"/>
       <c r="J76" s="5"/>
       <c r="K76" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L76" s="5"/>
       <c r="M76" s="5"/>
       <c r="N76" s="7"/>
-      <c r="O76" s="5"/>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O76" s="7"/>
+      <c r="P76" s="5"/>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A77" s="5">
         <v>2</v>
       </c>
       <c r="B77" s="5"/>
       <c r="C77" s="5" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D77" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H77" s="5"/>
       <c r="I77" s="5"/>
       <c r="J77" s="5"/>
       <c r="K77" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L77" s="5"/>
       <c r="M77" s="5"/>
       <c r="N77" s="7"/>
-      <c r="O77" s="5"/>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O77" s="7"/>
+      <c r="P77" s="5" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A78" s="5">
         <v>2</v>
       </c>
       <c r="B78" s="5"/>
       <c r="C78" s="5" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D78" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>232</v>
+        <v>331</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>87</v>
+        <v>329</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H78" s="5"/>
       <c r="I78" s="5"/>
       <c r="J78" s="5"/>
       <c r="K78" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L78" s="5"/>
       <c r="M78" s="5"/>
       <c r="N78" s="7"/>
-      <c r="O78" s="5"/>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O78" s="7"/>
+      <c r="P78" s="5"/>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A79" s="5">
         <v>2</v>
       </c>
       <c r="B79" s="5"/>
       <c r="C79" s="5" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="D79" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H79" s="5"/>
       <c r="I79" s="5"/>
       <c r="J79" s="5"/>
       <c r="K79" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L79" s="5"/>
       <c r="M79" s="5"/>
       <c r="N79" s="7"/>
-      <c r="O79" s="5"/>
-    </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O79" s="7"/>
+      <c r="P79" s="5"/>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A80" s="5">
         <v>2</v>
       </c>
       <c r="B80" s="5"/>
       <c r="C80" s="5" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="D80" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>332</v>
+        <v>251</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>330</v>
+        <v>110</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H80" s="5"/>
       <c r="I80" s="5"/>
       <c r="J80" s="5"/>
       <c r="K80" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L80" s="5"/>
       <c r="M80" s="5"/>
       <c r="N80" s="7"/>
-      <c r="O80" s="5"/>
-    </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O80" s="7"/>
+      <c r="P80" s="5"/>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A81" s="5">
         <v>2</v>
       </c>
@@ -4337,26 +4458,27 @@
         <v>51</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H81" s="5"/>
       <c r="I81" s="5"/>
       <c r="J81" s="5"/>
       <c r="K81" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L81" s="5"/>
       <c r="M81" s="5"/>
       <c r="N81" s="7"/>
-      <c r="O81" s="5"/>
-    </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O81" s="7"/>
+      <c r="P81" s="5"/>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A82" s="5">
         <v>2</v>
       </c>
@@ -4368,26 +4490,27 @@
         <v>51</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H82" s="5"/>
       <c r="I82" s="5"/>
       <c r="J82" s="5"/>
       <c r="K82" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L82" s="5"/>
       <c r="M82" s="5"/>
       <c r="N82" s="7"/>
-      <c r="O82" s="5"/>
-    </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O82" s="7"/>
+      <c r="P82" s="5"/>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A83" s="5">
         <v>2</v>
       </c>
@@ -4405,20 +4528,21 @@
         <v>112</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H83" s="5"/>
       <c r="I83" s="5"/>
       <c r="J83" s="5"/>
       <c r="K83" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L83" s="5"/>
       <c r="M83" s="5"/>
       <c r="N83" s="7"/>
-      <c r="O83" s="5"/>
-    </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O83" s="7"/>
+      <c r="P83" s="5"/>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A84" s="5">
         <v>2</v>
       </c>
@@ -4430,26 +4554,27 @@
         <v>51</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H84" s="5"/>
       <c r="I84" s="5"/>
       <c r="J84" s="5"/>
       <c r="K84" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L84" s="5"/>
       <c r="M84" s="5"/>
       <c r="N84" s="7"/>
-      <c r="O84" s="5"/>
-    </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O84" s="7"/>
+      <c r="P84" s="5"/>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A85" s="5">
         <v>2</v>
       </c>
@@ -4461,26 +4586,27 @@
         <v>51</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H85" s="5"/>
       <c r="I85" s="5"/>
       <c r="J85" s="5"/>
       <c r="K85" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L85" s="5"/>
       <c r="M85" s="5"/>
       <c r="N85" s="7"/>
-      <c r="O85" s="5"/>
-    </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O85" s="7"/>
+      <c r="P85" s="5"/>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A86" s="5">
         <v>2</v>
       </c>
@@ -4498,20 +4624,21 @@
         <v>114</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H86" s="5"/>
       <c r="I86" s="5"/>
       <c r="J86" s="5"/>
       <c r="K86" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L86" s="5"/>
       <c r="M86" s="5"/>
       <c r="N86" s="7"/>
-      <c r="O86" s="5"/>
-    </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O86" s="7"/>
+      <c r="P86" s="5"/>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A87" s="5">
         <v>2</v>
       </c>
@@ -4523,26 +4650,27 @@
         <v>51</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H87" s="5"/>
       <c r="I87" s="5"/>
       <c r="J87" s="5"/>
       <c r="K87" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L87" s="5"/>
       <c r="M87" s="5"/>
       <c r="N87" s="7"/>
-      <c r="O87" s="5"/>
-    </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O87" s="7"/>
+      <c r="P87" s="5"/>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A88" s="5">
         <v>2</v>
       </c>
@@ -4560,20 +4688,21 @@
         <v>115</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H88" s="5"/>
       <c r="I88" s="5"/>
       <c r="J88" s="5"/>
       <c r="K88" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L88" s="5"/>
       <c r="M88" s="5"/>
       <c r="N88" s="7"/>
-      <c r="O88" s="5"/>
-    </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O88" s="7"/>
+      <c r="P88" s="5"/>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A89" s="5">
         <v>2</v>
       </c>
@@ -4585,26 +4714,27 @@
         <v>51</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H89" s="5"/>
       <c r="I89" s="5"/>
       <c r="J89" s="5"/>
       <c r="K89" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L89" s="5"/>
       <c r="M89" s="5"/>
       <c r="N89" s="7"/>
-      <c r="O89" s="5"/>
-    </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O89" s="7"/>
+      <c r="P89" s="5"/>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A90" s="5">
         <v>2</v>
       </c>
@@ -4619,23 +4749,24 @@
         <v>257</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H90" s="5"/>
       <c r="I90" s="5"/>
       <c r="J90" s="5"/>
       <c r="K90" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L90" s="5"/>
       <c r="M90" s="5"/>
       <c r="N90" s="7"/>
-      <c r="O90" s="5"/>
-    </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O90" s="7"/>
+      <c r="P90" s="5"/>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A91" s="5">
         <v>2</v>
       </c>
@@ -4647,26 +4778,29 @@
         <v>51</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H91" s="5"/>
       <c r="I91" s="5"/>
       <c r="J91" s="5"/>
       <c r="K91" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L91" s="5"/>
       <c r="M91" s="5"/>
       <c r="N91" s="7"/>
-      <c r="O91" s="5"/>
-    </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O91" s="7"/>
+      <c r="P91" s="5" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A92" s="5">
         <v>2</v>
       </c>
@@ -4684,22 +4818,23 @@
         <v>118</v>
       </c>
       <c r="G92" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H92" s="5"/>
       <c r="I92" s="5"/>
       <c r="J92" s="5"/>
       <c r="K92" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L92" s="5"/>
       <c r="M92" s="5"/>
       <c r="N92" s="7"/>
-      <c r="O92" s="5"/>
-    </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O92" s="7"/>
+      <c r="P92" s="5"/>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A93" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B93" s="5"/>
       <c r="C93" s="5" t="s">
@@ -4709,32 +4844,33 @@
         <v>51</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="H93" s="5"/>
       <c r="I93" s="5"/>
       <c r="J93" s="5"/>
       <c r="K93" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L93" s="5"/>
       <c r="M93" s="5"/>
       <c r="N93" s="7"/>
-      <c r="O93" s="5"/>
-    </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O93" s="7"/>
+      <c r="P93" s="5"/>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A94" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B94" s="5"/>
       <c r="C94" s="5" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D94" s="5" t="s">
         <v>51</v>
@@ -4746,367 +4882,379 @@
         <v>119</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="H94" s="5"/>
       <c r="I94" s="5"/>
       <c r="J94" s="5"/>
       <c r="K94" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L94" s="5"/>
       <c r="M94" s="5"/>
       <c r="N94" s="7"/>
-      <c r="O94" s="5"/>
-    </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O94" s="7"/>
+      <c r="P94" s="5"/>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A95" s="5">
         <v>3</v>
       </c>
       <c r="B95" s="5"/>
       <c r="C95" s="5" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D95" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H95" s="5"/>
       <c r="I95" s="5"/>
       <c r="J95" s="5"/>
       <c r="K95" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L95" s="5"/>
       <c r="M95" s="5"/>
       <c r="N95" s="7"/>
-      <c r="O95" s="5"/>
-    </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O95" s="7"/>
+      <c r="P95" s="5"/>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A96" s="5">
         <v>3</v>
       </c>
       <c r="B96" s="5"/>
       <c r="C96" s="5" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="D96" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H96" s="5"/>
       <c r="I96" s="5"/>
       <c r="J96" s="5"/>
       <c r="K96" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L96" s="5"/>
       <c r="M96" s="5"/>
       <c r="N96" s="7"/>
-      <c r="O96" s="5"/>
-    </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O96" s="7"/>
+      <c r="P96" s="5"/>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A97" s="5">
         <v>3</v>
       </c>
       <c r="B97" s="5"/>
       <c r="C97" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D97" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="F97" s="5" t="s">
         <v>122</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H97" s="5"/>
       <c r="I97" s="5"/>
       <c r="J97" s="5"/>
       <c r="K97" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L97" s="5"/>
       <c r="M97" s="5"/>
       <c r="N97" s="7"/>
-      <c r="O97" s="5"/>
-    </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O97" s="7"/>
+      <c r="P97" s="5"/>
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A98" s="5">
         <v>3</v>
       </c>
       <c r="B98" s="5"/>
       <c r="C98" s="5" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D98" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H98" s="5"/>
       <c r="I98" s="5"/>
       <c r="J98" s="5"/>
       <c r="K98" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L98" s="5"/>
       <c r="M98" s="5"/>
       <c r="N98" s="7"/>
-      <c r="O98" s="5"/>
-    </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O98" s="7"/>
+      <c r="P98" s="5"/>
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A99" s="5">
         <v>3</v>
       </c>
       <c r="B99" s="5"/>
       <c r="C99" s="5" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="D99" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H99" s="5"/>
       <c r="I99" s="5"/>
       <c r="J99" s="5"/>
       <c r="K99" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L99" s="5"/>
       <c r="M99" s="5"/>
       <c r="N99" s="7"/>
-      <c r="O99" s="5"/>
-    </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O99" s="7"/>
+      <c r="P99" s="5"/>
+    </row>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A100" s="5">
         <v>3</v>
       </c>
       <c r="B100" s="5"/>
       <c r="C100" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D100" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H100" s="5"/>
       <c r="I100" s="5"/>
       <c r="J100" s="5"/>
       <c r="K100" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L100" s="5"/>
       <c r="M100" s="5"/>
       <c r="N100" s="7"/>
-      <c r="O100" s="5"/>
-    </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O100" s="7"/>
+      <c r="P100" s="5"/>
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A101" s="5">
         <v>3</v>
       </c>
       <c r="B101" s="5"/>
       <c r="C101" s="5" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D101" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H101" s="5"/>
       <c r="I101" s="5"/>
       <c r="J101" s="5"/>
       <c r="K101" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L101" s="5"/>
       <c r="M101" s="5"/>
       <c r="N101" s="7"/>
-      <c r="O101" s="5"/>
-    </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O101" s="7"/>
+      <c r="P101" s="5"/>
+    </row>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A102" s="5">
         <v>3</v>
       </c>
       <c r="B102" s="5"/>
       <c r="C102" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D102" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H102" s="5"/>
       <c r="I102" s="5"/>
       <c r="J102" s="5"/>
       <c r="K102" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L102" s="5"/>
       <c r="M102" s="5"/>
       <c r="N102" s="7"/>
-      <c r="O102" s="5"/>
-    </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O102" s="7"/>
+      <c r="P102" s="5"/>
+    </row>
+    <row r="103" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A103" s="5">
         <v>3</v>
       </c>
       <c r="B103" s="5"/>
       <c r="C103" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D103" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H103" s="5"/>
       <c r="I103" s="5"/>
       <c r="J103" s="5"/>
       <c r="K103" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L103" s="5"/>
       <c r="M103" s="5"/>
       <c r="N103" s="7"/>
-      <c r="O103" s="5"/>
-    </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O103" s="7"/>
+      <c r="P103" s="5"/>
+    </row>
+    <row r="104" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A104" s="5">
         <v>3</v>
       </c>
       <c r="B104" s="5"/>
       <c r="C104" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D104" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H104" s="5"/>
       <c r="I104" s="5"/>
       <c r="J104" s="5"/>
       <c r="K104" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L104" s="5"/>
       <c r="M104" s="5"/>
       <c r="N104" s="7"/>
-      <c r="O104" s="5"/>
-    </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O104" s="7"/>
+      <c r="P104" s="5"/>
+    </row>
+    <row r="105" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A105" s="5">
         <v>3</v>
       </c>
       <c r="B105" s="5"/>
       <c r="C105" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D105" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H105" s="5"/>
       <c r="I105" s="5"/>
       <c r="J105" s="5"/>
       <c r="K105" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L105" s="5"/>
       <c r="M105" s="5"/>
       <c r="N105" s="7"/>
-      <c r="O105" s="5"/>
-    </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O105" s="7"/>
+      <c r="P105" s="5"/>
+    </row>
+    <row r="106" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A106" s="5">
         <v>3</v>
       </c>
       <c r="B106" s="5"/>
       <c r="C106" s="5" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="D106" s="5" t="s">
         <v>51</v>
@@ -5118,150 +5266,155 @@
         <v>127</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H106" s="5"/>
       <c r="I106" s="5"/>
       <c r="J106" s="5"/>
       <c r="K106" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L106" s="5"/>
       <c r="M106" s="5"/>
       <c r="N106" s="7"/>
-      <c r="O106" s="5"/>
-    </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O106" s="7"/>
+      <c r="P106" s="5"/>
+    </row>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A107" s="5">
         <v>3</v>
       </c>
       <c r="B107" s="5"/>
       <c r="C107" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D107" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H107" s="5"/>
       <c r="I107" s="5"/>
       <c r="J107" s="5"/>
       <c r="K107" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L107" s="5"/>
       <c r="M107" s="5"/>
       <c r="N107" s="7"/>
-      <c r="O107" s="5"/>
-    </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O107" s="7"/>
+      <c r="P107" s="5"/>
+    </row>
+    <row r="108" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A108" s="5">
         <v>3</v>
       </c>
       <c r="B108" s="5"/>
       <c r="C108" s="5" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D108" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G108" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H108" s="5"/>
       <c r="I108" s="5"/>
       <c r="J108" s="5"/>
       <c r="K108" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L108" s="5"/>
       <c r="M108" s="5"/>
       <c r="N108" s="7"/>
-      <c r="O108" s="5"/>
-    </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O108" s="7"/>
+      <c r="P108" s="5"/>
+    </row>
+    <row r="109" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A109" s="5">
         <v>3</v>
       </c>
       <c r="B109" s="5"/>
       <c r="C109" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D109" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H109" s="5"/>
       <c r="I109" s="5"/>
       <c r="J109" s="5"/>
       <c r="K109" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L109" s="5"/>
       <c r="M109" s="5"/>
       <c r="N109" s="7"/>
-      <c r="O109" s="5"/>
-    </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O109" s="7"/>
+      <c r="P109" s="5"/>
+    </row>
+    <row r="110" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A110" s="5">
         <v>3</v>
       </c>
       <c r="B110" s="5"/>
       <c r="C110" s="5" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="D110" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H110" s="5"/>
       <c r="I110" s="5"/>
       <c r="J110" s="5"/>
       <c r="K110" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L110" s="5"/>
       <c r="M110" s="5"/>
-      <c r="N110" s="7"/>
-      <c r="O110" s="5"/>
-    </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="N110" s="16"/>
+      <c r="O110" s="7"/>
+      <c r="P110" s="5"/>
+    </row>
+    <row r="111" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A111" s="5">
         <v>3</v>
       </c>
       <c r="B111" s="5"/>
       <c r="C111" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D111" s="5" t="s">
         <v>51</v>
@@ -5273,57 +5426,59 @@
         <v>131</v>
       </c>
       <c r="G111" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H111" s="5"/>
       <c r="I111" s="5"/>
       <c r="J111" s="5"/>
       <c r="K111" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L111" s="5"/>
       <c r="M111" s="5"/>
-      <c r="N111" s="7"/>
-      <c r="O111" s="5"/>
-    </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="N111" s="16"/>
+      <c r="O111" s="7"/>
+      <c r="P111" s="5"/>
+    </row>
+    <row r="112" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A112" s="5">
         <v>3</v>
       </c>
       <c r="B112" s="5"/>
       <c r="C112" s="5" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D112" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="G112" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H112" s="5"/>
       <c r="I112" s="5"/>
       <c r="J112" s="5"/>
       <c r="K112" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L112" s="5"/>
       <c r="M112" s="5"/>
       <c r="N112" s="16"/>
-      <c r="O112" s="5"/>
-    </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O112" s="7"/>
+      <c r="P112" s="5"/>
+    </row>
+    <row r="113" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A113" s="5">
         <v>3</v>
       </c>
       <c r="B113" s="5"/>
       <c r="C113" s="5" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="D113" s="5" t="s">
         <v>51</v>
@@ -5335,88 +5490,91 @@
         <v>132</v>
       </c>
       <c r="G113" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H113" s="5"/>
       <c r="I113" s="5"/>
       <c r="J113" s="5"/>
       <c r="K113" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L113" s="5"/>
       <c r="M113" s="5"/>
       <c r="N113" s="16"/>
-      <c r="O113" s="5"/>
-    </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O113" s="7"/>
+      <c r="P113" s="5"/>
+    </row>
+    <row r="114" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A114" s="5">
         <v>3</v>
       </c>
       <c r="B114" s="5"/>
       <c r="C114" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D114" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="G114" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H114" s="5"/>
       <c r="I114" s="5"/>
       <c r="J114" s="5"/>
       <c r="K114" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L114" s="5"/>
       <c r="M114" s="5"/>
       <c r="N114" s="16"/>
-      <c r="O114" s="5"/>
-    </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O114" s="7"/>
+      <c r="P114" s="5"/>
+    </row>
+    <row r="115" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A115" s="5">
         <v>3</v>
       </c>
       <c r="B115" s="5"/>
       <c r="C115" s="5" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D115" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="G115" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H115" s="5"/>
       <c r="I115" s="5"/>
       <c r="J115" s="5"/>
       <c r="K115" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L115" s="5"/>
       <c r="M115" s="5"/>
       <c r="N115" s="16"/>
-      <c r="O115" s="5"/>
-    </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O115" s="7"/>
+      <c r="P115" s="5"/>
+    </row>
+    <row r="116" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A116" s="5">
         <v>3</v>
       </c>
       <c r="B116" s="5"/>
       <c r="C116" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D116" s="5" t="s">
         <v>51</v>
@@ -5428,26 +5586,27 @@
         <v>133</v>
       </c>
       <c r="G116" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H116" s="5"/>
       <c r="I116" s="5"/>
       <c r="J116" s="5"/>
       <c r="K116" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L116" s="5"/>
       <c r="M116" s="5"/>
       <c r="N116" s="16"/>
-      <c r="O116" s="5"/>
-    </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O116" s="7"/>
+      <c r="P116" s="5"/>
+    </row>
+    <row r="117" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A117" s="5">
         <v>3</v>
       </c>
       <c r="B117" s="5"/>
       <c r="C117" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D117" s="5" t="s">
         <v>51</v>
@@ -5459,82 +5618,85 @@
         <v>118</v>
       </c>
       <c r="G117" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H117" s="5"/>
       <c r="I117" s="5"/>
       <c r="J117" s="5"/>
       <c r="K117" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L117" s="5"/>
       <c r="M117" s="5"/>
       <c r="N117" s="16"/>
-      <c r="O117" s="5"/>
-    </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O117" s="7"/>
+      <c r="P117" s="5"/>
+    </row>
+    <row r="118" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A118" s="5">
         <v>3</v>
       </c>
       <c r="B118" s="5"/>
       <c r="C118" s="5" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="D118" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>273</v>
+        <v>228</v>
       </c>
       <c r="F118" s="5" t="s">
         <v>134</v>
       </c>
       <c r="G118" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H118" s="5"/>
       <c r="I118" s="5"/>
       <c r="J118" s="5"/>
       <c r="K118" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L118" s="5"/>
       <c r="M118" s="5"/>
       <c r="N118" s="16"/>
-      <c r="O118" s="5"/>
-    </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O118" s="7"/>
+      <c r="P118" s="5"/>
+    </row>
+    <row r="119" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A119" s="5">
         <v>3</v>
       </c>
       <c r="B119" s="5"/>
       <c r="C119" s="5" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="D119" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>259</v>
+        <v>230</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="G119" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H119" s="5"/>
       <c r="I119" s="5"/>
       <c r="J119" s="5"/>
       <c r="K119" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L119" s="5"/>
       <c r="M119" s="5"/>
       <c r="N119" s="16"/>
-      <c r="O119" s="5"/>
-    </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O119" s="7"/>
+      <c r="P119" s="5"/>
+    </row>
+    <row r="120" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A120" s="5">
         <v>3</v>
       </c>
@@ -5546,26 +5708,27 @@
         <v>51</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="G120" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H120" s="5"/>
       <c r="I120" s="5"/>
       <c r="J120" s="5"/>
       <c r="K120" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L120" s="5"/>
       <c r="M120" s="5"/>
       <c r="N120" s="16"/>
-      <c r="O120" s="5"/>
-    </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O120" s="7"/>
+      <c r="P120" s="5"/>
+    </row>
+    <row r="121" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A121" s="5">
         <v>3</v>
       </c>
@@ -5577,26 +5740,27 @@
         <v>51</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="G121" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H121" s="5"/>
       <c r="I121" s="5"/>
       <c r="J121" s="5"/>
       <c r="K121" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L121" s="5"/>
       <c r="M121" s="5"/>
       <c r="N121" s="16"/>
-      <c r="O121" s="5"/>
-    </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O121" s="7"/>
+      <c r="P121" s="5"/>
+    </row>
+    <row r="122" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A122" s="5">
         <v>3</v>
       </c>
@@ -5608,26 +5772,27 @@
         <v>51</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G122" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H122" s="5"/>
       <c r="I122" s="5"/>
       <c r="J122" s="5"/>
       <c r="K122" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L122" s="5"/>
       <c r="M122" s="5"/>
       <c r="N122" s="16"/>
-      <c r="O122" s="5"/>
-    </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O122" s="7"/>
+      <c r="P122" s="5"/>
+    </row>
+    <row r="123" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A123" s="5">
         <v>3</v>
       </c>
@@ -5639,26 +5804,27 @@
         <v>51</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H123" s="5"/>
       <c r="I123" s="5"/>
       <c r="J123" s="5"/>
       <c r="K123" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L123" s="5"/>
       <c r="M123" s="5"/>
       <c r="N123" s="16"/>
-      <c r="O123" s="5"/>
-    </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O123" s="7"/>
+      <c r="P123" s="5"/>
+    </row>
+    <row r="124" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A124" s="5">
         <v>3</v>
       </c>
@@ -5670,26 +5836,27 @@
         <v>51</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="G124" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H124" s="5"/>
       <c r="I124" s="5"/>
       <c r="J124" s="5"/>
       <c r="K124" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L124" s="5"/>
       <c r="M124" s="5"/>
       <c r="N124" s="16"/>
-      <c r="O124" s="5"/>
-    </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O124" s="7"/>
+      <c r="P124" s="5"/>
+    </row>
+    <row r="125" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A125" s="5">
         <v>3</v>
       </c>
@@ -5701,88 +5868,91 @@
         <v>51</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G125" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H125" s="5"/>
       <c r="I125" s="5"/>
       <c r="J125" s="5"/>
       <c r="K125" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L125" s="5"/>
       <c r="M125" s="5"/>
       <c r="N125" s="16"/>
-      <c r="O125" s="5"/>
-    </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O125" s="7"/>
+      <c r="P125" s="5"/>
+    </row>
+    <row r="126" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A126" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B126" s="5"/>
       <c r="C126" s="5" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>51</v>
+        <v>140</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>250</v>
+        <v>274</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>107</v>
+        <v>141</v>
       </c>
       <c r="G126" s="5" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="H126" s="5"/>
       <c r="I126" s="5"/>
       <c r="J126" s="5"/>
       <c r="K126" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L126" s="5"/>
       <c r="M126" s="5"/>
       <c r="N126" s="16"/>
-      <c r="O126" s="5"/>
-    </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O126" s="7"/>
+      <c r="P126" s="5"/>
+    </row>
+    <row r="127" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A127" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B127" s="5"/>
       <c r="C127" s="5" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>51</v>
+        <v>142</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>251</v>
+        <v>275</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="G127" s="5" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="H127" s="5"/>
       <c r="I127" s="5"/>
       <c r="J127" s="5"/>
       <c r="K127" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L127" s="5"/>
       <c r="M127" s="5"/>
       <c r="N127" s="16"/>
-      <c r="O127" s="5"/>
-    </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O127" s="7"/>
+      <c r="P127" s="5"/>
+    </row>
+    <row r="128" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A128" s="5">
         <v>2</v>
       </c>
@@ -5791,69 +5961,71 @@
         <v>13</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="G128" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H128" s="5"/>
       <c r="I128" s="5"/>
       <c r="J128" s="5"/>
       <c r="K128" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L128" s="5"/>
       <c r="M128" s="5"/>
       <c r="N128" s="16"/>
-      <c r="O128" s="5"/>
-    </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O128" s="7"/>
+      <c r="P128" s="5"/>
+    </row>
+    <row r="129" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A129" s="5">
         <v>2</v>
       </c>
       <c r="B129" s="5"/>
       <c r="C129" s="5" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>143</v>
+        <v>14</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>276</v>
+        <v>202</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>144</v>
+        <v>23</v>
       </c>
       <c r="G129" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H129" s="5"/>
       <c r="I129" s="5"/>
       <c r="J129" s="5"/>
       <c r="K129" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L129" s="5"/>
       <c r="M129" s="5"/>
       <c r="N129" s="16"/>
-      <c r="O129" s="5"/>
-    </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O129" s="7"/>
+      <c r="P129" s="5"/>
+    </row>
+    <row r="130" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A130" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B130" s="5"/>
       <c r="C130" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>145</v>
+        <v>14</v>
       </c>
       <c r="E130" s="5" t="s">
         <v>277</v>
@@ -5862,51 +6034,53 @@
         <v>146</v>
       </c>
       <c r="G130" s="5" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="H130" s="5"/>
       <c r="I130" s="5"/>
       <c r="J130" s="5"/>
       <c r="K130" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L130" s="5"/>
       <c r="M130" s="5"/>
       <c r="N130" s="16"/>
-      <c r="O130" s="5"/>
-    </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O130" s="7"/>
+      <c r="P130" s="5"/>
+    </row>
+    <row r="131" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A131" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B131" s="5"/>
       <c r="C131" s="5" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D131" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>203</v>
+        <v>278</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>23</v>
+        <v>147</v>
       </c>
       <c r="G131" s="5" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="H131" s="5"/>
       <c r="I131" s="5"/>
       <c r="J131" s="5"/>
       <c r="K131" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L131" s="5"/>
       <c r="M131" s="5"/>
       <c r="N131" s="16"/>
-      <c r="O131" s="5"/>
-    </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O131" s="7"/>
+      <c r="P131" s="5"/>
+    </row>
+    <row r="132" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A132" s="5">
         <v>3</v>
       </c>
@@ -5915,29 +6089,30 @@
         <v>13</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>14</v>
+        <v>148</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G132" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H132" s="5"/>
       <c r="I132" s="5"/>
       <c r="J132" s="5"/>
       <c r="K132" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L132" s="5"/>
       <c r="M132" s="5"/>
       <c r="N132" s="16"/>
-      <c r="O132" s="5"/>
-    </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O132" s="7"/>
+      <c r="P132" s="5"/>
+    </row>
+    <row r="133" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A133" s="5">
         <v>3</v>
       </c>
@@ -5949,26 +6124,27 @@
         <v>14</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G133" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H133" s="5"/>
       <c r="I133" s="5"/>
       <c r="J133" s="5"/>
       <c r="K133" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L133" s="5"/>
       <c r="M133" s="5"/>
       <c r="N133" s="16"/>
-      <c r="O133" s="5"/>
-    </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O133" s="7"/>
+      <c r="P133" s="5"/>
+    </row>
+    <row r="134" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A134" s="5">
         <v>3</v>
       </c>
@@ -5977,29 +6153,30 @@
         <v>13</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>149</v>
+        <v>14</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="G134" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H134" s="5"/>
       <c r="I134" s="5"/>
       <c r="J134" s="5"/>
       <c r="K134" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L134" s="5"/>
       <c r="M134" s="5"/>
       <c r="N134" s="16"/>
-      <c r="O134" s="5"/>
-    </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O134" s="7"/>
+      <c r="P134" s="5"/>
+    </row>
+    <row r="135" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A135" s="5">
         <v>3</v>
       </c>
@@ -6011,26 +6188,27 @@
         <v>14</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="G135" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H135" s="5"/>
       <c r="I135" s="5"/>
       <c r="J135" s="5"/>
       <c r="K135" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L135" s="5"/>
       <c r="M135" s="5"/>
       <c r="N135" s="16"/>
-      <c r="O135" s="5"/>
-    </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O135" s="7"/>
+      <c r="P135" s="5"/>
+    </row>
+    <row r="136" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A136" s="5">
         <v>3</v>
       </c>
@@ -6039,667 +6217,698 @@
         <v>13</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>14</v>
+        <v>155</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G136" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H136" s="5"/>
       <c r="I136" s="5"/>
       <c r="J136" s="5"/>
       <c r="K136" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L136" s="5"/>
       <c r="M136" s="5"/>
       <c r="N136" s="16"/>
-      <c r="O136" s="5"/>
-    </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O136" s="7"/>
+      <c r="P136" s="5"/>
+    </row>
+    <row r="137" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A137" s="5">
         <v>3</v>
       </c>
       <c r="B137" s="5"/>
       <c r="C137" s="5" t="s">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="G137" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H137" s="5"/>
       <c r="I137" s="5"/>
       <c r="J137" s="5"/>
       <c r="K137" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L137" s="5"/>
       <c r="M137" s="5"/>
       <c r="N137" s="16"/>
-      <c r="O137" s="5"/>
-    </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O137" s="7"/>
+      <c r="P137" s="5"/>
+    </row>
+    <row r="138" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A138" s="5">
         <v>3</v>
       </c>
       <c r="B138" s="5"/>
       <c r="C138" s="5" t="s">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>156</v>
+        <v>51</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G138" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H138" s="5"/>
       <c r="I138" s="5"/>
       <c r="J138" s="5"/>
       <c r="K138" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L138" s="5"/>
       <c r="M138" s="5"/>
       <c r="N138" s="16"/>
-      <c r="O138" s="5"/>
-    </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O138" s="7"/>
+      <c r="P138" s="5"/>
+    </row>
+    <row r="139" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A139" s="5">
         <v>3</v>
       </c>
       <c r="B139" s="5"/>
       <c r="C139" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D139" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>287</v>
+        <v>228</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G139" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H139" s="5"/>
       <c r="I139" s="5"/>
       <c r="J139" s="5"/>
       <c r="K139" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L139" s="5"/>
       <c r="M139" s="5"/>
       <c r="N139" s="16"/>
-      <c r="O139" s="5"/>
-    </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O139" s="7"/>
+      <c r="P139" s="5"/>
+    </row>
+    <row r="140" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A140" s="5">
         <v>3</v>
       </c>
       <c r="B140" s="5"/>
       <c r="C140" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D140" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>288</v>
+        <v>228</v>
       </c>
       <c r="F140" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G140" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H140" s="5"/>
       <c r="I140" s="5"/>
       <c r="J140" s="5"/>
       <c r="K140" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L140" s="5"/>
       <c r="M140" s="5"/>
       <c r="N140" s="16"/>
-      <c r="O140" s="5"/>
-    </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O140" s="7"/>
+      <c r="P140" s="5"/>
+    </row>
+    <row r="141" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A141" s="5">
         <v>3</v>
       </c>
       <c r="B141" s="5"/>
       <c r="C141" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D141" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G141" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H141" s="5"/>
       <c r="I141" s="5"/>
       <c r="J141" s="5"/>
       <c r="K141" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L141" s="5"/>
       <c r="M141" s="5"/>
       <c r="N141" s="16"/>
-      <c r="O141" s="5"/>
-    </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O141" s="7"/>
+      <c r="P141" s="5"/>
+    </row>
+    <row r="142" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A142" s="5">
         <v>3</v>
       </c>
       <c r="B142" s="5"/>
       <c r="C142" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D142" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G142" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H142" s="5"/>
       <c r="I142" s="5"/>
       <c r="J142" s="5"/>
       <c r="K142" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L142" s="5"/>
       <c r="M142" s="5"/>
       <c r="N142" s="16"/>
-      <c r="O142" s="5"/>
-    </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O142" s="7"/>
+      <c r="P142" s="5"/>
+    </row>
+    <row r="143" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A143" s="5">
         <v>3</v>
       </c>
       <c r="B143" s="5"/>
       <c r="C143" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D143" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E143" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F143" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G143" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H143" s="5"/>
       <c r="I143" s="5"/>
       <c r="J143" s="5"/>
       <c r="K143" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L143" s="5"/>
       <c r="M143" s="5"/>
       <c r="N143" s="16"/>
-      <c r="O143" s="5"/>
-    </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O143" s="7"/>
+      <c r="P143" s="5"/>
+    </row>
+    <row r="144" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A144" s="5">
         <v>3</v>
       </c>
       <c r="B144" s="5"/>
       <c r="C144" s="5" t="s">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="D144" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F144" s="5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G144" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H144" s="5"/>
       <c r="I144" s="5"/>
       <c r="J144" s="5"/>
       <c r="K144" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L144" s="5"/>
       <c r="M144" s="5"/>
       <c r="N144" s="16"/>
-      <c r="O144" s="5"/>
-    </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O144" s="7"/>
+      <c r="P144" s="5"/>
+    </row>
+    <row r="145" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A145" s="5">
         <v>3</v>
       </c>
       <c r="B145" s="5"/>
       <c r="C145" s="5" t="s">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="D145" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F145" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G145" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H145" s="5"/>
       <c r="I145" s="5"/>
       <c r="J145" s="5"/>
       <c r="K145" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L145" s="5"/>
       <c r="M145" s="5"/>
       <c r="N145" s="16"/>
-      <c r="O145" s="5"/>
-    </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O145" s="7"/>
+      <c r="P145" s="5"/>
+    </row>
+    <row r="146" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A146" s="5">
         <v>3</v>
       </c>
       <c r="B146" s="5"/>
       <c r="C146" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D146" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G146" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H146" s="5"/>
       <c r="I146" s="5"/>
       <c r="J146" s="5"/>
       <c r="K146" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L146" s="5"/>
       <c r="M146" s="5"/>
       <c r="N146" s="16"/>
-      <c r="O146" s="5"/>
-    </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O146" s="7"/>
+      <c r="P146" s="5"/>
+    </row>
+    <row r="147" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A147" s="5">
         <v>3</v>
       </c>
       <c r="B147" s="5"/>
       <c r="C147" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D147" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F147" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G147" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H147" s="5"/>
       <c r="I147" s="5"/>
       <c r="J147" s="5"/>
       <c r="K147" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L147" s="5"/>
       <c r="M147" s="5"/>
       <c r="N147" s="16"/>
-      <c r="O147" s="5"/>
-    </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O147" s="7"/>
+      <c r="P147" s="5"/>
+    </row>
+    <row r="148" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A148" s="5">
         <v>3</v>
       </c>
       <c r="B148" s="5"/>
       <c r="C148" s="5" t="s">
-        <v>166</v>
+        <v>50</v>
       </c>
       <c r="D148" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G148" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H148" s="5"/>
       <c r="I148" s="5"/>
       <c r="J148" s="5"/>
       <c r="K148" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L148" s="5"/>
       <c r="M148" s="5"/>
       <c r="N148" s="16"/>
-      <c r="O148" s="5"/>
-    </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O148" s="7"/>
+      <c r="P148" s="5"/>
+    </row>
+    <row r="149" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A149" s="5">
         <v>3</v>
       </c>
       <c r="B149" s="5"/>
       <c r="C149" s="5" t="s">
-        <v>166</v>
+        <v>81</v>
       </c>
       <c r="D149" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F149" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G149" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H149" s="5"/>
       <c r="I149" s="5"/>
       <c r="J149" s="5"/>
       <c r="K149" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L149" s="5"/>
       <c r="M149" s="5"/>
       <c r="N149" s="16"/>
-      <c r="O149" s="5"/>
-    </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O149" s="7"/>
+      <c r="P149" s="5"/>
+    </row>
+    <row r="150" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A150" s="5">
         <v>3</v>
       </c>
       <c r="B150" s="5"/>
       <c r="C150" s="5" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D150" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G150" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H150" s="5"/>
       <c r="I150" s="5"/>
       <c r="J150" s="5"/>
       <c r="K150" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L150" s="5"/>
       <c r="M150" s="5"/>
       <c r="N150" s="16"/>
-      <c r="O150" s="5"/>
-    </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O150" s="7"/>
+      <c r="P150" s="5"/>
+    </row>
+    <row r="151" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A151" s="5">
         <v>3</v>
       </c>
       <c r="B151" s="5"/>
       <c r="C151" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D151" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G151" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H151" s="5"/>
       <c r="I151" s="5"/>
       <c r="J151" s="5"/>
       <c r="K151" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L151" s="5"/>
       <c r="M151" s="5"/>
       <c r="N151" s="16"/>
-      <c r="O151" s="5"/>
-    </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O151" s="7"/>
+      <c r="P151" s="5"/>
+    </row>
+    <row r="152" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A152" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B152" s="5"/>
       <c r="C152" s="5" t="s">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>229</v>
+        <v>303</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G152" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="H152" s="5"/>
-      <c r="I152" s="5"/>
-      <c r="J152" s="5"/>
+        <v>315</v>
+      </c>
+      <c r="H152" s="6">
+        <v>46094</v>
+      </c>
+      <c r="I152" s="9">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="J152" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="K152" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L152" s="5"/>
       <c r="M152" s="5"/>
       <c r="N152" s="16"/>
-      <c r="O152" s="5"/>
-    </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O152" s="7"/>
+      <c r="P152" s="5"/>
+    </row>
+    <row r="153" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A153" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B153" s="5"/>
       <c r="C153" s="5" t="s">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>229</v>
+        <v>304</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G153" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="H153" s="5"/>
-      <c r="I153" s="5"/>
-      <c r="J153" s="5"/>
+        <v>315</v>
+      </c>
+      <c r="H153" s="6">
+        <v>46094</v>
+      </c>
+      <c r="I153" s="9">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="J153" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="K153" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L153" s="5"/>
       <c r="M153" s="5"/>
       <c r="N153" s="16"/>
-      <c r="O153" s="5"/>
-    </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O153" s="7"/>
+      <c r="P153" s="5"/>
+    </row>
+    <row r="154" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A154" s="5">
         <v>0</v>
       </c>
       <c r="B154" s="5"/>
       <c r="C154" s="5" t="s">
-        <v>136</v>
+        <v>176</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>304</v>
+        <v>177</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="G154" s="5" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="H154" s="6">
-        <v>46094</v>
+        <v>46095</v>
       </c>
       <c r="I154" s="9">
-        <v>0.41666666666666669</v>
+        <v>0.625</v>
       </c>
       <c r="J154" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K154" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L154" s="5"/>
       <c r="M154" s="5"/>
       <c r="N154" s="16"/>
-      <c r="O154" s="5"/>
-    </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O154" s="7"/>
+      <c r="P154" s="5"/>
+    </row>
+    <row r="155" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A155" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B155" s="5"/>
       <c r="C155" s="5" t="s">
-        <v>136</v>
+        <v>13</v>
       </c>
       <c r="D155" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>305</v>
+        <v>288</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G155" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H155" s="6">
-        <v>46094</v>
+        <v>46128</v>
       </c>
       <c r="I155" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J155" s="5" t="s">
-        <v>16</v>
-      </c>
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="J155" s="5"/>
       <c r="K155" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L155" s="5"/>
       <c r="M155" s="5"/>
       <c r="N155" s="16"/>
-      <c r="O155" s="5"/>
-    </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O155" s="7"/>
+      <c r="P155" s="5"/>
+    </row>
+    <row r="156" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A156" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B156" s="5"/>
       <c r="C156" s="5" t="s">
-        <v>177</v>
+        <v>13</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>178</v>
+        <v>289</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G156" s="5" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="H156" s="6">
-        <v>46095</v>
+        <v>46139</v>
       </c>
       <c r="I156" s="9">
-        <v>0.625</v>
-      </c>
-      <c r="J156" s="5" t="s">
-        <v>16</v>
+        <v>0.25</v>
+      </c>
+      <c r="J156" s="9">
+        <v>0.33333333333333331</v>
       </c>
       <c r="K156" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L156" s="5"/>
       <c r="M156" s="5"/>
       <c r="N156" s="16"/>
-      <c r="O156" s="5"/>
-    </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O156" s="7"/>
+      <c r="P156" s="5"/>
+    </row>
+    <row r="157" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A157" s="5">
         <v>3</v>
       </c>
@@ -6708,33 +6917,36 @@
         <v>13</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>14</v>
+        <v>181</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F157" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G157" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H157" s="6">
-        <v>46128</v>
+        <v>46141</v>
       </c>
       <c r="I157" s="9">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="J157" s="5"/>
+        <v>0.67361111111111116</v>
+      </c>
+      <c r="J157" s="9">
+        <v>0.96527777777777779</v>
+      </c>
       <c r="K157" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L157" s="5"/>
       <c r="M157" s="5"/>
       <c r="N157" s="16"/>
-      <c r="O157" s="5"/>
-    </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O157" s="7"/>
+      <c r="P157" s="5"/>
+    </row>
+    <row r="158" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A158" s="5">
         <v>3</v>
       </c>
@@ -6746,32 +6958,33 @@
         <v>14</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G158" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H158" s="6">
-        <v>46139</v>
+        <v>46146</v>
       </c>
       <c r="I158" s="9">
-        <v>0.25</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J158" s="9">
-        <v>0.33333333333333331</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="K158" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L158" s="5"/>
       <c r="M158" s="5"/>
       <c r="N158" s="16"/>
-      <c r="O158" s="5"/>
-    </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O158" s="7"/>
+      <c r="P158" s="5"/>
+    </row>
+    <row r="159" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A159" s="5">
         <v>3</v>
       </c>
@@ -6780,37 +6993,38 @@
         <v>13</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F159" s="5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G159" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H159" s="6">
-        <v>46141</v>
+        <v>46147</v>
       </c>
       <c r="I159" s="9">
-        <v>0.67361111111111116</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="J159" s="9">
-        <v>0.96527777777777779</v>
+        <v>0.5</v>
       </c>
       <c r="K159" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L159" s="5"/>
       <c r="M159" s="5"/>
       <c r="N159" s="16"/>
-      <c r="O159" s="5"/>
-    </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O159" s="7"/>
+      <c r="P159" s="5"/>
+    </row>
+    <row r="160" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A160" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B160" s="5"/>
       <c r="C160" s="5" t="s">
@@ -6820,32 +7034,33 @@
         <v>14</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G160" s="5" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="H160" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="I160" s="9">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="J160" s="9">
-        <v>0.41666666666666669</v>
-      </c>
+        <v>0.625</v>
+      </c>
+      <c r="J160" s="5"/>
       <c r="K160" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L160" s="5"/>
       <c r="M160" s="5"/>
       <c r="N160" s="16"/>
-      <c r="O160" s="5"/>
-    </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O160" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="P160" s="5"/>
+    </row>
+    <row r="161" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A161" s="5">
         <v>3</v>
       </c>
@@ -6854,70 +7069,72 @@
         <v>13</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>185</v>
+        <v>14</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G161" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H161" s="6">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="I161" s="9">
-        <v>0.45833333333333331</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J161" s="9">
-        <v>0.5</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="K161" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L161" s="5"/>
       <c r="M161" s="5"/>
       <c r="N161" s="16"/>
-      <c r="O161" s="5"/>
-    </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O161" s="7"/>
+      <c r="P161" s="5"/>
+    </row>
+    <row r="162" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A162" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B162" s="5"/>
       <c r="C162" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>14</v>
+        <v>188</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="G162" s="5" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="H162" s="6">
-        <v>46147</v>
-      </c>
-      <c r="I162" s="9">
-        <v>0.625</v>
-      </c>
-      <c r="J162" s="5"/>
+        <v>46155</v>
+      </c>
+      <c r="I162" s="5"/>
+      <c r="J162" s="9">
+        <v>0.45833333333333331</v>
+      </c>
       <c r="K162" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L162" s="5"/>
       <c r="M162" s="5"/>
       <c r="N162" s="16"/>
-      <c r="O162" s="5"/>
-    </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O162" s="7"/>
+      <c r="P162" s="5"/>
+    </row>
+    <row r="163" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A163" s="5">
         <v>3</v>
       </c>
@@ -6929,69 +7146,71 @@
         <v>14</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G163" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H163" s="6">
-        <v>46149</v>
-      </c>
-      <c r="I163" s="9">
-        <v>0.33333333333333331</v>
-      </c>
+        <v>46156</v>
+      </c>
+      <c r="I163" s="5"/>
       <c r="J163" s="9">
-        <v>0.41666666666666669</v>
+        <v>0.625</v>
       </c>
       <c r="K163" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L163" s="5"/>
       <c r="M163" s="5"/>
       <c r="N163" s="16"/>
-      <c r="O163" s="5"/>
-    </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O163" s="7"/>
+      <c r="P163" s="5"/>
+    </row>
+    <row r="164" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A164" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B164" s="5"/>
       <c r="C164" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>189</v>
+        <v>14</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G164" s="5" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="H164" s="6">
-        <v>46155</v>
-      </c>
-      <c r="I164" s="5"/>
+        <v>46163</v>
+      </c>
+      <c r="I164" s="9">
+        <v>0.29166666666666669</v>
+      </c>
       <c r="J164" s="9">
-        <v>0.45833333333333331</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="K164" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L164" s="5"/>
       <c r="M164" s="5"/>
       <c r="N164" s="16"/>
-      <c r="O164" s="5"/>
-    </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O164" s="7"/>
+      <c r="P164" s="5"/>
+    </row>
+    <row r="165" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A165" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B165" s="5"/>
       <c r="C165" s="5" t="s">
@@ -7001,69 +7220,71 @@
         <v>14</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F165" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G165" s="5" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="H165" s="6">
-        <v>46156</v>
+        <v>46164</v>
       </c>
       <c r="I165" s="5"/>
       <c r="J165" s="9">
-        <v>0.625</v>
+        <v>0.375</v>
       </c>
       <c r="K165" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L165" s="5"/>
       <c r="M165" s="5"/>
       <c r="N165" s="16"/>
-      <c r="O165" s="5"/>
-    </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O165" s="7"/>
+      <c r="P165" s="5"/>
+    </row>
+    <row r="166" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A166" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B166" s="5"/>
       <c r="C166" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>14</v>
+        <v>193</v>
       </c>
       <c r="E166" s="5" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G166" s="5" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="H166" s="6">
-        <v>46163</v>
+        <v>46167</v>
       </c>
       <c r="I166" s="9">
-        <v>0.29166666666666669</v>
+        <v>0.22916666666666666</v>
       </c>
       <c r="J166" s="9">
-        <v>0.33333333333333331</v>
+        <v>0.5625</v>
       </c>
       <c r="K166" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L166" s="5"/>
       <c r="M166" s="5"/>
       <c r="N166" s="16"/>
-      <c r="O166" s="5"/>
-    </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O166" s="7"/>
+      <c r="P166" s="5"/>
+    </row>
+    <row r="167" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A167" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B167" s="5"/>
       <c r="C167" s="5" t="s">
@@ -7073,30 +7294,33 @@
         <v>14</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G167" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="H167" s="6">
-        <v>46164</v>
-      </c>
-      <c r="I167" s="5"/>
-      <c r="J167" s="9">
-        <v>0.375</v>
+        <v>315</v>
+      </c>
+      <c r="H167" s="12">
+        <v>46170</v>
+      </c>
+      <c r="I167" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J167" s="13">
+        <v>0.41666666666666669</v>
       </c>
       <c r="K167" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L167" s="5"/>
       <c r="M167" s="5"/>
       <c r="N167" s="16"/>
-      <c r="O167" s="5"/>
-    </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O167" s="7"/>
+      <c r="P167" s="5"/>
+    </row>
+    <row r="168" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A168" s="5">
         <v>3</v>
       </c>
@@ -7105,37 +7329,38 @@
         <v>13</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>194</v>
+        <v>33</v>
       </c>
       <c r="E168" s="5" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G168" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H168" s="6">
-        <v>46167</v>
+        <v>46174</v>
       </c>
       <c r="I168" s="9">
-        <v>0.22916666666666666</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="J168" s="9">
-        <v>0.5625</v>
+        <v>0.72916666666666663</v>
       </c>
       <c r="K168" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L168" s="5"/>
       <c r="M168" s="5"/>
       <c r="N168" s="16"/>
-      <c r="O168" s="5"/>
-    </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O168" s="7"/>
+      <c r="P168" s="5"/>
+    </row>
+    <row r="169" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A169" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B169" s="5"/>
       <c r="C169" s="5" t="s">
@@ -7145,114 +7370,113 @@
         <v>14</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>301</v>
+        <v>200</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>196</v>
+        <v>20</v>
       </c>
       <c r="G169" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="H169" s="12">
-        <v>46170</v>
-      </c>
-      <c r="I169" s="9">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="J169" s="13">
-        <v>0.41666666666666669</v>
+        <v>310</v>
+      </c>
+      <c r="H169" s="6">
+        <v>46204</v>
+      </c>
+      <c r="I169" s="5"/>
+      <c r="J169" s="9">
+        <v>0.875</v>
       </c>
       <c r="K169" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="L169" s="5"/>
-      <c r="M169" s="5"/>
-      <c r="N169" s="16"/>
-      <c r="O169" s="5"/>
-    </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.35">
+        <v>74</v>
+      </c>
+      <c r="L169" s="6">
+        <v>46182</v>
+      </c>
+      <c r="M169" s="6"/>
+      <c r="N169" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="O169" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="P169" s="5"/>
+    </row>
+    <row r="170" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A170" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B170" s="5"/>
       <c r="C170" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>302</v>
+        <v>198</v>
       </c>
       <c r="F170" s="5" t="s">
-        <v>197</v>
+        <v>18</v>
       </c>
       <c r="G170" s="5" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="H170" s="6">
-        <v>46174</v>
-      </c>
-      <c r="I170" s="9">
-        <v>0.64583333333333337</v>
-      </c>
+        <v>46211</v>
+      </c>
+      <c r="I170" s="5"/>
       <c r="J170" s="9">
-        <v>0.72916666666666663</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="K170" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L170" s="5"/>
       <c r="M170" s="5"/>
-      <c r="N170" s="16"/>
-      <c r="O170" s="5"/>
-    </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="N170" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="O170" s="7"/>
+      <c r="P170" s="5"/>
+    </row>
+    <row r="171" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A171" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B171" s="5"/>
       <c r="C171" s="5" t="s">
-        <v>13</v>
+        <v>135</v>
       </c>
       <c r="D171" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E171" s="5" t="s">
-        <v>201</v>
+        <v>307</v>
       </c>
       <c r="F171" s="5" t="s">
-        <v>20</v>
+        <v>136</v>
       </c>
       <c r="G171" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="H171" s="6">
-        <v>46204</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="H171" s="5"/>
       <c r="I171" s="5"/>
-      <c r="J171" s="9">
-        <v>0.875</v>
-      </c>
+      <c r="J171" s="5"/>
       <c r="K171" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="L171" s="6">
-        <v>46182</v>
-      </c>
-      <c r="M171" s="6"/>
-      <c r="N171" s="16" t="s">
-        <v>315</v>
-      </c>
-      <c r="O171" s="5"/>
-    </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.35">
+        <v>305</v>
+      </c>
+      <c r="L171" s="5"/>
+      <c r="M171" s="5"/>
+      <c r="N171" s="16"/>
+      <c r="O171" s="7"/>
+      <c r="P171" s="5"/>
+    </row>
+    <row r="172" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A172" s="5">
         <v>0</v>
       </c>
       <c r="B172" s="5"/>
       <c r="C172" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D172" s="5" t="s">
         <v>14</v>
@@ -7264,57 +7488,67 @@
         <v>137</v>
       </c>
       <c r="G172" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H172" s="5"/>
       <c r="I172" s="5"/>
       <c r="J172" s="5"/>
       <c r="K172" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="L172" s="5"/>
       <c r="M172" s="5"/>
       <c r="N172" s="16"/>
-      <c r="O172" s="5"/>
-    </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O172" s="7"/>
+      <c r="P172" s="5"/>
+    </row>
+    <row r="173" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A173" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B173" s="5"/>
       <c r="C173" s="5" t="s">
-        <v>136</v>
+        <v>13</v>
       </c>
       <c r="D173" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>309</v>
+        <v>197</v>
       </c>
       <c r="F173" s="5" t="s">
-        <v>138</v>
+        <v>15</v>
       </c>
       <c r="G173" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="H173" s="5"/>
+        <v>310</v>
+      </c>
+      <c r="H173" s="6">
+        <v>46210</v>
+      </c>
       <c r="I173" s="5"/>
-      <c r="J173" s="5"/>
+      <c r="J173" s="9">
+        <v>0.625</v>
+      </c>
       <c r="K173" s="5" t="s">
-        <v>306</v>
+        <v>336</v>
       </c>
       <c r="L173" s="5"/>
       <c r="M173" s="5"/>
-      <c r="N173" s="16"/>
-      <c r="O173" s="5"/>
+      <c r="N173" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="O173" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="P173" s="5"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="K2:O173">
+  <conditionalFormatting sqref="K2:P173">
     <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
       <formula>"Programada"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
-      <formula>"Impl. Cancelada"</formula>
+      <formula>"Fallida"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
       <formula>"Listo para embarcar"</formula>

--- a/archivos/BD_Dashboard.xlsx
+++ b/archivos/BD_Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mexscitum-my.sharepoint.com/personal/erik_torres_scitum_com_mx/Documents/Documentos/ETP/GitHub/SCITUM-AMX/archivos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="97" documentId="11_F25DC773A252ABDACC1048E8499F6DC65BDE58F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A698EF4-9D56-4CC2-A7FD-A6F94132B163}"/>
+  <xr:revisionPtr revIDLastSave="99" documentId="11_F25DC773A252ABDACC1048E8499F6DC65BDE58F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BABA32DD-654C-4F64-AC18-58F9BFCE70E9}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2514,7 +2514,9 @@
       <c r="K22" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="L22" s="5"/>
+      <c r="L22" s="6">
+        <v>46209</v>
+      </c>
       <c r="M22" s="5">
         <v>4.0199999999999996</v>
       </c>
@@ -2548,7 +2550,9 @@
       <c r="K23" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="L23" s="5"/>
+      <c r="L23" s="6">
+        <v>46209</v>
+      </c>
       <c r="M23" s="5">
         <v>4.04</v>
       </c>

--- a/archivos/BD_Dashboard.xlsx
+++ b/archivos/BD_Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mexscitum-my.sharepoint.com/personal/erik_torres_scitum_com_mx/Documents/Documentos/ETP/GitHub/SCITUM-AMX/archivos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="99" documentId="11_F25DC773A252ABDACC1048E8499F6DC65BDE58F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BABA32DD-654C-4F64-AC18-58F9BFCE70E9}"/>
+  <xr:revisionPtr revIDLastSave="108" documentId="11_F25DC773A252ABDACC1048E8499F6DC65BDE58F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3FAE336-F271-416C-B033-5C4136E85709}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
     <author>Erik Alejandro Torres Piña</author>
   </authors>
   <commentList>
-    <comment ref="F44" authorId="0" shapeId="0" xr:uid="{AFA6DCEB-C9E5-47FD-BAC8-9E7E5F2DE266}">
+    <comment ref="F44" authorId="0" shapeId="0" xr:uid="{DD02932D-C22A-4603-A978-873DAC5479C0}">
       <text>
         <r>
           <rPr>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1099" uniqueCount="339">
   <si>
     <t>TIER</t>
   </si>
@@ -96,9 +96,6 @@
   </si>
   <si>
     <t>Fecha migración propuesta</t>
-  </si>
-  <si>
-    <t>Hora CDMX</t>
   </si>
   <si>
     <t>Hora local sitio</t>
@@ -1014,15 +1011,6 @@
     <t>Programada</t>
   </si>
   <si>
-    <t>se necesita informar con 48hrs de anticipación para solicitar al aeropuerto el acceso a cuarto de comunicación, compartir nombre del técnico</t>
-  </si>
-  <si>
-    <t>no requiere de permisos especiales solo tienen que anunciarse con la gerente Martha Liliana Gil.</t>
-  </si>
-  <si>
-    <t>No requieren de permisos especiales solo tendrán que anunciarse con Jose Garden</t>
-  </si>
-  <si>
     <t>Stand Alone</t>
   </si>
   <si>
@@ -1032,9 +1020,6 @@
     <t>SI</t>
   </si>
   <si>
-    <t>El envío del equipo se realizó el 09-jun-2026</t>
-  </si>
-  <si>
     <t>El envío del equipo se realizó el 16-jun-2026</t>
   </si>
   <si>
@@ -1050,16 +1035,9 @@
     <t>Se requiere llenar formulario para acceso a IDC. La foto parece ser la misma que la de LAS, por favor confirmar</t>
   </si>
   <si>
-    <t>Dependencia de AMX, no tiene UTM ni enlace de internet. AMX indico que esperaramos para enviar los equipos.
-No se observa si hay Firewall. No se observa disponibilidad en contacto eléctrico. Se solicita nombre, numero de celular, ID del técnico local (ultimos 4 digitos) y copia de identificación oficial.</t>
-  </si>
-  <si>
     <t xml:space="preserve">No se observa disponibilidad de contactos electricos. Rack elevado, no se observa a que altura. </t>
   </si>
   <si>
-    <t>No hay foto. Sin enlace, pendiente la cross</t>
-  </si>
-  <si>
     <t>Monterrey Terminal A (MTY)</t>
   </si>
   <si>
@@ -1091,13 +1069,37 @@
   </si>
   <si>
     <t>Aeroméxico autorizó la instalación temporal de los equipos sobre infraestructura existente de otro proveedor para mantener la ventana de implementación del sitio LAS. Durante la sesión se expusieron los riesgos asociados a esta alternativa y Aeroméxico confirmó la aceptación de dichos riesgos, asumiendo la responsabilidad ante cualquier incidente derivado del movimiento o manipulación de los equipos existentes durante o posterior a la ventana. No se tiene switch, Aeromexico reporta que desconocía esta situación, se conecta un solo equipo ION y no se habilita HA.</t>
+  </si>
+  <si>
+    <t>No hay foto. Tiene enlace SITA</t>
+  </si>
+  <si>
+    <t>En remodelación la oficina. Nombre, numero de telefono, copia de identificación oficial y lista de herramientas</t>
+  </si>
+  <si>
+    <t>AMX solicita sacarlo de la planeación hasta nuevo aviso</t>
+  </si>
+  <si>
+    <t>Al hacer el cambio no paso el rol de activo al ION 02. Se analiza el caso con PS PAN.</t>
+  </si>
+  <si>
+    <t>Aeroméxico buscará sesión con proveedor SITA para realizar analisis y entender como esta configurada la conexión del aeropuerto.</t>
+  </si>
+  <si>
+    <t>El envío del equipo se realizó el 07-jul-2026</t>
+  </si>
+  <si>
+    <t>El envío del equipo se realizó el 03-jul-2026</t>
+  </si>
+  <si>
+    <t>El envío del equipo se realizó el 06-jul-2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1155,6 +1157,13 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Century Gothic"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1209,7 +1218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1258,6 +1267,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1703,7 +1715,7 @@
   <sheetPr>
     <tabColor theme="5" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:P173"/>
+  <dimension ref="A1:O173"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.1796875" bestFit="1" customWidth="1"/>
@@ -1713,10 +1725,11 @@
     <col min="5" max="5" width="11.7265625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="24.81640625" customWidth="1"/>
     <col min="7" max="7" width="17.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1736,7 +1749,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>6</v>
@@ -1757,5797 +1770,5618 @@
         <v>11</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>12</v>
+        <v>325</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" s="5">
         <v>3</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H2" s="6">
         <v>46213</v>
       </c>
-      <c r="I2" s="5"/>
-      <c r="J2" s="9">
+      <c r="I2" s="9">
         <v>0.66666666666666663</v>
       </c>
-      <c r="K2" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="L2" s="6">
+      <c r="J2" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="K2" s="6">
         <v>46189</v>
       </c>
-      <c r="M2" s="5">
+      <c r="L2" s="5">
         <v>1.06</v>
       </c>
-      <c r="N2" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="O2" s="7"/>
-      <c r="P2" s="5"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="5"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" s="5">
         <v>1</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="G3" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="H3" s="6">
+        <v>46218</v>
+      </c>
+      <c r="I3" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J3" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="H3" s="12">
-        <v>46225</v>
-      </c>
-      <c r="I3" s="5"/>
-      <c r="J3" s="13">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="7" t="s">
-        <v>324</v>
-      </c>
-      <c r="O3" s="7"/>
-      <c r="P3" s="5"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="K3" s="5"/>
+      <c r="L3" s="14">
+        <v>2.08</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="N3" s="7"/>
+      <c r="O3" s="5"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>204</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G4" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="H4" s="6">
+        <v>46220</v>
+      </c>
+      <c r="I4" s="9">
+        <v>0.375</v>
+      </c>
+      <c r="J4" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="L4" s="6">
+      <c r="K4" s="6">
         <v>46189</v>
       </c>
-      <c r="M4" s="5">
-        <v>1.01</v>
-      </c>
-      <c r="N4" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="O4" s="7"/>
-      <c r="P4" s="5"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="L4" s="5">
+        <v>1.02</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="N4" s="7"/>
+      <c r="O4" s="5"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="E5" s="5" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="L5" s="6">
-        <v>46189</v>
-      </c>
-      <c r="M5" s="5">
-        <v>1.02</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="O5" s="7"/>
-      <c r="P5" s="5"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+        <v>309</v>
+      </c>
+      <c r="H5" s="12">
+        <v>46225</v>
+      </c>
+      <c r="I5" s="13">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="N5" s="7"/>
+      <c r="O5" s="5"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="L6" s="6">
+      <c r="J6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" s="6">
         <v>46189</v>
       </c>
-      <c r="M6" s="5">
-        <v>1.03</v>
-      </c>
-      <c r="N6" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="O6" s="7"/>
-      <c r="P6" s="5"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="L6" s="5">
+        <v>1.01</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="N6" s="7"/>
+      <c r="O6" s="5"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="E7" s="5" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="H7" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="H7" s="5"/>
       <c r="I7" s="5"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="L7" s="6">
-        <v>46182</v>
-      </c>
-      <c r="M7" s="6"/>
-      <c r="N7" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="O7" s="7"/>
-      <c r="P7" s="5"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="J7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K7" s="6">
+        <v>46189</v>
+      </c>
+      <c r="L7" s="5">
+        <v>1.03</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="N7" s="7"/>
+      <c r="O7" s="5"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>1</v>
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="E8" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="H8" s="1"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="L8" s="6">
+        <v>309</v>
+      </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K8" s="6">
         <v>46182</v>
       </c>
-      <c r="M8" s="6"/>
-      <c r="N8" s="7" t="s">
-        <v>326</v>
-      </c>
-      <c r="O8" s="7"/>
-      <c r="P8" s="5"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="L8" s="6"/>
+      <c r="M8" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="N8" s="7"/>
+      <c r="O8" s="5"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>2</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="E9" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H9" s="2"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="5" t="s">
-        <v>17</v>
-      </c>
+      <c r="I9" s="3"/>
+      <c r="J9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K9" s="5"/>
       <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="O9" s="7"/>
-      <c r="P9" s="5"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M9" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="N9" s="7"/>
+      <c r="O9" s="5"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>1</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D10" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>25</v>
-      </c>
       <c r="G10" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="L10" s="6">
+      <c r="J10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K10" s="6">
         <v>46182</v>
       </c>
-      <c r="M10" s="6"/>
-      <c r="N10" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="O10" s="7"/>
-      <c r="P10" s="5"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="L10" s="6"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="5"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>3</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5">
+      <c r="J11" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5">
         <v>2.02</v>
       </c>
+      <c r="M11" s="7"/>
       <c r="N11" s="7"/>
-      <c r="O11" s="7"/>
-      <c r="P11" s="5"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O11" s="5"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5">
-        <v>2.06</v>
-      </c>
+      <c r="J12" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5">
+        <v>2.09</v>
+      </c>
+      <c r="M12" s="7"/>
       <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
-      <c r="P12" s="5"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O12" s="5"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5" t="s">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>221</v>
+        <v>266</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>58</v>
+        <v>127</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5">
-        <v>2.0699999999999998</v>
-      </c>
+      <c r="J13" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5">
+        <v>4.05</v>
+      </c>
+      <c r="M13" s="7"/>
       <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="5"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O13" s="5"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5" t="s">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>220</v>
+        <v>261</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>56</v>
+        <v>122</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="L14" s="5"/>
-      <c r="M14" s="14">
-        <v>2.08</v>
-      </c>
+      <c r="J14" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5">
+        <v>4.03</v>
+      </c>
+      <c r="M14" s="7"/>
       <c r="N14" s="7"/>
-      <c r="O14" s="7"/>
-      <c r="P14" s="5"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O14" s="5"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5">
-        <v>2.09</v>
+      <c r="J15" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="K15" s="6">
+        <v>46189</v>
+      </c>
+      <c r="L15" s="5">
+        <v>1.04</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>314</v>
       </c>
       <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="5"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O15" s="5"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
         <v>3</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5" t="s">
-        <v>81</v>
+        <v>12</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>267</v>
+        <v>207</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>128</v>
+        <v>33</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="L16" s="5"/>
-      <c r="M16" s="5">
-        <v>4.05</v>
+      <c r="J16" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="K16" s="6">
+        <v>46189</v>
+      </c>
+      <c r="L16" s="5">
+        <v>1.05</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>314</v>
       </c>
       <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="5"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O16" s="5"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5" t="s">
-        <v>81</v>
+        <v>12</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>262</v>
+        <v>218</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>123</v>
+        <v>53</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="L17" s="5"/>
-      <c r="M17" s="5">
-        <v>4.03</v>
+      <c r="J17" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="K17" s="6">
+        <v>46210</v>
+      </c>
+      <c r="L17" s="5">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="M17" s="7" t="s">
+        <v>336</v>
       </c>
       <c r="N17" s="7"/>
-      <c r="O17" s="7"/>
-      <c r="P17" s="5"/>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O17" s="5"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" s="5">
         <v>3</v>
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="L18" s="6">
-        <v>46189</v>
-      </c>
-      <c r="M18" s="5">
-        <v>1.04</v>
-      </c>
-      <c r="N18" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="O18" s="7"/>
-      <c r="P18" s="5"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="J18" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="K18" s="6">
+        <v>46206</v>
+      </c>
+      <c r="L18" s="14">
+        <v>2.1</v>
+      </c>
+      <c r="M18" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="N18" s="7"/>
+      <c r="O18" s="5"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
         <v>3</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5" t="s">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>208</v>
+        <v>259</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>34</v>
+        <v>119</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="L19" s="6">
-        <v>46189</v>
-      </c>
-      <c r="M19" s="5">
-        <v>1.05</v>
-      </c>
-      <c r="N19" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="O19" s="7"/>
-      <c r="P19" s="5"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="J19" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="K19" s="6">
+        <v>46209</v>
+      </c>
+      <c r="L19" s="5">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="M19" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="N19" s="7"/>
+      <c r="O19" s="5"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5" t="s">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>219</v>
+        <v>284</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>54</v>
+        <v>156</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="L20" s="6">
-        <v>46210</v>
-      </c>
-      <c r="M20" s="5">
-        <v>2.0099999999999998</v>
+      <c r="J20" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="K20" s="17">
+        <v>46209</v>
+      </c>
+      <c r="L20" s="5">
+        <v>4.04</v>
+      </c>
+      <c r="M20" s="7" t="s">
+        <v>338</v>
       </c>
       <c r="N20" s="7"/>
-      <c r="O20" s="7"/>
-      <c r="P20" s="5"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O20" s="5"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D21" s="5" t="s">
-        <v>67</v>
-      </c>
       <c r="E21" s="5" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="H21" s="5"/>
+        <v>309</v>
+      </c>
+      <c r="H21" s="8"/>
       <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="L21" s="6">
-        <v>46206</v>
-      </c>
-      <c r="M21" s="14">
-        <v>2.1</v>
+      <c r="J21" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5">
+        <v>3.04</v>
+      </c>
+      <c r="M21" s="7" t="s">
+        <v>305</v>
       </c>
       <c r="N21" s="7"/>
-      <c r="O21" s="7"/>
-      <c r="P21" s="5"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O21" s="5"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
         <v>3</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5" t="s">
-        <v>81</v>
+        <v>12</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>51</v>
+        <v>326</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>260</v>
+        <v>223</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>120</v>
+        <v>62</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="L22" s="6">
-        <v>46209</v>
-      </c>
-      <c r="M22" s="5">
-        <v>4.0199999999999996</v>
-      </c>
+      <c r="J22" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="M22" s="7"/>
       <c r="N22" s="7"/>
-      <c r="O22" s="7"/>
-      <c r="P22" s="5"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O22" s="5"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
         <v>3</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5" t="s">
-        <v>81</v>
+        <v>12</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>285</v>
+        <v>225</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>157</v>
+        <v>65</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
-      <c r="K23" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="L23" s="6">
-        <v>46209</v>
-      </c>
-      <c r="M23" s="5">
-        <v>4.04</v>
-      </c>
+      <c r="J23" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5">
+        <v>2.04</v>
+      </c>
+      <c r="M23" s="7"/>
       <c r="N23" s="7"/>
-      <c r="O23" s="7"/>
-      <c r="P23" s="5"/>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O23" s="5"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
         <v>2</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="H24" s="8"/>
+        <v>309</v>
+      </c>
+      <c r="H24" s="5"/>
       <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
-      <c r="K24" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="L24" s="5"/>
-      <c r="M24" s="5">
-        <v>3.04</v>
-      </c>
-      <c r="N24" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="O24" s="7"/>
-      <c r="P24" s="5"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="J24" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="M24" s="7"/>
+      <c r="N24" s="7"/>
+      <c r="O24" s="5"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>333</v>
+        <v>137</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>224</v>
+        <v>272</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>63</v>
+        <v>138</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
-      <c r="K25" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="L25" s="5"/>
-      <c r="M25" s="5">
-        <v>2.0299999999999998</v>
-      </c>
+      <c r="J25" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5">
+        <v>3.01</v>
+      </c>
+      <c r="M25" s="7"/>
       <c r="N25" s="7"/>
-      <c r="O25" s="7"/>
-      <c r="P25" s="5"/>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O25" s="5"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26" s="5">
         <v>3</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>226</v>
+        <v>280</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>66</v>
+        <v>151</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
-      <c r="J26" s="5"/>
-      <c r="K26" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="L26" s="5"/>
-      <c r="M26" s="5">
-        <v>2.04</v>
-      </c>
+      <c r="J26" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5">
+        <v>3.02</v>
+      </c>
+      <c r="M26" s="7"/>
       <c r="N26" s="7"/>
-      <c r="O26" s="7"/>
-      <c r="P26" s="5"/>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O26" s="5"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D27" s="5" t="s">
-        <v>59</v>
-      </c>
       <c r="E27" s="5" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="H27" s="5"/>
+        <v>311</v>
+      </c>
+      <c r="H27" s="8"/>
       <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="L27" s="5"/>
-      <c r="M27" s="5">
-        <v>2.0499999999999998</v>
+      <c r="J27" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5">
+        <v>3.03</v>
+      </c>
+      <c r="M27" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="N27" s="7"/>
-      <c r="O27" s="7"/>
-      <c r="P27" s="5"/>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O27" s="5"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A28" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D28" s="5" t="s">
-        <v>138</v>
-      </c>
       <c r="E28" s="5" t="s">
-        <v>273</v>
+        <v>211</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>139</v>
+        <v>39</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="H28" s="5"/>
+        <v>311</v>
+      </c>
+      <c r="H28" s="8"/>
       <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
-      <c r="K28" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="L28" s="5"/>
-      <c r="M28" s="5">
-        <v>3.01</v>
+      <c r="J28" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5">
+        <v>4.01</v>
+      </c>
+      <c r="M28" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="N28" s="7"/>
-      <c r="O28" s="7"/>
-      <c r="P28" s="5"/>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O28" s="5"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A29" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>151</v>
+        <v>56</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>281</v>
+        <v>220</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>152</v>
+        <v>57</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="H29" s="5"/>
-      <c r="I29" s="5"/>
-      <c r="J29" s="5"/>
-      <c r="K29" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="L29" s="5"/>
-      <c r="M29" s="5">
-        <v>3.02</v>
+        <v>309</v>
+      </c>
+      <c r="H29" s="6">
+        <v>46223</v>
+      </c>
+      <c r="I29" s="9">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="M29" s="7" t="s">
+        <v>332</v>
       </c>
       <c r="N29" s="7"/>
-      <c r="O29" s="7"/>
-      <c r="P29" s="5"/>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O29" s="5"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A30" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D30" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="E30" s="5" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="H30" s="8"/>
-      <c r="I30" s="5"/>
-      <c r="J30" s="5"/>
-      <c r="K30" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="L30" s="5"/>
-      <c r="M30" s="5">
-        <v>3.03</v>
-      </c>
-      <c r="N30" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="O30" s="7"/>
-      <c r="P30" s="5"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
+        <v>309</v>
+      </c>
+      <c r="H30" s="1"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="K30" s="6">
+        <v>46182</v>
+      </c>
+      <c r="L30" s="6"/>
+      <c r="M30" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="N30" s="7"/>
+      <c r="O30" s="5"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="H31" s="8"/>
+        <v>309</v>
+      </c>
+      <c r="H31" s="5"/>
       <c r="I31" s="5"/>
-      <c r="J31" s="5"/>
-      <c r="K31" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="L31" s="5"/>
-      <c r="M31" s="5">
-        <v>4.01</v>
-      </c>
-      <c r="N31" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="O31" s="7"/>
-      <c r="P31" s="5"/>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="J31" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5">
+        <v>2.06</v>
+      </c>
+      <c r="M31" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="N31" s="7"/>
+      <c r="O31" s="5"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A32" s="5">
         <v>2</v>
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D32" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="E32" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H32" s="8"/>
       <c r="I32" s="5"/>
-      <c r="J32" s="5"/>
-      <c r="K32" s="5" t="s">
-        <v>37</v>
-      </c>
+      <c r="J32" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="K32" s="5"/>
       <c r="L32" s="5"/>
-      <c r="M32" s="5"/>
-      <c r="N32" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="O32" s="7"/>
-      <c r="P32" s="5"/>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M32" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="N32" s="7"/>
+      <c r="O32" s="5"/>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A33" s="5">
         <v>3</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D33" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D33" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="E33" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F33" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="H33" s="8"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="K33" s="5"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="H33" s="8"/>
-      <c r="I33" s="5"/>
-      <c r="J33" s="9"/>
-      <c r="K33" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="L33" s="5"/>
-      <c r="M33" s="5"/>
-      <c r="N33" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="O33" s="7"/>
-      <c r="P33" s="5"/>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="N33" s="7"/>
+      <c r="O33" s="5"/>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A34" s="5">
         <v>1</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D34" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="F34" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E34" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>52</v>
-      </c>
       <c r="G34" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H34" s="8"/>
       <c r="I34" s="5"/>
-      <c r="J34" s="5"/>
-      <c r="K34" s="5" t="s">
-        <v>48</v>
-      </c>
+      <c r="J34" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="K34" s="5"/>
       <c r="L34" s="5"/>
-      <c r="M34" s="5"/>
+      <c r="M34" s="7"/>
       <c r="N34" s="7"/>
-      <c r="O34" s="7"/>
-      <c r="P34" s="5"/>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O34" s="5"/>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A35" s="5">
         <v>1</v>
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
-      <c r="J35" s="5"/>
-      <c r="K35" s="5" t="s">
+      <c r="J35" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="K35" s="5"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="L35" s="5"/>
-      <c r="M35" s="5"/>
-      <c r="N35" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="O35" s="7"/>
-      <c r="P35" s="5"/>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="N35" s="7"/>
+      <c r="O35" s="5"/>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A36" s="5">
         <v>0</v>
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H36" s="5"/>
       <c r="I36" s="5"/>
-      <c r="J36" s="5"/>
-      <c r="K36" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J36" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K36" s="5"/>
       <c r="L36" s="5"/>
-      <c r="M36" s="5"/>
+      <c r="M36" s="7"/>
       <c r="N36" s="7"/>
-      <c r="O36" s="7"/>
-      <c r="P36" s="5" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O36" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A37" s="5">
         <v>1</v>
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H37" s="5"/>
       <c r="I37" s="5"/>
-      <c r="J37" s="5"/>
-      <c r="K37" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J37" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K37" s="5"/>
       <c r="L37" s="5"/>
-      <c r="M37" s="5"/>
-      <c r="N37" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="O37" s="7"/>
-      <c r="P37" s="5" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M37" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="N37" s="7"/>
+      <c r="O37" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A38" s="5">
         <v>2</v>
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H38" s="5"/>
       <c r="I38" s="5"/>
-      <c r="J38" s="5"/>
-      <c r="K38" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J38" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K38" s="5"/>
       <c r="L38" s="5"/>
-      <c r="M38" s="5"/>
-      <c r="N38" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="O38" s="7"/>
-      <c r="P38" s="5" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M38" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="N38" s="7"/>
+      <c r="O38" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A39" s="5">
         <v>0</v>
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="F39" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D39" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="F39" s="5" t="s">
-        <v>70</v>
-      </c>
       <c r="G39" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H39" s="5"/>
       <c r="I39" s="5"/>
-      <c r="J39" s="5"/>
-      <c r="K39" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J39" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K39" s="5"/>
       <c r="L39" s="5"/>
-      <c r="M39" s="5"/>
+      <c r="M39" s="7"/>
       <c r="N39" s="7"/>
-      <c r="O39" s="7"/>
-      <c r="P39" s="5"/>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O39" s="5"/>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A40" s="5">
         <v>0</v>
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
-      <c r="J40" s="5"/>
-      <c r="K40" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J40" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K40" s="5"/>
       <c r="L40" s="5"/>
-      <c r="M40" s="5"/>
+      <c r="M40" s="7"/>
       <c r="N40" s="7"/>
-      <c r="O40" s="7"/>
-      <c r="P40" s="5"/>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O40" s="5"/>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A41" s="5">
         <v>0</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H41" s="5"/>
       <c r="I41" s="5"/>
-      <c r="J41" s="5"/>
-      <c r="K41" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J41" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K41" s="5"/>
       <c r="L41" s="5"/>
-      <c r="M41" s="5"/>
+      <c r="M41" s="7"/>
       <c r="N41" s="7"/>
-      <c r="O41" s="7"/>
-      <c r="P41" s="5" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O41" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A42" s="5">
         <v>0</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H42" s="5"/>
       <c r="I42" s="5"/>
-      <c r="J42" s="5"/>
-      <c r="K42" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J42" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K42" s="5"/>
       <c r="L42" s="5"/>
-      <c r="M42" s="5"/>
+      <c r="M42" s="7"/>
       <c r="N42" s="7"/>
-      <c r="O42" s="7"/>
-      <c r="P42" s="5" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O42" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A43" s="5">
         <v>0</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H43" s="5"/>
       <c r="I43" s="5"/>
-      <c r="J43" s="5"/>
-      <c r="K43" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J43" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K43" s="5"/>
       <c r="L43" s="5"/>
-      <c r="M43" s="5"/>
+      <c r="M43" s="7"/>
       <c r="N43" s="7"/>
-      <c r="O43" s="7"/>
-      <c r="P43" s="5" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O43" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A44" s="10">
         <v>0</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E44" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="F44" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="D44" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="E44" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="F44" s="10" t="s">
-        <v>79</v>
-      </c>
       <c r="G44" s="10" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H44" s="10"/>
       <c r="I44" s="10"/>
-      <c r="J44" s="10"/>
-      <c r="K44" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J44" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K44" s="10"/>
       <c r="L44" s="10"/>
-      <c r="M44" s="10"/>
+      <c r="M44" s="11"/>
       <c r="N44" s="11"/>
-      <c r="O44" s="11"/>
-      <c r="P44" s="10"/>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O44" s="10"/>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A45" s="5">
         <v>0</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H45" s="5"/>
       <c r="I45" s="5"/>
-      <c r="J45" s="5"/>
-      <c r="K45" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J45" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K45" s="5"/>
       <c r="L45" s="5"/>
-      <c r="M45" s="5"/>
+      <c r="M45" s="7"/>
       <c r="N45" s="7"/>
-      <c r="O45" s="7"/>
-      <c r="P45" s="5"/>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O45" s="5"/>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A46" s="5">
         <v>1</v>
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="F46" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="D46" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="F46" s="5" t="s">
-        <v>82</v>
-      </c>
       <c r="G46" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
-      <c r="J46" s="5"/>
-      <c r="K46" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J46" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K46" s="5"/>
       <c r="L46" s="5"/>
-      <c r="M46" s="5"/>
+      <c r="M46" s="7"/>
       <c r="N46" s="7"/>
-      <c r="O46" s="7"/>
-      <c r="P46" s="5"/>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O46" s="5"/>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A47" s="5">
         <v>1</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H47" s="5"/>
       <c r="I47" s="5"/>
-      <c r="J47" s="5"/>
-      <c r="K47" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J47" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K47" s="5"/>
       <c r="L47" s="5"/>
-      <c r="M47" s="5"/>
+      <c r="M47" s="7"/>
       <c r="N47" s="7"/>
-      <c r="O47" s="7"/>
-      <c r="P47" s="5"/>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O47" s="5"/>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A48" s="5">
         <v>1</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H48" s="5"/>
       <c r="I48" s="5"/>
-      <c r="J48" s="5"/>
-      <c r="K48" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J48" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K48" s="5"/>
       <c r="L48" s="5"/>
-      <c r="M48" s="5"/>
+      <c r="M48" s="7"/>
       <c r="N48" s="7"/>
-      <c r="O48" s="7"/>
-      <c r="P48" s="5"/>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O48" s="5"/>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A49" s="5">
         <v>1</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H49" s="5"/>
       <c r="I49" s="5"/>
-      <c r="J49" s="5"/>
-      <c r="K49" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J49" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K49" s="5"/>
       <c r="L49" s="5"/>
-      <c r="M49" s="5"/>
+      <c r="M49" s="7"/>
       <c r="N49" s="7"/>
-      <c r="O49" s="7"/>
-      <c r="P49" s="5"/>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O49" s="5"/>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A50" s="5">
         <v>1</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H50" s="5"/>
       <c r="I50" s="5"/>
-      <c r="J50" s="5"/>
-      <c r="K50" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J50" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K50" s="5"/>
       <c r="L50" s="5"/>
-      <c r="M50" s="5"/>
+      <c r="M50" s="7"/>
       <c r="N50" s="7"/>
-      <c r="O50" s="7"/>
-      <c r="P50" s="5"/>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O50" s="5"/>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A51" s="5">
         <v>1</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H51" s="5"/>
       <c r="I51" s="5"/>
-      <c r="J51" s="5"/>
-      <c r="K51" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J51" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K51" s="5"/>
       <c r="L51" s="5"/>
-      <c r="M51" s="5"/>
+      <c r="M51" s="7"/>
       <c r="N51" s="7"/>
-      <c r="O51" s="7"/>
-      <c r="P51" s="5"/>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O51" s="5"/>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A52" s="5">
         <v>1</v>
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H52" s="5"/>
       <c r="I52" s="5"/>
-      <c r="J52" s="5"/>
-      <c r="K52" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J52" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K52" s="5"/>
       <c r="L52" s="5"/>
-      <c r="M52" s="5"/>
+      <c r="M52" s="7"/>
       <c r="N52" s="7"/>
-      <c r="O52" s="7"/>
-      <c r="P52" s="5" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O52" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A53" s="5">
         <v>1</v>
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H53" s="5"/>
       <c r="I53" s="5"/>
-      <c r="J53" s="5"/>
-      <c r="K53" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J53" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K53" s="5"/>
       <c r="L53" s="5"/>
-      <c r="M53" s="5"/>
+      <c r="M53" s="7"/>
       <c r="N53" s="7"/>
-      <c r="O53" s="7"/>
-      <c r="P53" s="5"/>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O53" s="5"/>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A54" s="5">
         <v>1</v>
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H54" s="5"/>
       <c r="I54" s="5"/>
-      <c r="J54" s="5"/>
-      <c r="K54" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J54" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K54" s="5"/>
       <c r="L54" s="5"/>
-      <c r="M54" s="5"/>
+      <c r="M54" s="7"/>
       <c r="N54" s="7"/>
-      <c r="O54" s="7"/>
-      <c r="P54" s="5"/>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O54" s="5"/>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A55" s="5">
         <v>1</v>
       </c>
       <c r="B55" s="5"/>
       <c r="C55" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H55" s="5"/>
       <c r="I55" s="5"/>
-      <c r="J55" s="5"/>
-      <c r="K55" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J55" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K55" s="5"/>
       <c r="L55" s="5"/>
-      <c r="M55" s="5"/>
+      <c r="M55" s="7"/>
       <c r="N55" s="7"/>
-      <c r="O55" s="7"/>
-      <c r="P55" s="5"/>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O55" s="5"/>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A56" s="5">
         <v>1</v>
       </c>
       <c r="B56" s="5"/>
       <c r="C56" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H56" s="5"/>
       <c r="I56" s="5"/>
-      <c r="J56" s="5"/>
-      <c r="K56" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J56" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K56" s="5"/>
       <c r="L56" s="5"/>
-      <c r="M56" s="5"/>
+      <c r="M56" s="7"/>
       <c r="N56" s="7"/>
-      <c r="O56" s="7"/>
-      <c r="P56" s="5"/>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O56" s="5"/>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A57" s="5">
         <v>1</v>
       </c>
       <c r="B57" s="5"/>
       <c r="C57" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H57" s="5"/>
       <c r="I57" s="5"/>
-      <c r="J57" s="5"/>
-      <c r="K57" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J57" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K57" s="5"/>
       <c r="L57" s="5"/>
-      <c r="M57" s="5"/>
+      <c r="M57" s="7"/>
       <c r="N57" s="7"/>
-      <c r="O57" s="7"/>
-      <c r="P57" s="5" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O57" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A58" s="5">
         <v>1</v>
       </c>
       <c r="B58" s="5"/>
       <c r="C58" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H58" s="5"/>
       <c r="I58" s="5"/>
-      <c r="J58" s="5"/>
-      <c r="K58" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J58" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K58" s="5"/>
       <c r="L58" s="5"/>
-      <c r="M58" s="5"/>
+      <c r="M58" s="7"/>
       <c r="N58" s="7"/>
-      <c r="O58" s="7"/>
-      <c r="P58" s="5"/>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O58" s="5"/>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A59" s="5">
         <v>1</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="F59" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="D59" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E59" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F59" s="5" t="s">
-        <v>93</v>
-      </c>
       <c r="G59" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H59" s="5"/>
       <c r="I59" s="5"/>
-      <c r="J59" s="5"/>
-      <c r="K59" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J59" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K59" s="5"/>
       <c r="L59" s="5"/>
-      <c r="M59" s="5"/>
+      <c r="M59" s="7"/>
       <c r="N59" s="7"/>
-      <c r="O59" s="7"/>
-      <c r="P59" s="5"/>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O59" s="5"/>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A60" s="5">
         <v>1</v>
       </c>
       <c r="B60" s="5"/>
       <c r="C60" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H60" s="5"/>
       <c r="I60" s="5"/>
-      <c r="J60" s="5"/>
-      <c r="K60" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J60" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K60" s="5"/>
       <c r="L60" s="5"/>
-      <c r="M60" s="5"/>
+      <c r="M60" s="7"/>
       <c r="N60" s="7"/>
-      <c r="O60" s="7"/>
-      <c r="P60" s="5" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O60" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A61" s="5">
         <v>1</v>
       </c>
       <c r="B61" s="5"/>
       <c r="C61" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H61" s="5"/>
       <c r="I61" s="5"/>
-      <c r="J61" s="5"/>
-      <c r="K61" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J61" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K61" s="5"/>
       <c r="L61" s="5"/>
-      <c r="M61" s="5"/>
+      <c r="M61" s="7"/>
       <c r="N61" s="7"/>
-      <c r="O61" s="7"/>
-      <c r="P61" s="5" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O61" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A62" s="5">
         <v>1</v>
       </c>
       <c r="B62" s="5"/>
       <c r="C62" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H62" s="5"/>
       <c r="I62" s="5"/>
-      <c r="J62" s="5"/>
-      <c r="K62" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J62" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K62" s="5"/>
       <c r="L62" s="5"/>
-      <c r="M62" s="5"/>
+      <c r="M62" s="7"/>
       <c r="N62" s="7"/>
-      <c r="O62" s="7"/>
-      <c r="P62" s="5"/>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O62" s="5"/>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A63" s="5">
         <v>1</v>
       </c>
       <c r="B63" s="5"/>
       <c r="C63" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H63" s="5"/>
       <c r="I63" s="5"/>
-      <c r="J63" s="5"/>
-      <c r="K63" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J63" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K63" s="5"/>
       <c r="L63" s="5"/>
-      <c r="M63" s="5"/>
+      <c r="M63" s="7"/>
       <c r="N63" s="7"/>
-      <c r="O63" s="7"/>
-      <c r="P63" s="5"/>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O63" s="5"/>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A64" s="5">
         <v>1</v>
       </c>
       <c r="B64" s="5"/>
       <c r="C64" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D64" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="F64" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E64" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="F64" s="5" t="s">
-        <v>52</v>
-      </c>
       <c r="G64" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H64" s="5"/>
       <c r="I64" s="5"/>
-      <c r="J64" s="5"/>
-      <c r="K64" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J64" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K64" s="5"/>
       <c r="L64" s="5"/>
-      <c r="M64" s="5"/>
+      <c r="M64" s="7"/>
       <c r="N64" s="7"/>
-      <c r="O64" s="7"/>
-      <c r="P64" s="5"/>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O64" s="5"/>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A65" s="5">
         <v>1</v>
       </c>
       <c r="B65" s="5"/>
       <c r="C65" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H65" s="5"/>
       <c r="I65" s="5"/>
-      <c r="J65" s="5"/>
-      <c r="K65" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J65" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K65" s="5"/>
       <c r="L65" s="5"/>
-      <c r="M65" s="5"/>
+      <c r="M65" s="7"/>
       <c r="N65" s="7"/>
-      <c r="O65" s="7"/>
-      <c r="P65" s="5" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O65" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A66" s="5">
         <v>1</v>
       </c>
       <c r="B66" s="5"/>
       <c r="C66" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H66" s="5"/>
       <c r="I66" s="5"/>
-      <c r="J66" s="5"/>
-      <c r="K66" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J66" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K66" s="5"/>
       <c r="L66" s="5"/>
-      <c r="M66" s="5"/>
+      <c r="M66" s="7"/>
       <c r="N66" s="7"/>
-      <c r="O66" s="7"/>
-      <c r="P66" s="5"/>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O66" s="5"/>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A67" s="5">
         <v>1</v>
       </c>
       <c r="B67" s="5"/>
       <c r="C67" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H67" s="5"/>
       <c r="I67" s="5"/>
-      <c r="J67" s="5"/>
-      <c r="K67" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J67" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K67" s="5"/>
       <c r="L67" s="5"/>
-      <c r="M67" s="5"/>
+      <c r="M67" s="7"/>
       <c r="N67" s="7"/>
-      <c r="O67" s="7"/>
-      <c r="P67" s="5"/>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O67" s="5"/>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A68" s="5">
         <v>2</v>
       </c>
       <c r="B68" s="5"/>
       <c r="C68" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H68" s="5"/>
       <c r="I68" s="5"/>
-      <c r="J68" s="5"/>
-      <c r="K68" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J68" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K68" s="5"/>
       <c r="L68" s="5"/>
-      <c r="M68" s="5"/>
+      <c r="M68" s="7"/>
       <c r="N68" s="7"/>
-      <c r="O68" s="7"/>
-      <c r="P68" s="5"/>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O68" s="5"/>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A69" s="5">
         <v>2</v>
       </c>
       <c r="B69" s="5"/>
       <c r="C69" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H69" s="5"/>
       <c r="I69" s="5"/>
-      <c r="J69" s="5"/>
-      <c r="K69" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J69" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K69" s="5"/>
       <c r="L69" s="5"/>
-      <c r="M69" s="5"/>
+      <c r="M69" s="7"/>
       <c r="N69" s="7"/>
-      <c r="O69" s="7"/>
-      <c r="P69" s="5" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O69" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A70" s="5">
         <v>2</v>
       </c>
       <c r="B70" s="5"/>
       <c r="C70" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H70" s="5"/>
       <c r="I70" s="5"/>
-      <c r="J70" s="5"/>
-      <c r="K70" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J70" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K70" s="5"/>
       <c r="L70" s="5"/>
-      <c r="M70" s="5"/>
+      <c r="M70" s="7"/>
       <c r="N70" s="7"/>
-      <c r="O70" s="7"/>
-      <c r="P70" s="5" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O70" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A71" s="5">
         <v>2</v>
       </c>
       <c r="B71" s="5"/>
       <c r="C71" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H71" s="5"/>
       <c r="I71" s="5"/>
-      <c r="J71" s="5"/>
-      <c r="K71" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J71" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K71" s="5"/>
       <c r="L71" s="5"/>
-      <c r="M71" s="5"/>
+      <c r="M71" s="7"/>
       <c r="N71" s="7"/>
-      <c r="O71" s="7"/>
-      <c r="P71" s="5" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O71" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A72" s="5">
         <v>2</v>
       </c>
       <c r="B72" s="5"/>
       <c r="C72" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H72" s="5"/>
       <c r="I72" s="5"/>
-      <c r="J72" s="5"/>
-      <c r="K72" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J72" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K72" s="5"/>
       <c r="L72" s="5"/>
-      <c r="M72" s="5"/>
+      <c r="M72" s="7"/>
       <c r="N72" s="7"/>
-      <c r="O72" s="7"/>
-      <c r="P72" s="5"/>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O72" s="5"/>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A73" s="5">
         <v>2</v>
       </c>
       <c r="B73" s="5"/>
       <c r="C73" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H73" s="5"/>
       <c r="I73" s="5"/>
-      <c r="J73" s="5"/>
-      <c r="K73" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J73" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K73" s="5"/>
       <c r="L73" s="5"/>
-      <c r="M73" s="5"/>
+      <c r="M73" s="7"/>
       <c r="N73" s="7"/>
-      <c r="O73" s="7"/>
-      <c r="P73" s="5" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O73" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A74" s="5">
         <v>2</v>
       </c>
       <c r="B74" s="5"/>
       <c r="C74" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H74" s="5"/>
       <c r="I74" s="5"/>
-      <c r="J74" s="5"/>
-      <c r="K74" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J74" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K74" s="5"/>
       <c r="L74" s="5"/>
-      <c r="M74" s="5"/>
+      <c r="M74" s="7"/>
       <c r="N74" s="7"/>
-      <c r="O74" s="7"/>
-      <c r="P74" s="5" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O74" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A75" s="5">
         <v>2</v>
       </c>
       <c r="B75" s="5"/>
       <c r="C75" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H75" s="5"/>
       <c r="I75" s="5"/>
-      <c r="J75" s="5"/>
-      <c r="K75" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J75" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K75" s="5"/>
       <c r="L75" s="5"/>
-      <c r="M75" s="5"/>
+      <c r="M75" s="7"/>
       <c r="N75" s="7"/>
-      <c r="O75" s="7"/>
-      <c r="P75" s="5"/>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O75" s="5"/>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A76" s="5">
         <v>2</v>
       </c>
       <c r="B76" s="5"/>
       <c r="C76" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H76" s="5"/>
       <c r="I76" s="5"/>
-      <c r="J76" s="5"/>
-      <c r="K76" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J76" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K76" s="5"/>
       <c r="L76" s="5"/>
-      <c r="M76" s="5"/>
+      <c r="M76" s="7"/>
       <c r="N76" s="7"/>
-      <c r="O76" s="7"/>
-      <c r="P76" s="5"/>
-    </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O76" s="5"/>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A77" s="5">
         <v>2</v>
       </c>
       <c r="B77" s="5"/>
       <c r="C77" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H77" s="5"/>
       <c r="I77" s="5"/>
-      <c r="J77" s="5"/>
-      <c r="K77" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J77" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K77" s="5"/>
       <c r="L77" s="5"/>
-      <c r="M77" s="5"/>
+      <c r="M77" s="7"/>
       <c r="N77" s="7"/>
-      <c r="O77" s="7"/>
-      <c r="P77" s="5" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O77" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A78" s="5">
         <v>2</v>
       </c>
       <c r="B78" s="5"/>
       <c r="C78" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H78" s="5"/>
       <c r="I78" s="5"/>
-      <c r="J78" s="5"/>
-      <c r="K78" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J78" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K78" s="5"/>
       <c r="L78" s="5"/>
-      <c r="M78" s="5"/>
+      <c r="M78" s="7"/>
       <c r="N78" s="7"/>
-      <c r="O78" s="7"/>
-      <c r="P78" s="5"/>
-    </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O78" s="5"/>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A79" s="5">
         <v>2</v>
       </c>
       <c r="B79" s="5"/>
       <c r="C79" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H79" s="5"/>
       <c r="I79" s="5"/>
-      <c r="J79" s="5"/>
-      <c r="K79" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J79" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K79" s="5"/>
       <c r="L79" s="5"/>
-      <c r="M79" s="5"/>
+      <c r="M79" s="7"/>
       <c r="N79" s="7"/>
-      <c r="O79" s="7"/>
-      <c r="P79" s="5"/>
-    </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O79" s="5"/>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A80" s="5">
         <v>2</v>
       </c>
       <c r="B80" s="5"/>
       <c r="C80" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H80" s="5"/>
       <c r="I80" s="5"/>
-      <c r="J80" s="5"/>
-      <c r="K80" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J80" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K80" s="5"/>
       <c r="L80" s="5"/>
-      <c r="M80" s="5"/>
+      <c r="M80" s="7"/>
       <c r="N80" s="7"/>
-      <c r="O80" s="7"/>
-      <c r="P80" s="5"/>
-    </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O80" s="5"/>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A81" s="5">
         <v>2</v>
       </c>
       <c r="B81" s="5"/>
       <c r="C81" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H81" s="5"/>
       <c r="I81" s="5"/>
-      <c r="J81" s="5"/>
-      <c r="K81" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J81" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K81" s="5"/>
       <c r="L81" s="5"/>
-      <c r="M81" s="5"/>
+      <c r="M81" s="7"/>
       <c r="N81" s="7"/>
-      <c r="O81" s="7"/>
-      <c r="P81" s="5"/>
-    </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O81" s="5"/>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A82" s="5">
         <v>2</v>
       </c>
       <c r="B82" s="5"/>
       <c r="C82" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H82" s="5"/>
       <c r="I82" s="5"/>
-      <c r="J82" s="5"/>
-      <c r="K82" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J82" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K82" s="5"/>
       <c r="L82" s="5"/>
-      <c r="M82" s="5"/>
+      <c r="M82" s="7"/>
       <c r="N82" s="7"/>
-      <c r="O82" s="7"/>
-      <c r="P82" s="5"/>
-    </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O82" s="5"/>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A83" s="5">
         <v>2</v>
       </c>
       <c r="B83" s="5"/>
       <c r="C83" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H83" s="5"/>
       <c r="I83" s="5"/>
-      <c r="J83" s="5"/>
-      <c r="K83" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J83" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K83" s="5"/>
       <c r="L83" s="5"/>
-      <c r="M83" s="5"/>
+      <c r="M83" s="7"/>
       <c r="N83" s="7"/>
-      <c r="O83" s="7"/>
-      <c r="P83" s="5"/>
-    </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O83" s="5"/>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A84" s="5">
         <v>2</v>
       </c>
       <c r="B84" s="5"/>
       <c r="C84" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H84" s="5"/>
       <c r="I84" s="5"/>
-      <c r="J84" s="5"/>
-      <c r="K84" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J84" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K84" s="5"/>
       <c r="L84" s="5"/>
-      <c r="M84" s="5"/>
+      <c r="M84" s="7"/>
       <c r="N84" s="7"/>
-      <c r="O84" s="7"/>
-      <c r="P84" s="5"/>
-    </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O84" s="5"/>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A85" s="5">
         <v>2</v>
       </c>
       <c r="B85" s="5"/>
       <c r="C85" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H85" s="5"/>
       <c r="I85" s="5"/>
-      <c r="J85" s="5"/>
-      <c r="K85" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J85" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K85" s="5"/>
       <c r="L85" s="5"/>
-      <c r="M85" s="5"/>
+      <c r="M85" s="7"/>
       <c r="N85" s="7"/>
-      <c r="O85" s="7"/>
-      <c r="P85" s="5"/>
-    </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O85" s="5"/>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A86" s="5">
         <v>2</v>
       </c>
       <c r="B86" s="5"/>
       <c r="C86" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H86" s="5"/>
       <c r="I86" s="5"/>
-      <c r="J86" s="5"/>
-      <c r="K86" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J86" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K86" s="5"/>
       <c r="L86" s="5"/>
-      <c r="M86" s="5"/>
+      <c r="M86" s="7"/>
       <c r="N86" s="7"/>
-      <c r="O86" s="7"/>
-      <c r="P86" s="5"/>
-    </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O86" s="5"/>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A87" s="5">
         <v>2</v>
       </c>
       <c r="B87" s="5"/>
       <c r="C87" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H87" s="5"/>
       <c r="I87" s="5"/>
-      <c r="J87" s="5"/>
-      <c r="K87" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J87" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K87" s="5"/>
       <c r="L87" s="5"/>
-      <c r="M87" s="5"/>
+      <c r="M87" s="7"/>
       <c r="N87" s="7"/>
-      <c r="O87" s="7"/>
-      <c r="P87" s="5"/>
-    </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O87" s="5"/>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A88" s="5">
         <v>2</v>
       </c>
       <c r="B88" s="5"/>
       <c r="C88" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H88" s="5"/>
       <c r="I88" s="5"/>
-      <c r="J88" s="5"/>
-      <c r="K88" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J88" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K88" s="5"/>
       <c r="L88" s="5"/>
-      <c r="M88" s="5"/>
+      <c r="M88" s="7"/>
       <c r="N88" s="7"/>
-      <c r="O88" s="7"/>
-      <c r="P88" s="5"/>
-    </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O88" s="5"/>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A89" s="5">
         <v>2</v>
       </c>
       <c r="B89" s="5"/>
       <c r="C89" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H89" s="5"/>
       <c r="I89" s="5"/>
-      <c r="J89" s="5"/>
-      <c r="K89" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J89" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K89" s="5"/>
       <c r="L89" s="5"/>
-      <c r="M89" s="5"/>
+      <c r="M89" s="7"/>
       <c r="N89" s="7"/>
-      <c r="O89" s="7"/>
-      <c r="P89" s="5"/>
-    </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O89" s="5"/>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A90" s="5">
         <v>2</v>
       </c>
       <c r="B90" s="5"/>
       <c r="C90" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H90" s="5"/>
       <c r="I90" s="5"/>
-      <c r="J90" s="5"/>
-      <c r="K90" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J90" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K90" s="5"/>
       <c r="L90" s="5"/>
-      <c r="M90" s="5"/>
+      <c r="M90" s="7"/>
       <c r="N90" s="7"/>
-      <c r="O90" s="7"/>
-      <c r="P90" s="5"/>
-    </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O90" s="5"/>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A91" s="5">
         <v>2</v>
       </c>
       <c r="B91" s="5"/>
       <c r="C91" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H91" s="5"/>
       <c r="I91" s="5"/>
-      <c r="J91" s="5"/>
-      <c r="K91" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J91" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K91" s="5"/>
       <c r="L91" s="5"/>
-      <c r="M91" s="5"/>
+      <c r="M91" s="7"/>
       <c r="N91" s="7"/>
-      <c r="O91" s="7"/>
-      <c r="P91" s="5" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O91" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A92" s="5">
         <v>2</v>
       </c>
       <c r="B92" s="5"/>
       <c r="C92" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G92" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H92" s="5"/>
       <c r="I92" s="5"/>
-      <c r="J92" s="5"/>
-      <c r="K92" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J92" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K92" s="5"/>
       <c r="L92" s="5"/>
-      <c r="M92" s="5"/>
+      <c r="M92" s="7"/>
       <c r="N92" s="7"/>
-      <c r="O92" s="7"/>
-      <c r="P92" s="5"/>
-    </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O92" s="5"/>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A93" s="5">
         <v>3</v>
       </c>
       <c r="B93" s="5"/>
       <c r="C93" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H93" s="5"/>
       <c r="I93" s="5"/>
-      <c r="J93" s="5"/>
-      <c r="K93" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J93" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K93" s="5"/>
       <c r="L93" s="5"/>
-      <c r="M93" s="5"/>
+      <c r="M93" s="7"/>
       <c r="N93" s="7"/>
-      <c r="O93" s="7"/>
-      <c r="P93" s="5"/>
-    </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O93" s="5"/>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A94" s="5">
         <v>3</v>
       </c>
       <c r="B94" s="5"/>
       <c r="C94" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H94" s="5"/>
       <c r="I94" s="5"/>
-      <c r="J94" s="5"/>
-      <c r="K94" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J94" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K94" s="5"/>
       <c r="L94" s="5"/>
-      <c r="M94" s="5"/>
+      <c r="M94" s="7"/>
       <c r="N94" s="7"/>
-      <c r="O94" s="7"/>
-      <c r="P94" s="5"/>
-    </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O94" s="5"/>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A95" s="5">
         <v>3</v>
       </c>
       <c r="B95" s="5"/>
       <c r="C95" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H95" s="5"/>
       <c r="I95" s="5"/>
-      <c r="J95" s="5"/>
-      <c r="K95" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J95" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K95" s="5"/>
       <c r="L95" s="5"/>
-      <c r="M95" s="5"/>
+      <c r="M95" s="7"/>
       <c r="N95" s="7"/>
-      <c r="O95" s="7"/>
-      <c r="P95" s="5"/>
-    </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O95" s="5"/>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A96" s="5">
         <v>3</v>
       </c>
       <c r="B96" s="5"/>
       <c r="C96" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H96" s="5"/>
       <c r="I96" s="5"/>
-      <c r="J96" s="5"/>
-      <c r="K96" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J96" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K96" s="5"/>
       <c r="L96" s="5"/>
-      <c r="M96" s="5"/>
+      <c r="M96" s="7"/>
       <c r="N96" s="7"/>
-      <c r="O96" s="7"/>
-      <c r="P96" s="5"/>
-    </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O96" s="5"/>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A97" s="5">
         <v>3</v>
       </c>
       <c r="B97" s="5"/>
       <c r="C97" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H97" s="5"/>
       <c r="I97" s="5"/>
-      <c r="J97" s="5"/>
-      <c r="K97" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J97" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K97" s="5"/>
       <c r="L97" s="5"/>
-      <c r="M97" s="5"/>
+      <c r="M97" s="7"/>
       <c r="N97" s="7"/>
-      <c r="O97" s="7"/>
-      <c r="P97" s="5"/>
-    </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O97" s="5"/>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A98" s="5">
         <v>3</v>
       </c>
       <c r="B98" s="5"/>
       <c r="C98" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H98" s="5"/>
       <c r="I98" s="5"/>
-      <c r="J98" s="5"/>
-      <c r="K98" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J98" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K98" s="5"/>
       <c r="L98" s="5"/>
-      <c r="M98" s="5"/>
+      <c r="M98" s="7"/>
       <c r="N98" s="7"/>
-      <c r="O98" s="7"/>
-      <c r="P98" s="5"/>
-    </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O98" s="5"/>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A99" s="5">
         <v>3</v>
       </c>
       <c r="B99" s="5"/>
       <c r="C99" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H99" s="5"/>
       <c r="I99" s="5"/>
-      <c r="J99" s="5"/>
-      <c r="K99" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J99" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K99" s="5"/>
       <c r="L99" s="5"/>
-      <c r="M99" s="5"/>
+      <c r="M99" s="7"/>
       <c r="N99" s="7"/>
-      <c r="O99" s="7"/>
-      <c r="P99" s="5"/>
-    </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O99" s="5"/>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A100" s="5">
         <v>3</v>
       </c>
       <c r="B100" s="5"/>
       <c r="C100" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H100" s="5"/>
       <c r="I100" s="5"/>
-      <c r="J100" s="5"/>
-      <c r="K100" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J100" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K100" s="5"/>
       <c r="L100" s="5"/>
-      <c r="M100" s="5"/>
+      <c r="M100" s="7"/>
       <c r="N100" s="7"/>
-      <c r="O100" s="7"/>
-      <c r="P100" s="5"/>
-    </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O100" s="5"/>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A101" s="5">
         <v>3</v>
       </c>
       <c r="B101" s="5"/>
       <c r="C101" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H101" s="5"/>
       <c r="I101" s="5"/>
-      <c r="J101" s="5"/>
-      <c r="K101" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J101" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K101" s="5"/>
       <c r="L101" s="5"/>
-      <c r="M101" s="5"/>
+      <c r="M101" s="7"/>
       <c r="N101" s="7"/>
-      <c r="O101" s="7"/>
-      <c r="P101" s="5"/>
-    </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O101" s="5"/>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A102" s="5">
         <v>3</v>
       </c>
       <c r="B102" s="5"/>
       <c r="C102" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H102" s="5"/>
       <c r="I102" s="5"/>
-      <c r="J102" s="5"/>
-      <c r="K102" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J102" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K102" s="5"/>
       <c r="L102" s="5"/>
-      <c r="M102" s="5"/>
+      <c r="M102" s="7"/>
       <c r="N102" s="7"/>
-      <c r="O102" s="7"/>
-      <c r="P102" s="5"/>
-    </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O102" s="5"/>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A103" s="5">
         <v>3</v>
       </c>
       <c r="B103" s="5"/>
       <c r="C103" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H103" s="5"/>
       <c r="I103" s="5"/>
-      <c r="J103" s="5"/>
-      <c r="K103" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J103" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K103" s="5"/>
       <c r="L103" s="5"/>
-      <c r="M103" s="5"/>
+      <c r="M103" s="7"/>
       <c r="N103" s="7"/>
-      <c r="O103" s="7"/>
-      <c r="P103" s="5"/>
-    </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O103" s="5"/>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A104" s="5">
         <v>3</v>
       </c>
       <c r="B104" s="5"/>
       <c r="C104" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H104" s="5"/>
       <c r="I104" s="5"/>
-      <c r="J104" s="5"/>
-      <c r="K104" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J104" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K104" s="5"/>
       <c r="L104" s="5"/>
-      <c r="M104" s="5"/>
+      <c r="M104" s="7"/>
       <c r="N104" s="7"/>
-      <c r="O104" s="7"/>
-      <c r="P104" s="5"/>
-    </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O104" s="5"/>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A105" s="5">
         <v>3</v>
       </c>
       <c r="B105" s="5"/>
       <c r="C105" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H105" s="5"/>
       <c r="I105" s="5"/>
-      <c r="J105" s="5"/>
-      <c r="K105" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J105" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K105" s="5"/>
       <c r="L105" s="5"/>
-      <c r="M105" s="5"/>
+      <c r="M105" s="7"/>
       <c r="N105" s="7"/>
-      <c r="O105" s="7"/>
-      <c r="P105" s="5"/>
-    </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O105" s="5"/>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A106" s="5">
         <v>3</v>
       </c>
       <c r="B106" s="5"/>
       <c r="C106" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H106" s="5"/>
       <c r="I106" s="5"/>
-      <c r="J106" s="5"/>
-      <c r="K106" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J106" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K106" s="5"/>
       <c r="L106" s="5"/>
-      <c r="M106" s="5"/>
+      <c r="M106" s="7"/>
       <c r="N106" s="7"/>
-      <c r="O106" s="7"/>
-      <c r="P106" s="5"/>
-    </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O106" s="5"/>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A107" s="5">
         <v>3</v>
       </c>
       <c r="B107" s="5"/>
       <c r="C107" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H107" s="5"/>
       <c r="I107" s="5"/>
-      <c r="J107" s="5"/>
-      <c r="K107" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J107" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K107" s="5"/>
       <c r="L107" s="5"/>
-      <c r="M107" s="5"/>
+      <c r="M107" s="7"/>
       <c r="N107" s="7"/>
-      <c r="O107" s="7"/>
-      <c r="P107" s="5"/>
-    </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O107" s="5"/>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A108" s="5">
         <v>3</v>
       </c>
       <c r="B108" s="5"/>
       <c r="C108" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G108" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H108" s="5"/>
       <c r="I108" s="5"/>
-      <c r="J108" s="5"/>
-      <c r="K108" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J108" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K108" s="5"/>
       <c r="L108" s="5"/>
-      <c r="M108" s="5"/>
+      <c r="M108" s="7"/>
       <c r="N108" s="7"/>
-      <c r="O108" s="7"/>
-      <c r="P108" s="5"/>
-    </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O108" s="5"/>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A109" s="5">
         <v>3</v>
       </c>
       <c r="B109" s="5"/>
       <c r="C109" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H109" s="5"/>
       <c r="I109" s="5"/>
-      <c r="J109" s="5"/>
-      <c r="K109" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J109" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K109" s="5"/>
       <c r="L109" s="5"/>
-      <c r="M109" s="5"/>
+      <c r="M109" s="7"/>
       <c r="N109" s="7"/>
-      <c r="O109" s="7"/>
-      <c r="P109" s="5"/>
-    </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O109" s="5"/>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A110" s="5">
         <v>3</v>
       </c>
       <c r="B110" s="5"/>
       <c r="C110" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H110" s="5"/>
       <c r="I110" s="5"/>
-      <c r="J110" s="5"/>
-      <c r="K110" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J110" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K110" s="5"/>
       <c r="L110" s="5"/>
-      <c r="M110" s="5"/>
-      <c r="N110" s="16"/>
-      <c r="O110" s="7"/>
-      <c r="P110" s="5"/>
-    </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M110" s="16"/>
+      <c r="N110" s="7"/>
+      <c r="O110" s="5"/>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A111" s="5">
         <v>3</v>
       </c>
       <c r="B111" s="5"/>
       <c r="C111" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G111" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H111" s="5"/>
       <c r="I111" s="5"/>
-      <c r="J111" s="5"/>
-      <c r="K111" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J111" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K111" s="5"/>
       <c r="L111" s="5"/>
-      <c r="M111" s="5"/>
-      <c r="N111" s="16"/>
-      <c r="O111" s="7"/>
-      <c r="P111" s="5"/>
-    </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M111" s="16"/>
+      <c r="N111" s="7"/>
+      <c r="O111" s="5"/>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A112" s="5">
         <v>3</v>
       </c>
       <c r="B112" s="5"/>
       <c r="C112" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G112" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H112" s="5"/>
       <c r="I112" s="5"/>
-      <c r="J112" s="5"/>
-      <c r="K112" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J112" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K112" s="5"/>
       <c r="L112" s="5"/>
-      <c r="M112" s="5"/>
-      <c r="N112" s="16"/>
-      <c r="O112" s="7"/>
-      <c r="P112" s="5"/>
-    </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M112" s="16"/>
+      <c r="N112" s="7"/>
+      <c r="O112" s="5"/>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A113" s="5">
         <v>3</v>
       </c>
       <c r="B113" s="5"/>
       <c r="C113" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G113" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H113" s="5"/>
       <c r="I113" s="5"/>
-      <c r="J113" s="5"/>
-      <c r="K113" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J113" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K113" s="5"/>
       <c r="L113" s="5"/>
-      <c r="M113" s="5"/>
-      <c r="N113" s="16"/>
-      <c r="O113" s="7"/>
-      <c r="P113" s="5"/>
-    </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M113" s="16"/>
+      <c r="N113" s="7"/>
+      <c r="O113" s="5"/>
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A114" s="5">
         <v>3</v>
       </c>
       <c r="B114" s="5"/>
       <c r="C114" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G114" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H114" s="5"/>
       <c r="I114" s="5"/>
-      <c r="J114" s="5"/>
-      <c r="K114" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J114" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K114" s="5"/>
       <c r="L114" s="5"/>
-      <c r="M114" s="5"/>
-      <c r="N114" s="16"/>
-      <c r="O114" s="7"/>
-      <c r="P114" s="5"/>
-    </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M114" s="16"/>
+      <c r="N114" s="7"/>
+      <c r="O114" s="5"/>
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A115" s="5">
         <v>3</v>
       </c>
       <c r="B115" s="5"/>
       <c r="C115" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G115" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H115" s="5"/>
       <c r="I115" s="5"/>
-      <c r="J115" s="5"/>
-      <c r="K115" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J115" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K115" s="5"/>
       <c r="L115" s="5"/>
-      <c r="M115" s="5"/>
-      <c r="N115" s="16"/>
-      <c r="O115" s="7"/>
-      <c r="P115" s="5"/>
-    </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M115" s="16"/>
+      <c r="N115" s="7"/>
+      <c r="O115" s="5"/>
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A116" s="5">
         <v>3</v>
       </c>
       <c r="B116" s="5"/>
       <c r="C116" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G116" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H116" s="5"/>
       <c r="I116" s="5"/>
-      <c r="J116" s="5"/>
-      <c r="K116" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J116" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K116" s="5"/>
       <c r="L116" s="5"/>
-      <c r="M116" s="5"/>
-      <c r="N116" s="16"/>
-      <c r="O116" s="7"/>
-      <c r="P116" s="5"/>
-    </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M116" s="16"/>
+      <c r="N116" s="7"/>
+      <c r="O116" s="5"/>
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A117" s="5">
         <v>3</v>
       </c>
       <c r="B117" s="5"/>
       <c r="C117" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G117" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H117" s="5"/>
       <c r="I117" s="5"/>
-      <c r="J117" s="5"/>
-      <c r="K117" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J117" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K117" s="5"/>
       <c r="L117" s="5"/>
-      <c r="M117" s="5"/>
-      <c r="N117" s="16"/>
-      <c r="O117" s="7"/>
-      <c r="P117" s="5"/>
-    </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M117" s="16"/>
+      <c r="N117" s="7"/>
+      <c r="O117" s="5"/>
+    </row>
+    <row r="118" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A118" s="5">
         <v>3</v>
       </c>
       <c r="B118" s="5"/>
       <c r="C118" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G118" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H118" s="5"/>
       <c r="I118" s="5"/>
-      <c r="J118" s="5"/>
-      <c r="K118" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J118" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K118" s="5"/>
       <c r="L118" s="5"/>
-      <c r="M118" s="5"/>
-      <c r="N118" s="16"/>
-      <c r="O118" s="7"/>
-      <c r="P118" s="5"/>
-    </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M118" s="16"/>
+      <c r="N118" s="7"/>
+      <c r="O118" s="5"/>
+    </row>
+    <row r="119" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A119" s="5">
         <v>3</v>
       </c>
       <c r="B119" s="5"/>
       <c r="C119" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G119" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H119" s="5"/>
       <c r="I119" s="5"/>
-      <c r="J119" s="5"/>
-      <c r="K119" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J119" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K119" s="5"/>
       <c r="L119" s="5"/>
-      <c r="M119" s="5"/>
-      <c r="N119" s="16"/>
-      <c r="O119" s="7"/>
-      <c r="P119" s="5"/>
-    </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M119" s="16"/>
+      <c r="N119" s="7"/>
+      <c r="O119" s="5"/>
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A120" s="5">
         <v>3</v>
       </c>
       <c r="B120" s="5"/>
       <c r="C120" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G120" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H120" s="5"/>
       <c r="I120" s="5"/>
-      <c r="J120" s="5"/>
-      <c r="K120" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J120" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K120" s="5"/>
       <c r="L120" s="5"/>
-      <c r="M120" s="5"/>
-      <c r="N120" s="16"/>
-      <c r="O120" s="7"/>
-      <c r="P120" s="5"/>
-    </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M120" s="16"/>
+      <c r="N120" s="7"/>
+      <c r="O120" s="5"/>
+    </row>
+    <row r="121" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A121" s="5">
         <v>3</v>
       </c>
       <c r="B121" s="5"/>
       <c r="C121" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G121" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H121" s="5"/>
       <c r="I121" s="5"/>
-      <c r="J121" s="5"/>
-      <c r="K121" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J121" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K121" s="5"/>
       <c r="L121" s="5"/>
-      <c r="M121" s="5"/>
-      <c r="N121" s="16"/>
-      <c r="O121" s="7"/>
-      <c r="P121" s="5"/>
-    </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M121" s="16"/>
+      <c r="N121" s="7"/>
+      <c r="O121" s="5"/>
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A122" s="5">
         <v>3</v>
       </c>
       <c r="B122" s="5"/>
       <c r="C122" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G122" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H122" s="5"/>
       <c r="I122" s="5"/>
-      <c r="J122" s="5"/>
-      <c r="K122" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J122" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K122" s="5"/>
       <c r="L122" s="5"/>
-      <c r="M122" s="5"/>
-      <c r="N122" s="16"/>
-      <c r="O122" s="7"/>
-      <c r="P122" s="5"/>
-    </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M122" s="16"/>
+      <c r="N122" s="7"/>
+      <c r="O122" s="5"/>
+    </row>
+    <row r="123" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A123" s="5">
         <v>3</v>
       </c>
       <c r="B123" s="5"/>
       <c r="C123" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H123" s="5"/>
       <c r="I123" s="5"/>
-      <c r="J123" s="5"/>
-      <c r="K123" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J123" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K123" s="5"/>
       <c r="L123" s="5"/>
-      <c r="M123" s="5"/>
-      <c r="N123" s="16"/>
-      <c r="O123" s="7"/>
-      <c r="P123" s="5"/>
-    </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M123" s="16"/>
+      <c r="N123" s="7"/>
+      <c r="O123" s="5"/>
+    </row>
+    <row r="124" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A124" s="5">
         <v>3</v>
       </c>
       <c r="B124" s="5"/>
       <c r="C124" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G124" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H124" s="5"/>
       <c r="I124" s="5"/>
-      <c r="J124" s="5"/>
-      <c r="K124" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J124" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K124" s="5"/>
       <c r="L124" s="5"/>
-      <c r="M124" s="5"/>
-      <c r="N124" s="16"/>
-      <c r="O124" s="7"/>
-      <c r="P124" s="5"/>
-    </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M124" s="16"/>
+      <c r="N124" s="7"/>
+      <c r="O124" s="5"/>
+    </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A125" s="5">
         <v>3</v>
       </c>
       <c r="B125" s="5"/>
       <c r="C125" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G125" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H125" s="5"/>
       <c r="I125" s="5"/>
-      <c r="J125" s="5"/>
-      <c r="K125" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J125" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K125" s="5"/>
       <c r="L125" s="5"/>
-      <c r="M125" s="5"/>
-      <c r="N125" s="16"/>
-      <c r="O125" s="7"/>
-      <c r="P125" s="5"/>
-    </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M125" s="16"/>
+      <c r="N125" s="7"/>
+      <c r="O125" s="5"/>
+    </row>
+    <row r="126" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A126" s="5">
         <v>2</v>
       </c>
       <c r="B126" s="5"/>
       <c r="C126" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D126" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="E126" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="F126" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="E126" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="F126" s="5" t="s">
-        <v>141</v>
-      </c>
       <c r="G126" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H126" s="5"/>
       <c r="I126" s="5"/>
-      <c r="J126" s="5"/>
-      <c r="K126" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J126" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K126" s="5"/>
       <c r="L126" s="5"/>
-      <c r="M126" s="5"/>
-      <c r="N126" s="16"/>
-      <c r="O126" s="7"/>
-      <c r="P126" s="5"/>
-    </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M126" s="16"/>
+      <c r="N126" s="7"/>
+      <c r="O126" s="5"/>
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A127" s="5">
         <v>2</v>
       </c>
       <c r="B127" s="5"/>
       <c r="C127" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D127" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="E127" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="F127" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="E127" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="F127" s="5" t="s">
-        <v>143</v>
-      </c>
       <c r="G127" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H127" s="5"/>
       <c r="I127" s="5"/>
-      <c r="J127" s="5"/>
-      <c r="K127" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J127" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K127" s="5"/>
       <c r="L127" s="5"/>
-      <c r="M127" s="5"/>
-      <c r="N127" s="16"/>
-      <c r="O127" s="7"/>
-      <c r="P127" s="5"/>
-    </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M127" s="16"/>
+      <c r="N127" s="7"/>
+      <c r="O127" s="5"/>
+    </row>
+    <row r="128" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A128" s="5">
         <v>2</v>
       </c>
       <c r="B128" s="5"/>
       <c r="C128" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D128" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="E128" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="F128" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="E128" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="F128" s="5" t="s">
-        <v>145</v>
-      </c>
       <c r="G128" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H128" s="5"/>
       <c r="I128" s="5"/>
-      <c r="J128" s="5"/>
-      <c r="K128" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J128" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K128" s="5"/>
       <c r="L128" s="5"/>
-      <c r="M128" s="5"/>
-      <c r="N128" s="16"/>
-      <c r="O128" s="7"/>
-      <c r="P128" s="5"/>
-    </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M128" s="16"/>
+      <c r="N128" s="7"/>
+      <c r="O128" s="5"/>
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A129" s="5">
         <v>2</v>
       </c>
       <c r="B129" s="5"/>
       <c r="C129" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G129" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H129" s="5"/>
       <c r="I129" s="5"/>
-      <c r="J129" s="5"/>
-      <c r="K129" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J129" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K129" s="5"/>
       <c r="L129" s="5"/>
-      <c r="M129" s="5"/>
-      <c r="N129" s="16"/>
-      <c r="O129" s="7"/>
-      <c r="P129" s="5"/>
-    </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M129" s="16"/>
+      <c r="N129" s="7"/>
+      <c r="O129" s="5"/>
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A130" s="5">
         <v>3</v>
       </c>
       <c r="B130" s="5"/>
       <c r="C130" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D130" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D130" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="E130" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G130" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H130" s="5"/>
       <c r="I130" s="5"/>
-      <c r="J130" s="5"/>
-      <c r="K130" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J130" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K130" s="5"/>
       <c r="L130" s="5"/>
-      <c r="M130" s="5"/>
-      <c r="N130" s="16"/>
-      <c r="O130" s="7"/>
-      <c r="P130" s="5"/>
-    </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M130" s="16"/>
+      <c r="N130" s="7"/>
+      <c r="O130" s="5"/>
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A131" s="5">
         <v>3</v>
       </c>
       <c r="B131" s="5"/>
       <c r="C131" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D131" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D131" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="E131" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G131" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H131" s="5"/>
       <c r="I131" s="5"/>
-      <c r="J131" s="5"/>
-      <c r="K131" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J131" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K131" s="5"/>
       <c r="L131" s="5"/>
-      <c r="M131" s="5"/>
-      <c r="N131" s="16"/>
-      <c r="O131" s="7"/>
-      <c r="P131" s="5"/>
-    </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M131" s="16"/>
+      <c r="N131" s="7"/>
+      <c r="O131" s="5"/>
+    </row>
+    <row r="132" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A132" s="5">
         <v>3</v>
       </c>
       <c r="B132" s="5"/>
       <c r="C132" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D132" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="E132" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="F132" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="E132" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="F132" s="5" t="s">
-        <v>149</v>
-      </c>
       <c r="G132" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H132" s="5"/>
       <c r="I132" s="5"/>
-      <c r="J132" s="5"/>
-      <c r="K132" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J132" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K132" s="5"/>
       <c r="L132" s="5"/>
-      <c r="M132" s="5"/>
-      <c r="N132" s="16"/>
-      <c r="O132" s="7"/>
-      <c r="P132" s="5"/>
-    </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M132" s="16"/>
+      <c r="N132" s="7"/>
+      <c r="O132" s="5"/>
+    </row>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A133" s="5">
         <v>3</v>
       </c>
       <c r="B133" s="5"/>
       <c r="C133" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D133" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D133" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="E133" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G133" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H133" s="5"/>
       <c r="I133" s="5"/>
-      <c r="J133" s="5"/>
-      <c r="K133" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J133" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K133" s="5"/>
       <c r="L133" s="5"/>
-      <c r="M133" s="5"/>
-      <c r="N133" s="16"/>
-      <c r="O133" s="7"/>
-      <c r="P133" s="5"/>
-    </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M133" s="16"/>
+      <c r="N133" s="7"/>
+      <c r="O133" s="5"/>
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A134" s="5">
         <v>3</v>
       </c>
       <c r="B134" s="5"/>
       <c r="C134" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D134" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D134" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="E134" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G134" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H134" s="5"/>
       <c r="I134" s="5"/>
-      <c r="J134" s="5"/>
-      <c r="K134" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J134" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K134" s="5"/>
       <c r="L134" s="5"/>
-      <c r="M134" s="5"/>
-      <c r="N134" s="16"/>
-      <c r="O134" s="7"/>
-      <c r="P134" s="5"/>
-    </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M134" s="16"/>
+      <c r="N134" s="7"/>
+      <c r="O134" s="5"/>
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A135" s="5">
         <v>3</v>
       </c>
       <c r="B135" s="5"/>
       <c r="C135" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D135" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D135" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="E135" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G135" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H135" s="5"/>
       <c r="I135" s="5"/>
-      <c r="J135" s="5"/>
-      <c r="K135" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J135" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K135" s="5"/>
       <c r="L135" s="5"/>
-      <c r="M135" s="5"/>
-      <c r="N135" s="16"/>
-      <c r="O135" s="7"/>
-      <c r="P135" s="5"/>
-    </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M135" s="16"/>
+      <c r="N135" s="7"/>
+      <c r="O135" s="5"/>
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A136" s="5">
         <v>3</v>
       </c>
       <c r="B136" s="5"/>
       <c r="C136" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D136" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="E136" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="F136" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="E136" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="F136" s="5" t="s">
-        <v>156</v>
-      </c>
       <c r="G136" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H136" s="5"/>
       <c r="I136" s="5"/>
-      <c r="J136" s="5"/>
-      <c r="K136" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J136" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K136" s="5"/>
       <c r="L136" s="5"/>
-      <c r="M136" s="5"/>
-      <c r="N136" s="16"/>
-      <c r="O136" s="7"/>
-      <c r="P136" s="5"/>
-    </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M136" s="16"/>
+      <c r="N136" s="7"/>
+      <c r="O136" s="5"/>
+    </row>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A137" s="5">
         <v>3</v>
       </c>
       <c r="B137" s="5"/>
       <c r="C137" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G137" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H137" s="5"/>
       <c r="I137" s="5"/>
-      <c r="J137" s="5"/>
-      <c r="K137" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J137" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K137" s="5"/>
       <c r="L137" s="5"/>
-      <c r="M137" s="5"/>
-      <c r="N137" s="16"/>
-      <c r="O137" s="7"/>
-      <c r="P137" s="5"/>
-    </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M137" s="16"/>
+      <c r="N137" s="7"/>
+      <c r="O137" s="5"/>
+    </row>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A138" s="5">
         <v>3</v>
       </c>
       <c r="B138" s="5"/>
       <c r="C138" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G138" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H138" s="5"/>
       <c r="I138" s="5"/>
-      <c r="J138" s="5"/>
-      <c r="K138" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J138" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K138" s="5"/>
       <c r="L138" s="5"/>
-      <c r="M138" s="5"/>
-      <c r="N138" s="16"/>
-      <c r="O138" s="7"/>
-      <c r="P138" s="5"/>
-    </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M138" s="16"/>
+      <c r="N138" s="7"/>
+      <c r="O138" s="5"/>
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A139" s="5">
         <v>3</v>
       </c>
       <c r="B139" s="5"/>
       <c r="C139" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G139" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H139" s="5"/>
       <c r="I139" s="5"/>
-      <c r="J139" s="5"/>
-      <c r="K139" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J139" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K139" s="5"/>
       <c r="L139" s="5"/>
-      <c r="M139" s="5"/>
-      <c r="N139" s="16"/>
-      <c r="O139" s="7"/>
-      <c r="P139" s="5"/>
-    </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M139" s="16"/>
+      <c r="N139" s="7"/>
+      <c r="O139" s="5"/>
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A140" s="5">
         <v>3</v>
       </c>
       <c r="B140" s="5"/>
       <c r="C140" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F140" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G140" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H140" s="5"/>
       <c r="I140" s="5"/>
-      <c r="J140" s="5"/>
-      <c r="K140" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J140" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K140" s="5"/>
       <c r="L140" s="5"/>
-      <c r="M140" s="5"/>
-      <c r="N140" s="16"/>
-      <c r="O140" s="7"/>
-      <c r="P140" s="5"/>
-    </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M140" s="16"/>
+      <c r="N140" s="7"/>
+      <c r="O140" s="5"/>
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A141" s="5">
         <v>3</v>
       </c>
       <c r="B141" s="5"/>
       <c r="C141" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G141" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H141" s="5"/>
       <c r="I141" s="5"/>
-      <c r="J141" s="5"/>
-      <c r="K141" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J141" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K141" s="5"/>
       <c r="L141" s="5"/>
-      <c r="M141" s="5"/>
-      <c r="N141" s="16"/>
-      <c r="O141" s="7"/>
-      <c r="P141" s="5"/>
-    </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M141" s="16"/>
+      <c r="N141" s="7"/>
+      <c r="O141" s="5"/>
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A142" s="5">
         <v>3</v>
       </c>
       <c r="B142" s="5"/>
       <c r="C142" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G142" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H142" s="5"/>
       <c r="I142" s="5"/>
-      <c r="J142" s="5"/>
-      <c r="K142" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J142" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K142" s="5"/>
       <c r="L142" s="5"/>
-      <c r="M142" s="5"/>
-      <c r="N142" s="16"/>
-      <c r="O142" s="7"/>
-      <c r="P142" s="5"/>
-    </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M142" s="16"/>
+      <c r="N142" s="7"/>
+      <c r="O142" s="5"/>
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A143" s="5">
         <v>3</v>
       </c>
       <c r="B143" s="5"/>
       <c r="C143" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E143" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F143" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G143" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H143" s="5"/>
       <c r="I143" s="5"/>
-      <c r="J143" s="5"/>
-      <c r="K143" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J143" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K143" s="5"/>
       <c r="L143" s="5"/>
-      <c r="M143" s="5"/>
-      <c r="N143" s="16"/>
-      <c r="O143" s="7"/>
-      <c r="P143" s="5"/>
-    </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M143" s="16"/>
+      <c r="N143" s="7"/>
+      <c r="O143" s="5"/>
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A144" s="5">
         <v>3</v>
       </c>
       <c r="B144" s="5"/>
       <c r="C144" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="D144" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E144" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="F144" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="D144" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E144" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="F144" s="5" t="s">
-        <v>166</v>
-      </c>
       <c r="G144" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H144" s="5"/>
       <c r="I144" s="5"/>
-      <c r="J144" s="5"/>
-      <c r="K144" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J144" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K144" s="5"/>
       <c r="L144" s="5"/>
-      <c r="M144" s="5"/>
-      <c r="N144" s="16"/>
-      <c r="O144" s="7"/>
-      <c r="P144" s="5"/>
-    </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M144" s="16"/>
+      <c r="N144" s="7"/>
+      <c r="O144" s="5"/>
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A145" s="5">
         <v>3</v>
       </c>
       <c r="B145" s="5"/>
       <c r="C145" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F145" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G145" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H145" s="5"/>
       <c r="I145" s="5"/>
-      <c r="J145" s="5"/>
-      <c r="K145" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J145" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K145" s="5"/>
       <c r="L145" s="5"/>
-      <c r="M145" s="5"/>
-      <c r="N145" s="16"/>
-      <c r="O145" s="7"/>
-      <c r="P145" s="5"/>
-    </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M145" s="16"/>
+      <c r="N145" s="7"/>
+      <c r="O145" s="5"/>
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A146" s="5">
         <v>3</v>
       </c>
       <c r="B146" s="5"/>
       <c r="C146" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G146" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H146" s="5"/>
       <c r="I146" s="5"/>
-      <c r="J146" s="5"/>
-      <c r="K146" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J146" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K146" s="5"/>
       <c r="L146" s="5"/>
-      <c r="M146" s="5"/>
-      <c r="N146" s="16"/>
-      <c r="O146" s="7"/>
-      <c r="P146" s="5"/>
-    </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M146" s="16"/>
+      <c r="N146" s="7"/>
+      <c r="O146" s="5"/>
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A147" s="5">
         <v>3</v>
       </c>
       <c r="B147" s="5"/>
       <c r="C147" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F147" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G147" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H147" s="5"/>
       <c r="I147" s="5"/>
-      <c r="J147" s="5"/>
-      <c r="K147" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J147" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K147" s="5"/>
       <c r="L147" s="5"/>
-      <c r="M147" s="5"/>
-      <c r="N147" s="16"/>
-      <c r="O147" s="7"/>
-      <c r="P147" s="5"/>
-    </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M147" s="16"/>
+      <c r="N147" s="7"/>
+      <c r="O147" s="5"/>
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A148" s="5">
         <v>3</v>
       </c>
       <c r="B148" s="5"/>
       <c r="C148" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G148" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H148" s="5"/>
       <c r="I148" s="5"/>
-      <c r="J148" s="5"/>
-      <c r="K148" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J148" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K148" s="5"/>
       <c r="L148" s="5"/>
-      <c r="M148" s="5"/>
-      <c r="N148" s="16"/>
-      <c r="O148" s="7"/>
-      <c r="P148" s="5"/>
-    </row>
-    <row r="149" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M148" s="16"/>
+      <c r="N148" s="7"/>
+      <c r="O148" s="5"/>
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A149" s="5">
         <v>3</v>
       </c>
       <c r="B149" s="5"/>
       <c r="C149" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F149" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G149" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H149" s="5"/>
       <c r="I149" s="5"/>
-      <c r="J149" s="5"/>
-      <c r="K149" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J149" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K149" s="5"/>
       <c r="L149" s="5"/>
-      <c r="M149" s="5"/>
-      <c r="N149" s="16"/>
-      <c r="O149" s="7"/>
-      <c r="P149" s="5"/>
-    </row>
-    <row r="150" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M149" s="16"/>
+      <c r="N149" s="7"/>
+      <c r="O149" s="5"/>
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A150" s="5">
         <v>3</v>
       </c>
       <c r="B150" s="5"/>
       <c r="C150" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G150" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H150" s="5"/>
       <c r="I150" s="5"/>
-      <c r="J150" s="5"/>
-      <c r="K150" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J150" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K150" s="5"/>
       <c r="L150" s="5"/>
-      <c r="M150" s="5"/>
-      <c r="N150" s="16"/>
-      <c r="O150" s="7"/>
-      <c r="P150" s="5"/>
-    </row>
-    <row r="151" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M150" s="16"/>
+      <c r="N150" s="7"/>
+      <c r="O150" s="5"/>
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A151" s="5">
         <v>3</v>
       </c>
       <c r="B151" s="5"/>
       <c r="C151" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G151" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H151" s="5"/>
       <c r="I151" s="5"/>
-      <c r="J151" s="5"/>
-      <c r="K151" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="J151" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K151" s="5"/>
       <c r="L151" s="5"/>
-      <c r="M151" s="5"/>
-      <c r="N151" s="16"/>
-      <c r="O151" s="7"/>
-      <c r="P151" s="5"/>
-    </row>
-    <row r="152" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M151" s="16"/>
+      <c r="N151" s="7"/>
+      <c r="O151" s="5"/>
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A152" s="5">
         <v>0</v>
       </c>
       <c r="B152" s="5"/>
       <c r="C152" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G152" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H152" s="6">
         <v>46094</v>
       </c>
-      <c r="I152" s="9">
-        <v>0.41666666666666669</v>
+      <c r="I152" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="J152" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K152" s="5" t="s">
-        <v>74</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="K152" s="5"/>
       <c r="L152" s="5"/>
-      <c r="M152" s="5"/>
-      <c r="N152" s="16"/>
-      <c r="O152" s="7"/>
-      <c r="P152" s="5"/>
-    </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M152" s="16"/>
+      <c r="N152" s="7"/>
+      <c r="O152" s="5"/>
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A153" s="5">
         <v>0</v>
       </c>
       <c r="B153" s="5"/>
       <c r="C153" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G153" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H153" s="6">
         <v>46094</v>
       </c>
-      <c r="I153" s="9">
-        <v>0.41666666666666669</v>
+      <c r="I153" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="J153" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K153" s="5" t="s">
-        <v>74</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="K153" s="5"/>
       <c r="L153" s="5"/>
-      <c r="M153" s="5"/>
-      <c r="N153" s="16"/>
-      <c r="O153" s="7"/>
-      <c r="P153" s="5"/>
-    </row>
-    <row r="154" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M153" s="16"/>
+      <c r="N153" s="7"/>
+      <c r="O153" s="5"/>
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A154" s="5">
         <v>0</v>
       </c>
       <c r="B154" s="5"/>
       <c r="C154" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="D154" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E154" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="D154" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E154" s="5" t="s">
+      <c r="F154" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="F154" s="5" t="s">
-        <v>178</v>
-      </c>
       <c r="G154" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H154" s="6">
         <v>46095</v>
       </c>
-      <c r="I154" s="9">
-        <v>0.625</v>
+      <c r="I154" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="J154" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K154" s="5" t="s">
-        <v>74</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="K154" s="5"/>
       <c r="L154" s="5"/>
-      <c r="M154" s="5"/>
-      <c r="N154" s="16"/>
-      <c r="O154" s="7"/>
-      <c r="P154" s="5"/>
-    </row>
-    <row r="155" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M154" s="16"/>
+      <c r="N154" s="7"/>
+      <c r="O154" s="5"/>
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A155" s="5">
         <v>3</v>
       </c>
       <c r="B155" s="5"/>
       <c r="C155" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D155" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D155" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="E155" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G155" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H155" s="6">
         <v>46128</v>
       </c>
-      <c r="I155" s="9">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="J155" s="5"/>
-      <c r="K155" s="5" t="s">
-        <v>74</v>
-      </c>
+      <c r="I155" s="5"/>
+      <c r="J155" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="K155" s="5"/>
       <c r="L155" s="5"/>
-      <c r="M155" s="5"/>
-      <c r="N155" s="16"/>
-      <c r="O155" s="7"/>
-      <c r="P155" s="5"/>
-    </row>
-    <row r="156" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M155" s="16"/>
+      <c r="N155" s="7"/>
+      <c r="O155" s="5"/>
+    </row>
+    <row r="156" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A156" s="5">
         <v>3</v>
       </c>
       <c r="B156" s="5"/>
       <c r="C156" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D156" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D156" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="E156" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G156" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H156" s="6">
         <v>46139</v>
       </c>
       <c r="I156" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="J156" s="9">
         <v>0.33333333333333331</v>
       </c>
-      <c r="K156" s="5" t="s">
-        <v>74</v>
-      </c>
+      <c r="J156" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="K156" s="5"/>
       <c r="L156" s="5"/>
-      <c r="M156" s="5"/>
-      <c r="N156" s="16"/>
-      <c r="O156" s="7"/>
-      <c r="P156" s="5"/>
-    </row>
-    <row r="157" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M156" s="16"/>
+      <c r="N156" s="7"/>
+      <c r="O156" s="5"/>
+    </row>
+    <row r="157" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A157" s="5">
         <v>3</v>
       </c>
       <c r="B157" s="5"/>
       <c r="C157" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D157" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="E157" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="F157" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="E157" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="F157" s="5" t="s">
-        <v>182</v>
-      </c>
       <c r="G157" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H157" s="6">
         <v>46141</v>
       </c>
       <c r="I157" s="9">
-        <v>0.67361111111111116</v>
-      </c>
-      <c r="J157" s="9">
         <v>0.96527777777777779</v>
       </c>
-      <c r="K157" s="5" t="s">
-        <v>74</v>
-      </c>
+      <c r="J157" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="K157" s="5"/>
       <c r="L157" s="5"/>
-      <c r="M157" s="5"/>
-      <c r="N157" s="16"/>
-      <c r="O157" s="7"/>
-      <c r="P157" s="5"/>
-    </row>
-    <row r="158" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M157" s="16"/>
+      <c r="N157" s="7"/>
+      <c r="O157" s="5"/>
+    </row>
+    <row r="158" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A158" s="5">
         <v>3</v>
       </c>
       <c r="B158" s="5"/>
       <c r="C158" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D158" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D158" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="E158" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G158" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H158" s="6">
         <v>46146</v>
       </c>
       <c r="I158" s="9">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="J158" s="9">
         <v>0.41666666666666669</v>
       </c>
-      <c r="K158" s="5" t="s">
-        <v>74</v>
-      </c>
+      <c r="J158" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="K158" s="5"/>
       <c r="L158" s="5"/>
-      <c r="M158" s="5"/>
-      <c r="N158" s="16"/>
-      <c r="O158" s="7"/>
-      <c r="P158" s="5"/>
-    </row>
-    <row r="159" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M158" s="16"/>
+      <c r="N158" s="7"/>
+      <c r="O158" s="5"/>
+    </row>
+    <row r="159" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A159" s="5">
         <v>3</v>
       </c>
       <c r="B159" s="5"/>
       <c r="C159" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D159" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="E159" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="F159" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="E159" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="F159" s="5" t="s">
-        <v>185</v>
-      </c>
       <c r="G159" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H159" s="6">
         <v>46147</v>
       </c>
       <c r="I159" s="9">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="J159" s="9">
         <v>0.5</v>
       </c>
-      <c r="K159" s="5" t="s">
-        <v>74</v>
-      </c>
+      <c r="J159" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="K159" s="5"/>
       <c r="L159" s="5"/>
-      <c r="M159" s="5"/>
-      <c r="N159" s="16"/>
-      <c r="O159" s="7"/>
-      <c r="P159" s="5"/>
-    </row>
-    <row r="160" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M159" s="16"/>
+      <c r="N159" s="7"/>
+      <c r="O159" s="5"/>
+    </row>
+    <row r="160" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A160" s="5">
         <v>1</v>
       </c>
       <c r="B160" s="5"/>
       <c r="C160" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D160" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D160" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="E160" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G160" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H160" s="6">
         <v>46147</v>
       </c>
-      <c r="I160" s="9">
-        <v>0.625</v>
-      </c>
-      <c r="J160" s="5"/>
-      <c r="K160" s="5" t="s">
-        <v>74</v>
-      </c>
+      <c r="I160" s="5"/>
+      <c r="J160" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="K160" s="5"/>
       <c r="L160" s="5"/>
-      <c r="M160" s="5"/>
-      <c r="N160" s="16"/>
-      <c r="O160" s="7" t="s">
-        <v>334</v>
-      </c>
-      <c r="P160" s="5"/>
-    </row>
-    <row r="161" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M160" s="16"/>
+      <c r="N160" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="O160" s="5"/>
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A161" s="5">
         <v>3</v>
       </c>
       <c r="B161" s="5"/>
       <c r="C161" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D161" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D161" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="E161" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G161" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H161" s="6">
         <v>46149</v>
       </c>
       <c r="I161" s="9">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="J161" s="9">
         <v>0.41666666666666669</v>
       </c>
-      <c r="K161" s="5" t="s">
-        <v>74</v>
-      </c>
+      <c r="J161" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="K161" s="5"/>
       <c r="L161" s="5"/>
-      <c r="M161" s="5"/>
-      <c r="N161" s="16"/>
-      <c r="O161" s="7"/>
-      <c r="P161" s="5"/>
-    </row>
-    <row r="162" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M161" s="16"/>
+      <c r="N161" s="7"/>
+      <c r="O161" s="5"/>
+    </row>
+    <row r="162" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A162" s="5">
         <v>3</v>
       </c>
       <c r="B162" s="5"/>
       <c r="C162" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D162" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="E162" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="F162" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="E162" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="F162" s="5" t="s">
-        <v>189</v>
-      </c>
       <c r="G162" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H162" s="6">
         <v>46155</v>
       </c>
-      <c r="I162" s="5"/>
-      <c r="J162" s="9">
+      <c r="I162" s="9">
         <v>0.45833333333333331</v>
       </c>
-      <c r="K162" s="5" t="s">
-        <v>74</v>
-      </c>
+      <c r="J162" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="K162" s="5"/>
       <c r="L162" s="5"/>
-      <c r="M162" s="5"/>
-      <c r="N162" s="16"/>
-      <c r="O162" s="7"/>
-      <c r="P162" s="5"/>
-    </row>
-    <row r="163" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M162" s="16"/>
+      <c r="N162" s="7"/>
+      <c r="O162" s="5"/>
+    </row>
+    <row r="163" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A163" s="5">
         <v>3</v>
       </c>
       <c r="B163" s="5"/>
       <c r="C163" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D163" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D163" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="E163" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G163" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H163" s="6">
         <v>46156</v>
       </c>
-      <c r="I163" s="5"/>
-      <c r="J163" s="9">
+      <c r="I163" s="9">
         <v>0.625</v>
       </c>
-      <c r="K163" s="5" t="s">
-        <v>74</v>
-      </c>
+      <c r="J163" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="K163" s="5"/>
       <c r="L163" s="5"/>
-      <c r="M163" s="5"/>
-      <c r="N163" s="16"/>
-      <c r="O163" s="7"/>
-      <c r="P163" s="5"/>
-    </row>
-    <row r="164" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M163" s="16"/>
+      <c r="N163" s="7"/>
+      <c r="O163" s="5"/>
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A164" s="5">
         <v>2</v>
       </c>
       <c r="B164" s="5"/>
       <c r="C164" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D164" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D164" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="E164" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G164" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H164" s="6">
         <v>46163</v>
       </c>
       <c r="I164" s="9">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="J164" s="9">
         <v>0.33333333333333331</v>
       </c>
-      <c r="K164" s="5" t="s">
-        <v>74</v>
-      </c>
+      <c r="J164" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="K164" s="5"/>
       <c r="L164" s="5"/>
-      <c r="M164" s="5"/>
-      <c r="N164" s="16"/>
-      <c r="O164" s="7"/>
-      <c r="P164" s="5"/>
-    </row>
-    <row r="165" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M164" s="16"/>
+      <c r="N164" s="7"/>
+      <c r="O164" s="5"/>
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A165" s="5">
         <v>2</v>
       </c>
       <c r="B165" s="5"/>
       <c r="C165" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D165" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D165" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="E165" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F165" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G165" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H165" s="6">
         <v>46164</v>
       </c>
-      <c r="I165" s="5"/>
-      <c r="J165" s="9">
+      <c r="I165" s="9">
         <v>0.375</v>
       </c>
-      <c r="K165" s="5" t="s">
-        <v>74</v>
-      </c>
+      <c r="J165" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="K165" s="5"/>
       <c r="L165" s="5"/>
-      <c r="M165" s="5"/>
-      <c r="N165" s="16"/>
-      <c r="O165" s="7"/>
-      <c r="P165" s="5"/>
-    </row>
-    <row r="166" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M165" s="16"/>
+      <c r="N165" s="7"/>
+      <c r="O165" s="5"/>
+    </row>
+    <row r="166" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A166" s="5">
         <v>3</v>
       </c>
       <c r="B166" s="5"/>
       <c r="C166" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D166" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="E166" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="F166" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="E166" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="F166" s="5" t="s">
-        <v>194</v>
-      </c>
       <c r="G166" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H166" s="6">
         <v>46167</v>
       </c>
       <c r="I166" s="9">
-        <v>0.22916666666666666</v>
-      </c>
-      <c r="J166" s="9">
         <v>0.5625</v>
       </c>
-      <c r="K166" s="5" t="s">
-        <v>74</v>
-      </c>
+      <c r="J166" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="K166" s="5"/>
       <c r="L166" s="5"/>
-      <c r="M166" s="5"/>
-      <c r="N166" s="16"/>
-      <c r="O166" s="7"/>
-      <c r="P166" s="5"/>
-    </row>
-    <row r="167" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M166" s="16"/>
+      <c r="N166" s="7"/>
+      <c r="O166" s="5"/>
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A167" s="5">
         <v>3</v>
       </c>
       <c r="B167" s="5"/>
       <c r="C167" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D167" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D167" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="E167" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G167" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H167" s="12">
         <v>46170</v>
       </c>
-      <c r="I167" s="9">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="J167" s="13">
+      <c r="I167" s="13">
         <v>0.41666666666666669</v>
       </c>
-      <c r="K167" s="5" t="s">
-        <v>74</v>
-      </c>
+      <c r="J167" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="K167" s="5"/>
       <c r="L167" s="5"/>
-      <c r="M167" s="5"/>
-      <c r="N167" s="16"/>
-      <c r="O167" s="7"/>
-      <c r="P167" s="5"/>
-    </row>
-    <row r="168" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M167" s="16"/>
+      <c r="N167" s="7"/>
+      <c r="O167" s="5"/>
+    </row>
+    <row r="168" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A168" s="5">
         <v>3</v>
       </c>
       <c r="B168" s="5"/>
       <c r="C168" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E168" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G168" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H168" s="6">
         <v>46174</v>
       </c>
       <c r="I168" s="9">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="J168" s="9">
         <v>0.72916666666666663</v>
       </c>
-      <c r="K168" s="5" t="s">
-        <v>74</v>
-      </c>
+      <c r="J168" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="K168" s="5"/>
       <c r="L168" s="5"/>
-      <c r="M168" s="5"/>
-      <c r="N168" s="16"/>
-      <c r="O168" s="7"/>
-      <c r="P168" s="5"/>
-    </row>
-    <row r="169" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M168" s="16"/>
+      <c r="N168" s="7"/>
+      <c r="O168" s="5"/>
+    </row>
+    <row r="169" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A169" s="5">
         <v>1</v>
       </c>
       <c r="B169" s="5"/>
       <c r="C169" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D169" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D169" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="E169" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G169" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H169" s="6">
         <v>46204</v>
       </c>
-      <c r="I169" s="5"/>
-      <c r="J169" s="9">
+      <c r="I169" s="9">
         <v>0.875</v>
       </c>
-      <c r="K169" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="L169" s="6">
+      <c r="J169" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="K169" s="6">
         <v>46182</v>
       </c>
-      <c r="M169" s="6"/>
-      <c r="N169" s="16" t="s">
-        <v>314</v>
-      </c>
-      <c r="O169" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="P169" s="5"/>
-    </row>
-    <row r="170" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="L169" s="6"/>
+      <c r="M169" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="N169" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="O169" s="5"/>
+    </row>
+    <row r="170" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A170" s="5">
         <v>1</v>
       </c>
       <c r="B170" s="5"/>
       <c r="C170" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D170" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D170" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="E170" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F170" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G170" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H170" s="6">
         <v>46211</v>
       </c>
-      <c r="I170" s="5"/>
-      <c r="J170" s="9">
+      <c r="I170" s="9">
         <v>0.41666666666666669</v>
       </c>
-      <c r="K170" s="5" t="s">
-        <v>74</v>
-      </c>
+      <c r="J170" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="K170" s="5"/>
       <c r="L170" s="5"/>
-      <c r="M170" s="5"/>
+      <c r="M170" s="7" t="s">
+        <v>334</v>
+      </c>
       <c r="N170" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="O170" s="7"/>
-      <c r="P170" s="5"/>
-    </row>
-    <row r="171" spans="1:16" x14ac:dyDescent="0.35">
+        <v>334</v>
+      </c>
+      <c r="O170" s="5"/>
+    </row>
+    <row r="171" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A171" s="5">
         <v>0</v>
       </c>
       <c r="B171" s="5"/>
       <c r="C171" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D171" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E171" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="F171" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="D171" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E171" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="F171" s="5" t="s">
-        <v>136</v>
-      </c>
       <c r="G171" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H171" s="5"/>
       <c r="I171" s="5"/>
-      <c r="J171" s="5"/>
-      <c r="K171" s="5" t="s">
-        <v>305</v>
-      </c>
+      <c r="J171" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="K171" s="5"/>
       <c r="L171" s="5"/>
-      <c r="M171" s="5"/>
-      <c r="N171" s="16"/>
-      <c r="O171" s="7"/>
-      <c r="P171" s="5"/>
-    </row>
-    <row r="172" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M171" s="16"/>
+      <c r="N171" s="7"/>
+      <c r="O171" s="5"/>
+    </row>
+    <row r="172" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A172" s="5">
         <v>0</v>
       </c>
       <c r="B172" s="5"/>
       <c r="C172" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D172" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F172" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G172" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H172" s="5"/>
       <c r="I172" s="5"/>
-      <c r="J172" s="5"/>
-      <c r="K172" s="5" t="s">
-        <v>305</v>
-      </c>
+      <c r="J172" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="K172" s="5"/>
       <c r="L172" s="5"/>
-      <c r="M172" s="5"/>
-      <c r="N172" s="16"/>
-      <c r="O172" s="7"/>
-      <c r="P172" s="5"/>
-    </row>
-    <row r="173" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M172" s="16"/>
+      <c r="N172" s="7"/>
+      <c r="O172" s="5"/>
+    </row>
+    <row r="173" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A173" s="5">
         <v>2</v>
       </c>
       <c r="B173" s="5"/>
       <c r="C173" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D173" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D173" s="5" t="s">
+      <c r="E173" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="F173" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E173" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="F173" s="5" t="s">
-        <v>15</v>
-      </c>
       <c r="G173" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H173" s="6">
         <v>46210</v>
       </c>
-      <c r="I173" s="5"/>
-      <c r="J173" s="9">
+      <c r="I173" s="9">
         <v>0.625</v>
       </c>
-      <c r="K173" s="5" t="s">
-        <v>336</v>
-      </c>
+      <c r="J173" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="K173" s="5"/>
       <c r="L173" s="5"/>
-      <c r="M173" s="5"/>
+      <c r="M173" s="7" t="s">
+        <v>335</v>
+      </c>
       <c r="N173" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="O173" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="P173" s="5"/>
+        <v>330</v>
+      </c>
+      <c r="O173" s="5"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="K2:P173">
+  <conditionalFormatting sqref="J2:O173">
     <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
       <formula>"Programada"</formula>
     </cfRule>

--- a/archivos/BD_Dashboard.xlsx
+++ b/archivos/BD_Dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mexscitum-my.sharepoint.com/personal/erik_torres_scitum_com_mx/Documents/Documentos/ETP/GitHub/SCITUM-AMX/archivos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="108" documentId="11_F25DC773A252ABDACC1048E8499F6DC65BDE58F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3FAE336-F271-416C-B033-5C4136E85709}"/>
+  <xr:revisionPtr revIDLastSave="116" documentId="11_F25DC773A252ABDACC1048E8499F6DC65BDE58F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F85C021-42F9-45D7-B7C8-53D7DA77AA6A}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inventario SDWAN &amp; FW" sheetId="2" r:id="rId1"/>
@@ -46,7 +46,7 @@
     <author>Erik Alejandro Torres Piña</author>
   </authors>
   <commentList>
-    <comment ref="F44" authorId="0" shapeId="0" xr:uid="{DD02932D-C22A-4603-A978-873DAC5479C0}">
+    <comment ref="F46" authorId="0" shapeId="0" xr:uid="{4E98F78C-2D02-4920-97E6-96F2E3D293F6}">
       <text>
         <r>
           <rPr>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1099" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="341">
   <si>
     <t>TIER</t>
   </si>
@@ -1074,9 +1074,6 @@
     <t>No hay foto. Tiene enlace SITA</t>
   </si>
   <si>
-    <t>En remodelación la oficina. Nombre, numero de telefono, copia de identificación oficial y lista de herramientas</t>
-  </si>
-  <si>
     <t>AMX solicita sacarlo de la planeación hasta nuevo aviso</t>
   </si>
   <si>
@@ -1093,6 +1090,15 @@
   </si>
   <si>
     <t>El envío del equipo se realizó el 06-jul-2026</t>
+  </si>
+  <si>
+    <t>Programada.</t>
+  </si>
+  <si>
+    <t>No se requieren permisos especiales solo compartan nombre del IDC.</t>
+  </si>
+  <si>
+    <t>Nombre, numero de telefono, copia de identificación oficial y lista de herramientas</t>
   </si>
 </sst>
 </file>
@@ -1449,6 +1455,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1716,20 +1726,20 @@
     <tabColor theme="5" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:O173"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="1.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.81640625" customWidth="1"/>
-    <col min="7" max="7" width="17.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.7265625" customWidth="1"/>
+    <col min="1" max="1" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="1.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.85546875" customWidth="1"/>
+    <col min="7" max="7" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1776,126 +1786,124 @@
         <v>312</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H2" s="6">
-        <v>46213</v>
+        <v>46218</v>
       </c>
       <c r="I2" s="9">
-        <v>0.66666666666666663</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="K2" s="6">
-        <v>46189</v>
-      </c>
-      <c r="L2" s="5">
-        <v>1.06</v>
-      </c>
-      <c r="M2" s="7"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="14">
+        <v>2.08</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>331</v>
+      </c>
       <c r="N2" s="7"/>
       <c r="O2" s="5"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="H3" s="6">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="I3" s="9">
-        <v>0.33333333333333331</v>
+        <v>0.375</v>
       </c>
       <c r="J3" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="K3" s="5"/>
-      <c r="L3" s="14">
-        <v>2.08</v>
+      <c r="K3" s="6">
+        <v>46189</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1.02</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="N3" s="7"/>
       <c r="O3" s="5"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="H4" s="6">
-        <v>46220</v>
-      </c>
-      <c r="I4" s="9">
-        <v>0.375</v>
+        <v>309</v>
+      </c>
+      <c r="H4" s="12">
+        <v>46225</v>
+      </c>
+      <c r="I4" s="13">
+        <v>0.41666666666666669</v>
       </c>
       <c r="J4" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="K4" s="6">
-        <v>46189</v>
-      </c>
-      <c r="L4" s="5">
-        <v>1.02</v>
-      </c>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
       <c r="M4" s="7" t="s">
         <v>317</v>
       </c>
       <c r="N4" s="7"/>
       <c r="O4" s="5"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>1</v>
       </c>
@@ -1904,35 +1912,37 @@
         <v>12</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="H5" s="12">
-        <v>46225</v>
-      </c>
-      <c r="I5" s="13">
-        <v>0.41666666666666669</v>
+      <c r="H5" s="6">
+        <v>46218</v>
+      </c>
+      <c r="I5" s="9">
+        <v>0.5</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
+        <v>338</v>
+      </c>
+      <c r="K5" s="6">
+        <v>46182</v>
+      </c>
+      <c r="L5" s="6"/>
       <c r="M5" s="7" t="s">
-        <v>317</v>
+        <v>339</v>
       </c>
       <c r="N5" s="7"/>
       <c r="O5" s="5"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>1</v>
       </c>
@@ -1941,50 +1951,52 @@
         <v>12</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
+      <c r="H6" s="6">
+        <v>46223</v>
+      </c>
+      <c r="I6" s="9">
+        <v>0.79166666666666663</v>
+      </c>
       <c r="J6" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K6" s="6">
-        <v>46189</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="K6" s="5"/>
       <c r="L6" s="5">
-        <v>1.01</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>318</v>
+        <v>340</v>
       </c>
       <c r="N6" s="7"/>
       <c r="O6" s="5"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>309</v>
@@ -1998,83 +2010,85 @@
         <v>46189</v>
       </c>
       <c r="L7" s="5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N7" s="7"/>
       <c r="O7" s="5"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="H8" s="2"/>
-      <c r="I8" s="3"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
       <c r="J8" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K8" s="6">
-        <v>46182</v>
-      </c>
-      <c r="L8" s="6"/>
+        <v>46189</v>
+      </c>
+      <c r="L8" s="5">
+        <v>1.03</v>
+      </c>
       <c r="M8" s="7" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="N8" s="7"/>
       <c r="O8" s="5"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="3"/>
+        <v>311</v>
+      </c>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
       <c r="J9" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="7" t="s">
-        <v>317</v>
-      </c>
+      <c r="L9" s="5">
+        <v>2.02</v>
+      </c>
+      <c r="M9" s="7"/>
       <c r="N9" s="7"/>
       <c r="O9" s="5"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>1</v>
       </c>
@@ -2083,13 +2097,13 @@
         <v>12</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>309</v>
@@ -2099,30 +2113,30 @@
       <c r="J10" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="6">
-        <v>46182</v>
-      </c>
-      <c r="L10" s="6"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5">
+        <v>2.09</v>
+      </c>
       <c r="M10" s="7"/>
       <c r="N10" s="7"/>
       <c r="O10" s="5"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>3</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>224</v>
+        <v>261</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>63</v>
+        <v>122</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>311</v>
@@ -2134,31 +2148,31 @@
       </c>
       <c r="K11" s="5"/>
       <c r="L11" s="5">
-        <v>2.02</v>
+        <v>4.03</v>
       </c>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
       <c r="O11" s="5"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>217</v>
+        <v>266</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>52</v>
+        <v>127</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
@@ -2167,79 +2181,81 @@
       </c>
       <c r="K12" s="5"/>
       <c r="L12" s="5">
-        <v>2.09</v>
+        <v>4.05</v>
       </c>
       <c r="M12" s="7"/>
       <c r="N12" s="7"/>
       <c r="O12" s="5"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>266</v>
+        <v>200</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>127</v>
+        <v>20</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
+        <v>309</v>
+      </c>
+      <c r="H13" s="2"/>
+      <c r="I13" s="3"/>
       <c r="J13" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5">
-        <v>4.05</v>
-      </c>
-      <c r="M13" s="7"/>
+      <c r="K13" s="6">
+        <v>46182</v>
+      </c>
+      <c r="L13" s="6"/>
+      <c r="M13" s="7" t="s">
+        <v>319</v>
+      </c>
       <c r="N13" s="7"/>
       <c r="O13" s="5"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>261</v>
+        <v>209</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>122</v>
+        <v>35</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
+        <v>309</v>
+      </c>
+      <c r="H14" s="2"/>
+      <c r="I14" s="3"/>
       <c r="J14" s="5" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="5"/>
-      <c r="L14" s="5">
-        <v>4.03</v>
-      </c>
-      <c r="M14" s="7"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="7" t="s">
+        <v>317</v>
+      </c>
       <c r="N14" s="7"/>
       <c r="O14" s="5"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>3</v>
       </c>
@@ -2276,7 +2292,7 @@
       <c r="N15" s="7"/>
       <c r="O15" s="5"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>3</v>
       </c>
@@ -2313,7 +2329,7 @@
       <c r="N16" s="7"/>
       <c r="O16" s="5"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>1</v>
       </c>
@@ -2345,12 +2361,12 @@
         <v>2.0099999999999998</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="N17" s="7"/>
       <c r="O17" s="5"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>3</v>
       </c>
@@ -2382,12 +2398,12 @@
         <v>2.1</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="N18" s="7"/>
       <c r="O18" s="5"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>3</v>
       </c>
@@ -2419,12 +2435,12 @@
         <v>4.0199999999999996</v>
       </c>
       <c r="M19" s="7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="N19" s="7"/>
       <c r="O19" s="5"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>3</v>
       </c>
@@ -2456,47 +2472,45 @@
         <v>4.04</v>
       </c>
       <c r="M20" s="7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="N20" s="7"/>
       <c r="O20" s="5"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>13</v>
+        <v>326</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="H21" s="8"/>
+        <v>311</v>
+      </c>
+      <c r="H21" s="5"/>
       <c r="I21" s="5"/>
       <c r="J21" s="5" t="s">
         <v>301</v>
       </c>
       <c r="K21" s="5"/>
       <c r="L21" s="5">
-        <v>3.04</v>
-      </c>
-      <c r="M21" s="7" t="s">
-        <v>305</v>
-      </c>
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="M21" s="7"/>
       <c r="N21" s="7"/>
       <c r="O21" s="5"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>3</v>
       </c>
@@ -2505,13 +2519,13 @@
         <v>12</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>326</v>
+        <v>64</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>311</v>
@@ -2523,31 +2537,31 @@
       </c>
       <c r="K22" s="5"/>
       <c r="L22" s="5">
-        <v>2.0299999999999998</v>
+        <v>2.04</v>
       </c>
       <c r="M22" s="7"/>
       <c r="N22" s="7"/>
       <c r="O22" s="5"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
@@ -2556,28 +2570,28 @@
       </c>
       <c r="K23" s="5"/>
       <c r="L23" s="5">
-        <v>2.04</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="M23" s="7"/>
       <c r="N23" s="7"/>
       <c r="O23" s="5"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>58</v>
+        <v>137</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>221</v>
+        <v>272</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>309</v>
@@ -2589,31 +2603,31 @@
       </c>
       <c r="K24" s="5"/>
       <c r="L24" s="5">
-        <v>2.0499999999999998</v>
+        <v>3.01</v>
       </c>
       <c r="M24" s="7"/>
       <c r="N24" s="7"/>
       <c r="O24" s="5"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
@@ -2622,13 +2636,13 @@
       </c>
       <c r="K25" s="5"/>
       <c r="L25" s="5">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="M25" s="7"/>
       <c r="N25" s="7"/>
       <c r="O25" s="5"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>3</v>
       </c>
@@ -2637,33 +2651,35 @@
         <v>12</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>150</v>
+        <v>13</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>280</v>
+        <v>210</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>151</v>
+        <v>37</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="H26" s="5"/>
+      <c r="H26" s="8"/>
       <c r="I26" s="5"/>
       <c r="J26" s="5" t="s">
         <v>301</v>
       </c>
       <c r="K26" s="5"/>
       <c r="L26" s="5">
-        <v>3.02</v>
-      </c>
-      <c r="M26" s="7"/>
+        <v>3.03</v>
+      </c>
+      <c r="M26" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="N26" s="7"/>
       <c r="O26" s="5"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5" t="s">
@@ -2673,13 +2689,13 @@
         <v>13</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H27" s="8"/>
       <c r="I27" s="5"/>
@@ -2688,15 +2704,15 @@
       </c>
       <c r="K27" s="5"/>
       <c r="L27" s="5">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="M27" s="7" t="s">
-        <v>38</v>
+        <v>305</v>
       </c>
       <c r="N27" s="7"/>
       <c r="O27" s="5"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>3</v>
       </c>
@@ -2731,228 +2747,226 @@
       <c r="N28" s="7"/>
       <c r="O28" s="5"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5" t="s">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="H29" s="6">
-        <v>46223</v>
-      </c>
-      <c r="I29" s="9">
-        <v>0.79166666666666663</v>
-      </c>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
       <c r="J29" s="5" t="s">
-        <v>36</v>
+        <v>301</v>
       </c>
       <c r="K29" s="5"/>
       <c r="L29" s="5">
-        <v>2.0699999999999998</v>
-      </c>
-      <c r="M29" s="7" t="s">
-        <v>332</v>
-      </c>
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="M29" s="7"/>
       <c r="N29" s="7"/>
-      <c r="O29" s="5"/>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O29" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5" t="s">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>201</v>
+        <v>227</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="H30" s="1"/>
-      <c r="I30" s="3"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
       <c r="J30" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="K30" s="6">
-        <v>46182</v>
-      </c>
-      <c r="L30" s="6"/>
-      <c r="M30" s="7" t="s">
-        <v>333</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="K30" s="5"/>
+      <c r="L30" s="5">
+        <v>5.2</v>
+      </c>
+      <c r="M30" s="7"/>
       <c r="N30" s="7"/>
-      <c r="O30" s="5"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O30" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>222</v>
+        <v>268</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>61</v>
+        <v>129</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
       <c r="J31" s="5" t="s">
-        <v>36</v>
+        <v>301</v>
       </c>
       <c r="K31" s="5"/>
       <c r="L31" s="5">
-        <v>2.06</v>
-      </c>
-      <c r="M31" s="7" t="s">
-        <v>333</v>
-      </c>
+        <v>5.3</v>
+      </c>
+      <c r="M31" s="7"/>
       <c r="N31" s="7"/>
       <c r="O31" s="5"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>212</v>
+        <v>271</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>41</v>
+        <v>132</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="H32" s="8"/>
+        <v>311</v>
+      </c>
+      <c r="H32" s="5"/>
       <c r="I32" s="5"/>
       <c r="J32" s="5" t="s">
-        <v>36</v>
+        <v>301</v>
       </c>
       <c r="K32" s="5"/>
-      <c r="L32" s="5"/>
-      <c r="M32" s="7" t="s">
-        <v>42</v>
-      </c>
+      <c r="L32" s="5">
+        <v>5.4</v>
+      </c>
+      <c r="M32" s="16"/>
       <c r="N32" s="7"/>
       <c r="O32" s="5"/>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="H33" s="8"/>
-      <c r="I33" s="9"/>
+        <v>309</v>
+      </c>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
       <c r="J33" s="5" t="s">
-        <v>36</v>
+        <v>301</v>
       </c>
       <c r="K33" s="5"/>
-      <c r="L33" s="5"/>
-      <c r="M33" s="7" t="s">
-        <v>45</v>
-      </c>
+      <c r="L33" s="5">
+        <v>5.5</v>
+      </c>
+      <c r="M33" s="7"/>
       <c r="N33" s="7"/>
       <c r="O33" s="5"/>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>1</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="G34" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="H34" s="8"/>
+      <c r="H34" s="5"/>
       <c r="I34" s="5"/>
       <c r="J34" s="5" t="s">
-        <v>47</v>
+        <v>301</v>
       </c>
       <c r="K34" s="5"/>
-      <c r="L34" s="5"/>
-      <c r="M34" s="7"/>
+      <c r="L34" s="5">
+        <v>5.6</v>
+      </c>
+      <c r="M34" s="7" t="s">
+        <v>48</v>
+      </c>
       <c r="N34" s="7"/>
       <c r="O34" s="5"/>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="G35" s="5" t="s">
         <v>309</v>
@@ -2960,143 +2974,143 @@
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
       <c r="J35" s="5" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="K35" s="5"/>
-      <c r="L35" s="5"/>
+      <c r="L35" s="5">
+        <v>2.06</v>
+      </c>
       <c r="M35" s="7" t="s">
-        <v>48</v>
+        <v>332</v>
       </c>
       <c r="N35" s="7"/>
       <c r="O35" s="5"/>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5" t="s">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>227</v>
+        <v>201</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="G36" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="H36" s="5"/>
-      <c r="I36" s="5"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="3"/>
       <c r="J36" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K36" s="5"/>
-      <c r="L36" s="5"/>
-      <c r="M36" s="7"/>
+        <v>36</v>
+      </c>
+      <c r="K36" s="6">
+        <v>46182</v>
+      </c>
+      <c r="L36" s="6"/>
+      <c r="M36" s="7" t="s">
+        <v>332</v>
+      </c>
       <c r="N36" s="7"/>
-      <c r="O36" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O36" s="5"/>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>234</v>
+        <v>212</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>90</v>
+        <v>41</v>
       </c>
       <c r="G37" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="H37" s="5"/>
+      <c r="H37" s="8"/>
       <c r="I37" s="5"/>
       <c r="J37" s="5" t="s">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="K37" s="5"/>
       <c r="L37" s="5"/>
       <c r="M37" s="7" t="s">
-        <v>315</v>
+        <v>42</v>
       </c>
       <c r="N37" s="7"/>
-      <c r="O37" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O37" s="5"/>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>108</v>
+        <v>44</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
+        <v>311</v>
+      </c>
+      <c r="H38" s="8"/>
+      <c r="I38" s="9"/>
       <c r="J38" s="5" t="s">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="K38" s="5"/>
       <c r="L38" s="5"/>
       <c r="M38" s="7" t="s">
-        <v>316</v>
+        <v>45</v>
       </c>
       <c r="N38" s="7"/>
-      <c r="O38" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O38" s="5"/>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="G39" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="H39" s="5"/>
+      <c r="H39" s="8"/>
       <c r="I39" s="5"/>
       <c r="J39" s="5" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="K39" s="5"/>
       <c r="L39" s="5"/>
@@ -3104,7 +3118,7 @@
       <c r="N39" s="7"/>
       <c r="O39" s="5"/>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>0</v>
       </c>
@@ -3119,7 +3133,7 @@
         <v>227</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G40" s="5" t="s">
         <v>309</v>
@@ -3133,24 +3147,26 @@
       <c r="L40" s="5"/>
       <c r="M40" s="7"/>
       <c r="N40" s="7"/>
-      <c r="O40" s="5"/>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O40" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="G41" s="5" t="s">
         <v>309</v>
@@ -3162,19 +3178,21 @@
       </c>
       <c r="K41" s="5"/>
       <c r="L41" s="5"/>
-      <c r="M41" s="7"/>
+      <c r="M41" s="7" t="s">
+        <v>315</v>
+      </c>
       <c r="N41" s="7"/>
       <c r="O41" s="5" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>50</v>
@@ -3183,7 +3201,7 @@
         <v>227</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="G42" s="5" t="s">
         <v>309</v>
@@ -3195,13 +3213,15 @@
       </c>
       <c r="K42" s="5"/>
       <c r="L42" s="5"/>
-      <c r="M42" s="7"/>
+      <c r="M42" s="7" t="s">
+        <v>316</v>
+      </c>
       <c r="N42" s="7"/>
       <c r="O42" s="5" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <v>0</v>
       </c>
@@ -3216,7 +3236,7 @@
         <v>227</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="G43" s="5" t="s">
         <v>309</v>
@@ -3230,42 +3250,40 @@
       <c r="L43" s="5"/>
       <c r="M43" s="7"/>
       <c r="N43" s="7"/>
-      <c r="O43" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A44" s="10">
+      <c r="O43" s="5"/>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A44" s="5">
         <v>0</v>
       </c>
       <c r="B44" s="5"/>
-      <c r="C44" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="D44" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="E44" s="10" t="s">
+      <c r="C44" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E44" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="F44" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="G44" s="10" t="s">
-        <v>309</v>
-      </c>
-      <c r="H44" s="10"/>
-      <c r="I44" s="10"/>
+      <c r="F44" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="H44" s="5"/>
+      <c r="I44" s="5"/>
       <c r="J44" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="K44" s="10"/>
-      <c r="L44" s="10"/>
-      <c r="M44" s="11"/>
-      <c r="N44" s="11"/>
-      <c r="O44" s="10"/>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="K44" s="5"/>
+      <c r="L44" s="5"/>
+      <c r="M44" s="7"/>
+      <c r="N44" s="7"/>
+      <c r="O44" s="5"/>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
         <v>0</v>
       </c>
@@ -3280,7 +3298,7 @@
         <v>227</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G45" s="5" t="s">
         <v>309</v>
@@ -3294,46 +3312,48 @@
       <c r="L45" s="5"/>
       <c r="M45" s="7"/>
       <c r="N45" s="7"/>
-      <c r="O45" s="5"/>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A46" s="5">
-        <v>1</v>
+      <c r="O45" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A46" s="10">
+        <v>0</v>
       </c>
       <c r="B46" s="5"/>
-      <c r="C46" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E46" s="5" t="s">
+      <c r="C46" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E46" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="F46" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="G46" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="H46" s="5"/>
-      <c r="I46" s="5"/>
+      <c r="F46" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="G46" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="H46" s="10"/>
+      <c r="I46" s="10"/>
       <c r="J46" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="K46" s="5"/>
-      <c r="L46" s="5"/>
-      <c r="M46" s="7"/>
-      <c r="N46" s="7"/>
-      <c r="O46" s="5"/>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="K46" s="10"/>
+      <c r="L46" s="10"/>
+      <c r="M46" s="11"/>
+      <c r="N46" s="11"/>
+      <c r="O46" s="10"/>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>50</v>
@@ -3342,7 +3362,7 @@
         <v>227</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G47" s="5" t="s">
         <v>309</v>
@@ -3358,22 +3378,22 @@
       <c r="N47" s="7"/>
       <c r="O47" s="5"/>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
         <v>1</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G48" s="5" t="s">
         <v>309</v>
@@ -3389,22 +3409,22 @@
       <c r="N48" s="7"/>
       <c r="O48" s="5"/>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
         <v>1</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G49" s="5" t="s">
         <v>309</v>
@@ -3420,7 +3440,7 @@
       <c r="N49" s="7"/>
       <c r="O49" s="5"/>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
         <v>1</v>
       </c>
@@ -3432,10 +3452,10 @@
         <v>50</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G50" s="5" t="s">
         <v>309</v>
@@ -3451,7 +3471,7 @@
       <c r="N50" s="7"/>
       <c r="O50" s="5"/>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
         <v>1</v>
       </c>
@@ -3463,10 +3483,10 @@
         <v>50</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G51" s="5" t="s">
         <v>309</v>
@@ -3482,7 +3502,7 @@
       <c r="N51" s="7"/>
       <c r="O51" s="5"/>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
         <v>1</v>
       </c>
@@ -3494,10 +3514,10 @@
         <v>50</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G52" s="5" t="s">
         <v>309</v>
@@ -3511,11 +3531,9 @@
       <c r="L52" s="5"/>
       <c r="M52" s="7"/>
       <c r="N52" s="7"/>
-      <c r="O52" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O52" s="5"/>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
         <v>1</v>
       </c>
@@ -3527,10 +3545,10 @@
         <v>50</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G53" s="5" t="s">
         <v>309</v>
@@ -3544,15 +3562,17 @@
       <c r="L53" s="5"/>
       <c r="M53" s="7"/>
       <c r="N53" s="7"/>
-      <c r="O53" s="5"/>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O53" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
         <v>1</v>
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>50</v>
@@ -3577,22 +3597,22 @@
       <c r="N54" s="7"/>
       <c r="O54" s="5"/>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
         <v>1</v>
       </c>
       <c r="B55" s="5"/>
       <c r="C55" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G55" s="5" t="s">
         <v>309</v>
@@ -3608,22 +3628,22 @@
       <c r="N55" s="7"/>
       <c r="O55" s="5"/>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
         <v>1</v>
       </c>
       <c r="B56" s="5"/>
       <c r="C56" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D56" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G56" s="5" t="s">
         <v>309</v>
@@ -3639,22 +3659,22 @@
       <c r="N56" s="7"/>
       <c r="O56" s="5"/>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
         <v>1</v>
       </c>
       <c r="B57" s="5"/>
       <c r="C57" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>320</v>
+        <v>90</v>
       </c>
       <c r="G57" s="5" t="s">
         <v>309</v>
@@ -3668,26 +3688,24 @@
       <c r="L57" s="5"/>
       <c r="M57" s="7"/>
       <c r="N57" s="7"/>
-      <c r="O57" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O57" s="5"/>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
         <v>1</v>
       </c>
       <c r="B58" s="5"/>
       <c r="C58" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D58" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>323</v>
+        <v>235</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G58" s="5" t="s">
         <v>309</v>
@@ -3701,24 +3719,26 @@
       <c r="L58" s="5"/>
       <c r="M58" s="7"/>
       <c r="N58" s="7"/>
-      <c r="O58" s="5"/>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O58" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
         <v>1</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5" t="s">
-        <v>91</v>
+        <v>49</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>236</v>
+        <v>323</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>92</v>
+        <v>321</v>
       </c>
       <c r="G59" s="5" t="s">
         <v>309</v>
@@ -3734,22 +3754,22 @@
       <c r="N59" s="7"/>
       <c r="O59" s="5"/>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
         <v>1</v>
       </c>
       <c r="B60" s="5"/>
       <c r="C60" s="5" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G60" s="5" t="s">
         <v>309</v>
@@ -3763,11 +3783,9 @@
       <c r="L60" s="5"/>
       <c r="M60" s="7"/>
       <c r="N60" s="7"/>
-      <c r="O60" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O60" s="5"/>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="5">
         <v>1</v>
       </c>
@@ -3779,10 +3797,10 @@
         <v>50</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G61" s="5" t="s">
         <v>309</v>
@@ -3800,22 +3818,22 @@
         <v>313</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
         <v>1</v>
       </c>
       <c r="B62" s="5"/>
       <c r="C62" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G62" s="5" t="s">
         <v>309</v>
@@ -3829,24 +3847,26 @@
       <c r="L62" s="5"/>
       <c r="M62" s="7"/>
       <c r="N62" s="7"/>
-      <c r="O62" s="5"/>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O62" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="5">
         <v>1</v>
       </c>
       <c r="B63" s="5"/>
       <c r="C63" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G63" s="5" t="s">
         <v>309</v>
@@ -3862,7 +3882,7 @@
       <c r="N63" s="7"/>
       <c r="O63" s="5"/>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
         <v>1</v>
       </c>
@@ -3874,10 +3894,10 @@
         <v>50</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="G64" s="5" t="s">
         <v>309</v>
@@ -3893,7 +3913,7 @@
       <c r="N64" s="7"/>
       <c r="O64" s="5"/>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="5">
         <v>1</v>
       </c>
@@ -3905,10 +3925,10 @@
         <v>50</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>97</v>
+        <v>51</v>
       </c>
       <c r="G65" s="5" t="s">
         <v>309</v>
@@ -3922,11 +3942,9 @@
       <c r="L65" s="5"/>
       <c r="M65" s="7"/>
       <c r="N65" s="7"/>
-      <c r="O65" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O65" s="5"/>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="5">
         <v>1</v>
       </c>
@@ -3938,10 +3956,10 @@
         <v>50</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G66" s="5" t="s">
         <v>309</v>
@@ -3955,9 +3973,11 @@
       <c r="L66" s="5"/>
       <c r="M66" s="7"/>
       <c r="N66" s="7"/>
-      <c r="O66" s="5"/>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O66" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="5">
         <v>1</v>
       </c>
@@ -3969,10 +3989,10 @@
         <v>50</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G67" s="5" t="s">
         <v>309</v>
@@ -3988,9 +4008,9 @@
       <c r="N67" s="7"/>
       <c r="O67" s="5"/>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B68" s="5"/>
       <c r="C68" s="5" t="s">
@@ -4000,10 +4020,10 @@
         <v>50</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G68" s="5" t="s">
         <v>309</v>
@@ -4019,7 +4039,7 @@
       <c r="N68" s="7"/>
       <c r="O68" s="5"/>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="5">
         <v>2</v>
       </c>
@@ -4031,10 +4051,10 @@
         <v>50</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G69" s="5" t="s">
         <v>309</v>
@@ -4048,11 +4068,9 @@
       <c r="L69" s="5"/>
       <c r="M69" s="7"/>
       <c r="N69" s="7"/>
-      <c r="O69" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O69" s="5"/>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
         <v>2</v>
       </c>
@@ -4064,10 +4082,10 @@
         <v>50</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G70" s="5" t="s">
         <v>309</v>
@@ -4085,7 +4103,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="5">
         <v>2</v>
       </c>
@@ -4097,10 +4115,10 @@
         <v>50</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G71" s="5" t="s">
         <v>309</v>
@@ -4118,7 +4136,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="5">
         <v>2</v>
       </c>
@@ -4130,10 +4148,10 @@
         <v>50</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G72" s="5" t="s">
         <v>309</v>
@@ -4147,9 +4165,11 @@
       <c r="L72" s="5"/>
       <c r="M72" s="7"/>
       <c r="N72" s="7"/>
-      <c r="O72" s="5"/>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O72" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="5">
         <v>2</v>
       </c>
@@ -4161,10 +4181,10 @@
         <v>50</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G73" s="5" t="s">
         <v>309</v>
@@ -4178,11 +4198,9 @@
       <c r="L73" s="5"/>
       <c r="M73" s="7"/>
       <c r="N73" s="7"/>
-      <c r="O73" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O73" s="5"/>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="5">
         <v>2</v>
       </c>
@@ -4194,10 +4212,10 @@
         <v>50</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G74" s="5" t="s">
         <v>309</v>
@@ -4215,22 +4233,22 @@
         <v>313</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="5">
         <v>2</v>
       </c>
       <c r="B75" s="5"/>
       <c r="C75" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D75" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="G75" s="5" t="s">
         <v>309</v>
@@ -4244,9 +4262,11 @@
       <c r="L75" s="5"/>
       <c r="M75" s="7"/>
       <c r="N75" s="7"/>
-      <c r="O75" s="5"/>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O75" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
         <v>2</v>
       </c>
@@ -4258,10 +4278,10 @@
         <v>50</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G76" s="5" t="s">
         <v>309</v>
@@ -4277,22 +4297,22 @@
       <c r="N76" s="7"/>
       <c r="O76" s="5"/>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="5">
         <v>2</v>
       </c>
       <c r="B77" s="5"/>
       <c r="C77" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D77" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="G77" s="5" t="s">
         <v>309</v>
@@ -4306,11 +4326,9 @@
       <c r="L77" s="5"/>
       <c r="M77" s="7"/>
       <c r="N77" s="7"/>
-      <c r="O77" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O77" s="5"/>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="5">
         <v>2</v>
       </c>
@@ -4322,10 +4340,10 @@
         <v>50</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>324</v>
+        <v>227</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>322</v>
+        <v>107</v>
       </c>
       <c r="G78" s="5" t="s">
         <v>309</v>
@@ -4339,24 +4357,26 @@
       <c r="L78" s="5"/>
       <c r="M78" s="7"/>
       <c r="N78" s="7"/>
-      <c r="O78" s="5"/>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O78" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="5">
         <v>2</v>
       </c>
       <c r="B79" s="5"/>
       <c r="C79" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D79" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>245</v>
+        <v>324</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>102</v>
+        <v>322</v>
       </c>
       <c r="G79" s="5" t="s">
         <v>309</v>
@@ -4372,7 +4392,7 @@
       <c r="N79" s="7"/>
       <c r="O79" s="5"/>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="5">
         <v>2</v>
       </c>
@@ -4384,10 +4404,10 @@
         <v>50</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="G80" s="5" t="s">
         <v>309</v>
@@ -4403,7 +4423,7 @@
       <c r="N80" s="7"/>
       <c r="O80" s="5"/>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="5">
         <v>2</v>
       </c>
@@ -4415,10 +4435,10 @@
         <v>50</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G81" s="5" t="s">
         <v>309</v>
@@ -4434,7 +4454,7 @@
       <c r="N81" s="7"/>
       <c r="O81" s="5"/>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="5">
         <v>2</v>
       </c>
@@ -4446,10 +4466,10 @@
         <v>50</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>231</v>
+        <v>251</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="G82" s="5" t="s">
         <v>309</v>
@@ -4465,7 +4485,7 @@
       <c r="N82" s="7"/>
       <c r="O82" s="5"/>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="5">
         <v>2</v>
       </c>
@@ -4477,10 +4497,10 @@
         <v>50</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="G83" s="5" t="s">
         <v>309</v>
@@ -4496,7 +4516,7 @@
       <c r="N83" s="7"/>
       <c r="O83" s="5"/>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="5">
         <v>2</v>
       </c>
@@ -4508,10 +4528,10 @@
         <v>50</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G84" s="5" t="s">
         <v>309</v>
@@ -4527,7 +4547,7 @@
       <c r="N84" s="7"/>
       <c r="O84" s="5"/>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="5">
         <v>2</v>
       </c>
@@ -4539,10 +4559,10 @@
         <v>50</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="G85" s="5" t="s">
         <v>309</v>
@@ -4558,7 +4578,7 @@
       <c r="N85" s="7"/>
       <c r="O85" s="5"/>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="5">
         <v>2</v>
       </c>
@@ -4570,10 +4590,10 @@
         <v>50</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="G86" s="5" t="s">
         <v>309</v>
@@ -4589,7 +4609,7 @@
       <c r="N86" s="7"/>
       <c r="O86" s="5"/>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="5">
         <v>2</v>
       </c>
@@ -4601,10 +4621,10 @@
         <v>50</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="G87" s="5" t="s">
         <v>309</v>
@@ -4620,7 +4640,7 @@
       <c r="N87" s="7"/>
       <c r="O87" s="5"/>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="5">
         <v>2</v>
       </c>
@@ -4632,10 +4652,10 @@
         <v>50</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="G88" s="5" t="s">
         <v>309</v>
@@ -4651,7 +4671,7 @@
       <c r="N88" s="7"/>
       <c r="O88" s="5"/>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="5">
         <v>2</v>
       </c>
@@ -4663,10 +4683,10 @@
         <v>50</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G89" s="5" t="s">
         <v>309</v>
@@ -4682,7 +4702,7 @@
       <c r="N89" s="7"/>
       <c r="O89" s="5"/>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="5">
         <v>2</v>
       </c>
@@ -4694,10 +4714,10 @@
         <v>50</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G90" s="5" t="s">
         <v>309</v>
@@ -4713,7 +4733,7 @@
       <c r="N90" s="7"/>
       <c r="O90" s="5"/>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="5">
         <v>2</v>
       </c>
@@ -4725,10 +4745,10 @@
         <v>50</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="G91" s="5" t="s">
         <v>309</v>
@@ -4742,11 +4762,9 @@
       <c r="L91" s="5"/>
       <c r="M91" s="7"/>
       <c r="N91" s="7"/>
-      <c r="O91" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O91" s="5"/>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="5">
         <v>2</v>
       </c>
@@ -4758,10 +4776,10 @@
         <v>50</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="G92" s="5" t="s">
         <v>309</v>
@@ -4775,11 +4793,13 @@
       <c r="L92" s="5"/>
       <c r="M92" s="7"/>
       <c r="N92" s="7"/>
-      <c r="O92" s="5"/>
-    </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O92" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B93" s="5"/>
       <c r="C93" s="5" t="s">
@@ -4789,13 +4809,13 @@
         <v>50</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H93" s="5"/>
       <c r="I93" s="5"/>
@@ -4808,13 +4828,13 @@
       <c r="N93" s="7"/>
       <c r="O93" s="5"/>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="5">
         <v>3</v>
       </c>
       <c r="B94" s="5"/>
       <c r="C94" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D94" s="5" t="s">
         <v>50</v>
@@ -4839,7 +4859,7 @@
       <c r="N94" s="7"/>
       <c r="O94" s="5"/>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="5">
         <v>3</v>
       </c>
@@ -4851,10 +4871,10 @@
         <v>50</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G95" s="5" t="s">
         <v>311</v>
@@ -4870,22 +4890,22 @@
       <c r="N95" s="7"/>
       <c r="O95" s="5"/>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="5">
         <v>3</v>
       </c>
       <c r="B96" s="5"/>
       <c r="C96" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D96" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G96" s="5" t="s">
         <v>311</v>
@@ -4901,13 +4921,13 @@
       <c r="N96" s="7"/>
       <c r="O96" s="5"/>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="5">
         <v>3</v>
       </c>
       <c r="B97" s="5"/>
       <c r="C97" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D97" s="5" t="s">
         <v>50</v>
@@ -4932,7 +4952,7 @@
       <c r="N97" s="7"/>
       <c r="O97" s="5"/>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="5">
         <v>3</v>
       </c>
@@ -4944,10 +4964,10 @@
         <v>50</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="G98" s="5" t="s">
         <v>311</v>
@@ -4963,22 +4983,22 @@
       <c r="N98" s="7"/>
       <c r="O98" s="5"/>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="5">
         <v>3</v>
       </c>
       <c r="B99" s="5"/>
       <c r="C99" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D99" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="G99" s="5" t="s">
         <v>311</v>
@@ -4994,13 +5014,13 @@
       <c r="N99" s="7"/>
       <c r="O99" s="5"/>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" s="5">
         <v>3</v>
       </c>
       <c r="B100" s="5"/>
       <c r="C100" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D100" s="5" t="s">
         <v>50</v>
@@ -5025,7 +5045,7 @@
       <c r="N100" s="7"/>
       <c r="O100" s="5"/>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="5">
         <v>3</v>
       </c>
@@ -5037,10 +5057,10 @@
         <v>50</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="G101" s="5" t="s">
         <v>311</v>
@@ -5056,7 +5076,7 @@
       <c r="N101" s="7"/>
       <c r="O101" s="5"/>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" s="5">
         <v>3</v>
       </c>
@@ -5068,10 +5088,10 @@
         <v>50</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G102" s="5" t="s">
         <v>311</v>
@@ -5087,7 +5107,7 @@
       <c r="N102" s="7"/>
       <c r="O102" s="5"/>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" s="5">
         <v>3</v>
       </c>
@@ -5099,10 +5119,10 @@
         <v>50</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="G103" s="5" t="s">
         <v>311</v>
@@ -5118,7 +5138,7 @@
       <c r="N103" s="7"/>
       <c r="O103" s="5"/>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" s="5">
         <v>3</v>
       </c>
@@ -5130,10 +5150,10 @@
         <v>50</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G104" s="5" t="s">
         <v>311</v>
@@ -5149,7 +5169,7 @@
       <c r="N104" s="7"/>
       <c r="O104" s="5"/>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" s="5">
         <v>3</v>
       </c>
@@ -5161,10 +5181,10 @@
         <v>50</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="G105" s="5" t="s">
         <v>311</v>
@@ -5180,22 +5200,22 @@
       <c r="N105" s="7"/>
       <c r="O105" s="5"/>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" s="5">
         <v>3</v>
       </c>
       <c r="B106" s="5"/>
       <c r="C106" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D106" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="G106" s="5" t="s">
         <v>311</v>
@@ -5211,13 +5231,13 @@
       <c r="N106" s="7"/>
       <c r="O106" s="5"/>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" s="5">
         <v>3</v>
       </c>
       <c r="B107" s="5"/>
       <c r="C107" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D107" s="5" t="s">
         <v>50</v>
@@ -5242,7 +5262,7 @@
       <c r="N107" s="7"/>
       <c r="O107" s="5"/>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" s="5">
         <v>3</v>
       </c>
@@ -5254,10 +5274,10 @@
         <v>50</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G108" s="5" t="s">
         <v>311</v>
@@ -5273,7 +5293,7 @@
       <c r="N108" s="7"/>
       <c r="O108" s="5"/>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109" s="5">
         <v>3</v>
       </c>
@@ -5285,10 +5305,10 @@
         <v>50</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G109" s="5" t="s">
         <v>311</v>
@@ -5304,7 +5324,7 @@
       <c r="N109" s="7"/>
       <c r="O109" s="5"/>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110" s="5">
         <v>3</v>
       </c>
@@ -5335,7 +5355,7 @@
       <c r="N110" s="7"/>
       <c r="O110" s="5"/>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111" s="5">
         <v>3</v>
       </c>
@@ -5366,7 +5386,7 @@
       <c r="N111" s="7"/>
       <c r="O111" s="5"/>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112" s="5">
         <v>3</v>
       </c>
@@ -5397,7 +5417,7 @@
       <c r="N112" s="7"/>
       <c r="O112" s="5"/>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113" s="5">
         <v>3</v>
       </c>
@@ -5428,7 +5448,7 @@
       <c r="N113" s="7"/>
       <c r="O113" s="5"/>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114" s="5">
         <v>3</v>
       </c>
@@ -5459,7 +5479,7 @@
       <c r="N114" s="7"/>
       <c r="O114" s="5"/>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115" s="5">
         <v>3</v>
       </c>
@@ -5490,7 +5510,7 @@
       <c r="N115" s="7"/>
       <c r="O115" s="5"/>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116" s="5">
         <v>3</v>
       </c>
@@ -5502,10 +5522,10 @@
         <v>50</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="G116" s="5" t="s">
         <v>311</v>
@@ -5521,22 +5541,22 @@
       <c r="N116" s="7"/>
       <c r="O116" s="5"/>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117" s="5">
         <v>3</v>
       </c>
       <c r="B117" s="5"/>
       <c r="C117" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D117" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="G117" s="5" t="s">
         <v>311</v>
@@ -5552,7 +5572,7 @@
       <c r="N117" s="7"/>
       <c r="O117" s="5"/>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118" s="5">
         <v>3</v>
       </c>
@@ -5564,10 +5584,10 @@
         <v>50</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>133</v>
+        <v>84</v>
       </c>
       <c r="G118" s="5" t="s">
         <v>311</v>
@@ -5583,7 +5603,7 @@
       <c r="N118" s="7"/>
       <c r="O118" s="5"/>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119" s="5">
         <v>3</v>
       </c>
@@ -5595,10 +5615,10 @@
         <v>50</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="G119" s="5" t="s">
         <v>311</v>
@@ -5614,7 +5634,7 @@
       <c r="N119" s="7"/>
       <c r="O119" s="5"/>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120" s="5">
         <v>3</v>
       </c>
@@ -5626,10 +5646,10 @@
         <v>50</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="G120" s="5" t="s">
         <v>311</v>
@@ -5645,7 +5665,7 @@
       <c r="N120" s="7"/>
       <c r="O120" s="5"/>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121" s="5">
         <v>3</v>
       </c>
@@ -5657,10 +5677,10 @@
         <v>50</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G121" s="5" t="s">
         <v>311</v>
@@ -5676,7 +5696,7 @@
       <c r="N121" s="7"/>
       <c r="O121" s="5"/>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122" s="5">
         <v>3</v>
       </c>
@@ -5688,10 +5708,10 @@
         <v>50</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G122" s="5" t="s">
         <v>311</v>
@@ -5707,7 +5727,7 @@
       <c r="N122" s="7"/>
       <c r="O122" s="5"/>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123" s="5">
         <v>3</v>
       </c>
@@ -5719,10 +5739,10 @@
         <v>50</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G123" s="5" t="s">
         <v>311</v>
@@ -5738,7 +5758,7 @@
       <c r="N123" s="7"/>
       <c r="O123" s="5"/>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124" s="5">
         <v>3</v>
       </c>
@@ -5750,10 +5770,10 @@
         <v>50</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G124" s="5" t="s">
         <v>311</v>
@@ -5769,25 +5789,25 @@
       <c r="N124" s="7"/>
       <c r="O124" s="5"/>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B125" s="5"/>
       <c r="C125" s="5" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>50</v>
+        <v>139</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>249</v>
+        <v>273</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>106</v>
+        <v>140</v>
       </c>
       <c r="G125" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H125" s="5"/>
       <c r="I125" s="5"/>
@@ -5800,7 +5820,7 @@
       <c r="N125" s="7"/>
       <c r="O125" s="5"/>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A126" s="5">
         <v>2</v>
       </c>
@@ -5809,13 +5829,13 @@
         <v>12</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G126" s="5" t="s">
         <v>309</v>
@@ -5831,7 +5851,7 @@
       <c r="N126" s="7"/>
       <c r="O126" s="5"/>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A127" s="5">
         <v>2</v>
       </c>
@@ -5840,13 +5860,13 @@
         <v>12</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G127" s="5" t="s">
         <v>309</v>
@@ -5862,22 +5882,22 @@
       <c r="N127" s="7"/>
       <c r="O127" s="5"/>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A128" s="5">
         <v>2</v>
       </c>
       <c r="B128" s="5"/>
       <c r="C128" s="5" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>143</v>
+        <v>13</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>275</v>
+        <v>201</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>144</v>
+        <v>22</v>
       </c>
       <c r="G128" s="5" t="s">
         <v>309</v>
@@ -5893,25 +5913,25 @@
       <c r="N128" s="7"/>
       <c r="O128" s="5"/>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A129" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B129" s="5"/>
       <c r="C129" s="5" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D129" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>201</v>
+        <v>276</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>22</v>
+        <v>145</v>
       </c>
       <c r="G129" s="5" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="H129" s="5"/>
       <c r="I129" s="5"/>
@@ -5924,7 +5944,7 @@
       <c r="N129" s="7"/>
       <c r="O129" s="5"/>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A130" s="5">
         <v>3</v>
       </c>
@@ -5936,10 +5956,10 @@
         <v>13</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G130" s="5" t="s">
         <v>311</v>
@@ -5955,7 +5975,7 @@
       <c r="N130" s="7"/>
       <c r="O130" s="5"/>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A131" s="5">
         <v>3</v>
       </c>
@@ -5964,13 +5984,13 @@
         <v>12</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>13</v>
+        <v>147</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G131" s="5" t="s">
         <v>311</v>
@@ -5986,7 +6006,7 @@
       <c r="N131" s="7"/>
       <c r="O131" s="5"/>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A132" s="5">
         <v>3</v>
       </c>
@@ -5995,13 +6015,13 @@
         <v>12</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>147</v>
+        <v>13</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G132" s="5" t="s">
         <v>311</v>
@@ -6017,7 +6037,7 @@
       <c r="N132" s="7"/>
       <c r="O132" s="5"/>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A133" s="5">
         <v>3</v>
       </c>
@@ -6029,10 +6049,10 @@
         <v>13</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G133" s="5" t="s">
         <v>311</v>
@@ -6048,7 +6068,7 @@
       <c r="N133" s="7"/>
       <c r="O133" s="5"/>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A134" s="5">
         <v>3</v>
       </c>
@@ -6060,10 +6080,10 @@
         <v>13</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G134" s="5" t="s">
         <v>311</v>
@@ -6079,7 +6099,7 @@
       <c r="N134" s="7"/>
       <c r="O134" s="5"/>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A135" s="5">
         <v>3</v>
       </c>
@@ -6088,13 +6108,13 @@
         <v>12</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>13</v>
+        <v>154</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G135" s="5" t="s">
         <v>311</v>
@@ -6110,22 +6130,22 @@
       <c r="N135" s="7"/>
       <c r="O135" s="5"/>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A136" s="5">
         <v>3</v>
       </c>
       <c r="B136" s="5"/>
       <c r="C136" s="5" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>154</v>
+        <v>50</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G136" s="5" t="s">
         <v>311</v>
@@ -6141,7 +6161,7 @@
       <c r="N136" s="7"/>
       <c r="O136" s="5"/>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A137" s="5">
         <v>3</v>
       </c>
@@ -6153,10 +6173,10 @@
         <v>50</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G137" s="5" t="s">
         <v>311</v>
@@ -6172,7 +6192,7 @@
       <c r="N137" s="7"/>
       <c r="O137" s="5"/>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A138" s="5">
         <v>3</v>
       </c>
@@ -6184,10 +6204,10 @@
         <v>50</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>286</v>
+        <v>227</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G138" s="5" t="s">
         <v>311</v>
@@ -6203,7 +6223,7 @@
       <c r="N138" s="7"/>
       <c r="O138" s="5"/>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A139" s="5">
         <v>3</v>
       </c>
@@ -6218,7 +6238,7 @@
         <v>227</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G139" s="5" t="s">
         <v>311</v>
@@ -6234,7 +6254,7 @@
       <c r="N139" s="7"/>
       <c r="O139" s="5"/>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A140" s="5">
         <v>3</v>
       </c>
@@ -6249,7 +6269,7 @@
         <v>227</v>
       </c>
       <c r="F140" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G140" s="5" t="s">
         <v>311</v>
@@ -6265,7 +6285,7 @@
       <c r="N140" s="7"/>
       <c r="O140" s="5"/>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A141" s="5">
         <v>3</v>
       </c>
@@ -6280,7 +6300,7 @@
         <v>227</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G141" s="5" t="s">
         <v>311</v>
@@ -6296,7 +6316,7 @@
       <c r="N141" s="7"/>
       <c r="O141" s="5"/>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A142" s="5">
         <v>3</v>
       </c>
@@ -6311,7 +6331,7 @@
         <v>227</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G142" s="5" t="s">
         <v>311</v>
@@ -6327,13 +6347,13 @@
       <c r="N142" s="7"/>
       <c r="O142" s="5"/>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A143" s="5">
         <v>3</v>
       </c>
       <c r="B143" s="5"/>
       <c r="C143" s="5" t="s">
-        <v>80</v>
+        <v>164</v>
       </c>
       <c r="D143" s="5" t="s">
         <v>50</v>
@@ -6342,7 +6362,7 @@
         <v>227</v>
       </c>
       <c r="F143" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G143" s="5" t="s">
         <v>311</v>
@@ -6358,7 +6378,7 @@
       <c r="N143" s="7"/>
       <c r="O143" s="5"/>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A144" s="5">
         <v>3</v>
       </c>
@@ -6373,7 +6393,7 @@
         <v>227</v>
       </c>
       <c r="F144" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G144" s="5" t="s">
         <v>311</v>
@@ -6389,7 +6409,7 @@
       <c r="N144" s="7"/>
       <c r="O144" s="5"/>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A145" s="5">
         <v>3</v>
       </c>
@@ -6404,7 +6424,7 @@
         <v>227</v>
       </c>
       <c r="F145" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G145" s="5" t="s">
         <v>311</v>
@@ -6420,7 +6440,7 @@
       <c r="N145" s="7"/>
       <c r="O145" s="5"/>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A146" s="5">
         <v>3</v>
       </c>
@@ -6435,7 +6455,7 @@
         <v>227</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G146" s="5" t="s">
         <v>311</v>
@@ -6451,13 +6471,13 @@
       <c r="N146" s="7"/>
       <c r="O146" s="5"/>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A147" s="5">
         <v>3</v>
       </c>
       <c r="B147" s="5"/>
       <c r="C147" s="5" t="s">
-        <v>164</v>
+        <v>49</v>
       </c>
       <c r="D147" s="5" t="s">
         <v>50</v>
@@ -6466,7 +6486,7 @@
         <v>227</v>
       </c>
       <c r="F147" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G147" s="5" t="s">
         <v>311</v>
@@ -6482,13 +6502,13 @@
       <c r="N147" s="7"/>
       <c r="O147" s="5"/>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A148" s="5">
         <v>3</v>
       </c>
       <c r="B148" s="5"/>
       <c r="C148" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D148" s="5" t="s">
         <v>50</v>
@@ -6497,7 +6517,7 @@
         <v>227</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G148" s="5" t="s">
         <v>311</v>
@@ -6513,7 +6533,7 @@
       <c r="N148" s="7"/>
       <c r="O148" s="5"/>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A149" s="5">
         <v>3</v>
       </c>
@@ -6528,7 +6548,7 @@
         <v>227</v>
       </c>
       <c r="F149" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G149" s="5" t="s">
         <v>311</v>
@@ -6544,7 +6564,7 @@
       <c r="N149" s="7"/>
       <c r="O149" s="5"/>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A150" s="5">
         <v>3</v>
       </c>
@@ -6559,7 +6579,7 @@
         <v>227</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G150" s="5" t="s">
         <v>311</v>
@@ -6575,30 +6595,34 @@
       <c r="N150" s="7"/>
       <c r="O150" s="5"/>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A151" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B151" s="5"/>
       <c r="C151" s="5" t="s">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>227</v>
+        <v>302</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G151" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="H151" s="5"/>
-      <c r="I151" s="5"/>
+      <c r="H151" s="6">
+        <v>46094</v>
+      </c>
+      <c r="I151" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="J151" s="5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K151" s="5"/>
       <c r="L151" s="5"/>
@@ -6606,7 +6630,7 @@
       <c r="N151" s="7"/>
       <c r="O151" s="5"/>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A152" s="5">
         <v>0</v>
       </c>
@@ -6618,10 +6642,10 @@
         <v>13</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G152" s="5" t="s">
         <v>311</v>
@@ -6641,28 +6665,28 @@
       <c r="N152" s="7"/>
       <c r="O152" s="5"/>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A153" s="5">
         <v>0</v>
       </c>
       <c r="B153" s="5"/>
       <c r="C153" s="5" t="s">
-        <v>134</v>
+        <v>175</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>303</v>
+        <v>176</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="G153" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H153" s="6">
-        <v>46094</v>
+        <v>46095</v>
       </c>
       <c r="I153" s="5" t="s">
         <v>15</v>
@@ -6676,32 +6700,30 @@
       <c r="N153" s="7"/>
       <c r="O153" s="5"/>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A154" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B154" s="5"/>
       <c r="C154" s="5" t="s">
-        <v>175</v>
+        <v>12</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>176</v>
+        <v>287</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G154" s="5" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="H154" s="6">
-        <v>46095</v>
-      </c>
-      <c r="I154" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>46128</v>
+      </c>
+      <c r="I154" s="5"/>
       <c r="J154" s="5" t="s">
         <v>73</v>
       </c>
@@ -6711,7 +6733,7 @@
       <c r="N154" s="7"/>
       <c r="O154" s="5"/>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A155" s="5">
         <v>3</v>
       </c>
@@ -6723,18 +6745,20 @@
         <v>13</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G155" s="5" t="s">
         <v>311</v>
       </c>
       <c r="H155" s="6">
-        <v>46128</v>
-      </c>
-      <c r="I155" s="5"/>
+        <v>46139</v>
+      </c>
+      <c r="I155" s="9">
+        <v>0.33333333333333331</v>
+      </c>
       <c r="J155" s="5" t="s">
         <v>73</v>
       </c>
@@ -6744,7 +6768,7 @@
       <c r="N155" s="7"/>
       <c r="O155" s="5"/>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A156" s="5">
         <v>3</v>
       </c>
@@ -6753,22 +6777,22 @@
         <v>12</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>13</v>
+        <v>180</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G156" s="5" t="s">
         <v>311</v>
       </c>
       <c r="H156" s="6">
-        <v>46139</v>
+        <v>46141</v>
       </c>
       <c r="I156" s="9">
-        <v>0.33333333333333331</v>
+        <v>0.96527777777777779</v>
       </c>
       <c r="J156" s="5" t="s">
         <v>73</v>
@@ -6779,7 +6803,7 @@
       <c r="N156" s="7"/>
       <c r="O156" s="5"/>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A157" s="5">
         <v>3</v>
       </c>
@@ -6788,22 +6812,22 @@
         <v>12</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>180</v>
+        <v>13</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F157" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G157" s="5" t="s">
         <v>311</v>
       </c>
       <c r="H157" s="6">
-        <v>46141</v>
+        <v>46146</v>
       </c>
       <c r="I157" s="9">
-        <v>0.96527777777777779</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="J157" s="5" t="s">
         <v>73</v>
@@ -6814,7 +6838,7 @@
       <c r="N157" s="7"/>
       <c r="O157" s="5"/>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A158" s="5">
         <v>3</v>
       </c>
@@ -6823,22 +6847,22 @@
         <v>12</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>13</v>
+        <v>183</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G158" s="5" t="s">
         <v>311</v>
       </c>
       <c r="H158" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="I158" s="9">
-        <v>0.41666666666666669</v>
+        <v>0.5</v>
       </c>
       <c r="J158" s="5" t="s">
         <v>73</v>
@@ -6849,44 +6873,44 @@
       <c r="N158" s="7"/>
       <c r="O158" s="5"/>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A159" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B159" s="5"/>
       <c r="C159" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>183</v>
+        <v>13</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F159" s="5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G159" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H159" s="6">
         <v>46147</v>
       </c>
-      <c r="I159" s="9">
-        <v>0.5</v>
-      </c>
+      <c r="I159" s="5"/>
       <c r="J159" s="5" t="s">
         <v>73</v>
       </c>
       <c r="K159" s="5"/>
       <c r="L159" s="5"/>
       <c r="M159" s="16"/>
-      <c r="N159" s="7"/>
+      <c r="N159" s="7" t="s">
+        <v>327</v>
+      </c>
       <c r="O159" s="5"/>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A160" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B160" s="5"/>
       <c r="C160" s="5" t="s">
@@ -6896,30 +6920,30 @@
         <v>13</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G160" s="5" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="H160" s="6">
-        <v>46147</v>
-      </c>
-      <c r="I160" s="5"/>
+        <v>46149</v>
+      </c>
+      <c r="I160" s="9">
+        <v>0.41666666666666669</v>
+      </c>
       <c r="J160" s="5" t="s">
         <v>73</v>
       </c>
       <c r="K160" s="5"/>
       <c r="L160" s="5"/>
       <c r="M160" s="16"/>
-      <c r="N160" s="7" t="s">
-        <v>327</v>
-      </c>
+      <c r="N160" s="7"/>
       <c r="O160" s="5"/>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A161" s="5">
         <v>3</v>
       </c>
@@ -6928,22 +6952,22 @@
         <v>12</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>13</v>
+        <v>187</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G161" s="5" t="s">
         <v>311</v>
       </c>
       <c r="H161" s="6">
-        <v>46149</v>
+        <v>46155</v>
       </c>
       <c r="I161" s="9">
-        <v>0.41666666666666669</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="J161" s="5" t="s">
         <v>73</v>
@@ -6954,7 +6978,7 @@
       <c r="N161" s="7"/>
       <c r="O161" s="5"/>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A162" s="5">
         <v>3</v>
       </c>
@@ -6963,22 +6987,22 @@
         <v>12</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>187</v>
+        <v>13</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G162" s="5" t="s">
         <v>311</v>
       </c>
       <c r="H162" s="6">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="I162" s="9">
-        <v>0.45833333333333331</v>
+        <v>0.625</v>
       </c>
       <c r="J162" s="5" t="s">
         <v>73</v>
@@ -6989,9 +7013,9 @@
       <c r="N162" s="7"/>
       <c r="O162" s="5"/>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A163" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B163" s="5"/>
       <c r="C163" s="5" t="s">
@@ -7001,19 +7025,19 @@
         <v>13</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G163" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H163" s="6">
-        <v>46156</v>
+        <v>46163</v>
       </c>
       <c r="I163" s="9">
-        <v>0.625</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J163" s="5" t="s">
         <v>73</v>
@@ -7024,7 +7048,7 @@
       <c r="N163" s="7"/>
       <c r="O163" s="5"/>
     </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A164" s="5">
         <v>2</v>
       </c>
@@ -7036,19 +7060,19 @@
         <v>13</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G164" s="5" t="s">
         <v>309</v>
       </c>
       <c r="H164" s="6">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="I164" s="9">
-        <v>0.33333333333333331</v>
+        <v>0.375</v>
       </c>
       <c r="J164" s="5" t="s">
         <v>73</v>
@@ -7059,31 +7083,31 @@
       <c r="N164" s="7"/>
       <c r="O164" s="5"/>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A165" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B165" s="5"/>
       <c r="C165" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>13</v>
+        <v>192</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F165" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G165" s="5" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="H165" s="6">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="I165" s="9">
-        <v>0.375</v>
+        <v>0.5625</v>
       </c>
       <c r="J165" s="5" t="s">
         <v>73</v>
@@ -7094,7 +7118,7 @@
       <c r="N165" s="7"/>
       <c r="O165" s="5"/>
     </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A166" s="5">
         <v>3</v>
       </c>
@@ -7103,22 +7127,22 @@
         <v>12</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>192</v>
+        <v>13</v>
       </c>
       <c r="E166" s="5" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G166" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="H166" s="6">
-        <v>46167</v>
-      </c>
-      <c r="I166" s="9">
-        <v>0.5625</v>
+      <c r="H166" s="12">
+        <v>46170</v>
+      </c>
+      <c r="I166" s="13">
+        <v>0.41666666666666669</v>
       </c>
       <c r="J166" s="5" t="s">
         <v>73</v>
@@ -7129,7 +7153,7 @@
       <c r="N166" s="7"/>
       <c r="O166" s="5"/>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A167" s="5">
         <v>3</v>
       </c>
@@ -7138,22 +7162,22 @@
         <v>12</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G167" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="H167" s="12">
-        <v>46170</v>
-      </c>
-      <c r="I167" s="13">
-        <v>0.41666666666666669</v>
+      <c r="H167" s="6">
+        <v>46174</v>
+      </c>
+      <c r="I167" s="9">
+        <v>0.72916666666666663</v>
       </c>
       <c r="J167" s="5" t="s">
         <v>73</v>
@@ -7164,42 +7188,48 @@
       <c r="N167" s="7"/>
       <c r="O167" s="5"/>
     </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A168" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B168" s="5"/>
       <c r="C168" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="E168" s="5" t="s">
-        <v>300</v>
+        <v>199</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>195</v>
+        <v>19</v>
       </c>
       <c r="G168" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H168" s="6">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="I168" s="9">
-        <v>0.72916666666666663</v>
+        <v>0.875</v>
       </c>
       <c r="J168" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="K168" s="5"/>
-      <c r="L168" s="5"/>
-      <c r="M168" s="16"/>
-      <c r="N168" s="7"/>
+      <c r="K168" s="6">
+        <v>46182</v>
+      </c>
+      <c r="L168" s="6"/>
+      <c r="M168" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="N168" s="7" t="s">
+        <v>328</v>
+      </c>
       <c r="O168" s="5"/>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A169" s="5">
         <v>1</v>
       </c>
@@ -7211,75 +7241,73 @@
         <v>13</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G169" s="5" t="s">
         <v>309</v>
       </c>
       <c r="H169" s="6">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="I169" s="9">
-        <v>0.875</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="J169" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="K169" s="6">
-        <v>46182</v>
-      </c>
-      <c r="L169" s="6"/>
+      <c r="K169" s="5"/>
+      <c r="L169" s="5"/>
       <c r="M169" s="7" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="N169" s="7" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="O169" s="5"/>
     </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A170" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B170" s="5"/>
       <c r="C170" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="F170" s="5" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="G170" s="5" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="H170" s="6">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="I170" s="9">
-        <v>0.41666666666666669</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="J170" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="K170" s="5"/>
-      <c r="L170" s="5"/>
-      <c r="M170" s="7" t="s">
-        <v>334</v>
-      </c>
-      <c r="N170" s="7" t="s">
-        <v>334</v>
-      </c>
+      <c r="K170" s="6">
+        <v>46189</v>
+      </c>
+      <c r="L170" s="5">
+        <v>1.06</v>
+      </c>
+      <c r="M170" s="7"/>
+      <c r="N170" s="7"/>
       <c r="O170" s="5"/>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A171" s="5">
         <v>0</v>
       </c>
@@ -7310,7 +7338,7 @@
       <c r="N171" s="7"/>
       <c r="O171" s="5"/>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A172" s="5">
         <v>0</v>
       </c>
@@ -7341,7 +7369,7 @@
       <c r="N172" s="7"/>
       <c r="O172" s="5"/>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A173" s="5">
         <v>2</v>
       </c>
@@ -7373,7 +7401,7 @@
       <c r="K173" s="5"/>
       <c r="L173" s="5"/>
       <c r="M173" s="7" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="N173" s="7" t="s">
         <v>330</v>

--- a/archivos/BD_Dashboard.xlsx
+++ b/archivos/BD_Dashboard.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mexscitum-my.sharepoint.com/personal/erik_torres_scitum_com_mx/Documents/Documentos/ETP/GitHub/SCITUM-AMX/archivos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="116" documentId="11_F25DC773A252ABDACC1048E8499F6DC65BDE58F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F85C021-42F9-45D7-B7C8-53D7DA77AA6A}"/>
+  <xr:revisionPtr revIDLastSave="129" documentId="11_F25DC773A252ABDACC1048E8499F6DC65BDE58F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B4BEDA1-7F4A-4BD9-8B08-00B3EBE5B416}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
     <author>Erik Alejandro Torres Piña</author>
   </authors>
   <commentList>
-    <comment ref="F46" authorId="0" shapeId="0" xr:uid="{4E98F78C-2D02-4920-97E6-96F2E3D293F6}">
+    <comment ref="F43" authorId="0" shapeId="0" xr:uid="{2F252D48-D2F5-47BC-8FC8-5F3C91252D36}">
       <text>
         <r>
           <rPr>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="358">
   <si>
     <t>TIER</t>
   </si>
@@ -320,9 +320,6 @@
     <t>ATO Nacional</t>
   </si>
   <si>
-    <t>AICM T1</t>
-  </si>
-  <si>
     <t>AIFA</t>
   </si>
   <si>
@@ -402,9 +399,6 @@
   </si>
   <si>
     <t>AEROMEXICO GDL NVO HANGAR DE MANTO</t>
-  </si>
-  <si>
-    <t>Ciudad del Carmen (CME)</t>
   </si>
   <si>
     <t>Culiacán  (CUL)</t>
@@ -1071,9 +1065,6 @@
     <t>Aeroméxico autorizó la instalación temporal de los equipos sobre infraestructura existente de otro proveedor para mantener la ventana de implementación del sitio LAS. Durante la sesión se expusieron los riesgos asociados a esta alternativa y Aeroméxico confirmó la aceptación de dichos riesgos, asumiendo la responsabilidad ante cualquier incidente derivado del movimiento o manipulación de los equipos existentes durante o posterior a la ventana. No se tiene switch, Aeromexico reporta que desconocía esta situación, se conecta un solo equipo ION y no se habilita HA.</t>
   </si>
   <si>
-    <t>No hay foto. Tiene enlace SITA</t>
-  </si>
-  <si>
     <t>AMX solicita sacarlo de la planeación hasta nuevo aviso</t>
   </si>
   <si>
@@ -1092,13 +1083,76 @@
     <t>El envío del equipo se realizó el 06-jul-2026</t>
   </si>
   <si>
-    <t>Programada.</t>
-  </si>
-  <si>
-    <t>No se requieren permisos especiales solo compartan nombre del IDC.</t>
-  </si>
-  <si>
-    <t>Nombre, numero de telefono, copia de identificación oficial y lista de herramientas</t>
+    <t>Hora CDMX</t>
+  </si>
+  <si>
+    <t>No hay foto. Nombre, numero de telefono, copia de identificación oficial y lista de herramientas</t>
+  </si>
+  <si>
+    <t>Compartir datos del IDC y su ID, del lado de AM se requiere presencia en sitio ya que Delta no moverá un solo cable es responsabilidad total de AM, enviar pasaporte para tramite de permisos. No hay foto de sitio</t>
+  </si>
+  <si>
+    <t>No hay foto. No requieren permisos especiales solo confirmen nombre de IDC. No se observa espacio para conexión electrica, no se observan puertos disponibles en el switch. Rack elevado, no se observa a que altura.</t>
+  </si>
+  <si>
+    <t>HANGAR_MEX</t>
+  </si>
+  <si>
+    <t>No quedo el HA por que no había switch disponible</t>
+  </si>
+  <si>
+    <t>Al hacer el cambio no paso el rol de activo al ION 02. Se analiza el caso con PS PAN. No habia puertos disponibles con DHCP.</t>
+  </si>
+  <si>
+    <t>Tiene enlace SITA</t>
+  </si>
+  <si>
+    <t>Se realizó el rollback de la actividad en Costa Rica (SJO) con el VoBo de Cristian Villa de Aeroméxico.
+La integración de la red de SDWAN con el dispositivo ION fue correcta, las VPN hacia el DC CECAM y DC Equinix levantaron correctamente; sin embargo, los equipos de escritorio (desktops) perdieron la conexión en la red LAN, incluso sin poder alcanzar su gateway.
+Dicho gateway es un dispositivo router denominado SITA que se encuentra conectado por debajo del firewall Fortinet como parte de la LAN; asimismo, el firewall recibe el tráfico y lo envía al ION para establecer la conexión SD-WAN sin embargo no se observo trafico que envie Fortinet al ION durante la actividad.
+Aeroméxico realizara el análisis correspondiente de esta red LAN.</t>
+  </si>
+  <si>
+    <t>Orden Enlace Telmex</t>
+  </si>
+  <si>
+    <t>AICM T1 (AICM_T1)</t>
+  </si>
+  <si>
+    <t>Ciudad Juárez (CJS_CARGO)</t>
+  </si>
+  <si>
+    <t>Mazatlán (MZT_CARGO)</t>
+  </si>
+  <si>
+    <t>Chihuahua (CUU_CARGO)</t>
+  </si>
+  <si>
+    <t>Oaxaca (OAX_CARGO)</t>
+  </si>
+  <si>
+    <t>Ciudad del Carmen (CME_CARGO)</t>
+  </si>
+  <si>
+    <t>AICM_T1</t>
+  </si>
+  <si>
+    <t>CJS_CARGO</t>
+  </si>
+  <si>
+    <t>MZT_CARGO</t>
+  </si>
+  <si>
+    <t>CUU_CARGO</t>
+  </si>
+  <si>
+    <t>OAX_CARGO</t>
+  </si>
+  <si>
+    <t>CME_CARGO</t>
+  </si>
+  <si>
+    <t>No se requieren permisos especiales solo compartan nombre del IDC. Switch administrable por el aeropuerto y el enlace es del aeropuerto. No se observa si existe espacio para contacto electrico. No hay espacio para colocar equipo, se colocaría encima del switch</t>
   </si>
 </sst>
 </file>
@@ -1171,7 +1225,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1193,6 +1247,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF7C7AC"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -1224,7 +1284,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1275,6 +1335,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="15" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1453,10 +1516,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1725,7 +1784,7 @@
   <sheetPr>
     <tabColor theme="5" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:O173"/>
+  <dimension ref="A1:Q173"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.140625" bestFit="1" customWidth="1"/>
@@ -1735,11 +1794,9 @@
     <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="24.85546875" customWidth="1"/>
     <col min="7" max="7" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1759,34 +1816,40 @@
         <v>5</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
       <c r="I1" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="4" t="s">
-        <v>325</v>
-      </c>
       <c r="O1" s="4" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -1795,37 +1858,41 @@
         <v>12</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="H2" s="6">
-        <v>46218</v>
+        <v>307</v>
+      </c>
+      <c r="H2" s="2">
+        <v>46219</v>
       </c>
       <c r="I2" s="9">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="K2" s="5"/>
-      <c r="L2" s="14">
-        <v>2.08</v>
-      </c>
-      <c r="M2" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="N2" s="7"/>
-      <c r="O2" s="5"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="J2" s="3">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="L2" s="6">
+        <v>46182</v>
+      </c>
+      <c r="M2" s="6"/>
+      <c r="N2" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="O2" s="7"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>3</v>
       </c>
@@ -1837,36 +1904,40 @@
         <v>26</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>27</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H3" s="6">
         <v>46220</v>
       </c>
       <c r="I3" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J3" s="9">
         <v>0.375</v>
       </c>
-      <c r="J3" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="K3" s="6">
+      <c r="K3" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="L3" s="6">
         <v>46189</v>
       </c>
-      <c r="L3" s="5">
+      <c r="M3" s="5">
         <v>1.02</v>
       </c>
-      <c r="M3" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="N3" s="7"/>
-      <c r="O3" s="5"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N3" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="O3" s="7"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>1</v>
       </c>
@@ -1875,35 +1946,41 @@
         <v>12</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="H4" s="12">
-        <v>46225</v>
-      </c>
-      <c r="I4" s="13">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="K4" s="5"/>
+        <v>307</v>
+      </c>
+      <c r="H4" s="2">
+        <v>46223</v>
+      </c>
+      <c r="I4" s="9">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="J4" s="3">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>308</v>
+      </c>
       <c r="L4" s="5"/>
-      <c r="M4" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="N4" s="7"/>
-      <c r="O4" s="5"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M4" s="5">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="O4" s="7"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>1</v>
       </c>
@@ -1912,152 +1989,170 @@
         <v>12</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="H5" s="6">
-        <v>46218</v>
+        <v>307</v>
+      </c>
+      <c r="H5" s="12">
+        <v>46225</v>
       </c>
       <c r="I5" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="K5" s="6">
-        <v>46182</v>
-      </c>
-      <c r="L5" s="6"/>
-      <c r="M5" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="N5" s="7"/>
-      <c r="O5" s="5"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J5" s="13">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="O5" s="7"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="5"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="H6" s="6">
-        <v>46223</v>
-      </c>
-      <c r="I6" s="9">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5">
-        <v>2.0699999999999998</v>
-      </c>
-      <c r="M6" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="N6" s="7"/>
-      <c r="O6" s="5"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+        <v>307</v>
+      </c>
+      <c r="H6" s="2">
+        <v>46226</v>
+      </c>
+      <c r="I6" s="5"/>
+      <c r="J6" s="3">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="O6" s="7"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>203</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K7" s="6">
+        <v>307</v>
+      </c>
+      <c r="H7" s="2">
+        <v>46230</v>
+      </c>
+      <c r="I7" s="9">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="J7" s="3">
+        <v>0.6875</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="L7" s="6">
         <v>46189</v>
       </c>
-      <c r="L7" s="5">
-        <v>1.01</v>
-      </c>
-      <c r="M7" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="N7" s="7"/>
-      <c r="O7" s="5"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M7" s="5">
+        <v>1.03</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="O7" s="7"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K8" s="6">
+        <v>307</v>
+      </c>
+      <c r="H8" s="2">
+        <v>46230</v>
+      </c>
+      <c r="I8" s="9">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="J8" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="L8" s="6">
         <v>46189</v>
       </c>
-      <c r="L8" s="5">
-        <v>1.03</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="N8" s="7"/>
-      <c r="O8" s="5"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M8" s="5">
+        <v>1.01</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="O8" s="7"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5" t="s">
@@ -2067,61 +2162,65 @@
         <v>26</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
-      <c r="J9" s="5" t="s">
+      <c r="J9" s="5"/>
+      <c r="K9" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5">
-        <v>2.02</v>
-      </c>
-      <c r="M9" s="7"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5">
+        <v>2.09</v>
+      </c>
       <c r="N9" s="7"/>
-      <c r="O9" s="5"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O9" s="7"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>217</v>
+        <v>259</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>309</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
-      <c r="J10" s="5" t="s">
+      <c r="J10" s="5"/>
+      <c r="K10" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5">
-        <v>2.09</v>
-      </c>
-      <c r="M10" s="7"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5">
+        <v>4.03</v>
+      </c>
       <c r="N10" s="7"/>
-      <c r="O10" s="5"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O10" s="7"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="5"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>3</v>
       </c>
@@ -2133,28 +2232,30 @@
         <v>50</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
-      <c r="J11" s="5" t="s">
+      <c r="J11" s="5"/>
+      <c r="K11" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5">
-        <v>4.03</v>
-      </c>
-      <c r="M11" s="7"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5">
+        <v>4.05</v>
+      </c>
       <c r="N11" s="7"/>
-      <c r="O11" s="5"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O11" s="7"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>3</v>
       </c>
@@ -2166,96 +2267,112 @@
         <v>50</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
-      <c r="J12" s="5" t="s">
+      <c r="J12" s="5"/>
+      <c r="K12" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5">
-        <v>4.05</v>
-      </c>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="5"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="L12" s="6">
+        <v>46209</v>
+      </c>
+      <c r="M12" s="5">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="N12" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="O12" s="7"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>200</v>
+        <v>282</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>20</v>
+        <v>154</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="H13" s="2"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="5" t="s">
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="K13" s="6">
-        <v>46182</v>
-      </c>
-      <c r="L13" s="6"/>
-      <c r="M13" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="N13" s="7"/>
-      <c r="O13" s="5"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="L13" s="17">
+        <v>46209</v>
+      </c>
+      <c r="M13" s="5">
+        <v>4.04</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="O13" s="7"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="H14" s="2"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="N14" s="7"/>
-      <c r="O14" s="5"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" s="6">
+        <v>46189</v>
+      </c>
+      <c r="M14" s="5">
+        <v>1.04</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="O14" s="7"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>3</v>
       </c>
@@ -2264,109 +2381,115 @@
         <v>12</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
-      <c r="J15" s="5" t="s">
+      <c r="J15" s="5"/>
+      <c r="K15" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K15" s="6">
+      <c r="L15" s="6">
         <v>46189</v>
       </c>
-      <c r="L15" s="5">
-        <v>1.04</v>
-      </c>
-      <c r="M15" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="N15" s="7"/>
-      <c r="O15" s="5"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M15" s="5">
+        <v>1.05</v>
+      </c>
+      <c r="N15" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="O15" s="7"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="5"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
-      <c r="J16" s="5" t="s">
+      <c r="J16" s="5"/>
+      <c r="K16" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K16" s="6">
-        <v>46189</v>
-      </c>
-      <c r="L16" s="5">
-        <v>1.05</v>
-      </c>
-      <c r="M16" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="N16" s="7"/>
-      <c r="O16" s="5"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="L16" s="6">
+        <v>46210</v>
+      </c>
+      <c r="M16" s="5">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="N16" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="O16" s="7"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="5"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>309</v>
       </c>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
-      <c r="J17" s="5" t="s">
+      <c r="J17" s="5"/>
+      <c r="K17" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K17" s="6">
-        <v>46210</v>
-      </c>
-      <c r="L17" s="5">
-        <v>2.0099999999999998</v>
-      </c>
-      <c r="M17" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="N17" s="7"/>
-      <c r="O17" s="5"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="L17" s="6">
+        <v>46206</v>
+      </c>
+      <c r="M17" s="14">
+        <v>2.1</v>
+      </c>
+      <c r="N17" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="O17" s="7"/>
+      <c r="P17" s="5"/>
+      <c r="Q17" s="5"/>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>3</v>
       </c>
@@ -2375,142 +2498,138 @@
         <v>12</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>66</v>
+        <v>324</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
-      <c r="J18" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K18" s="6">
-        <v>46206</v>
-      </c>
-      <c r="L18" s="14">
-        <v>2.1</v>
-      </c>
-      <c r="M18" s="7" t="s">
-        <v>336</v>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5">
+        <v>2.0299999999999998</v>
       </c>
       <c r="N18" s="7"/>
-      <c r="O18" s="5"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O18" s="7"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="5"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>3</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>259</v>
+        <v>223</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>119</v>
+        <v>65</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
-      <c r="J19" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K19" s="6">
-        <v>46209</v>
-      </c>
-      <c r="L19" s="5">
-        <v>4.0199999999999996</v>
-      </c>
-      <c r="M19" s="7" t="s">
-        <v>337</v>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5">
+        <v>2.04</v>
       </c>
       <c r="N19" s="7"/>
-      <c r="O19" s="5"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O19" s="7"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="5"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>284</v>
+        <v>219</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>156</v>
+        <v>59</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
-      <c r="J20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K20" s="17">
-        <v>46209</v>
-      </c>
-      <c r="L20" s="5">
-        <v>4.04</v>
-      </c>
-      <c r="M20" s="7" t="s">
-        <v>337</v>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5">
+        <v>2.0499999999999998</v>
       </c>
       <c r="N20" s="7"/>
-      <c r="O20" s="5"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O20" s="7"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="5"/>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>326</v>
+        <v>135</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>223</v>
+        <v>270</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
-      <c r="J21" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="K21" s="5"/>
-      <c r="L21" s="5">
-        <v>2.0299999999999998</v>
-      </c>
-      <c r="M21" s="7"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5">
+        <v>3.01</v>
+      </c>
       <c r="N21" s="7"/>
-      <c r="O21" s="5"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O21" s="7"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="5"/>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>3</v>
       </c>
@@ -2519,97 +2638,107 @@
         <v>12</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>64</v>
+        <v>148</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>65</v>
+        <v>149</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
-      <c r="J22" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="K22" s="5"/>
-      <c r="L22" s="5">
-        <v>2.04</v>
-      </c>
-      <c r="M22" s="7"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5">
+        <v>3.02</v>
+      </c>
       <c r="N22" s="7"/>
-      <c r="O22" s="5"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O22" s="7"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="5"/>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="H23" s="5"/>
+      <c r="H23" s="8"/>
       <c r="I23" s="5"/>
-      <c r="J23" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="K23" s="5"/>
-      <c r="L23" s="5">
-        <v>2.0499999999999998</v>
-      </c>
-      <c r="M23" s="7"/>
-      <c r="N23" s="7"/>
-      <c r="O23" s="5"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="J23" s="5"/>
+      <c r="K23" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5">
+        <v>3.03</v>
+      </c>
+      <c r="N23" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="O23" s="7"/>
+      <c r="P23" s="5"/>
+      <c r="Q23" s="5"/>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>137</v>
+        <v>13</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>272</v>
+        <v>211</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>138</v>
+        <v>43</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="H24" s="5"/>
+        <v>307</v>
+      </c>
+      <c r="H24" s="8"/>
       <c r="I24" s="5"/>
-      <c r="J24" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="K24" s="5"/>
-      <c r="L24" s="5">
-        <v>3.01</v>
-      </c>
-      <c r="M24" s="7"/>
-      <c r="N24" s="7"/>
-      <c r="O24" s="5"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="J24" s="5"/>
+      <c r="K24" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5">
+        <v>3.04</v>
+      </c>
+      <c r="N24" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="O24" s="7"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="5"/>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>3</v>
       </c>
@@ -2618,507 +2747,547 @@
         <v>12</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>150</v>
+        <v>13</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>280</v>
+        <v>209</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>151</v>
+        <v>39</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="H25" s="5"/>
+        <v>309</v>
+      </c>
+      <c r="H25" s="8"/>
       <c r="I25" s="5"/>
-      <c r="J25" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="K25" s="5"/>
-      <c r="L25" s="5">
-        <v>3.02</v>
-      </c>
-      <c r="M25" s="7"/>
-      <c r="N25" s="7"/>
-      <c r="O25" s="5"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="J25" s="5"/>
+      <c r="K25" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5">
+        <v>4.01</v>
+      </c>
+      <c r="N25" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="O25" s="7"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="5"/>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5" t="s">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>210</v>
+        <v>76</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="G26" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="L26" s="5"/>
+      <c r="M26" s="5">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="N26" s="7"/>
+      <c r="O26" s="7"/>
+      <c r="P26" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="H26" s="8"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="K26" s="5"/>
-      <c r="L26" s="5">
-        <v>3.03</v>
-      </c>
-      <c r="M26" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="N26" s="7"/>
-      <c r="O26" s="5"/>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q26" s="5">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5" t="s">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>213</v>
+        <v>339</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="H27" s="8"/>
+        <v>307</v>
+      </c>
+      <c r="H27" s="5"/>
       <c r="I27" s="5"/>
-      <c r="J27" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="K27" s="5"/>
-      <c r="L27" s="5">
-        <v>3.04</v>
-      </c>
-      <c r="M27" s="7" t="s">
-        <v>305</v>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="L27" s="5"/>
+      <c r="M27" s="5">
+        <v>5.2</v>
       </c>
       <c r="N27" s="7"/>
-      <c r="O27" s="5"/>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O27" s="7"/>
+      <c r="P27" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q27" s="5">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>3</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>39</v>
+        <v>127</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="H28" s="8"/>
+        <v>309</v>
+      </c>
+      <c r="H28" s="5"/>
       <c r="I28" s="5"/>
-      <c r="J28" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="K28" s="5"/>
-      <c r="L28" s="5">
-        <v>4.01</v>
-      </c>
-      <c r="M28" s="7" t="s">
-        <v>40</v>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5">
+        <v>5.3</v>
       </c>
       <c r="N28" s="7"/>
-      <c r="O28" s="5"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O28" s="7"/>
+      <c r="P28" s="5"/>
+      <c r="Q28" s="5"/>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>227</v>
+        <v>269</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>309</v>
       </c>
       <c r="H29" s="5"/>
       <c r="I29" s="5"/>
-      <c r="J29" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="K29" s="5"/>
-      <c r="L29" s="5">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="M29" s="7"/>
-      <c r="N29" s="7"/>
-      <c r="O29" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="J29" s="5"/>
+      <c r="K29" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="L29" s="5"/>
+      <c r="M29" s="5">
+        <v>5.4</v>
+      </c>
+      <c r="N29" s="16"/>
+      <c r="O29" s="7"/>
+      <c r="P29" s="5"/>
+      <c r="Q29" s="5"/>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>227</v>
+        <v>81</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
-      <c r="J30" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="K30" s="5"/>
-      <c r="L30" s="5">
-        <v>5.2</v>
-      </c>
-      <c r="M30" s="7"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="L30" s="5"/>
+      <c r="M30" s="5">
+        <v>5.5</v>
+      </c>
       <c r="N30" s="7"/>
-      <c r="O30" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O30" s="7"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="5"/>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>268</v>
+        <v>213</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>129</v>
+        <v>46</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
-      <c r="J31" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="K31" s="5"/>
-      <c r="L31" s="5">
-        <v>5.3</v>
-      </c>
-      <c r="M31" s="7"/>
-      <c r="N31" s="7"/>
-      <c r="O31" s="5"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="J31" s="5"/>
+      <c r="K31" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5">
+        <v>5.6</v>
+      </c>
+      <c r="N31" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="O31" s="7"/>
+      <c r="P31" s="5"/>
+      <c r="Q31" s="5"/>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>271</v>
+        <v>220</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>132</v>
+        <v>61</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
-      <c r="J32" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="K32" s="5"/>
-      <c r="L32" s="5">
-        <v>5.4</v>
-      </c>
-      <c r="M32" s="16"/>
-      <c r="N32" s="7"/>
-      <c r="O32" s="5"/>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="J32" s="5"/>
+      <c r="K32" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="L32" s="5"/>
+      <c r="M32" s="5">
+        <v>2.06</v>
+      </c>
+      <c r="N32" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="O32" s="7"/>
+      <c r="P32" s="5"/>
+      <c r="Q32" s="5"/>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>1</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>227</v>
+        <v>199</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="H33" s="5"/>
+        <v>307</v>
+      </c>
+      <c r="H33" s="1"/>
       <c r="I33" s="5"/>
-      <c r="J33" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="K33" s="5"/>
-      <c r="L33" s="5">
-        <v>5.5</v>
-      </c>
-      <c r="M33" s="7"/>
-      <c r="N33" s="7"/>
-      <c r="O33" s="5"/>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="J33" s="3"/>
+      <c r="K33" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="L33" s="6">
+        <v>46182</v>
+      </c>
+      <c r="M33" s="6"/>
+      <c r="N33" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="O33" s="7"/>
+      <c r="P33" s="5"/>
+      <c r="Q33" s="5"/>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="H34" s="5"/>
+        <v>307</v>
+      </c>
+      <c r="H34" s="8"/>
       <c r="I34" s="5"/>
-      <c r="J34" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="K34" s="5"/>
-      <c r="L34" s="5">
-        <v>5.6</v>
-      </c>
-      <c r="M34" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="N34" s="7"/>
-      <c r="O34" s="5"/>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="J34" s="5"/>
+      <c r="K34" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="L34" s="5"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="O34" s="7"/>
+      <c r="P34" s="5"/>
+      <c r="Q34" s="5"/>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="G35" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="H35" s="5"/>
+      <c r="H35" s="8"/>
       <c r="I35" s="5"/>
-      <c r="J35" s="5" t="s">
+      <c r="J35" s="9"/>
+      <c r="K35" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="K35" s="5"/>
-      <c r="L35" s="5">
-        <v>2.06</v>
-      </c>
-      <c r="M35" s="7" t="s">
-        <v>332</v>
-      </c>
-      <c r="N35" s="7"/>
-      <c r="O35" s="5"/>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="O35" s="7"/>
+      <c r="P35" s="5"/>
+      <c r="Q35" s="5"/>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>1</v>
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="H36" s="1"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="K36" s="6">
-        <v>46182</v>
-      </c>
-      <c r="L36" s="6"/>
-      <c r="M36" s="7" t="s">
-        <v>332</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="H36" s="8"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="L36" s="5"/>
+      <c r="M36" s="5"/>
       <c r="N36" s="7"/>
-      <c r="O36" s="5"/>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O36" s="7"/>
+      <c r="P36" s="5"/>
+      <c r="Q36" s="5"/>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5" t="s">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="H37" s="8"/>
+        <v>307</v>
+      </c>
+      <c r="H37" s="5"/>
       <c r="I37" s="5"/>
-      <c r="J37" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="K37" s="5"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L37" s="5"/>
-      <c r="M37" s="7" t="s">
-        <v>42</v>
-      </c>
+      <c r="M37" s="5"/>
       <c r="N37" s="7"/>
-      <c r="O37" s="5"/>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O37" s="7"/>
+      <c r="P37" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q37" s="5">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="G38" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="L38" s="5"/>
+      <c r="M38" s="5"/>
+      <c r="N38" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="O38" s="7"/>
+      <c r="P38" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="H38" s="8"/>
-      <c r="I38" s="9"/>
-      <c r="J38" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="K38" s="5"/>
-      <c r="L38" s="5"/>
-      <c r="M38" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="N38" s="7"/>
-      <c r="O38" s="5"/>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q38" s="5">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>51</v>
+        <v>107</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="H39" s="8"/>
+        <v>307</v>
+      </c>
+      <c r="H39" s="5"/>
       <c r="I39" s="5"/>
-      <c r="J39" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="K39" s="5"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L39" s="5"/>
-      <c r="M39" s="7"/>
-      <c r="N39" s="7"/>
-      <c r="O39" s="5"/>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M39" s="5"/>
+      <c r="N39" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="O39" s="7"/>
+      <c r="P39" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q39" s="5">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>0</v>
       </c>
@@ -3130,129 +3299,131 @@
         <v>50</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
-      <c r="J40" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K40" s="5"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L40" s="5"/>
-      <c r="M40" s="7"/>
+      <c r="M40" s="5"/>
       <c r="N40" s="7"/>
-      <c r="O40" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O40" s="7"/>
+      <c r="P40" s="5"/>
+      <c r="Q40" s="5"/>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H41" s="5"/>
       <c r="I41" s="5"/>
-      <c r="J41" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K41" s="5"/>
+      <c r="J41" s="5"/>
+      <c r="K41" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L41" s="5"/>
-      <c r="M41" s="7" t="s">
-        <v>315</v>
-      </c>
+      <c r="M41" s="5"/>
       <c r="N41" s="7"/>
-      <c r="O41" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O41" s="7"/>
+      <c r="P41" s="5"/>
+      <c r="Q41" s="5"/>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H42" s="5"/>
       <c r="I42" s="5"/>
-      <c r="J42" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K42" s="5"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L42" s="5"/>
-      <c r="M42" s="7" t="s">
-        <v>316</v>
-      </c>
+      <c r="M42" s="5"/>
       <c r="N42" s="7"/>
-      <c r="O42" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A43" s="5">
+      <c r="O42" s="7"/>
+      <c r="P42" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q42" s="5">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A43" s="10">
         <v>0</v>
       </c>
       <c r="B43" s="5"/>
-      <c r="C43" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="G43" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="H43" s="5"/>
-      <c r="I43" s="5"/>
-      <c r="J43" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K43" s="5"/>
-      <c r="L43" s="5"/>
-      <c r="M43" s="7"/>
-      <c r="N43" s="7"/>
-      <c r="O43" s="5"/>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C43" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="G43" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="H43" s="10"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="L43" s="10"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="11"/>
+      <c r="O43" s="11"/>
+      <c r="P43" s="10"/>
+      <c r="Q43" s="10"/>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
         <v>0</v>
       </c>
@@ -3264,96 +3435,104 @@
         <v>50</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H44" s="5"/>
       <c r="I44" s="5"/>
-      <c r="J44" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K44" s="5"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L44" s="5"/>
-      <c r="M44" s="7"/>
+      <c r="M44" s="5"/>
       <c r="N44" s="7"/>
-      <c r="O44" s="5"/>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O44" s="7"/>
+      <c r="P44" s="5"/>
+      <c r="Q44" s="5"/>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H45" s="5"/>
       <c r="I45" s="5"/>
-      <c r="J45" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K45" s="5"/>
+      <c r="J45" s="5"/>
+      <c r="K45" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L45" s="5"/>
-      <c r="M45" s="7"/>
+      <c r="M45" s="5"/>
       <c r="N45" s="7"/>
-      <c r="O45" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A46" s="10">
-        <v>0</v>
+      <c r="O45" s="7"/>
+      <c r="P45" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q45" s="5">
+        <v>2.0099999999999998</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A46" s="5">
+        <v>1</v>
       </c>
       <c r="B46" s="5"/>
-      <c r="C46" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="D46" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="E46" s="10" t="s">
-        <v>227</v>
-      </c>
-      <c r="F46" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="G46" s="10" t="s">
-        <v>309</v>
-      </c>
-      <c r="H46" s="10"/>
-      <c r="I46" s="10"/>
-      <c r="J46" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K46" s="10"/>
-      <c r="L46" s="10"/>
-      <c r="M46" s="11"/>
-      <c r="N46" s="11"/>
-      <c r="O46" s="10"/>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C46" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="H46" s="5"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="5"/>
+      <c r="K46" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="L46" s="5"/>
+      <c r="M46" s="5"/>
+      <c r="N46" s="7"/>
+      <c r="O46" s="7"/>
+      <c r="P46" s="5"/>
+      <c r="Q46" s="5"/>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>50</v>
@@ -3362,23 +3541,25 @@
         <v>227</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H47" s="5"/>
       <c r="I47" s="5"/>
-      <c r="J47" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K47" s="5"/>
+      <c r="J47" s="5"/>
+      <c r="K47" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L47" s="5"/>
-      <c r="M47" s="7"/>
+      <c r="M47" s="5"/>
       <c r="N47" s="7"/>
-      <c r="O47" s="5"/>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O47" s="7"/>
+      <c r="P47" s="5"/>
+      <c r="Q47" s="5"/>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
         <v>1</v>
       </c>
@@ -3390,57 +3571,61 @@
         <v>50</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H48" s="5"/>
       <c r="I48" s="5"/>
-      <c r="J48" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K48" s="5"/>
+      <c r="J48" s="5"/>
+      <c r="K48" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L48" s="5"/>
-      <c r="M48" s="7"/>
+      <c r="M48" s="5"/>
       <c r="N48" s="7"/>
-      <c r="O48" s="5"/>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O48" s="7"/>
+      <c r="P48" s="5"/>
+      <c r="Q48" s="5"/>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
         <v>1</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H49" s="5"/>
       <c r="I49" s="5"/>
-      <c r="J49" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K49" s="5"/>
+      <c r="J49" s="5"/>
+      <c r="K49" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L49" s="5"/>
-      <c r="M49" s="7"/>
+      <c r="M49" s="5"/>
       <c r="N49" s="7"/>
-      <c r="O49" s="5"/>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O49" s="7"/>
+      <c r="P49" s="5"/>
+      <c r="Q49" s="5"/>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
         <v>1</v>
       </c>
@@ -3455,23 +3640,29 @@
         <v>229</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H50" s="5"/>
       <c r="I50" s="5"/>
-      <c r="J50" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K50" s="5"/>
+      <c r="J50" s="5"/>
+      <c r="K50" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L50" s="5"/>
-      <c r="M50" s="7"/>
+      <c r="M50" s="5"/>
       <c r="N50" s="7"/>
-      <c r="O50" s="5"/>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O50" s="7"/>
+      <c r="P50" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q50" s="5">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
         <v>1</v>
       </c>
@@ -3486,54 +3677,58 @@
         <v>230</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H51" s="5"/>
       <c r="I51" s="5"/>
-      <c r="J51" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K51" s="5"/>
+      <c r="J51" s="5"/>
+      <c r="K51" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L51" s="5"/>
-      <c r="M51" s="7"/>
+      <c r="M51" s="5"/>
       <c r="N51" s="7"/>
-      <c r="O51" s="5"/>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O51" s="7"/>
+      <c r="P51" s="5"/>
+      <c r="Q51" s="5"/>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
         <v>1</v>
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H52" s="5"/>
       <c r="I52" s="5"/>
-      <c r="J52" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K52" s="5"/>
+      <c r="J52" s="5"/>
+      <c r="K52" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L52" s="5"/>
-      <c r="M52" s="7"/>
+      <c r="M52" s="5"/>
       <c r="N52" s="7"/>
-      <c r="O52" s="5"/>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O52" s="7"/>
+      <c r="P52" s="5"/>
+      <c r="Q52" s="5"/>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
         <v>1</v>
       </c>
@@ -3548,31 +3743,31 @@
         <v>231</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H53" s="5"/>
       <c r="I53" s="5"/>
-      <c r="J53" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K53" s="5"/>
+      <c r="J53" s="5"/>
+      <c r="K53" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L53" s="5"/>
-      <c r="M53" s="7"/>
+      <c r="M53" s="5"/>
       <c r="N53" s="7"/>
-      <c r="O53" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O53" s="7"/>
+      <c r="P53" s="5"/>
+      <c r="Q53" s="5"/>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
         <v>1</v>
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>50</v>
@@ -3581,54 +3776,62 @@
         <v>232</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H54" s="5"/>
       <c r="I54" s="5"/>
-      <c r="J54" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K54" s="5"/>
+      <c r="J54" s="5"/>
+      <c r="K54" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L54" s="5"/>
-      <c r="M54" s="7"/>
+      <c r="M54" s="5"/>
       <c r="N54" s="7"/>
-      <c r="O54" s="5"/>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O54" s="7"/>
+      <c r="P54" s="5"/>
+      <c r="Q54" s="5"/>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
         <v>1</v>
       </c>
       <c r="B55" s="5"/>
       <c r="C55" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>88</v>
+        <v>318</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H55" s="5"/>
       <c r="I55" s="5"/>
-      <c r="J55" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K55" s="5"/>
+      <c r="J55" s="5"/>
+      <c r="K55" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L55" s="5"/>
-      <c r="M55" s="7"/>
+      <c r="M55" s="5"/>
       <c r="N55" s="7"/>
-      <c r="O55" s="5"/>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O55" s="7"/>
+      <c r="P55" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q55" s="5">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
         <v>1</v>
       </c>
@@ -3640,28 +3843,34 @@
         <v>50</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>233</v>
+        <v>351</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>89</v>
+        <v>345</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H56" s="5"/>
       <c r="I56" s="5"/>
-      <c r="J56" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K56" s="5"/>
+      <c r="J56" s="5"/>
+      <c r="K56" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L56" s="5"/>
-      <c r="M56" s="7"/>
+      <c r="M56" s="5"/>
       <c r="N56" s="7"/>
-      <c r="O56" s="5"/>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O56" s="7"/>
+      <c r="P56" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q56" s="5">
+        <v>2.02</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B57" s="5"/>
       <c r="C57" s="5" t="s">
@@ -3671,26 +3880,32 @@
         <v>50</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>234</v>
+        <v>352</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>90</v>
+        <v>346</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H57" s="5"/>
       <c r="I57" s="5"/>
-      <c r="J57" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K57" s="5"/>
+      <c r="J57" s="5"/>
+      <c r="K57" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L57" s="5"/>
-      <c r="M57" s="7"/>
+      <c r="M57" s="5"/>
       <c r="N57" s="7"/>
-      <c r="O57" s="5"/>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O57" s="7"/>
+      <c r="P57" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q57" s="5">
+        <v>2.0299999999999998</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
         <v>1</v>
       </c>
@@ -3705,87 +3920,99 @@
         <v>235</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>320</v>
+        <v>92</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H58" s="5"/>
       <c r="I58" s="5"/>
-      <c r="J58" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K58" s="5"/>
+      <c r="J58" s="5"/>
+      <c r="K58" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L58" s="5"/>
-      <c r="M58" s="7"/>
+      <c r="M58" s="5"/>
       <c r="N58" s="7"/>
-      <c r="O58" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O58" s="7"/>
+      <c r="P58" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q58" s="5">
+        <v>1.0900000000000001</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
         <v>1</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>323</v>
+        <v>236</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>321</v>
+        <v>93</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H59" s="5"/>
       <c r="I59" s="5"/>
-      <c r="J59" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K59" s="5"/>
+      <c r="J59" s="5"/>
+      <c r="K59" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L59" s="5"/>
-      <c r="M59" s="7"/>
+      <c r="M59" s="5"/>
       <c r="N59" s="7"/>
-      <c r="O59" s="5"/>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O59" s="7"/>
+      <c r="P59" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q59" s="14">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
         <v>1</v>
       </c>
       <c r="B60" s="5"/>
       <c r="C60" s="5" t="s">
-        <v>91</v>
+        <v>49</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H60" s="5"/>
       <c r="I60" s="5"/>
-      <c r="J60" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K60" s="5"/>
+      <c r="J60" s="5"/>
+      <c r="K60" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L60" s="5"/>
-      <c r="M60" s="7"/>
+      <c r="M60" s="5"/>
       <c r="N60" s="7"/>
-      <c r="O60" s="5"/>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O60" s="7"/>
+      <c r="P60" s="5"/>
+      <c r="Q60" s="5"/>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="5">
         <v>1</v>
       </c>
@@ -3800,25 +4027,25 @@
         <v>237</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H61" s="5"/>
       <c r="I61" s="5"/>
-      <c r="J61" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K61" s="5"/>
+      <c r="J61" s="5"/>
+      <c r="K61" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L61" s="5"/>
-      <c r="M61" s="7"/>
+      <c r="M61" s="5"/>
       <c r="N61" s="7"/>
-      <c r="O61" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O61" s="7"/>
+      <c r="P61" s="5"/>
+      <c r="Q61" s="5"/>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
         <v>1</v>
       </c>
@@ -3830,59 +4057,65 @@
         <v>50</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>94</v>
+        <v>51</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H62" s="5"/>
       <c r="I62" s="5"/>
-      <c r="J62" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K62" s="5"/>
+      <c r="J62" s="5"/>
+      <c r="K62" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L62" s="5"/>
-      <c r="M62" s="7"/>
+      <c r="M62" s="5"/>
       <c r="N62" s="7"/>
-      <c r="O62" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O62" s="7"/>
+      <c r="P62" s="5"/>
+      <c r="Q62" s="5"/>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="5">
         <v>1</v>
       </c>
       <c r="B63" s="5"/>
       <c r="C63" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H63" s="5"/>
       <c r="I63" s="5"/>
-      <c r="J63" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K63" s="5"/>
+      <c r="J63" s="5"/>
+      <c r="K63" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L63" s="5"/>
-      <c r="M63" s="7"/>
+      <c r="M63" s="5"/>
       <c r="N63" s="7"/>
-      <c r="O63" s="5"/>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O63" s="7"/>
+      <c r="P63" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q63" s="5">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
         <v>1</v>
       </c>
@@ -3897,23 +4130,25 @@
         <v>239</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H64" s="5"/>
       <c r="I64" s="5"/>
-      <c r="J64" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K64" s="5"/>
+      <c r="J64" s="5"/>
+      <c r="K64" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L64" s="5"/>
-      <c r="M64" s="7"/>
+      <c r="M64" s="5"/>
       <c r="N64" s="7"/>
-      <c r="O64" s="5"/>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O64" s="7"/>
+      <c r="P64" s="5"/>
+      <c r="Q64" s="5"/>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="5">
         <v>1</v>
       </c>
@@ -3925,28 +4160,30 @@
         <v>50</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>216</v>
+        <v>240</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>51</v>
+        <v>98</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H65" s="5"/>
       <c r="I65" s="5"/>
-      <c r="J65" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K65" s="5"/>
+      <c r="J65" s="5"/>
+      <c r="K65" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L65" s="5"/>
-      <c r="M65" s="7"/>
+      <c r="M65" s="5"/>
       <c r="N65" s="7"/>
-      <c r="O65" s="5"/>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O65" s="7"/>
+      <c r="P65" s="5"/>
+      <c r="Q65" s="5"/>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B66" s="5"/>
       <c r="C66" s="5" t="s">
@@ -3956,30 +4193,30 @@
         <v>50</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H66" s="5"/>
       <c r="I66" s="5"/>
-      <c r="J66" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K66" s="5"/>
+      <c r="J66" s="5"/>
+      <c r="K66" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L66" s="5"/>
-      <c r="M66" s="7"/>
+      <c r="M66" s="5"/>
       <c r="N66" s="7"/>
-      <c r="O66" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O66" s="7"/>
+      <c r="P66" s="5"/>
+      <c r="Q66" s="5"/>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B67" s="5"/>
       <c r="C67" s="5" t="s">
@@ -3989,28 +4226,34 @@
         <v>50</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H67" s="5"/>
       <c r="I67" s="5"/>
-      <c r="J67" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K67" s="5"/>
+      <c r="J67" s="5"/>
+      <c r="K67" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L67" s="5"/>
-      <c r="M67" s="7"/>
+      <c r="M67" s="5"/>
       <c r="N67" s="7"/>
-      <c r="O67" s="5"/>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O67" s="7"/>
+      <c r="P67" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q67" s="5">
+        <v>1.1200000000000001</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B68" s="5"/>
       <c r="C68" s="5" t="s">
@@ -4020,26 +4263,32 @@
         <v>50</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H68" s="5"/>
       <c r="I68" s="5"/>
-      <c r="J68" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K68" s="5"/>
+      <c r="J68" s="5"/>
+      <c r="K68" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L68" s="5"/>
-      <c r="M68" s="7"/>
+      <c r="M68" s="5"/>
       <c r="N68" s="7"/>
-      <c r="O68" s="5"/>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O68" s="7"/>
+      <c r="P68" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q68" s="5">
+        <v>1.1299999999999999</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="5">
         <v>2</v>
       </c>
@@ -4051,26 +4300,32 @@
         <v>50</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H69" s="5"/>
       <c r="I69" s="5"/>
-      <c r="J69" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K69" s="5"/>
+      <c r="J69" s="5"/>
+      <c r="K69" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L69" s="5"/>
-      <c r="M69" s="7"/>
+      <c r="M69" s="5"/>
       <c r="N69" s="7"/>
-      <c r="O69" s="5"/>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O69" s="7"/>
+      <c r="P69" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q69" s="5">
+        <v>1.1399999999999999</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
         <v>2</v>
       </c>
@@ -4082,28 +4337,28 @@
         <v>50</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H70" s="5"/>
       <c r="I70" s="5"/>
-      <c r="J70" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K70" s="5"/>
+      <c r="J70" s="5"/>
+      <c r="K70" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L70" s="5"/>
-      <c r="M70" s="7"/>
+      <c r="M70" s="5"/>
       <c r="N70" s="7"/>
-      <c r="O70" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O70" s="7"/>
+      <c r="P70" s="5"/>
+      <c r="Q70" s="5"/>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="5">
         <v>2</v>
       </c>
@@ -4115,28 +4370,32 @@
         <v>50</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H71" s="5"/>
       <c r="I71" s="5"/>
-      <c r="J71" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K71" s="5"/>
+      <c r="J71" s="5"/>
+      <c r="K71" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L71" s="5"/>
-      <c r="M71" s="7"/>
+      <c r="M71" s="5"/>
       <c r="N71" s="7"/>
-      <c r="O71" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O71" s="7"/>
+      <c r="P71" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q71" s="5">
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="5">
         <v>2</v>
       </c>
@@ -4148,92 +4407,98 @@
         <v>50</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H72" s="5"/>
       <c r="I72" s="5"/>
-      <c r="J72" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K72" s="5"/>
+      <c r="J72" s="5"/>
+      <c r="K72" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L72" s="5"/>
-      <c r="M72" s="7"/>
+      <c r="M72" s="5"/>
       <c r="N72" s="7"/>
-      <c r="O72" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O72" s="7"/>
+      <c r="P72" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q72" s="5">
+        <v>1.1599999999999999</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="5">
         <v>2</v>
       </c>
       <c r="B73" s="5"/>
       <c r="C73" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D73" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H73" s="5"/>
       <c r="I73" s="5"/>
-      <c r="J73" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K73" s="5"/>
+      <c r="J73" s="5"/>
+      <c r="K73" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L73" s="5"/>
-      <c r="M73" s="7"/>
+      <c r="M73" s="5"/>
       <c r="N73" s="7"/>
-      <c r="O73" s="5"/>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O73" s="7"/>
+      <c r="P73" s="5"/>
+      <c r="Q73" s="5"/>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="5">
         <v>2</v>
       </c>
       <c r="B74" s="5"/>
       <c r="C74" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D74" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>248</v>
+        <v>228</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H74" s="5"/>
       <c r="I74" s="5"/>
-      <c r="J74" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K74" s="5"/>
+      <c r="J74" s="5"/>
+      <c r="K74" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L74" s="5"/>
-      <c r="M74" s="7"/>
+      <c r="M74" s="5"/>
       <c r="N74" s="7"/>
-      <c r="O74" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O74" s="7"/>
+      <c r="P74" s="5"/>
+      <c r="Q74" s="5"/>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="5">
         <v>2</v>
       </c>
@@ -4245,59 +4510,65 @@
         <v>50</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="F75" s="5" t="s">
         <v>106</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H75" s="5"/>
       <c r="I75" s="5"/>
-      <c r="J75" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K75" s="5"/>
+      <c r="J75" s="5"/>
+      <c r="K75" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L75" s="5"/>
-      <c r="M75" s="7"/>
+      <c r="M75" s="5"/>
       <c r="N75" s="7"/>
-      <c r="O75" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O75" s="7"/>
+      <c r="P75" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q75" s="5">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
         <v>2</v>
       </c>
       <c r="B76" s="5"/>
       <c r="C76" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D76" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>233</v>
+        <v>322</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>89</v>
+        <v>320</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H76" s="5"/>
       <c r="I76" s="5"/>
-      <c r="J76" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K76" s="5"/>
+      <c r="J76" s="5"/>
+      <c r="K76" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L76" s="5"/>
-      <c r="M76" s="7"/>
+      <c r="M76" s="5"/>
       <c r="N76" s="7"/>
-      <c r="O76" s="5"/>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O76" s="7"/>
+      <c r="P76" s="5"/>
+      <c r="Q76" s="5"/>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="5">
         <v>2</v>
       </c>
@@ -4309,90 +4580,102 @@
         <v>50</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>230</v>
+        <v>353</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>85</v>
+        <v>347</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H77" s="5"/>
       <c r="I77" s="5"/>
-      <c r="J77" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K77" s="5"/>
+      <c r="J77" s="5"/>
+      <c r="K77" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L77" s="5"/>
-      <c r="M77" s="7"/>
+      <c r="M77" s="5"/>
       <c r="N77" s="7"/>
-      <c r="O77" s="5"/>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O77" s="7"/>
+      <c r="P77" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q77" s="5">
+        <v>2.04</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B78" s="5"/>
       <c r="C78" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D78" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>227</v>
+        <v>321</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>107</v>
+        <v>319</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H78" s="5"/>
       <c r="I78" s="5"/>
-      <c r="J78" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K78" s="5"/>
+      <c r="J78" s="5"/>
+      <c r="K78" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L78" s="5"/>
-      <c r="M78" s="7"/>
+      <c r="M78" s="5"/>
       <c r="N78" s="7"/>
-      <c r="O78" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O78" s="7"/>
+      <c r="P78" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q78" s="5">
+        <v>2.0499999999999998</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="5">
         <v>2</v>
       </c>
       <c r="B79" s="5"/>
       <c r="C79" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D79" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>324</v>
+        <v>249</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>322</v>
+        <v>108</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H79" s="5"/>
       <c r="I79" s="5"/>
-      <c r="J79" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K79" s="5"/>
+      <c r="J79" s="5"/>
+      <c r="K79" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L79" s="5"/>
-      <c r="M79" s="7"/>
+      <c r="M79" s="5"/>
       <c r="N79" s="7"/>
-      <c r="O79" s="5"/>
-    </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O79" s="7"/>
+      <c r="P79" s="5"/>
+      <c r="Q79" s="5"/>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="5">
         <v>2</v>
       </c>
@@ -4404,26 +4687,32 @@
         <v>50</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>245</v>
+        <v>354</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>102</v>
+        <v>348</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H80" s="5"/>
       <c r="I80" s="5"/>
-      <c r="J80" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K80" s="5"/>
+      <c r="J80" s="5"/>
+      <c r="K80" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L80" s="5"/>
-      <c r="M80" s="7"/>
+      <c r="M80" s="5"/>
       <c r="N80" s="7"/>
-      <c r="O80" s="5"/>
-    </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O80" s="7"/>
+      <c r="P80" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q80" s="5">
+        <v>2.06</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="5">
         <v>2</v>
       </c>
@@ -4441,20 +4730,22 @@
         <v>109</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H81" s="5"/>
       <c r="I81" s="5"/>
-      <c r="J81" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K81" s="5"/>
+      <c r="J81" s="5"/>
+      <c r="K81" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L81" s="5"/>
-      <c r="M81" s="7"/>
+      <c r="M81" s="5"/>
       <c r="N81" s="7"/>
-      <c r="O81" s="5"/>
-    </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O81" s="7"/>
+      <c r="P81" s="5"/>
+      <c r="Q81" s="5"/>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="5">
         <v>2</v>
       </c>
@@ -4472,20 +4763,22 @@
         <v>110</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H82" s="5"/>
       <c r="I82" s="5"/>
-      <c r="J82" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K82" s="5"/>
+      <c r="J82" s="5"/>
+      <c r="K82" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L82" s="5"/>
-      <c r="M82" s="7"/>
+      <c r="M82" s="5"/>
       <c r="N82" s="7"/>
-      <c r="O82" s="5"/>
-    </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O82" s="7"/>
+      <c r="P82" s="5"/>
+      <c r="Q82" s="5"/>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="5">
         <v>2</v>
       </c>
@@ -4497,57 +4790,65 @@
         <v>50</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H83" s="5"/>
       <c r="I83" s="5"/>
-      <c r="J83" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K83" s="5"/>
+      <c r="J83" s="5"/>
+      <c r="K83" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L83" s="5"/>
-      <c r="M83" s="7"/>
+      <c r="M83" s="5"/>
       <c r="N83" s="7"/>
-      <c r="O83" s="5"/>
-    </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O83" s="7"/>
+      <c r="P83" s="5"/>
+      <c r="Q83" s="5"/>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B84" s="5"/>
       <c r="C84" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D84" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>252</v>
+        <v>283</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>111</v>
+        <v>155</v>
       </c>
       <c r="G84" s="5" t="s">
         <v>309</v>
       </c>
       <c r="H84" s="5"/>
       <c r="I84" s="5"/>
-      <c r="J84" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K84" s="5"/>
+      <c r="J84" s="5"/>
+      <c r="K84" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L84" s="5"/>
-      <c r="M84" s="7"/>
-      <c r="N84" s="7"/>
-      <c r="O84" s="5"/>
-    </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M84" s="5"/>
+      <c r="N84" s="16"/>
+      <c r="O84" s="7"/>
+      <c r="P84" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q84" s="5">
+        <v>2.0699999999999998</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="5">
         <v>2</v>
       </c>
@@ -4559,26 +4860,28 @@
         <v>50</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>253</v>
+        <v>355</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>112</v>
+        <v>349</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H85" s="5"/>
       <c r="I85" s="5"/>
-      <c r="J85" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K85" s="5"/>
+      <c r="J85" s="5"/>
+      <c r="K85" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L85" s="5"/>
-      <c r="M85" s="7"/>
+      <c r="M85" s="5"/>
       <c r="N85" s="7"/>
-      <c r="O85" s="5"/>
-    </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O85" s="7"/>
+      <c r="P85" s="5"/>
+      <c r="Q85" s="5"/>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="5">
         <v>2</v>
       </c>
@@ -4590,26 +4893,28 @@
         <v>50</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H86" s="5"/>
       <c r="I86" s="5"/>
-      <c r="J86" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K86" s="5"/>
+      <c r="J86" s="5"/>
+      <c r="K86" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L86" s="5"/>
-      <c r="M86" s="7"/>
+      <c r="M86" s="5"/>
       <c r="N86" s="7"/>
-      <c r="O86" s="5"/>
-    </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O86" s="7"/>
+      <c r="P86" s="5"/>
+      <c r="Q86" s="5"/>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="5">
         <v>2</v>
       </c>
@@ -4621,26 +4926,28 @@
         <v>50</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="F87" s="5" t="s">
         <v>113</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H87" s="5"/>
       <c r="I87" s="5"/>
-      <c r="J87" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K87" s="5"/>
+      <c r="J87" s="5"/>
+      <c r="K87" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L87" s="5"/>
-      <c r="M87" s="7"/>
+      <c r="M87" s="5"/>
       <c r="N87" s="7"/>
-      <c r="O87" s="5"/>
-    </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O87" s="7"/>
+      <c r="P87" s="5"/>
+      <c r="Q87" s="5"/>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="5">
         <v>2</v>
       </c>
@@ -4652,26 +4959,28 @@
         <v>50</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H88" s="5"/>
       <c r="I88" s="5"/>
-      <c r="J88" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K88" s="5"/>
+      <c r="J88" s="5"/>
+      <c r="K88" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L88" s="5"/>
-      <c r="M88" s="7"/>
+      <c r="M88" s="5"/>
       <c r="N88" s="7"/>
-      <c r="O88" s="5"/>
-    </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O88" s="7"/>
+      <c r="P88" s="5"/>
+      <c r="Q88" s="5"/>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="5">
         <v>2</v>
       </c>
@@ -4683,26 +4992,32 @@
         <v>50</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H89" s="5"/>
       <c r="I89" s="5"/>
-      <c r="J89" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K89" s="5"/>
+      <c r="J89" s="5"/>
+      <c r="K89" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L89" s="5"/>
-      <c r="M89" s="7"/>
+      <c r="M89" s="5"/>
       <c r="N89" s="7"/>
-      <c r="O89" s="5"/>
-    </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O89" s="7"/>
+      <c r="P89" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q89" s="5">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="5">
         <v>2</v>
       </c>
@@ -4714,28 +5029,30 @@
         <v>50</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="F90" s="5" t="s">
         <v>115</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H90" s="5"/>
       <c r="I90" s="5"/>
-      <c r="J90" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K90" s="5"/>
+      <c r="J90" s="5"/>
+      <c r="K90" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L90" s="5"/>
-      <c r="M90" s="7"/>
+      <c r="M90" s="5"/>
       <c r="N90" s="7"/>
-      <c r="O90" s="5"/>
-    </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O90" s="7"/>
+      <c r="P90" s="5"/>
+      <c r="Q90" s="5"/>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B91" s="5"/>
       <c r="C91" s="5" t="s">
@@ -4755,80 +5072,84 @@
       </c>
       <c r="H91" s="5"/>
       <c r="I91" s="5"/>
-      <c r="J91" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K91" s="5"/>
+      <c r="J91" s="5"/>
+      <c r="K91" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L91" s="5"/>
-      <c r="M91" s="7"/>
+      <c r="M91" s="5"/>
       <c r="N91" s="7"/>
-      <c r="O91" s="5"/>
-    </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O91" s="7"/>
+      <c r="P91" s="5"/>
+      <c r="Q91" s="5"/>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B92" s="5"/>
       <c r="C92" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D92" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="G92" s="5" t="s">
         <v>309</v>
       </c>
       <c r="H92" s="5"/>
       <c r="I92" s="5"/>
-      <c r="J92" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K92" s="5"/>
+      <c r="J92" s="5"/>
+      <c r="K92" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L92" s="5"/>
-      <c r="M92" s="7"/>
+      <c r="M92" s="5"/>
       <c r="N92" s="7"/>
-      <c r="O92" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O92" s="7"/>
+      <c r="P92" s="5"/>
+      <c r="Q92" s="5"/>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B93" s="5"/>
       <c r="C93" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D93" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G93" s="5" t="s">
         <v>309</v>
       </c>
       <c r="H93" s="5"/>
       <c r="I93" s="5"/>
-      <c r="J93" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K93" s="5"/>
+      <c r="J93" s="5"/>
+      <c r="K93" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L93" s="5"/>
-      <c r="M93" s="7"/>
+      <c r="M93" s="5"/>
       <c r="N93" s="7"/>
-      <c r="O93" s="5"/>
-    </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O93" s="7"/>
+      <c r="P93" s="5"/>
+      <c r="Q93" s="5"/>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" s="5">
         <v>3</v>
       </c>
@@ -4843,23 +5164,25 @@
         <v>258</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H94" s="5"/>
       <c r="I94" s="5"/>
-      <c r="J94" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K94" s="5"/>
+      <c r="J94" s="5"/>
+      <c r="K94" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L94" s="5"/>
-      <c r="M94" s="7"/>
+      <c r="M94" s="5"/>
       <c r="N94" s="7"/>
-      <c r="O94" s="5"/>
-    </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O94" s="7"/>
+      <c r="P94" s="5"/>
+      <c r="Q94" s="5"/>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="5">
         <v>3</v>
       </c>
@@ -4874,23 +5197,25 @@
         <v>258</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H95" s="5"/>
       <c r="I95" s="5"/>
-      <c r="J95" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K95" s="5"/>
+      <c r="J95" s="5"/>
+      <c r="K95" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L95" s="5"/>
-      <c r="M95" s="7"/>
+      <c r="M95" s="5"/>
       <c r="N95" s="7"/>
-      <c r="O95" s="5"/>
-    </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O95" s="7"/>
+      <c r="P95" s="5"/>
+      <c r="Q95" s="5"/>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" s="5">
         <v>3</v>
       </c>
@@ -4902,26 +5227,28 @@
         <v>50</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H96" s="5"/>
       <c r="I96" s="5"/>
-      <c r="J96" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K96" s="5"/>
+      <c r="J96" s="5"/>
+      <c r="K96" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L96" s="5"/>
-      <c r="M96" s="7"/>
+      <c r="M96" s="5"/>
       <c r="N96" s="7"/>
-      <c r="O96" s="5"/>
-    </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O96" s="7"/>
+      <c r="P96" s="5"/>
+      <c r="Q96" s="5"/>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" s="5">
         <v>3</v>
       </c>
@@ -4939,20 +5266,22 @@
         <v>121</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H97" s="5"/>
       <c r="I97" s="5"/>
-      <c r="J97" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K97" s="5"/>
+      <c r="J97" s="5"/>
+      <c r="K97" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L97" s="5"/>
-      <c r="M97" s="7"/>
+      <c r="M97" s="5"/>
       <c r="N97" s="7"/>
-      <c r="O97" s="5"/>
-    </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O97" s="7"/>
+      <c r="P97" s="5"/>
+      <c r="Q97" s="5"/>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="5">
         <v>3</v>
       </c>
@@ -4970,20 +5299,22 @@
         <v>121</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H98" s="5"/>
       <c r="I98" s="5"/>
-      <c r="J98" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K98" s="5"/>
+      <c r="J98" s="5"/>
+      <c r="K98" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L98" s="5"/>
-      <c r="M98" s="7"/>
+      <c r="M98" s="5"/>
       <c r="N98" s="7"/>
-      <c r="O98" s="5"/>
-    </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O98" s="7"/>
+      <c r="P98" s="5"/>
+      <c r="Q98" s="5"/>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" s="5">
         <v>3</v>
       </c>
@@ -4995,57 +5326,61 @@
         <v>50</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H99" s="5"/>
       <c r="I99" s="5"/>
-      <c r="J99" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K99" s="5"/>
+      <c r="J99" s="5"/>
+      <c r="K99" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L99" s="5"/>
-      <c r="M99" s="7"/>
+      <c r="M99" s="5"/>
       <c r="N99" s="7"/>
-      <c r="O99" s="5"/>
-    </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O99" s="7"/>
+      <c r="P99" s="5"/>
+      <c r="Q99" s="5"/>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" s="5">
         <v>3</v>
       </c>
       <c r="B100" s="5"/>
       <c r="C100" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D100" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H100" s="5"/>
       <c r="I100" s="5"/>
-      <c r="J100" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K100" s="5"/>
+      <c r="J100" s="5"/>
+      <c r="K100" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L100" s="5"/>
-      <c r="M100" s="7"/>
+      <c r="M100" s="5"/>
       <c r="N100" s="7"/>
-      <c r="O100" s="5"/>
-    </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O100" s="7"/>
+      <c r="P100" s="5"/>
+      <c r="Q100" s="5"/>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="5">
         <v>3</v>
       </c>
@@ -5057,26 +5392,28 @@
         <v>50</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H101" s="5"/>
       <c r="I101" s="5"/>
-      <c r="J101" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K101" s="5"/>
+      <c r="J101" s="5"/>
+      <c r="K101" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L101" s="5"/>
-      <c r="M101" s="7"/>
+      <c r="M101" s="5"/>
       <c r="N101" s="7"/>
-      <c r="O101" s="5"/>
-    </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O101" s="7"/>
+      <c r="P101" s="5"/>
+      <c r="Q101" s="5"/>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" s="5">
         <v>3</v>
       </c>
@@ -5088,26 +5425,28 @@
         <v>50</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H102" s="5"/>
       <c r="I102" s="5"/>
-      <c r="J102" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K102" s="5"/>
+      <c r="J102" s="5"/>
+      <c r="K102" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L102" s="5"/>
-      <c r="M102" s="7"/>
+      <c r="M102" s="5"/>
       <c r="N102" s="7"/>
-      <c r="O102" s="5"/>
-    </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O102" s="7"/>
+      <c r="P102" s="5"/>
+      <c r="Q102" s="5"/>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" s="5">
         <v>3</v>
       </c>
@@ -5119,32 +5458,34 @@
         <v>50</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H103" s="5"/>
       <c r="I103" s="5"/>
-      <c r="J103" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K103" s="5"/>
+      <c r="J103" s="5"/>
+      <c r="K103" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L103" s="5"/>
-      <c r="M103" s="7"/>
+      <c r="M103" s="5"/>
       <c r="N103" s="7"/>
-      <c r="O103" s="5"/>
-    </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O103" s="7"/>
+      <c r="P103" s="5"/>
+      <c r="Q103" s="5"/>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" s="5">
         <v>3</v>
       </c>
       <c r="B104" s="5"/>
       <c r="C104" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D104" s="5" t="s">
         <v>50</v>
@@ -5156,20 +5497,22 @@
         <v>124</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H104" s="5"/>
       <c r="I104" s="5"/>
-      <c r="J104" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K104" s="5"/>
+      <c r="J104" s="5"/>
+      <c r="K104" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L104" s="5"/>
-      <c r="M104" s="7"/>
+      <c r="M104" s="5"/>
       <c r="N104" s="7"/>
-      <c r="O104" s="5"/>
-    </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O104" s="7"/>
+      <c r="P104" s="5"/>
+      <c r="Q104" s="5"/>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" s="5">
         <v>3</v>
       </c>
@@ -5181,26 +5524,28 @@
         <v>50</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H105" s="5"/>
       <c r="I105" s="5"/>
-      <c r="J105" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K105" s="5"/>
+      <c r="J105" s="5"/>
+      <c r="K105" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L105" s="5"/>
-      <c r="M105" s="7"/>
+      <c r="M105" s="5"/>
       <c r="N105" s="7"/>
-      <c r="O105" s="5"/>
-    </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O105" s="7"/>
+      <c r="P105" s="5"/>
+      <c r="Q105" s="5"/>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" s="5">
         <v>3</v>
       </c>
@@ -5212,26 +5557,28 @@
         <v>50</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H106" s="5"/>
       <c r="I106" s="5"/>
-      <c r="J106" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K106" s="5"/>
+      <c r="J106" s="5"/>
+      <c r="K106" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L106" s="5"/>
-      <c r="M106" s="7"/>
+      <c r="M106" s="5"/>
       <c r="N106" s="7"/>
-      <c r="O106" s="5"/>
-    </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O106" s="7"/>
+      <c r="P106" s="5"/>
+      <c r="Q106" s="5"/>
+    </row>
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" s="5">
         <v>3</v>
       </c>
@@ -5243,26 +5590,28 @@
         <v>50</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H107" s="5"/>
       <c r="I107" s="5"/>
-      <c r="J107" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K107" s="5"/>
+      <c r="J107" s="5"/>
+      <c r="K107" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L107" s="5"/>
-      <c r="M107" s="7"/>
-      <c r="N107" s="7"/>
-      <c r="O107" s="5"/>
-    </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M107" s="5"/>
+      <c r="N107" s="16"/>
+      <c r="O107" s="7"/>
+      <c r="P107" s="5"/>
+      <c r="Q107" s="5"/>
+    </row>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" s="5">
         <v>3</v>
       </c>
@@ -5274,26 +5623,28 @@
         <v>50</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G108" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H108" s="5"/>
       <c r="I108" s="5"/>
-      <c r="J108" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K108" s="5"/>
+      <c r="J108" s="5"/>
+      <c r="K108" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L108" s="5"/>
-      <c r="M108" s="7"/>
-      <c r="N108" s="7"/>
-      <c r="O108" s="5"/>
-    </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M108" s="5"/>
+      <c r="N108" s="16"/>
+      <c r="O108" s="7"/>
+      <c r="P108" s="5"/>
+      <c r="Q108" s="5"/>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" s="5">
         <v>3</v>
       </c>
@@ -5305,26 +5656,28 @@
         <v>50</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H109" s="5"/>
       <c r="I109" s="5"/>
-      <c r="J109" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K109" s="5"/>
+      <c r="J109" s="5"/>
+      <c r="K109" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L109" s="5"/>
-      <c r="M109" s="7"/>
-      <c r="N109" s="7"/>
-      <c r="O109" s="5"/>
-    </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M109" s="5"/>
+      <c r="N109" s="16"/>
+      <c r="O109" s="7"/>
+      <c r="P109" s="5"/>
+      <c r="Q109" s="5"/>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" s="5">
         <v>3</v>
       </c>
@@ -5336,26 +5689,28 @@
         <v>50</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H110" s="5"/>
       <c r="I110" s="5"/>
-      <c r="J110" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K110" s="5"/>
+      <c r="J110" s="5"/>
+      <c r="K110" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L110" s="5"/>
-      <c r="M110" s="16"/>
-      <c r="N110" s="7"/>
-      <c r="O110" s="5"/>
-    </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M110" s="5"/>
+      <c r="N110" s="16"/>
+      <c r="O110" s="7"/>
+      <c r="P110" s="5"/>
+      <c r="Q110" s="5"/>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111" s="5">
         <v>3</v>
       </c>
@@ -5367,26 +5722,28 @@
         <v>50</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G111" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H111" s="5"/>
       <c r="I111" s="5"/>
-      <c r="J111" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K111" s="5"/>
+      <c r="J111" s="5"/>
+      <c r="K111" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L111" s="5"/>
-      <c r="M111" s="16"/>
-      <c r="N111" s="7"/>
-      <c r="O111" s="5"/>
-    </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M111" s="5"/>
+      <c r="N111" s="16"/>
+      <c r="O111" s="7"/>
+      <c r="P111" s="5"/>
+      <c r="Q111" s="5"/>
+    </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112" s="5">
         <v>3</v>
       </c>
@@ -5398,150 +5755,160 @@
         <v>50</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F112" s="5" t="s">
         <v>114</v>
       </c>
       <c r="G112" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H112" s="5"/>
       <c r="I112" s="5"/>
-      <c r="J112" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K112" s="5"/>
+      <c r="J112" s="5"/>
+      <c r="K112" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L112" s="5"/>
-      <c r="M112" s="16"/>
-      <c r="N112" s="7"/>
-      <c r="O112" s="5"/>
-    </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M112" s="5"/>
+      <c r="N112" s="16"/>
+      <c r="O112" s="7"/>
+      <c r="P112" s="5"/>
+      <c r="Q112" s="5"/>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" s="5">
         <v>3</v>
       </c>
       <c r="B113" s="5"/>
       <c r="C113" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D113" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="G113" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H113" s="5"/>
       <c r="I113" s="5"/>
-      <c r="J113" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K113" s="5"/>
+      <c r="J113" s="5"/>
+      <c r="K113" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L113" s="5"/>
-      <c r="M113" s="16"/>
-      <c r="N113" s="7"/>
-      <c r="O113" s="5"/>
-    </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M113" s="5"/>
+      <c r="N113" s="16"/>
+      <c r="O113" s="7"/>
+      <c r="P113" s="5"/>
+      <c r="Q113" s="5"/>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" s="5">
         <v>3</v>
       </c>
       <c r="B114" s="5"/>
       <c r="C114" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D114" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>270</v>
+        <v>225</v>
       </c>
       <c r="F114" s="5" t="s">
         <v>131</v>
       </c>
       <c r="G114" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H114" s="5"/>
       <c r="I114" s="5"/>
-      <c r="J114" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K114" s="5"/>
+      <c r="J114" s="5"/>
+      <c r="K114" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L114" s="5"/>
-      <c r="M114" s="16"/>
-      <c r="N114" s="7"/>
-      <c r="O114" s="5"/>
-    </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M114" s="5"/>
+      <c r="N114" s="16"/>
+      <c r="O114" s="7"/>
+      <c r="P114" s="5"/>
+      <c r="Q114" s="5"/>
+    </row>
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115" s="5">
         <v>3</v>
       </c>
       <c r="B115" s="5"/>
       <c r="C115" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D115" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>256</v>
+        <v>227</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="G115" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H115" s="5"/>
       <c r="I115" s="5"/>
-      <c r="J115" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K115" s="5"/>
+      <c r="J115" s="5"/>
+      <c r="K115" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L115" s="5"/>
-      <c r="M115" s="16"/>
-      <c r="N115" s="7"/>
-      <c r="O115" s="5"/>
-    </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M115" s="5"/>
+      <c r="N115" s="16"/>
+      <c r="O115" s="7"/>
+      <c r="P115" s="5"/>
+      <c r="Q115" s="5"/>
+    </row>
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116" s="5">
         <v>3</v>
       </c>
       <c r="B116" s="5"/>
       <c r="C116" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D116" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>117</v>
+        <v>92</v>
       </c>
       <c r="G116" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H116" s="5"/>
       <c r="I116" s="5"/>
-      <c r="J116" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K116" s="5"/>
+      <c r="J116" s="5"/>
+      <c r="K116" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L116" s="5"/>
-      <c r="M116" s="16"/>
-      <c r="N116" s="7"/>
-      <c r="O116" s="5"/>
-    </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M116" s="5"/>
+      <c r="N116" s="16"/>
+      <c r="O116" s="7"/>
+      <c r="P116" s="5"/>
+      <c r="Q116" s="5"/>
+    </row>
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117" s="5">
         <v>3</v>
       </c>
@@ -5553,26 +5920,28 @@
         <v>50</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="G117" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H117" s="5"/>
       <c r="I117" s="5"/>
-      <c r="J117" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K117" s="5"/>
+      <c r="J117" s="5"/>
+      <c r="K117" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L117" s="5"/>
-      <c r="M117" s="16"/>
-      <c r="N117" s="7"/>
-      <c r="O117" s="5"/>
-    </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M117" s="5"/>
+      <c r="N117" s="16"/>
+      <c r="O117" s="7"/>
+      <c r="P117" s="5"/>
+      <c r="Q117" s="5"/>
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118" s="5">
         <v>3</v>
       </c>
@@ -5584,26 +5953,28 @@
         <v>50</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="G118" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H118" s="5"/>
       <c r="I118" s="5"/>
-      <c r="J118" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K118" s="5"/>
+      <c r="J118" s="5"/>
+      <c r="K118" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L118" s="5"/>
-      <c r="M118" s="16"/>
-      <c r="N118" s="7"/>
-      <c r="O118" s="5"/>
-    </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M118" s="5"/>
+      <c r="N118" s="16"/>
+      <c r="O118" s="7"/>
+      <c r="P118" s="5"/>
+      <c r="Q118" s="5"/>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119" s="5">
         <v>3</v>
       </c>
@@ -5615,26 +5986,28 @@
         <v>50</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="G119" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H119" s="5"/>
       <c r="I119" s="5"/>
-      <c r="J119" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K119" s="5"/>
+      <c r="J119" s="5"/>
+      <c r="K119" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L119" s="5"/>
-      <c r="M119" s="16"/>
-      <c r="N119" s="7"/>
-      <c r="O119" s="5"/>
-    </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M119" s="5"/>
+      <c r="N119" s="16"/>
+      <c r="O119" s="7"/>
+      <c r="P119" s="5"/>
+      <c r="Q119" s="5"/>
+    </row>
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120" s="5">
         <v>3</v>
       </c>
@@ -5646,26 +6019,28 @@
         <v>50</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="G120" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H120" s="5"/>
       <c r="I120" s="5"/>
-      <c r="J120" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K120" s="5"/>
+      <c r="J120" s="5"/>
+      <c r="K120" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L120" s="5"/>
-      <c r="M120" s="16"/>
-      <c r="N120" s="7"/>
-      <c r="O120" s="5"/>
-    </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M120" s="5"/>
+      <c r="N120" s="16"/>
+      <c r="O120" s="7"/>
+      <c r="P120" s="5"/>
+      <c r="Q120" s="5"/>
+    </row>
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121" s="5">
         <v>3</v>
       </c>
@@ -5677,190 +6052,202 @@
         <v>50</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="G121" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H121" s="5"/>
       <c r="I121" s="5"/>
-      <c r="J121" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K121" s="5"/>
+      <c r="J121" s="5"/>
+      <c r="K121" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L121" s="5"/>
-      <c r="M121" s="16"/>
-      <c r="N121" s="7"/>
-      <c r="O121" s="5"/>
-    </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M121" s="5"/>
+      <c r="N121" s="16"/>
+      <c r="O121" s="7"/>
+      <c r="P121" s="5"/>
+      <c r="Q121" s="5"/>
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B122" s="5"/>
       <c r="C122" s="5" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>244</v>
+        <v>271</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>101</v>
+        <v>138</v>
       </c>
       <c r="G122" s="5" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="H122" s="5"/>
       <c r="I122" s="5"/>
-      <c r="J122" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K122" s="5"/>
+      <c r="J122" s="5"/>
+      <c r="K122" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L122" s="5"/>
-      <c r="M122" s="16"/>
-      <c r="N122" s="7"/>
-      <c r="O122" s="5"/>
-    </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M122" s="5"/>
+      <c r="N122" s="16"/>
+      <c r="O122" s="7"/>
+      <c r="P122" s="5"/>
+      <c r="Q122" s="5"/>
+    </row>
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B123" s="5"/>
       <c r="C123" s="5" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>50</v>
+        <v>139</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>248</v>
+        <v>272</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="H123" s="5"/>
       <c r="I123" s="5"/>
-      <c r="J123" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K123" s="5"/>
+      <c r="J123" s="5"/>
+      <c r="K123" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L123" s="5"/>
-      <c r="M123" s="16"/>
-      <c r="N123" s="7"/>
-      <c r="O123" s="5"/>
-    </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M123" s="5"/>
+      <c r="N123" s="16"/>
+      <c r="O123" s="7"/>
+      <c r="P123" s="5"/>
+      <c r="Q123" s="5"/>
+    </row>
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B124" s="5"/>
       <c r="C124" s="5" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>50</v>
+        <v>141</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>249</v>
+        <v>273</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>106</v>
+        <v>142</v>
       </c>
       <c r="G124" s="5" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="H124" s="5"/>
       <c r="I124" s="5"/>
-      <c r="J124" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K124" s="5"/>
+      <c r="J124" s="5"/>
+      <c r="K124" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L124" s="5"/>
-      <c r="M124" s="16"/>
-      <c r="N124" s="7"/>
-      <c r="O124" s="5"/>
-    </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M124" s="5"/>
+      <c r="N124" s="16"/>
+      <c r="O124" s="7"/>
+      <c r="P124" s="5"/>
+      <c r="Q124" s="5"/>
+    </row>
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125" s="5">
         <v>2</v>
       </c>
       <c r="B125" s="5"/>
       <c r="C125" s="5" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>139</v>
+        <v>13</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>273</v>
+        <v>199</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>140</v>
+        <v>22</v>
       </c>
       <c r="G125" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H125" s="5"/>
       <c r="I125" s="5"/>
-      <c r="J125" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K125" s="5"/>
+      <c r="J125" s="5"/>
+      <c r="K125" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L125" s="5"/>
-      <c r="M125" s="16"/>
-      <c r="N125" s="7"/>
-      <c r="O125" s="5"/>
-    </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M125" s="5"/>
+      <c r="N125" s="16"/>
+      <c r="O125" s="7"/>
+      <c r="P125" s="5"/>
+      <c r="Q125" s="5"/>
+    </row>
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B126" s="5"/>
       <c r="C126" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>141</v>
+        <v>13</v>
       </c>
       <c r="E126" s="5" t="s">
         <v>274</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G126" s="5" t="s">
         <v>309</v>
       </c>
       <c r="H126" s="5"/>
       <c r="I126" s="5"/>
-      <c r="J126" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K126" s="5"/>
+      <c r="J126" s="5"/>
+      <c r="K126" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L126" s="5"/>
-      <c r="M126" s="16"/>
-      <c r="N126" s="7"/>
-      <c r="O126" s="5"/>
-    </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M126" s="5"/>
+      <c r="N126" s="16"/>
+      <c r="O126" s="7"/>
+      <c r="P126" s="5"/>
+      <c r="Q126" s="5"/>
+    </row>
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B127" s="5"/>
       <c r="C127" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>143</v>
+        <v>13</v>
       </c>
       <c r="E127" s="5" t="s">
         <v>275</v>
@@ -5873,47 +6260,51 @@
       </c>
       <c r="H127" s="5"/>
       <c r="I127" s="5"/>
-      <c r="J127" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K127" s="5"/>
+      <c r="J127" s="5"/>
+      <c r="K127" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L127" s="5"/>
-      <c r="M127" s="16"/>
-      <c r="N127" s="7"/>
-      <c r="O127" s="5"/>
-    </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M127" s="5"/>
+      <c r="N127" s="16"/>
+      <c r="O127" s="7"/>
+      <c r="P127" s="5"/>
+      <c r="Q127" s="5"/>
+    </row>
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B128" s="5"/>
       <c r="C128" s="5" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>201</v>
+        <v>276</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>22</v>
+        <v>146</v>
       </c>
       <c r="G128" s="5" t="s">
         <v>309</v>
       </c>
       <c r="H128" s="5"/>
       <c r="I128" s="5"/>
-      <c r="J128" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K128" s="5"/>
+      <c r="J128" s="5"/>
+      <c r="K128" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L128" s="5"/>
-      <c r="M128" s="16"/>
-      <c r="N128" s="7"/>
-      <c r="O128" s="5"/>
-    </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M128" s="5"/>
+      <c r="N128" s="16"/>
+      <c r="O128" s="7"/>
+      <c r="P128" s="5"/>
+      <c r="Q128" s="5"/>
+    </row>
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129" s="5">
         <v>3</v>
       </c>
@@ -5925,26 +6316,28 @@
         <v>13</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G129" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H129" s="5"/>
       <c r="I129" s="5"/>
-      <c r="J129" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K129" s="5"/>
+      <c r="J129" s="5"/>
+      <c r="K129" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L129" s="5"/>
-      <c r="M129" s="16"/>
-      <c r="N129" s="7"/>
-      <c r="O129" s="5"/>
-    </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M129" s="5"/>
+      <c r="N129" s="16"/>
+      <c r="O129" s="7"/>
+      <c r="P129" s="5"/>
+      <c r="Q129" s="5"/>
+    </row>
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130" s="5">
         <v>3</v>
       </c>
@@ -5956,26 +6349,28 @@
         <v>13</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="G130" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H130" s="5"/>
       <c r="I130" s="5"/>
-      <c r="J130" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K130" s="5"/>
+      <c r="J130" s="5"/>
+      <c r="K130" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L130" s="5"/>
-      <c r="M130" s="16"/>
-      <c r="N130" s="7"/>
-      <c r="O130" s="5"/>
-    </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M130" s="5"/>
+      <c r="N130" s="16"/>
+      <c r="O130" s="7"/>
+      <c r="P130" s="5"/>
+      <c r="Q130" s="5"/>
+    </row>
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131" s="5">
         <v>3</v>
       </c>
@@ -5984,29 +6379,31 @@
         <v>12</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>147</v>
+        <v>13</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G131" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H131" s="5"/>
       <c r="I131" s="5"/>
-      <c r="J131" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K131" s="5"/>
+      <c r="J131" s="5"/>
+      <c r="K131" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L131" s="5"/>
-      <c r="M131" s="16"/>
-      <c r="N131" s="7"/>
-      <c r="O131" s="5"/>
-    </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M131" s="5"/>
+      <c r="N131" s="16"/>
+      <c r="O131" s="7"/>
+      <c r="P131" s="5"/>
+      <c r="Q131" s="5"/>
+    </row>
+    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132" s="5">
         <v>3</v>
       </c>
@@ -6015,122 +6412,134 @@
         <v>12</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>13</v>
+        <v>152</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="G132" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H132" s="5"/>
       <c r="I132" s="5"/>
-      <c r="J132" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K132" s="5"/>
+      <c r="J132" s="5"/>
+      <c r="K132" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L132" s="5"/>
-      <c r="M132" s="16"/>
-      <c r="N132" s="7"/>
-      <c r="O132" s="5"/>
-    </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M132" s="5"/>
+      <c r="N132" s="16"/>
+      <c r="O132" s="7"/>
+      <c r="P132" s="5"/>
+      <c r="Q132" s="5"/>
+    </row>
+    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B133" s="5"/>
       <c r="C133" s="5" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>281</v>
+        <v>356</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>152</v>
+        <v>350</v>
       </c>
       <c r="G133" s="5" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="H133" s="5"/>
       <c r="I133" s="5"/>
-      <c r="J133" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K133" s="5"/>
+      <c r="J133" s="5"/>
+      <c r="K133" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L133" s="5"/>
-      <c r="M133" s="16"/>
+      <c r="M133" s="5"/>
       <c r="N133" s="7"/>
-      <c r="O133" s="5"/>
-    </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O133" s="7"/>
+      <c r="P133" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q133" s="5">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A134" s="5">
         <v>3</v>
       </c>
       <c r="B134" s="5"/>
       <c r="C134" s="5" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="G134" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H134" s="5"/>
       <c r="I134" s="5"/>
-      <c r="J134" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K134" s="5"/>
+      <c r="J134" s="5"/>
+      <c r="K134" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L134" s="5"/>
-      <c r="M134" s="16"/>
-      <c r="N134" s="7"/>
-      <c r="O134" s="5"/>
-    </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M134" s="5"/>
+      <c r="N134" s="16"/>
+      <c r="O134" s="7"/>
+      <c r="P134" s="5"/>
+      <c r="Q134" s="5"/>
+    </row>
+    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A135" s="5">
         <v>3</v>
       </c>
       <c r="B135" s="5"/>
       <c r="C135" s="5" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>154</v>
+        <v>50</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>283</v>
+        <v>225</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G135" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H135" s="5"/>
       <c r="I135" s="5"/>
-      <c r="J135" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K135" s="5"/>
+      <c r="J135" s="5"/>
+      <c r="K135" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L135" s="5"/>
-      <c r="M135" s="16"/>
-      <c r="N135" s="7"/>
-      <c r="O135" s="5"/>
-    </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M135" s="5"/>
+      <c r="N135" s="16"/>
+      <c r="O135" s="7"/>
+      <c r="P135" s="5"/>
+      <c r="Q135" s="5"/>
+    </row>
+    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A136" s="5">
         <v>3</v>
       </c>
@@ -6142,26 +6551,28 @@
         <v>50</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>285</v>
+        <v>225</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G136" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H136" s="5"/>
       <c r="I136" s="5"/>
-      <c r="J136" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K136" s="5"/>
+      <c r="J136" s="5"/>
+      <c r="K136" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L136" s="5"/>
-      <c r="M136" s="16"/>
-      <c r="N136" s="7"/>
-      <c r="O136" s="5"/>
-    </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M136" s="5"/>
+      <c r="N136" s="16"/>
+      <c r="O136" s="7"/>
+      <c r="P136" s="5"/>
+      <c r="Q136" s="5"/>
+    </row>
+    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A137" s="5">
         <v>3</v>
       </c>
@@ -6173,26 +6584,28 @@
         <v>50</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>286</v>
+        <v>225</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G137" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H137" s="5"/>
       <c r="I137" s="5"/>
-      <c r="J137" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K137" s="5"/>
+      <c r="J137" s="5"/>
+      <c r="K137" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L137" s="5"/>
-      <c r="M137" s="16"/>
-      <c r="N137" s="7"/>
-      <c r="O137" s="5"/>
-    </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M137" s="5"/>
+      <c r="N137" s="16"/>
+      <c r="O137" s="7"/>
+      <c r="P137" s="5"/>
+      <c r="Q137" s="5"/>
+    </row>
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A138" s="5">
         <v>3</v>
       </c>
@@ -6204,26 +6617,28 @@
         <v>50</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G138" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H138" s="5"/>
       <c r="I138" s="5"/>
-      <c r="J138" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K138" s="5"/>
+      <c r="J138" s="5"/>
+      <c r="K138" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L138" s="5"/>
-      <c r="M138" s="16"/>
-      <c r="N138" s="7"/>
-      <c r="O138" s="5"/>
-    </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M138" s="5"/>
+      <c r="N138" s="16"/>
+      <c r="O138" s="7"/>
+      <c r="P138" s="5"/>
+      <c r="Q138" s="5"/>
+    </row>
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A139" s="5">
         <v>3</v>
       </c>
@@ -6235,472 +6650,524 @@
         <v>50</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G139" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H139" s="5"/>
       <c r="I139" s="5"/>
-      <c r="J139" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K139" s="5"/>
+      <c r="J139" s="5"/>
+      <c r="K139" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L139" s="5"/>
-      <c r="M139" s="16"/>
-      <c r="N139" s="7"/>
-      <c r="O139" s="5"/>
-    </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M139" s="5"/>
+      <c r="N139" s="16"/>
+      <c r="O139" s="7"/>
+      <c r="P139" s="5"/>
+      <c r="Q139" s="5"/>
+    </row>
+    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A140" s="5">
         <v>3</v>
       </c>
       <c r="B140" s="5"/>
       <c r="C140" s="5" t="s">
-        <v>80</v>
+        <v>162</v>
       </c>
       <c r="D140" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F140" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G140" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H140" s="5"/>
       <c r="I140" s="5"/>
-      <c r="J140" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K140" s="5"/>
+      <c r="J140" s="5"/>
+      <c r="K140" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L140" s="5"/>
-      <c r="M140" s="16"/>
-      <c r="N140" s="7"/>
-      <c r="O140" s="5"/>
-    </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M140" s="5"/>
+      <c r="N140" s="16"/>
+      <c r="O140" s="7"/>
+      <c r="P140" s="5"/>
+      <c r="Q140" s="5"/>
+    </row>
+    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A141" s="5">
         <v>3</v>
       </c>
       <c r="B141" s="5"/>
       <c r="C141" s="5" t="s">
-        <v>80</v>
+        <v>162</v>
       </c>
       <c r="D141" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G141" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H141" s="5"/>
       <c r="I141" s="5"/>
-      <c r="J141" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K141" s="5"/>
+      <c r="J141" s="5"/>
+      <c r="K141" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L141" s="5"/>
-      <c r="M141" s="16"/>
-      <c r="N141" s="7"/>
-      <c r="O141" s="5"/>
-    </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M141" s="5"/>
+      <c r="N141" s="16"/>
+      <c r="O141" s="7"/>
+      <c r="P141" s="5"/>
+      <c r="Q141" s="5"/>
+    </row>
+    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A142" s="5">
         <v>3</v>
       </c>
       <c r="B142" s="5"/>
       <c r="C142" s="5" t="s">
-        <v>80</v>
+        <v>162</v>
       </c>
       <c r="D142" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G142" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H142" s="5"/>
       <c r="I142" s="5"/>
-      <c r="J142" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K142" s="5"/>
+      <c r="J142" s="5"/>
+      <c r="K142" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L142" s="5"/>
-      <c r="M142" s="16"/>
-      <c r="N142" s="7"/>
-      <c r="O142" s="5"/>
-    </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M142" s="5"/>
+      <c r="N142" s="16"/>
+      <c r="O142" s="7"/>
+      <c r="P142" s="5"/>
+      <c r="Q142" s="5"/>
+    </row>
+    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A143" s="5">
         <v>3</v>
       </c>
       <c r="B143" s="5"/>
       <c r="C143" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D143" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E143" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F143" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G143" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H143" s="5"/>
       <c r="I143" s="5"/>
-      <c r="J143" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K143" s="5"/>
+      <c r="J143" s="5"/>
+      <c r="K143" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L143" s="5"/>
-      <c r="M143" s="16"/>
-      <c r="N143" s="7"/>
-      <c r="O143" s="5"/>
-    </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M143" s="5"/>
+      <c r="N143" s="16"/>
+      <c r="O143" s="7"/>
+      <c r="P143" s="5"/>
+      <c r="Q143" s="5"/>
+    </row>
+    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A144" s="5">
         <v>3</v>
       </c>
       <c r="B144" s="5"/>
       <c r="C144" s="5" t="s">
-        <v>164</v>
+        <v>49</v>
       </c>
       <c r="D144" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F144" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G144" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H144" s="5"/>
       <c r="I144" s="5"/>
-      <c r="J144" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K144" s="5"/>
+      <c r="J144" s="5"/>
+      <c r="K144" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L144" s="5"/>
-      <c r="M144" s="16"/>
-      <c r="N144" s="7"/>
-      <c r="O144" s="5"/>
-    </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M144" s="5"/>
+      <c r="N144" s="16"/>
+      <c r="O144" s="7"/>
+      <c r="P144" s="5"/>
+      <c r="Q144" s="5"/>
+    </row>
+    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A145" s="5">
         <v>3</v>
       </c>
       <c r="B145" s="5"/>
       <c r="C145" s="5" t="s">
-        <v>164</v>
+        <v>80</v>
       </c>
       <c r="D145" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F145" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G145" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H145" s="5"/>
       <c r="I145" s="5"/>
-      <c r="J145" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K145" s="5"/>
+      <c r="J145" s="5"/>
+      <c r="K145" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L145" s="5"/>
-      <c r="M145" s="16"/>
-      <c r="N145" s="7"/>
-      <c r="O145" s="5"/>
-    </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M145" s="5"/>
+      <c r="N145" s="16"/>
+      <c r="O145" s="7"/>
+      <c r="P145" s="5"/>
+      <c r="Q145" s="5"/>
+    </row>
+    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A146" s="5">
         <v>3</v>
       </c>
       <c r="B146" s="5"/>
       <c r="C146" s="5" t="s">
-        <v>164</v>
+        <v>80</v>
       </c>
       <c r="D146" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G146" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H146" s="5"/>
       <c r="I146" s="5"/>
-      <c r="J146" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K146" s="5"/>
+      <c r="J146" s="5"/>
+      <c r="K146" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L146" s="5"/>
-      <c r="M146" s="16"/>
-      <c r="N146" s="7"/>
-      <c r="O146" s="5"/>
-    </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M146" s="5"/>
+      <c r="N146" s="16"/>
+      <c r="O146" s="7"/>
+      <c r="P146" s="5"/>
+      <c r="Q146" s="5"/>
+    </row>
+    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A147" s="5">
         <v>3</v>
       </c>
       <c r="B147" s="5"/>
       <c r="C147" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D147" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F147" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G147" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H147" s="5"/>
       <c r="I147" s="5"/>
-      <c r="J147" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K147" s="5"/>
+      <c r="J147" s="5"/>
+      <c r="K147" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="L147" s="5"/>
-      <c r="M147" s="16"/>
-      <c r="N147" s="7"/>
-      <c r="O147" s="5"/>
-    </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M147" s="5"/>
+      <c r="N147" s="16"/>
+      <c r="O147" s="7"/>
+      <c r="P147" s="5"/>
+      <c r="Q147" s="5"/>
+    </row>
+    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A148" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B148" s="5"/>
       <c r="C148" s="5" t="s">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>227</v>
+        <v>300</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G148" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="H148" s="5"/>
-      <c r="I148" s="5"/>
+        <v>309</v>
+      </c>
+      <c r="H148" s="6">
+        <v>46094</v>
+      </c>
+      <c r="I148" s="9">
+        <v>0.41666666666666669</v>
+      </c>
       <c r="J148" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K148" s="5"/>
+        <v>15</v>
+      </c>
+      <c r="K148" s="5" t="s">
+        <v>73</v>
+      </c>
       <c r="L148" s="5"/>
-      <c r="M148" s="16"/>
-      <c r="N148" s="7"/>
-      <c r="O148" s="5"/>
-    </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M148" s="5"/>
+      <c r="N148" s="16"/>
+      <c r="O148" s="7"/>
+      <c r="P148" s="5"/>
+      <c r="Q148" s="5"/>
+    </row>
+    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A149" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B149" s="5"/>
       <c r="C149" s="5" t="s">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>227</v>
+        <v>301</v>
       </c>
       <c r="F149" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G149" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="H149" s="5"/>
-      <c r="I149" s="5"/>
+        <v>309</v>
+      </c>
+      <c r="H149" s="6">
+        <v>46094</v>
+      </c>
+      <c r="I149" s="9">
+        <v>0.41666666666666669</v>
+      </c>
       <c r="J149" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K149" s="5"/>
+        <v>15</v>
+      </c>
+      <c r="K149" s="5" t="s">
+        <v>73</v>
+      </c>
       <c r="L149" s="5"/>
-      <c r="M149" s="16"/>
-      <c r="N149" s="7"/>
-      <c r="O149" s="5"/>
-    </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M149" s="5"/>
+      <c r="N149" s="16"/>
+      <c r="O149" s="7"/>
+      <c r="P149" s="5"/>
+      <c r="Q149" s="5"/>
+    </row>
+    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A150" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B150" s="5"/>
       <c r="C150" s="5" t="s">
-        <v>80</v>
+        <v>173</v>
       </c>
       <c r="D150" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>227</v>
+        <v>174</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="G150" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="H150" s="5"/>
-      <c r="I150" s="5"/>
+        <v>307</v>
+      </c>
+      <c r="H150" s="6">
+        <v>46095</v>
+      </c>
+      <c r="I150" s="9">
+        <v>0.625</v>
+      </c>
       <c r="J150" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K150" s="5"/>
+        <v>15</v>
+      </c>
+      <c r="K150" s="5" t="s">
+        <v>73</v>
+      </c>
       <c r="L150" s="5"/>
-      <c r="M150" s="16"/>
-      <c r="N150" s="7"/>
-      <c r="O150" s="5"/>
-    </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M150" s="5"/>
+      <c r="N150" s="16"/>
+      <c r="O150" s="7"/>
+      <c r="P150" s="5"/>
+      <c r="Q150" s="5"/>
+    </row>
+    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A151" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B151" s="5"/>
       <c r="C151" s="5" t="s">
-        <v>134</v>
+        <v>12</v>
       </c>
       <c r="D151" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>302</v>
+        <v>285</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G151" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H151" s="6">
-        <v>46094</v>
-      </c>
-      <c r="I151" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J151" s="5" t="s">
+        <v>46128</v>
+      </c>
+      <c r="I151" s="9">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="J151" s="5"/>
+      <c r="K151" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="K151" s="5"/>
       <c r="L151" s="5"/>
-      <c r="M151" s="16"/>
-      <c r="N151" s="7"/>
-      <c r="O151" s="5"/>
-    </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M151" s="5"/>
+      <c r="N151" s="16"/>
+      <c r="O151" s="7"/>
+      <c r="P151" s="5"/>
+      <c r="Q151" s="5"/>
+    </row>
+    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A152" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B152" s="5"/>
       <c r="C152" s="5" t="s">
-        <v>134</v>
+        <v>12</v>
       </c>
       <c r="D152" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="G152" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H152" s="6">
-        <v>46094</v>
-      </c>
-      <c r="I152" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J152" s="5" t="s">
+        <v>46139</v>
+      </c>
+      <c r="I152" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="J152" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="K152" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="K152" s="5"/>
       <c r="L152" s="5"/>
-      <c r="M152" s="16"/>
-      <c r="N152" s="7"/>
-      <c r="O152" s="5"/>
-    </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M152" s="5"/>
+      <c r="N152" s="16"/>
+      <c r="O152" s="7"/>
+      <c r="P152" s="5"/>
+      <c r="Q152" s="5"/>
+    </row>
+    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A153" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B153" s="5"/>
       <c r="C153" s="5" t="s">
-        <v>175</v>
+        <v>12</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>50</v>
+        <v>178</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>176</v>
+        <v>287</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G153" s="5" t="s">
         <v>309</v>
       </c>
       <c r="H153" s="6">
-        <v>46095</v>
-      </c>
-      <c r="I153" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J153" s="5" t="s">
+        <v>46141</v>
+      </c>
+      <c r="I153" s="9">
+        <v>0.67361111111111116</v>
+      </c>
+      <c r="J153" s="9">
+        <v>0.96527777777777779</v>
+      </c>
+      <c r="K153" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="K153" s="5"/>
       <c r="L153" s="5"/>
-      <c r="M153" s="16"/>
-      <c r="N153" s="7"/>
-      <c r="O153" s="5"/>
-    </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M153" s="5"/>
+      <c r="N153" s="16"/>
+      <c r="O153" s="7"/>
+      <c r="P153" s="5"/>
+      <c r="Q153" s="5"/>
+    </row>
+    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A154" s="5">
         <v>3</v>
       </c>
@@ -6712,28 +7179,34 @@
         <v>13</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G154" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H154" s="6">
-        <v>46128</v>
-      </c>
-      <c r="I154" s="5"/>
-      <c r="J154" s="5" t="s">
+        <v>46146</v>
+      </c>
+      <c r="I154" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J154" s="9">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K154" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="K154" s="5"/>
       <c r="L154" s="5"/>
-      <c r="M154" s="16"/>
-      <c r="N154" s="7"/>
-      <c r="O154" s="5"/>
-    </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M154" s="5"/>
+      <c r="N154" s="16"/>
+      <c r="O154" s="7"/>
+      <c r="P154" s="5"/>
+      <c r="Q154" s="5"/>
+    </row>
+    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A155" s="5">
         <v>3</v>
       </c>
@@ -6742,68 +7215,76 @@
         <v>12</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>13</v>
+        <v>181</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G155" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H155" s="6">
-        <v>46139</v>
+        <v>46147</v>
       </c>
       <c r="I155" s="9">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="J155" s="5" t="s">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="J155" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="K155" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="K155" s="5"/>
       <c r="L155" s="5"/>
-      <c r="M155" s="16"/>
-      <c r="N155" s="7"/>
-      <c r="O155" s="5"/>
-    </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M155" s="5"/>
+      <c r="N155" s="16"/>
+      <c r="O155" s="7"/>
+      <c r="P155" s="5"/>
+      <c r="Q155" s="5"/>
+    </row>
+    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A156" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B156" s="5"/>
       <c r="C156" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>180</v>
+        <v>13</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="F156" s="5" t="s">
-        <v>181</v>
+        <v>290</v>
+      </c>
+      <c r="F156" s="18" t="s">
+        <v>183</v>
       </c>
       <c r="G156" s="5" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="H156" s="6">
-        <v>46141</v>
+        <v>46147</v>
       </c>
       <c r="I156" s="9">
-        <v>0.96527777777777779</v>
-      </c>
-      <c r="J156" s="5" t="s">
+        <v>0.625</v>
+      </c>
+      <c r="J156" s="5"/>
+      <c r="K156" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="K156" s="5"/>
       <c r="L156" s="5"/>
-      <c r="M156" s="16"/>
-      <c r="N156" s="7"/>
-      <c r="O156" s="5"/>
-    </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M156" s="5"/>
+      <c r="N156" s="16"/>
+      <c r="O156" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="P156" s="5"/>
+      <c r="Q156" s="5"/>
+    </row>
+    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A157" s="5">
         <v>3</v>
       </c>
@@ -6815,30 +7296,34 @@
         <v>13</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F157" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G157" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H157" s="6">
-        <v>46146</v>
+        <v>46149</v>
       </c>
       <c r="I157" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J157" s="9">
         <v>0.41666666666666669</v>
       </c>
-      <c r="J157" s="5" t="s">
+      <c r="K157" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="K157" s="5"/>
       <c r="L157" s="5"/>
-      <c r="M157" s="16"/>
-      <c r="N157" s="7"/>
-      <c r="O157" s="5"/>
-    </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M157" s="5"/>
+      <c r="N157" s="16"/>
+      <c r="O157" s="7"/>
+      <c r="P157" s="5"/>
+      <c r="Q157" s="5"/>
+    </row>
+    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A158" s="5">
         <v>3</v>
       </c>
@@ -6847,35 +7332,37 @@
         <v>12</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G158" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H158" s="6">
-        <v>46147</v>
-      </c>
-      <c r="I158" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="J158" s="5" t="s">
+        <v>46155</v>
+      </c>
+      <c r="I158" s="5"/>
+      <c r="J158" s="9">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="K158" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="K158" s="5"/>
       <c r="L158" s="5"/>
-      <c r="M158" s="16"/>
-      <c r="N158" s="7"/>
-      <c r="O158" s="5"/>
-    </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M158" s="5"/>
+      <c r="N158" s="16"/>
+      <c r="O158" s="7"/>
+      <c r="P158" s="5"/>
+      <c r="Q158" s="5"/>
+    </row>
+    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A159" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B159" s="5"/>
       <c r="C159" s="5" t="s">
@@ -6885,32 +7372,34 @@
         <v>13</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F159" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G159" s="5" t="s">
         <v>309</v>
       </c>
       <c r="H159" s="6">
-        <v>46147</v>
+        <v>46156</v>
       </c>
       <c r="I159" s="5"/>
-      <c r="J159" s="5" t="s">
+      <c r="J159" s="9">
+        <v>0.625</v>
+      </c>
+      <c r="K159" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="K159" s="5"/>
       <c r="L159" s="5"/>
-      <c r="M159" s="16"/>
-      <c r="N159" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="O159" s="5"/>
-    </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M159" s="5"/>
+      <c r="N159" s="16"/>
+      <c r="O159" s="7"/>
+      <c r="P159" s="5"/>
+      <c r="Q159" s="5"/>
+    </row>
+    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A160" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B160" s="5"/>
       <c r="C160" s="5" t="s">
@@ -6920,65 +7409,75 @@
         <v>13</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G160" s="5" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="H160" s="6">
-        <v>46149</v>
+        <v>46163</v>
       </c>
       <c r="I160" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J160" s="5" t="s">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="J160" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="K160" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="K160" s="5"/>
       <c r="L160" s="5"/>
-      <c r="M160" s="16"/>
-      <c r="N160" s="7"/>
-      <c r="O160" s="5"/>
-    </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M160" s="5"/>
+      <c r="N160" s="16"/>
+      <c r="O160" s="7"/>
+      <c r="P160" s="5"/>
+      <c r="Q160" s="5"/>
+    </row>
+    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A161" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B161" s="5"/>
       <c r="C161" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>187</v>
+        <v>13</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="F161" s="5" t="s">
-        <v>188</v>
+        <v>295</v>
+      </c>
+      <c r="F161" s="18" t="s">
+        <v>189</v>
       </c>
       <c r="G161" s="5" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="H161" s="6">
-        <v>46155</v>
-      </c>
-      <c r="I161" s="9">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="J161" s="5" t="s">
+        <v>46164</v>
+      </c>
+      <c r="I161" s="5"/>
+      <c r="J161" s="9">
+        <v>0.375</v>
+      </c>
+      <c r="K161" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="K161" s="5"/>
       <c r="L161" s="5"/>
-      <c r="M161" s="16"/>
-      <c r="N161" s="7"/>
-      <c r="O161" s="5"/>
-    </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M161" s="5"/>
+      <c r="N161" s="16" t="s">
+        <v>340</v>
+      </c>
+      <c r="O161" s="16" t="s">
+        <v>340</v>
+      </c>
+      <c r="P161" s="5"/>
+      <c r="Q161" s="5"/>
+    </row>
+    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A162" s="5">
         <v>3</v>
       </c>
@@ -6987,35 +7486,39 @@
         <v>12</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>13</v>
+        <v>190</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G162" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H162" s="6">
-        <v>46156</v>
+        <v>46167</v>
       </c>
       <c r="I162" s="9">
-        <v>0.625</v>
-      </c>
-      <c r="J162" s="5" t="s">
+        <v>0.22916666666666666</v>
+      </c>
+      <c r="J162" s="9">
+        <v>0.5625</v>
+      </c>
+      <c r="K162" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="K162" s="5"/>
       <c r="L162" s="5"/>
-      <c r="M162" s="16"/>
-      <c r="N162" s="7"/>
-      <c r="O162" s="5"/>
-    </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M162" s="5"/>
+      <c r="N162" s="16"/>
+      <c r="O162" s="7"/>
+      <c r="P162" s="5"/>
+      <c r="Q162" s="5"/>
+    </row>
+    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A163" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B163" s="5"/>
       <c r="C163" s="5" t="s">
@@ -7025,102 +7528,118 @@
         <v>13</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G163" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="H163" s="6">
-        <v>46163</v>
+      <c r="H163" s="12">
+        <v>46170</v>
       </c>
       <c r="I163" s="9">
         <v>0.33333333333333331</v>
       </c>
-      <c r="J163" s="5" t="s">
+      <c r="J163" s="13">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K163" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="K163" s="5"/>
       <c r="L163" s="5"/>
-      <c r="M163" s="16"/>
-      <c r="N163" s="7"/>
-      <c r="O163" s="5"/>
-    </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M163" s="5"/>
+      <c r="N163" s="16"/>
+      <c r="O163" s="7"/>
+      <c r="P163" s="5"/>
+      <c r="Q163" s="5"/>
+    </row>
+    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A164" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B164" s="5"/>
       <c r="C164" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G164" s="5" t="s">
         <v>309</v>
       </c>
       <c r="H164" s="6">
-        <v>46164</v>
+        <v>46174</v>
       </c>
       <c r="I164" s="9">
-        <v>0.375</v>
-      </c>
-      <c r="J164" s="5" t="s">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="J164" s="9">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K164" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="K164" s="5"/>
       <c r="L164" s="5"/>
-      <c r="M164" s="16"/>
-      <c r="N164" s="7"/>
-      <c r="O164" s="5"/>
-    </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M164" s="5"/>
+      <c r="N164" s="16"/>
+      <c r="O164" s="7"/>
+      <c r="P164" s="5"/>
+      <c r="Q164" s="5"/>
+    </row>
+    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A165" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B165" s="5"/>
       <c r="C165" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>192</v>
+        <v>13</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="F165" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
+      </c>
+      <c r="F165" s="18" t="s">
+        <v>19</v>
       </c>
       <c r="G165" s="5" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="H165" s="6">
-        <v>46167</v>
-      </c>
-      <c r="I165" s="9">
-        <v>0.5625</v>
-      </c>
-      <c r="J165" s="5" t="s">
+        <v>46204</v>
+      </c>
+      <c r="I165" s="5"/>
+      <c r="J165" s="9">
+        <v>0.875</v>
+      </c>
+      <c r="K165" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="K165" s="5"/>
-      <c r="L165" s="5"/>
-      <c r="M165" s="16"/>
-      <c r="N165" s="7"/>
-      <c r="O165" s="5"/>
-    </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="L165" s="6">
+        <v>46182</v>
+      </c>
+      <c r="M165" s="6"/>
+      <c r="N165" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="O165" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="P165" s="5"/>
+      <c r="Q165" s="5"/>
+    </row>
+    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A166" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B166" s="5"/>
       <c r="C166" s="5" t="s">
@@ -7130,30 +7649,36 @@
         <v>13</v>
       </c>
       <c r="E166" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="F166" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
+      </c>
+      <c r="F166" s="18" t="s">
+        <v>17</v>
       </c>
       <c r="G166" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="H166" s="12">
-        <v>46170</v>
-      </c>
-      <c r="I166" s="13">
+        <v>307</v>
+      </c>
+      <c r="H166" s="6">
+        <v>46211</v>
+      </c>
+      <c r="I166" s="5"/>
+      <c r="J166" s="9">
         <v>0.41666666666666669</v>
       </c>
-      <c r="J166" s="5" t="s">
+      <c r="K166" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="K166" s="5"/>
       <c r="L166" s="5"/>
-      <c r="M166" s="16"/>
-      <c r="N166" s="7"/>
-      <c r="O166" s="5"/>
-    </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M166" s="5"/>
+      <c r="N166" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="O166" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="P166" s="5"/>
+      <c r="Q166" s="5"/>
+    </row>
+    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A167" s="5">
         <v>3</v>
       </c>
@@ -7162,33 +7687,39 @@
         <v>12</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>300</v>
+        <v>206</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>195</v>
+        <v>34</v>
       </c>
       <c r="G167" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H167" s="6">
-        <v>46174</v>
-      </c>
-      <c r="I167" s="9">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="J167" s="5" t="s">
+        <v>46213</v>
+      </c>
+      <c r="I167" s="5"/>
+      <c r="J167" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="K167" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="K167" s="5"/>
-      <c r="L167" s="5"/>
-      <c r="M167" s="16"/>
+      <c r="L167" s="6">
+        <v>46189</v>
+      </c>
+      <c r="M167" s="5">
+        <v>1.06</v>
+      </c>
       <c r="N167" s="7"/>
-      <c r="O167" s="5"/>
-    </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O167" s="7"/>
+      <c r="P167" s="5"/>
+      <c r="Q167" s="5"/>
+    </row>
+    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A168" s="5">
         <v>1</v>
       </c>
@@ -7197,219 +7728,237 @@
         <v>12</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E168" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G168" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="H168" s="6">
-        <v>46204</v>
+        <v>307</v>
+      </c>
+      <c r="H168" s="2">
+        <v>46218</v>
       </c>
       <c r="I168" s="9">
-        <v>0.875</v>
-      </c>
-      <c r="J168" s="5" t="s">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="J168" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="K168" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="K168" s="6">
+      <c r="L168" s="6">
         <v>46182</v>
       </c>
-      <c r="L168" s="6"/>
-      <c r="M168" s="7" t="s">
-        <v>328</v>
-      </c>
+      <c r="M168" s="6"/>
       <c r="N168" s="7" t="s">
-        <v>328</v>
-      </c>
-      <c r="O168" s="5"/>
-    </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
+        <v>357</v>
+      </c>
+      <c r="O168" s="7"/>
+      <c r="P168" s="5"/>
+      <c r="Q168" s="5"/>
+    </row>
+    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A169" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B169" s="5"/>
       <c r="C169" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="G169" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="H169" s="6">
-        <v>46211</v>
+      <c r="H169" s="12">
+        <v>46218</v>
       </c>
       <c r="I169" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J169" s="5" t="s">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="J169" s="13">
+        <v>0.625</v>
+      </c>
+      <c r="K169" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="K169" s="5"/>
       <c r="L169" s="5"/>
-      <c r="M169" s="7" t="s">
-        <v>333</v>
+      <c r="M169" s="5">
+        <v>2.02</v>
       </c>
       <c r="N169" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="O169" s="5"/>
-    </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
+        <v>315</v>
+      </c>
+      <c r="O169" s="7"/>
+      <c r="P169" s="5"/>
+      <c r="Q169" s="5"/>
+    </row>
+    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A170" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B170" s="5"/>
       <c r="C170" s="5" t="s">
-        <v>12</v>
+        <v>132</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>208</v>
+        <v>304</v>
       </c>
       <c r="F170" s="5" t="s">
-        <v>34</v>
+        <v>133</v>
       </c>
       <c r="G170" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="H170" s="6">
-        <v>46213</v>
-      </c>
-      <c r="I170" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="J170" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="K170" s="6">
-        <v>46189</v>
-      </c>
-      <c r="L170" s="5">
-        <v>1.06</v>
-      </c>
-      <c r="M170" s="7"/>
-      <c r="N170" s="7"/>
-      <c r="O170" s="5"/>
-    </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
+        <v>307</v>
+      </c>
+      <c r="H170" s="5"/>
+      <c r="I170" s="5"/>
+      <c r="J170" s="5"/>
+      <c r="K170" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="L170" s="5"/>
+      <c r="M170" s="5"/>
+      <c r="N170" s="16"/>
+      <c r="O170" s="7"/>
+      <c r="P170" s="5"/>
+      <c r="Q170" s="5"/>
+    </row>
+    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A171" s="5">
         <v>0</v>
       </c>
       <c r="B171" s="5"/>
       <c r="C171" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D171" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E171" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F171" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G171" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H171" s="5"/>
       <c r="I171" s="5"/>
-      <c r="J171" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="K171" s="5"/>
+      <c r="J171" s="5"/>
+      <c r="K171" s="5" t="s">
+        <v>302</v>
+      </c>
       <c r="L171" s="5"/>
-      <c r="M171" s="16"/>
-      <c r="N171" s="7"/>
-      <c r="O171" s="5"/>
-    </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M171" s="5"/>
+      <c r="N171" s="16"/>
+      <c r="O171" s="7"/>
+      <c r="P171" s="5"/>
+      <c r="Q171" s="5"/>
+    </row>
+    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A172" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B172" s="5"/>
       <c r="C172" s="5" t="s">
-        <v>134</v>
+        <v>12</v>
       </c>
       <c r="D172" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="F172" s="5" t="s">
-        <v>136</v>
+        <v>194</v>
+      </c>
+      <c r="F172" s="18" t="s">
+        <v>14</v>
       </c>
       <c r="G172" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="H172" s="5"/>
+        <v>307</v>
+      </c>
+      <c r="H172" s="6">
+        <v>46210</v>
+      </c>
       <c r="I172" s="5"/>
-      <c r="J172" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="K172" s="5"/>
+      <c r="J172" s="9">
+        <v>0.625</v>
+      </c>
+      <c r="K172" s="5" t="s">
+        <v>327</v>
+      </c>
       <c r="L172" s="5"/>
-      <c r="M172" s="16"/>
-      <c r="N172" s="7"/>
-      <c r="O172" s="5"/>
-    </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M172" s="5"/>
+      <c r="N172" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="O172" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="P172" s="5"/>
+      <c r="Q172" s="5"/>
+    </row>
+    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A173" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B173" s="5"/>
       <c r="C173" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D173" s="5" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="F173" s="5" t="s">
-        <v>14</v>
+        <v>217</v>
+      </c>
+      <c r="F173" s="18" t="s">
+        <v>55</v>
       </c>
       <c r="G173" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H173" s="6">
-        <v>46210</v>
+        <v>46218</v>
       </c>
       <c r="I173" s="9">
-        <v>0.625</v>
-      </c>
-      <c r="J173" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="K173" s="5"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J173" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="K173" s="5" t="s">
+        <v>327</v>
+      </c>
       <c r="L173" s="5"/>
-      <c r="M173" s="7" t="s">
-        <v>334</v>
+      <c r="M173" s="14">
+        <v>2.08</v>
       </c>
       <c r="N173" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="O173" s="5"/>
+        <v>342</v>
+      </c>
+      <c r="O173" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="P173" s="5"/>
+      <c r="Q173" s="5"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:O173">
+  <conditionalFormatting sqref="K2:Q173">
     <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
       <formula>"Programada"</formula>
     </cfRule>

--- a/archivos/BD_Dashboard.xlsx
+++ b/archivos/BD_Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mexscitum-my.sharepoint.com/personal/erik_torres_scitum_com_mx/Documents/Documentos/ETP/GitHub/SCITUM-AMX/archivos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="129" documentId="11_F25DC773A252ABDACC1048E8499F6DC65BDE58F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B4BEDA1-7F4A-4BD9-8B08-00B3EBE5B416}"/>
+  <xr:revisionPtr revIDLastSave="133" documentId="11_F25DC773A252ABDACC1048E8499F6DC65BDE58F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13AC1362-4657-475E-91F7-42A6E32F3F19}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
     <author>Erik Alejandro Torres Piña</author>
   </authors>
   <commentList>
-    <comment ref="F43" authorId="0" shapeId="0" xr:uid="{2F252D48-D2F5-47BC-8FC8-5F3C91252D36}">
+    <comment ref="F42" authorId="0" shapeId="0" xr:uid="{88CC45FE-6D09-445C-A9A4-C7433F8FBF6E}">
       <text>
         <r>
           <rPr>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="359">
   <si>
     <t>TIER</t>
   </si>
@@ -1087,12 +1087,6 @@
   </si>
   <si>
     <t>No hay foto. Nombre, numero de telefono, copia de identificación oficial y lista de herramientas</t>
-  </si>
-  <si>
-    <t>Compartir datos del IDC y su ID, del lado de AM se requiere presencia en sitio ya que Delta no moverá un solo cable es responsabilidad total de AM, enviar pasaporte para tramite de permisos. No hay foto de sitio</t>
-  </si>
-  <si>
-    <t>No hay foto. No requieren permisos especiales solo confirmen nombre de IDC. No se observa espacio para conexión electrica, no se observan puertos disponibles en el switch. Rack elevado, no se observa a que altura.</t>
   </si>
   <si>
     <t>HANGAR_MEX</t>
@@ -1153,13 +1147,25 @@
   </si>
   <si>
     <t>No se requieren permisos especiales solo compartan nombre del IDC. Switch administrable por el aeropuerto y el enlace es del aeropuerto. No se observa si existe espacio para contacto electrico. No hay espacio para colocar equipo, se colocaría encima del switch</t>
+  </si>
+  <si>
+    <t>Hasta nuevo aviso de AMX</t>
+  </si>
+  <si>
+    <t>Quedo integrado SDWAN sin embargo debido a que inicio la operación no fue posible ejecutar las pruebas de HA.
+Dos contratiempos. 
+La llegada del IDC no fue en tiempo  debido a que no logro encontrar estacionamiento dentro del aeropuerto.
+El IDC desconecto otro cable del Fortinet que no fue indicado en la sesión y esto presento un problema que llevo tiempo identificar.</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1219,6 +1225,13 @@
     </font>
     <font>
       <u/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Century Gothic"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Century Gothic"/>
@@ -1284,7 +1297,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1339,6 +1352,15 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1784,7 +1806,7 @@
   <sheetPr>
     <tabColor theme="5" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:Q173"/>
+  <dimension ref="A1:Q174"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.140625" bestFit="1" customWidth="1"/>
@@ -1846,47 +1868,49 @@
         <v>310</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="H2" s="2">
-        <v>46219</v>
+        <v>309</v>
+      </c>
+      <c r="H2" s="6">
+        <v>46220</v>
       </c>
       <c r="I2" s="9">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="J2" s="3">
-        <v>0.58333333333333337</v>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J2" s="9">
+        <v>0.375</v>
       </c>
       <c r="K2" s="5" t="s">
         <v>308</v>
       </c>
       <c r="L2" s="6">
-        <v>46182</v>
-      </c>
-      <c r="M2" s="6"/>
+        <v>46189</v>
+      </c>
+      <c r="M2" s="5">
+        <v>1.02</v>
+      </c>
       <c r="N2" s="7" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="O2" s="7"/>
       <c r="P2" s="5"/>
@@ -1894,44 +1918,42 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="H3" s="6">
-        <v>46220</v>
+        <v>307</v>
+      </c>
+      <c r="H3" s="2">
+        <v>46223</v>
       </c>
       <c r="I3" s="9">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="J3" s="9">
-        <v>0.375</v>
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="J3" s="3">
+        <v>0.79166666666666663</v>
       </c>
       <c r="K3" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="L3" s="6">
-        <v>46189</v>
-      </c>
+      <c r="L3" s="5"/>
       <c r="M3" s="5">
-        <v>1.02</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="O3" s="7"/>
       <c r="P3" s="5"/>
@@ -1946,35 +1968,37 @@
         <v>12</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>307</v>
       </c>
       <c r="H4" s="2">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="I4" s="9">
-        <v>0.79166666666666663</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="J4" s="3">
-        <v>0.79166666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="K4" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="L4" s="5"/>
+      <c r="L4" s="6">
+        <v>46189</v>
+      </c>
       <c r="M4" s="5">
-        <v>2.0699999999999998</v>
+        <v>1.01</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>336</v>
+        <v>316</v>
       </c>
       <c r="O4" s="7"/>
       <c r="P4" s="5"/>
@@ -1989,162 +2013,136 @@
         <v>12</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="H5" s="12">
-        <v>46225</v>
-      </c>
-      <c r="I5" s="9">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="J5" s="13">
-        <v>0.41666666666666669</v>
-      </c>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
       <c r="K5" s="5" t="s">
-        <v>308</v>
+        <v>16</v>
       </c>
       <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="7" t="s">
-        <v>315</v>
-      </c>
+      <c r="M5" s="5">
+        <v>2.09</v>
+      </c>
+      <c r="N5" s="7"/>
       <c r="O5" s="7"/>
       <c r="P5" s="5"/>
       <c r="Q5" s="5"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>207</v>
+        <v>259</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="H6" s="2">
-        <v>46226</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="H6" s="5"/>
       <c r="I6" s="5"/>
-      <c r="J6" s="3">
-        <v>0.47916666666666669</v>
-      </c>
+      <c r="J6" s="5"/>
       <c r="K6" s="5" t="s">
-        <v>308</v>
+        <v>16</v>
       </c>
       <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="7" t="s">
-        <v>337</v>
-      </c>
+      <c r="M6" s="5">
+        <v>4.03</v>
+      </c>
+      <c r="N6" s="7"/>
       <c r="O6" s="7"/>
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5" t="s">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>203</v>
+        <v>264</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>29</v>
+        <v>125</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="H7" s="2">
-        <v>46230</v>
-      </c>
-      <c r="I7" s="9">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="J7" s="3">
-        <v>0.6875</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
       <c r="K7" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="L7" s="6">
-        <v>46189</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="L7" s="5"/>
       <c r="M7" s="5">
-        <v>1.03</v>
-      </c>
-      <c r="N7" s="7" t="s">
-        <v>338</v>
-      </c>
+        <v>4.05</v>
+      </c>
+      <c r="N7" s="7"/>
       <c r="O7" s="7"/>
       <c r="P7" s="5"/>
       <c r="Q7" s="5"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>201</v>
+        <v>257</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>25</v>
+        <v>117</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="H8" s="2">
-        <v>46230</v>
-      </c>
-      <c r="I8" s="9">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0.625</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
       <c r="K8" s="5" t="s">
-        <v>308</v>
+        <v>16</v>
       </c>
       <c r="L8" s="6">
-        <v>46189</v>
+        <v>46209</v>
       </c>
       <c r="M8" s="5">
-        <v>1.01</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="O8" s="7"/>
       <c r="P8" s="5"/>
@@ -2152,23 +2150,23 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>215</v>
+        <v>282</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>52</v>
+        <v>154</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
@@ -2176,11 +2174,15 @@
       <c r="K9" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="L9" s="5"/>
+      <c r="L9" s="17">
+        <v>46209</v>
+      </c>
       <c r="M9" s="5">
-        <v>2.09</v>
-      </c>
-      <c r="N9" s="7"/>
+        <v>4.04</v>
+      </c>
+      <c r="N9" s="7" t="s">
+        <v>334</v>
+      </c>
       <c r="O9" s="7"/>
       <c r="P9" s="5"/>
       <c r="Q9" s="5"/>
@@ -2191,16 +2193,16 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>259</v>
+        <v>204</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>309</v>
@@ -2209,13 +2211,17 @@
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
       <c r="K10" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="L10" s="5"/>
+        <v>21</v>
+      </c>
+      <c r="L10" s="6">
+        <v>46189</v>
+      </c>
       <c r="M10" s="5">
-        <v>4.03</v>
-      </c>
-      <c r="N10" s="7"/>
+        <v>1.04</v>
+      </c>
+      <c r="N10" s="7" t="s">
+        <v>312</v>
+      </c>
       <c r="O10" s="7"/>
       <c r="P10" s="5"/>
       <c r="Q10" s="5"/>
@@ -2226,16 +2232,16 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>264</v>
+        <v>205</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>125</v>
+        <v>33</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>309</v>
@@ -2244,51 +2250,55 @@
       <c r="I11" s="5"/>
       <c r="J11" s="5"/>
       <c r="K11" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="L11" s="5"/>
+        <v>21</v>
+      </c>
+      <c r="L11" s="6">
+        <v>46189</v>
+      </c>
       <c r="M11" s="5">
-        <v>4.05</v>
-      </c>
-      <c r="N11" s="7"/>
+        <v>1.05</v>
+      </c>
+      <c r="N11" s="7" t="s">
+        <v>312</v>
+      </c>
       <c r="O11" s="7"/>
       <c r="P11" s="5"/>
       <c r="Q11" s="5"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>257</v>
+        <v>216</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>117</v>
+        <v>53</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
       <c r="K12" s="5" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="L12" s="6">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="M12" s="5">
-        <v>4.0199999999999996</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="O12" s="7"/>
       <c r="P12" s="5"/>
@@ -2300,16 +2310,16 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>282</v>
+        <v>224</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>154</v>
+        <v>67</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>309</v>
@@ -2318,16 +2328,16 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
       <c r="K13" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="L13" s="17">
-        <v>46209</v>
-      </c>
-      <c r="M13" s="5">
-        <v>4.04</v>
+        <v>21</v>
+      </c>
+      <c r="L13" s="6">
+        <v>46206</v>
+      </c>
+      <c r="M13" s="14">
+        <v>2.1</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="O13" s="7"/>
       <c r="P13" s="5"/>
@@ -2342,13 +2352,13 @@
         <v>12</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>30</v>
+        <v>324</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>309</v>
@@ -2357,17 +2367,13 @@
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
       <c r="K14" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L14" s="6">
-        <v>46189</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="L14" s="5"/>
       <c r="M14" s="5">
-        <v>1.04</v>
-      </c>
-      <c r="N14" s="7" t="s">
-        <v>312</v>
-      </c>
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="N14" s="7"/>
       <c r="O14" s="7"/>
       <c r="P14" s="5"/>
       <c r="Q14" s="5"/>
@@ -2381,13 +2387,13 @@
         <v>12</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>309</v>
@@ -2396,37 +2402,33 @@
       <c r="I15" s="5"/>
       <c r="J15" s="5"/>
       <c r="K15" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L15" s="6">
-        <v>46189</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="L15" s="5"/>
       <c r="M15" s="5">
-        <v>1.05</v>
-      </c>
-      <c r="N15" s="7" t="s">
-        <v>312</v>
-      </c>
+        <v>2.04</v>
+      </c>
+      <c r="N15" s="7"/>
       <c r="O15" s="7"/>
       <c r="P15" s="5"/>
       <c r="Q15" s="5"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>307</v>
@@ -2435,56 +2437,48 @@
       <c r="I16" s="5"/>
       <c r="J16" s="5"/>
       <c r="K16" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L16" s="6">
-        <v>46210</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="L16" s="5"/>
       <c r="M16" s="5">
-        <v>2.0099999999999998</v>
-      </c>
-      <c r="N16" s="7" t="s">
-        <v>332</v>
-      </c>
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="N16" s="7"/>
       <c r="O16" s="7"/>
       <c r="P16" s="5"/>
       <c r="Q16" s="5"/>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>224</v>
+        <v>270</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>67</v>
+        <v>136</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
       <c r="K17" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L17" s="6">
-        <v>46206</v>
-      </c>
-      <c r="M17" s="14">
-        <v>2.1</v>
-      </c>
-      <c r="N17" s="7" t="s">
-        <v>333</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5">
+        <v>3.01</v>
+      </c>
+      <c r="N17" s="7"/>
       <c r="O17" s="7"/>
       <c r="P17" s="5"/>
       <c r="Q17" s="5"/>
@@ -2498,13 +2492,13 @@
         <v>12</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>324</v>
+        <v>148</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>221</v>
+        <v>278</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>62</v>
+        <v>149</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>309</v>
@@ -2517,7 +2511,7 @@
       </c>
       <c r="L18" s="5"/>
       <c r="M18" s="5">
-        <v>2.0299999999999998</v>
+        <v>3.02</v>
       </c>
       <c r="N18" s="7"/>
       <c r="O18" s="7"/>
@@ -2533,18 +2527,18 @@
         <v>12</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="H19" s="5"/>
+      <c r="H19" s="8"/>
       <c r="I19" s="5"/>
       <c r="J19" s="5"/>
       <c r="K19" s="5" t="s">
@@ -2552,9 +2546,11 @@
       </c>
       <c r="L19" s="5"/>
       <c r="M19" s="5">
-        <v>2.04</v>
-      </c>
-      <c r="N19" s="7"/>
+        <v>3.03</v>
+      </c>
+      <c r="N19" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="O19" s="7"/>
       <c r="P19" s="5"/>
       <c r="Q19" s="5"/>
@@ -2568,18 +2564,18 @@
         <v>12</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="H20" s="5"/>
+      <c r="H20" s="8"/>
       <c r="I20" s="5"/>
       <c r="J20" s="5"/>
       <c r="K20" s="5" t="s">
@@ -2587,34 +2583,36 @@
       </c>
       <c r="L20" s="5"/>
       <c r="M20" s="5">
-        <v>2.0499999999999998</v>
-      </c>
-      <c r="N20" s="7"/>
+        <v>3.04</v>
+      </c>
+      <c r="N20" s="7" t="s">
+        <v>303</v>
+      </c>
       <c r="O20" s="7"/>
       <c r="P20" s="5"/>
       <c r="Q20" s="5"/>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>270</v>
+        <v>209</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>136</v>
+        <v>39</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="H21" s="5"/>
+        <v>309</v>
+      </c>
+      <c r="H21" s="8"/>
       <c r="I21" s="5"/>
       <c r="J21" s="5"/>
       <c r="K21" s="5" t="s">
@@ -2622,32 +2620,34 @@
       </c>
       <c r="L21" s="5"/>
       <c r="M21" s="5">
-        <v>3.01</v>
-      </c>
-      <c r="N21" s="7"/>
+        <v>4.01</v>
+      </c>
+      <c r="N21" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="O21" s="7"/>
       <c r="P21" s="5"/>
       <c r="Q21" s="5"/>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5" t="s">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>148</v>
+        <v>50</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>278</v>
+        <v>76</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>149</v>
+        <v>76</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
@@ -2657,34 +2657,38 @@
       </c>
       <c r="L22" s="5"/>
       <c r="M22" s="5">
-        <v>3.02</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="N22" s="7"/>
       <c r="O22" s="7"/>
-      <c r="P22" s="5"/>
-      <c r="Q22" s="5"/>
+      <c r="P22" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q22" s="5">
+        <v>1.01</v>
+      </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5" t="s">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>208</v>
+        <v>337</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="H23" s="8"/>
+        <v>307</v>
+      </c>
+      <c r="H23" s="5"/>
       <c r="I23" s="5"/>
       <c r="J23" s="5"/>
       <c r="K23" s="5" t="s">
@@ -2692,36 +2696,38 @@
       </c>
       <c r="L23" s="5"/>
       <c r="M23" s="5">
-        <v>3.03</v>
-      </c>
-      <c r="N23" s="7" t="s">
-        <v>38</v>
-      </c>
+        <v>5.2</v>
+      </c>
+      <c r="N23" s="7"/>
       <c r="O23" s="7"/>
-      <c r="P23" s="5"/>
-      <c r="Q23" s="5"/>
+      <c r="P23" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q23" s="5">
+        <v>1.02</v>
+      </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>43</v>
+        <v>127</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="H24" s="8"/>
+        <v>309</v>
+      </c>
+      <c r="H24" s="5"/>
       <c r="I24" s="5"/>
       <c r="J24" s="5"/>
       <c r="K24" s="5" t="s">
@@ -2729,11 +2735,9 @@
       </c>
       <c r="L24" s="5"/>
       <c r="M24" s="5">
-        <v>3.04</v>
-      </c>
-      <c r="N24" s="7" t="s">
-        <v>303</v>
-      </c>
+        <v>5.3</v>
+      </c>
+      <c r="N24" s="7"/>
       <c r="O24" s="7"/>
       <c r="P24" s="5"/>
       <c r="Q24" s="5"/>
@@ -2744,21 +2748,21 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>209</v>
+        <v>269</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>39</v>
+        <v>130</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="H25" s="8"/>
+      <c r="H25" s="5"/>
       <c r="I25" s="5"/>
       <c r="J25" s="5"/>
       <c r="K25" s="5" t="s">
@@ -2766,31 +2770,29 @@
       </c>
       <c r="L25" s="5"/>
       <c r="M25" s="5">
-        <v>4.01</v>
-      </c>
-      <c r="N25" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>5.4</v>
+      </c>
+      <c r="N25" s="16"/>
       <c r="O25" s="7"/>
       <c r="P25" s="5"/>
       <c r="Q25" s="5"/>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>307</v>
@@ -2803,33 +2805,29 @@
       </c>
       <c r="L26" s="5"/>
       <c r="M26" s="5">
-        <v>5.0999999999999996</v>
+        <v>5.5</v>
       </c>
       <c r="N26" s="7"/>
       <c r="O26" s="7"/>
-      <c r="P26" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q26" s="5">
-        <v>1.01</v>
-      </c>
+      <c r="P26" s="5"/>
+      <c r="Q26" s="5"/>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5" t="s">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>339</v>
+        <v>213</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="G27" s="5" t="s">
         <v>307</v>
@@ -2842,138 +2840,156 @@
       </c>
       <c r="L27" s="5"/>
       <c r="M27" s="5">
-        <v>5.2</v>
-      </c>
-      <c r="N27" s="7"/>
+        <v>5.6</v>
+      </c>
+      <c r="N27" s="7" t="s">
+        <v>48</v>
+      </c>
       <c r="O27" s="7"/>
-      <c r="P27" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q27" s="5">
-        <v>1.02</v>
-      </c>
+      <c r="P27" s="5"/>
+      <c r="Q27" s="5"/>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>266</v>
+        <v>196</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>127</v>
+        <v>18</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
+        <v>307</v>
+      </c>
+      <c r="H28" s="12">
+        <v>46225</v>
+      </c>
+      <c r="I28" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J28" s="13">
+        <v>0.41666666666666669</v>
+      </c>
       <c r="K28" s="5" t="s">
-        <v>299</v>
+        <v>36</v>
       </c>
       <c r="L28" s="5"/>
-      <c r="M28" s="5">
-        <v>5.3</v>
-      </c>
-      <c r="N28" s="7"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="7" t="s">
+        <v>356</v>
+      </c>
       <c r="O28" s="7"/>
       <c r="P28" s="5"/>
       <c r="Q28" s="5"/>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>269</v>
+        <v>207</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>130</v>
+        <v>35</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="H29" s="5"/>
+        <v>307</v>
+      </c>
+      <c r="H29" s="2">
+        <v>46226</v>
+      </c>
       <c r="I29" s="5"/>
-      <c r="J29" s="5"/>
+      <c r="J29" s="3">
+        <v>0.47916666666666669</v>
+      </c>
       <c r="K29" s="5" t="s">
-        <v>299</v>
+        <v>36</v>
       </c>
       <c r="L29" s="5"/>
-      <c r="M29" s="5">
-        <v>5.4</v>
-      </c>
-      <c r="N29" s="16"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="7" t="s">
+        <v>356</v>
+      </c>
       <c r="O29" s="7"/>
       <c r="P29" s="5"/>
       <c r="Q29" s="5"/>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5" t="s">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>81</v>
+        <v>203</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="H30" s="5"/>
-      <c r="I30" s="5"/>
-      <c r="J30" s="5"/>
+      <c r="H30" s="2">
+        <v>46230</v>
+      </c>
+      <c r="I30" s="9">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="J30" s="3">
+        <v>0.6875</v>
+      </c>
       <c r="K30" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="L30" s="5"/>
+        <v>36</v>
+      </c>
+      <c r="L30" s="6">
+        <v>46189</v>
+      </c>
       <c r="M30" s="5">
-        <v>5.5</v>
-      </c>
-      <c r="N30" s="7"/>
+        <v>1.03</v>
+      </c>
+      <c r="N30" s="7" t="s">
+        <v>356</v>
+      </c>
       <c r="O30" s="7"/>
       <c r="P30" s="5"/>
       <c r="Q30" s="5"/>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="G31" s="5" t="s">
         <v>307</v>
@@ -2982,14 +2998,14 @@
       <c r="I31" s="5"/>
       <c r="J31" s="5"/>
       <c r="K31" s="5" t="s">
-        <v>299</v>
+        <v>36</v>
       </c>
       <c r="L31" s="5"/>
       <c r="M31" s="5">
-        <v>5.6</v>
+        <v>2.06</v>
       </c>
       <c r="N31" s="7" t="s">
-        <v>48</v>
+        <v>329</v>
       </c>
       <c r="O31" s="7"/>
       <c r="P31" s="5"/>
@@ -2997,34 +3013,34 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>220</v>
+        <v>199</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="G32" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="H32" s="5"/>
+      <c r="H32" s="1"/>
       <c r="I32" s="5"/>
-      <c r="J32" s="5"/>
+      <c r="J32" s="3"/>
       <c r="K32" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="L32" s="5"/>
-      <c r="M32" s="5">
-        <v>2.06</v>
-      </c>
+      <c r="L32" s="6">
+        <v>46182</v>
+      </c>
+      <c r="M32" s="6"/>
       <c r="N32" s="7" t="s">
         <v>329</v>
       </c>
@@ -3034,7 +3050,7 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5" t="s">
@@ -3044,26 +3060,24 @@
         <v>13</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="G33" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="H33" s="1"/>
+      <c r="H33" s="8"/>
       <c r="I33" s="5"/>
-      <c r="J33" s="3"/>
+      <c r="J33" s="5"/>
       <c r="K33" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="L33" s="6">
-        <v>46182</v>
-      </c>
-      <c r="M33" s="6"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="5"/>
       <c r="N33" s="7" t="s">
-        <v>329</v>
+        <v>42</v>
       </c>
       <c r="O33" s="7"/>
       <c r="P33" s="5"/>
@@ -3071,7 +3085,7 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5" t="s">
@@ -3081,24 +3095,24 @@
         <v>13</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H34" s="8"/>
       <c r="I34" s="5"/>
-      <c r="J34" s="5"/>
+      <c r="J34" s="9"/>
       <c r="K34" s="5" t="s">
         <v>36</v>
       </c>
       <c r="L34" s="5"/>
       <c r="M34" s="5"/>
       <c r="N34" s="7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="O34" s="7"/>
       <c r="P34" s="5"/>
@@ -3106,88 +3120,90 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H35" s="8"/>
       <c r="I35" s="5"/>
-      <c r="J35" s="9"/>
+      <c r="J35" s="5"/>
       <c r="K35" s="5" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="L35" s="5"/>
       <c r="M35" s="5"/>
-      <c r="N35" s="7" t="s">
-        <v>45</v>
-      </c>
+      <c r="N35" s="7"/>
       <c r="O35" s="7"/>
       <c r="P35" s="5"/>
       <c r="Q35" s="5"/>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="G36" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="H36" s="8"/>
+      <c r="H36" s="5"/>
       <c r="I36" s="5"/>
       <c r="J36" s="5"/>
       <c r="K36" s="5" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="L36" s="5"/>
       <c r="M36" s="5"/>
       <c r="N36" s="7"/>
       <c r="O36" s="7"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="5"/>
+      <c r="P36" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q36" s="5">
+        <v>1.03</v>
+      </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="G37" s="5" t="s">
         <v>307</v>
@@ -3200,18 +3216,20 @@
       </c>
       <c r="L37" s="5"/>
       <c r="M37" s="5"/>
-      <c r="N37" s="7"/>
+      <c r="N37" s="7" t="s">
+        <v>313</v>
+      </c>
       <c r="O37" s="7"/>
       <c r="P37" s="5" t="s">
         <v>311</v>
       </c>
       <c r="Q37" s="5">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5" t="s">
@@ -3221,10 +3239,10 @@
         <v>50</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>307</v>
@@ -3238,23 +3256,23 @@
       <c r="L38" s="5"/>
       <c r="M38" s="5"/>
       <c r="N38" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O38" s="7"/>
       <c r="P38" s="5" t="s">
         <v>311</v>
       </c>
       <c r="Q38" s="5">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>50</v>
@@ -3263,7 +3281,7 @@
         <v>225</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>107</v>
+        <v>69</v>
       </c>
       <c r="G39" s="5" t="s">
         <v>307</v>
@@ -3276,16 +3294,10 @@
       </c>
       <c r="L39" s="5"/>
       <c r="M39" s="5"/>
-      <c r="N39" s="7" t="s">
-        <v>314</v>
-      </c>
+      <c r="N39" s="7"/>
       <c r="O39" s="7"/>
-      <c r="P39" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q39" s="5">
-        <v>1.05</v>
-      </c>
+      <c r="P39" s="5"/>
+      <c r="Q39" s="5"/>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
@@ -3302,7 +3314,7 @@
         <v>225</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G40" s="5" t="s">
         <v>307</v>
@@ -3335,7 +3347,7 @@
         <v>225</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G41" s="5" t="s">
         <v>307</v>
@@ -3350,95 +3362,95 @@
       <c r="M41" s="5"/>
       <c r="N41" s="7"/>
       <c r="O41" s="7"/>
-      <c r="P41" s="5"/>
-      <c r="Q41" s="5"/>
+      <c r="P41" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q41" s="5">
+        <v>1.06</v>
+      </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A42" s="5">
+      <c r="A42" s="10">
         <v>0</v>
       </c>
       <c r="B42" s="5"/>
-      <c r="C42" s="5" t="s">
+      <c r="C42" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="F42" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="G42" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="H42" s="10"/>
+      <c r="I42" s="10"/>
+      <c r="J42" s="10"/>
+      <c r="K42" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="L42" s="10"/>
+      <c r="M42" s="10"/>
+      <c r="N42" s="11"/>
+      <c r="O42" s="11"/>
+      <c r="P42" s="10"/>
+      <c r="Q42" s="10"/>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A43" s="5">
+        <v>0</v>
+      </c>
+      <c r="B43" s="5"/>
+      <c r="C43" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D42" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E42" s="5" t="s">
+      <c r="D43" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E43" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="F42" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="H42" s="5"/>
-      <c r="I42" s="5"/>
-      <c r="J42" s="5"/>
-      <c r="K42" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="L42" s="5"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="7"/>
-      <c r="O42" s="7"/>
-      <c r="P42" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q42" s="5">
-        <v>1.06</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A43" s="10">
-        <v>0</v>
-      </c>
-      <c r="B43" s="5"/>
-      <c r="C43" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="D43" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="E43" s="10" t="s">
-        <v>225</v>
-      </c>
-      <c r="F43" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="G43" s="10" t="s">
-        <v>307</v>
-      </c>
-      <c r="H43" s="10"/>
-      <c r="I43" s="10"/>
-      <c r="J43" s="10"/>
+      <c r="F43" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5"/>
+      <c r="J43" s="5"/>
       <c r="K43" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="L43" s="10"/>
-      <c r="M43" s="10"/>
-      <c r="N43" s="11"/>
-      <c r="O43" s="11"/>
-      <c r="P43" s="10"/>
-      <c r="Q43" s="10"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="5"/>
+      <c r="N43" s="7"/>
+      <c r="O43" s="7"/>
+      <c r="P43" s="5"/>
+      <c r="Q43" s="5"/>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G44" s="5" t="s">
         <v>307</v>
@@ -3453,8 +3465,12 @@
       <c r="M44" s="5"/>
       <c r="N44" s="7"/>
       <c r="O44" s="7"/>
-      <c r="P44" s="5"/>
-      <c r="Q44" s="5"/>
+      <c r="P44" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q44" s="5">
+        <v>2.0099999999999998</v>
+      </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
@@ -3462,16 +3478,16 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5" t="s">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="G45" s="5" t="s">
         <v>307</v>
@@ -3486,12 +3502,8 @@
       <c r="M45" s="5"/>
       <c r="N45" s="7"/>
       <c r="O45" s="7"/>
-      <c r="P45" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q45" s="5">
-        <v>2.0099999999999998</v>
-      </c>
+      <c r="P45" s="5"/>
+      <c r="Q45" s="5"/>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
@@ -3499,16 +3511,16 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G46" s="5" t="s">
         <v>307</v>
@@ -3538,10 +3550,10 @@
         <v>50</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G47" s="5" t="s">
         <v>307</v>
@@ -3571,10 +3583,10 @@
         <v>50</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G48" s="5" t="s">
         <v>307</v>
@@ -3604,10 +3616,10 @@
         <v>50</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G49" s="5" t="s">
         <v>307</v>
@@ -3622,8 +3634,12 @@
       <c r="M49" s="5"/>
       <c r="N49" s="7"/>
       <c r="O49" s="7"/>
-      <c r="P49" s="5"/>
-      <c r="Q49" s="5"/>
+      <c r="P49" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q49" s="5">
+        <v>1.07</v>
+      </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
@@ -3637,10 +3653,10 @@
         <v>50</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G50" s="5" t="s">
         <v>307</v>
@@ -3655,12 +3671,8 @@
       <c r="M50" s="5"/>
       <c r="N50" s="7"/>
       <c r="O50" s="7"/>
-      <c r="P50" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q50" s="5">
-        <v>1.07</v>
-      </c>
+      <c r="P50" s="5"/>
+      <c r="Q50" s="5"/>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
@@ -3668,7 +3680,7 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D51" s="5" t="s">
         <v>50</v>
@@ -3701,16 +3713,16 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G52" s="5" t="s">
         <v>307</v>
@@ -3734,16 +3746,16 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G53" s="5" t="s">
         <v>307</v>
@@ -3767,16 +3779,16 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>89</v>
+        <v>318</v>
       </c>
       <c r="G54" s="5" t="s">
         <v>307</v>
@@ -3791,8 +3803,12 @@
       <c r="M54" s="5"/>
       <c r="N54" s="7"/>
       <c r="O54" s="7"/>
-      <c r="P54" s="5"/>
-      <c r="Q54" s="5"/>
+      <c r="P54" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q54" s="5">
+        <v>1.08</v>
+      </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
@@ -3806,10 +3822,10 @@
         <v>50</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>233</v>
+        <v>349</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>318</v>
+        <v>343</v>
       </c>
       <c r="G55" s="5" t="s">
         <v>307</v>
@@ -3828,25 +3844,25 @@
         <v>311</v>
       </c>
       <c r="Q55" s="5">
-        <v>1.08</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B56" s="5"/>
       <c r="C56" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D56" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G56" s="5" t="s">
         <v>307</v>
@@ -3865,25 +3881,25 @@
         <v>311</v>
       </c>
       <c r="Q56" s="5">
-        <v>2.02</v>
+        <v>2.0299999999999998</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B57" s="5"/>
       <c r="C57" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>352</v>
+        <v>235</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>346</v>
+        <v>92</v>
       </c>
       <c r="G57" s="5" t="s">
         <v>307</v>
@@ -3902,7 +3918,7 @@
         <v>311</v>
       </c>
       <c r="Q57" s="5">
-        <v>2.0299999999999998</v>
+        <v>1.0900000000000001</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
@@ -3917,10 +3933,10 @@
         <v>50</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G58" s="5" t="s">
         <v>307</v>
@@ -3938,8 +3954,8 @@
       <c r="P58" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="Q58" s="5">
-        <v>1.0900000000000001</v>
+      <c r="Q58" s="14">
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
@@ -3948,16 +3964,16 @@
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G59" s="5" t="s">
         <v>307</v>
@@ -3972,12 +3988,8 @@
       <c r="M59" s="5"/>
       <c r="N59" s="7"/>
       <c r="O59" s="7"/>
-      <c r="P59" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q59" s="14">
-        <v>1.1000000000000001</v>
-      </c>
+      <c r="P59" s="5"/>
+      <c r="Q59" s="5"/>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
@@ -3985,16 +3997,16 @@
       </c>
       <c r="B60" s="5"/>
       <c r="C60" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G60" s="5" t="s">
         <v>307</v>
@@ -4024,10 +4036,10 @@
         <v>50</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>237</v>
+        <v>214</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="G61" s="5" t="s">
         <v>307</v>
@@ -4057,10 +4069,10 @@
         <v>50</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>214</v>
+        <v>238</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="G62" s="5" t="s">
         <v>307</v>
@@ -4075,8 +4087,12 @@
       <c r="M62" s="5"/>
       <c r="N62" s="7"/>
       <c r="O62" s="7"/>
-      <c r="P62" s="5"/>
-      <c r="Q62" s="5"/>
+      <c r="P62" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q62" s="5">
+        <v>1.1100000000000001</v>
+      </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="5">
@@ -4090,10 +4106,10 @@
         <v>50</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G63" s="5" t="s">
         <v>307</v>
@@ -4108,12 +4124,8 @@
       <c r="M63" s="5"/>
       <c r="N63" s="7"/>
       <c r="O63" s="7"/>
-      <c r="P63" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q63" s="5">
-        <v>1.1100000000000001</v>
-      </c>
+      <c r="P63" s="5"/>
+      <c r="Q63" s="5"/>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
@@ -4127,10 +4139,10 @@
         <v>50</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G64" s="5" t="s">
         <v>307</v>
@@ -4150,7 +4162,7 @@
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B65" s="5"/>
       <c r="C65" s="5" t="s">
@@ -4160,10 +4172,10 @@
         <v>50</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G65" s="5" t="s">
         <v>307</v>
@@ -4193,10 +4205,10 @@
         <v>50</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G66" s="5" t="s">
         <v>307</v>
@@ -4211,8 +4223,12 @@
       <c r="M66" s="5"/>
       <c r="N66" s="7"/>
       <c r="O66" s="7"/>
-      <c r="P66" s="5"/>
-      <c r="Q66" s="5"/>
+      <c r="P66" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q66" s="5">
+        <v>1.1200000000000001</v>
+      </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="5">
@@ -4226,10 +4242,10 @@
         <v>50</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G67" s="5" t="s">
         <v>307</v>
@@ -4248,7 +4264,7 @@
         <v>311</v>
       </c>
       <c r="Q67" s="5">
-        <v>1.1200000000000001</v>
+        <v>1.1299999999999999</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
@@ -4263,10 +4279,10 @@
         <v>50</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G68" s="5" t="s">
         <v>307</v>
@@ -4285,7 +4301,7 @@
         <v>311</v>
       </c>
       <c r="Q68" s="5">
-        <v>1.1299999999999999</v>
+        <v>1.1399999999999999</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
@@ -4300,10 +4316,10 @@
         <v>50</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G69" s="5" t="s">
         <v>307</v>
@@ -4318,12 +4334,8 @@
       <c r="M69" s="5"/>
       <c r="N69" s="7"/>
       <c r="O69" s="7"/>
-      <c r="P69" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q69" s="5">
-        <v>1.1399999999999999</v>
-      </c>
+      <c r="P69" s="5"/>
+      <c r="Q69" s="5"/>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
@@ -4337,10 +4349,10 @@
         <v>50</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G70" s="5" t="s">
         <v>307</v>
@@ -4355,8 +4367,12 @@
       <c r="M70" s="5"/>
       <c r="N70" s="7"/>
       <c r="O70" s="7"/>
-      <c r="P70" s="5"/>
-      <c r="Q70" s="5"/>
+      <c r="P70" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q70" s="5">
+        <v>1.1499999999999999</v>
+      </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="5">
@@ -4370,10 +4386,10 @@
         <v>50</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G71" s="5" t="s">
         <v>307</v>
@@ -4392,7 +4408,7 @@
         <v>311</v>
       </c>
       <c r="Q71" s="5">
-        <v>1.1499999999999999</v>
+        <v>1.1599999999999999</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
@@ -4401,16 +4417,16 @@
       </c>
       <c r="B72" s="5"/>
       <c r="C72" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D72" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="G72" s="5" t="s">
         <v>307</v>
@@ -4425,12 +4441,8 @@
       <c r="M72" s="5"/>
       <c r="N72" s="7"/>
       <c r="O72" s="7"/>
-      <c r="P72" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q72" s="5">
-        <v>1.1599999999999999</v>
-      </c>
+      <c r="P72" s="5"/>
+      <c r="Q72" s="5"/>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="5">
@@ -4444,10 +4456,10 @@
         <v>50</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G73" s="5" t="s">
         <v>307</v>
@@ -4471,16 +4483,16 @@
       </c>
       <c r="B74" s="5"/>
       <c r="C74" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D74" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="G74" s="5" t="s">
         <v>307</v>
@@ -4495,8 +4507,12 @@
       <c r="M74" s="5"/>
       <c r="N74" s="7"/>
       <c r="O74" s="7"/>
-      <c r="P74" s="5"/>
-      <c r="Q74" s="5"/>
+      <c r="P74" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q74" s="5">
+        <v>1.17</v>
+      </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="5">
@@ -4510,10 +4526,10 @@
         <v>50</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>225</v>
+        <v>322</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>106</v>
+        <v>320</v>
       </c>
       <c r="G75" s="5" t="s">
         <v>307</v>
@@ -4528,12 +4544,8 @@
       <c r="M75" s="5"/>
       <c r="N75" s="7"/>
       <c r="O75" s="7"/>
-      <c r="P75" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q75" s="5">
-        <v>1.17</v>
-      </c>
+      <c r="P75" s="5"/>
+      <c r="Q75" s="5"/>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
@@ -4541,16 +4553,16 @@
       </c>
       <c r="B76" s="5"/>
       <c r="C76" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D76" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>322</v>
+        <v>351</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>320</v>
+        <v>345</v>
       </c>
       <c r="G76" s="5" t="s">
         <v>307</v>
@@ -4565,12 +4577,16 @@
       <c r="M76" s="5"/>
       <c r="N76" s="7"/>
       <c r="O76" s="7"/>
-      <c r="P76" s="5"/>
-      <c r="Q76" s="5"/>
+      <c r="P76" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q76" s="5">
+        <v>2.04</v>
+      </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B77" s="5"/>
       <c r="C77" s="5" t="s">
@@ -4580,10 +4596,10 @@
         <v>50</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>353</v>
+        <v>321</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>347</v>
+        <v>319</v>
       </c>
       <c r="G77" s="5" t="s">
         <v>307</v>
@@ -4602,12 +4618,12 @@
         <v>311</v>
       </c>
       <c r="Q77" s="5">
-        <v>2.04</v>
+        <v>2.0499999999999998</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B78" s="5"/>
       <c r="C78" s="5" t="s">
@@ -4617,10 +4633,10 @@
         <v>50</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>321</v>
+        <v>249</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>319</v>
+        <v>108</v>
       </c>
       <c r="G78" s="5" t="s">
         <v>307</v>
@@ -4635,12 +4651,8 @@
       <c r="M78" s="5"/>
       <c r="N78" s="7"/>
       <c r="O78" s="7"/>
-      <c r="P78" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q78" s="5">
-        <v>2.0499999999999998</v>
-      </c>
+      <c r="P78" s="5"/>
+      <c r="Q78" s="5"/>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="5">
@@ -4654,10 +4666,10 @@
         <v>50</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>249</v>
+        <v>352</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>108</v>
+        <v>346</v>
       </c>
       <c r="G79" s="5" t="s">
         <v>307</v>
@@ -4672,8 +4684,12 @@
       <c r="M79" s="5"/>
       <c r="N79" s="7"/>
       <c r="O79" s="7"/>
-      <c r="P79" s="5"/>
-      <c r="Q79" s="5"/>
+      <c r="P79" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q79" s="5">
+        <v>2.06</v>
+      </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="5">
@@ -4687,10 +4703,10 @@
         <v>50</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>354</v>
+        <v>250</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>348</v>
+        <v>109</v>
       </c>
       <c r="G80" s="5" t="s">
         <v>307</v>
@@ -4705,12 +4721,8 @@
       <c r="M80" s="5"/>
       <c r="N80" s="7"/>
       <c r="O80" s="7"/>
-      <c r="P80" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q80" s="5">
-        <v>2.06</v>
-      </c>
+      <c r="P80" s="5"/>
+      <c r="Q80" s="5"/>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="5">
@@ -4724,10 +4736,10 @@
         <v>50</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G81" s="5" t="s">
         <v>307</v>
@@ -4757,10 +4769,10 @@
         <v>50</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="G82" s="5" t="s">
         <v>307</v>
@@ -4780,23 +4792,23 @@
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B83" s="5"/>
       <c r="C83" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D83" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>245</v>
+        <v>283</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>103</v>
+        <v>155</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H83" s="5"/>
       <c r="I83" s="5"/>
@@ -4806,30 +4818,34 @@
       </c>
       <c r="L83" s="5"/>
       <c r="M83" s="5"/>
-      <c r="N83" s="7"/>
+      <c r="N83" s="16"/>
       <c r="O83" s="7"/>
-      <c r="P83" s="5"/>
-      <c r="Q83" s="5"/>
+      <c r="P83" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q83" s="5">
+        <v>2.0699999999999998</v>
+      </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B84" s="5"/>
       <c r="C84" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D84" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>283</v>
+        <v>353</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>155</v>
+        <v>347</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H84" s="5"/>
       <c r="I84" s="5"/>
@@ -4839,14 +4855,10 @@
       </c>
       <c r="L84" s="5"/>
       <c r="M84" s="5"/>
-      <c r="N84" s="16"/>
+      <c r="N84" s="7"/>
       <c r="O84" s="7"/>
-      <c r="P84" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q84" s="5">
-        <v>2.0699999999999998</v>
-      </c>
+      <c r="P84" s="5"/>
+      <c r="Q84" s="5"/>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="5">
@@ -4860,10 +4872,10 @@
         <v>50</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>355</v>
+        <v>253</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>349</v>
+        <v>112</v>
       </c>
       <c r="G85" s="5" t="s">
         <v>307</v>
@@ -4893,10 +4905,10 @@
         <v>50</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G86" s="5" t="s">
         <v>307</v>
@@ -4926,10 +4938,10 @@
         <v>50</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G87" s="5" t="s">
         <v>307</v>
@@ -4959,10 +4971,10 @@
         <v>50</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="G88" s="5" t="s">
         <v>307</v>
@@ -4977,8 +4989,12 @@
       <c r="M88" s="5"/>
       <c r="N88" s="7"/>
       <c r="O88" s="7"/>
-      <c r="P88" s="5"/>
-      <c r="Q88" s="5"/>
+      <c r="P88" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q88" s="5">
+        <v>1.18</v>
+      </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="5">
@@ -4992,10 +5008,10 @@
         <v>50</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="G89" s="5" t="s">
         <v>307</v>
@@ -5010,16 +5026,12 @@
       <c r="M89" s="5"/>
       <c r="N89" s="7"/>
       <c r="O89" s="7"/>
-      <c r="P89" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q89" s="5">
-        <v>1.18</v>
-      </c>
+      <c r="P89" s="5"/>
+      <c r="Q89" s="5"/>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B90" s="5"/>
       <c r="C90" s="5" t="s">
@@ -5029,13 +5041,13 @@
         <v>50</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H90" s="5"/>
       <c r="I90" s="5"/>
@@ -5056,7 +5068,7 @@
       </c>
       <c r="B91" s="5"/>
       <c r="C91" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D91" s="5" t="s">
         <v>50</v>
@@ -5095,10 +5107,10 @@
         <v>50</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G92" s="5" t="s">
         <v>309</v>
@@ -5122,16 +5134,16 @@
       </c>
       <c r="B93" s="5"/>
       <c r="C93" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D93" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G93" s="5" t="s">
         <v>309</v>
@@ -5155,7 +5167,7 @@
       </c>
       <c r="B94" s="5"/>
       <c r="C94" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D94" s="5" t="s">
         <v>50</v>
@@ -5194,10 +5206,10 @@
         <v>50</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="G95" s="5" t="s">
         <v>309</v>
@@ -5221,16 +5233,16 @@
       </c>
       <c r="B96" s="5"/>
       <c r="C96" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D96" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="G96" s="5" t="s">
         <v>309</v>
@@ -5254,7 +5266,7 @@
       </c>
       <c r="B97" s="5"/>
       <c r="C97" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D97" s="5" t="s">
         <v>50</v>
@@ -5293,10 +5305,10 @@
         <v>50</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="G98" s="5" t="s">
         <v>309</v>
@@ -5326,10 +5338,10 @@
         <v>50</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G99" s="5" t="s">
         <v>309</v>
@@ -5359,10 +5371,10 @@
         <v>50</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="G100" s="5" t="s">
         <v>309</v>
@@ -5392,10 +5404,10 @@
         <v>50</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G101" s="5" t="s">
         <v>309</v>
@@ -5425,10 +5437,10 @@
         <v>50</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="G102" s="5" t="s">
         <v>309</v>
@@ -5452,16 +5464,16 @@
       </c>
       <c r="B103" s="5"/>
       <c r="C103" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D103" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="G103" s="5" t="s">
         <v>309</v>
@@ -5485,7 +5497,7 @@
       </c>
       <c r="B104" s="5"/>
       <c r="C104" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D104" s="5" t="s">
         <v>50</v>
@@ -5524,10 +5536,10 @@
         <v>50</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G105" s="5" t="s">
         <v>309</v>
@@ -5551,16 +5563,16 @@
       </c>
       <c r="B106" s="5"/>
       <c r="C106" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D106" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G106" s="5" t="s">
         <v>309</v>
@@ -5573,7 +5585,7 @@
       </c>
       <c r="L106" s="5"/>
       <c r="M106" s="5"/>
-      <c r="N106" s="7"/>
+      <c r="N106" s="16"/>
       <c r="O106" s="7"/>
       <c r="P106" s="5"/>
       <c r="Q106" s="5"/>
@@ -5584,7 +5596,7 @@
       </c>
       <c r="B107" s="5"/>
       <c r="C107" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D107" s="5" t="s">
         <v>50</v>
@@ -5623,10 +5635,10 @@
         <v>50</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="G108" s="5" t="s">
         <v>309</v>
@@ -5650,16 +5662,16 @@
       </c>
       <c r="B109" s="5"/>
       <c r="C109" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D109" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="G109" s="5" t="s">
         <v>309</v>
@@ -5683,7 +5695,7 @@
       </c>
       <c r="B110" s="5"/>
       <c r="C110" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D110" s="5" t="s">
         <v>50</v>
@@ -5722,10 +5734,10 @@
         <v>50</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="G111" s="5" t="s">
         <v>309</v>
@@ -5755,10 +5767,10 @@
         <v>50</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G112" s="5" t="s">
         <v>309</v>
@@ -5782,16 +5794,16 @@
       </c>
       <c r="B113" s="5"/>
       <c r="C113" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D113" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>255</v>
+        <v>225</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="G113" s="5" t="s">
         <v>309</v>
@@ -5821,10 +5833,10 @@
         <v>50</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>131</v>
+        <v>83</v>
       </c>
       <c r="G114" s="5" t="s">
         <v>309</v>
@@ -5854,10 +5866,10 @@
         <v>50</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="G115" s="5" t="s">
         <v>309</v>
@@ -5887,10 +5899,10 @@
         <v>50</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G116" s="5" t="s">
         <v>309</v>
@@ -5920,10 +5932,10 @@
         <v>50</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G117" s="5" t="s">
         <v>309</v>
@@ -5953,10 +5965,10 @@
         <v>50</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G118" s="5" t="s">
         <v>309</v>
@@ -5986,10 +5998,10 @@
         <v>50</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G119" s="5" t="s">
         <v>309</v>
@@ -6019,10 +6031,10 @@
         <v>50</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G120" s="5" t="s">
         <v>309</v>
@@ -6042,23 +6054,23 @@
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B121" s="5"/>
       <c r="C121" s="5" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>247</v>
+        <v>271</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>105</v>
+        <v>138</v>
       </c>
       <c r="G121" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H121" s="5"/>
       <c r="I121" s="5"/>
@@ -6082,13 +6094,13 @@
         <v>12</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G122" s="5" t="s">
         <v>307</v>
@@ -6115,13 +6127,13 @@
         <v>12</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G123" s="5" t="s">
         <v>307</v>
@@ -6145,16 +6157,16 @@
       </c>
       <c r="B124" s="5"/>
       <c r="C124" s="5" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>141</v>
+        <v>13</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>273</v>
+        <v>199</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>142</v>
+        <v>22</v>
       </c>
       <c r="G124" s="5" t="s">
         <v>307</v>
@@ -6174,23 +6186,23 @@
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B125" s="5"/>
       <c r="C125" s="5" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D125" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>199</v>
+        <v>274</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>22</v>
+        <v>143</v>
       </c>
       <c r="G125" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H125" s="5"/>
       <c r="I125" s="5"/>
@@ -6217,10 +6229,10 @@
         <v>13</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G126" s="5" t="s">
         <v>309</v>
@@ -6247,13 +6259,13 @@
         <v>12</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G127" s="5" t="s">
         <v>309</v>
@@ -6280,13 +6292,13 @@
         <v>12</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>145</v>
+        <v>13</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G128" s="5" t="s">
         <v>309</v>
@@ -6316,10 +6328,10 @@
         <v>13</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="G129" s="5" t="s">
         <v>309</v>
@@ -6349,10 +6361,10 @@
         <v>13</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G130" s="5" t="s">
         <v>309</v>
@@ -6379,13 +6391,13 @@
         <v>12</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>13</v>
+        <v>152</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G131" s="5" t="s">
         <v>309</v>
@@ -6405,23 +6417,23 @@
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B132" s="5"/>
       <c r="C132" s="5" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>152</v>
+        <v>50</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>281</v>
+        <v>354</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>153</v>
+        <v>348</v>
       </c>
       <c r="G132" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H132" s="5"/>
       <c r="I132" s="5"/>
@@ -6431,30 +6443,34 @@
       </c>
       <c r="L132" s="5"/>
       <c r="M132" s="5"/>
-      <c r="N132" s="16"/>
+      <c r="N132" s="7"/>
       <c r="O132" s="7"/>
-      <c r="P132" s="5"/>
-      <c r="Q132" s="5"/>
+      <c r="P132" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q132" s="5">
+        <v>2.08</v>
+      </c>
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B133" s="5"/>
       <c r="C133" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D133" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>356</v>
+        <v>284</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>350</v>
+        <v>156</v>
       </c>
       <c r="G133" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H133" s="5"/>
       <c r="I133" s="5"/>
@@ -6464,14 +6480,10 @@
       </c>
       <c r="L133" s="5"/>
       <c r="M133" s="5"/>
-      <c r="N133" s="7"/>
+      <c r="N133" s="16"/>
       <c r="O133" s="7"/>
-      <c r="P133" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q133" s="5">
-        <v>2.08</v>
-      </c>
+      <c r="P133" s="5"/>
+      <c r="Q133" s="5"/>
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A134" s="5">
@@ -6485,10 +6497,10 @@
         <v>50</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>284</v>
+        <v>225</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G134" s="5" t="s">
         <v>309</v>
@@ -6521,7 +6533,7 @@
         <v>225</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G135" s="5" t="s">
         <v>309</v>
@@ -6554,7 +6566,7 @@
         <v>225</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G136" s="5" t="s">
         <v>309</v>
@@ -6587,7 +6599,7 @@
         <v>225</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G137" s="5" t="s">
         <v>309</v>
@@ -6620,7 +6632,7 @@
         <v>225</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G138" s="5" t="s">
         <v>309</v>
@@ -6644,7 +6656,7 @@
       </c>
       <c r="B139" s="5"/>
       <c r="C139" s="5" t="s">
-        <v>80</v>
+        <v>162</v>
       </c>
       <c r="D139" s="5" t="s">
         <v>50</v>
@@ -6653,7 +6665,7 @@
         <v>225</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G139" s="5" t="s">
         <v>309</v>
@@ -6686,7 +6698,7 @@
         <v>225</v>
       </c>
       <c r="F140" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G140" s="5" t="s">
         <v>309</v>
@@ -6719,7 +6731,7 @@
         <v>225</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G141" s="5" t="s">
         <v>309</v>
@@ -6752,7 +6764,7 @@
         <v>225</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G142" s="5" t="s">
         <v>309</v>
@@ -6776,7 +6788,7 @@
       </c>
       <c r="B143" s="5"/>
       <c r="C143" s="5" t="s">
-        <v>162</v>
+        <v>49</v>
       </c>
       <c r="D143" s="5" t="s">
         <v>50</v>
@@ -6785,7 +6797,7 @@
         <v>225</v>
       </c>
       <c r="F143" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G143" s="5" t="s">
         <v>309</v>
@@ -6809,7 +6821,7 @@
       </c>
       <c r="B144" s="5"/>
       <c r="C144" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D144" s="5" t="s">
         <v>50</v>
@@ -6818,7 +6830,7 @@
         <v>225</v>
       </c>
       <c r="F144" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G144" s="5" t="s">
         <v>309</v>
@@ -6851,7 +6863,7 @@
         <v>225</v>
       </c>
       <c r="F145" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G145" s="5" t="s">
         <v>309</v>
@@ -6884,7 +6896,7 @@
         <v>225</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G146" s="5" t="s">
         <v>309</v>
@@ -6904,29 +6916,35 @@
     </row>
     <row r="147" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A147" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B147" s="5"/>
       <c r="C147" s="5" t="s">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="F147" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G147" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="H147" s="5"/>
-      <c r="I147" s="5"/>
-      <c r="J147" s="5"/>
+      <c r="H147" s="6">
+        <v>46094</v>
+      </c>
+      <c r="I147" s="9">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="J147" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="K147" s="5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L147" s="5"/>
       <c r="M147" s="5"/>
@@ -6947,10 +6965,10 @@
         <v>13</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G148" s="5" t="s">
         <v>309</v>
@@ -6980,25 +6998,25 @@
       </c>
       <c r="B149" s="5"/>
       <c r="C149" s="5" t="s">
-        <v>132</v>
+        <v>173</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>301</v>
+        <v>174</v>
       </c>
       <c r="F149" s="5" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="G149" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H149" s="6">
-        <v>46094</v>
+        <v>46095</v>
       </c>
       <c r="I149" s="9">
-        <v>0.41666666666666669</v>
+        <v>0.625</v>
       </c>
       <c r="J149" s="5" t="s">
         <v>15</v>
@@ -7015,33 +7033,31 @@
     </row>
     <row r="150" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A150" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B150" s="5"/>
       <c r="C150" s="5" t="s">
-        <v>173</v>
+        <v>12</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>174</v>
+        <v>285</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G150" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H150" s="6">
-        <v>46095</v>
+        <v>46128</v>
       </c>
       <c r="I150" s="9">
-        <v>0.625</v>
-      </c>
-      <c r="J150" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="J150" s="5"/>
       <c r="K150" s="5" t="s">
         <v>73</v>
       </c>
@@ -7064,21 +7080,23 @@
         <v>13</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G151" s="5" t="s">
         <v>309</v>
       </c>
       <c r="H151" s="6">
-        <v>46128</v>
+        <v>46139</v>
       </c>
       <c r="I151" s="9">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="J151" s="5"/>
+        <v>0.25</v>
+      </c>
+      <c r="J151" s="9">
+        <v>0.33333333333333331</v>
+      </c>
       <c r="K151" s="5" t="s">
         <v>73</v>
       </c>
@@ -7098,25 +7116,25 @@
         <v>12</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>13</v>
+        <v>178</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G152" s="5" t="s">
         <v>309</v>
       </c>
       <c r="H152" s="6">
-        <v>46139</v>
+        <v>46141</v>
       </c>
       <c r="I152" s="9">
-        <v>0.25</v>
+        <v>0.67361111111111116</v>
       </c>
       <c r="J152" s="9">
-        <v>0.33333333333333331</v>
+        <v>0.96527777777777779</v>
       </c>
       <c r="K152" s="5" t="s">
         <v>73</v>
@@ -7137,25 +7155,25 @@
         <v>12</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>178</v>
+        <v>13</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G153" s="5" t="s">
         <v>309</v>
       </c>
       <c r="H153" s="6">
-        <v>46141</v>
+        <v>46146</v>
       </c>
       <c r="I153" s="9">
-        <v>0.67361111111111116</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J153" s="9">
-        <v>0.96527777777777779</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="K153" s="5" t="s">
         <v>73</v>
@@ -7176,25 +7194,25 @@
         <v>12</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>13</v>
+        <v>181</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G154" s="5" t="s">
         <v>309</v>
       </c>
       <c r="H154" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="I154" s="9">
-        <v>0.33333333333333331</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="J154" s="9">
-        <v>0.41666666666666669</v>
+        <v>0.5</v>
       </c>
       <c r="K154" s="5" t="s">
         <v>73</v>
@@ -7208,46 +7226,46 @@
     </row>
     <row r="155" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A155" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B155" s="5"/>
       <c r="C155" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>181</v>
+        <v>13</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="F155" s="5" t="s">
-        <v>182</v>
+        <v>290</v>
+      </c>
+      <c r="F155" s="18" t="s">
+        <v>183</v>
       </c>
       <c r="G155" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H155" s="6">
         <v>46147</v>
       </c>
       <c r="I155" s="9">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="J155" s="9">
-        <v>0.5</v>
-      </c>
+        <v>0.625</v>
+      </c>
+      <c r="J155" s="5"/>
       <c r="K155" s="5" t="s">
         <v>73</v>
       </c>
       <c r="L155" s="5"/>
       <c r="M155" s="5"/>
       <c r="N155" s="16"/>
-      <c r="O155" s="7"/>
+      <c r="O155" s="7" t="s">
+        <v>325</v>
+      </c>
       <c r="P155" s="5"/>
       <c r="Q155" s="5"/>
     </row>
     <row r="156" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A156" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B156" s="5"/>
       <c r="C156" s="5" t="s">
@@ -7257,30 +7275,30 @@
         <v>13</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="F156" s="18" t="s">
-        <v>183</v>
+        <v>291</v>
+      </c>
+      <c r="F156" s="5" t="s">
+        <v>184</v>
       </c>
       <c r="G156" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H156" s="6">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="I156" s="9">
-        <v>0.625</v>
-      </c>
-      <c r="J156" s="5"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J156" s="9">
+        <v>0.41666666666666669</v>
+      </c>
       <c r="K156" s="5" t="s">
         <v>73</v>
       </c>
       <c r="L156" s="5"/>
       <c r="M156" s="5"/>
       <c r="N156" s="16"/>
-      <c r="O156" s="7" t="s">
-        <v>325</v>
-      </c>
+      <c r="O156" s="7"/>
       <c r="P156" s="5"/>
       <c r="Q156" s="5"/>
     </row>
@@ -7293,25 +7311,23 @@
         <v>12</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>13</v>
+        <v>185</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F157" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G157" s="5" t="s">
         <v>309</v>
       </c>
       <c r="H157" s="6">
-        <v>46149</v>
-      </c>
-      <c r="I157" s="9">
-        <v>0.33333333333333331</v>
-      </c>
+        <v>46155</v>
+      </c>
+      <c r="I157" s="5"/>
       <c r="J157" s="9">
-        <v>0.41666666666666669</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="K157" s="5" t="s">
         <v>73</v>
@@ -7332,23 +7348,23 @@
         <v>12</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>185</v>
+        <v>13</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G158" s="5" t="s">
         <v>309</v>
       </c>
       <c r="H158" s="6">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="I158" s="5"/>
       <c r="J158" s="9">
-        <v>0.45833333333333331</v>
+        <v>0.625</v>
       </c>
       <c r="K158" s="5" t="s">
         <v>73</v>
@@ -7362,7 +7378,7 @@
     </row>
     <row r="159" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A159" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B159" s="5"/>
       <c r="C159" s="5" t="s">
@@ -7372,20 +7388,22 @@
         <v>13</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F159" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G159" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H159" s="6">
-        <v>46156</v>
-      </c>
-      <c r="I159" s="5"/>
+        <v>46163</v>
+      </c>
+      <c r="I159" s="9">
+        <v>0.29166666666666669</v>
+      </c>
       <c r="J159" s="9">
-        <v>0.625</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="K159" s="5" t="s">
         <v>73</v>
@@ -7409,71 +7427,71 @@
         <v>13</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="F160" s="5" t="s">
-        <v>188</v>
+        <v>295</v>
+      </c>
+      <c r="F160" s="18" t="s">
+        <v>189</v>
       </c>
       <c r="G160" s="5" t="s">
         <v>307</v>
       </c>
       <c r="H160" s="6">
-        <v>46163</v>
-      </c>
-      <c r="I160" s="9">
-        <v>0.29166666666666669</v>
-      </c>
+        <v>46164</v>
+      </c>
+      <c r="I160" s="5"/>
       <c r="J160" s="9">
-        <v>0.33333333333333331</v>
+        <v>0.375</v>
       </c>
       <c r="K160" s="5" t="s">
         <v>73</v>
       </c>
       <c r="L160" s="5"/>
       <c r="M160" s="5"/>
-      <c r="N160" s="16"/>
-      <c r="O160" s="7"/>
+      <c r="N160" s="16" t="s">
+        <v>338</v>
+      </c>
+      <c r="O160" s="16" t="s">
+        <v>338</v>
+      </c>
       <c r="P160" s="5"/>
       <c r="Q160" s="5"/>
     </row>
     <row r="161" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A161" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B161" s="5"/>
       <c r="C161" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>13</v>
+        <v>190</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="F161" s="18" t="s">
-        <v>189</v>
+        <v>296</v>
+      </c>
+      <c r="F161" s="5" t="s">
+        <v>191</v>
       </c>
       <c r="G161" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H161" s="6">
-        <v>46164</v>
-      </c>
-      <c r="I161" s="5"/>
+        <v>46167</v>
+      </c>
+      <c r="I161" s="9">
+        <v>0.22916666666666666</v>
+      </c>
       <c r="J161" s="9">
-        <v>0.375</v>
+        <v>0.5625</v>
       </c>
       <c r="K161" s="5" t="s">
         <v>73</v>
       </c>
       <c r="L161" s="5"/>
       <c r="M161" s="5"/>
-      <c r="N161" s="16" t="s">
-        <v>340</v>
-      </c>
-      <c r="O161" s="16" t="s">
-        <v>340</v>
-      </c>
+      <c r="N161" s="16"/>
+      <c r="O161" s="7"/>
       <c r="P161" s="5"/>
       <c r="Q161" s="5"/>
     </row>
@@ -7486,25 +7504,25 @@
         <v>12</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>190</v>
+        <v>13</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G162" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="H162" s="6">
-        <v>46167</v>
+      <c r="H162" s="12">
+        <v>46170</v>
       </c>
       <c r="I162" s="9">
-        <v>0.22916666666666666</v>
-      </c>
-      <c r="J162" s="9">
-        <v>0.5625</v>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J162" s="13">
+        <v>0.41666666666666669</v>
       </c>
       <c r="K162" s="5" t="s">
         <v>73</v>
@@ -7525,25 +7543,25 @@
         <v>12</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G163" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="H163" s="12">
-        <v>46170</v>
+      <c r="H163" s="6">
+        <v>46174</v>
       </c>
       <c r="I163" s="9">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="J163" s="13">
-        <v>0.41666666666666669</v>
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="J163" s="9">
+        <v>0.72916666666666663</v>
       </c>
       <c r="K163" s="5" t="s">
         <v>73</v>
@@ -7557,40 +7575,44 @@
     </row>
     <row r="164" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A164" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B164" s="5"/>
       <c r="C164" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="F164" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
+      </c>
+      <c r="F164" s="18" t="s">
+        <v>19</v>
       </c>
       <c r="G164" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H164" s="6">
-        <v>46174</v>
-      </c>
-      <c r="I164" s="9">
-        <v>0.64583333333333337</v>
-      </c>
+        <v>46204</v>
+      </c>
+      <c r="I164" s="5"/>
       <c r="J164" s="9">
-        <v>0.72916666666666663</v>
+        <v>0.875</v>
       </c>
       <c r="K164" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="L164" s="5"/>
-      <c r="M164" s="5"/>
-      <c r="N164" s="16"/>
-      <c r="O164" s="7"/>
+      <c r="L164" s="6">
+        <v>46182</v>
+      </c>
+      <c r="M164" s="6"/>
+      <c r="N164" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="O164" s="7" t="s">
+        <v>326</v>
+      </c>
       <c r="P164" s="5"/>
       <c r="Q164" s="5"/>
     </row>
@@ -7606,157 +7628,157 @@
         <v>13</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F165" s="18" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G165" s="5" t="s">
         <v>307</v>
       </c>
       <c r="H165" s="6">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="I165" s="5"/>
       <c r="J165" s="9">
-        <v>0.875</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="K165" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="L165" s="6">
-        <v>46182</v>
-      </c>
-      <c r="M165" s="6"/>
+      <c r="L165" s="5"/>
+      <c r="M165" s="5"/>
       <c r="N165" s="7" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="O165" s="7" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="P165" s="5"/>
       <c r="Q165" s="5"/>
     </row>
     <row r="166" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A166" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B166" s="5"/>
       <c r="C166" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E166" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="F166" s="18" t="s">
-        <v>17</v>
+        <v>206</v>
+      </c>
+      <c r="F166" s="5" t="s">
+        <v>34</v>
       </c>
       <c r="G166" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H166" s="6">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="I166" s="5"/>
       <c r="J166" s="9">
-        <v>0.41666666666666669</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="K166" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="L166" s="5"/>
-      <c r="M166" s="5"/>
-      <c r="N166" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="O166" s="7" t="s">
-        <v>330</v>
-      </c>
+      <c r="L166" s="6">
+        <v>46189</v>
+      </c>
+      <c r="M166" s="5">
+        <v>1.06</v>
+      </c>
+      <c r="N166" s="7"/>
+      <c r="O166" s="7"/>
       <c r="P166" s="5"/>
       <c r="Q166" s="5"/>
     </row>
     <row r="167" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A167" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B167" s="5"/>
       <c r="C167" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="G167" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="H167" s="6">
-        <v>46213</v>
-      </c>
-      <c r="I167" s="5"/>
-      <c r="J167" s="9">
-        <v>0.66666666666666663</v>
+        <v>307</v>
+      </c>
+      <c r="H167" s="2">
+        <v>46218</v>
+      </c>
+      <c r="I167" s="9">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="J167" s="3">
+        <v>0.5</v>
       </c>
       <c r="K167" s="5" t="s">
         <v>73</v>
       </c>
       <c r="L167" s="6">
-        <v>46189</v>
-      </c>
-      <c r="M167" s="5">
-        <v>1.06</v>
-      </c>
-      <c r="N167" s="7"/>
+        <v>46182</v>
+      </c>
+      <c r="M167" s="6"/>
+      <c r="N167" s="7" t="s">
+        <v>355</v>
+      </c>
       <c r="O167" s="7"/>
       <c r="P167" s="5"/>
       <c r="Q167" s="5"/>
     </row>
     <row r="168" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A168" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B168" s="5"/>
       <c r="C168" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E168" s="5" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="G168" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="H168" s="2">
+        <v>309</v>
+      </c>
+      <c r="H168" s="12">
         <v>46218</v>
       </c>
       <c r="I168" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J168" s="3">
-        <v>0.5</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="J168" s="13">
+        <v>0.625</v>
       </c>
       <c r="K168" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="L168" s="6">
-        <v>46182</v>
-      </c>
-      <c r="M168" s="6"/>
+      <c r="L168" s="5"/>
+      <c r="M168" s="5">
+        <v>2.02</v>
+      </c>
       <c r="N168" s="7" t="s">
-        <v>357</v>
+        <v>315</v>
       </c>
       <c r="O168" s="7"/>
       <c r="P168" s="5"/>
@@ -7764,44 +7786,46 @@
     </row>
     <row r="169" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A169" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B169" s="5"/>
       <c r="C169" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="F169" s="5" t="s">
-        <v>63</v>
+        <v>198</v>
+      </c>
+      <c r="F169" s="18" t="s">
+        <v>20</v>
       </c>
       <c r="G169" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="H169" s="12">
-        <v>46218</v>
+        <v>307</v>
+      </c>
+      <c r="H169" s="2">
+        <v>46219</v>
       </c>
       <c r="I169" s="9">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="J169" s="3">
         <v>0.58333333333333337</v>
-      </c>
-      <c r="J169" s="13">
-        <v>0.625</v>
       </c>
       <c r="K169" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="L169" s="5"/>
-      <c r="M169" s="5">
-        <v>2.02</v>
-      </c>
+      <c r="L169" s="6">
+        <v>46182</v>
+      </c>
+      <c r="M169" s="6"/>
       <c r="N169" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="O169" s="7"/>
+        <v>317</v>
+      </c>
+      <c r="O169" s="7" t="s">
+        <v>357</v>
+      </c>
       <c r="P169" s="5"/>
       <c r="Q169" s="5"/>
     </row>
@@ -7949,13 +7973,38 @@
         <v>2.08</v>
       </c>
       <c r="N173" s="7" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="O173" s="7" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="P173" s="5"/>
       <c r="Q173" s="5"/>
+    </row>
+    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A174" s="19" t="s">
+        <v>358</v>
+      </c>
+      <c r="B174" s="19"/>
+      <c r="C174" s="19"/>
+      <c r="D174" s="19"/>
+      <c r="E174" s="19"/>
+      <c r="F174" s="19">
+        <v>172</v>
+      </c>
+      <c r="G174" s="19"/>
+      <c r="H174" s="19"/>
+      <c r="I174" s="19"/>
+      <c r="J174" s="19"/>
+      <c r="K174" s="19">
+        <v>172</v>
+      </c>
+      <c r="L174" s="19"/>
+      <c r="M174" s="19"/>
+      <c r="N174" s="20"/>
+      <c r="O174" s="21"/>
+      <c r="P174" s="19"/>
+      <c r="Q174" s="19"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="K2:Q173">

--- a/archivos/BD_Dashboard.xlsx
+++ b/archivos/BD_Dashboard.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mexscitum-my.sharepoint.com/personal/erik_torres_scitum_com_mx/Documents/Documentos/ETP/GitHub/SCITUM-AMX/archivos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="133" documentId="11_F25DC773A252ABDACC1048E8499F6DC65BDE58F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13AC1362-4657-475E-91F7-42A6E32F3F19}"/>
+  <xr:revisionPtr revIDLastSave="138" documentId="11_F25DC773A252ABDACC1048E8499F6DC65BDE58F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F739FEFF-B474-4B57-AEC1-73EFA45BE77D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inventario SDWAN &amp; FW" sheetId="2" r:id="rId1"/>
@@ -46,7 +46,7 @@
     <author>Erik Alejandro Torres Piña</author>
   </authors>
   <commentList>
-    <comment ref="F42" authorId="0" shapeId="0" xr:uid="{88CC45FE-6D09-445C-A9A4-C7433F8FBF6E}">
+    <comment ref="F41" authorId="0" shapeId="0" xr:uid="{3873DA3F-6CE5-4EB5-8AFF-CCBB8AFCCAC6}">
       <text>
         <r>
           <rPr>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1115" uniqueCount="358">
   <si>
     <t>TIER</t>
   </si>
@@ -1156,16 +1156,13 @@
 Dos contratiempos. 
 La llegada del IDC no fue en tiempo  debido a que no logro encontrar estacionamiento dentro del aeropuerto.
 El IDC desconecto otro cable del Fortinet que no fue indicado en la sesión y esto presento un problema que llevo tiempo identificar.</t>
-  </si>
-  <si>
-    <t>Total</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1225,13 +1222,6 @@
     </font>
     <font>
       <u/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Century Gothic"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Century Gothic"/>
@@ -1297,7 +1287,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1352,15 +1342,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1806,19 +1787,19 @@
   <sheetPr>
     <tabColor theme="5" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:Q174"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Q173"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="4.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="1.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.85546875" customWidth="1"/>
-    <col min="7" max="7" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="1.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.81640625" customWidth="1"/>
+    <col min="7" max="7" width="17.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1871,52 +1852,50 @@
         <v>342</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="H2" s="6">
-        <v>46220</v>
+        <v>307</v>
+      </c>
+      <c r="H2" s="2">
+        <v>46223</v>
       </c>
       <c r="I2" s="9">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="J2" s="9">
-        <v>0.375</v>
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="J2" s="3">
+        <v>0.79166666666666663</v>
       </c>
       <c r="K2" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="L2" s="6">
-        <v>46189</v>
-      </c>
+      <c r="L2" s="5"/>
       <c r="M2" s="5">
-        <v>1.02</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="N2" s="7" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="O2" s="7"/>
       <c r="P2" s="5"/>
       <c r="Q2" s="5"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -1925,41 +1904,43 @@
         <v>12</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>307</v>
       </c>
       <c r="H3" s="2">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="I3" s="9">
-        <v>0.79166666666666663</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="J3" s="3">
-        <v>0.79166666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="K3" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="L3" s="5"/>
+      <c r="L3" s="6">
+        <v>46189</v>
+      </c>
       <c r="M3" s="5">
-        <v>2.0699999999999998</v>
+        <v>1.01</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>336</v>
+        <v>316</v>
       </c>
       <c r="O3" s="7"/>
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" s="5">
         <v>1</v>
       </c>
@@ -1968,61 +1949,51 @@
         <v>12</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="H4" s="2">
-        <v>46230</v>
-      </c>
-      <c r="I4" s="9">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="J4" s="3">
-        <v>0.625</v>
-      </c>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
       <c r="K4" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="L4" s="6">
-        <v>46189</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="L4" s="5"/>
       <c r="M4" s="5">
-        <v>1.01</v>
-      </c>
-      <c r="N4" s="7" t="s">
-        <v>316</v>
-      </c>
+        <v>2.09</v>
+      </c>
+      <c r="N4" s="7"/>
       <c r="O4" s="7"/>
       <c r="P4" s="5"/>
       <c r="Q4" s="5"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>215</v>
+        <v>259</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
@@ -2032,14 +2003,14 @@
       </c>
       <c r="L5" s="5"/>
       <c r="M5" s="5">
-        <v>2.09</v>
+        <v>4.03</v>
       </c>
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
       <c r="P5" s="5"/>
       <c r="Q5" s="5"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>3</v>
       </c>
@@ -2051,10 +2022,10 @@
         <v>50</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>309</v>
@@ -2067,14 +2038,14 @@
       </c>
       <c r="L6" s="5"/>
       <c r="M6" s="5">
-        <v>4.03</v>
+        <v>4.05</v>
       </c>
       <c r="N6" s="7"/>
       <c r="O6" s="7"/>
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
         <v>3</v>
       </c>
@@ -2086,10 +2057,10 @@
         <v>50</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>309</v>
@@ -2100,16 +2071,20 @@
       <c r="K7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="L7" s="5"/>
+      <c r="L7" s="6">
+        <v>46209</v>
+      </c>
       <c r="M7" s="5">
-        <v>4.05</v>
-      </c>
-      <c r="N7" s="7"/>
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>334</v>
+      </c>
       <c r="O7" s="7"/>
       <c r="P7" s="5"/>
       <c r="Q7" s="5"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>3</v>
       </c>
@@ -2121,10 +2096,10 @@
         <v>50</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>257</v>
+        <v>282</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>117</v>
+        <v>154</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>309</v>
@@ -2135,11 +2110,11 @@
       <c r="K8" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="17">
         <v>46209</v>
       </c>
       <c r="M8" s="5">
-        <v>4.0199999999999996</v>
+        <v>4.04</v>
       </c>
       <c r="N8" s="7" t="s">
         <v>334</v>
@@ -2148,22 +2123,22 @@
       <c r="P8" s="5"/>
       <c r="Q8" s="5"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>3</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>282</v>
+        <v>204</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>154</v>
+        <v>31</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>309</v>
@@ -2172,22 +2147,22 @@
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
       <c r="K9" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="L9" s="17">
-        <v>46209</v>
+        <v>21</v>
+      </c>
+      <c r="L9" s="6">
+        <v>46189</v>
       </c>
       <c r="M9" s="5">
-        <v>4.04</v>
+        <v>1.04</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>334</v>
+        <v>312</v>
       </c>
       <c r="O9" s="7"/>
       <c r="P9" s="5"/>
       <c r="Q9" s="5"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>3</v>
       </c>
@@ -2196,13 +2171,13 @@
         <v>12</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>309</v>
@@ -2217,7 +2192,7 @@
         <v>46189</v>
       </c>
       <c r="M10" s="5">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N10" s="7" t="s">
         <v>312</v>
@@ -2226,25 +2201,25 @@
       <c r="P10" s="5"/>
       <c r="Q10" s="5"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
@@ -2253,37 +2228,37 @@
         <v>21</v>
       </c>
       <c r="L11" s="6">
-        <v>46189</v>
+        <v>46210</v>
       </c>
       <c r="M11" s="5">
-        <v>1.05</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>312</v>
+        <v>332</v>
       </c>
       <c r="O11" s="7"/>
       <c r="P11" s="5"/>
       <c r="Q11" s="5"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
@@ -2292,19 +2267,19 @@
         <v>21</v>
       </c>
       <c r="L12" s="6">
-        <v>46210</v>
-      </c>
-      <c r="M12" s="5">
-        <v>2.0099999999999998</v>
+        <v>46206</v>
+      </c>
+      <c r="M12" s="14">
+        <v>2.1</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O12" s="7"/>
       <c r="P12" s="5"/>
       <c r="Q12" s="5"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
         <v>3</v>
       </c>
@@ -2313,13 +2288,13 @@
         <v>12</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>66</v>
+        <v>324</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>309</v>
@@ -2328,22 +2303,18 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
       <c r="K13" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L13" s="6">
-        <v>46206</v>
-      </c>
-      <c r="M13" s="14">
-        <v>2.1</v>
-      </c>
-      <c r="N13" s="7" t="s">
-        <v>333</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="N13" s="7"/>
       <c r="O13" s="7"/>
       <c r="P13" s="5"/>
       <c r="Q13" s="5"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <v>3</v>
       </c>
@@ -2352,13 +2323,13 @@
         <v>12</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>324</v>
+        <v>64</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>309</v>
@@ -2371,32 +2342,32 @@
       </c>
       <c r="L14" s="5"/>
       <c r="M14" s="5">
-        <v>2.0299999999999998</v>
+        <v>2.04</v>
       </c>
       <c r="N14" s="7"/>
       <c r="O14" s="7"/>
       <c r="P14" s="5"/>
       <c r="Q14" s="5"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
@@ -2406,29 +2377,29 @@
       </c>
       <c r="L15" s="5"/>
       <c r="M15" s="5">
-        <v>2.04</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
       <c r="P15" s="5"/>
       <c r="Q15" s="5"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>58</v>
+        <v>135</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>219</v>
+        <v>270</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>59</v>
+        <v>136</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>307</v>
@@ -2441,32 +2412,32 @@
       </c>
       <c r="L16" s="5"/>
       <c r="M16" s="5">
-        <v>2.0499999999999998</v>
+        <v>3.01</v>
       </c>
       <c r="N16" s="7"/>
       <c r="O16" s="7"/>
       <c r="P16" s="5"/>
       <c r="Q16" s="5"/>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
@@ -2476,14 +2447,14 @@
       </c>
       <c r="L17" s="5"/>
       <c r="M17" s="5">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="N17" s="7"/>
       <c r="O17" s="7"/>
       <c r="P17" s="5"/>
       <c r="Q17" s="5"/>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18" s="5">
         <v>3</v>
       </c>
@@ -2492,18 +2463,18 @@
         <v>12</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>148</v>
+        <v>13</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>278</v>
+        <v>208</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>149</v>
+        <v>37</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="H18" s="5"/>
+      <c r="H18" s="8"/>
       <c r="I18" s="5"/>
       <c r="J18" s="5"/>
       <c r="K18" s="5" t="s">
@@ -2511,16 +2482,18 @@
       </c>
       <c r="L18" s="5"/>
       <c r="M18" s="5">
-        <v>3.02</v>
-      </c>
-      <c r="N18" s="7"/>
+        <v>3.03</v>
+      </c>
+      <c r="N18" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="O18" s="7"/>
       <c r="P18" s="5"/>
       <c r="Q18" s="5"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5" t="s">
@@ -2530,13 +2503,13 @@
         <v>13</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H19" s="8"/>
       <c r="I19" s="5"/>
@@ -2546,18 +2519,18 @@
       </c>
       <c r="L19" s="5"/>
       <c r="M19" s="5">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="N19" s="7" t="s">
-        <v>38</v>
+        <v>303</v>
       </c>
       <c r="O19" s="7"/>
       <c r="P19" s="5"/>
       <c r="Q19" s="5"/>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5" t="s">
@@ -2567,13 +2540,13 @@
         <v>13</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H20" s="8"/>
       <c r="I20" s="5"/>
@@ -2583,36 +2556,36 @@
       </c>
       <c r="L20" s="5"/>
       <c r="M20" s="5">
-        <v>3.04</v>
+        <v>4.01</v>
       </c>
       <c r="N20" s="7" t="s">
-        <v>303</v>
+        <v>40</v>
       </c>
       <c r="O20" s="7"/>
       <c r="P20" s="5"/>
       <c r="Q20" s="5"/>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5" t="s">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>209</v>
+        <v>76</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="H21" s="8"/>
+        <v>307</v>
+      </c>
+      <c r="H21" s="5"/>
       <c r="I21" s="5"/>
       <c r="J21" s="5"/>
       <c r="K21" s="5" t="s">
@@ -2620,16 +2593,18 @@
       </c>
       <c r="L21" s="5"/>
       <c r="M21" s="5">
-        <v>4.01</v>
-      </c>
-      <c r="N21" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="N21" s="7"/>
       <c r="O21" s="7"/>
-      <c r="P21" s="5"/>
-      <c r="Q21" s="5"/>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P21" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q21" s="5">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
         <v>0</v>
       </c>
@@ -2641,10 +2616,10 @@
         <v>50</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>76</v>
+        <v>337</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>307</v>
@@ -2657,7 +2632,7 @@
       </c>
       <c r="L22" s="5"/>
       <c r="M22" s="5">
-        <v>5.0999999999999996</v>
+        <v>5.2</v>
       </c>
       <c r="N22" s="7"/>
       <c r="O22" s="7"/>
@@ -2665,28 +2640,28 @@
         <v>311</v>
       </c>
       <c r="Q22" s="5">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>337</v>
+        <v>266</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
@@ -2696,18 +2671,14 @@
       </c>
       <c r="L23" s="5"/>
       <c r="M23" s="5">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="N23" s="7"/>
       <c r="O23" s="7"/>
-      <c r="P23" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q23" s="5">
-        <v>1.02</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P23" s="5"/>
+      <c r="Q23" s="5"/>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
         <v>3</v>
       </c>
@@ -2719,10 +2690,10 @@
         <v>50</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>309</v>
@@ -2735,16 +2706,16 @@
       </c>
       <c r="L24" s="5"/>
       <c r="M24" s="5">
-        <v>5.3</v>
-      </c>
-      <c r="N24" s="7"/>
+        <v>5.4</v>
+      </c>
+      <c r="N24" s="16"/>
       <c r="O24" s="7"/>
       <c r="P24" s="5"/>
       <c r="Q24" s="5"/>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5" t="s">
@@ -2754,13 +2725,13 @@
         <v>50</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>269</v>
+        <v>81</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>130</v>
+        <v>81</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
@@ -2770,29 +2741,29 @@
       </c>
       <c r="L25" s="5"/>
       <c r="M25" s="5">
-        <v>5.4</v>
-      </c>
-      <c r="N25" s="16"/>
+        <v>5.5</v>
+      </c>
+      <c r="N25" s="7"/>
       <c r="O25" s="7"/>
       <c r="P25" s="5"/>
       <c r="Q25" s="5"/>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26" s="5">
         <v>1</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>81</v>
+        <v>213</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>307</v>
@@ -2805,14 +2776,16 @@
       </c>
       <c r="L26" s="5"/>
       <c r="M26" s="5">
-        <v>5.5</v>
-      </c>
-      <c r="N26" s="7"/>
+        <v>5.6</v>
+      </c>
+      <c r="N26" s="7" t="s">
+        <v>48</v>
+      </c>
       <c r="O26" s="7"/>
       <c r="P26" s="5"/>
       <c r="Q26" s="5"/>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27" s="5">
         <v>1</v>
       </c>
@@ -2821,37 +2794,41 @@
         <v>12</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="G27" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
+      <c r="H27" s="12">
+        <v>46225</v>
+      </c>
+      <c r="I27" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J27" s="13">
+        <v>0.41666666666666669</v>
+      </c>
       <c r="K27" s="5" t="s">
-        <v>299</v>
+        <v>36</v>
       </c>
       <c r="L27" s="5"/>
-      <c r="M27" s="5">
-        <v>5.6</v>
-      </c>
+      <c r="M27" s="5"/>
       <c r="N27" s="7" t="s">
-        <v>48</v>
+        <v>356</v>
       </c>
       <c r="O27" s="7"/>
       <c r="P27" s="5"/>
       <c r="Q27" s="5"/>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5" t="s">
@@ -2861,22 +2838,20 @@
         <v>13</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="G28" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="H28" s="12">
-        <v>46225</v>
-      </c>
-      <c r="I28" s="9">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="J28" s="13">
-        <v>0.41666666666666669</v>
+      <c r="H28" s="2">
+        <v>46226</v>
+      </c>
+      <c r="I28" s="5"/>
+      <c r="J28" s="3">
+        <v>0.47916666666666669</v>
       </c>
       <c r="K28" s="5" t="s">
         <v>36</v>
@@ -2890,38 +2865,44 @@
       <c r="P28" s="5"/>
       <c r="Q28" s="5"/>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29" s="5">
         <v>2</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>307</v>
       </c>
       <c r="H29" s="2">
-        <v>46226</v>
-      </c>
-      <c r="I29" s="5"/>
+        <v>46230</v>
+      </c>
+      <c r="I29" s="9">
+        <v>0.60416666666666663</v>
+      </c>
       <c r="J29" s="3">
-        <v>0.47916666666666669</v>
+        <v>0.6875</v>
       </c>
       <c r="K29" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="L29" s="5"/>
-      <c r="M29" s="5"/>
+      <c r="L29" s="6">
+        <v>46189</v>
+      </c>
+      <c r="M29" s="5">
+        <v>1.03</v>
+      </c>
       <c r="N29" s="7" t="s">
         <v>356</v>
       </c>
@@ -2929,81 +2910,73 @@
       <c r="P29" s="5"/>
       <c r="Q29" s="5"/>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30" s="5">
         <v>2</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="H30" s="2">
-        <v>46230</v>
-      </c>
-      <c r="I30" s="9">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="J30" s="3">
-        <v>0.6875</v>
-      </c>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
       <c r="K30" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="L30" s="6">
-        <v>46189</v>
-      </c>
+      <c r="L30" s="5"/>
       <c r="M30" s="5">
-        <v>1.03</v>
+        <v>2.06</v>
       </c>
       <c r="N30" s="7" t="s">
-        <v>356</v>
+        <v>329</v>
       </c>
       <c r="O30" s="7"/>
       <c r="P30" s="5"/>
       <c r="Q30" s="5"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>220</v>
+        <v>199</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="G31" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="H31" s="5"/>
+      <c r="H31" s="1"/>
       <c r="I31" s="5"/>
-      <c r="J31" s="5"/>
+      <c r="J31" s="3"/>
       <c r="K31" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="L31" s="5"/>
-      <c r="M31" s="5">
-        <v>2.06</v>
-      </c>
+      <c r="L31" s="6">
+        <v>46182</v>
+      </c>
+      <c r="M31" s="6"/>
       <c r="N31" s="7" t="s">
         <v>329</v>
       </c>
@@ -3011,9 +2984,9 @@
       <c r="P31" s="5"/>
       <c r="Q31" s="5"/>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5" t="s">
@@ -3023,34 +2996,32 @@
         <v>13</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="G32" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="H32" s="1"/>
+      <c r="H32" s="8"/>
       <c r="I32" s="5"/>
-      <c r="J32" s="3"/>
+      <c r="J32" s="5"/>
       <c r="K32" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="L32" s="6">
-        <v>46182</v>
-      </c>
-      <c r="M32" s="6"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="5"/>
       <c r="N32" s="7" t="s">
-        <v>329</v>
+        <v>42</v>
       </c>
       <c r="O32" s="7"/>
       <c r="P32" s="5"/>
       <c r="Q32" s="5"/>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5" t="s">
@@ -3060,113 +3031,115 @@
         <v>13</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H33" s="8"/>
       <c r="I33" s="5"/>
-      <c r="J33" s="5"/>
+      <c r="J33" s="9"/>
       <c r="K33" s="5" t="s">
         <v>36</v>
       </c>
       <c r="L33" s="5"/>
       <c r="M33" s="5"/>
       <c r="N33" s="7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="O33" s="7"/>
       <c r="P33" s="5"/>
       <c r="Q33" s="5"/>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H34" s="8"/>
       <c r="I34" s="5"/>
-      <c r="J34" s="9"/>
+      <c r="J34" s="5"/>
       <c r="K34" s="5" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="L34" s="5"/>
       <c r="M34" s="5"/>
-      <c r="N34" s="7" t="s">
-        <v>45</v>
-      </c>
+      <c r="N34" s="7"/>
       <c r="O34" s="7"/>
       <c r="P34" s="5"/>
       <c r="Q34" s="5"/>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="G35" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="H35" s="8"/>
+      <c r="H35" s="5"/>
       <c r="I35" s="5"/>
       <c r="J35" s="5"/>
       <c r="K35" s="5" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="L35" s="5"/>
       <c r="M35" s="5"/>
       <c r="N35" s="7"/>
       <c r="O35" s="7"/>
-      <c r="P35" s="5"/>
-      <c r="Q35" s="5"/>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P35" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q35" s="5">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="G36" s="5" t="s">
         <v>307</v>
@@ -3179,18 +3152,20 @@
       </c>
       <c r="L36" s="5"/>
       <c r="M36" s="5"/>
-      <c r="N36" s="7"/>
+      <c r="N36" s="7" t="s">
+        <v>313</v>
+      </c>
       <c r="O36" s="7"/>
       <c r="P36" s="5" t="s">
         <v>311</v>
       </c>
       <c r="Q36" s="5">
-        <v>1.03</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5" t="s">
@@ -3200,10 +3175,10 @@
         <v>50</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="G37" s="5" t="s">
         <v>307</v>
@@ -3217,23 +3192,23 @@
       <c r="L37" s="5"/>
       <c r="M37" s="5"/>
       <c r="N37" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O37" s="7"/>
       <c r="P37" s="5" t="s">
         <v>311</v>
       </c>
       <c r="Q37" s="5">
-        <v>1.04</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>50</v>
@@ -3242,7 +3217,7 @@
         <v>225</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>107</v>
+        <v>69</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>307</v>
@@ -3255,18 +3230,12 @@
       </c>
       <c r="L38" s="5"/>
       <c r="M38" s="5"/>
-      <c r="N38" s="7" t="s">
-        <v>314</v>
-      </c>
+      <c r="N38" s="7"/>
       <c r="O38" s="7"/>
-      <c r="P38" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q38" s="5">
-        <v>1.05</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P38" s="5"/>
+      <c r="Q38" s="5"/>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39" s="5">
         <v>0</v>
       </c>
@@ -3281,7 +3250,7 @@
         <v>225</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G39" s="5" t="s">
         <v>307</v>
@@ -3299,7 +3268,7 @@
       <c r="P39" s="5"/>
       <c r="Q39" s="5"/>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40" s="5">
         <v>0</v>
       </c>
@@ -3314,7 +3283,7 @@
         <v>225</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G40" s="5" t="s">
         <v>307</v>
@@ -3329,95 +3298,95 @@
       <c r="M40" s="5"/>
       <c r="N40" s="7"/>
       <c r="O40" s="7"/>
-      <c r="P40" s="5"/>
-      <c r="Q40" s="5"/>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A41" s="5">
+      <c r="P40" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q40" s="5">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A41" s="10">
         <v>0</v>
       </c>
       <c r="B41" s="5"/>
-      <c r="C41" s="5" t="s">
+      <c r="C41" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="H41" s="10"/>
+      <c r="I41" s="10"/>
+      <c r="J41" s="10"/>
+      <c r="K41" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="L41" s="10"/>
+      <c r="M41" s="10"/>
+      <c r="N41" s="11"/>
+      <c r="O41" s="11"/>
+      <c r="P41" s="10"/>
+      <c r="Q41" s="10"/>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A42" s="5">
+        <v>0</v>
+      </c>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D41" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E41" s="5" t="s">
+      <c r="D42" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E42" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="F41" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="G41" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="H41" s="5"/>
-      <c r="I41" s="5"/>
-      <c r="J41" s="5"/>
-      <c r="K41" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="L41" s="5"/>
-      <c r="M41" s="5"/>
-      <c r="N41" s="7"/>
-      <c r="O41" s="7"/>
-      <c r="P41" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q41" s="5">
-        <v>1.06</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A42" s="10">
-        <v>0</v>
-      </c>
-      <c r="B42" s="5"/>
-      <c r="C42" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="D42" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="E42" s="10" t="s">
-        <v>225</v>
-      </c>
-      <c r="F42" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="G42" s="10" t="s">
-        <v>307</v>
-      </c>
-      <c r="H42" s="10"/>
-      <c r="I42" s="10"/>
-      <c r="J42" s="10"/>
+      <c r="F42" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="H42" s="5"/>
+      <c r="I42" s="5"/>
+      <c r="J42" s="5"/>
       <c r="K42" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="L42" s="10"/>
-      <c r="M42" s="10"/>
-      <c r="N42" s="11"/>
-      <c r="O42" s="11"/>
-      <c r="P42" s="10"/>
-      <c r="Q42" s="10"/>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="L42" s="5"/>
+      <c r="M42" s="5"/>
+      <c r="N42" s="7"/>
+      <c r="O42" s="7"/>
+      <c r="P42" s="5"/>
+      <c r="Q42" s="5"/>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A43" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G43" s="5" t="s">
         <v>307</v>
@@ -3432,25 +3401,29 @@
       <c r="M43" s="5"/>
       <c r="N43" s="7"/>
       <c r="O43" s="7"/>
-      <c r="P43" s="5"/>
-      <c r="Q43" s="5"/>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P43" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q43" s="5">
+        <v>2.0099999999999998</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A44" s="5">
         <v>1</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5" t="s">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="G44" s="5" t="s">
         <v>307</v>
@@ -3465,29 +3438,25 @@
       <c r="M44" s="5"/>
       <c r="N44" s="7"/>
       <c r="O44" s="7"/>
-      <c r="P44" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q44" s="5">
-        <v>2.0099999999999998</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P44" s="5"/>
+      <c r="Q44" s="5"/>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A45" s="5">
         <v>1</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G45" s="5" t="s">
         <v>307</v>
@@ -3505,7 +3474,7 @@
       <c r="P45" s="5"/>
       <c r="Q45" s="5"/>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46" s="5">
         <v>1</v>
       </c>
@@ -3517,10 +3486,10 @@
         <v>50</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G46" s="5" t="s">
         <v>307</v>
@@ -3538,7 +3507,7 @@
       <c r="P46" s="5"/>
       <c r="Q46" s="5"/>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A47" s="5">
         <v>1</v>
       </c>
@@ -3550,10 +3519,10 @@
         <v>50</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G47" s="5" t="s">
         <v>307</v>
@@ -3571,7 +3540,7 @@
       <c r="P47" s="5"/>
       <c r="Q47" s="5"/>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A48" s="5">
         <v>1</v>
       </c>
@@ -3583,10 +3552,10 @@
         <v>50</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G48" s="5" t="s">
         <v>307</v>
@@ -3601,10 +3570,14 @@
       <c r="M48" s="5"/>
       <c r="N48" s="7"/>
       <c r="O48" s="7"/>
-      <c r="P48" s="5"/>
-      <c r="Q48" s="5"/>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P48" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q48" s="5">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A49" s="5">
         <v>1</v>
       </c>
@@ -3616,10 +3589,10 @@
         <v>50</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G49" s="5" t="s">
         <v>307</v>
@@ -3634,20 +3607,16 @@
       <c r="M49" s="5"/>
       <c r="N49" s="7"/>
       <c r="O49" s="7"/>
-      <c r="P49" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q49" s="5">
-        <v>1.07</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P49" s="5"/>
+      <c r="Q49" s="5"/>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A50" s="5">
         <v>1</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>50</v>
@@ -3674,22 +3643,22 @@
       <c r="P50" s="5"/>
       <c r="Q50" s="5"/>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A51" s="5">
         <v>1</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D51" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G51" s="5" t="s">
         <v>307</v>
@@ -3707,22 +3676,22 @@
       <c r="P51" s="5"/>
       <c r="Q51" s="5"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A52" s="5">
         <v>1</v>
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G52" s="5" t="s">
         <v>307</v>
@@ -3740,22 +3709,22 @@
       <c r="P52" s="5"/>
       <c r="Q52" s="5"/>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A53" s="5">
         <v>1</v>
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>89</v>
+        <v>318</v>
       </c>
       <c r="G53" s="5" t="s">
         <v>307</v>
@@ -3770,10 +3739,14 @@
       <c r="M53" s="5"/>
       <c r="N53" s="7"/>
       <c r="O53" s="7"/>
-      <c r="P53" s="5"/>
-      <c r="Q53" s="5"/>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P53" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q53" s="5">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A54" s="5">
         <v>1</v>
       </c>
@@ -3785,10 +3758,10 @@
         <v>50</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>233</v>
+        <v>349</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>318</v>
+        <v>343</v>
       </c>
       <c r="G54" s="5" t="s">
         <v>307</v>
@@ -3807,25 +3780,25 @@
         <v>311</v>
       </c>
       <c r="Q54" s="5">
-        <v>1.08</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+        <v>2.02</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A55" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B55" s="5"/>
       <c r="C55" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G55" s="5" t="s">
         <v>307</v>
@@ -3844,25 +3817,25 @@
         <v>311</v>
       </c>
       <c r="Q55" s="5">
-        <v>2.02</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+        <v>2.0299999999999998</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A56" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B56" s="5"/>
       <c r="C56" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D56" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>350</v>
+        <v>235</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>344</v>
+        <v>92</v>
       </c>
       <c r="G56" s="5" t="s">
         <v>307</v>
@@ -3881,10 +3854,10 @@
         <v>311</v>
       </c>
       <c r="Q56" s="5">
-        <v>2.0299999999999998</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+        <v>1.0900000000000001</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A57" s="5">
         <v>1</v>
       </c>
@@ -3896,10 +3869,10 @@
         <v>50</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G57" s="5" t="s">
         <v>307</v>
@@ -3917,26 +3890,26 @@
       <c r="P57" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="Q57" s="5">
-        <v>1.0900000000000001</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q57" s="14">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A58" s="5">
         <v>1</v>
       </c>
       <c r="B58" s="5"/>
       <c r="C58" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D58" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G58" s="5" t="s">
         <v>307</v>
@@ -3951,29 +3924,25 @@
       <c r="M58" s="5"/>
       <c r="N58" s="7"/>
       <c r="O58" s="7"/>
-      <c r="P58" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q58" s="14">
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P58" s="5"/>
+      <c r="Q58" s="5"/>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A59" s="5">
         <v>1</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G59" s="5" t="s">
         <v>307</v>
@@ -3991,7 +3960,7 @@
       <c r="P59" s="5"/>
       <c r="Q59" s="5"/>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A60" s="5">
         <v>1</v>
       </c>
@@ -4003,10 +3972,10 @@
         <v>50</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>237</v>
+        <v>214</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="G60" s="5" t="s">
         <v>307</v>
@@ -4024,7 +3993,7 @@
       <c r="P60" s="5"/>
       <c r="Q60" s="5"/>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A61" s="5">
         <v>1</v>
       </c>
@@ -4036,10 +4005,10 @@
         <v>50</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>214</v>
+        <v>238</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="G61" s="5" t="s">
         <v>307</v>
@@ -4054,10 +4023,14 @@
       <c r="M61" s="5"/>
       <c r="N61" s="7"/>
       <c r="O61" s="7"/>
-      <c r="P61" s="5"/>
-      <c r="Q61" s="5"/>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P61" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q61" s="5">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A62" s="5">
         <v>1</v>
       </c>
@@ -4069,10 +4042,10 @@
         <v>50</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G62" s="5" t="s">
         <v>307</v>
@@ -4087,14 +4060,10 @@
       <c r="M62" s="5"/>
       <c r="N62" s="7"/>
       <c r="O62" s="7"/>
-      <c r="P62" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q62" s="5">
-        <v>1.1100000000000001</v>
-      </c>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P62" s="5"/>
+      <c r="Q62" s="5"/>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A63" s="5">
         <v>1</v>
       </c>
@@ -4106,10 +4075,10 @@
         <v>50</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G63" s="5" t="s">
         <v>307</v>
@@ -4127,9 +4096,9 @@
       <c r="P63" s="5"/>
       <c r="Q63" s="5"/>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A64" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B64" s="5"/>
       <c r="C64" s="5" t="s">
@@ -4139,10 +4108,10 @@
         <v>50</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G64" s="5" t="s">
         <v>307</v>
@@ -4160,7 +4129,7 @@
       <c r="P64" s="5"/>
       <c r="Q64" s="5"/>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A65" s="5">
         <v>2</v>
       </c>
@@ -4172,10 +4141,10 @@
         <v>50</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G65" s="5" t="s">
         <v>307</v>
@@ -4190,10 +4159,14 @@
       <c r="M65" s="5"/>
       <c r="N65" s="7"/>
       <c r="O65" s="7"/>
-      <c r="P65" s="5"/>
-      <c r="Q65" s="5"/>
-    </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P65" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q65" s="5">
+        <v>1.1200000000000001</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A66" s="5">
         <v>2</v>
       </c>
@@ -4205,10 +4178,10 @@
         <v>50</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G66" s="5" t="s">
         <v>307</v>
@@ -4227,10 +4200,10 @@
         <v>311</v>
       </c>
       <c r="Q66" s="5">
-        <v>1.1200000000000001</v>
-      </c>
-    </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+        <v>1.1299999999999999</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A67" s="5">
         <v>2</v>
       </c>
@@ -4242,10 +4215,10 @@
         <v>50</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G67" s="5" t="s">
         <v>307</v>
@@ -4264,10 +4237,10 @@
         <v>311</v>
       </c>
       <c r="Q67" s="5">
-        <v>1.1299999999999999</v>
-      </c>
-    </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+        <v>1.1399999999999999</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A68" s="5">
         <v>2</v>
       </c>
@@ -4279,10 +4252,10 @@
         <v>50</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G68" s="5" t="s">
         <v>307</v>
@@ -4297,14 +4270,10 @@
       <c r="M68" s="5"/>
       <c r="N68" s="7"/>
       <c r="O68" s="7"/>
-      <c r="P68" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q68" s="5">
-        <v>1.1399999999999999</v>
-      </c>
-    </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P68" s="5"/>
+      <c r="Q68" s="5"/>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A69" s="5">
         <v>2</v>
       </c>
@@ -4316,10 +4285,10 @@
         <v>50</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G69" s="5" t="s">
         <v>307</v>
@@ -4334,10 +4303,14 @@
       <c r="M69" s="5"/>
       <c r="N69" s="7"/>
       <c r="O69" s="7"/>
-      <c r="P69" s="5"/>
-      <c r="Q69" s="5"/>
-    </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P69" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q69" s="5">
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A70" s="5">
         <v>2</v>
       </c>
@@ -4349,10 +4322,10 @@
         <v>50</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G70" s="5" t="s">
         <v>307</v>
@@ -4371,25 +4344,25 @@
         <v>311</v>
       </c>
       <c r="Q70" s="5">
-        <v>1.1499999999999999</v>
-      </c>
-    </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+        <v>1.1599999999999999</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A71" s="5">
         <v>2</v>
       </c>
       <c r="B71" s="5"/>
       <c r="C71" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D71" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="G71" s="5" t="s">
         <v>307</v>
@@ -4404,14 +4377,10 @@
       <c r="M71" s="5"/>
       <c r="N71" s="7"/>
       <c r="O71" s="7"/>
-      <c r="P71" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q71" s="5">
-        <v>1.1599999999999999</v>
-      </c>
-    </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P71" s="5"/>
+      <c r="Q71" s="5"/>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A72" s="5">
         <v>2</v>
       </c>
@@ -4423,10 +4392,10 @@
         <v>50</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G72" s="5" t="s">
         <v>307</v>
@@ -4444,22 +4413,22 @@
       <c r="P72" s="5"/>
       <c r="Q72" s="5"/>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A73" s="5">
         <v>2</v>
       </c>
       <c r="B73" s="5"/>
       <c r="C73" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D73" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="G73" s="5" t="s">
         <v>307</v>
@@ -4474,10 +4443,14 @@
       <c r="M73" s="5"/>
       <c r="N73" s="7"/>
       <c r="O73" s="7"/>
-      <c r="P73" s="5"/>
-      <c r="Q73" s="5"/>
-    </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P73" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q73" s="5">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A74" s="5">
         <v>2</v>
       </c>
@@ -4489,10 +4462,10 @@
         <v>50</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>225</v>
+        <v>322</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>106</v>
+        <v>320</v>
       </c>
       <c r="G74" s="5" t="s">
         <v>307</v>
@@ -4507,29 +4480,25 @@
       <c r="M74" s="5"/>
       <c r="N74" s="7"/>
       <c r="O74" s="7"/>
-      <c r="P74" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q74" s="5">
-        <v>1.17</v>
-      </c>
-    </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P74" s="5"/>
+      <c r="Q74" s="5"/>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A75" s="5">
         <v>2</v>
       </c>
       <c r="B75" s="5"/>
       <c r="C75" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D75" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>322</v>
+        <v>351</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>320</v>
+        <v>345</v>
       </c>
       <c r="G75" s="5" t="s">
         <v>307</v>
@@ -4544,12 +4513,16 @@
       <c r="M75" s="5"/>
       <c r="N75" s="7"/>
       <c r="O75" s="7"/>
-      <c r="P75" s="5"/>
-      <c r="Q75" s="5"/>
-    </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P75" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q75" s="5">
+        <v>2.04</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A76" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B76" s="5"/>
       <c r="C76" s="5" t="s">
@@ -4559,10 +4532,10 @@
         <v>50</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>351</v>
+        <v>321</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>345</v>
+        <v>319</v>
       </c>
       <c r="G76" s="5" t="s">
         <v>307</v>
@@ -4581,12 +4554,12 @@
         <v>311</v>
       </c>
       <c r="Q76" s="5">
-        <v>2.04</v>
-      </c>
-    </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+        <v>2.0499999999999998</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A77" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B77" s="5"/>
       <c r="C77" s="5" t="s">
@@ -4596,10 +4569,10 @@
         <v>50</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>321</v>
+        <v>249</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>319</v>
+        <v>108</v>
       </c>
       <c r="G77" s="5" t="s">
         <v>307</v>
@@ -4614,14 +4587,10 @@
       <c r="M77" s="5"/>
       <c r="N77" s="7"/>
       <c r="O77" s="7"/>
-      <c r="P77" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q77" s="5">
-        <v>2.0499999999999998</v>
-      </c>
-    </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P77" s="5"/>
+      <c r="Q77" s="5"/>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A78" s="5">
         <v>2</v>
       </c>
@@ -4633,10 +4602,10 @@
         <v>50</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>249</v>
+        <v>352</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>108</v>
+        <v>346</v>
       </c>
       <c r="G78" s="5" t="s">
         <v>307</v>
@@ -4651,10 +4620,14 @@
       <c r="M78" s="5"/>
       <c r="N78" s="7"/>
       <c r="O78" s="7"/>
-      <c r="P78" s="5"/>
-      <c r="Q78" s="5"/>
-    </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P78" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q78" s="5">
+        <v>2.06</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A79" s="5">
         <v>2</v>
       </c>
@@ -4666,10 +4639,10 @@
         <v>50</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>352</v>
+        <v>250</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>346</v>
+        <v>109</v>
       </c>
       <c r="G79" s="5" t="s">
         <v>307</v>
@@ -4684,14 +4657,10 @@
       <c r="M79" s="5"/>
       <c r="N79" s="7"/>
       <c r="O79" s="7"/>
-      <c r="P79" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q79" s="5">
-        <v>2.06</v>
-      </c>
-    </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P79" s="5"/>
+      <c r="Q79" s="5"/>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A80" s="5">
         <v>2</v>
       </c>
@@ -4703,10 +4672,10 @@
         <v>50</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G80" s="5" t="s">
         <v>307</v>
@@ -4724,7 +4693,7 @@
       <c r="P80" s="5"/>
       <c r="Q80" s="5"/>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A81" s="5">
         <v>2</v>
       </c>
@@ -4736,10 +4705,10 @@
         <v>50</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="G81" s="5" t="s">
         <v>307</v>
@@ -4757,25 +4726,25 @@
       <c r="P81" s="5"/>
       <c r="Q81" s="5"/>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A82" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B82" s="5"/>
       <c r="C82" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D82" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>245</v>
+        <v>283</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>103</v>
+        <v>155</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H82" s="5"/>
       <c r="I82" s="5"/>
@@ -4785,30 +4754,34 @@
       </c>
       <c r="L82" s="5"/>
       <c r="M82" s="5"/>
-      <c r="N82" s="7"/>
+      <c r="N82" s="16"/>
       <c r="O82" s="7"/>
-      <c r="P82" s="5"/>
-      <c r="Q82" s="5"/>
-    </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P82" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q82" s="5">
+        <v>2.0699999999999998</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A83" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B83" s="5"/>
       <c r="C83" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D83" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>283</v>
+        <v>353</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>155</v>
+        <v>347</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H83" s="5"/>
       <c r="I83" s="5"/>
@@ -4818,16 +4791,12 @@
       </c>
       <c r="L83" s="5"/>
       <c r="M83" s="5"/>
-      <c r="N83" s="16"/>
+      <c r="N83" s="7"/>
       <c r="O83" s="7"/>
-      <c r="P83" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q83" s="5">
-        <v>2.0699999999999998</v>
-      </c>
-    </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P83" s="5"/>
+      <c r="Q83" s="5"/>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A84" s="5">
         <v>2</v>
       </c>
@@ -4839,10 +4808,10 @@
         <v>50</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>353</v>
+        <v>253</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>347</v>
+        <v>112</v>
       </c>
       <c r="G84" s="5" t="s">
         <v>307</v>
@@ -4860,7 +4829,7 @@
       <c r="P84" s="5"/>
       <c r="Q84" s="5"/>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A85" s="5">
         <v>2</v>
       </c>
@@ -4872,10 +4841,10 @@
         <v>50</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G85" s="5" t="s">
         <v>307</v>
@@ -4893,7 +4862,7 @@
       <c r="P85" s="5"/>
       <c r="Q85" s="5"/>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A86" s="5">
         <v>2</v>
       </c>
@@ -4905,10 +4874,10 @@
         <v>50</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G86" s="5" t="s">
         <v>307</v>
@@ -4926,7 +4895,7 @@
       <c r="P86" s="5"/>
       <c r="Q86" s="5"/>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A87" s="5">
         <v>2</v>
       </c>
@@ -4938,10 +4907,10 @@
         <v>50</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="G87" s="5" t="s">
         <v>307</v>
@@ -4956,10 +4925,14 @@
       <c r="M87" s="5"/>
       <c r="N87" s="7"/>
       <c r="O87" s="7"/>
-      <c r="P87" s="5"/>
-      <c r="Q87" s="5"/>
-    </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P87" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q87" s="5">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A88" s="5">
         <v>2</v>
       </c>
@@ -4971,10 +4944,10 @@
         <v>50</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="G88" s="5" t="s">
         <v>307</v>
@@ -4989,16 +4962,12 @@
       <c r="M88" s="5"/>
       <c r="N88" s="7"/>
       <c r="O88" s="7"/>
-      <c r="P88" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q88" s="5">
-        <v>1.18</v>
-      </c>
-    </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P88" s="5"/>
+      <c r="Q88" s="5"/>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A89" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B89" s="5"/>
       <c r="C89" s="5" t="s">
@@ -5008,13 +4977,13 @@
         <v>50</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H89" s="5"/>
       <c r="I89" s="5"/>
@@ -5029,13 +4998,13 @@
       <c r="P89" s="5"/>
       <c r="Q89" s="5"/>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A90" s="5">
         <v>3</v>
       </c>
       <c r="B90" s="5"/>
       <c r="C90" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D90" s="5" t="s">
         <v>50</v>
@@ -5062,7 +5031,7 @@
       <c r="P90" s="5"/>
       <c r="Q90" s="5"/>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A91" s="5">
         <v>3</v>
       </c>
@@ -5074,10 +5043,10 @@
         <v>50</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G91" s="5" t="s">
         <v>309</v>
@@ -5095,22 +5064,22 @@
       <c r="P91" s="5"/>
       <c r="Q91" s="5"/>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A92" s="5">
         <v>3</v>
       </c>
       <c r="B92" s="5"/>
       <c r="C92" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D92" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G92" s="5" t="s">
         <v>309</v>
@@ -5128,13 +5097,13 @@
       <c r="P92" s="5"/>
       <c r="Q92" s="5"/>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A93" s="5">
         <v>3</v>
       </c>
       <c r="B93" s="5"/>
       <c r="C93" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D93" s="5" t="s">
         <v>50</v>
@@ -5161,7 +5130,7 @@
       <c r="P93" s="5"/>
       <c r="Q93" s="5"/>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A94" s="5">
         <v>3</v>
       </c>
@@ -5173,10 +5142,10 @@
         <v>50</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="G94" s="5" t="s">
         <v>309</v>
@@ -5194,22 +5163,22 @@
       <c r="P94" s="5"/>
       <c r="Q94" s="5"/>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A95" s="5">
         <v>3</v>
       </c>
       <c r="B95" s="5"/>
       <c r="C95" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D95" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="G95" s="5" t="s">
         <v>309</v>
@@ -5227,13 +5196,13 @@
       <c r="P95" s="5"/>
       <c r="Q95" s="5"/>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A96" s="5">
         <v>3</v>
       </c>
       <c r="B96" s="5"/>
       <c r="C96" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D96" s="5" t="s">
         <v>50</v>
@@ -5260,7 +5229,7 @@
       <c r="P96" s="5"/>
       <c r="Q96" s="5"/>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A97" s="5">
         <v>3</v>
       </c>
@@ -5272,10 +5241,10 @@
         <v>50</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="G97" s="5" t="s">
         <v>309</v>
@@ -5293,7 +5262,7 @@
       <c r="P97" s="5"/>
       <c r="Q97" s="5"/>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A98" s="5">
         <v>3</v>
       </c>
@@ -5305,10 +5274,10 @@
         <v>50</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G98" s="5" t="s">
         <v>309</v>
@@ -5326,7 +5295,7 @@
       <c r="P98" s="5"/>
       <c r="Q98" s="5"/>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A99" s="5">
         <v>3</v>
       </c>
@@ -5338,10 +5307,10 @@
         <v>50</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="G99" s="5" t="s">
         <v>309</v>
@@ -5359,7 +5328,7 @@
       <c r="P99" s="5"/>
       <c r="Q99" s="5"/>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A100" s="5">
         <v>3</v>
       </c>
@@ -5371,10 +5340,10 @@
         <v>50</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G100" s="5" t="s">
         <v>309</v>
@@ -5392,7 +5361,7 @@
       <c r="P100" s="5"/>
       <c r="Q100" s="5"/>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A101" s="5">
         <v>3</v>
       </c>
@@ -5404,10 +5373,10 @@
         <v>50</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="G101" s="5" t="s">
         <v>309</v>
@@ -5425,22 +5394,22 @@
       <c r="P101" s="5"/>
       <c r="Q101" s="5"/>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A102" s="5">
         <v>3</v>
       </c>
       <c r="B102" s="5"/>
       <c r="C102" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D102" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="G102" s="5" t="s">
         <v>309</v>
@@ -5458,13 +5427,13 @@
       <c r="P102" s="5"/>
       <c r="Q102" s="5"/>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A103" s="5">
         <v>3</v>
       </c>
       <c r="B103" s="5"/>
       <c r="C103" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D103" s="5" t="s">
         <v>50</v>
@@ -5491,7 +5460,7 @@
       <c r="P103" s="5"/>
       <c r="Q103" s="5"/>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A104" s="5">
         <v>3</v>
       </c>
@@ -5503,10 +5472,10 @@
         <v>50</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G104" s="5" t="s">
         <v>309</v>
@@ -5524,22 +5493,22 @@
       <c r="P104" s="5"/>
       <c r="Q104" s="5"/>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A105" s="5">
         <v>3</v>
       </c>
       <c r="B105" s="5"/>
       <c r="C105" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D105" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G105" s="5" t="s">
         <v>309</v>
@@ -5552,18 +5521,18 @@
       </c>
       <c r="L105" s="5"/>
       <c r="M105" s="5"/>
-      <c r="N105" s="7"/>
+      <c r="N105" s="16"/>
       <c r="O105" s="7"/>
       <c r="P105" s="5"/>
       <c r="Q105" s="5"/>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A106" s="5">
         <v>3</v>
       </c>
       <c r="B106" s="5"/>
       <c r="C106" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D106" s="5" t="s">
         <v>50</v>
@@ -5590,7 +5559,7 @@
       <c r="P106" s="5"/>
       <c r="Q106" s="5"/>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A107" s="5">
         <v>3</v>
       </c>
@@ -5602,10 +5571,10 @@
         <v>50</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="G107" s="5" t="s">
         <v>309</v>
@@ -5623,22 +5592,22 @@
       <c r="P107" s="5"/>
       <c r="Q107" s="5"/>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A108" s="5">
         <v>3</v>
       </c>
       <c r="B108" s="5"/>
       <c r="C108" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D108" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="G108" s="5" t="s">
         <v>309</v>
@@ -5656,13 +5625,13 @@
       <c r="P108" s="5"/>
       <c r="Q108" s="5"/>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A109" s="5">
         <v>3</v>
       </c>
       <c r="B109" s="5"/>
       <c r="C109" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D109" s="5" t="s">
         <v>50</v>
@@ -5689,7 +5658,7 @@
       <c r="P109" s="5"/>
       <c r="Q109" s="5"/>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A110" s="5">
         <v>3</v>
       </c>
@@ -5701,10 +5670,10 @@
         <v>50</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="G110" s="5" t="s">
         <v>309</v>
@@ -5722,7 +5691,7 @@
       <c r="P110" s="5"/>
       <c r="Q110" s="5"/>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A111" s="5">
         <v>3</v>
       </c>
@@ -5734,10 +5703,10 @@
         <v>50</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G111" s="5" t="s">
         <v>309</v>
@@ -5755,22 +5724,22 @@
       <c r="P111" s="5"/>
       <c r="Q111" s="5"/>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A112" s="5">
         <v>3</v>
       </c>
       <c r="B112" s="5"/>
       <c r="C112" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D112" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>255</v>
+        <v>225</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="G112" s="5" t="s">
         <v>309</v>
@@ -5788,7 +5757,7 @@
       <c r="P112" s="5"/>
       <c r="Q112" s="5"/>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A113" s="5">
         <v>3</v>
       </c>
@@ -5800,10 +5769,10 @@
         <v>50</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>131</v>
+        <v>83</v>
       </c>
       <c r="G113" s="5" t="s">
         <v>309</v>
@@ -5821,7 +5790,7 @@
       <c r="P113" s="5"/>
       <c r="Q113" s="5"/>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A114" s="5">
         <v>3</v>
       </c>
@@ -5833,10 +5802,10 @@
         <v>50</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="G114" s="5" t="s">
         <v>309</v>
@@ -5854,7 +5823,7 @@
       <c r="P114" s="5"/>
       <c r="Q114" s="5"/>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A115" s="5">
         <v>3</v>
       </c>
@@ -5866,10 +5835,10 @@
         <v>50</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G115" s="5" t="s">
         <v>309</v>
@@ -5887,7 +5856,7 @@
       <c r="P115" s="5"/>
       <c r="Q115" s="5"/>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A116" s="5">
         <v>3</v>
       </c>
@@ -5899,10 +5868,10 @@
         <v>50</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G116" s="5" t="s">
         <v>309</v>
@@ -5920,7 +5889,7 @@
       <c r="P116" s="5"/>
       <c r="Q116" s="5"/>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A117" s="5">
         <v>3</v>
       </c>
@@ -5932,10 +5901,10 @@
         <v>50</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G117" s="5" t="s">
         <v>309</v>
@@ -5953,7 +5922,7 @@
       <c r="P117" s="5"/>
       <c r="Q117" s="5"/>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A118" s="5">
         <v>3</v>
       </c>
@@ -5965,10 +5934,10 @@
         <v>50</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G118" s="5" t="s">
         <v>309</v>
@@ -5986,7 +5955,7 @@
       <c r="P118" s="5"/>
       <c r="Q118" s="5"/>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A119" s="5">
         <v>3</v>
       </c>
@@ -5998,10 +5967,10 @@
         <v>50</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G119" s="5" t="s">
         <v>309</v>
@@ -6019,25 +5988,25 @@
       <c r="P119" s="5"/>
       <c r="Q119" s="5"/>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A120" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B120" s="5"/>
       <c r="C120" s="5" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>247</v>
+        <v>271</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>105</v>
+        <v>138</v>
       </c>
       <c r="G120" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H120" s="5"/>
       <c r="I120" s="5"/>
@@ -6052,7 +6021,7 @@
       <c r="P120" s="5"/>
       <c r="Q120" s="5"/>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A121" s="5">
         <v>2</v>
       </c>
@@ -6061,13 +6030,13 @@
         <v>12</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G121" s="5" t="s">
         <v>307</v>
@@ -6085,7 +6054,7 @@
       <c r="P121" s="5"/>
       <c r="Q121" s="5"/>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A122" s="5">
         <v>2</v>
       </c>
@@ -6094,13 +6063,13 @@
         <v>12</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G122" s="5" t="s">
         <v>307</v>
@@ -6118,22 +6087,22 @@
       <c r="P122" s="5"/>
       <c r="Q122" s="5"/>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A123" s="5">
         <v>2</v>
       </c>
       <c r="B123" s="5"/>
       <c r="C123" s="5" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>141</v>
+        <v>13</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>273</v>
+        <v>199</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>142</v>
+        <v>22</v>
       </c>
       <c r="G123" s="5" t="s">
         <v>307</v>
@@ -6151,25 +6120,25 @@
       <c r="P123" s="5"/>
       <c r="Q123" s="5"/>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A124" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B124" s="5"/>
       <c r="C124" s="5" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D124" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>199</v>
+        <v>274</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>22</v>
+        <v>143</v>
       </c>
       <c r="G124" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H124" s="5"/>
       <c r="I124" s="5"/>
@@ -6184,7 +6153,7 @@
       <c r="P124" s="5"/>
       <c r="Q124" s="5"/>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A125" s="5">
         <v>3</v>
       </c>
@@ -6196,10 +6165,10 @@
         <v>13</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G125" s="5" t="s">
         <v>309</v>
@@ -6217,7 +6186,7 @@
       <c r="P125" s="5"/>
       <c r="Q125" s="5"/>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A126" s="5">
         <v>3</v>
       </c>
@@ -6226,13 +6195,13 @@
         <v>12</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G126" s="5" t="s">
         <v>309</v>
@@ -6250,7 +6219,7 @@
       <c r="P126" s="5"/>
       <c r="Q126" s="5"/>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A127" s="5">
         <v>3</v>
       </c>
@@ -6259,13 +6228,13 @@
         <v>12</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>145</v>
+        <v>13</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G127" s="5" t="s">
         <v>309</v>
@@ -6283,7 +6252,7 @@
       <c r="P127" s="5"/>
       <c r="Q127" s="5"/>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A128" s="5">
         <v>3</v>
       </c>
@@ -6295,10 +6264,10 @@
         <v>13</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="G128" s="5" t="s">
         <v>309</v>
@@ -6316,7 +6285,7 @@
       <c r="P128" s="5"/>
       <c r="Q128" s="5"/>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A129" s="5">
         <v>3</v>
       </c>
@@ -6328,10 +6297,10 @@
         <v>13</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G129" s="5" t="s">
         <v>309</v>
@@ -6349,7 +6318,7 @@
       <c r="P129" s="5"/>
       <c r="Q129" s="5"/>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A130" s="5">
         <v>3</v>
       </c>
@@ -6358,13 +6327,13 @@
         <v>12</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>13</v>
+        <v>152</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G130" s="5" t="s">
         <v>309</v>
@@ -6382,25 +6351,25 @@
       <c r="P130" s="5"/>
       <c r="Q130" s="5"/>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A131" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B131" s="5"/>
       <c r="C131" s="5" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>152</v>
+        <v>50</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>281</v>
+        <v>354</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>153</v>
+        <v>348</v>
       </c>
       <c r="G131" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H131" s="5"/>
       <c r="I131" s="5"/>
@@ -6410,30 +6379,34 @@
       </c>
       <c r="L131" s="5"/>
       <c r="M131" s="5"/>
-      <c r="N131" s="16"/>
+      <c r="N131" s="7"/>
       <c r="O131" s="7"/>
-      <c r="P131" s="5"/>
-      <c r="Q131" s="5"/>
-    </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P131" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q131" s="5">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="132" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A132" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B132" s="5"/>
       <c r="C132" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D132" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>354</v>
+        <v>284</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>348</v>
+        <v>156</v>
       </c>
       <c r="G132" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H132" s="5"/>
       <c r="I132" s="5"/>
@@ -6443,16 +6416,12 @@
       </c>
       <c r="L132" s="5"/>
       <c r="M132" s="5"/>
-      <c r="N132" s="7"/>
+      <c r="N132" s="16"/>
       <c r="O132" s="7"/>
-      <c r="P132" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q132" s="5">
-        <v>2.08</v>
-      </c>
-    </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P132" s="5"/>
+      <c r="Q132" s="5"/>
+    </row>
+    <row r="133" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A133" s="5">
         <v>3</v>
       </c>
@@ -6464,10 +6433,10 @@
         <v>50</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>284</v>
+        <v>225</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G133" s="5" t="s">
         <v>309</v>
@@ -6485,7 +6454,7 @@
       <c r="P133" s="5"/>
       <c r="Q133" s="5"/>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A134" s="5">
         <v>3</v>
       </c>
@@ -6500,7 +6469,7 @@
         <v>225</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G134" s="5" t="s">
         <v>309</v>
@@ -6518,7 +6487,7 @@
       <c r="P134" s="5"/>
       <c r="Q134" s="5"/>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A135" s="5">
         <v>3</v>
       </c>
@@ -6533,7 +6502,7 @@
         <v>225</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G135" s="5" t="s">
         <v>309</v>
@@ -6551,7 +6520,7 @@
       <c r="P135" s="5"/>
       <c r="Q135" s="5"/>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A136" s="5">
         <v>3</v>
       </c>
@@ -6566,7 +6535,7 @@
         <v>225</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G136" s="5" t="s">
         <v>309</v>
@@ -6584,7 +6553,7 @@
       <c r="P136" s="5"/>
       <c r="Q136" s="5"/>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A137" s="5">
         <v>3</v>
       </c>
@@ -6599,7 +6568,7 @@
         <v>225</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G137" s="5" t="s">
         <v>309</v>
@@ -6617,13 +6586,13 @@
       <c r="P137" s="5"/>
       <c r="Q137" s="5"/>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A138" s="5">
         <v>3</v>
       </c>
       <c r="B138" s="5"/>
       <c r="C138" s="5" t="s">
-        <v>80</v>
+        <v>162</v>
       </c>
       <c r="D138" s="5" t="s">
         <v>50</v>
@@ -6632,7 +6601,7 @@
         <v>225</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G138" s="5" t="s">
         <v>309</v>
@@ -6650,7 +6619,7 @@
       <c r="P138" s="5"/>
       <c r="Q138" s="5"/>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A139" s="5">
         <v>3</v>
       </c>
@@ -6665,7 +6634,7 @@
         <v>225</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G139" s="5" t="s">
         <v>309</v>
@@ -6683,7 +6652,7 @@
       <c r="P139" s="5"/>
       <c r="Q139" s="5"/>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A140" s="5">
         <v>3</v>
       </c>
@@ -6698,7 +6667,7 @@
         <v>225</v>
       </c>
       <c r="F140" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G140" s="5" t="s">
         <v>309</v>
@@ -6716,7 +6685,7 @@
       <c r="P140" s="5"/>
       <c r="Q140" s="5"/>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A141" s="5">
         <v>3</v>
       </c>
@@ -6731,7 +6700,7 @@
         <v>225</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G141" s="5" t="s">
         <v>309</v>
@@ -6749,13 +6718,13 @@
       <c r="P141" s="5"/>
       <c r="Q141" s="5"/>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A142" s="5">
         <v>3</v>
       </c>
       <c r="B142" s="5"/>
       <c r="C142" s="5" t="s">
-        <v>162</v>
+        <v>49</v>
       </c>
       <c r="D142" s="5" t="s">
         <v>50</v>
@@ -6764,7 +6733,7 @@
         <v>225</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G142" s="5" t="s">
         <v>309</v>
@@ -6782,13 +6751,13 @@
       <c r="P142" s="5"/>
       <c r="Q142" s="5"/>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A143" s="5">
         <v>3</v>
       </c>
       <c r="B143" s="5"/>
       <c r="C143" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D143" s="5" t="s">
         <v>50</v>
@@ -6797,7 +6766,7 @@
         <v>225</v>
       </c>
       <c r="F143" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G143" s="5" t="s">
         <v>309</v>
@@ -6815,7 +6784,7 @@
       <c r="P143" s="5"/>
       <c r="Q143" s="5"/>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A144" s="5">
         <v>3</v>
       </c>
@@ -6830,7 +6799,7 @@
         <v>225</v>
       </c>
       <c r="F144" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G144" s="5" t="s">
         <v>309</v>
@@ -6848,7 +6817,7 @@
       <c r="P144" s="5"/>
       <c r="Q144" s="5"/>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A145" s="5">
         <v>3</v>
       </c>
@@ -6863,7 +6832,7 @@
         <v>225</v>
       </c>
       <c r="F145" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G145" s="5" t="s">
         <v>309</v>
@@ -6881,31 +6850,37 @@
       <c r="P145" s="5"/>
       <c r="Q145" s="5"/>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A146" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B146" s="5"/>
       <c r="C146" s="5" t="s">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G146" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="H146" s="5"/>
-      <c r="I146" s="5"/>
-      <c r="J146" s="5"/>
+      <c r="H146" s="6">
+        <v>46094</v>
+      </c>
+      <c r="I146" s="9">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="J146" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="K146" s="5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L146" s="5"/>
       <c r="M146" s="5"/>
@@ -6914,7 +6889,7 @@
       <c r="P146" s="5"/>
       <c r="Q146" s="5"/>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A147" s="5">
         <v>0</v>
       </c>
@@ -6926,10 +6901,10 @@
         <v>13</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F147" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G147" s="5" t="s">
         <v>309</v>
@@ -6953,31 +6928,31 @@
       <c r="P147" s="5"/>
       <c r="Q147" s="5"/>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A148" s="5">
         <v>0</v>
       </c>
       <c r="B148" s="5"/>
       <c r="C148" s="5" t="s">
-        <v>132</v>
+        <v>173</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>301</v>
+        <v>174</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="G148" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H148" s="6">
-        <v>46094</v>
+        <v>46095</v>
       </c>
       <c r="I148" s="9">
-        <v>0.41666666666666669</v>
+        <v>0.625</v>
       </c>
       <c r="J148" s="5" t="s">
         <v>15</v>
@@ -6992,35 +6967,33 @@
       <c r="P148" s="5"/>
       <c r="Q148" s="5"/>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A149" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B149" s="5"/>
       <c r="C149" s="5" t="s">
-        <v>173</v>
+        <v>12</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>174</v>
+        <v>285</v>
       </c>
       <c r="F149" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G149" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H149" s="6">
-        <v>46095</v>
+        <v>46128</v>
       </c>
       <c r="I149" s="9">
-        <v>0.625</v>
-      </c>
-      <c r="J149" s="5" t="s">
-        <v>15</v>
-      </c>
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="J149" s="5"/>
       <c r="K149" s="5" t="s">
         <v>73</v>
       </c>
@@ -7031,7 +7004,7 @@
       <c r="P149" s="5"/>
       <c r="Q149" s="5"/>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A150" s="5">
         <v>3</v>
       </c>
@@ -7043,21 +7016,23 @@
         <v>13</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G150" s="5" t="s">
         <v>309</v>
       </c>
       <c r="H150" s="6">
-        <v>46128</v>
+        <v>46139</v>
       </c>
       <c r="I150" s="9">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="J150" s="5"/>
+        <v>0.25</v>
+      </c>
+      <c r="J150" s="9">
+        <v>0.33333333333333331</v>
+      </c>
       <c r="K150" s="5" t="s">
         <v>73</v>
       </c>
@@ -7068,7 +7043,7 @@
       <c r="P150" s="5"/>
       <c r="Q150" s="5"/>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A151" s="5">
         <v>3</v>
       </c>
@@ -7077,25 +7052,25 @@
         <v>12</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>13</v>
+        <v>178</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G151" s="5" t="s">
         <v>309</v>
       </c>
       <c r="H151" s="6">
-        <v>46139</v>
+        <v>46141</v>
       </c>
       <c r="I151" s="9">
-        <v>0.25</v>
+        <v>0.67361111111111116</v>
       </c>
       <c r="J151" s="9">
-        <v>0.33333333333333331</v>
+        <v>0.96527777777777779</v>
       </c>
       <c r="K151" s="5" t="s">
         <v>73</v>
@@ -7107,7 +7082,7 @@
       <c r="P151" s="5"/>
       <c r="Q151" s="5"/>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A152" s="5">
         <v>3</v>
       </c>
@@ -7116,25 +7091,25 @@
         <v>12</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>178</v>
+        <v>13</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G152" s="5" t="s">
         <v>309</v>
       </c>
       <c r="H152" s="6">
-        <v>46141</v>
+        <v>46146</v>
       </c>
       <c r="I152" s="9">
-        <v>0.67361111111111116</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J152" s="9">
-        <v>0.96527777777777779</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="K152" s="5" t="s">
         <v>73</v>
@@ -7146,7 +7121,7 @@
       <c r="P152" s="5"/>
       <c r="Q152" s="5"/>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A153" s="5">
         <v>3</v>
       </c>
@@ -7155,25 +7130,25 @@
         <v>12</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>13</v>
+        <v>181</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G153" s="5" t="s">
         <v>309</v>
       </c>
       <c r="H153" s="6">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="I153" s="9">
-        <v>0.33333333333333331</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="J153" s="9">
-        <v>0.41666666666666669</v>
+        <v>0.5</v>
       </c>
       <c r="K153" s="5" t="s">
         <v>73</v>
@@ -7185,48 +7160,48 @@
       <c r="P153" s="5"/>
       <c r="Q153" s="5"/>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A154" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B154" s="5"/>
       <c r="C154" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>181</v>
+        <v>13</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="F154" s="5" t="s">
-        <v>182</v>
+        <v>290</v>
+      </c>
+      <c r="F154" s="18" t="s">
+        <v>183</v>
       </c>
       <c r="G154" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H154" s="6">
         <v>46147</v>
       </c>
       <c r="I154" s="9">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="J154" s="9">
-        <v>0.5</v>
-      </c>
+        <v>0.625</v>
+      </c>
+      <c r="J154" s="5"/>
       <c r="K154" s="5" t="s">
         <v>73</v>
       </c>
       <c r="L154" s="5"/>
       <c r="M154" s="5"/>
       <c r="N154" s="16"/>
-      <c r="O154" s="7"/>
+      <c r="O154" s="7" t="s">
+        <v>325</v>
+      </c>
       <c r="P154" s="5"/>
       <c r="Q154" s="5"/>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A155" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B155" s="5"/>
       <c r="C155" s="5" t="s">
@@ -7236,34 +7211,34 @@
         <v>13</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="F155" s="18" t="s">
-        <v>183</v>
+        <v>291</v>
+      </c>
+      <c r="F155" s="5" t="s">
+        <v>184</v>
       </c>
       <c r="G155" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H155" s="6">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="I155" s="9">
-        <v>0.625</v>
-      </c>
-      <c r="J155" s="5"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J155" s="9">
+        <v>0.41666666666666669</v>
+      </c>
       <c r="K155" s="5" t="s">
         <v>73</v>
       </c>
       <c r="L155" s="5"/>
       <c r="M155" s="5"/>
       <c r="N155" s="16"/>
-      <c r="O155" s="7" t="s">
-        <v>325</v>
-      </c>
+      <c r="O155" s="7"/>
       <c r="P155" s="5"/>
       <c r="Q155" s="5"/>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A156" s="5">
         <v>3</v>
       </c>
@@ -7272,25 +7247,23 @@
         <v>12</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>13</v>
+        <v>185</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G156" s="5" t="s">
         <v>309</v>
       </c>
       <c r="H156" s="6">
-        <v>46149</v>
-      </c>
-      <c r="I156" s="9">
-        <v>0.33333333333333331</v>
-      </c>
+        <v>46155</v>
+      </c>
+      <c r="I156" s="5"/>
       <c r="J156" s="9">
-        <v>0.41666666666666669</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="K156" s="5" t="s">
         <v>73</v>
@@ -7302,7 +7275,7 @@
       <c r="P156" s="5"/>
       <c r="Q156" s="5"/>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A157" s="5">
         <v>3</v>
       </c>
@@ -7311,23 +7284,23 @@
         <v>12</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>185</v>
+        <v>13</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F157" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G157" s="5" t="s">
         <v>309</v>
       </c>
       <c r="H157" s="6">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="I157" s="5"/>
       <c r="J157" s="9">
-        <v>0.45833333333333331</v>
+        <v>0.625</v>
       </c>
       <c r="K157" s="5" t="s">
         <v>73</v>
@@ -7339,9 +7312,9 @@
       <c r="P157" s="5"/>
       <c r="Q157" s="5"/>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A158" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B158" s="5"/>
       <c r="C158" s="5" t="s">
@@ -7351,20 +7324,22 @@
         <v>13</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G158" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H158" s="6">
-        <v>46156</v>
-      </c>
-      <c r="I158" s="5"/>
+        <v>46163</v>
+      </c>
+      <c r="I158" s="9">
+        <v>0.29166666666666669</v>
+      </c>
       <c r="J158" s="9">
-        <v>0.625</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="K158" s="5" t="s">
         <v>73</v>
@@ -7376,7 +7351,7 @@
       <c r="P158" s="5"/>
       <c r="Q158" s="5"/>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A159" s="5">
         <v>2</v>
       </c>
@@ -7388,75 +7363,75 @@
         <v>13</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="F159" s="5" t="s">
-        <v>188</v>
+        <v>295</v>
+      </c>
+      <c r="F159" s="18" t="s">
+        <v>189</v>
       </c>
       <c r="G159" s="5" t="s">
         <v>307</v>
       </c>
       <c r="H159" s="6">
-        <v>46163</v>
-      </c>
-      <c r="I159" s="9">
-        <v>0.29166666666666669</v>
-      </c>
+        <v>46164</v>
+      </c>
+      <c r="I159" s="5"/>
       <c r="J159" s="9">
-        <v>0.33333333333333331</v>
+        <v>0.375</v>
       </c>
       <c r="K159" s="5" t="s">
         <v>73</v>
       </c>
       <c r="L159" s="5"/>
       <c r="M159" s="5"/>
-      <c r="N159" s="16"/>
-      <c r="O159" s="7"/>
+      <c r="N159" s="16" t="s">
+        <v>338</v>
+      </c>
+      <c r="O159" s="16" t="s">
+        <v>338</v>
+      </c>
       <c r="P159" s="5"/>
       <c r="Q159" s="5"/>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A160" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B160" s="5"/>
       <c r="C160" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>13</v>
+        <v>190</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="F160" s="18" t="s">
-        <v>189</v>
+        <v>296</v>
+      </c>
+      <c r="F160" s="5" t="s">
+        <v>191</v>
       </c>
       <c r="G160" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H160" s="6">
-        <v>46164</v>
-      </c>
-      <c r="I160" s="5"/>
+        <v>46167</v>
+      </c>
+      <c r="I160" s="9">
+        <v>0.22916666666666666</v>
+      </c>
       <c r="J160" s="9">
-        <v>0.375</v>
+        <v>0.5625</v>
       </c>
       <c r="K160" s="5" t="s">
         <v>73</v>
       </c>
       <c r="L160" s="5"/>
       <c r="M160" s="5"/>
-      <c r="N160" s="16" t="s">
-        <v>338</v>
-      </c>
-      <c r="O160" s="16" t="s">
-        <v>338</v>
-      </c>
+      <c r="N160" s="16"/>
+      <c r="O160" s="7"/>
       <c r="P160" s="5"/>
       <c r="Q160" s="5"/>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A161" s="5">
         <v>3</v>
       </c>
@@ -7465,25 +7440,25 @@
         <v>12</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>190</v>
+        <v>13</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G161" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="H161" s="6">
-        <v>46167</v>
+      <c r="H161" s="12">
+        <v>46170</v>
       </c>
       <c r="I161" s="9">
-        <v>0.22916666666666666</v>
-      </c>
-      <c r="J161" s="9">
-        <v>0.5625</v>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J161" s="13">
+        <v>0.41666666666666669</v>
       </c>
       <c r="K161" s="5" t="s">
         <v>73</v>
@@ -7495,7 +7470,7 @@
       <c r="P161" s="5"/>
       <c r="Q161" s="5"/>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A162" s="5">
         <v>3</v>
       </c>
@@ -7504,25 +7479,25 @@
         <v>12</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G162" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="H162" s="12">
-        <v>46170</v>
+      <c r="H162" s="6">
+        <v>46174</v>
       </c>
       <c r="I162" s="9">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="J162" s="13">
-        <v>0.41666666666666669</v>
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="J162" s="9">
+        <v>0.72916666666666663</v>
       </c>
       <c r="K162" s="5" t="s">
         <v>73</v>
@@ -7534,46 +7509,50 @@
       <c r="P162" s="5"/>
       <c r="Q162" s="5"/>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A163" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B163" s="5"/>
       <c r="C163" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="F163" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
+      </c>
+      <c r="F163" s="18" t="s">
+        <v>19</v>
       </c>
       <c r="G163" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H163" s="6">
-        <v>46174</v>
-      </c>
-      <c r="I163" s="9">
-        <v>0.64583333333333337</v>
-      </c>
+        <v>46204</v>
+      </c>
+      <c r="I163" s="5"/>
       <c r="J163" s="9">
-        <v>0.72916666666666663</v>
+        <v>0.875</v>
       </c>
       <c r="K163" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="L163" s="5"/>
-      <c r="M163" s="5"/>
-      <c r="N163" s="16"/>
-      <c r="O163" s="7"/>
+      <c r="L163" s="6">
+        <v>46182</v>
+      </c>
+      <c r="M163" s="6"/>
+      <c r="N163" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="O163" s="7" t="s">
+        <v>326</v>
+      </c>
       <c r="P163" s="5"/>
       <c r="Q163" s="5"/>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A164" s="5">
         <v>1</v>
       </c>
@@ -7585,251 +7564,253 @@
         <v>13</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F164" s="18" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G164" s="5" t="s">
         <v>307</v>
       </c>
       <c r="H164" s="6">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="I164" s="5"/>
       <c r="J164" s="9">
-        <v>0.875</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="K164" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="L164" s="6">
-        <v>46182</v>
-      </c>
-      <c r="M164" s="6"/>
+      <c r="L164" s="5"/>
+      <c r="M164" s="5"/>
       <c r="N164" s="7" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="O164" s="7" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="P164" s="5"/>
       <c r="Q164" s="5"/>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A165" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B165" s="5"/>
       <c r="C165" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="F165" s="18" t="s">
-        <v>17</v>
+        <v>206</v>
+      </c>
+      <c r="F165" s="5" t="s">
+        <v>34</v>
       </c>
       <c r="G165" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H165" s="6">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="I165" s="5"/>
       <c r="J165" s="9">
-        <v>0.41666666666666669</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="K165" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="L165" s="5"/>
-      <c r="M165" s="5"/>
-      <c r="N165" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="O165" s="7" t="s">
-        <v>330</v>
-      </c>
+      <c r="L165" s="6">
+        <v>46189</v>
+      </c>
+      <c r="M165" s="5">
+        <v>1.06</v>
+      </c>
+      <c r="N165" s="7"/>
+      <c r="O165" s="7"/>
       <c r="P165" s="5"/>
       <c r="Q165" s="5"/>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A166" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B166" s="5"/>
       <c r="C166" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E166" s="5" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="G166" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="H166" s="6">
-        <v>46213</v>
-      </c>
-      <c r="I166" s="5"/>
-      <c r="J166" s="9">
-        <v>0.66666666666666663</v>
+        <v>307</v>
+      </c>
+      <c r="H166" s="2">
+        <v>46218</v>
+      </c>
+      <c r="I166" s="9">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="J166" s="3">
+        <v>0.5</v>
       </c>
       <c r="K166" s="5" t="s">
         <v>73</v>
       </c>
       <c r="L166" s="6">
-        <v>46189</v>
-      </c>
-      <c r="M166" s="5">
-        <v>1.06</v>
-      </c>
-      <c r="N166" s="7"/>
+        <v>46182</v>
+      </c>
+      <c r="M166" s="6"/>
+      <c r="N166" s="7" t="s">
+        <v>355</v>
+      </c>
       <c r="O166" s="7"/>
       <c r="P166" s="5"/>
       <c r="Q166" s="5"/>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A167" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B167" s="5"/>
       <c r="C167" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="G167" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="H167" s="2">
+        <v>309</v>
+      </c>
+      <c r="H167" s="12">
         <v>46218</v>
       </c>
       <c r="I167" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J167" s="3">
-        <v>0.5</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="J167" s="13">
+        <v>0.625</v>
       </c>
       <c r="K167" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="L167" s="6">
-        <v>46182</v>
-      </c>
-      <c r="M167" s="6"/>
+      <c r="L167" s="5"/>
+      <c r="M167" s="5">
+        <v>2.02</v>
+      </c>
       <c r="N167" s="7" t="s">
-        <v>355</v>
+        <v>315</v>
       </c>
       <c r="O167" s="7"/>
       <c r="P167" s="5"/>
       <c r="Q167" s="5"/>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A168" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B168" s="5"/>
       <c r="C168" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E168" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="F168" s="5" t="s">
-        <v>63</v>
+        <v>198</v>
+      </c>
+      <c r="F168" s="18" t="s">
+        <v>20</v>
       </c>
       <c r="G168" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="H168" s="12">
-        <v>46218</v>
+        <v>307</v>
+      </c>
+      <c r="H168" s="2">
+        <v>46219</v>
       </c>
       <c r="I168" s="9">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="J168" s="3">
         <v>0.58333333333333337</v>
-      </c>
-      <c r="J168" s="13">
-        <v>0.625</v>
       </c>
       <c r="K168" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="L168" s="5"/>
-      <c r="M168" s="5">
-        <v>2.02</v>
-      </c>
+      <c r="L168" s="6">
+        <v>46182</v>
+      </c>
+      <c r="M168" s="6"/>
       <c r="N168" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="O168" s="7"/>
+        <v>317</v>
+      </c>
+      <c r="O168" s="7" t="s">
+        <v>357</v>
+      </c>
       <c r="P168" s="5"/>
       <c r="Q168" s="5"/>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A169" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B169" s="5"/>
       <c r="C169" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="F169" s="18" t="s">
-        <v>20</v>
+        <v>202</v>
+      </c>
+      <c r="F169" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="G169" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="H169" s="2">
-        <v>46219</v>
+        <v>309</v>
+      </c>
+      <c r="H169" s="6">
+        <v>46220</v>
       </c>
       <c r="I169" s="9">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="J169" s="3">
-        <v>0.58333333333333337</v>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J169" s="9">
+        <v>0.375</v>
       </c>
       <c r="K169" s="5" t="s">
         <v>73</v>
       </c>
       <c r="L169" s="6">
-        <v>46182</v>
-      </c>
-      <c r="M169" s="6"/>
+        <v>46189</v>
+      </c>
+      <c r="M169" s="5">
+        <v>1.02</v>
+      </c>
       <c r="N169" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="O169" s="7" t="s">
-        <v>357</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="O169" s="7"/>
       <c r="P169" s="5"/>
       <c r="Q169" s="5"/>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A170" s="5">
         <v>0</v>
       </c>
@@ -7862,7 +7843,7 @@
       <c r="P170" s="5"/>
       <c r="Q170" s="5"/>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A171" s="5">
         <v>0</v>
       </c>
@@ -7895,7 +7876,7 @@
       <c r="P171" s="5"/>
       <c r="Q171" s="5"/>
     </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A172" s="5">
         <v>2</v>
       </c>
@@ -7936,7 +7917,7 @@
       <c r="P172" s="5"/>
       <c r="Q172" s="5"/>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A173" s="5">
         <v>1</v>
       </c>
@@ -7980,31 +7961,6 @@
       </c>
       <c r="P173" s="5"/>
       <c r="Q173" s="5"/>
-    </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A174" s="19" t="s">
-        <v>358</v>
-      </c>
-      <c r="B174" s="19"/>
-      <c r="C174" s="19"/>
-      <c r="D174" s="19"/>
-      <c r="E174" s="19"/>
-      <c r="F174" s="19">
-        <v>172</v>
-      </c>
-      <c r="G174" s="19"/>
-      <c r="H174" s="19"/>
-      <c r="I174" s="19"/>
-      <c r="J174" s="19"/>
-      <c r="K174" s="19">
-        <v>172</v>
-      </c>
-      <c r="L174" s="19"/>
-      <c r="M174" s="19"/>
-      <c r="N174" s="20"/>
-      <c r="O174" s="21"/>
-      <c r="P174" s="19"/>
-      <c r="Q174" s="19"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="K2:Q173">

--- a/archivos/BD_Dashboard.xlsx
+++ b/archivos/BD_Dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mexscitum-my.sharepoint.com/personal/erik_torres_scitum_com_mx/Documents/Documentos/ETP/GitHub/SCITUM-AMX/archivos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="138" documentId="11_F25DC773A252ABDACC1048E8499F6DC65BDE58F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F739FEFF-B474-4B57-AEC1-73EFA45BE77D}"/>
+  <xr:revisionPtr revIDLastSave="146" documentId="11_F25DC773A252ABDACC1048E8499F6DC65BDE58F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20F12896-B8A2-43C2-B0B2-21C08FD34F2B}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inventario SDWAN &amp; FW" sheetId="2" r:id="rId1"/>
@@ -46,7 +46,7 @@
     <author>Erik Alejandro Torres Piña</author>
   </authors>
   <commentList>
-    <comment ref="F41" authorId="0" shapeId="0" xr:uid="{3873DA3F-6CE5-4EB5-8AFF-CCBB8AFCCAC6}">
+    <comment ref="F41" authorId="0" shapeId="0" xr:uid="{29E84AC9-F44A-4AED-A5BE-1306A8BF60E9}">
       <text>
         <r>
           <rPr>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1115" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="357">
   <si>
     <t>TIER</t>
   </si>
@@ -1074,15 +1074,9 @@
     <t>Aeroméxico buscará sesión con proveedor SITA para realizar analisis y entender como esta configurada la conexión del aeropuerto.</t>
   </si>
   <si>
-    <t>El envío del equipo se realizó el 07-jul-2026</t>
-  </si>
-  <si>
     <t>El envío del equipo se realizó el 03-jul-2026</t>
   </si>
   <si>
-    <t>El envío del equipo se realizó el 06-jul-2026</t>
-  </si>
-  <si>
     <t>Hora CDMX</t>
   </si>
   <si>
@@ -1096,9 +1090,6 @@
   </si>
   <si>
     <t>Al hacer el cambio no paso el rol de activo al ION 02. Se analiza el caso con PS PAN. No habia puertos disponibles con DHCP.</t>
-  </si>
-  <si>
-    <t>Tiene enlace SITA</t>
   </si>
   <si>
     <t>Se realizó el rollback de la actividad en Costa Rica (SJO) con el VoBo de Cristian Villa de Aeroméxico.
@@ -1156,13 +1147,19 @@
 Dos contratiempos. 
 La llegada del IDC no fue en tiempo  debido a que no logro encontrar estacionamiento dentro del aeropuerto.
 El IDC desconecto otro cable del Fortinet que no fue indicado en la sesión y esto presento un problema que llevo tiempo identificar.</t>
+  </si>
+  <si>
+    <t>Carta donde se explique al aeropuerto la finalidad de instalar el equipo y su funciones. </t>
+  </si>
+  <si>
+    <t>Enlace de Telmex</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1227,6 +1224,12 @@
       <name val="Century Gothic"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Century Gothic"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1287,7 +1290,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1341,6 +1344,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1797,6 +1806,7 @@
     <col min="5" max="5" width="11.7265625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="24.81640625" customWidth="1"/>
     <col min="7" max="7" width="17.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1825,7 +1835,7 @@
         <v>6</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>7</v>
@@ -1849,7 +1859,7 @@
         <v>310</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
@@ -1872,13 +1882,13 @@
       <c r="G2" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="H2" s="2">
-        <v>46223</v>
-      </c>
-      <c r="I2" s="9">
+      <c r="H2" s="19">
+        <v>46227</v>
+      </c>
+      <c r="I2" s="20">
         <v>0.79166666666666663</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="20">
         <v>0.79166666666666663</v>
       </c>
       <c r="K2" s="5" t="s">
@@ -1889,7 +1899,7 @@
         <v>2.0699999999999998</v>
       </c>
       <c r="N2" s="7" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="O2" s="7"/>
       <c r="P2" s="5"/>
@@ -1915,13 +1925,13 @@
       <c r="G3" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="19">
         <v>46230</v>
       </c>
-      <c r="I3" s="9">
+      <c r="I3" s="20">
         <v>0.54166666666666663</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="20">
         <v>0.625</v>
       </c>
       <c r="K3" s="5" t="s">
@@ -1949,13 +1959,13 @@
         <v>12</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>307</v>
@@ -1966,9 +1976,11 @@
       <c r="K4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="L4" s="5"/>
+      <c r="L4" s="6">
+        <v>46210</v>
+      </c>
       <c r="M4" s="5">
-        <v>2.09</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="N4" s="7"/>
       <c r="O4" s="7"/>
@@ -1981,16 +1993,16 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>50</v>
+        <v>324</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>259</v>
+        <v>221</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>120</v>
+        <v>62</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>309</v>
@@ -2003,32 +2015,34 @@
       </c>
       <c r="L5" s="5"/>
       <c r="M5" s="5">
-        <v>4.03</v>
-      </c>
-      <c r="N5" s="7"/>
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>355</v>
+      </c>
       <c r="O5" s="7"/>
       <c r="P5" s="5"/>
       <c r="Q5" s="5"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>264</v>
+        <v>215</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>125</v>
+        <v>52</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
@@ -2038,7 +2052,7 @@
       </c>
       <c r="L6" s="5"/>
       <c r="M6" s="5">
-        <v>4.05</v>
+        <v>2.09</v>
       </c>
       <c r="N6" s="7"/>
       <c r="O6" s="7"/>
@@ -2069,7 +2083,7 @@
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
       <c r="K7" s="5" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="L7" s="6">
         <v>46209</v>
@@ -2078,7 +2092,7 @@
         <v>4.0199999999999996</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>334</v>
+        <v>356</v>
       </c>
       <c r="O7" s="7"/>
       <c r="P7" s="5"/>
@@ -2096,10 +2110,10 @@
         <v>50</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>282</v>
+        <v>259</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>154</v>
+        <v>120</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>309</v>
@@ -2108,16 +2122,14 @@
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
       <c r="K8" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="L8" s="17">
-        <v>46209</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="L8" s="5"/>
       <c r="M8" s="5">
-        <v>4.04</v>
+        <v>4.03</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>334</v>
+        <v>356</v>
       </c>
       <c r="O8" s="7"/>
       <c r="P8" s="5"/>
@@ -2129,16 +2141,16 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>204</v>
+        <v>282</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>31</v>
+        <v>154</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>309</v>
@@ -2147,16 +2159,16 @@
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
       <c r="K9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L9" s="6">
-        <v>46189</v>
+        <v>36</v>
+      </c>
+      <c r="L9" s="17">
+        <v>46209</v>
       </c>
       <c r="M9" s="5">
-        <v>1.04</v>
+        <v>4.04</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>312</v>
+        <v>356</v>
       </c>
       <c r="O9" s="7"/>
       <c r="P9" s="5"/>
@@ -2168,16 +2180,16 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>205</v>
+        <v>264</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>33</v>
+        <v>125</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>309</v>
@@ -2186,16 +2198,14 @@
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
       <c r="K10" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L10" s="6">
-        <v>46189</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="L10" s="5"/>
       <c r="M10" s="5">
-        <v>1.05</v>
+        <v>4.05</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>312</v>
+        <v>356</v>
       </c>
       <c r="O10" s="7"/>
       <c r="P10" s="5"/>
@@ -2203,23 +2213,23 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
@@ -2228,13 +2238,13 @@
         <v>21</v>
       </c>
       <c r="L11" s="6">
-        <v>46210</v>
+        <v>46189</v>
       </c>
       <c r="M11" s="5">
-        <v>2.0099999999999998</v>
+        <v>1.04</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>332</v>
+        <v>312</v>
       </c>
       <c r="O11" s="7"/>
       <c r="P11" s="5"/>
@@ -2249,13 +2259,13 @@
         <v>12</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>309</v>
@@ -2267,13 +2277,13 @@
         <v>21</v>
       </c>
       <c r="L12" s="6">
-        <v>46206</v>
-      </c>
-      <c r="M12" s="14">
-        <v>2.1</v>
+        <v>46189</v>
+      </c>
+      <c r="M12" s="5">
+        <v>1.05</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>333</v>
+        <v>312</v>
       </c>
       <c r="O12" s="7"/>
       <c r="P12" s="5"/>
@@ -2288,13 +2298,13 @@
         <v>12</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>324</v>
+        <v>66</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>309</v>
@@ -2303,13 +2313,17 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
       <c r="K13" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5">
-        <v>2.0299999999999998</v>
-      </c>
-      <c r="N13" s="7"/>
+        <v>21</v>
+      </c>
+      <c r="L13" s="6">
+        <v>46206</v>
+      </c>
+      <c r="M13" s="14">
+        <v>2.1</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>332</v>
+      </c>
       <c r="O13" s="7"/>
       <c r="P13" s="5"/>
       <c r="Q13" s="5"/>
@@ -2616,7 +2630,7 @@
         <v>50</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>72</v>
@@ -2820,7 +2834,7 @@
       <c r="L27" s="5"/>
       <c r="M27" s="5"/>
       <c r="N27" s="7" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="O27" s="7"/>
       <c r="P27" s="5"/>
@@ -2859,7 +2873,7 @@
       <c r="L28" s="5"/>
       <c r="M28" s="5"/>
       <c r="N28" s="7" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="O28" s="7"/>
       <c r="P28" s="5"/>
@@ -2904,7 +2918,7 @@
         <v>1.03</v>
       </c>
       <c r="N29" s="7" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="O29" s="7"/>
       <c r="P29" s="5"/>
@@ -3758,10 +3772,10 @@
         <v>50</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="G54" s="5" t="s">
         <v>307</v>
@@ -3795,10 +3809,10 @@
         <v>50</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="G55" s="5" t="s">
         <v>307</v>
@@ -4495,10 +4509,10 @@
         <v>50</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="G75" s="5" t="s">
         <v>307</v>
@@ -4602,10 +4616,10 @@
         <v>50</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="G78" s="5" t="s">
         <v>307</v>
@@ -4775,10 +4789,10 @@
         <v>50</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="G83" s="5" t="s">
         <v>307</v>
@@ -6363,10 +6377,10 @@
         <v>50</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="G131" s="5" t="s">
         <v>307</v>
@@ -7384,10 +7398,10 @@
       <c r="L159" s="5"/>
       <c r="M159" s="5"/>
       <c r="N159" s="16" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="O159" s="16" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="P159" s="5"/>
       <c r="Q159" s="5"/>
@@ -7585,7 +7599,7 @@
       <c r="L164" s="5"/>
       <c r="M164" s="5"/>
       <c r="N164" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="O164" s="7" t="s">
         <v>330</v>
@@ -7636,42 +7650,42 @@
     </row>
     <row r="166" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A166" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B166" s="5"/>
       <c r="C166" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E166" s="5" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="G166" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="H166" s="2">
+        <v>309</v>
+      </c>
+      <c r="H166" s="12">
         <v>46218</v>
       </c>
       <c r="I166" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J166" s="3">
-        <v>0.5</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="J166" s="13">
+        <v>0.625</v>
       </c>
       <c r="K166" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="L166" s="6">
-        <v>46182</v>
-      </c>
-      <c r="M166" s="6"/>
+      <c r="L166" s="5"/>
+      <c r="M166" s="5">
+        <v>2.02</v>
+      </c>
       <c r="N166" s="7" t="s">
-        <v>355</v>
+        <v>315</v>
       </c>
       <c r="O166" s="7"/>
       <c r="P166" s="5"/>
@@ -7679,42 +7693,42 @@
     </row>
     <row r="167" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A167" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B167" s="5"/>
       <c r="C167" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="G167" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="H167" s="12">
+        <v>307</v>
+      </c>
+      <c r="H167" s="2">
         <v>46218</v>
       </c>
       <c r="I167" s="9">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="J167" s="13">
-        <v>0.625</v>
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="J167" s="3">
+        <v>0.5</v>
       </c>
       <c r="K167" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="L167" s="5"/>
-      <c r="M167" s="5">
-        <v>2.02</v>
-      </c>
+      <c r="L167" s="6">
+        <v>46182</v>
+      </c>
+      <c r="M167" s="6"/>
       <c r="N167" s="7" t="s">
-        <v>315</v>
+        <v>352</v>
       </c>
       <c r="O167" s="7"/>
       <c r="P167" s="5"/>
@@ -7760,7 +7774,7 @@
         <v>317</v>
       </c>
       <c r="O168" s="7" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="P168" s="5"/>
       <c r="Q168" s="5"/>
@@ -7954,10 +7968,10 @@
         <v>2.08</v>
       </c>
       <c r="N173" s="7" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="O173" s="7" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="P173" s="5"/>
       <c r="Q173" s="5"/>

--- a/archivos/BD_Dashboard.xlsx
+++ b/archivos/BD_Dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mexscitum-my.sharepoint.com/personal/erik_torres_scitum_com_mx/Documents/Documentos/ETP/GitHub/SCITUM-AMX/archivos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="146" documentId="11_F25DC773A252ABDACC1048E8499F6DC65BDE58F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20F12896-B8A2-43C2-B0B2-21C08FD34F2B}"/>
+  <xr:revisionPtr revIDLastSave="156" documentId="11_F25DC773A252ABDACC1048E8499F6DC65BDE58F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18B87441-1A50-46C8-AA88-5CEE5C879389}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inventario SDWAN &amp; FW" sheetId="2" r:id="rId1"/>
@@ -46,7 +46,7 @@
     <author>Erik Alejandro Torres Piña</author>
   </authors>
   <commentList>
-    <comment ref="F41" authorId="0" shapeId="0" xr:uid="{29E84AC9-F44A-4AED-A5BE-1306A8BF60E9}">
+    <comment ref="F43" authorId="0" shapeId="0" xr:uid="{EDFF5F0F-58FA-495B-8AFD-5DF21FB916FE}">
       <text>
         <r>
           <rPr>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="360">
   <si>
     <t>TIER</t>
   </si>
@@ -1014,9 +1014,6 @@
     <t>SI</t>
   </si>
   <si>
-    <t>El envío del equipo se realizó el 16-jun-2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hace falta la información del segmento de interconexión con el Firewall </t>
   </si>
   <si>
@@ -1029,9 +1026,6 @@
     <t>Se requiere llenar formulario para acceso a IDC. La foto parece ser la misma que la de LAS, por favor confirmar</t>
   </si>
   <si>
-    <t xml:space="preserve">No se observa disponibilidad de contactos electricos. Rack elevado, no se observa a que altura. </t>
-  </si>
-  <si>
     <t>Monterrey Terminal A (MTY)</t>
   </si>
   <si>
@@ -1053,18 +1047,12 @@
     <t>Nicaragua</t>
   </si>
   <si>
-    <t>Para el HA esta directo ION-ION, posterior Palo Alto hizo una recomendación (por best practices) de conectar a un switch para habilitar el HA.</t>
-  </si>
-  <si>
     <t>Aeroméxico no proporcionó los cables requeridos para la ventana de implementación. El cliente programará una visita posterior con recursos propios para realizar la conexión del segundo equipo, y SCITUM brindará soporte de forma remota.</t>
   </si>
   <si>
     <t>Fallida</t>
   </si>
   <si>
-    <t>Aeroméxico autorizó la instalación temporal de los equipos sobre infraestructura existente de otro proveedor para mantener la ventana de implementación del sitio LAS. Durante la sesión se expusieron los riesgos asociados a esta alternativa y Aeroméxico confirmó la aceptación de dichos riesgos, asumiendo la responsabilidad ante cualquier incidente derivado del movimiento o manipulación de los equipos existentes durante o posterior a la ventana. No se tiene switch, Aeromexico reporta que desconocía esta situación, se conecta un solo equipo ION y no se habilita HA.</t>
-  </si>
-  <si>
     <t>AMX solicita sacarlo de la planeación hasta nuevo aviso</t>
   </si>
   <si>
@@ -1074,9 +1062,6 @@
     <t>Aeroméxico buscará sesión con proveedor SITA para realizar analisis y entender como esta configurada la conexión del aeropuerto.</t>
   </si>
   <si>
-    <t>El envío del equipo se realizó el 03-jul-2026</t>
-  </si>
-  <si>
     <t>Hora CDMX</t>
   </si>
   <si>
@@ -1090,76 +1075,99 @@
   </si>
   <si>
     <t>Al hacer el cambio no paso el rol de activo al ION 02. Se analiza el caso con PS PAN. No habia puertos disponibles con DHCP.</t>
+  </si>
+  <si>
+    <t>Orden Enlace Telmex</t>
+  </si>
+  <si>
+    <t>AICM T1 (AICM_T1)</t>
+  </si>
+  <si>
+    <t>Ciudad Juárez (CJS_CARGO)</t>
+  </si>
+  <si>
+    <t>Mazatlán (MZT_CARGO)</t>
+  </si>
+  <si>
+    <t>Chihuahua (CUU_CARGO)</t>
+  </si>
+  <si>
+    <t>Oaxaca (OAX_CARGO)</t>
+  </si>
+  <si>
+    <t>Ciudad del Carmen (CME_CARGO)</t>
+  </si>
+  <si>
+    <t>AICM_T1</t>
+  </si>
+  <si>
+    <t>CJS_CARGO</t>
+  </si>
+  <si>
+    <t>MZT_CARGO</t>
+  </si>
+  <si>
+    <t>CUU_CARGO</t>
+  </si>
+  <si>
+    <t>OAX_CARGO</t>
+  </si>
+  <si>
+    <t>CME_CARGO</t>
+  </si>
+  <si>
+    <t>No se requieren permisos especiales solo compartan nombre del IDC. Switch administrable por el aeropuerto y el enlace es del aeropuerto. No se observa si existe espacio para contacto electrico. No hay espacio para colocar equipo, se colocaría encima del switch</t>
+  </si>
+  <si>
+    <t>Hasta nuevo aviso de AMX</t>
+  </si>
+  <si>
+    <t>Carta donde se explique al aeropuerto la finalidad de instalar el equipo y su funciones. </t>
+  </si>
+  <si>
+    <t>Enlace de Telmex</t>
+  </si>
+  <si>
+    <t>Se solicito el retorno de los equipos</t>
+  </si>
+  <si>
+    <t>Guadalajara (GDL_CARGO)</t>
+  </si>
+  <si>
+    <t>Para el HA esta directo ION-ION, posterior Palo Alto hizo una recomendación (por best practices) de conectar a un switch para habilitar el HA. SCITUM espera ventana para asignar IDC y realizar la actividad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMX - No quedo el HA por que no había switch disponible. AMX programará una visita posterior con recursos propios para realizar la conexión del segundo equipo, y SCITUM brindará soporte de forma remota. </t>
+  </si>
+  <si>
+    <t>AMX - No se encontraban disponibles los cables requeridos para la ventana de implementación. AMX programará una visita posterior con recursos propios para realizar la conexión del segundo equipo, y SCITUM brindará soporte de forma remota.</t>
+  </si>
+  <si>
+    <t>No se observa disponibilidad de contactos electricos. Rack elevado, no se observa a que altura. Dos contratiempos. 
+La llegada del IDC no fue en tiempo  debido a que no logro encontrar estacionamiento dentro del aeropuerto.
+El IDC desconecto otro cable del Fortinet que no fue indicado en la sesión y esto presento un problema que llevo tiempo identificar.</t>
+  </si>
+  <si>
+    <t>Quedo integrado SDWAN sin embargo debido a que inicio la operación no fue posible ejecutar las pruebas de HA. En espera de que AMX indique fecha para realizar las pruebas de HA.</t>
+  </si>
+  <si>
+    <t>Aeroméxico autorizó la instalación temporal de los equipos sobre infraestructura existente de otro proveedor para mantener la ventana de implementación. Durante la sesión se expusieron los riesgos asociados a esta alternativa y Aeroméxico confirmó la aceptación de dichos riesgos, asumiendo la responsabilidad ante cualquier incidente derivado del movimiento o manipulación de los equipos existentes durante o posterior a la ventana. No se tiene switch, Aeromexico reporta que desconocía esta situación, se conecta un solo equipo ION y no se habilita HA. Se ejecuto rollback por temas en la LAN, Aeroméxico realizara el análisis correspondiente de esta red LAN y buscara asistir a sitio con recursos propios, SCITUM apoyará de forma remota.</t>
   </si>
   <si>
     <t>Se realizó el rollback de la actividad en Costa Rica (SJO) con el VoBo de Cristian Villa de Aeroméxico.
 La integración de la red de SDWAN con el dispositivo ION fue correcta, las VPN hacia el DC CECAM y DC Equinix levantaron correctamente; sin embargo, los equipos de escritorio (desktops) perdieron la conexión en la red LAN, incluso sin poder alcanzar su gateway.
 Dicho gateway es un dispositivo router denominado SITA que se encuentra conectado por debajo del firewall Fortinet como parte de la LAN; asimismo, el firewall recibe el tráfico y lo envía al ION para establecer la conexión SD-WAN sin embargo no se observo trafico que envie Fortinet al ION durante la actividad.
-Aeroméxico realizara el análisis correspondiente de esta red LAN.</t>
-  </si>
-  <si>
-    <t>Orden Enlace Telmex</t>
-  </si>
-  <si>
-    <t>AICM T1 (AICM_T1)</t>
-  </si>
-  <si>
-    <t>Ciudad Juárez (CJS_CARGO)</t>
-  </si>
-  <si>
-    <t>Mazatlán (MZT_CARGO)</t>
-  </si>
-  <si>
-    <t>Chihuahua (CUU_CARGO)</t>
-  </si>
-  <si>
-    <t>Oaxaca (OAX_CARGO)</t>
-  </si>
-  <si>
-    <t>Ciudad del Carmen (CME_CARGO)</t>
-  </si>
-  <si>
-    <t>AICM_T1</t>
-  </si>
-  <si>
-    <t>CJS_CARGO</t>
-  </si>
-  <si>
-    <t>MZT_CARGO</t>
-  </si>
-  <si>
-    <t>CUU_CARGO</t>
-  </si>
-  <si>
-    <t>OAX_CARGO</t>
-  </si>
-  <si>
-    <t>CME_CARGO</t>
-  </si>
-  <si>
-    <t>No se requieren permisos especiales solo compartan nombre del IDC. Switch administrable por el aeropuerto y el enlace es del aeropuerto. No se observa si existe espacio para contacto electrico. No hay espacio para colocar equipo, se colocaría encima del switch</t>
-  </si>
-  <si>
-    <t>Hasta nuevo aviso de AMX</t>
-  </si>
-  <si>
-    <t>Quedo integrado SDWAN sin embargo debido a que inicio la operación no fue posible ejecutar las pruebas de HA.
-Dos contratiempos. 
-La llegada del IDC no fue en tiempo  debido a que no logro encontrar estacionamiento dentro del aeropuerto.
-El IDC desconecto otro cable del Fortinet que no fue indicado en la sesión y esto presento un problema que llevo tiempo identificar.</t>
-  </si>
-  <si>
-    <t>Carta donde se explique al aeropuerto la finalidad de instalar el equipo y su funciones. </t>
-  </si>
-  <si>
-    <t>Enlace de Telmex</t>
+Aeroméxico realizara el análisis correspondiente de esta red LAN y buscara asistir a sitio con recursos propios, SCITUM apoyará de forma remota.</t>
+  </si>
+  <si>
+    <t>GDL_CARGO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1224,12 +1232,6 @@
       <name val="Century Gothic"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Century Gothic"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1290,7 +1292,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1344,12 +1346,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1806,7 +1802,6 @@
     <col min="5" max="5" width="11.7265625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="24.81640625" customWidth="1"/>
     <col min="7" max="7" width="17.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1835,7 +1830,7 @@
         <v>6</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>7</v>
@@ -1853,13 +1848,13 @@
         <v>11</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="P1" s="4" t="s">
         <v>310</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
@@ -1882,14 +1877,14 @@
       <c r="G2" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="H2" s="19">
-        <v>46227</v>
-      </c>
-      <c r="I2" s="20">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="J2" s="20">
-        <v>0.79166666666666663</v>
+      <c r="H2" s="2">
+        <v>46230</v>
+      </c>
+      <c r="I2" s="9">
+        <v>0.75</v>
+      </c>
+      <c r="J2" s="3">
+        <v>0.75</v>
       </c>
       <c r="K2" s="5" t="s">
         <v>308</v>
@@ -1899,7 +1894,7 @@
         <v>2.0699999999999998</v>
       </c>
       <c r="N2" s="7" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="O2" s="7"/>
       <c r="P2" s="5"/>
@@ -1925,13 +1920,13 @@
       <c r="G3" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="H3" s="19">
+      <c r="H3" s="2">
         <v>46230</v>
       </c>
-      <c r="I3" s="20">
+      <c r="I3" s="9">
         <v>0.54166666666666663</v>
       </c>
-      <c r="J3" s="20">
+      <c r="J3" s="3">
         <v>0.625</v>
       </c>
       <c r="K3" s="5" t="s">
@@ -1944,7 +1939,7 @@
         <v>1.01</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O3" s="7"/>
       <c r="P3" s="5"/>
@@ -1996,7 +1991,7 @@
         <v>12</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>221</v>
@@ -2018,7 +2013,7 @@
         <v>2.0299999999999998</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="O5" s="7"/>
       <c r="P5" s="5"/>
@@ -2065,16 +2060,16 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>257</v>
+        <v>204</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>117</v>
+        <v>31</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>309</v>
@@ -2083,16 +2078,16 @@
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
       <c r="K7" s="5" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="L7" s="6">
-        <v>46209</v>
+        <v>46189</v>
       </c>
       <c r="M7" s="5">
-        <v>4.0199999999999996</v>
+        <v>1.04</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="O7" s="7"/>
       <c r="P7" s="5"/>
@@ -2104,16 +2099,16 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>259</v>
+        <v>205</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>120</v>
+        <v>33</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>309</v>
@@ -2122,14 +2117,16 @@
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
       <c r="K8" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="L8" s="5"/>
+        <v>21</v>
+      </c>
+      <c r="L8" s="6">
+        <v>46189</v>
+      </c>
       <c r="M8" s="5">
-        <v>4.03</v>
+        <v>1.05</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="O8" s="7"/>
       <c r="P8" s="5"/>
@@ -2141,16 +2138,16 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>282</v>
+        <v>224</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>154</v>
+        <v>67</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>309</v>
@@ -2159,16 +2156,16 @@
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
       <c r="K9" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="L9" s="17">
-        <v>46209</v>
-      </c>
-      <c r="M9" s="5">
-        <v>4.04</v>
+        <v>21</v>
+      </c>
+      <c r="L9" s="6">
+        <v>46206</v>
+      </c>
+      <c r="M9" s="14">
+        <v>2.1</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="O9" s="7"/>
       <c r="P9" s="5"/>
@@ -2180,16 +2177,16 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>264</v>
+        <v>223</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>309</v>
@@ -2198,93 +2195,83 @@
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
       <c r="K10" s="5" t="s">
-        <v>36</v>
+        <v>299</v>
       </c>
       <c r="L10" s="5"/>
       <c r="M10" s="5">
-        <v>4.05</v>
-      </c>
-      <c r="N10" s="7" t="s">
-        <v>356</v>
-      </c>
+        <v>2.04</v>
+      </c>
+      <c r="N10" s="7"/>
       <c r="O10" s="7"/>
       <c r="P10" s="5"/>
       <c r="Q10" s="5"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
       <c r="J11" s="5"/>
       <c r="K11" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L11" s="6">
-        <v>46189</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="L11" s="5"/>
       <c r="M11" s="5">
-        <v>1.04</v>
-      </c>
-      <c r="N11" s="7" t="s">
-        <v>312</v>
-      </c>
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="N11" s="7"/>
       <c r="O11" s="7"/>
       <c r="P11" s="5"/>
       <c r="Q11" s="5"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>32</v>
+        <v>135</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>205</v>
+        <v>270</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>33</v>
+        <v>136</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
       <c r="K12" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L12" s="6">
-        <v>46189</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="L12" s="5"/>
       <c r="M12" s="5">
-        <v>1.05</v>
-      </c>
-      <c r="N12" s="7" t="s">
-        <v>312</v>
-      </c>
+        <v>3.01</v>
+      </c>
+      <c r="N12" s="7"/>
       <c r="O12" s="7"/>
       <c r="P12" s="5"/>
       <c r="Q12" s="5"/>
@@ -2298,13 +2285,13 @@
         <v>12</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>66</v>
+        <v>148</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>67</v>
+        <v>149</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>309</v>
@@ -2313,17 +2300,13 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
       <c r="K13" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L13" s="6">
-        <v>46206</v>
-      </c>
-      <c r="M13" s="14">
-        <v>2.1</v>
-      </c>
-      <c r="N13" s="7" t="s">
-        <v>332</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5">
+        <v>3.02</v>
+      </c>
+      <c r="N13" s="7"/>
       <c r="O13" s="7"/>
       <c r="P13" s="5"/>
       <c r="Q13" s="5"/>
@@ -2337,18 +2320,18 @@
         <v>12</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="H14" s="5"/>
+      <c r="H14" s="8"/>
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
       <c r="K14" s="5" t="s">
@@ -2356,9 +2339,11 @@
       </c>
       <c r="L14" s="5"/>
       <c r="M14" s="5">
-        <v>2.04</v>
-      </c>
-      <c r="N14" s="7"/>
+        <v>3.03</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="O14" s="7"/>
       <c r="P14" s="5"/>
       <c r="Q14" s="5"/>
@@ -2372,18 +2357,18 @@
         <v>12</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="H15" s="5"/>
+      <c r="H15" s="8"/>
       <c r="I15" s="5"/>
       <c r="J15" s="5"/>
       <c r="K15" s="5" t="s">
@@ -2391,34 +2376,36 @@
       </c>
       <c r="L15" s="5"/>
       <c r="M15" s="5">
-        <v>2.0499999999999998</v>
-      </c>
-      <c r="N15" s="7"/>
+        <v>3.04</v>
+      </c>
+      <c r="N15" s="7" t="s">
+        <v>303</v>
+      </c>
       <c r="O15" s="7"/>
       <c r="P15" s="5"/>
       <c r="Q15" s="5"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>135</v>
+        <v>13</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>270</v>
+        <v>209</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>136</v>
+        <v>39</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="H16" s="5"/>
+        <v>309</v>
+      </c>
+      <c r="H16" s="8"/>
       <c r="I16" s="5"/>
       <c r="J16" s="5"/>
       <c r="K16" s="5" t="s">
@@ -2426,32 +2413,34 @@
       </c>
       <c r="L16" s="5"/>
       <c r="M16" s="5">
-        <v>3.01</v>
-      </c>
-      <c r="N16" s="7"/>
+        <v>4.01</v>
+      </c>
+      <c r="N16" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="O16" s="7"/>
       <c r="P16" s="5"/>
       <c r="Q16" s="5"/>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5" t="s">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>148</v>
+        <v>50</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>278</v>
+        <v>76</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>149</v>
+        <v>76</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
@@ -2461,34 +2450,38 @@
       </c>
       <c r="L17" s="5"/>
       <c r="M17" s="5">
-        <v>3.02</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="N17" s="7"/>
       <c r="O17" s="7"/>
-      <c r="P17" s="5"/>
-      <c r="Q17" s="5"/>
+      <c r="P17" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q17" s="5">
+        <v>1.01</v>
+      </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5" t="s">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>208</v>
+        <v>330</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="H18" s="8"/>
+        <v>307</v>
+      </c>
+      <c r="H18" s="5"/>
       <c r="I18" s="5"/>
       <c r="J18" s="5"/>
       <c r="K18" s="5" t="s">
@@ -2496,36 +2489,38 @@
       </c>
       <c r="L18" s="5"/>
       <c r="M18" s="5">
-        <v>3.03</v>
-      </c>
-      <c r="N18" s="7" t="s">
-        <v>38</v>
-      </c>
+        <v>5.2</v>
+      </c>
+      <c r="N18" s="7"/>
       <c r="O18" s="7"/>
-      <c r="P18" s="5"/>
-      <c r="Q18" s="5"/>
+      <c r="P18" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q18" s="5">
+        <v>1.02</v>
+      </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>43</v>
+        <v>127</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="H19" s="8"/>
+        <v>309</v>
+      </c>
+      <c r="H19" s="5"/>
       <c r="I19" s="5"/>
       <c r="J19" s="5"/>
       <c r="K19" s="5" t="s">
@@ -2533,11 +2528,9 @@
       </c>
       <c r="L19" s="5"/>
       <c r="M19" s="5">
-        <v>3.04</v>
-      </c>
-      <c r="N19" s="7" t="s">
-        <v>303</v>
-      </c>
+        <v>5.3</v>
+      </c>
+      <c r="N19" s="7"/>
       <c r="O19" s="7"/>
       <c r="P19" s="5"/>
       <c r="Q19" s="5"/>
@@ -2548,21 +2541,21 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>209</v>
+        <v>269</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>39</v>
+        <v>130</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="H20" s="8"/>
+      <c r="H20" s="5"/>
       <c r="I20" s="5"/>
       <c r="J20" s="5"/>
       <c r="K20" s="5" t="s">
@@ -2570,31 +2563,29 @@
       </c>
       <c r="L20" s="5"/>
       <c r="M20" s="5">
-        <v>4.01</v>
-      </c>
-      <c r="N20" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>5.4</v>
+      </c>
+      <c r="N20" s="16"/>
       <c r="O20" s="7"/>
       <c r="P20" s="5"/>
       <c r="Q20" s="5"/>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>307</v>
@@ -2607,33 +2598,29 @@
       </c>
       <c r="L21" s="5"/>
       <c r="M21" s="5">
-        <v>5.0999999999999996</v>
+        <v>5.5</v>
       </c>
       <c r="N21" s="7"/>
       <c r="O21" s="7"/>
-      <c r="P21" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q21" s="5">
-        <v>1.01</v>
-      </c>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="5"/>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5" t="s">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>335</v>
+        <v>213</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>307</v>
@@ -2646,154 +2633,174 @@
       </c>
       <c r="L22" s="5"/>
       <c r="M22" s="5">
-        <v>5.2</v>
-      </c>
-      <c r="N22" s="7"/>
+        <v>5.6</v>
+      </c>
+      <c r="N22" s="7" t="s">
+        <v>48</v>
+      </c>
       <c r="O22" s="7"/>
-      <c r="P22" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q22" s="5">
-        <v>1.02</v>
-      </c>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="5"/>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>266</v>
+        <v>196</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>127</v>
+        <v>18</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
+        <v>307</v>
+      </c>
+      <c r="H23" s="12">
+        <v>46225</v>
+      </c>
+      <c r="I23" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J23" s="13">
+        <v>0.41666666666666669</v>
+      </c>
       <c r="K23" s="5" t="s">
-        <v>299</v>
+        <v>36</v>
       </c>
       <c r="L23" s="5"/>
-      <c r="M23" s="5">
-        <v>5.3</v>
-      </c>
-      <c r="N23" s="7"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="7" t="s">
+        <v>347</v>
+      </c>
       <c r="O23" s="7"/>
       <c r="P23" s="5"/>
       <c r="Q23" s="5"/>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>269</v>
+        <v>207</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>130</v>
+        <v>35</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="H24" s="5"/>
+        <v>307</v>
+      </c>
+      <c r="H24" s="2">
+        <v>46226</v>
+      </c>
       <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
+      <c r="J24" s="3">
+        <v>0.47916666666666669</v>
+      </c>
       <c r="K24" s="5" t="s">
-        <v>299</v>
+        <v>36</v>
       </c>
       <c r="L24" s="5"/>
-      <c r="M24" s="5">
-        <v>5.4</v>
-      </c>
-      <c r="N24" s="16"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="7" t="s">
+        <v>347</v>
+      </c>
       <c r="O24" s="7"/>
       <c r="P24" s="5"/>
       <c r="Q24" s="5"/>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5" t="s">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>81</v>
+        <v>203</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
+      <c r="H25" s="2">
+        <v>46230</v>
+      </c>
+      <c r="I25" s="9">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="J25" s="3">
+        <v>0.6875</v>
+      </c>
       <c r="K25" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="L25" s="5"/>
+        <v>36</v>
+      </c>
+      <c r="L25" s="6">
+        <v>46189</v>
+      </c>
       <c r="M25" s="5">
-        <v>5.5</v>
-      </c>
-      <c r="N25" s="7"/>
+        <v>1.03</v>
+      </c>
+      <c r="N25" s="7" t="s">
+        <v>347</v>
+      </c>
       <c r="O25" s="7"/>
       <c r="P25" s="5"/>
       <c r="Q25" s="5"/>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>213</v>
+        <v>257</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>46</v>
+        <v>117</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
       <c r="J26" s="5"/>
       <c r="K26" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="L26" s="5"/>
+        <v>36</v>
+      </c>
+      <c r="L26" s="6">
+        <v>46209</v>
+      </c>
       <c r="M26" s="5">
-        <v>5.6</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="N26" s="7" t="s">
-        <v>48</v>
+        <v>349</v>
       </c>
       <c r="O26" s="7"/>
       <c r="P26" s="5"/>
@@ -2801,40 +2808,36 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>196</v>
+        <v>259</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>18</v>
+        <v>120</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="H27" s="12">
-        <v>46225</v>
-      </c>
-      <c r="I27" s="9">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="J27" s="13">
-        <v>0.41666666666666669</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
       <c r="K27" s="5" t="s">
         <v>36</v>
       </c>
       <c r="L27" s="5"/>
-      <c r="M27" s="5"/>
+      <c r="M27" s="5">
+        <v>4.03</v>
+      </c>
       <c r="N27" s="7" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="O27" s="7"/>
       <c r="P27" s="5"/>
@@ -2842,38 +2845,38 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>207</v>
+        <v>282</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>35</v>
+        <v>154</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="H28" s="2">
-        <v>46226</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="H28" s="5"/>
       <c r="I28" s="5"/>
-      <c r="J28" s="3">
-        <v>0.47916666666666669</v>
-      </c>
+      <c r="J28" s="5"/>
       <c r="K28" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="L28" s="5"/>
-      <c r="M28" s="5"/>
+      <c r="L28" s="17">
+        <v>46209</v>
+      </c>
+      <c r="M28" s="5">
+        <v>4.04</v>
+      </c>
       <c r="N28" s="7" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="O28" s="7"/>
       <c r="P28" s="5"/>
@@ -2881,44 +2884,36 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5" t="s">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>203</v>
+        <v>264</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>29</v>
+        <v>125</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="H29" s="2">
-        <v>46230</v>
-      </c>
-      <c r="I29" s="9">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0.6875</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
       <c r="K29" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="L29" s="6">
-        <v>46189</v>
-      </c>
+      <c r="L29" s="5"/>
       <c r="M29" s="5">
-        <v>1.03</v>
+        <v>4.05</v>
       </c>
       <c r="N29" s="7" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="O29" s="7"/>
       <c r="P29" s="5"/>
@@ -2955,7 +2950,7 @@
         <v>2.06</v>
       </c>
       <c r="N30" s="7" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="O30" s="7"/>
       <c r="P30" s="5"/>
@@ -2992,7 +2987,7 @@
       </c>
       <c r="M31" s="6"/>
       <c r="N31" s="7" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="O31" s="7"/>
       <c r="P31" s="5"/>
@@ -3103,11 +3098,11 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>50</v>
@@ -3116,7 +3111,7 @@
         <v>225</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="G35" s="5" t="s">
         <v>307</v>
@@ -3125,22 +3120,18 @@
       <c r="I35" s="5"/>
       <c r="J35" s="5"/>
       <c r="K35" s="5" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="L35" s="5"/>
       <c r="M35" s="5"/>
       <c r="N35" s="7"/>
       <c r="O35" s="7"/>
-      <c r="P35" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q35" s="5">
-        <v>1.03</v>
-      </c>
+      <c r="P35" s="5"/>
+      <c r="Q35" s="5"/>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5" t="s">
@@ -3150,10 +3141,10 @@
         <v>50</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="G36" s="5" t="s">
         <v>307</v>
@@ -3162,7 +3153,7 @@
       <c r="I36" s="5"/>
       <c r="J36" s="5"/>
       <c r="K36" s="5" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="L36" s="5"/>
       <c r="M36" s="5"/>
@@ -3174,7 +3165,7 @@
         <v>311</v>
       </c>
       <c r="Q36" s="5">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.35">
@@ -3192,7 +3183,7 @@
         <v>225</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G37" s="5" t="s">
         <v>307</v>
@@ -3201,19 +3192,17 @@
       <c r="I37" s="5"/>
       <c r="J37" s="5"/>
       <c r="K37" s="5" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="L37" s="5"/>
       <c r="M37" s="5"/>
-      <c r="N37" s="7" t="s">
-        <v>314</v>
-      </c>
+      <c r="N37" s="7"/>
       <c r="O37" s="7"/>
       <c r="P37" s="5" t="s">
         <v>311</v>
       </c>
       <c r="Q37" s="5">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.35">
@@ -3231,7 +3220,7 @@
         <v>225</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>307</v>
@@ -3246,25 +3235,29 @@
       <c r="M38" s="5"/>
       <c r="N38" s="7"/>
       <c r="O38" s="7"/>
-      <c r="P38" s="5"/>
-      <c r="Q38" s="5"/>
+      <c r="P38" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q38" s="5">
+        <v>1.03</v>
+      </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="G39" s="5" t="s">
         <v>307</v>
@@ -3277,10 +3270,16 @@
       </c>
       <c r="L39" s="5"/>
       <c r="M39" s="5"/>
-      <c r="N39" s="7"/>
+      <c r="N39" s="7" t="s">
+        <v>312</v>
+      </c>
       <c r="O39" s="7"/>
-      <c r="P39" s="5"/>
-      <c r="Q39" s="5"/>
+      <c r="P39" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q39" s="5">
+        <v>1.04</v>
+      </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40" s="5">
@@ -3297,7 +3296,7 @@
         <v>225</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="G40" s="5" t="s">
         <v>307</v>
@@ -3312,45 +3311,41 @@
       <c r="M40" s="5"/>
       <c r="N40" s="7"/>
       <c r="O40" s="7"/>
-      <c r="P40" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q40" s="5">
-        <v>1.06</v>
-      </c>
+      <c r="P40" s="5"/>
+      <c r="Q40" s="5"/>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A41" s="10">
+      <c r="A41" s="5">
         <v>0</v>
       </c>
       <c r="B41" s="5"/>
-      <c r="C41" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="D41" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="E41" s="10" t="s">
+      <c r="C41" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E41" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="F41" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="G41" s="10" t="s">
-        <v>307</v>
-      </c>
-      <c r="H41" s="10"/>
-      <c r="I41" s="10"/>
-      <c r="J41" s="10"/>
+      <c r="F41" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="5"/>
       <c r="K41" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="L41" s="10"/>
-      <c r="M41" s="10"/>
-      <c r="N41" s="11"/>
-      <c r="O41" s="11"/>
-      <c r="P41" s="10"/>
-      <c r="Q41" s="10"/>
+      <c r="L41" s="5"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="7"/>
+      <c r="O41" s="7"/>
+      <c r="P41" s="5"/>
+      <c r="Q41" s="5"/>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A42" s="5">
@@ -3367,7 +3362,7 @@
         <v>225</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G42" s="5" t="s">
         <v>307</v>
@@ -3382,62 +3377,62 @@
       <c r="M42" s="5"/>
       <c r="N42" s="7"/>
       <c r="O42" s="7"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="5"/>
+      <c r="P42" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q42" s="5">
+        <v>1.06</v>
+      </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A43" s="5">
-        <v>1</v>
+      <c r="A43" s="10">
+        <v>0</v>
       </c>
       <c r="B43" s="5"/>
-      <c r="C43" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="G43" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="H43" s="5"/>
-      <c r="I43" s="5"/>
-      <c r="J43" s="5"/>
+      <c r="C43" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="G43" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="H43" s="10"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
       <c r="K43" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="L43" s="5"/>
-      <c r="M43" s="5"/>
-      <c r="N43" s="7"/>
-      <c r="O43" s="7"/>
-      <c r="P43" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q43" s="5">
-        <v>2.0099999999999998</v>
-      </c>
+      <c r="L43" s="10"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="11"/>
+      <c r="O43" s="11"/>
+      <c r="P43" s="10"/>
+      <c r="Q43" s="10"/>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A44" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G44" s="5" t="s">
         <v>307</v>
@@ -3467,10 +3462,10 @@
         <v>50</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G45" s="5" t="s">
         <v>307</v>
@@ -3485,8 +3480,12 @@
       <c r="M45" s="5"/>
       <c r="N45" s="7"/>
       <c r="O45" s="7"/>
-      <c r="P45" s="5"/>
-      <c r="Q45" s="5"/>
+      <c r="P45" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q45" s="5">
+        <v>1.07</v>
+      </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46" s="5">
@@ -3494,16 +3493,16 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G46" s="5" t="s">
         <v>307</v>
@@ -3533,10 +3532,10 @@
         <v>50</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G47" s="5" t="s">
         <v>307</v>
@@ -3566,10 +3565,10 @@
         <v>50</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G48" s="5" t="s">
         <v>307</v>
@@ -3584,12 +3583,8 @@
       <c r="M48" s="5"/>
       <c r="N48" s="7"/>
       <c r="O48" s="7"/>
-      <c r="P48" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q48" s="5">
-        <v>1.07</v>
-      </c>
+      <c r="P48" s="5"/>
+      <c r="Q48" s="5"/>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A49" s="5">
@@ -3603,10 +3598,10 @@
         <v>50</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G49" s="5" t="s">
         <v>307</v>
@@ -3630,16 +3625,16 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>87</v>
+        <v>316</v>
       </c>
       <c r="G50" s="5" t="s">
         <v>307</v>
@@ -3654,8 +3649,12 @@
       <c r="M50" s="5"/>
       <c r="N50" s="7"/>
       <c r="O50" s="7"/>
-      <c r="P50" s="5"/>
-      <c r="Q50" s="5"/>
+      <c r="P50" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q50" s="5">
+        <v>1.08</v>
+      </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A51" s="5">
@@ -3669,10 +3668,10 @@
         <v>50</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G51" s="5" t="s">
         <v>307</v>
@@ -3702,10 +3701,10 @@
         <v>50</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>232</v>
+        <v>359</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>89</v>
+        <v>351</v>
       </c>
       <c r="G52" s="5" t="s">
         <v>307</v>
@@ -3735,10 +3734,10 @@
         <v>50</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>318</v>
+        <v>88</v>
       </c>
       <c r="G53" s="5" t="s">
         <v>307</v>
@@ -3753,12 +3752,8 @@
       <c r="M53" s="5"/>
       <c r="N53" s="7"/>
       <c r="O53" s="7"/>
-      <c r="P53" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q53" s="5">
-        <v>1.08</v>
-      </c>
+      <c r="P53" s="5"/>
+      <c r="Q53" s="5"/>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A54" s="5">
@@ -3766,16 +3761,16 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>346</v>
+        <v>232</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>340</v>
+        <v>89</v>
       </c>
       <c r="G54" s="5" t="s">
         <v>307</v>
@@ -3790,29 +3785,25 @@
       <c r="M54" s="5"/>
       <c r="N54" s="7"/>
       <c r="O54" s="7"/>
-      <c r="P54" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q54" s="5">
-        <v>2.02</v>
-      </c>
+      <c r="P54" s="5"/>
+      <c r="Q54" s="5"/>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A55" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B55" s="5"/>
       <c r="C55" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>347</v>
+        <v>235</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>341</v>
+        <v>92</v>
       </c>
       <c r="G55" s="5" t="s">
         <v>307</v>
@@ -3831,7 +3822,7 @@
         <v>311</v>
       </c>
       <c r="Q55" s="5">
-        <v>2.0299999999999998</v>
+        <v>1.0900000000000001</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.35">
@@ -3846,10 +3837,10 @@
         <v>50</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G56" s="5" t="s">
         <v>307</v>
@@ -3867,8 +3858,8 @@
       <c r="P56" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="Q56" s="5">
-        <v>1.0900000000000001</v>
+      <c r="Q56" s="14">
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.35">
@@ -3883,10 +3874,10 @@
         <v>50</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G57" s="5" t="s">
         <v>307</v>
@@ -3904,26 +3895,26 @@
       <c r="P57" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="Q57" s="14">
-        <v>1.1000000000000001</v>
+      <c r="Q57" s="5">
+        <v>1.1100000000000001</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A58" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B58" s="5"/>
       <c r="C58" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D58" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="G58" s="5" t="s">
         <v>307</v>
@@ -3938,12 +3929,16 @@
       <c r="M58" s="5"/>
       <c r="N58" s="7"/>
       <c r="O58" s="7"/>
-      <c r="P58" s="5"/>
-      <c r="Q58" s="5"/>
+      <c r="P58" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q58" s="5">
+        <v>1.1200000000000001</v>
+      </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A59" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5" t="s">
@@ -3953,10 +3948,10 @@
         <v>50</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G59" s="5" t="s">
         <v>307</v>
@@ -3971,8 +3966,12 @@
       <c r="M59" s="5"/>
       <c r="N59" s="7"/>
       <c r="O59" s="7"/>
-      <c r="P59" s="5"/>
-      <c r="Q59" s="5"/>
+      <c r="P59" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q59" s="5">
+        <v>1.1299999999999999</v>
+      </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A60" s="5">
@@ -3986,10 +3985,10 @@
         <v>50</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>214</v>
+        <v>237</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>51</v>
+        <v>95</v>
       </c>
       <c r="G60" s="5" t="s">
         <v>307</v>
@@ -4019,10 +4018,10 @@
         <v>50</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="G61" s="5" t="s">
         <v>307</v>
@@ -4037,16 +4036,12 @@
       <c r="M61" s="5"/>
       <c r="N61" s="7"/>
       <c r="O61" s="7"/>
-      <c r="P61" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q61" s="5">
-        <v>1.1100000000000001</v>
-      </c>
+      <c r="P61" s="5"/>
+      <c r="Q61" s="5"/>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A62" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B62" s="5"/>
       <c r="C62" s="5" t="s">
@@ -4056,10 +4051,10 @@
         <v>50</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="G62" s="5" t="s">
         <v>307</v>
@@ -4074,8 +4069,12 @@
       <c r="M62" s="5"/>
       <c r="N62" s="7"/>
       <c r="O62" s="7"/>
-      <c r="P62" s="5"/>
-      <c r="Q62" s="5"/>
+      <c r="P62" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q62" s="5">
+        <v>1.1399999999999999</v>
+      </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A63" s="5">
@@ -4089,10 +4088,10 @@
         <v>50</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G63" s="5" t="s">
         <v>307</v>
@@ -4112,7 +4111,7 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A64" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B64" s="5"/>
       <c r="C64" s="5" t="s">
@@ -4122,10 +4121,10 @@
         <v>50</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G64" s="5" t="s">
         <v>307</v>
@@ -4155,10 +4154,10 @@
         <v>50</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G65" s="5" t="s">
         <v>307</v>
@@ -4173,12 +4172,8 @@
       <c r="M65" s="5"/>
       <c r="N65" s="7"/>
       <c r="O65" s="7"/>
-      <c r="P65" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q65" s="5">
-        <v>1.1200000000000001</v>
-      </c>
+      <c r="P65" s="5"/>
+      <c r="Q65" s="5"/>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A66" s="5">
@@ -4192,10 +4187,10 @@
         <v>50</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G66" s="5" t="s">
         <v>307</v>
@@ -4214,7 +4209,7 @@
         <v>311</v>
       </c>
       <c r="Q66" s="5">
-        <v>1.1299999999999999</v>
+        <v>1.1499999999999999</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.35">
@@ -4229,10 +4224,10 @@
         <v>50</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G67" s="5" t="s">
         <v>307</v>
@@ -4251,7 +4246,7 @@
         <v>311</v>
       </c>
       <c r="Q67" s="5">
-        <v>1.1399999999999999</v>
+        <v>1.1599999999999999</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.35">
@@ -4293,16 +4288,16 @@
       </c>
       <c r="B69" s="5"/>
       <c r="C69" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D69" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G69" s="5" t="s">
         <v>307</v>
@@ -4321,25 +4316,25 @@
         <v>311</v>
       </c>
       <c r="Q69" s="5">
-        <v>1.1499999999999999</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A70" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B70" s="5"/>
       <c r="C70" s="5" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="D70" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="G70" s="5" t="s">
         <v>307</v>
@@ -4358,7 +4353,7 @@
         <v>311</v>
       </c>
       <c r="Q70" s="5">
-        <v>1.1599999999999999</v>
+        <v>2.0099999999999998</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.35">
@@ -4429,7 +4424,7 @@
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A73" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B73" s="5"/>
       <c r="C73" s="5" t="s">
@@ -4439,10 +4434,10 @@
         <v>50</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>225</v>
+        <v>340</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>106</v>
+        <v>334</v>
       </c>
       <c r="G73" s="5" t="s">
         <v>307</v>
@@ -4461,7 +4456,7 @@
         <v>311</v>
       </c>
       <c r="Q73" s="5">
-        <v>1.17</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.35">
@@ -4476,10 +4471,10 @@
         <v>50</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="G74" s="5" t="s">
         <v>307</v>
@@ -4509,10 +4504,10 @@
         <v>50</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="G75" s="5" t="s">
         <v>307</v>
@@ -4531,12 +4526,12 @@
         <v>311</v>
       </c>
       <c r="Q75" s="5">
-        <v>2.04</v>
+        <v>2.0299999999999998</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A76" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B76" s="5"/>
       <c r="C76" s="5" t="s">
@@ -4546,10 +4541,10 @@
         <v>50</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="G76" s="5" t="s">
         <v>307</v>
@@ -4568,7 +4563,7 @@
         <v>311</v>
       </c>
       <c r="Q76" s="5">
-        <v>2.0499999999999998</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.35">
@@ -4606,7 +4601,7 @@
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A78" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B78" s="5"/>
       <c r="C78" s="5" t="s">
@@ -4616,10 +4611,10 @@
         <v>50</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>349</v>
+        <v>319</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>343</v>
+        <v>317</v>
       </c>
       <c r="G78" s="5" t="s">
         <v>307</v>
@@ -4638,7 +4633,7 @@
         <v>311</v>
       </c>
       <c r="Q78" s="5">
-        <v>2.06</v>
+        <v>2.0499999999999998</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.35">
@@ -4742,23 +4737,23 @@
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A82" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B82" s="5"/>
       <c r="C82" s="5" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D82" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>283</v>
+        <v>343</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>155</v>
+        <v>337</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H82" s="5"/>
       <c r="I82" s="5"/>
@@ -4768,13 +4763,13 @@
       </c>
       <c r="L82" s="5"/>
       <c r="M82" s="5"/>
-      <c r="N82" s="16"/>
+      <c r="N82" s="7"/>
       <c r="O82" s="7"/>
       <c r="P82" s="5" t="s">
         <v>311</v>
       </c>
       <c r="Q82" s="5">
-        <v>2.0699999999999998</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.35">
@@ -4789,10 +4784,10 @@
         <v>50</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="G83" s="5" t="s">
         <v>307</v>
@@ -4911,23 +4906,23 @@
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A87" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B87" s="5"/>
       <c r="C87" s="5" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D87" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>240</v>
+        <v>283</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>98</v>
+        <v>155</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H87" s="5"/>
       <c r="I87" s="5"/>
@@ -4937,13 +4932,13 @@
       </c>
       <c r="L87" s="5"/>
       <c r="M87" s="5"/>
-      <c r="N87" s="7"/>
+      <c r="N87" s="16"/>
       <c r="O87" s="7"/>
       <c r="P87" s="5" t="s">
         <v>311</v>
       </c>
       <c r="Q87" s="5">
-        <v>1.18</v>
+        <v>2.0699999999999998</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.35">
@@ -6377,10 +6372,10 @@
         <v>50</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="G131" s="5" t="s">
         <v>307</v>
@@ -7208,7 +7203,7 @@
       <c r="M154" s="5"/>
       <c r="N154" s="16"/>
       <c r="O154" s="7" t="s">
-        <v>325</v>
+        <v>352</v>
       </c>
       <c r="P154" s="5"/>
       <c r="Q154" s="5"/>
@@ -7398,10 +7393,10 @@
       <c r="L159" s="5"/>
       <c r="M159" s="5"/>
       <c r="N159" s="16" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="O159" s="16" t="s">
-        <v>336</v>
+        <v>353</v>
       </c>
       <c r="P159" s="5"/>
       <c r="Q159" s="5"/>
@@ -7558,10 +7553,10 @@
       </c>
       <c r="M163" s="6"/>
       <c r="N163" s="7" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="O163" s="7" t="s">
-        <v>326</v>
+        <v>354</v>
       </c>
       <c r="P163" s="5"/>
       <c r="Q163" s="5"/>
@@ -7599,10 +7594,10 @@
       <c r="L164" s="5"/>
       <c r="M164" s="5"/>
       <c r="N164" s="7" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="O164" s="7" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="P164" s="5"/>
       <c r="Q164" s="5"/>
@@ -7685,7 +7680,7 @@
         <v>2.02</v>
       </c>
       <c r="N166" s="7" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O166" s="7"/>
       <c r="P166" s="5"/>
@@ -7728,7 +7723,7 @@
       </c>
       <c r="M167" s="6"/>
       <c r="N167" s="7" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="O167" s="7"/>
       <c r="P167" s="5"/>
@@ -7771,10 +7766,10 @@
       </c>
       <c r="M168" s="6"/>
       <c r="N168" s="7" t="s">
-        <v>317</v>
+        <v>355</v>
       </c>
       <c r="O168" s="7" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="P168" s="5"/>
       <c r="Q168" s="5"/>
@@ -7818,7 +7813,7 @@
         <v>1.02</v>
       </c>
       <c r="N169" s="7" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O169" s="7"/>
       <c r="P169" s="5"/>
@@ -7918,15 +7913,15 @@
         <v>0.625</v>
       </c>
       <c r="K172" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="L172" s="5"/>
       <c r="M172" s="5"/>
       <c r="N172" s="7" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="O172" s="7" t="s">
-        <v>328</v>
+        <v>357</v>
       </c>
       <c r="P172" s="5"/>
       <c r="Q172" s="5"/>
@@ -7961,17 +7956,17 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="K173" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="L173" s="5"/>
       <c r="M173" s="14">
         <v>2.08</v>
       </c>
       <c r="N173" s="7" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="O173" s="7" t="s">
-        <v>338</v>
+        <v>358</v>
       </c>
       <c r="P173" s="5"/>
       <c r="Q173" s="5"/>
